--- a/backend/src/crawler/data/raw_bmsce.xlsx
+++ b/backend/src/crawler/data/raw_bmsce.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F290"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,10 +415,13 @@
       <c r="E1" t="str">
         <v>crawled_at</v>
       </c>
+      <c r="F1" t="str">
+        <v>depth</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://bmsce.ac.in</v>
+        <v>https://bmsce.ac.in/home</v>
       </c>
       <c r="B2" t="str">
         <v>html</v>
@@ -430,595 +433,5721 @@
         <v>0</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-03-14T06:31:29.379Z</v>
+        <v>2026-03-19T18:34:50.133Z</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://bmsce.ac.in/assets/img/Slider/Admission_document_and_process_flow.pdf</v>
+        <v>https://bmsce.ac.in/home/Civil-Engineering-About</v>
       </c>
       <c r="B3" t="str">
-        <v>pdf</v>
+        <v>html</v>
       </c>
       <c r="C3" t="str">
-        <v>Admission Process Flow Procedure www.bmsce.ac.in For any query: 080-26614357 College E-mail ID Creation College official mail ID along with Password provided, keep it safely for future process. Photography Live photo is taken for ID card purpose KEA Admission card download Document Verification Process Candidate should take allotment copy from respected KEA portal for verification process Online Admission form process Candidate should fill required details in college portal and pay the college miscellaneous fee through online. Candidate should submit required documents in college along with a set of self attested copy. (Soft &amp; Hard Copy) admissionsupport@bmsce.ac.in Start Exit B.M.S. COLLEGE OF ENGINEERING (An Autonomous Institute, Affiliated to VTU, Belagavi) Step 1 Step 2 Step 3 Step 4 Step 5 ENGINEERING ADMISSIONS 2025-2026 B.M.S. COLLEGE OF ENGINEERING, BENGALURU (AUTONOMUS INSTITUTION UNDER VTU) C h e c k l i s t o f t h e O r i g i n a l D o c u m e n t s t o b e submitted by the Candidates selected through CET / at the time of verification of documents in the college DCET KEA Verifica_x0000_on Slip TH II PUC/12 STD. / Diploma (For DCET) Marks Cards A.Study Cer_x0000_ficate from previous College/ Ins_x0000_tute (Total 07 Years) B.Students allo_x0000_ed under RURAL / Kannada Medium QUOTA are required to submit 10 years cer_x0000_ficates Caste Cer_x0000_ficate in case of Reserved Category [ i.e., SC, ST &amp; OBC] and students admi_x0000_ed under SNQ Quota are required to submi_x0000_ed Income Cer_x0000_ficate compulsorily Transfer Cer_x0000_ficate Migra_x0000_on Cer_x0000_ficate shall be submi_x0000_ed by Non-Karnataka students and students who have passed their qualifying examina_x0000_on other than PU Board. Students allo_x0000_ed under SPECIAL CATEGORY QUOTA (i.e. NCC, Sports, PH, Defence candidates etc.,) are required to submit the relevant original cer_x0000_ficates &amp; students admi_x0000_ed under Hyderabad Karnataka Quota (371J), are required to submit the relevant original cer_x0000_ficates. [ Annexure - “A'' – Eligibility Cer_x0000_ficate &amp; Annexure - “B'' – Residience Cer_x0000_ficate] Recent Photos – 02 Nos. (Passport Size) Copy of AADHAAR CARD and any other documents if required CANDIDATES HAVE TO SUBMIT ORIGINALS OF ALL THE ABOVE DOCUMENTS FOR VERIFICATION ALONG WITH OF SELF TWO SETS ATTESTED XEROX COPIES. . STUDENTS ARE INFORMED TO KEEP SUFFICIENT COPIES OF NOTE : THE ABOVE DOCUMENTS WITH THEM AS THE ORIGINAL WILL BE SENT TO VTU FOR APPROVAL OF THEIR ADMISSION. Q ORIGINAL MARKS CARDS WILL BE RETURNED TO STUDENTS ONLY AFTER APPROVAL OBTAINED / U S N RECEIVED FROM V T U, BELAGAVI. COLOUR XEROX NOT ALLOWED INSIDE THE VERIFICATION CENTER ENGINEERING ADMISSIONS 2025-2026 B.M.S. COLLEGE OF ENGINEERING, BENGALURU (AUTONOMUS INSTITUTION UNDER VTU) Check list of the Original Documents to be submitted by the Candidates selected through at the time of verification of Management &amp; Comed-K documents in the college Seat Allotment Letter issued by Comed-K / Original Fee reciept issued by Management (04 Copies) . Please ensure that the candidate name and parent name should be printed as per SSLC / 10th STD. marks cards TH II PUC/12 STD. Marks Cards TH SSLC / 10 STD. Marks Cards [ for proof of Date of Birth] Transfer Cer_x0000_ficate Migration Certificate shall be submitted by Non-Karnataka students and students who have passed their qualifying examination other than PU Board. Students allotted through Comed-K under Hyderabad Karnataka Quota, are required to submit the relevant original certificates. [ Annexure - “A'' – Eligibility Certificate &amp; Annexure - “B'' – Residience Certificate] Rank Card of any one of the Competitive Examination i.e, CET/Comed-K / JEE of Current Year (i.e., 2025-26 ) in respect of Management Quota only Recent Photos – 02 Nos. (Passport Size) Copy of AADHAAR CARD and any other documents if required CANDIDATES HAVE TO SUBMIT ORIGINALS OF ALL THE ABOVE DOCUMENTS FOR VERIFICATION ALONG WITH OF TWO SETS SELF ATTESTED XEROX COPIES. STUDENTS ARE INFORMED TO KEEP SUFFICIENT COPIES NOTE : OF THE ABOVE DOCUMENTS WITH THEM AS THE ORIGINAL WILL BE SENT TO VTU FOR APPROVAL OF THEIR ADMISSION. a ORIGINAL MARKS CARDS WILL BE RETURNED TO STUDENTS ONLY AFTER APPROVAL OBTAINED / U S N RECEIVED FROM V T U, BELAGAVI COLOUR XEROX NOT ALLOWED INSIDE THE VERIFICATION CENTER B.M.S. COLLEGE OF ENGINEERING, BENGALURU (AUTONOMUS INSTITUTION UNDER VTU) ENGINEERING ADMISSIONS 2025-2026 GENERAL INSTRUCTIONS TO CANDIDATES Venue : CCP Lab – FOURTH FLOOR, PG BLOCK Step Step by Step Process Venue On-line entry of application Remittance of Fees On-Line / Indian Bank, BMSCE Campus 1. 2. 3. 4. 5. 6. 7. 8. 9. 10. 1. 2. 3. 4. 5. 6. 7. 8. 9. 10. 1. 2. 4. TH SSLC / 10 STD. Marks Cards [ for proof of Date of Birth] A. Study Cer_x0000_ficate from previous College/ Ins_x0000_tute B. Caste Cer_x0000_ficate in respect of students having score less than 45% in qualifying examina_x0000_on i.e.,II PUC/12TH Std Lunch Time: 01.00 PM to 02.00 PM 3. AT VERIFICATION CENTER [4th Floor] CCP LAB [4th Floor] CCP LAB [ 4th floor PG, BLOCK] Students are required to Submit all the original documents and Scan file along with name. The scan file should be in JPEG format only (200 DPI resolution) &amp; size should be less than 2MB and need to be submitted in the form of soft copy compulsorily. (Mobile scanned copy not allowed) Documents Verification &amp; submit Original Documents along with three sets of self-attested copies in respect of Comed-K &amp; Management Students and Two Sets of self-attested copies in respect of KEA Students (Colour xerox not allowed). WORKING HOURS Monday to Friday : 09.30 AM to 04.30 PM Saturdays : 09.30 AM to 01.30 PM College is remain closed on all Sundays and on Government Holidays. Process is supervised by : Prof. K Girish – Faculty of M C A People to be contacted: 1. Dr. Srinidhi Raghavan M ., (Assistant Professor, Dept. of Chemistry) In-charge of Document related issues. 2. Dr. H S Gururaja - (Faculty of CSBS) In-charge of Software related issues. Overall In-Charge of Admission Process Dr. Bheemsha Arya - Principal</v>
+        <v>About Dr. Sureka Naagesh Professor &amp; Head - Civil Engineering About Department Established in the year 1946, the Department of Civil Engineering at B.M.S College of Engineering has progressively achieved academic excellence, quality research and consultancy for over period of seven decades. The focus of the Department is to impart quality technical education in Civil Engineering holistically in order to meet professional challenges in the society with required competency. The Department receives grant from government of Karnataka and offers B.E, M.Tech and Ph.D programmes which are globally recognized. The undergraduate B.E program was accredited for 3 years under Tier-I (Washington Accord) in 2022, recognizing our academic achievements and is continuously accredited till date. PG programs are also accredited by NBA. The sanctioned intake for UG currently is 120 and 18 for PG in each program. From the year 2008, UG program was granted academic autonomy status from VTU, allowing to tailor our curriculum to cater for growth of knowledge, skills, and attitudes among students. With three postgraduate M.Tech programmes (Construction Technology, Environmental Engineering, and Transportation Engineering and Management,) the department has been a recognized VTU research centre since 2002. The Department is also recognized as AICTE QIP Research centre since 2012 and is AICTE ADF Research centre since 2018. This transformation elevated the department from primarily undergraduate department to a hub of research-based learning. As on date 46 candidates have acquired Ph.D from the research centre and 58 scholars are currently pursuing Ph.D and MSc (Engg.) in various domains. Our well qualified and expert team of faculty, comprising of 35 members currently, 28 of whom hold Ph.D. qualifications, contribute significantly to academic excellence. With Excellent support from college management and other funding agencies, including the World Bank-funded TEQIP, the state-of-the-art infrastructure and well equipped laboratory facilities reflects our commitment in providing a conducive learning environment. Faculties from various domains interact and work closely with industry for consultancy and projects which benefit young minds that join us. Adopting outcome based and project based learning methods, entrepreneurship and research we make students to graduate with multifaceted skill, and to tackle societal challenges so as to make meaningful contributions. With the assistance of our dedicated placement cell, students are placed in promising career opportunities. Supported by a robust Alumni network, Civil Engineering Department continues to inspire excellence in curricular co-curricular and extracurricular endeavours, making us a leading centre of learning. Department Profile « Established in 1946 as one of the founding branches of B. M. S. College of Engineering « Offers undergraduate, postgraduate, and research programs in Civil Engineering « Granted academic autonomy status by VTU in 2008, allowing for customized curriculum development « Offers three distinguished postgraduate courses in Construction Technology, Environmental Engineering, and Transportation Engineering and Management « Recognized as a research center by VTU and a QIP center by MHRD, emphasizing research-based learning « To date, our research center has produced 57 Ph.D. recipients, with an additional 58 dedicated scholars currently engaged in pursuing Ph.D. and MSc (Engg.) programs « Faculty comprises 35 members, with 28 holding Ph.D. qualifications « State-of-the-art infrastructure supported by funding agencies and management, including World Bank-funded TEQIP « UG programme accredited by the National Board of Accreditation under Tier-I (Washington Accord) in 2014 and 2022 « Focuses on practical learning, projects, and research, with an emphasis on industry placements, entrepreneurship, and global challenges Vision To be a center of excellence for imparting quality education in Civil Engineering with integrity and ethical standards for societal needs . Mission Accomplish Excellence in Civil Engineering through dedicated teaching, learning and Research to produce technically competent civil engineers to serve the society with pride.</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-03-14T06:31:30.475Z</v>
+        <v>2026-03-19T18:34:50.794Z</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>http://www.bmsce.ac.in/</v>
+        <v>https://bmsce.ac.in/home/Mechanical-Engineering-About</v>
       </c>
       <c r="B4" t="str">
         <v>html</v>
       </c>
       <c r="C4" t="str">
-        <v>View Document Seva Sindu Link Documents Required Know More ! News &amp; Events 09 Mar DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” read more 16 Feb Illuminating the Future: A Comprehensive Workshop on Indian Standards, Codes and Regulations in Lighting read more 05 Feb Sri S Nijalingappa Scholarship 2025-26 read more 14 Nov NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru on 14th and 15th November 2025 read more 19 Sep Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 read more View All Notifications COE Notifications Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25/03/2026. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), 2. Department of Machine Learning (AI &amp; ML), 3. MCA 4. Department of Mechanical Engineering 5. Department of Electronics &amp; Communication Engineering Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10th January 2026. Please refer to the advertisement for more details. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/12/2025. Teaching Application General Condition B.S. Narayan Doctoral Fellowship 2025-26. Last date for receipt of filled-in application form is 31st December 2025 link Admissions are Open for Management Quota seats for First Year PG Courses (M.Tech, MBA &amp; MCA) for 2025-26 at B. M. S. College of Engineering. Kindly contact the undersigned on or before 13th November 2025. Sd/- Principal Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10/11/2025. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Mathematics. Note: PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/10/2025 Teaching Application General Condition Application for Change Of Branch(COB) Circular for the Academic Year 2025-26 Download Circular for payment of Tuition and Miscellaneous Fee for 2nd Semester (MTech, MCA and MBA) for AY-2025-26 Download Circular for Fee Structure for 2nd Year B.E admitted through CET, COMEDK and Management Quota for AY-2025-26 Download View All Time Table for IV Semester Makeup Examination MBA- Mar-2026. read more Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. III Semester End Examinations conducted during Jan/Feb-26. read more Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. I, III Semesters and Reappear Semester UG Semester End Examinations conducted during Jan/Feb-26. read more Notification for Answer Scripts of I &amp; III Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure as per the attached schedule. read more Circular for makeup registration for I and III Semester March -2026 read more Addtional Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester MBA (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for I Semester M.Tech (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester Makeup Examination - Mar-2026. read more View All Late Sri. B.M.Sreenivasaiah Founder B.M.S. Educational Trust Late Sri. B.S.Narayan Donor Trustee B.M.S. Educational Trust The Visionaries B.M.S. College of Engineering (BMSCE) was Founded in the year 1946 by Late Sri. B. M. Sreenivasaiah a great visionary and philanthropist and nurtured by his illustrious son Late Sri. B. S. Narayan. BMSCE is the first private sector initiative in engineering education in India. BMSCE has completed 70+ years of dedicated service in the field of Engineering Education. Started with only 03 undergraduate courses, BMSCE today offers 13 Undergraduate &amp; 16 Postgraduate courses both in conventional and emerging areas. Know More Dr. Bheemsha Arya Principal, B.M.S.C.E A nation’s real and sustainable growth is possible with technological advancement as well as development of its human resource and the role of engineers is immensely pertinent. With globalization, engineers should be able to perform in a larger environment and are expected to face challenges &amp; find solutions in any given situation. The key to meet the demand for such quality engineers remains in providing holistic engineering education. Over the last 75 years, B.M.S.C.E has been offering best engineering programmes and is benchmarked with the leading educational institutions in the Country. Ever since its inception, B.M.S.C.E has focused on augmenting human resource by producing world-class engineers. Today, BMS Alumni occupy coveted positions in reputed organizations both in India and abroad. They have acted as the ambassadors of change. Magnanimous and committed College management has been regularly augmenting the academic/para-academic facilities at the college to suite the present day requirements. A cozy and well maintained campus provides good academic ambience. Well qualified &amp; experienced faculty and committed staff of the college are eager to provide effective education to students. In addition to gaining academic knowledge and skills, opportunities are many for the students to groom and develop further. View Profile B.M.S. College of Engineering BMSCE Alumni can be found all over the world. BMSCE takes proud in educating students since 1946 in various fields of Engineering and continues to provide world class education in the coming years with more emphasis on research and development. Values View More Research View More Placements View More Library View More Innovative Labs View More Accreditations and Rankings B.M.S. College of Engineering is determined to impart quality education to students and provide industry ready engineers for the country. To make this possible the college participates in several audits internally and externally for quality assurance with quality assurance committees and university committees from AICTE, VTU, NBA and NAAC. Know More Rankings / Surveys A++ in NAAC Third Cycle 83rd NIRF-2022 Ranking 8th among top 140 Eng8ineering in The Times Engineering Institute 2019 Survey 1st among top 50 Institutes on Placements in The Times Engineering Institute 2019</v>
+        <v>About Dr. H. M. Shivaprasad Associate Professor and Head - Department of Mechanical Engineering About Department Department of Mechanical Engineering was one of the three UG programs started in B.M.S. College of Engineering Bengaluru, in 1946. In the past seven decades, the department has seen lot of progress in academics, research and consultancy activities. The Department offers PG program, M. Tech. in Machine Design is started in 1985. Department has well experienced, qualified and dedicated faculties with multidisciplinary specialization. Both the programs are granted academic autonomy by VTU in the year 2008 that has enabled us to have our own curriculum to enable and empower the students with enhanced knowledge, skill sets and positive attitude. The UG program was first time accredited in the year 2004 for 3 years and process of accreditation journey continued. Further, UG program was accredited for 6 years by NBA, India under Tier-I (According to Washington Accord) in 2014, the first of its kind in the entire nation. Again, UG program was accredited for 6 years by NBA under Tier-I &amp; Cycle-II (According to Washington Accord) in 2022. PG program in Machine Design was accredited by NBA in 2018 for 5 years and an extension has been granted in 2023 for one more year (Up-to 2024). And is going for NBA accreditation in the month of DEC 2024. Department Profile Strengths of the Department  UG program of the department was accredited for 6 years by National Board of Accreditation (NBA), India under Tier-I &amp; Cycle-II (According to Washington Accord) in 2022.  PG program in Machine Design was accredited by NBA in 2018 for 5 years and an extension has been granted in 2023 for one more year (Up-to 2024).  Centre of Excellence in Advanced Materials Science was established to a tune of Six crore rupees sponsored under TEQIP-II in 2015.  Holds a good track record of around 80% placements in each academic year and good number of students opts for Higher studies through out the globe.  Product Innovation Lab is a industry initiative by Dassault Systemes (3DPLM), Pune in 2016.  BMSCE and Volvo group Centre for flexible material research is established in 2024.  A Well-equipped R&amp;D infrastructure available in Vibration and Noise Control domain.  Rs. 2.20 Crores received as R&amp;D project funding from various agencies i.e AICTE, DRDO (CVRDE, AR&amp;DB), DST, VGST, VTU RGS FINP-NIAS, TEQIP, Dassault Systemes ( La-foundation) for the past three years (2021-2024).  Rs. 0.36 Crores is generated as a consultancy service charges for the past three years (2021-2024).  UG program was accredited for 6 years by NBA, India under Tier-I (According to Washington Accord) in 2014, the first of its kind in the entire nation.  PG program in Machine Design for 5 years in the year 2018 and Manufacturing Science for 3 years in the year 2019 were accredited by NBA.  Department is recognized as a Research Centre by VTU QIP Centre by MHRD as well as NDF Centre.  49 well qualified faculty members, of which 35 have earned Ph.D. from top ranked institutions of India and abroad.  On an average, 40 research publications per year is published in reputed journals.  47 PhDs are produced till 2021 and currently 34 candidates are pursuing their Ph.D. and M.Sc. (Engg.) in research. Vision To become a center of excellence in educating students to become successful Mechanical Engineers. Mission M1. To empower the students with the fundamentals for a successful career in the field of Mechanical engineering. M2. To continue their education through post-graduation, Research &amp; Development. M3. To provide service to the society.</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-03-14T06:31:32.615Z</v>
+        <v>2026-03-19T18:34:51.446Z</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://bmsce.ac.in/home/AllNews</v>
+        <v>https://bmsce.ac.in/home/Electrical-and-Electronics-Engineering-About</v>
       </c>
       <c r="B5" t="str">
         <v>html</v>
       </c>
       <c r="C5" t="str">
-        <v>HomeHomeHome # Date News / Event Actions 1.09-03-2026DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” Read more2.16-02-2026Illuminating the Future: A Comprehensive Workshop on Indian Standards, Codes and Regulations in Lighting Read more3.05-02-2026Sri S Nijalingappa Scholarship 2025-26 Read more4.14-11-2025NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru on 14th and 15th November 2025 Read more5.19-09-2025Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 Read more6.08-09-2025Induction and Inauguration for the 2025 Batch of Students Event is on September 8th 2025 Read more7.05-04-2025Graduation Day - IIAwarding Degree Certifcates to the Autonomous Batch UG &amp; PG Graduates of 2024 on Saturday, 05th April 2025 at 4.30 PM Read more8.21-03-2025Reg-Blood Donation Drive Read more9.05-03-2025IP awareness talk on 12th March 2025 Read more10.01-02-2025Grand challenge impact Lab (GCIL) with university of Washington : Sessions Read more11.16-01-2025UDYAMOTSAV 2025 - On Thursday 16th January 2025 at 9 AM in Auditorium I, PJ Block, BMSCE Read more12.17-12-202411th Annual Alumni Day -2024 on Saturday, 21st December, 2024. Read more13.17-09-2024B.M.S. College of Engineering and B.M.S. College of Architecture Cordially invites you to "Inauguration Function of First Year B.E., &amp; B.Arch for the Academic year 2024-25 on Friday 20th September 2024. Read more14.30-07-2024Department of Civil Engineering is organising a One Week Hands-On Faculty Development Programme on “BIM Application in Civil Engineering and Construction” 29-7-2024 to 2-8-2024 Read more15.16-07-2024The Department of Computer Applications, in collaboration with the Indian Society for Technical Education (ISTE), is organizing a One Week Faculty Development Program (FDP) on DevOps. The FDP will be held in Online mode from 29th July 2024 to 03rd August 2024. Read more16.21-04-2024IEEE INTERNATIONAL CONFERENCE ON EMERGING TECHNOLOGIES IN COMPUTER SCIENCE FOR INTERDISCIPLINARY APPLICATIONS (ICETCS 2024), 22nd -23rd April 2024 Read more17.19-03-2024State-Level Wheel Chair Cricket Tournament Date: March 23, 2024. Read more18.01-02-2024First IEEE International Conference on Communications and Computer Science-2024 (InCCCS-2024) 22nd – 24th May, 2024 Read more19.12-01-2024Department of Mechanical Engineering is organising a FDP on "Latest Trends in Additive Manufacturing" from 29 January to 2 February, 2024. Read more20.27-12-2023ATAL sponsored FDP is organized from Dept. of EEE, BMSCE during 29th Jan 2024 to 3rd Feb 2024. Read more21.20-12-2023Department of Electronics and Instrumentation Engineering, conducting A one day Tech Summit “ TechSolstice ” on 21 December 2023 (Thursday) at BMSCE, Auditorium 1, Platinum Jubilee Academic Block Read more22.15-12-202310th Annual Alumni Day 2023. Read more23.15-11-2023Department of EEE in association with EEEA, invited talk on “Internship Opportunities at IISc” on 17 November 2023 (Friday),3pm at Auditorium 2. Read more24.26-10-2023" Award of 100 5G use case Labs to to selected academic institutions was held by Hon'ble Prime Minister Shri. Narendra Modiji on 27th October 2023 as part of Indian Mobile Congress, 2023 Read more25.06-06-2023Department of Electronics and Instrumentation Engineering, presents a one day workshop on ADFT-2023,'' Antenna design, Fabrication and testing workshop", on 16th June 2023 (Friday) at Auditorium 1,PJAB , BMSCE. Read more26.06-05-2023Faculty development programme on "Current Trends in Material Physics for Engineering Applications" by the Department of Physics from 15-05-2023 to 19-05-2023. Read more27.27-04-2023Department of EEE is organising an FDP in blended mode on "Modelling and Design of Power Converters-Hands-On '' from 15th May to 19th May 2023. Read more28.20-04-2023Department of Computer Science and Engineering &amp; Department of Medical Electronics organizing one week FDP/SDP on “Bio-Medical Signal Acquisition and Analysis " 24th April 2023 to 28th April 2023 Read more29.28-03-2023Department of Electronics and Instrumentation Engineering Organizing “IACT 2023” (ISA Bangalore Automation and Control Technology day) on 31st March (Friday) and 1 April, (Saturday) 2023 Read more30.12-01-2023Department of Computer Applications organizes Two Weeks Value Added Program on “Augment Reality” in Blended mode Date: 18th January 2023 to 31th January, 2023 Read more31.11-01-2023The NSS UNIT in collaboration with NCC UNIT, Civil Defence Corps and Leo Satva of BMSCE is organizing a Blood Donation Camp in association with Jayadeva Hospital, Kidwai Memorial Institute of Oncology and BMST Rotary on 12/01/2023. Read more32.01-12-2022Annual Alumni day -2022 and Alumni Sports Day- 2022 Read more33.01-12-2022International Conference on Data, Decision and Systems (ICDDS) 2022 - 2nd and 3rd of December, 2022. Read more34.12-11-2022Inauguration of First Year Induction Program on 13.11.2022 @ 11 AM Read more35.08-11-2022Department of Computer Science and Engineering and BMSCE IEEE SB in association with is conducting a value added course on "Problem Solving and Working with HackerRank Platform" from 11th to 15th November 2022 Read more36.12-10-2022IEEE Power and Energy Society Bangalore Chapter in collaboration with BMSCE IEEE PES and Sensors Council presents Young Researchers' Meet 2022* on 4th and 5th November 2022 Read more37.22-08-2022IEEE IC SCT in collaboration with BMSCE IEEE SB presents, ICHACK'22 - A Student Run Hackathon! This is your opportunity to show-off your technical skills at National Level - 3rd &amp; 4th September 2022 Read more38.22-08-2022IEEE India Council in collaboration with BMSCE IEEE SB and BMSCE IEEE CS presents to you "SCYTALE - Lost In The Abyss Of Time", an 18-hour online cryptic hunt on 27 August, 2022 @ 9 PM Read more39.09-08-2022To upload selfie with flag on website www.harghartiranga.com and use official hashtag#harghartiranga for social media promotions Read more40.24-07-2022Technical fest BMSCE- SRISHTI July 25-27, 2022 Read more41.15-07-2022National Level Seminar on “Digital Transformations under NEP 2020” on 15-07-2022 Read more42.22-07-2022BMSCE Alumni Network is pleased to invite the batch of 2021, 2020 and 2019 students for their Graduation Day. on 22nd and 23rd July 2022 Read more43.08-07-2022“Sensing and Related Technologies for the Grand Challenges of the 21st Century: Climate, Energy, Water, Food, Health and Mega-Cities” is scheduled from 11th July to 22nd July 2022, Read more44.02-07-2022One day National conference on "Additive Manufacturing in Aerospace, Defence (AMAD-2022) &amp; Other Engineering Sectors (In Online Mode)" Co-hosted by the Department of Mechanical Engineering,BMSCE on 2nd July(Saturday) at 9.15 A.M. Read more45.16-06-2022Department of Electronics &amp; Communication Engineering in Association with IETE is organizing Fifth National Conference on Networking, Embedded and Wireless Systems-NEWS-2022 which will be held during October 12th -14th, 2022. Read more46.16-06-2022 BMSCE IEEE Computer Society in collaboration with the IEEE Computer Society Bangalore - an intercollegiate hackathon - GirlGeeksHack 2022 on the 18th and 19th of June, 2022. Read more47.04-06-2022Department of EEE is organizing a Two weeks online Value Added Course on VLSI, Verilog and Image Processing - 6th June 2022 to 18th June 2022 Read more48.09-05-2022The Department of Computer Applications, BMSCE is organizing a Two-week Online Value Added Course on "Python for Data Science" from 16th to 27th May, 2022 Read more49.02-05-2022Department of ISE, Student's Club, BMSCE in association with IEEE student's Chapter and BMSCEAN is organizing a 30 hrs hand-on value added course on "Kubernetes for Beginners" from 4th May, 2022 in blended Mode Read more50.16-04-2022Two Week Value Added Course on "Python Programming" from 18th to 29th April, 2022 Read more51.26-03-2022Department of EEE (EEE Association) and BMSCE IEEE PES and Sensors Council present ENERGY SWARAJ YATRA Talk by Prof. Chetan Singh Solanki on 28th March 2022 from 2:00 PM Read more52.24-03-2022Interactive contents development enabling the better presentation of fluid mechanics and hydraulic engineering concept in engineering education Read more53.21-03-2022Two weeks Value Added Program on Introduction to Python and LaTeX Programming 28th March, 2022 to 8th April, 2022 Read more54.19-03-2022Two week Value Added course on Modelling, Simulation, Robotics &amp; Automation - March 21st to 1st April 2022 Read more55.12-03-2022Department of Information Science and Engineering is organizing VGST Sponsored Five Day Faculty Development Program on “Machine Learning and Deep Learning with Python” from 14th to 18th March 2022. Read more56.18-02-2022GIAN course "Modeling and Simulation of Turbulence" in collaboration with the Department of Mechanical Engineering during March 25-29th,2022 Read more57.20-01-2022Department of Civil Engineering is organizing an AICTE Training and Learning (ATAL) Academy sponsored Online Faculty Development Program (FDP) on "Carbon Balance and Environmental Sustainability",CBES-2022 during 7th-11th February 2022. Read more58.29-11-2021UG/PG Online Admission Registration for the AY 2021-22 (CET/COMED-K/MGT/GOI/PMSS/PIO/ DCET/PGCET) Read more59.25-11-2021BMSCE PHASE SHIFT 2021 - November 26-27,2021 Read more60.13-11-2021Two-Days WORKSHOP ON IMPLEMENTATION OF NEP 2020 15.11.2021 and 16.11.2021 Read more61.06-11-2021International Conference on Power, Control and Sustainable Energy Systems 28th – 30th JULY 2022. Read more62.24-09-2021Virtual Education Series - Industry 4.0 Real Life Implementation Case Studies 25th September 2021 Saturday - 11:30 am to 01.30 pm Read more63.20-09-2021One week online FDP program on " Recent Advances in CFD &amp; Its Applications" from 27th to 01st October 2021 Read more64.09-09-2021Analog Signal Processing Concepts using Python - 15th to 30th September 2021. Read more65.02-09-20212 Week online Internship on Simulation Tools for Engineering Applications - 6th - 18th September 2021 Read more66.02-09-2021Virtual Series of Lectures on 'Digital Transformation' in Industries for students. Read more67.24-08-2021AICTE Invites all students and faculty to observe 30th August to 4th September as YuWaah Echoes – by Young Warrior filled with knowledge sessions, talks, presentations, competitions and challenges. Read more68.23-08-2021Two week online Internship on MULTISIM between 23-08-2021 and 04-09-2021. Read more69.21-08-2021Python Bootcamp. A 36 Hour Learn-A-Thon starts at 11:00 am on the 28th of August 2021. Read more70.28-06-2021Hands-on Workshop on " Up &amp; Running in AWS" Saturdays ( 03/07/2021, 10/07/2021, 17/07/2021 and 24/07/2021) from 2:00 PM to 4:30 PM.) Read more71.27-05-2021Online 24-hour Hackathon - "Ode to Code" on 5th June 2021 (Saturday) organized by CSE, BMSCE in association with Riskcovry Read more72.19-02-2021International Conference on Operations Management, Systems &amp; Business Analytics (COMSB) on 26th March 2021 Read more73.10-02-2021Talk by Padma Sri Dr. Sudha Murty, Chairperson of Infosys Foundation a Prolific Writer and Social Worker to address the 75th batch of Engineering students on 12.02.2021 at 11.00 AM. Read more74.09-02-2021One week online STTP on " REO-AMST-2021”, “Renewable Energy options in developing countries with Advanced Materials and Scientific Tools " from 8th to 13th March , 2021. Read more75.05-02-2021One Week Faculty Development Program (FDP) on Functional Materials for Engineering Applications -15-02-2021 to 19-02-2021 Read more76.22-01-2021VETOMAC - XVI 16th International Conference on Vibration Engineering and Technology of Machinery on 16–18 December 2021. Read more77.21-01-2021Level One C Programming Bootcamp, is being conducted by the department of CSE and ECE, for the first-year UG students on the 23rd and 24th of January 2021.” Read more78.13-01-2021JustVend: Smart App based vending machine developed by BMS students. Read more79.07-01-2021Department of Mathematics and Humanities is organizing a Two-Days Webinar on Skill-set and Stress Management on 11th &amp; 12th, January 2021 from 5.00 to 6.30 PM Read more80.02-01-2021Blockchain &amp; Decentralized Application Development (Hands-on)" from 27th January to 2nd February 2021 Read more81.29-12-2020Inauguration of Techbarath Hackthon 2021 0n 30-12-2020 @ 3 PM Read more82.02-12-2020UG/PG Online Admission Registration for the AY 2020-21 (CET/COMED-K/MGT/GOI/PMSS/PIO/DCET/PGCET) Read more83.21-11-2020Two day online Workshop for faculties on Virtual Lab - 23.11.2020 and 24.11.2020 Read more84.01-10-2020Implementation Plan on NEP 2020 on MyGov portal seeking suggestions/feedbacks-Date Extended 31.10.2020 Read more85.09-09-2020FDP on AICTE- ATAL on Waste Technologies - Wealth From Waste from 23 to 27th November 2020 Read more86.01-09-2020One week Online Value-added Course on "Emerging Technologies: Industry Perspectives" from 4th to 10th September 2020 Read more87.02-09-2020Webinar on Cross Platform Mobile App Development Webinar - 08/09/2020 @ 11.30 am Read more88.29-08-2020AICTE Training And Learning (ATAL) Academy Online Faculty Development Programme (FDP) On “Prospects and Challenges in 3D Printing: A Design Perspective” -01/09/2020 to 05/09/2020 Read more89.22-08-2020IEEE-SSIT-ES Joint Chapter Bangalore Section is Organizing an Online Lecture on “Sociological, Psychological Issues and Possible Remedies During COVID-19” on 29/08/2020 at 11AM Read more90.06-08-2020Value-added Course on "Challenges and Opportunities in the Semiconductor Industry" from 10th to 14th August 2020 Read more91.05-08-2020Guest Lecture on National Education Policy 2020 - from the perspective of Higher Education - 05/08/2020 @ 2.30 pm Read more92.01-10-2020Admissions for MBA Programme for the Academic Year 2020-21 - Reg Read more93.29-07-2020One week Faculty Development Programme on Python Programming - 24th to 29th August, 2020 Read more94.25-07-2020IEEE Online Hands-on Workshop on “Simulation tools for Power converters and applications”. - 27th to 31st July 2020 Read more95.16-07-2020FDP on "IoT and Data Analytics: an End to End perspective" from 27th July to 1st Aug 2020 Read more96.13-07-2020One week online FDP on "MATLAB for Mechanical Engineers" from 20th to 24th of July 2020 Read more97.01-09-2020Admissions to B.E. Degree Program in Artificial Intelligence and Machine Learning Read more98.02-07-2020Protocol Club is organizing Protocol Day 2020 from 4th July 2020 to 5th July 2020. Read more99.01-07-2020WEBINAR on "Civil Services As a Career Option", Wednesday , 1st July 2020 at 5:30 PM - 7:00 PM Read more100.02-07-2020Two-Week Online FDP on "Applied Data Science" from 6th to 17th July 2020 Read more101.30-06-2020"Recent Advances in Heat Transfer and Its Applications" - 13th to 17th July 2020. Read more102.29-06-2020ONE WEEK Online FDP On "Climate change and Carbon Issues" from " 6th July to 10th July 2020" Read more103.25-06-2020One Week Online FDP on "GREEN ENERGY" from JUNE 29th to JULY 4th, 2020. Read more104.20-06-2020Enhancement of curriculum through CDIO on 24th and 25th June 2020 Read more105.12-06-2020One - Week Online FDP on Structural Health Monitoring and its Implications -- 15th -19th June 2020 Read more106.10-06-2020BMSCE Hackathon: Beat the Pandemic (June 5 to 7, 2020) Read more107.26-05-2020BMSCE Hackathon:Building effective solution to win battle against COVID19 - 5th to 7th June,2020. Read more108.26-05-2020Webinar on “Three Amigos: Mouse clicks, Humans and Threats” on 28 May 2020 from 4.30 to 6.00 PM Read more109.07-05-2020Duration of MCA Program as per AICTE Approval Hand Book 2020-21 Read more110.12-05-2020Young Professional Program to infuse fresh and young talent in its incubator at IIT Kanpur Read more111.11-05-2020PUBLIC NOTICE on REDRESSAL OF GRIEVANCES RELATED TO COVID-19 Read more112.08-05-2020Urgent Circular- Live QnA session of VCs and Principals/Directors of TEQIP Institutions with Guruji Sri Sri Ravishankar Tommorow- May 9th,2020 11:30 AM-reg Read more113.06-05-2020edX Remote Access Program at BMSCE Read more114.24-04-2020Coursera at B.M.S. College of Engineering - Free registration and Certification Read more115.06-03-2020International Women's Week 2020 - Activities from 6th March to 10th March 2020. Read more116.17-02-2020National Science Day events from 17th Feb. 2020 to 28th Feb. 2020 Read more117.12-02-2020B.M.S College of Engineering in association with Mitsubishi Electric India is organizing a mega event, the 5th Edition of Mitsubishi Electric Cup 2020, a National Level Competition for Factory Automation on 14th and 15th February 2020 (Friday and Saturday). Read more118.25-01-2020Schedule of Induction Program for First B.E.Students 2019-2020, Phase-II - 27/01/2020 to 01/02/2020. Read more119.09-01-2020"Machine Learning and Deep Learning with Python" - 20/01/2020 to 24/01/2020 Read more120.01-01-2020Recent trends in Deep learning and its applications - 21/01/2020 to 25/01/2020 Read more121.21-12-2019IEEE International Conference on Mainstream Block Chain Implementation (ICOMBI) Read more122.14-10-2019BMSCE - Dassault Systems La Fondation Academic Partnership Read more123.23-08-2019Two day’s National Symposium Read more124.04-08-2019Inaugural function of commencement of First Year B.E. &amp; B.Arch - 2019-20 Read more125.22-07-2019One week FDP on 'Contact and Non-Contact Measurements' Read more</v>
+        <v>About Dr.R .S. Geetha Professor and Head - Department of Electrical and Electronics About Department The Department of Electrical Engineering was established in 1946 and subsequently emerged as Department of Electrical and Electronics Engineering. The Department has the distinction of having its graduates known worldwide for their contributions and accomplishments in varied domains. It nurtures a tradition of providing a free, at the same time an encouraging and motivating environment conducive to an effective learning experience beyond the curriculum. The focus of the department is to equip students with capabilities through a wide exposure to all aspects facilitating their development as professionals. This enables them to adapt to the societal needs and the progressive technological requirements. The students are selected for jobs in the industry through campus as well as off campus placements. They are also encouraged to pursue higher studies in India as well as abroad. The students and faculty of the department receive support and encouragement from its alumni and guidance from experts from premier institutions and industry. Their academic performance is rewarded through meritorious scholarships constituted by alumni and past Professors. Collaborative projects and activities are taken up from time to time. The students are well known for their zeal and enthusiasm to organize and participate in professional society activities. The history of taking the lead in organizing several Technical symposia such as Blitzkrieg, E^3, Phase shift, National and international Conferences are testimony to this fact. Department Profile The Department receives grants from Govt. of Karnataka and offers an undergraduate program B.E, Electrical and Electronics, with a sanctioned intake of 60. The department is NBA Accredited under Tier I of Washington Accord and has a Student Faculty Ratio of 16:1. The department offers M.Tech, program in Power Electronics which started in 1991 with a sanctioned intake of 18 which is also NBA Accredited. It has a research Centre under VTU since 2003. It is a recognized AICTE QIP Research Centre since 2012, AICTE NDF (National Doctoral Fellowship Scheme) Research centre since 2018. The number of awarded Ph.Ds till date is 16 and currently 30 research scholars are pursuing their research in various domains. The department has dedicated faculty with a wide spectrum of specialization such as, Power Systems, Power Electronics and Drives, Renewable Energy, HVDC, Power Quality, Nano Technology, High Voltage and Insulation Diagnostics and Phase Change Memory Materials. Department is accredited by NBA(Washington accord) for UG Program for 3 years under TIER-1 from 2022-2025. Department is accredited by NBA(Washington accord) for PG Program for 3 years from 2023-2026. Vision Facilitating the development of competent professionals capable of adapting to the constantly changing global scenario in the field of Electrical Sciences. Mission Impart quality technical education and encourage research in the field of Electrical Sciences. Empower every individual to develop as a professional with an ability to apply his/her knowledge and skills to adapt to the evolving technological requirements of society.</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-03-14T06:31:33.572Z</v>
+        <v>2026-03-19T18:34:52.117Z</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>https://bmsce.ac.in/home</v>
+        <v>https://bmsce.ac.in/home/Electronics-and-Communication-Engineering-About</v>
       </c>
       <c r="B6" t="str">
         <v>html</v>
       </c>
       <c r="C6" t="str">
-        <v>View Document Seva Sindu Link Documents Required Know More ! News &amp; Events 09 Mar DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” read more 16 Feb Illuminating the Future: A Comprehensive Workshop on Indian Standards, Codes and Regulations in Lighting read more 05 Feb Sri S Nijalingappa Scholarship 2025-26 read more 14 Nov NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru on 14th and 15th November 2025 read more 19 Sep Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 read more View All Notifications COE Notifications Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25/03/2026. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), 2. Department of Machine Learning (AI &amp; ML), 3. MCA 4. Department of Mechanical Engineering 5. Department of Electronics &amp; Communication Engineering Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10th January 2026. Please refer to the advertisement for more details. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/12/2025. Teaching Application General Condition B.S. Narayan Doctoral Fellowship 2025-26. Last date for receipt of filled-in application form is 31st December 2025 link Admissions are Open for Management Quota seats for First Year PG Courses (M.Tech, MBA &amp; MCA) for 2025-26 at B. M. S. College of Engineering. Kindly contact the undersigned on or before 13th November 2025. Sd/- Principal Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10/11/2025. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Mathematics. Note: PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/10/2025 Teaching Application General Condition Application for Change Of Branch(COB) Circular for the Academic Year 2025-26 Download Circular for payment of Tuition and Miscellaneous Fee for 2nd Semester (MTech, MCA and MBA) for AY-2025-26 Download Circular for Fee Structure for 2nd Year B.E admitted through CET, COMEDK and Management Quota for AY-2025-26 Download View All Time Table for IV Semester Makeup Examination MBA- Mar-2026. read more Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. III Semester End Examinations conducted during Jan/Feb-26. read more Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. I, III Semesters and Reappear Semester UG Semester End Examinations conducted during Jan/Feb-26. read more Notification for Answer Scripts of I &amp; III Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure as per the attached schedule. read more Circular for makeup registration for I and III Semester March -2026 read more Addtional Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester MBA (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for I Semester M.Tech (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester Makeup Examination - Mar-2026. read more View All Late Sri. B.M.Sreenivasaiah Founder B.M.S. Educational Trust Late Sri. B.S.Narayan Donor Trustee B.M.S. Educational Trust The Visionaries B.M.S. College of Engineering (BMSCE) was Founded in the year 1946 by Late Sri. B. M. Sreenivasaiah a great visionary and philanthropist and nurtured by his illustrious son Late Sri. B. S. Narayan. BMSCE is the first private sector initiative in engineering education in India. BMSCE has completed 70+ years of dedicated service in the field of Engineering Education. Started with only 03 undergraduate courses, BMSCE today offers 13 Undergraduate &amp; 16 Postgraduate courses both in conventional and emerging areas. Know More Dr. Bheemsha Arya Principal, B.M.S.C.E A nation’s real and sustainable growth is possible with technological advancement as well as development of its human resource and the role of engineers is immensely pertinent. With globalization, engineers should be able to perform in a larger environment and are expected to face challenges &amp; find solutions in any given situation. The key to meet the demand for such quality engineers remains in providing holistic engineering education. Over the last 75 years, B.M.S.C.E has been offering best engineering programmes and is benchmarked with the leading educational institutions in the Country. Ever since its inception, B.M.S.C.E has focused on augmenting human resource by producing world-class engineers. Today, BMS Alumni occupy coveted positions in reputed organizations both in India and abroad. They have acted as the ambassadors of change. Magnanimous and committed College management has been regularly augmenting the academic/para-academic facilities at the college to suite the present day requirements. A cozy and well maintained campus provides good academic ambience. Well qualified &amp; experienced faculty and committed staff of the college are eager to provide effective education to students. In addition to gaining academic knowledge and skills, opportunities are many for the students to groom and develop further. View Profile B.M.S. College of Engineering BMSCE Alumni can be found all over the world. BMSCE takes proud in educating students since 1946 in various fields of Engineering and continues to provide world class education in the coming years with more emphasis on research and development. Values View More Research View More Placements View More Library View More Innovative Labs View More Accreditations and Rankings B.M.S. College of Engineering is determined to impart quality education to students and provide industry ready engineers for the country. To make this possible the college participates in several audits internally and externally for quality assurance with quality assurance committees and university committees from AICTE, VTU, NBA and NAAC. Know More Rankings / Surveys A++ in NAAC Third Cycle 83rd NIRF-2022 Ranking 8th among top 140 Eng8ineering in The Times Engineering Institute 2019 Survey 1st among top 50 Institutes on Placements in The Times Engineering Institute 2019</v>
+        <v>About Dr. K. P. Lakshmi Professor and Head - Department of Electronics and Communication Engineering About Department The Department has a long tradition of excellence in educating, mentoring, and inspiring future technology leaders and researchers in the area of Electronics and Communication Engineering. The department offers undergraduate and post graduate programs and a recognized Research centre under the Quality Improvement Program (QIP) of the Government of India where the students are involved in Industry collaborative Research, Consultancy and State of Art Labs which contributes to the social betterment. To achieve this, our curriculum provides a strong foundation in both the analytic and technological aspects of E&amp;C Engineering and explore internship opportunities in industry and world-class universities. The department caters to Outcome based Education which help our students to learn, develop, and lead lives of impact. Faculty who are very passionate about teaching are also involved in a number of research projects independently and in collaboration with industry and other renowned Research organisations. Students are provided with ample opportunities to work on projects, skill development apart from regular curriculum, encourage taking part in national / international design contest / tests / quiz, in order to make them competitive and industry ready. The major goal of the Department is to cater the holistic development of a student with a conducive Learning Environment. Department Profile The department of Electronics and Communication Engineering (ECE) of BMSCE was established in 1971 with an initial intake of 60 students to the Under Graduate (UG) program and enhanced to an intake of 120 students from 1983, 180 students from 2018, 276 students from 2022,420 from 2024. The department offers three Postgraduate Programs “Electronics” from 1986, “Digital Communication Engineering” from 1996 with an intake of 18 students and 6 from 2024, “VLSI Design &amp; Embedded Systems” from 2014 with an intake of 24 students. The department is also a recognized Research Centre (RC) by VTU from 2002 and is a recognized Quality Improvement Program (QIP) center by the AICTE from 2011. With these activities on-hand, the overall objective of the department is to contribute significantly, to the realization of the Vision of BMSCE. The department has formalized this objective in terms of its own Program Vision and Mission which are in-line with the Vision and Mission of the college. Department was accredited by NBA (Washington accord) for 6 years under TIER-1 (cycle-1) from 2017-2023. Department is accredited by NBA (Washington accord) for 3 years under TIER-1 ( cycle -2) from 2023-2026. Vision To emerge as a center of academic excellence in electronics, communication and related domains through knowledge acquisition, knowledge dissemination and knowledge generation meeting global needs and standards. Mission Imparting quality education through state of the art curriculum, conducive learning environment and research with scope for continuous improvement leading to overall professional success.</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-03-14T06:31:34.503Z</v>
+        <v>2026-03-19T18:34:53.029Z</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>https://bmsce.ac.in/#CollegeNotifications</v>
+        <v>https://bmsce.ac.in/home/Industrial-Engineering-and-Management-About</v>
       </c>
       <c r="B7" t="str">
         <v>html</v>
       </c>
       <c r="C7" t="str">
-        <v>View Document Seva Sindu Link Documents Required Know More ! News &amp; Events 09 Mar DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” read more 16 Feb Illuminating the Future: A Comprehensive Workshop on Indian Standards, Codes and Regulations in Lighting read more 05 Feb Sri S Nijalingappa Scholarship 2025-26 read more 14 Nov NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru on 14th and 15th November 2025 read more 19 Sep Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 read more View All Notifications COE Notifications Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25/03/2026. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), 2. Department of Machine Learning (AI &amp; ML), 3. MCA 4. Department of Mechanical Engineering 5. Department of Electronics &amp; Communication Engineering Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10th January 2026. Please refer to the advertisement for more details. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/12/2025. Teaching Application General Condition B.S. Narayan Doctoral Fellowship 2025-26. Last date for receipt of filled-in application form is 31st December 2025 link Admissions are Open for Management Quota seats for First Year PG Courses (M.Tech, MBA &amp; MCA) for 2025-26 at B. M. S. College of Engineering. Kindly contact the undersigned on or before 13th November 2025. Sd/- Principal Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10/11/2025. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Mathematics. Note: PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/10/2025 Teaching Application General Condition Application for Change Of Branch(COB) Circular for the Academic Year 2025-26 Download Circular for payment of Tuition and Miscellaneous Fee for 2nd Semester (MTech, MCA and MBA) for AY-2025-26 Download Circular for Fee Structure for 2nd Year B.E admitted through CET, COMEDK and Management Quota for AY-2025-26 Download View All Time Table for IV Semester Makeup Examination MBA- Mar-2026. read more Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. III Semester End Examinations conducted during Jan/Feb-26. read more Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. I, III Semesters and Reappear Semester UG Semester End Examinations conducted during Jan/Feb-26. read more Notification for Answer Scripts of I &amp; III Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure as per the attached schedule. read more Circular for makeup registration for I and III Semester March -2026 read more Addtional Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester MBA (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for I Semester M.Tech (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester Makeup Examination - Mar-2026. read more View All Late Sri. B.M.Sreenivasaiah Founder B.M.S. Educational Trust Late Sri. B.S.Narayan Donor Trustee B.M.S. Educational Trust The Visionaries B.M.S. College of Engineering (BMSCE) was Founded in the year 1946 by Late Sri. B. M. Sreenivasaiah a great visionary and philanthropist and nurtured by his illustrious son Late Sri. B. S. Narayan. BMSCE is the first private sector initiative in engineering education in India. BMSCE has completed 70+ years of dedicated service in the field of Engineering Education. Started with only 03 undergraduate courses, BMSCE today offers 13 Undergraduate &amp; 16 Postgraduate courses both in conventional and emerging areas. Know More Dr. Bheemsha Arya Principal, B.M.S.C.E A nation’s real and sustainable growth is possible with technological advancement as well as development of its human resource and the role of engineers is immensely pertinent. With globalization, engineers should be able to perform in a larger environment and are expected to face challenges &amp; find solutions in any given situation. The key to meet the demand for such quality engineers remains in providing holistic engineering education. Over the last 75 years, B.M.S.C.E has been offering best engineering programmes and is benchmarked with the leading educational institutions in the Country. Ever since its inception, B.M.S.C.E has focused on augmenting human resource by producing world-class engineers. Today, BMS Alumni occupy coveted positions in reputed organizations both in India and abroad. They have acted as the ambassadors of change. Magnanimous and committed College management has been regularly augmenting the academic/para-academic facilities at the college to suite the present day requirements. A cozy and well maintained campus provides good academic ambience. Well qualified &amp; experienced faculty and committed staff of the college are eager to provide effective education to students. In addition to gaining academic knowledge and skills, opportunities are many for the students to groom and develop further. View Profile B.M.S. College of Engineering BMSCE Alumni can be found all over the world. BMSCE takes proud in educating students since 1946 in various fields of Engineering and continues to provide world class education in the coming years with more emphasis on research and development. Values View More Research View More Placements View More Library View More Innovative Labs View More Accreditations and Rankings B.M.S. College of Engineering is determined to impart quality education to students and provide industry ready engineers for the country. To make this possible the college participates in several audits internally and externally for quality assurance with quality assurance committees and university committees from AICTE, VTU, NBA and NAAC. Know More Rankings / Surveys A++ in NAAC Third Cycle 83rd NIRF-2022 Ranking 8th among top 140 Eng8ineering in The Times Engineering Institute 2019 Survey 1st among top 50 Institutes on Placements in The Times Engineering Institute 2019</v>
+        <v>About Dr. Shailaja V.N. Professor and Head - Department of Industrial Engineering and Management About Department The IEM department was established in 1979. The department has an intake of 60 students. The department offers undergraduate degree in Industrial Engineering and Management. It emphasizes thrust on productivity, management, and software engineering. The department houses suitable labs to give our students a competitive edge. It enables them to fit in as the key link between the technical personnel and the management in any organization and thus contribute to the organization’s growth and development including profitability. The department is VTU recognized research centre for PhD and M.Sc. Engineering degrees. The lab of the department houses top of the line computers to aid students in Robotics, CIM, CAD/CAM, ERP, Modeling, Drafting and Simulation. The department also has its own library and a student activity centre. The department forum is called as Industrial Engineering Club (INDEC). The department has 12 qualified staff out of them seven are doctorates in various Industrial Engineering areas. The students joining this department will be trained to perform in Engineering Management, Production and Software based Industry practices. It is also a QIP centre for pursuing PhD course in Industrial Engineering. Department Profile The IEM department was established in 1979. The department has an intake of 60 students. The department offers undergraduate degree in Industrial Engineering and Management. Vision To emerge as an excellent center for imparting quality higher education and generating highly proficient technical manpower to adopt to the constantly changing global scenario with professional and ethical values. Mission Providing excellent education in curricular, co- curricular and extra-curricular activities to students. Facilitating to continue their education through research activities Catering to the needs of the Industry and society. Nurturing and mentoring students to acceptance by stake holders</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-03-14T06:31:35.435Z</v>
+        <v>2026-03-19T18:34:53.674Z</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>https://bmsce.ac.in/#COENotifications</v>
+        <v>https://bmsce.ac.in/home/Computer-Science-and-Engineering-About</v>
       </c>
       <c r="B8" t="str">
         <v>html</v>
       </c>
       <c r="C8" t="str">
-        <v>View Document Seva Sindu Link Documents Required Know More ! News &amp; Events 09 Mar DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” read more 16 Feb Illuminating the Future: A Comprehensive Workshop on Indian Standards, Codes and Regulations in Lighting read more 05 Feb Sri S Nijalingappa Scholarship 2025-26 read more 14 Nov NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru on 14th and 15th November 2025 read more 19 Sep Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 read more View All Notifications COE Notifications Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25/03/2026. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), 2. Department of Machine Learning (AI &amp; ML), 3. MCA 4. Department of Mechanical Engineering 5. Department of Electronics &amp; Communication Engineering Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10th January 2026. Please refer to the advertisement for more details. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/12/2025. Teaching Application General Condition B.S. Narayan Doctoral Fellowship 2025-26. Last date for receipt of filled-in application form is 31st December 2025 link Admissions are Open for Management Quota seats for First Year PG Courses (M.Tech, MBA &amp; MCA) for 2025-26 at B. M. S. College of Engineering. Kindly contact the undersigned on or before 13th November 2025. Sd/- Principal Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10/11/2025. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Mathematics. Note: PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/10/2025 Teaching Application General Condition Application for Change Of Branch(COB) Circular for the Academic Year 2025-26 Download Circular for payment of Tuition and Miscellaneous Fee for 2nd Semester (MTech, MCA and MBA) for AY-2025-26 Download Circular for Fee Structure for 2nd Year B.E admitted through CET, COMEDK and Management Quota for AY-2025-26 Download View All Time Table for IV Semester Makeup Examination MBA- Mar-2026. read more Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. III Semester End Examinations conducted during Jan/Feb-26. read more Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. I, III Semesters and Reappear Semester UG Semester End Examinations conducted during Jan/Feb-26. read more Notification for Answer Scripts of I &amp; III Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure as per the attached schedule. read more Circular for makeup registration for I and III Semester March -2026 read more Addtional Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester MBA (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for I Semester M.Tech (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester Makeup Examination - Mar-2026. read more View All Late Sri. B.M.Sreenivasaiah Founder B.M.S. Educational Trust Late Sri. B.S.Narayan Donor Trustee B.M.S. Educational Trust The Visionaries B.M.S. College of Engineering (BMSCE) was Founded in the year 1946 by Late Sri. B. M. Sreenivasaiah a great visionary and philanthropist and nurtured by his illustrious son Late Sri. B. S. Narayan. BMSCE is the first private sector initiative in engineering education in India. BMSCE has completed 70+ years of dedicated service in the field of Engineering Education. Started with only 03 undergraduate courses, BMSCE today offers 13 Undergraduate &amp; 16 Postgraduate courses both in conventional and emerging areas. Know More Dr. Bheemsha Arya Principal, B.M.S.C.E A nation’s real and sustainable growth is possible with technological advancement as well as development of its human resource and the role of engineers is immensely pertinent. With globalization, engineers should be able to perform in a larger environment and are expected to face challenges &amp; find solutions in any given situation. The key to meet the demand for such quality engineers remains in providing holistic engineering education. Over the last 75 years, B.M.S.C.E has been offering best engineering programmes and is benchmarked with the leading educational institutions in the Country. Ever since its inception, B.M.S.C.E has focused on augmenting human resource by producing world-class engineers. Today, BMS Alumni occupy coveted positions in reputed organizations both in India and abroad. They have acted as the ambassadors of change. Magnanimous and committed College management has been regularly augmenting the academic/para-academic facilities at the college to suite the present day requirements. A cozy and well maintained campus provides good academic ambience. Well qualified &amp; experienced faculty and committed staff of the college are eager to provide effective education to students. In addition to gaining academic knowledge and skills, opportunities are many for the students to groom and develop further. View Profile B.M.S. College of Engineering BMSCE Alumni can be found all over the world. BMSCE takes proud in educating students since 1946 in various fields of Engineering and continues to provide world class education in the coming years with more emphasis on research and development. Values View More Research View More Placements View More Library View More Innovative Labs View More Accreditations and Rankings B.M.S. College of Engineering is determined to impart quality education to students and provide industry ready engineers for the country. To make this possible the college participates in several audits internally and externally for quality assurance with quality assurance committees and university committees from AICTE, VTU, NBA and NAAC. Know More Rankings / Surveys A++ in NAAC Third Cycle 83rd NIRF-2022 Ranking 8th among top 140 Eng8ineering in The Times Engineering Institute 2019 Survey 1st among top 50 Institutes on Placements in The Times Engineering Institute 2019</v>
+        <v>About Dr. Kavitha Sooda Professor &amp; Head - Computer Science and Engineering About Department The department of Computer Science and Engineering, B.M.S College of Engineering is a regionally and nationally renowned department in computer science and information technology since 1983. With the vision to produce professionals, researchers, innovators and entrepreneurs having ethics and social responsibilities,our focus is towards moulding the students with strong technical knowledge, research attitude and societal values. The syllabus of department of CSE has been designed by including core fundamental subjects, advanced and cutting-edge technologies which prepares the students for industries and higher studies. The department has well experienced and dedicated faculty team to deliver quality education to the students. The department has eighteen faculties with Ph.D.and others are pursuing. The department excels in academic performance and also in research activities. The students of CSE department are placed in various top MNCs like COHESITY, GOLDMAN SACHS, NUTANIX, ORACLE, ZENKEN, QUALCOMM, HONEYWELL, AKAMAI, etc. with an emolument in the range of4Lakhs to 27 Lakhs per annum. The department of CSE has good interactions and MOUs with leading information technology domain Industries like INFOSYS, GE, HPE etc. The department is committed to encourage students to carry out innovative research in trending technologies, keeping excellence in focus and to deliver quality services matching the needs of the technical education system, industry and society as per its Programme Educational Objectives. Apart from regular research, the faculty and student teams are involved in developing R&amp;D projects for SAMSUNG, HPE, GE etc. The students are molded with multi-dimensional skill sets covering all the required graduate attributes. More focus is emphasized on practical learning, projects, and research. The students of the department get into the industry through placements majorly and there is a high inclination towards entrepreneurship and research. The department is supported by a large alumni group. Students are introduced to global challenges and encouraged to take up projects in this direction. Department Profile The department of Computer Science &amp; Engineering started in the year 1983 with an intake of 60 students for the undergraduate programme. The intake was increased to 90 seats in 2000, to 120 in the year 2011 and to 180 in the year 2019. UG programme of the department was accredited by NBA from Jun-2004 to May 2007 for 3 years, Jul-2008 to Jun-2011 for 3 years, Jul-2014 to Jun-2017 for 3 years , Jul-2017 to Jun-2020 for 3 years, Jul-2020 to Jun-2021 for one year, Jul-2021 to Jun-2022 for one year, 2022-2025 for 3 years. The department of Computer Science &amp; Engineering also has PG programme, M Tech (CSE) established in 1993 with an intake of 18. PG programme of the department was accredited for 5 years from Jul-2017 to Jun-2022 and extended for 1 year period from July-2022 to Jun-2023. Extension of affiliation for the academic year 2022-23 for PG, CSE is applicable till 2024-25. The Research Centre, Department of Computer Science &amp; Engineering was started in the year 2010 under VTU, Belgaum. The research areas of the centre cover Machine learning, Cloud computing, Big data analytics, Wireless networks, Social networks analysis, Network Security, etc. Currently, there are twelve registered guides who are experts in fields like artificial intelligence, wireless networks, reconfiguration computing, data analytics etc. 22 of research scholars are awarded with Ph.D. and currently there are 59 research scholars working in the research centre. Vision To be a model centre for education and training in the frontier areas of Computer Science and Engineering. Mission M1:To Educate and Empower the students in the area of Computer Science by providing best practices of Teaching Learning Process for successful professional career. M2: To enhance skills of the students to pursue higher studies and research. M3: To foster the students to innovate and nurture them towards Entrepreneurship.</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-03-14T06:31:36.384Z</v>
+        <v>2026-03-19T18:34:54.326Z</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://bmsce.ac.in/home/B-S-Narayan-PhD-Fellowship</v>
+        <v>https://bmsce.ac.in/home/Electronics-and-Telecommunication-Engineering-About</v>
       </c>
       <c r="B9" t="str">
         <v>html</v>
       </c>
       <c r="C9" t="str">
-        <v>B S Narayan Ph.D FellowshipHomeResearch B.S Narayan Doctoral Fellowship 2025-2026 No Details Action 1. Terms and Conditions for BSN Fellowship &amp; Application form for BSN Fellowship Download 2. BSN Ph.D Fellowship Brochure Download ResearchAbout R &amp; DR &amp; D CommitteeStaffApplication DownloadsResearch CentersInnovative LabsFunded Research ProjectsMoU's With Industries &amp; Research CenterList of Ph.D AwardedList of M.Sc AwardedPh.D Enrollment in Reseach CentresB S Narayan Ph.D FellowshipB S Narayan Centre for Nano-Materials &amp; DisplaysJournal PublicationsPatents FiledGalleryIRINS PortalContact Us</v>
+        <v>About Dr. BALACHANDRA K Professor and Head - Department of Electronics and Telecommunication Engineering About Department The Department of Electronics and Telecommunication Engineering established in the year 1986 offers four-year undergraduate program in Telecommunication Engineering. The faculty, along with other stakeholders of the department constantly strive to ensure an effective implementation of Outcomes-Based-Education (OBE). These efforts have enhanced the academic quality, and have resulted in the department getting Accredited by NBA for FIVE years in the Tier-I Format (applicable for Batches graduating from 2014 to 2018, and subsequent extension in validity by One year, and One more year) valid upto June 2025. The Faculty have shared their Best Academic practices through more than 55 Publications in the domain of Engineering Education. In addition to quality teaching, all faculty actively pursue research. Research carried out in the department has resulted in a total of 439 publications (152 Peer-Reviewed Journal publications,248 International Conference publications, 39 National Conference publications). These research activities have resulted in the department being recognized research center by VTU and has produced six Doctorates. The Electronics and Telecommunication Program is a multidisciplinary program that includes concepts from the two programs: ‘Electronics and Communication Engineering’ and ‘Computer Science Engineering’. The Under Graduate Electronics and Telecommunication Engineering program is designed to develop the ability to comprehend, design and build electronic systems that can acquire and process real signals (audio/video/data) for point-to-point communication or broadcast. Signal acquisition and processing form the core content of the course. Accordingly, the program is structured to include concepts from Electronics, Communication, and Computer science. Students are introduced to various electronic- components, circuits, equipment, and engineering simulation tools through the laboratory sessions to strengthen concepts. The curriculum takes the student through effective usage of Engineering Tools like Python, Matlab, LabVIEW, Multisim, Xilinx, Mentor Graphics, Code-Composer-Studio, Qualnet and HFSS simulation tools. In addition, students are required to formulate, design, implement, and demonstrate course projects/mini-projects. To ensure an overall development of student skills, the curriculum includes courses from the Humanities and Management stream as well. Accordingly, the Teaching-Learning Process of the department prepares our graduates to pursue careers in either the core ‘Electronics and Communication Engineering domain or in the ‘Computer Science and Engineering domain. A well-designed curriculum, together with an equally well-planned delivery and assessment is the major strength of the department. One parameter that reflects the academic quality of the department is the quality of our undergraduate projects. The Projects of our students have resulted in a total of 179 publications (Publications in International Journals/Conferences). Another parameter that serves as a measure our academic quality, is student placements. Our students, get an opportunity to compete with all industries looking for Electronics Engineers and/or Computer Science Engineers. Pleased to observe that our students have secured on-campus placements with Analog Devices, National Instruments, Cypress Semiconductors, Dell Technologies, Hewlett Packard, Cisco Systems, Tektronix, Siliconch Systems Pvt.Ltd., Bharati Airtell, Delloite, Finastra, Capgemini, Oracle, Honeywell, TCS, and Accenture. Our students are able to do well in the National and International competitive examinations (GATE, GRE-TOEFL). Proud to mention that we have a few students taking up National Level competitive examinations for a career in the administrative Sector. Few of our students are successful entrepreneurs. A significant number of our graduates pursue higher education in Engineering/ Management in prestigious Universities in India and outside India. Department Profile The Department of Electronics and Telecommunication Engineering was established in the year 1986. The efforts of the faculty, along with other stakeholders of the department to ensure an effective implementation of Outcomes-Based-Education (OBE) has resulted in the department getting Accredited by NBA for FIVE years in the Tier-I Format (applicable for Batches graduating from 2014 to 2018, and subsequent extension in validity by One year, and One more year). The department is a recognized research centre by VTU and has produced seven Doctorates. The department is proud to mention that a large number of our graduates have secured on-campus placements with reputed core and IT companies. A good number of our students pursue higher education in Engineering/ Management in prestigious Universities in India and abroad. Few of our students are successful entrepreneurs and also have a career in the administrative Sector. Vision Our graduates shall be globally competent Engineering professionals Mission The department will achieve the Vision through: • Curriculum designed for holistic development • Effective implementation of the designed curriculum • Active association with Industry, Academia and Alumni • Research leading to publications/patent/start-up • Emphasis on professional ethics, contribution to society and concern for environment</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-03-14T06:31:37.327Z</v>
+        <v>2026-03-19T18:34:55.040Z</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://bmsce.ac.in/home/Notifications</v>
+        <v>https://bmsce.ac.in/home/Information-Science-and-Engineering-About</v>
+      </c>
+      <c r="B10" t="str">
+        <v>html</v>
       </c>
       <c r="C10" t="str">
-        <v>NotificationsHomeNotifications # Details Files 1.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25/03/2026. Teaching Application General Condition 2.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), 2. Department of Machine Learning (AI &amp; ML), 3. MCA 4. Department of Mechanical Engineering 5. Department of Electronics &amp; Communication Engineering Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10th January 2026. Please refer to the advertisement for more details. Teaching Application General Condition3.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/12/2025. Teaching Application General Condition4.B.S. Narayan Doctoral Fellowship 2025-26. Last date for receipt of filled-in application form is 31st December 2025 Link5.Admissions are Open for Management Quota seats for First Year PG Courses (M.Tech, MBA &amp; MCA) for 2025-26 at B. M. S. College of Engineering. Kindly contact the undersigned on or before 13th November 2025. Sd/- Principal 6.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10/11/2025. Teaching Application General Condition7.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Mathematics. Note: PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/10/2025 Teaching Application General Condition8.Application for Change Of Branch(COB) Circular for the Academic Year 2025-26 Download 9.Circular for payment of Tuition and Miscellaneous Fee for 2nd Semester (MTech, MCA and MBA) for AY-2025-26 Download 10.Circular for Fee Structure for 2nd Year B.E admitted through CET, COMEDK and Management Quota for AY-2025-26 Download 11.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25/09/2025. Teaching Application General Condition12.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. 2. Department of Physics Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 08.09.2025 Teaching Application General Condition13.Notification for Faculty Recruitment under Management Cadre for the post of ADJUNCT FACULTY AND PROFESSOR OF PRACTICE in ALL DEPARTMENTS. Note: Preference shall be given to candidates with Degree from premier institutions in addition to the qualification and experience as per AICTE norms. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25.08.2025 Teaching Application General Condition14.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. 2. Department of Mathematics Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25.08.2025 Teaching Application General Condition15.Fee Structure for 3rd Year and 4th Year B.E students for the Academic Year 2025-26. Download 16.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 09.08.2025 Teaching Application General Condition17.1. Fees in respect of 1st year BE CET/COMEDK/MGMT/GOI Quota admission for the year 2025-26 2. Fees in respect of 2nd year BE (Diploma) DCET Quota admission for the year 2025-26 1st year BE CET/COMEDK/MGMT/GOI 2nd year BE (Diploma)18.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 22.07.2025 Teaching Application General Condition19.PM-Vidyalaxmi Scheme The Government of India has approved PM-Vidyalaxmi scheme to provide financial support to meritorious students so that financial constraints do not prevent any youth of India from pursuing quality higher education. A special loan product has been introduced to enable for collateral free, guarantor free education loans to meritorious students who get admission in the top 860 quality higher educational institutions of the nation; made accessible through a simple, transparent, student-friendly and entirely digital application process. Furthermore, for students with up to Rs. 8 lakhs annual family income, the scheme will also provide for 3% interest subvention on loans up to Rs 10 lakh. The list of 860 quality higher education institutions is at: https://dashboard.aishe.gov.in Please visit the PM-Vidyalaxm portal for the detailed guidelines of the Scheme Students can apply online for education loan and interest subvention under PM-Vidyalaxmi and CSIS Scheme at https://pmvidyalaxmi.co.in Link20.1. Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. 2. Placement Officer in Department of Training &amp; Placement with TWO years MBA preferably specialization in HR. At least 10 years prior experience in placement related activities in leading Institutes/Organizations. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS for Teaching positions. The duly filled-in applications along with the required enclosures should reach the Principal on or before 05.07.2025 Teaching Application Non Teaching Notification Advertisement General Condition 21.Applications are invited for the post of Project Associate under the Dassault Systemes Foundation Grant for the project "3-D Modelling based Simulation of Rain induced Urban Flooding and creation of methodology for mitigation Measures". Principal investigator of the project is Dr. Reshmi Devi T.V, Associate Professor, Dept. Civil Engineering, B.M.S. College of Engineering, Bengaluru. The project team includes Prof. Alok Pandey and Dr. Geetha Kuntoji (Dept. Civil Engineering, BMSCE) and Dr. Dr. ShivashankarR. Srivatsa (Dept. Mechanicl Engineering, BMSCE). Eligible candidates fulfilling the criteria, may apply through the following Google form - https://forms.gle/a532di5bHYq8J5Mu9 Notification22.Applications are invited from eligible candidates for the post of a Senior Research Fellow (SRF) on contract basis for the Prasanna Technologies Pvt. Ltd. (PTPL) funded project entitled: “Predicting residual life of structures using artificial intelligence enabled thermography”, under Dr. Anil Chandra A. R., and Dr. Sangamesh C. Godi, , Department of Mechanical Engineering, B.M.S. College of Engineering, Bengaluru. Eligible candidates fulfilling the criteria, may apply with their resume and relevant documents by sending the same through e-mail to the address anilchandraar.mech@bmsce.ac.in or by posting to the address mentioned below. Last date for submitting the documents is 12 th April 2025, 5PM IST. For further details please refer the notification. Download 23.DATE EXTENDED till 30/04/2025 Applications are invited for JRP position(1 post ) under DRDO grant sanctioned by DRDO titled "Investigations on Ge-Sn Alloys Suitable for photodetector in SWIR range". Desiring candidates are requested to submit their CV to PI via email: chandasreedas.eee@bmsce.ac.in with the subject line "Application for DRDO Grant JRF Advertisement No: BMSCE/EEE/DRDO/JRF/1/2025" on or before 30/04/2025 Notification24.Notification for Faculty and Staff Recruitment under Management Cadre for the Post of 1. Assistant Professor in Department of Management Studies and Research Centre 2. System Analyst Note: 1. For Faculty:7th PAY SCALE AS PER MANAGEMENT NORMS. 2. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10.04.2025. Notification Teaching Application Non-Teaching Application25.APPLICATIONS ARE INVITED FOR B.S. NARAYAN DOCTORAL FELLOWSHIP PH.D. ADMISSION (FULL TIME) FOR THE ACADEMIC YEAR 2025-26. The last date to submit the application is extended to 20th March 2025. Ph.D. Notification Application 26.Admission to Ph.D. Programme (Full-Time/Part-Time) under Visvesvaraya Ph.D. Scheme - Last date for the submission of online Application form 15/02/2025 Download 27.In view of Government Order No. ಸಿಆಸುಇ 40 ಹೆಚ್ ಹೆಚ್ ಎಲ್ 2024, dated 26.12.2024, 27th December 2024 (Friday) is declared as holiday to mourn the sad demise of Sri. Manmohan Singh, Former Prime Minister of India. Download 28.Notification for Faculty Recruitment under Management Cadre for the Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Block Chain Technology), Computer Science &amp; Business Systems, Statistics, MCA (Ph.D. Preferable). Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled in applications along with the required enclosures should reach the Principal on or before 31.12.2024. General Conditions Application Form (Teaching) 29.In view of Government Order No.DPAR/35/HHL/2024 dated 10.12.2024, 11th December 2024 (Wednesday) is declared as holiday to mourn the sad demise of Sri. S.M. Krishna, Former Chief Minister of Karnataka. Download 30.In accordance with the communication received from Basavanagudi Traffic Police Station and the direction from the higher authorities, the college remains closed on 25th November 2024(Monday) owing to the issues regarding mobility of people and vehicles in view of Kadalekai Parishe.31.NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE (Department of MBA-Placement Officer) Last Date: 14-12-2024. Application Form (Non-Teaching Application form) Notification32.First year Miscellaneous Fees of M.Tech, MBA and MCA for the academic year 2024-25. Download 33.Due to Annual Kadalekai Parishe, the entry and exit of all the staff and students’ vehicles on 22nd, 25th, and 26th November 2024 will be through the Hostel Gate only. Download 34.Notification for Faculty Recruitment under Management Cadre for the Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Block Chain Technology), Computer Science &amp; Business Systems, Statistics, MCA (Ph.D. Preferable). Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled in applications along with the required enclosures should reach the Principal on or before 30.11.2024. General Conditions Application Form (Teaching) 35.NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE (Diploma in Mechanical/Civil/Aero/Tool &amp; Die making) Last Date: 28-11-2024. Application Form (Non-Teaching Application form) Notification36.Change of Branch Students List 2024-25 Download 37.Change of branch 2024 -25 (Date of Counselling: 19th October 2024 @ 9:30 AM Download 38.Change of Branch (CoB) for the Academic year 2024-2025. The last date to apply in the VTU portal is 22-09-2024 Download 39.Fees in respect of 1 year BE CET Quota admission for the year 2024-25 Download 40.Admission to Ph.D. Programme (Full-Time/Part-Time) under Visvesvaraya Ph.D. Scheme - Last date to apply is 15-08-2024 Download 41.Fees in respect of 1 year BE GOI Quota and Management Quota admission for the year 2024-25 Download 42.Check list of the Original Documents to be submitted by the Candidates selected through Various Quota at the time of verification of documents in the college. Download 43.Notification for Faculty Recruitment under Management Cadre for the Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Block Chain Technology), Computer Science &amp; Business Systems, Statistics, Mathematics, Chemistry and Physics. Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Assistant/Associate Professor Position for Computer Science Cluster Departments. The duly filled in applications along with the required enclosures should reach the Principal on or before 03.08.2024. General Conditions Application Form (Teaching) 44.Fee in respect of II year BE CET DIPLOMA Lateral entry quota admission for the year 2024-25 Download 45.Fee in respect of 1st year COMEDK quota admission for the year 2024-25. Download 46.TECHNOLOGY DEMONSTRATION OF INTERSHAFT SQUEEZE FILM DAMPER (ISSFD) FOR TWO SPOOL GAS TURBINE APPLICATION. A write up on the Project details and requirement for the JRF recruitment(PDF) JRF Application Format (Word File 47.Notification for Faculty Recruitment under Management Cadre for For the Departments of Computer Science &amp; Engineering (CSE), Machine Learning (Artificial Intelligence &amp; Machine Learning), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Block Chain Technology), Computer Science &amp; Business Systems, MBA, Statistics Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled in applications along with required enclosures should reach the Principal on or before 29.06.2024. General Conditions Application Form (Teaching) Application Form (Placement officer) Notification 48.The students belonging to the SC category admitted to UG/PG 2023–24 are hereby informed to submit their scholarship applications online at the State Scholarship Portal (SSP), https://ssp.postmatric.karnataka.gov.in immediately and without fail. Note: Last date for SC category students is April 30, 202449.NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE(e-Governance). Last Date: 19-02-2024. Click here to Apply Online50.Notification for Faculty Recruitment under Management Cadre for Computer Science &amp; Engineering, Information Science &amp; Engineering, Machine Learning( AI &amp; ML), CSE (Data Science), CSE (IOT and Cyber Security &amp; blockchain technology), Artificial Intelligence (AI), and Data Science, Computer Science &amp; Business Systems. The last date to apply online is June 10th, 2024. Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Click here to Apply Online 51.VTU Notification (Submission of online Exam application forms for UG Silver Jubilee Special Examination to be held during December 2023/January 2024) dated 17.01.2024 Download 52.First Year Miscellaneous Fees for M.Tech, MBA and MCA for the academic year 2023-24 Download 53.Applications are invited from eligible and interested candidates for the post of Junior Research Fellow (JRF) or Project Associate on a consolidated basis to work on the Scheme for Transformational and Advanced Research in Sciences (STARS) funded project by IISC, Bangalore. Download 54.Notification for Faculty Recruitment under Management Cadre for Computer Science &amp; Engineering, Information Science &amp; Engineering, Machine Learning( AI &amp; ML), CSE (Data Science), CSE (IOT and Cyber Security &amp; blockchain technology), Artificial Intelligence (AI), and Data Science, Computer Science &amp; Business Systems. Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Click here to Apply Online 55.Applications are invited from eligible and interested candidates for the post of Junior Research Fellow (JRF) on a consolidated basis to work on the Scheme for Transformational and Advanced Research in Sciences (STARS) funded project by IISC, Bangalore. Download 56.Notification for Faculty Recruitment under Management Cadre for Computer Science Engineering, Information Science Engg, &amp; Machine Learning( AI &amp; ML), CSE (Data Science),CSE (IOT and Cyber Security &amp; blockchain technology), Artificial Intelligence (AI), and Data Science and Placement Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Notification Click here to Apply Online Application Form (Teaching) Download 57.Fees in respect of II year BE CET Diploma Lateral entry quota admission for the year 2023-24 Download 58.Change of Branch (CoB) for the Academic year 2023 - 2024. The last date to apply in the VTU portal is 22-11-2022 Download 59.Call for Research Assistant / Field Investigator ICSSR Funded Short-Term Empirical Research Project Download 60.Applications are invited for the position of Junior Research Fellow (JRF) Senior Research Fellow (SRF) and Research Assistant (RA), in a research and development project (under CHIPS TO START-UP PROGRAMME (C2S) CATEGORY – I PROPOSALS) for the duration of 2 years (2023-2025) Download 61.Call for recruitment of Field Officer and Resaerch Assistant as per ICSSR for Short-term Empirical Research Project Download 62.Call for Application : Research Study (National Commission for Women) on : “Women in Decision Making Roles in Corporate” Download 63.Dear Students, The First year classes will commence from October 11, 2023. Principal, BMSCE.64.Fees in respect of 1 year, II year lateral entry BE CET, Comed-K, and Management Quota admission for the year 2023-24 Download 65.Fees in respect of 1st year BE CET, Comed-K, and Management Quota admission for the year 2023-24 Download 66.Advertisement for the post of Faculty Positions for various departments in B.M.S.C.E. The duly filled application along with required enclosures should reach the Principal on or before 02-08-2023. Advertisement General Conditions Teaching Application67.Students of non-NEP branch (6th &amp; 8th Semesters) are informed that supplementary semester (fast track) is commencing tentatively from 25th July 2023. The students can enroll the failed courses at the respective departments . The last date for enrollment is 22nd July 2023.68.CHECK LIST FOR FIRST YEAR BE ADMISSION FOR STUDENTS REPORTING TROUGH VARIOUS QUOTA FOR THE ACADEMIC YEAR 2023-24 in BMSCE. Download 69.Special examinations for UG and PG Students who have completed their course and have only backlogs - VTU circular attached for your reference. you may contact the COE office {OR} Dean Academics Office. Download 70.Pubic Holiday Declared on Wednesday, 10th May 2023 due to Karnataka Legislative Assembly Elections. Download 71.Notification for Faculty Recruitment under Management Cadre for Computer Science Engineering, Information Science Engg, &amp; Machine Learning( AI &amp; ML), CSE (Data Science),CSE (IOT and Cyber Security &amp; blockchain technology), Artificial Intelligence (AI), and Data Science. Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Click here to Apply Online 72.First year Miscellaneous Fees of M.Tech, MBA, and MCA for the academic year 2022-23. Download 73.Fees in respect of II year BE CET Diploma Fresh admission Students for the Year 2022-23. Download 74.Notification for Faculty Recruitment under Management Cadre for Computer Science Engineering, Information Science Engg, Machine Learning( AI &amp; ML), Aerospace Engineering &amp; Department of Mathematics. The last date is 27-01-2023. Application Form (Teaching) Notification 75.NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE. Last Date: 16-01-2023. Application Form (Non-Teaching Application form) Notification76.Scholarship Circulars - Submissions of online Applications for the AY 2022-23. Scholarship Circular-1 Scholarship Circular-2 Scholarship Circular-3 Scholarship Circular-477.NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE(R &amp; D, Electronics * Instrumentation Engg, Aerospace Engg. Last Date: 16-01-2023. Application Form (Non-Teaching Application form) Notification78.The Dean (Academic) of BMSCE, Dr. Seshachalam D, will be addressing the first year students of the batch of 2022-2023 regarding the online Course Registration and choice of courses for 1st semester, tomorrow (Friday 09.12.2022 ) at 11.00 AM. The address will be online. Please find the link for the online session attached herewith: https://ieeemeetings.webex.com/ieeemeetings/j.php?MTID=m3d98a0aec81dc4e96559500f3bcac9e2 The Mock Online registration will be conducted tomorrow (Friday 09.12.2022) at 2.00 PM. Link to the portal: https://firstyear.bmsce.ttcindia.co/ If a first year student has not yet registered on the student portal, please register using the aforementioned link. The actual online Course Registration will be conducted on 10.12.2022 (Saturday) at 9.30 AM, instead of 12.12.2022 (Monday). User Manual Download Link79.Change of Branch (CoB) for the Academic year 2022 - 2023. The last date to apply in the VTU portal is 30-11-2022. Change of Branch Notification Download 80.Advertisement for Research Assistant for the project “Development of a Polymer Nanocomposite based Rapid Malaria Sensing Device” sponsored by the SCIENCE &amp; ENGINEERING RESEARCH BOARD (SERB) - Last Date is 7th Nov.2022 Download 81.Notification for Faculty Recruitment under Management Cadre for Computer Science Engineering, Information Science Engg &amp; Department of Mathematics. Application Form (Teaching) Notification 82.Fees in respect of 1 Year B.E. CET, Comed-K and Management Quota admission for the year 2022-23 - Circular Download 83.Housekeeping Tender Notification - Last Date 31st October 2022 Tender Notification Covering Letter Quotation HK Services84.Notification for Faculty Recruitment under Management Cadre for Computer Science Engineering, Information Science Engg &amp; Department of Mathematics. Notification Application Form (Teaching) Download 85.Advertisement for the post of Teaching and Non-Teaching Positions for various departments in B.M.S.C.E. The dully filled application along with required enclosures should reach the Principal on or before 11-05-2022. Notification General Conditions (Teaching &amp; Non-Teaching) Application Form (Teaching) Application Form (Non-Teaching) Application Form (Librarian)86.As per the latest directions from the GOK &amp; VTU, the classes are to be conducted in Offline mode. For further details, students are informed to contact their concerned HOD. Further, as per the Government Order, in view of weekend curfew, the college remains closed on 8th January 2022 (Saturday). However, online classes would be conducted on 8th Jan. 2022. The CIE &amp; SEE scheduled will be conducted in Offline mode only at the college. 87.Melton Foundation is opening fellowship applications Download 88.Inauguration of First Year B.E.(2021-2022) classes to be held on 19th December 2021 at 11 AM. Download 89.Results of Supervisors Allotment and Document Verification - The last date is 20-12-2021 Download 90.Commencement of First Year B.E. (2021-2022) Program - Monday 13th December 2021. Download 91.Change of Branch for the academic year 2021-22 as per the merit list -Counselling dated 17.11.2021 @ 10 AM. Download 92.Change of Branch (CoB) for the Academic year 2021 - 2022. Change of Branch-VTU Circular College Circular VTU Revised Circular93.AICTE Swanath Scholarship Scheme (Both Degree and Diploma Level) Download 94.Advertisement for the post of Assistant Professor for Civil Engineering Department in B.M.S.C.E. The duly filled application along with required enclosures should reach the Principal on or before 04-10-2021. - CLOSED Advertisement Teaching Application95.Advertisement for JRF (Junior Research Fellow) position under SERB POWER Grant sanctioned by DST-SERB. The last date to submit their Curriculum Vitae to the Principal Investigator email is 15-09-2021 - CLOSED Download 96.Advertisement for the post of Faculty Positions for various departments in B.M.S.C.E. The duly filled application along with required enclosures should reach the Principal on or before 06-09-2021. - CLOSED Advertisement General Conditions Teaching Application97.Applications are invited from eligible candidates for the post of Junior Research Fellow (JRF) - Last date for submitting the application is 25 July 2021, 5 PM IST. - CLOSED Download Link98.Advertisement for the post of Technical Assistant in the Department of Electrical &amp; Electronics Engineering, B.M.S.C.E. The duly filled in application with all relevant documents should reach the Principal on or before 15.05.2021 through post or through e-mail to "establishmentsection@bmsce.ac.in". - CLOSED Advertisement Application 99.II Semester B.E. classes Time Table with effect from 28th April 2021 Download 100.Constitution of Task Team for implementation of COVID-precaution-SOPs - Circular Download 101.B.E.,5th Semester, 7th Semester, MCA 3rd and 5th Semester, MBA 3rd Semester Results - January 2021 Link102.Revised III Semester B.E. Consolidated Theory Semester End Main Examination - Time Table March 2021 Examinations Download 103.submission of online applications at the State Scholarship Portal (SSP) by eligible students 2020-21. Download 104.Commencement of First semester B.E. (2020-2021) offline classes from 22.02.2021. Download 105.SEE for III Semester B.E., are scheduled from 12.03.2021. Download 106.SEE Timetable for the Odd Semester B.E., B.Arch, MBA, MCA and M.Tech &amp; Even Semester Improvement Examinations - January/February 2021 starting from 27.01.2021. Download 107.No change in the examination schedule as per the VTU Circular - Text Highlighted FYI. Download 108.SEE for VII Semester B.E., B. ARCH, III &amp; V Semester MCA, III Semester MBA and MTech Jan/Feb 2021 are rescheduled from 27.01.2021. Download 109.Attention to 5th Semester BE Students - SEE Circular Download 110.Grade Improvement Examinations for the II Semester - Circular Download 111. First Semester B.E.(2020-2021) Time Table with effect from 28.12.2020. Physics Cycle (2020) Chemistry Cycle (2020)112.II Semester Grade Improvement Examinations - Circular Download 113.SCHEDULE OF INDUCTION PROGRAM FOR FIRST YEAR B.E. STUDENTS 2020-2021 Phase -I. Circular114.Advertisement for the post of Teaching and Non-Teaching for various departments in B.M.S.C.E. The duly filled application along with required enclosures should reach the Principal on or before 20-12-2020. Advertisement General Conditions Teaching Application115.VTU Circular related to offline examinations for both UG and PG Courses -Reg Download 116.Final List of Students who have been allotted change of branch for the academic year 2020-21 Download 117.Online Examination Circular for UG/PG Students for Supplementary Semester End Exams, Re-registered, Grade Improvement Students Download 118.B.E. /M.Tech /M.C.A /M.B.A Programmes Results Announced - July/August 2020 Link119. CONDUCTION OF FINAL YE</v>
+        <v>About Dr. M K Nalini Associate Professor &amp; Head - Department of Information Science and Engineering About Department The department of Information Science and Engineering was established in the year 1987 with an intake of 60 for UG program. Since then, the department has evolved over the years to portray its excellent academic performance. The intake was enhanced to 90 in the year 2000, 120 in the year 2018 , 180 in the year 2019,207 in the year 2022 and 267 in the year 2023. The PG programme, M.Tech in Computer Network and Engineering under VTU, was started in 2011 with an intake of 18 As an autonomous institution, the department has flexibility in designing the curriculum. The curriculum has been designed by considering the feedback from the stakeholders including final year students, Alumni, parents Industry experts and academicians of other premier Institutions. The courses offered cover the major upcoming technologies with more emphasis to fundamental concepts. The innate strength of the department is its faculty. The department has 31 experienced faculty out of which 19 are Ph.D. holders and 12 are pursuing Ph.D. All the faculty and staff committedly guide the students all the way through and make them adequately competent in order to match global standards. With student centric innovative practices and latest pedagogical concepts and training, the department transforms students into competent professionals with domain knowledge and skills to meet the challenges. The research activities were promoted in the department with the launch of Research Center in the year 2011. There are 15 research supervisors guiding 13 research scholars in various research areas like Bio-metrics, Networks and Communications, Cloud Computing, Wireless Networks, Data Sciences, Natural Language Processing, Internet of Things etc. Both UG and PG programme of the department have been accredited by NBA in Tier-I format [as per Washington Accord] till 2025-26. Department has very good computing facility with updated software and hardware to aid innovative teaching-learning methods and the research needs with campus wide internet connectivity. The department has an outstanding placement record with an average placement percentage of 95% over last 3 years. Both UG and PG students are offered with Internship and Remote mentoring projects from various Industries during their final and pre-final years.The students of ISE department are placed in various top MNCs like Walmart, VISA, NUTANIX, COHESITY,ORACLE, SIEMENS, HONEYWELL,SUKI, etc. The department has close interaction with companies such as HPE, EMC, Intel, Phillips, TCS, SAP and IBM to promote student projects. Vision Promote Quality Human Resource Capital by inculcating in every student the art of Creativity and Productivity in the field of Information Technology. Mission Offer High Quality Graduate, Post Graduate Programme in Information Technology to prepare students for higher studies and professional career in the industry. Provide good Teaching and Research environment for Quality Education in the field of Information Technology</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-03-14T06:31:38.267Z</v>
+        <v>2026-03-19T18:34:55.704Z</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://bmsce.ac.in/home/Notifications</v>
+        <v>https://bmsce.ac.in/home/Electronics-and-Instrumentation-Engineering-About</v>
+      </c>
+      <c r="B11" t="str">
+        <v>html</v>
       </c>
       <c r="C11" t="str">
-        <v>AR EXAMINATION AUGUST 2020 (ADDITIONAL INSTRUCTIONS TO STUDENTS) Download 120.Online Examination Time Table August - 2020 Download 121.Examination Circular - Reg Download 122.UPDATED CIRCULAR-CONDUCTION OF FINAL YEAR EXAMINATION AUGUST 2020 Download 123.SUPPLEMENTARY SEMESTER 2019-20 (AUG-SEPT 2020) UG &amp; PG PROGRAMMES - Calendar &amp; Guidelines (Fast Track Semester UG, MBA &amp; MCA) Download 124. Examination and Announcements Important Information- 2020 Download 125.APPLY NOW!(Students/Faculty) for SEED FUNDING UP TO 15 LACS to MSME approved Business incubator at B.M.S. COLLEGE OF ENGINEERING (Institute's HI/BI Number: HIBIKI 000342) Deadline: 20th Feb 2020. MSME-HI_BI Brochure Innovate Indiea (Teaching &amp; Non-Teaching) 126.Advertisement for the post of Teaching and Non-Teaching Positions for various departments in B.M.S.C.E. The dully filled application along with required enclosures should reach the Principal on or before 07-02-2020. Notification General Conditions (Teaching &amp; Non-Teaching) Application Form (Teaching) Application Form (Non-Teaching)127.KSCST invites project proposals from the final year BE, M Tech. MSc, and MBA students for sponsorship under the 43rd series of SPP: 2019-20 Download 128.Advertisement for Positions at BMSET Hostel Download 129.Advertisement for JRF (Junior Research Fellow) position under ASEAN-India Collaborative Project sanctioned by DST-SERB. Download 130.Admissions are open for Management Quota seats for First Year PG Courses (MCA, MBA) for 2019-20 at B.M.S. College of Engineering. Link131.CHANGE OF BRANCH FOR III SEMESTER FOR THE ACADEMIC YEAR 2019-20. Download 132.Schedule of Activities for Odd Semester B.E. Programs 2019-20 Download 133.First Semester B. E classes (2019-2020) Time Table. Link134.First Year B.E Syllabus Book (2019-2020) Download 135.Results and Notifications - COE Link</v>
+        <v>About Dr. PREETHI K MANE Associate Professor and Head - Department of Electronics and Instrumentation Engineering About Department The Department of Instrumentation Technology started in the year 1991. More than twenty five batches of Engineers have graduated from Department of Instrumentation Technology, B.M.S College of Engineering. The program name has been changed by VTU as Electronics &amp; Instrumentation Engineering with effect from, 2014 batch onwards. Currently the program offers Under Graduate (UG) degree with an intake of 60. The Department Infrastructure fulfills the requirements of academics and learning skills on the latest technology in the industry. Dedicated faculty with Ph.D who are into Research and Development activities at Institution level, Qualified technical staff and enthusiastic and intelligent students are the strength of the department. A well designed curriculum takes the student through basics of Engineering, core domain and development of competencies by the effective usage of Modern Engineering Tools like: MATLAB, LabVIEW, Multisim, Xilinx, IAR Embedded workbench, Code-Composer-Studio, Simulation tools, PCB design labs, process control loops and PLCs applications. The department has strong industry collaborations in the field of Sensors, Automation Control, Embedded Systems, IoT solutions through Professional bodies as well as through faculty contacts. Their contribution is reflected through guidance in curriculum design, organization of industrial visits, conduction of expert lectures, organization of workshops, and joint research. One of the important developmental activity of the department in latest years is to draw together key stakeholders viz. Alumni, employers, Faculty, Industries, Professional bodies and students in a neutral venue, one that allows them to discuss issues and foster collaborative activities around issues in which they have a strong common interest for the growth of the department. The UG projects implemented by our students have resulted many awards at National level and publications in and conferences, peer-reviewed journals. The department projects are adjudged as best Projects at Institution level as well as at different intercollegiate competitions. The department prepares the graduating engineers so that they are able to pursue a successful professional career in the outside world. The quality of the graduating students is reflected in good on-campus/off-campus recruitments, in core and allied industries up to 80% among the eligible candidates. A significant number of our graduates pursue higher education in Engineering/ Management in prestigious Universities in India and abroad. Department has been accredited by National Board of Accreditation (NBA) under Tier –I, Washington Accord. Vision To bring forth globally emerging competent professionals with high quality of technical education who meet the demands of modern industrial world which seeks innovation and continuous improvement in performance Mission To accomplish excellence in curricular, co-curricular and R&amp;D activities and active participation of students, faculty and staff To impart quality education based on in-depth and thorough understanding of fundamentals To prepare the students to meet the demands of the Electronics, Instrumentation industry To Motivate and inspire young engineers to contribute to development of the society.</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-03-14T06:31:38.267Z</v>
+        <v>2026-03-19T18:34:56.336Z</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://bmsce.ac.in/home/COE-Notifications</v>
+        <v>https://bmsce.ac.in/home/Medical-Electronics-Engineering-About</v>
+      </c>
+      <c r="B12" t="str">
+        <v>html</v>
       </c>
       <c r="C12" t="str">
-        <v>NotificationsHomeCOE # Details Files 1.Time Table for IV Semester Makeup Examination MBA- Mar-2026. Download 2.Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. III Semester End Examinations conducted during Jan/Feb-26. Download 3.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. I, III Semesters and Reappear Semester UG Semester End Examinations conducted during Jan/Feb-26. Download 4.Notification for Answer Scripts of I &amp; III Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure as per the attached schedule. Download 5.Circular for makeup registration for I and III Semester March -2026 Download 6.Addtional Time Table for III Semester Makeup Examination - Mar-2026. Download 7.Time Table for I Semester MBA (Re-Appear) theory Semester End Examination March- 2026. Download 8.Time Table for I Semester M.Tech (Re-Appear) theory Semester End Examination March- 2026. Download 9.Time Table for III Semester Makeup Examination - Mar-2026. Download 10.Time Table for I Semester Makeup Examination - Mar-2026. Download 11.Time Table for MBA I Semester (Reappear) theory Semester End Examination March- 2026. Download 12.Time Table for M.Tech I Semester theory Semester End Examination March- 2026. Download 13.Time Table for MCA I Semester theory Semester End Examination March- 2026. Download 14.Time Table for MBA I Semester theory Semester End Examination March- 2026. Download 15.Additional/Revised Time Table for V Semester B.E. theory Semester End Examinations-Jan/Feb-2026. Download 16.Additional/Revised Time Table for IV Semester B.E. theory Semester End Examinations-Jan/Feb-2026. Download 17.Revised Time Table for I Semester B.E. theory Semester End Examinations-Jan/Feb-2026 Download 18.Additional/Revised Time Table for III Semester B.E. theory Semester End Examinations-Jan/Feb-2026. Download 19.Time Table for VII Semester B.E. makeup theory Semester End Examinations-Jan/Feb-2026 Download 20.Time Table for V Semester B.E. makeup theory Semester End Examinations-Jan/Feb-2026 Download 21.Time Table for Revised VI Semester B.E. theory Semester End Examinations-Jan/Feb-2026 Download 22.Time Table for PG M.Tech Re-Appear II Semester theory Semester End Examination JAN/FEB-2026. Download 23.Additional Time Table for MBA III Semester theory Semester End Examination JAN/FEB- 2026. Download 24.Time Table for VIII Semester B.E. theory Re-Appear Semester End Examinations- Jan/Feb -2026 Download 25.Time Table for VI Semester B.E. theory Re-Appear Semester End Examinations- Jan/Feb -2026 Download 26.Additional Time Table for III Semester B.E theory Semester End Examination Jan/Feb- 2026. Download 27.Revised Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (for 2024, 2023, 2022 &amp; 2021 batch Reappear -Reregisteration) Download 28.attached Time Table for PG II Semester Re-appear M.Tech Theory Semester End Examination Jan- 2026. Download 29.attached Time Table for PG Revised III Semester M.Tech Theory Semester End Examination Jan- 2026. Download 30.Time Table for III Semester MCA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 31.Time Table for III Semester MBA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 32.Time Table for II Semester MBA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 33.Time Table for II Semester MCA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 34.Revised Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. V, VII and Reappear Semester Dec-2025/Jan-2026 Semester End Examination. Download 35.NOTIFICATION:Answer Scripts of V &amp; VII Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure on 28-01-2026 &amp; 29-01-2026. Download 36.Time Table for PG III Semester M.Tech Theory Semester End Examination Jan- 2026. Download 37.Additional /Revised Time Table for IV Semester B.E. theory Semester End Examinations-Jan-2026. Download 38.Additional /Revised Time Table for III Semester B.E. theory Semester End Examinations-Jan-2026. Download 39.Time Table for IV Semester B.E. theory Semester End Examinations-Jan-2026 (All batch Reappear &amp; Re registeration).. Download 40.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. V, VII and Reappear Semester Dec-2025/Jan-2026 Semester End Examination. Download 41.Time Table for III Semester B.E. theory Semester End Examinations-Jan-2026 (All batch Regular, Reappear &amp; Re registeration) Download 42.Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (Non-NEP batch Reappear -Re registeration) Download 43.Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (for 2021 batch Reappear -Re registeration) Download 44.Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (for 2024, 2023 &amp; 2022 batch Reappear -Reregisteration) Download 45.Time Table for Semester B.E. theory Semester End Examinations-Jan-2026 (for 2025 batch only) Download 46.Time Table for MCA III Semester theory Semester End Examination JAN- 2026. Download 47.Time Table for MBA III Semester theory Semester End Examination JAN- 2026. Download 48.Notifications for submission of application for ensuring Reappear Examination PG -ODD-2026 Download 49.Additional Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 50.additional Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 51.Additional Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 52.Additional Time Table for VIII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 53.additional Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 54.additional Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 55.Additional Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 56.Revised Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.( For 2022,2021 and Non-NEP Batches) Download 57.Revised Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2022,2021 Batches) Download 58.Revised Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2023 ,2022,2021 and Non-NEP Batches) Download 59.Time Table for VIII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.( For 2023, 2022,2021 Batches) Download 60.Notifications for submission of application for ensuing Reappear Examination Dec-2025 to Jan-2026 (NEP Batches). (21 TO 23 BATCH).. Download 61.Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.( For 2022,2021 and Non-NEP Batches) Download 62.Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2022,2021 Batches) Download 63.Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2023 ,2022,2021 and Non-NEP Batches) Download 64.Notifications for submission of application for ensuing Reappear Examination Dec-2025 to Jan-2026 (NEP Batches)(24 BATCH) .. Download 65.Circular for Fees and Regulations for Photocopy and Challenge Valuation of Re-Appear for I to II semester of P.G. Oct 2025 Examination. Download 66.Circular for Fees and Regulations for Photocopy and Challenge Valuation of Supplementary/Re-Appear for I to IV semester of P.G. Sep/Oct 2025 Examination. Download 67.Circular for Fees and Regulations for Photocopy and Challenge Valuation of Supplementary III to VIII semester of U.G. Sep/Oct 2025 Examination. Download 68.Time Table for PG M.Tech II Semester(2024 batch) theory Re-Appear Examinations Oct- 2025. Download 69.Time Table for PG M.Tech I Semester(2024 batch) theory Re-Appear Examinations Oct- 2025. Download 70.Time Table for PG MBA II Semester theory Re-Appear Examinations Oct- 2025. Download 71.Time Table for PG MBA I Semester theory Re-Appear Examinations Oct- 2025. Download 72.Time Table for PG MCA II Semester theory Re-Appear Examinations Oct- 2025. Download 73.Time Table for PG MCA I Semester theory Re-Appear Examinations Oct- 2025. Download 74.Circular for Fees and Regulations for Challenge Valuation of Summer semester/Supplementary semester of U.G. Sep 2025 Examination. Download 75.Time Table for PG M.Tech I Semester theory Supplementary Examination Sep- 2025 Download 76.Notifications for Reappear Examination Application for PG Sep-2025. Download 77.Time table for Supplementary Examination -Sep- 2025 (MCA). Download 78.Time tables for Supplementary Examination -Sep- 2025 (MBA). Download 79.Revised/additional Time Table for V Semester theory Supplementary /Reappear Examination Sep- 2025 Download 80.Additional Time Table for PG I-II Semester MBA reappear Examination Sep-2025. Download 81.Additional Time Table for PG M.Tech SEE Reappear Examination Sep-2025. Download 82.Additional Time Table for V Semester B.E theory Supplementary Examination Aug/Sep- 2025. Download 83.Additional Time Table for III Semester B.E theory Supplementary Examination Aug/Sep- 2025. Download 84.Revised Time Table for I/II Semester B.E theory Summer Semester Examination Sep- 2025.(Regular 2024 batch and 2022 batch*only). *Ref : VTU notification 12-09-2025 Download 85.Submission of reappear examination application for summer semester examination (2022 batch only-who are not eligible to move to VII Semester due to vertical progression) Download 86.Time Table for PG theory Reappear Examination Sep- 2025 III and IV Semester MBA theory Reappear Examinations. Download 87.Time Table for PG theory Reappear Examination Sep- 2025 I and II Semester MBA theory Reappear Examinations. Download 88.Time Table for PG theory Reappear Examination Sep- 2025 I,II and III Semester MCA theory Reappear Examination. Download 89.Time Table for PG theory Reappear Examination Sep- 2025 I,II,III and IV Semester M.Tech theory Reappear Examination. Download 90.Time Table for I/II Semester theory Summer Semester Examination Sep- 2025 (2024 batch only). Download 91.Time Table for VI Semester theory Supplementary /Makeup Examination Aug- Sep- 2025 (All batches). Download 92.Time Table for V Semester theory Supplementary Examination Aug-Sep- 2025 (All batches). Download 93.additional Time Table for VII Semester theory Supplementary /Reappear Examination Sep- 2025 Download 94.Additional Time Table for III Semester theory Supplementary /Reappear Examination Sep- 2025 Download 95.Additional Time Table for VII Semester B.E theory Supplementary Examination Aug/Sep- 2025 Download 96.Additional Time Table for VIII Semester B.E theory Supplementary Examination Aug/Sep- 2025 Download 97.Notifications for Summer Semester Examination Sep-2025.(2024 Batch) Download 98.Additional Time Table for I Semester theory Supplementary /Reappear Examination Sep- 2025 Download 99.Time Table for VIII Semester theory Supplementary Examination Aug-Sep- 2025. Download 100.Time Table for VII Semester theory Supplementary Examination Aug-Sep- 2025. Download 101.Time Table for IV Semester theory Supplementary /Makeup Examination Aug- Sep- 2025. Download 102.Time Table for III Semester theory Supplementary Examination Aug-Sep- 2025. Download 103.Revised I/II Semester Supplementary Time Table -Aug-2025. Download 104.Notifications for extension of reappear examination PG -MBA/MCA/M.Tech . Download 105.Time Table for I/II Semester B.E theory Makeup Examination Aug- 2025( 2024 batch). Download 106.Time Table for I/II Semester B.E theory Supplementary Examination Aug- 2025 (2022 &amp; 2023 batches). Download 107.Time Table for I/II Semester B.E theory Supplementary Examination Aug- 2025 (2021 batch). Download 108.Time Table for I/II Semester B.E theory Supplementary Examination Aug- 2025 (2016/2017/2018/2018/2020 batches). Download 109.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. II Semester July/Aug-2025 Semester End Examination. Download 110.Notifications for Supplementary Examination Aug-2025.(2023 and 2024 lateral entry Re-Appear) Download 111.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. IV, VI Semester July/Aug-2025 Semester End Examination. Download 112.Time Table for PG II theory Semester End Examination JULY/AUG- 2025 (Re-Registered). Download 113.Notifications for Supplementary Examination Aug-2025.(non-NEP batch) Download 114.Notifications for Supplementary Examination Aug-2025.(2021 and 2022 lateral entry) Download 115.Time Table for PG theory (M TECH)Semester End Examination JULY/AUG- 2025. Download 116.Time Table for PG theory (MCA)Semester End Examination JULY/AUG- 2025. Download 117.Time Table for PG theory (MBA)Semester End Examination JULY/AUG- 2025. Download 118.Time Table for VIII Semester B.E theory Semester End Examination JULY- 2025( Makeup Examination). Download 119.Time Table for Additional I/II Semester B.E theory Semester End Examination JULY- 2025 (2022 BATCH ONLY). Download 120.Time Table for IV Semester M Tech theory Semester End Examination July- 2025. Download 121.Revised Time Table for I/II Semester B.E theory Semester End Examination JULY- 2025.(Regular 2024 batch, 2023,2022 batch reappear &amp; Re-registration). Download 122.Revised Time Table for IV Semester MBA theory Semester End Examination JULY- 2025. Download 123.I/II SEMESTER Time Table for 2022,2023,2024 batch (Re reg and Re Appear) Download 124.I/II SEMESTER Time Table for 2021 batch (Re reg and Re Appear) Download 125.Notifications for reappear examination for UG (2024 Batch)-2025. Download 126.I/II SEMESTER Time Table for 2016 to 2020 batch (Re reg and Re Appear) Download 127.Additional Time Table for VI Semester B.E theory Semester End Examination May/June- 2025. Download 128.Notifications for reappear examination for UG-2025. Download 129.Additional Time Table for IV &amp; VI Semester B.E theory Semester End Examination May/June- 2025. Download 130.Revised Time Table -June-2025 Download 131.Revised Time Table -June-2025. (AEROSPACE ENGINEERING) Download 132.Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. MBA, MCA, M.Tech I Semester May-2025 Semester End Examination. Download 133.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. VIII Semester JUNE-2025 Semester End Examination. Download 134.Revised Time Table -June-2025 (4TH,5TH,6TH AND 7TH SEMESTER) Download 135.Revised Time Table for VII Semester B.E. Theory Semester End Main Examination - June-2025 ( Re-Appear- 2021) Download 136.Revised Time Table for VI Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2022 batch, Re-Appear- 2021 batch &amp; NON NEP REREGISTRATION) Download 137.Revised Time Table for V Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear- 2022, 2021 batch) Download 138.Revised Time Table for IV Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2023 batch, Re-Appear- 2022, 2021 batch) Download 139.Revised Time Table for III Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear-2023, 2022, 2021 batch) Download 140.Time Table for VII Semester B.E. Theory Semester End Main Examination - June-2025 ( Re-Appear- 2021) Download 141.Time Table for VI Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2022 batch, Re-Appear- 2021 batch &amp; NON NEP RE-REGISTRATION) Download 142.Time Table for V Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear- 2022, 2021 batch) Download 143.Time Table for IV Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2023 batch, Re-Appear- 2022, 2021 batch) Download 144.Time Table for III Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear-2023, 2022, 2021 batch) Download 145.Reschedule of Time Table for VIII Semester Semester End Examination May- 2025. Download 146.Notifications for reappear examination for UG-2025. Download 147.notification regarding Graduation day fee -2025. Download 148.Revised Time Table for VIII Semester B.E. theory Semester End Examination MAY- 2025. Download 149. Notification regarding the submission of applications for Annual Convocation-2024-2025. Download 150.Time Table for VIII Semester B.E. theory Semester End Examination MAY- 2025. Download 151.RE APPEAR Time Table for I Semester MCA, MBA, M.Tech theory Semester End Examination April- 2025. Download 152.Notification Answer Scripts disclosure of III Semester MBA/MCA/M.TECH Students SEE Examination April-2025 Download 153.1st semester Makeup Examinations Time table - APR-2025 Download 154.Circular for Fees and Regulations for Reappear Examination of I Semester P.G (MBA/MCA/M.TECH) Apr -2025. Download 155.Circular for Fees and Regulations for Makeup Examination of I Semester U.G Semester End Makeup Examinations Apr -2025. Download 156.Circular for Fees and Regulations for Photocopy/Revaluation/Challenge Valuation of I Semester U.G Semester End Examinations Feb/Mar -2025. Download 157.Time Table for P.G I Semester M Tech Semester End Examination Apr-2025 Download 158.Time Table for P.G I Semester MCA Semester End Examination Apr-2025 Download 159.Time Table for P.G I Semester MBA Semester End Examination Apr-2025 Download 160.Revised Time Table for VII Semester Makeup Examination - Mar/Apr-2025 Download 161.Revised Time Table for V Semester Makeup Examination - Mar/Apr-2025 Download 162. Revised Time Table for III Semester Makeup Examination - Mar/Apr-2025 Download 163.III SEM MBA REAPPEAR TIME TABLE -MAR-2025 Download 164.Time Table for III Semester Makeup Examinations Mar-2025 Download 165.Circular for Makeup Examination -mar-2025 Download 166.Time Table for V Semester Makeup Examinations -Mar-2025 Download 167.Time Table for III Semester MBA theory Semester End Examination March- 2025.. Download 168.Time Table for III Semester MCA theory Semester End Examination March- 2025. Download 169.Fee and Regulations for RV,CV,Photocopyfor III,V,VII Semester -jan-feb-2025 Download 170.Revised and additional Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025 (2022 reappear). Download 171.Notifications for PG -MBA/MCA. Download 172.Time Table for III Semester M.Tech theory Semester End Examination JAN/FEB- 2025. Download 173.Revised and additional Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan/Feb- 2025 (2021 &amp; 2022 batch only) Download 174.Revised and additional Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025 (2021 reappear). Download 175.Revised and additional Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025 (2022 reappear). Download 176.Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025.(2021 batch re-registration/ reappear) Download 177.Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025.(2016,2017,2018,2019,2020 batch re-registration) Download 178.Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025.(Regular 2024 batch, 2023,2022 batch reappear) Download 179.Revised and additional Time Table for MBA Semester End MAKEUP Examination-OCT-2024 Download 180.Revised and additional Time Table for VI Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 batch &amp; non nep equivalent) Download 181.Revised and additional Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 &amp; 2022 batch only) Download 182.Revised and additional Time Table for III Semester B.E theory Semester End Examination Jan- 2025 (2023 batch regular, reappear 2021, 2022 batch and non NEP batch re-registration) Download 183.Revised and additional Time Table for V Semester B.E theory Semester End Examination Jan- 2025 ( 2022 batch regular, reappear 2021 &amp; non NEP rereg) Download 184.Revised and additional Time Table for VII Semester B.E theory Semester End Examination Jan- 2025 (2021 regular &amp; Non-NEP). Download 185.Circular for Fees and Regulations for Photocopy / Challenge Valuation of PG Supplementary Dec - 2024. Download 186.Revised Time Table for IV, IV and VIII Semester B.E theory Semester End Examination Jan- 2025 ( All Non-Nep batch only) Download 187.Revised Time Table for VI Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 batch &amp; non nep equivalent) Download 188.Revised Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 &amp; 2022 batch only) Download 189.Revised Time Table for III Semester B.E theory Semester End Examination Jan- 2025 (2023 batch regular, reappear 2021, 2022 batch and non nep batch re-registration) Download 190.Revised Time Table for V Semester B.E theory Semester End Examination Jan- 2025 ( 2022 batch regular, reappear 2021 &amp; non nep rereg) Download 191.Revised Time Table for VII Semester B.E theory Semester End Examination Jan- 2025 (2021 regular &amp; Non-Nep). Download 192.Time Table for IV, IV and VIII Semester B.E theory Semester End Examination Jan- 2025 ( All Non-Nep batch only) Download 193.Time Table for VI Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 batch &amp; non nep equivalent) Download 194.Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 &amp; 2022 batch only) Download 195.Time Table for III Semester B.E theory Semester End Examination Jan- 2025 (2023 batch regular, reappear 2021, 2022 batch and non nep batch re-registration) Download 196.Time Table for V Semester B.E theory Semester End Examination Jan- 2025 ( 2022 batch regular, reappear 2021 &amp; non NEP rereg) Download 197.Time Table for VII Semester B.E theory Semester End Examination Jan- 2025 (2021 regular &amp; Non-Nep). Download 198.Circular for extended date of reappearing for the Ensuing Examination UG- (2021,2022,2023 Batch). Download 199.Rescheduling of M.Tech/MBA/MCA Examination reg. Download 200.Notifications for Reappearing for the Ensuing Examination UG- (2021,2022,2023 Batch). Download 201.Reschedule of Time Table for M.Tech Supplementary Examination December- 2024. Download 202.Revised Time Table for Supplementary Examination December- 2024 I,III Semester MCA: Supplementary Examination Dec-2024. Download 203.Revised Time Table for Supplementary Examination December- 2024 I,II,III and VI Semester MBA: Supplementary Examination Dec-2024. Download 204.Time Table for Supplementary Examination December- 2024 III &amp; VI Semester MCA : Supplementary Examination Dec-2024 Download 205.Revised Time Table for Supplementary Examination December- 2024 II and IV Semester M.Tech: Supplementary Examination Dec-2024. Download 206.Time Table for Supplementary Examination December- 2024 II &amp; IV Semester M.Tech: Supplementary Examination Dec-2024 Download 207.Time Table for Supplementary Examination December- 2024 I Semester M.Tech: Supplementary Examination Dec-2024 Download 208.Time Table for Supplementary Examination December- 2024 III &amp; VI Semester MBA : Supplementary Examination Dec-2024 Download 209.Time Table for Supplementary Examination December- 2024 II Semester MBA: Supplementary Examination Dec-2024 Download 210.Time Table for Supplementary Examination December- 2024 I Semester MBA: Supplementary Examination Dec-2024 Download 211.Time Table for Supplementary Examination December- 2024 III &amp; VI Semester MCA : Supplementary Examination Dec-2024 Download 212.Time Table for Supplementary Examination December- 2024 II Semester MCA: Supplementary Examination Dec-2024 Download 213.Time Table for Supplementary Examination December- 2024 I Semester MCA: Supplementary Examination Dec-2024 Download 214.Circular for Fees and Regulations for Photocopy / Challenge Valuation of II semester (PG) Exam Oct - 2024. Download 215.Notifications for Reappearing for the Ensuing Examination PG- MBA/MCA/M.Tech. Download 216.Circular for Fees and Regulations for Challenge Valuation of III to VIII semester of Evening Batch Supplementary Reappear Exam Oct - 2024. Download 217.Time Table for IV Semester M.Tech theory Reappear Examination Nov- 2024. Download 218.Circular for Fees and Regulations for Challenge Valuation of supplementary semester of U.G. 2024 Examination. Download 219.Additional Time Table for III Semester MCA theory Reappear Examination Oct- 2024. Download 220.Additional Time Table for I Semester M.Tech theory Reappear Examination Oct- 2024. Download 221.Circular for Fees and Regulations for Challenge Valuation of I and II semester of U.G. Oct -2024 Semester End Examination. Download 222.Time Table for I &amp; IV Semester M.Tech theory Reappear Examination Oct- 2024. Download 223.Time Table for III Semester Supplementary Examination Oct- 2024 (2022 batch). Download 224.Time Table for IV Semester Supplementary /Re-Appear/ Makeup Examination Oct- 2024 (2022 batch). Download 225.Time Table for III &amp; IV Semester MBA Re-Appear Examination Oct- 2024. Download 226.Time Table for I &amp; II Semester MCA Re-Appear Examination Oct- 2024. Download 227.Time Table for I Semester MBA Re-Appear Examination Oct- 2024. Download 228.Time Table for III &amp; IV Semester MCA Re-Appear Examination Oct- 2024. Download 229.Time Table for Re-Scheduling of I &amp; II Semester Supplementary-2022 batch. Download 230.Time Table for Re-Scheduling of II Semester M.Tech Examination Sep- 2024. Download 231.Additional Time Table for VII Semester theory Supplementary /Reappear Examination Sep- 2024.(Evening Batch) Download 232.Revised Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of IV semester of U.G. Sep -2024 Semester End Examination. Download 233.Time Table for II Semester MCA theory Semester End Examination (Regular &amp; Reappear) Download 234.Time Table for II Semester MBA theory Semester End Examination (Regular &amp; Reappear) Download 235.Time Table for II Semester M.Tech theory Semester End Examination (Regular &amp; Reappear) Download 236.Circular for Fees and Regulations for Challenge Valuation of I &amp; II semester (2023 Batch Supplementary reappear exam Sep -2024) Semester End Examination. Download 237.Notifications for Reappearing and Makeup for the Ensuing Examination UG-2022 batch. Download 238.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of IV semester of U.G. Sep -2024 Semester End Examination. Download 239.Time Table for Revised VI Semester theory Supplementary/Re-Appear/MAKEUP Examination Sep- 2024.(2021 BATCH) Download 240.Time Table for VII Semester theory Supplementary /Reappear Examination Sep- 2024.(Evening Batch) Download 241.Time Table for I &amp; II Semester theory Supplementary Examination Sep- 2024.(2022 BATCH) Download 242.Time Table for revised IV Semester B.E. Supplementary Examination Sep- 2024 (2021 batch). Download 243.Time Table for VI Semester theory Supplementary/ reappear/ Makeup Semester End Examination Sep- 2024.(2021 BATCH ) Download 244.Time Table for VII &amp; VIII Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 245.Time Table for VI Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 246.Time Table for V Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 247.Time Table for IV Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 248.Time Table for III Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 249.additional Time Table for V Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 250.Additional Time Table for III Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 251.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of Re-registered Exams (Evening Batch) of U.G. Aug/Sep -2024 Semester End Examination. Download 252.PG Notifications for Reappearing for the Ensuing Examination (PG). Download 253.Time Table for V Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 254.Time Table for IV Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 255.Time Table for III Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 256.Time Table for I &amp; II Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 257.Notifications and formats for Reappearing for the Ensuing Examination-2021 batch( UG). Download 258.Time Table for Reappear and Makeup Examinations - Sep-2024 (for 2023 Batch). Download 259.Time Table for I Semester MBA Makeup theory Examination Sep- 2024. Download 260.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of I &amp; II Semester (2023 batch &amp; 2022 batch reappear) of U.G. July/Aug -2024 Semester End Examination. Download 261.Notifications and formats for Reappearing for the Ensuing Examination( UG). Download 262.Time Table for additional /revised V Semester B.E. Supplementary/Reappear and III Semester Reappear (NEP) theory Examination Aug- 2024. Download 263.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. &amp; P.G. June/July -2024 Semester End Examination. Download 264.Time Table for III Semester theory Semester End Examination Aug- 2024.(2022 &amp; 2021 BATCH REAPPEAR) Download 265.Time Table for Additional /revised III Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non- Nep batch. Download 266.Time Table for Additional /revised VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non- Nep batch. Download 267.Time Table for I/II Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 268.Time Table for additional /revised VI Semester B.E.</v>
+        <v>About Dr. R. Jayagowri Professor and Head - Department of Medical Electronics Engineering About Department HODs MESSAGE: Welcome to the Department of Medical Electronics Engineering at B.M.S.College of Engineering, Bengaluru. We are the pioneers to start Medical Electronics Engineering in the year 1992 and continued our journey to make the future, the bridge between engineering, biology, and medicine. Medical Electronics Engineering is fostering collaborations among disciplines at its core by building on basic concepts in engineering and biology. We strive to educate where the needs, opportunities, and jobs are and will be in the future. With dynamic changes in healthcare, Make in India Start-ups and global economies it is going to bring a revolution in the healthcare domain. Over the last three decades, we have grown our expertise and competence in the core Medical Electronics Engineering curriculum and research. We have a strong undergraduate program in Medical Electronics Engineering and a postgraduate program in Biosignal Processing and Instrumentation. The primary focus of our curriculum is to impart technical know-how to students, promote their problem-solving skills and innovation of new technologies. The course contents are periodically updated for introducing new technological developments. Students are encouraged to work on various research projects. The department has a distinguished record in both teaching and research and has established an active research profile for carrying out collaborative research with Medtech start-ups and research institutes. To our alums, we welcome your feedback, participation, and ideas to continue to help us move ahead in our educational and research initiatives. We wish to engage you to establish a strong network of support and opportunity for our students and help us map future directions for our program as we mature. About Department: The department of Medical Electronics Engineering was established in 1992 to expand its academic horizon to the fast-growing field of healthcare technologies. The college has laid its focus to impart education in the field of medical electronics and health sciences to translate it into real-world applications. With experienced and well-qualified faculty (90% doctorates), with an average experience of 25 years, the department has been able to contribute a large pool of talented biomedical engineers into the industry. The current intake for the undergraduate programme is sixty, and the department is also offering an M.Tech programme in Biomedical Signal Processing and Instrumentation since 2013 with an intake of 18. With the belief that collaboration is everything, the department has networked with premier research institutes like Stanford University, Oxford University, Maastricht University, Ohio State University, Texas A&amp;M University, Indian Institute of Science, Narayana Nethralaya, Kempegowda Institute of Medical Sciences and many more. The department also has a center for innovation in medical electronics (CIME). It has been set up with the objective of creating a forum for industry, institutions, and hospitals to work together for developing affordable innovative healthcare devices and encouraging faculty/student research-driven entrepreneurship. Department Profile The department of Medical Electronics started in the year 1992 with an intake of 30 students for undergraduate programme. The intake was increased to 60 seats in 2018. The department is accredited by NBA for 6 years.The department of Medical Electronics also has PG programme, M.Tech in Biomedical Signal Processing &amp; Instrumentation (BMSP&amp;I) established in 2013 with an intake of 18. The research areas of the the department majorly include Biomedical Signal Processing, Biomedical Image Processing, Biomedical Instrumentation, Biosensors, Biomedical VLSI, etc. Currently, there are 5 research guides who are guiding students in are of Biomedical and Electronics engineering. Vision To promote quality education in Medical Electronics Engineering for Health and well-being of humankind through teaching and research platforms. Mission To impart knowledge and skills necessary for professional development of graduates in Medical Electronics Engineering. To provide continuous up gradation of technical education with strong academic progression. To propagate creativity, responsibility, commitment and leadership qualities and exhibit professional ethics and values.</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-03-14T06:31:39.615Z</v>
+        <v>2026-03-19T18:34:56.955Z</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://bmsce.ac.in/home/COE-Notifications</v>
+        <v>https://bmsce.ac.in/home/Chemical-Engineering-About</v>
+      </c>
+      <c r="B13" t="str">
+        <v>html</v>
       </c>
       <c r="C13" t="str">
-        <v xml:space="preserve"> Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non- NEP batch. Download 269.Time Table for V Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 270.Time Table for IV Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 271.Time Table for III Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 272.Rescheduling of Examination Aug-2024 for M.Tech IV Semester Civil stream. Download 273.Time Table for Additional /revised VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-NEP batch. Download 274.Time Table for Additional /revised VI Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-NEPbatch. Download 275.Additional/revised Time Table for VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 276.Additional/revised Time Table for VIII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 277.additional/revised Time Table for VI Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 278.Time Table for IV Semester B.E. theory Semester End Main Examination-Aug-2024 (2022 Batch Regular &amp; 2021 Batch Reappear) Download 279.Time Table for VI Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 batch (Non-Nep). Download 280.Time Table for VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 batch (Non-Nep). Download 281.Time Table for Revised IV Semester M.Tech Semester End Main Examination-Aug-2024 Download 282.Time Table for VIII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 batch. Download 283.Time Table for IV Semester PG (MBA) theory Semester End Examination Aug- 2024. Download 284.Time Table for IV Semester PG (M.Tech) theory Semester End Examination Aug- 2024. Download 285.Revised Time Table for I &amp; II Semester theory Semester End Examination July- 2024. Download 286.Circular regarding disclosure of answer Scripts of I Semester PG Students who have obtained 'F' Grade in the SEE Examination Download 287.Revised 2 Time Table for I-II Semester 2021 batch (Re-Appear &amp; Re-Registration) and I/II old scheme re-registration (non-nep) theory Semester End Examination Aug- 2024. Download 288.Time Table for V Semester (Re-Appear) theory Semester End Examination July- 2024. Download 289.Time Table for III, IV and VI Semester theory Semester End Examination (Evening) July- 2024. Download 290.Supplementary Exam Non NEP Batch notification. Download 291.Time Table for VIII Semester theory Semester End Examination July- 2024. Download 292.Reappearing for the Ensuing Examination( UG) 2021 BATCH Download 293.Reappearing for the Ensuing Examination( UG) 2022 BATCH Download 294.Reappearing for the Ensuing Examination( UG) 2023 BATCH Download 295.additional (makeup) and re registration Time Table for VI Semester B.E. theory Semester End Examination June- 2024. Download 296.Additional (makeup) and re registration Time Table for VIII B.E. theory Semester End Examination June- 2024. Download 297.Revised Time Table for VI Semester B.E. theory Semester End Examination June- 2024. Download 298.Time Table for VI Semester B.E. theory Semester End Examination June- 2024. Download 299.Tme Table for III Semester B.E theory Semester End Makeup Examination June- 2024. Download 300.Tme Table for VIII Semester B.E. theory Semester End Makeup Examination June- 2024. Download 301.Tme Table for VII Semester B.E theory Semester End makeup Examination (Second Phase) June- 2024. Download 302.Tme Table for III Semester MBA theory Semester End Makeup Examination June- 2024. Download 303.Revised Disclosure of Answer Scripts of III Semester PG Students who have obtained 'F' Grade in the SEE Examination. Download 304.Revised Time Table for I M.Tech theory Semester End Examination May- 2024. Download 305.Revised Time Table for II Semester MCA theory Semester End Examination May- 2024. Download 306.Revised Time Table for I Semester MBA theory Semester End Examination May- 2024. Download 307.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation for U.G and P G April- May -2024 Semester End Examination. Download 308.Disclosure of Answer Scripts of III Semester PG Students who have obtained 'F' Grade in the SEE Examination. Download 309.Revised Disclosure of Answer Scripts of III Semester UG Students who have obtained 'F' Grade in the SEE Examination. Download 310.Time Table for II Semester (Re appear) PG theory Semester End Examination (MCA) May- 2024. Download 311.Time Table for II Semester (Re appear) PG theory Semester End Examination (MBA) May- 2024. Download 312.Revised Time Table for I and II Semester PG theory Semester End Examination (MCA) May- 2024. Download 313.Revised Time Table for I Semester PG theory Semester End Examination (MBA) May- 2024. Download 314.Time Table for V Semester Re-Registered theory Semester End Examination May- 2024. Download 315.Time Table for I Semester PG theory Semester End Examination (M TECH) May- 2024. Download 316.Time Table for I Semester PG theory Semester End Examination (MCA) May- 2024. Download 317.Time Table for I Semester PG theory Semester End Examination (MBA) May- 2024. Download 318.Notification for Reappearing for the Ensuing Examination (PG -I &amp; II Semester). Download 319.Time Table for VIII Semester theory Semester End Examination May- 2024. Download 320.Makeup Examination Timetable for the 5th semester May-2024 . Download 321.3rd Semester Re registered Time table. Download 322.Makeup Examination Timetable for the 1st semester May-2024 . Download 323.Circular for the Semester End Makeup Examination for I, V Semester B.E April 2024. Download 324.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of I and V Semester U.G. March-April -2024 Semester End Examination. Download 325.Time Table for VII Semester B.E. theory Semester End Examination April- 2024. Download 326.III Semester M.Tech theory Semester End Examination April- 2024(Re-Appear). Download 327.III Semester M.Tech theory Semester End Examination April- 2024. Download 328. Revised VII Semester B.E. theory Semester End Makeup Examination April- 2024. Download 329. III Semester MCA theory Semester End Examination April- 2024 (Re-Appear). Download 330.III &amp; IV Semester MBA theory Semester End Examination April- 2024 (Re-Appear). Download 331.Revised IV Semester ( 2021 batch Re-Appear) B.E. theory Semester End Examination April- 2024. Download 332.Revised III Semester ( 2022 batch regular, 2021 batch Re-Appear and Re-Registration non-NEP batch) B.E. theory Semester End Examination April- 2024. Download 333.Time Table for VII Semester B.E. theory Semester End Makeup Examination April- 2024. Download 334.IV Semester ( 2021 batch Re-Appear) B.E. theory Semester End Examination April- 2024. Download 335.Time Table for III Semester ( 2022 batch regular, 2021 batch Re-Appear and Re-Registration non-NEP batch) Download 336.Time Table for III Semester MCA theory Semester End Examination March- 2024. Download 337.Time Table for III Semester MBA theory Semester End Examination March- 2024 Download 338.Notification for Reappearing for the Ensuing Examination (PG -III &amp; IV Semester) Download 339.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of VII Semester U.G Semester End Examination Jan-2024. Download 340.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of I/II/III and IV Semester (2021 batch) U.G. Supplementary Examination Dec-2023. Download 341.Revised Time Table for the I Semester (2022 batch &amp; 2023 batch) B.E. Theory Semester End Examination Feb/March- 2024. Download 342.Time Table I/II Semester Re-appear (2021 Batch), and the Re-Registered non-NEP batch B.E. Theory Semester End Examination Feb/March- 2024. Download 343.Notification for Reappearing for the Ensuing Examination (UG 2021 batch -III &amp; IV Semester). Download 344.Additional timetable for the V Semester Examination Feb/March-2024 Download 345.Circular Regarding rescheduling of V Semester B.E. Theory Semester End Examination Feb- 2024. Download 346.Time Table for V Semester B.E. Theory Semester End Examination Feb- 2024. Download 347.Notification for Reappearing for the Ensuing Examination (UG 2021 &amp; 2022 batch). Download 348.Circular for Fees and Regulations for Photocopy/Challenge Valuation of Supplementary Semester Examination for MBA/MCA/M.Tech Dec-2023. Download 349.Revised time table for VII Semester B.E. (CIVIL ENGINEERING) Theory Semester End Examination Jan- 2024. Download 350.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of I/II Semester 2022 batch B.E Semester End Examination Dec-2023. Download 351.Revised Time table for VII Semester B.E. Theory Semester End Examination Jan- 2024. Download 352.Additional Time table for VII Semester B.E. (Biotechnology)Theory Semester End Examination Jan- 2024. Download 353.Revised M.Tech timetable for Supplementary Examination Dec-2023. Download 354.Revised MCA timetable for Supplementary Examination Dec-2023 . Download 355.Revised MBA timetable for Supplementary Examination Dec-2023 . Download 356.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of IV Semester B.E Sep/Oct-2023 Semester End Examination and II semester PG Semester End Examination MBA/MCA/M.Tech Oct/Nov-2023. Download 357.Circular for Answer Scripts disclosure of M.Tech II Semester PG Students who have obtained 'F' Grade in the SEE Examination . Download 358.Circular for Answer Scripts disclosure of IV Semester UG Students who have obtained 'F' Grade in the SEE Examination . Download 359.Timetable for the B.E. (Evening College) Supplementary Examination Jan 2024 Download 360.Revised Timetable for the 5TH and 6TH SEMESTER B.E. (Evening College) Supplementary Examination Jan 2024. Download 361.Circular for Reappearing Examination December-2023 for 2021 batch Download 362.Time Table for I/II Semester (2022 scheme) B.E. Supplementary Examination Dec- 2023. Download 363.Revised notification for reappearing for ensuing examinations. Download 364.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of II Semester B.E Sep/Oct-2023 Semester End Examination. Download 365.Answer Scripts of II Semesters UG Students who have obtained 'F' Grade in the SEE Examination are open for disclosure from 27.11.2023 to 29.11.2023. Venue: P.G Block -IV Floor.-Room No.EE 4003 Download 366.Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of MBA IV Semester B.E Sep/Oct-2023 Semester End Examination. Download 367.Timetable for (Re-Registered) IV Semester B.E. Theory Semester End Examination Oct- 2023. Download 368.Timetable for (Re-Registered) III Semester MBA Theory Semester End Examination Oct- 2023. Download 369.Timetable for (Re-Registered) II Semester B.E. Theory Semester End Examination Oct- 2023. Download 370.Timetable for VI Semester B.E. Theory Semester End Examination Nov- 2023. Download 371.Revised Timetable for (Re-Registered) IV Semester B.E. Theory Semester End Examination Oct- 2023. Download 372.Time Table for the Rescheduling of the Examination for III Semester B.E. Theory Semester End Examination (Re-appear) Oct- 2023. Download 373.Time table for II Semester M TECH theory Semester End Examination Oct- 2023. Download 374.Time table for II Semester MCA theory Semester End Examination Oct- 2023. Download 375.Time table for II Semester MBA theory Semester End Examination Oct- 2023. Download 376.Circular Regarding Reschedule of Examination on 26th and 29th of September,14th and 19th of October . Download 377.Circular Regarding Reschedule of Examination on 26th of September. Download 378.ADDITIONAL (4)SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 379.Time Table for I/II Semester B.E Reappear (2021 Scheme) theory Semester End Examination Sep- 2023. Download 380.Time Table for III Semester B.E Reappear (2021 Scheme) theory Semester End Examination Sep- 2023. Download 381.Time Table for II Semester B.E and I Semester Reappear (2022 Scheme) theory Semester End Examination Sep- 2023. Download 382.ADDITIONAL (3)SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 383.ADDITIONAL (2)SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 384.Time Table for IV Semester UG (BE) theory SEMESTER END EXAMINATION SEP/OCT-2023. Download 385.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER /MAKEUP EXAMINATION FOR 5TH AND 6TH SEMESTER SEP 2023 Download 386.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of VI Semester B.E July-2023 Semester End Examination. Download 387.ADDITIONAL SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 388.Answer Scripts of VI Semesters UG Students who have obtained 'F' Grade in the SEE Examination are open for disclosure -CIRCULAR Download 389.Notification for Reappearing for the Ensuing Examination. Download 390.Circular Regarding disclosure of Answer Scripts of VI Semester B.E Students who have obtained 'F' Grade in the SEE Examination July-2023 Download 391.Time Table for IV SEM Semester M.Tech theory SEE Aug-2023 Download 392.Time Table for Revised III Semester B.E theory Makeup Examination Aug-2023 Download 393.Time Table for Revised I Semester B.E theory Makeup Examination Aug-2023 Download 394.Circular for registration fees for SEE Makeup Exam B.E I, II &amp; VIII Semester &amp; I Semester MBA August 2023. Download 395.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of VIII Semester B.E July-2023 Semester End Examination. Download 396.Time Table for IV Semester MBA theory SEE Sep-2023 Download 397.CIRCULAR FOR VIII SEM - MAKE-UP CHALLENGE VALUATION Download 398.III SEMESTER BE (RE-REGISTRATION) Time Table- AUG-2023 Download 399.VIII SEMESTER BE MAKEUP Time Table- AUG-2023 Download 400.I SEM M TECH MAKEUP Time Table- AUG-2023 Download 401.I SEM MBA MAKEUP Time Table- AUG-2023 Download 402.CIRCULAR:The Answer Scripts of VIII Semesters UG Students who have obtained 'F' Grade in the SEE Examination July-2023 are open for disclosure Download 403.CIRCULAR:The Answer Scripts of I Semesters UG Students who have obtained 'F' Grade in the SEE Examination May/June-2023 are open for disclosure Download 404.CIRCULAR:The Answer Scripts of I Semesters PG Students who have obtained 'F' Grade in the SEE Examination May/June-2023 are open for disclosure Download 405.CIRCULAR:The Answer Scripts of III Semesters UG Students who have obtained 'F' Grade in the SEE Examination May/June-2023 are open for disclosure Download 406.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of I Sem and III Semester B.E May -2023 &amp; PG I Sem June-2023 Semester End Examination. Download 407.Time Table for III Semester Semester End Examination - May - 2023.. Download 408.Circular Regarding disclosure of Answer Scripts of V,VII Semester B.E Students who have obtained 'F' Grade in the SEE Examination March-2023 Download 409.Time Table for I and II Semester Semester End Examination (UG-Re appear and re-registration)- May - 2023.. Download 410.Time Table for I Semester Semester End Examination - May- 2023. Download 411.Circular for Fees and Regulations for RT/Photocopy/CV for 5th and 7th semester SEE Semester U.G Feb/March -2023. Download 412.Circular Reg-Rescheduling of Examination-MCA &amp; MBA Mar/April-2023. Download 413.III Semester MCA Time Table for Semester End Examination - March- 2023. Download 414.III Semester MBA Time Table for Semester End Examination - March- 2023. Download 415.Time Table for III and IV Semester Supplementary Examination - March- 2023. Download 416.M TECH Time Table for III Semester SEE - March-2023. Download 417.REVISED Time Table for VII Semester Semester End Examination - Feb/March- 2023. Download 418.REVISED Time Table for V Semester Semester End Examination - Feb/March- 2023. Download 419.Circular Regarding disclosure of Answer Scripts of IV Semester B.E Students who have obtained 'F' Grade in the SEE Examination Jan-2023 . Download 420.Circular Regarding Rescheduling of exam for SEE Examination Jan-2023 . Download 421.Revised Time Table for IV Semester B.E. Theory SEE Examination January- 2023. Download 422.Circular for Fees and Regulations for Challenge Valuation of Supplementary and SEE Semester U.G/P.G December Examinations-2022. Download 423.Circular Regarding Reappear of ensuing Examination . Download 424.M TECH Time Table for I,II and III Semester Supplementary Examination - Dec- 2022. Download 425.Time Table for IV Semester Supplementary/Makeup Examination - Dec- 2022.(ADDITIONAL) Download 426.MBA Time Table for II Semester Supplementary Examination - Dec- 2022. Download 427.MCA Time Table for I and II Semester Supplementary Examination - Dec- 2022. Download 428.Time Table for IV Semester Supplementary/Makeup Examination - Dec- 2022. Download 429.Time Table for III Semester Supplementary/Makeup Examination - Dec- 2022. Download 430.Revised Time Table for B.E. II Semester SEE Makeup Examination November- 2022. Download 431.Circular regarding disclosure of answer Scripts of II Semester M.Tech Students who have appeared in the SEE Examination Oct/Nov-2022 on 26.11.2022. Download 432.Revised IV Semester B.E Students who have obtained 'F' Grade in the SEE Examination Oct-2022 are open for disclosure from 22.11.2022 to 24.11.2022. Download 433.Revised II Semester B.E Students who have obtained 'F' Grade in the SEE Examination Oct-2022 are open for disclosure from 22.11.2022 to 24.11.2022. Download 434.Circular for Fees and Regulations for Re-totaling/Photocopy/Revaluation/Challenge Valuation of II Semester &amp; IV Semester U.G SEE October-2022. Download 435.Circular regarding Semester End Makeup Exam II &amp; IV Semester B.E. Nov/Dec-2022 Download 436.Time Table for I and II Semester Supplementary Examination - Dec- 2022. Download 437.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of M.B.A. &amp; M.C.A. II Semester SEE Examinations -Oct-2022. Download 438.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of M.Tech I Semester SEE Examinations (21-22 ACY). Download 439.Circular Regarding Disclosure of answer scripts for 2nd Semester MBA &amp; MCA OCT 2022 SEE. Download 440.Circular for Fees and Regulations for Re-totaling/Photocopy/Revaluation/Challenge Valuation of VIII, VII, V Semester U.G Supplementary Examinations Sep/Oct-2022. Download 441.II Semester M.Tech Theory SEE Examination October/November- 2022 Download 442.8TH SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE OCT 2022.. Download 443.REVISED Time Table for II Semester MCA. SEE Examination - Oct- 2022. Download 444.Time Table for II Semester MBA SEE Examination - Oct- 2022. Download 445.Revised Time Table for IV Semester B.E. Theory SEE Examination October- 2022. Download 446.MBA Supplementary III and IV Semester Examination Time Table - Sep/Oct- 2022. Download 447.2ND SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) OCT 2022.. Download 448.Circular Regarding Disclosure of answer scripts for 6th semester BE (ALL BRANCHES) AUG 2022 SEE. Download 449.SUPPLEMENTARY EXAMINATION TIME TABLE FOR 2ND,3RD,5TH,7TH SEMESTER B ARCH SEP 2022.. Download 450.SUPPLEMENTARY EXAMINATION TIME TABLE FOR 3RD AND 5TH SEMESTER MCA SEP 2022.. Download 451.REVISED MBA MAKEUP EXAMINATION TIME TABLE FOR 1ST SEMESTER MBA SEP 2022.. Download 452.Notification regd: Reappear for ensuing examination Download 453.SUPPLEMENTARY EXAMINATION TIME TABLE FOR 6TH SEMESTER BE (ALL BRANCHES) SEP 2022.. Download 454.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 5TH SEMESTER BE (ALL BRANCHES) SEP 2022.. Download 455.REGISTRATION FEE FOR MBA MAKEUP EXAMINATION (1ST SEMESTER) SEP 2022.. Download 456.MBA MAKEUP EXAMINATION TIME TABLE FOR 1ST SEMESTER MBA SEP 2022.. Download 457.SEMESTER END EXAMINATION TIME TABLE FOR 3RD SEM BE SEP 2022.. Download 458.REVISED SEMESTER END EXAMINATION TIME TABLE FOR 3RD SEM BE SEP 2022.. Download 459.Time Table for II Semester MCA. SEE Examination - Oct- 2022. Download 460.Circular Regarding Disclosure of answer scripts for M TECH 1ST semester JUNE 2022 SEE. Download 461.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR MBA,MCA FOR 1ST SEM --SEE JUNE/JULY 2022 Download 462.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 8TH SEMESTER BE (ALL BRANCHES) AUGUST 2022.. Download 463.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 7TH SEMESTER BE (ALL BRANCHES) AUGUST 2022.. Download 464.Circular Regarding Disclosure of answer scripts for 1st semester MBA,MCA JUNE/JULY 2022 SEE. Download 465.SEMESTER END EXAMINATION TIME TABLE FOR 4TH MBA AUGUST 2022.. Download 466.SEMESTER END EXAMINATION TIME TABLE FOR 4TH B ARCH AUGUST 2022.. Download 467.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 8TH SEM --SEE JULY 2022 Download 468.6TH SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) AUGUST 2022.. REVISED Download 469.8TH SEMESTER MAKEUP EXAM TIME TABLE FOR BE (ALL BRANCHES) AUGUST 2022. Download 470.Circular Regarding Disclosure of Answer scripts for B.E VIII semester-July 2022 Download 471.Circular Regarding Disclosure of answer scripts for 1st semester M TECH(ALL BRANCHES) JUNE 2022 SEE. Download 472.Circular -FEE STRUCTURE SEMESTER END MAKEUP EXAMINATION FOR 1ST AND 3RD SEMESTER BE (all branches) --MAY/JUNE 2022 Download 473.SEMESTER END MAKEUP EXAMINATION TIME TABLE FOR 3RD SEMESTER BE (ALL BRANCHES) JULY 2022 Download 474.SEMESTER END MAKEUP EXAMINATION TIME TABLE FOR 1ST SEMESTER BE (ALL BRANCHES) JULY 2022 Download 475.SEMESTER END EXAMINATION TIME TABLE FOR 4TH SEMESTER M TECH AND 6TH SEMESTER MCA JULY 2022.. Download 476.8TH SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) JULY 2022.. Download 477.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 1ST SEM --SEE MAY 2022 Download 478.Circular Regarding DISCLOSURE OF ANSWER SCRIPTS FOR 1ST SEMESTER BE (all branches) SEE MAY 2022 Download 479.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 3rd SEM --SEE MAY 2022 Download 480.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 5TH AND 7TH SEM --SEE FEB/MARCH 2022 Download 481.Circular Regarding Disclosure of answer scripts for 5TH semester BE FEB/MARCH 2022 SEE. Download 482.Circular REGARDING REGISTRATION FOR SEMESTER END MAKEUP EXAMINATION FOR BE (all branches)5TH AND 7TH SEMESTER,PG (MBA 3RD SEM,MCA 3RD AND 5TH SEMESTER) --FEB/MARCH 2022 Download 483.Circular Regarding Disclosure of answer scripts for MBA 3RD SEM ,MCA 3RD AND 5TH semester FEB/MARCH 2022 SEE. Download 484.Circular Regarding Disclosure of answer scripts for 7th semester BE FEB/MARCH 2022 SEE. Download 485.Notification regarding Registration for grade improvement exam with registration form.(BOTH UG AND PG) Download 486.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 3RD AND 5TH SEMESTER MCA SEP 2022.. Download 487.REVISED 2ND SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) (OLD SCHEME) SEP/OCT 2022.. Download 488.SEE Time Table for MCA 1st semester - June- 2023. Download 489.SEE Time Table for MBA 1st semester - June- 2023. Download 490.SEE Time Table for M TECH 1st semester (ALL BRANCH)0- June- 2023. Download 491.ADDITIONAL Time Table for VI Semester Semester End Examination - July- 2023. Download 492.ADDITIONAL Time Table for VIII Semester Semester End Examination - July- 2023. Download 493.Revised Time Table for VI Semester Semester End Examination - July- 2023. Download 494.Revised Time Table for VIII Semester Semester End Examination - July- 2023. Download 495.Time Table for 5th Semester Semester End Examination - July- 2023. Download 496.Circular Regd RESCHEDULED of Time Table for III Semester (due to overlapping) Semester End Examination - May - 2023.. Download 497.Circular Regarding disclosure of Answer Scripts of III Semester MBA,MCA Students who have obtained 'F' Grade in the SEE Examination March-2023 Download 498.Circular for Fees and Regulations for RT/Photocopy/CV for MBA,MCA SEE P.G Feb/March -2023. Download 499.Circular for Fees and Regulations for RT/Photocopy/CV for 3rd and 4th supplementary semester SEE Semester U.G Feb/March -2023. Download 500.Time Table for 5th Semester makeup Examination - May- 2023. Download 501.Time Table for 7th Semester makeup Examination - May- 2023. Download 502.Time Table for MBA 3rd semester makeup Examination - May- 2023. Download 503.Circular regarding 23rd annual Convocation Download 504.Circular regarding registration for 5th,7th semester UG &amp; 3rd semester MBA SEE Makeup Exam-2023 Download COEAbout COE OfficeCOE MessageDCOENotificationsResultsCOE StaffMalpractice Rules and RegulationsGalleryContact Us</v>
+        <v>About Dr. Chetan A Nayak Professor and Head - Department of Chemical Engineering About Department The department was started in 1995 by the great visionary, Late B S Narayan. Currently, the department runs an undergraduate course in Chemical Engineering with twelve teaching faculty. The department was NBA accredited for the duration of 5 years in the year 2004. Later the department was accredited for 7 years in the year 2014 under the Washington Accord Format. The NBA had extended the department status of the accreditation until June 2022. Consequently, the NBA accreditation under the Tier-1, 2nd cycle was conducted in Nov 2022, and the department was granted 6 years of accreditation till 30th June 2028. The department has been accredited with the highest grade continuously for three times. The NBA accreditation shows the potential of the department in all respects to meet the needs of the vision and mission at the Institute. The autonomous undergraduate course takes its cognizance from the program-specific criteria established in all reputed institutes offering courses in Chemical Engineering. The well-balanced curriculum includes the titles like Basic Sciences (BS), Engineering Sciences (ES), Professional Core (PC), Professional Electives (PE), Humanities and Social Sciences (HSS), and Project Work (PW). PG in Biochemical Engineering was run between the academic year 2013-14 to 2020-21. Department Profile The undergraduate program started in the year 1995 with an intake of 30. Subsequently, the student intake was increased to 40 in the year 2002 and 60 in the year 2006. The current intake of students is 60. The Department of Chemical Engineering was approved as a Research Centre for Ph.D. and MSc. (Engg.) - research by AICTE in the year 2004. The research centre is affiliated with Visveswaraya Technological University (VTU) and approved by AICTE. Presently, the department has ten doctorate fellows as members of the faculty. One of the faculty members is pursuing PhD at NIT, Warangal, as an external candidate and another faculty member is deputed from the Institution to IIT, Kharagpur on QIP for Ph. D. Four members are awarded doctoral degrees under the research centre. Presently, six research scholars are working for a doctoral degree. And one student has registered for M.Sc. by research under the research centre, Chemical Engineering department, BMSCE. Two of the department faculty members in collaboration with Central Manufacturing Institute, Bengaluru have worked on a project that is now available as technology-ready. Few other faculty members are involved in consultancy work with various industries. One of the faculty members is an expert in NBA accreditation as an evaluator. The department's research facilities include instruments like Gas Chromatography (ionization detector, packed column, and thermal conductivity detector), High-pressure reactor (up to 50 atm. and 500℃), Total Organic Carbon analyzer, Roto Vap, Vacuum Distillation setup, Brookfield Viscometer, Deep Freezer, UV-visible Spectrophotometer, Laboratory Fermenter, Cold Centrifuge, and FTIR, Ultrafiltration test kit, 3D printer, Electroless and electroplating, film coating machine, Ball mill, Lab Centrifuge, Bomb Calorimeter, Muffle furnace, fume hood and silicon oil bath with temperature controller. Vision Be a globally recognized Chemical Engineering Department by imparting quality education. Mission 1. Imparting Quality education and exposure to the budding chemical engineers. 2. Foster and encourage the pursuit of excellence in chemical science and engineering with research potential. 3. Chemical engineering graduates to acquire coveted positions in industries and society</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-03-14T06:31:39.615Z</v>
+        <v>2026-03-19T18:34:57.892Z</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://bmsce.ac.in/home/The-Visionaries</v>
+        <v>https://bmsce.ac.in/home/Bio-Technology-About</v>
       </c>
       <c r="B14" t="str">
         <v>html</v>
       </c>
       <c r="C14" t="str">
-        <v>The VisionariesHomeAbout UsGoverning Body Late Sri. B.M.Sreenivasaiah Founder B.M.S. Educational Trust In the history of Karnataka, the name of Late Businayana Mukundadas Sreenivasaiah (BMS) occupies a prominent place in the field of Philanthropy. The Maharaja of Mysore honored him with the title of Raja Karya Prasaktha in 1946. He started the B.M.S. College of Engineering in the same year. He had forseen the urgent need for high quality technical education in India, even before independence. The ideals for which Sri. B. M. Sreenivasaiah stood, continued to inspire the inheritors of his legacy. Late Sri. B. S. Narayan Donor Trustee B.M.S. Educational Trust After the demise of "Sri. B.M.Sreenivasaiah", his dynamic and enterprising son Sri. B. S. Narayan, took over the reigns of the college. The institution grew from strength-to-strength under his able guidance. He was also instrumental in initiating international collaborative programmes such as training foreign students under International Co-operation Division (ICD) and cross cultural programs with Melton Foundation. Governing BodyThe VisionariesTrusteesBoard of GovernorsGood Governance DocumentsAbout UsAbout BMSCEGoverning BodyAdministrationStaff DetailsStatutory CommitteeExecutive Councile-GovernanceInstitute Industry Interaction Cell (IIIC)Internal Quality Assurance Cell (IQAC)Annual Reports (Finance)Life at BMSCEGroup InstitutionsTendersConsultancy Page</v>
+        <v>About Dr. Saisha Vinjamuri Professor and Head - Department of Biotechnology About Department The Department of Biotechnology offers BE in Biotechnology. The department has well qualified, experienced, trained and committed faculty to provide quality education. The Department has adequate infrastructure and being funded by Department of Biotechnology, Govt of India under the DBT- STAR College scheme for better hands on learning experience for the students. Many faculties pursue research in several areas of biotechnology with externally funded research grants from DST, Govt of India , DBT and VGST, govt. of Karnataka. Department Profile Department of Biotechnology started in the year 2002 with an intake of 30 students for the undergraduate programme. The intake was increased to 40 seats in 2007, to 60 in the year 2018. UG programme of the Department is accredited by NBA tier1 of Washington Accord for 6 years with validity up to June 2028. The department has 10 faculty members with considerable teaching &amp; research experience and being supported by well-trained supporting staff. Research Centre of the department is well equipped with high end equipment. Thrust areas of research are Cancer research, natural products, plant tissue culture, neuroscience, enzymes, waste water treatment, food wastes to energy, batteries, food nutraceuticals and computational biology. Currently, there are five recognized faculty from VTU and Mangaluru University. Six Ph.D scholars are pursuing research from the department. The department has currently MOUs with Swakit Biotech private limited, Bangalore, India and Apratima Bisolutions private limited . Vision To be a Centre of excellence in the field of Biotechnology equipped to create graduates who endeavor for the welfare of mankind. Mission To impart quality education for life long professional growth and opportunity in a wide range of Careers. To create awareness towards socio-ethical implications of potentials of Biotechnology.</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-03-14T06:31:40.539Z</v>
+        <v>2026-03-19T18:34:58.725Z</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://bmsce.ac.in/home/About-BMSCE</v>
+        <v>https://bmsce.ac.in/home/Computer-Applications-MCA-About</v>
       </c>
       <c r="B15" t="str">
         <v>html</v>
       </c>
       <c r="C15" t="str">
-        <v>About BMSCEHomeAbout Us Vision Promoting Prosperity of mankind by augmenting human resource capital through quality Technical Education &amp; Training. Mission Accomplish Excellence in the field of Technical Education through Education, Research and Service needs of Society. B.M.S. College of Engineering (BMSCE) Bengaluru has the unique distinction of being the first private engineering college established in the country. Started in the year 1946, the institution owes its existence to the vision of its beloved founders, Late Sri. B. M. Sreenivasaiah and his illustrious son Late Sri. B. S. Narayan. Over the past 77 years of its illustrious existence, BMSCE has produced more than 40,000 graduates who have enriched the world through their immense contributions as engineers or leaders for mankind. The Institution is approved by All India Council of Technical Education (AICTE) and permanently affiliated to Visvesvaraya Technological University (VTU), Belagavi. The college is aided by Government of Karnataka. BMSCE is approved as QIP Centre in Engineering &amp; Technology by AICTE. The College became autonomous, UGC approved, in 2008 and has been effectively practicing Outcomes-based Education. The College has the distinction of being awarded best performance rating in all three Phases of TEQIP. The institution is also a Beneficiary of Global Initiative Academic Network (GIAN). BMSCE is the only Partner institution in the country of the Melton Foundation, USA which promotes cross cultural learning for the selected students along with peers from five other countries. The College is accredited by National Assessment and Accreditation Council (NAAC) with the highest grade of A++ in the Second Cycle and a CGPA of 3.83 on a scale of four. Currently all the Undergraduate Programmes and post-Graduate Programmes hold the status of Accreditation from National Board of Accreditation (NBA), New Delhi in tier I Format. AICTE has recognized the college under AICTE Doctoral Fellowship Scheme (ADF) since 2018-19. BMSCE is listed as a lead innovator for the year 2020 and 2021 by Clarivate Analytics (Web of Science) based on the Derwent World Patent Index. In the ARIIA (ATAL Rankings) 2021, the college is ranked in band-Excellent. BMSCE is one of the 100 colleges in the country awarded 5G use case laboratory. The College currently offers 17 Undergraduate &amp; 15 Postgraduate courses both in conventional and emerging areas. More than 344 research scholars are pursuing their Ph.D Degree in the 14 research centres of the college. 244 PhDs and 22 M.Sc. (by research) have been produced so far through these research centres. BMSCE has recently achieved the prestigious ISO 14001:2015 certification for its Environmental Management System through qualified external ISO 14001 auditors. The Institution has MOUs with various organizations across the globe. It has developed many Centres of Excellence, cutting edge laboratories and incubation centres in collaboration with industries with an aim to enrich the learning experiences of the graduating students and to comply with the programme outcomes. The learning experiences and quality educational practices created at the institute supplemented with academic ambience, state of the art infrastructure, pedagogy, academic innovations, research, incubation, training opportunities and entrepreneurship provided to diverse student population is enabling the institute to produce graduates who are industry ready. BMSCE is one of the most preferred higher educational destination for the students all across the country and also attracts students from various countries. The institution has played significant role in developing human resource capital to meet the requirement of society in India and abroad. The College has one of the largest student populations amongst engineering colleges in the state of Karnataka. The academic performance of the students has been exceptional. The Institution has an excellent Training and Placement Cell. More than 350 reputed companies visit the campus every year. The College results and placement bear testimony to the high standard of education provided by the institution. The academic processes are developed with due weightage to provide skills through project-based learning model. Curriculum design &amp; development, Pedagogy and Assessment are given highest priority. The institution has consciously put efforts in encouraging innovation and has adopted best practices/processes in Teaching Learning Processes. In order to enhance the learnability of the students and to make them industry ready by bringing down the gap, technology tools, self-learning, social learning, MOOCs, internships/industry training are introduced as a part of the curriculum. The faculties are well qualified, experienced and highly dedicated. Many of whom have the distinction of being NBA, NAAC Evaluators, Members of BOS, BOE, LIC, AICTE, governing bodies of VTU etc. Faculty members have received numerous awards for their teaching, research, and public service also for their contribution in finding suitable solutions to environmental challenges. The institution has adopted best practices and key principles of good governance in all its administrative procedures. The Institution has received many Distinctions/Awards in recognition of its contribution in the field of Technical Education. The college is being ranked consistently among the top engineering colleges in the country by various media sources. About UsAbout BMSCEGoverning BodyAdministrationStaff DetailsStatutory CommitteeExecutive Councile-GovernanceInstitute Industry Interaction Cell (IIIC)Internal Quality Assurance Cell (IQAC)Annual Reports (Finance)Life at BMSCEGroup InstitutionsTendersConsultancy Page</v>
+        <v>About Dr. S. Uma Professor &amp; Head - Computer Applications About Department The Department of Computer Applications (MCA) was established during 1984-85 when computer science education was in its infancy in India. The department offers a Master in Computer Applications programme with an autonomous curriculum for students in the field of applied computer science and technologies. The MCA programme was started with an initial intake of 30 and later enhanced to 60. The MCA Programme duration was previously 3 years till the academic year 2019-20. However, starting with the academic year 2020-21, it has been reduced to 2 years with an intake of 60. The present intake of the MCA programme is 120 students from the academic year 2023-24. The Master of Computer Applications (MCA) program has been accredited by the National Board of Accreditation (NBA) for a period of five years (2019–2024). This prestigious quality recognition reflects the program’s commitment to academic excellence, robust curriculum design, qualified faculty, state-of-the-art infrastructure, and effective implementation of Outcome-Based Education (OBE) practices. Further, the Accreditation has been extended till 31st June 2025. The MCA program has been reaccredited by the NBA for an additional period from 1st July 2025 to 31st December 2025, and from 1st January 2026 to 31st December 2028. This continued recognition reaffirms the department’s consistent effort towards maintaining high academic standards, continuous quality improvement, and alignment with global benchmarks in postgraduate computing education. The accreditation reflects the department’s dedication to quality enhancement, innovation, research orientation, and fostering graduates equipped with strong technical, professional, and ethical values to contribute effectively to the computing industry and society. The strengths of the department are its Alumni, Faculty, staff members, and students. Our alumni have esteemed positions in prominent industrial and academic organisations.. The department has dedicated, committed, and accomplished faculty members supported by technical &amp; administrative staff. members. The Department of Computer Applications has been recognized as a research center by VTU. There are 5 research supervisors guiding research scholars in the areas of Data Science, Machine Learning, Software Engineering, Web Services, Computer Networks, IoT, etc. About the Curriculum The focus of the department curriculum is to provide a holistic learning approach. The curriculum covers fundamental concepts and aims to build learning abilities spanning various concepts and modern, emerging technologies. The curriculum encourages students to keep their minds and body fit with physical activities, yoga, meditation, etc. Students are allowed to improve their skills on the self-paced online courses on the MOOCS platform. Further, the curriculum includes Internships, Projects, Mini-projects, Soft Skills, Industry visits, and Emerging technologies like Machine Learning, IoT, Big Data, Block Chain, Agile methodologies, etc. The department has collaborations with the Ministry of Micro, Small &amp; Medium Enterprises (M/o MSME), Bangalore, Medha Tech Solutions Pvt. Ltd, and Vande Foundation. The department has a state-of-the-art Computing Lab with more than 100 modern PCs and an exclusive department library with over 6500 books and access to various journals &amp; conference proceedings. In addition, the department has developed an Innovation Cluster Lab (ICL) supported by Industry Experts and a Data Analytics and Research Lab (DAR) to promote lifelong learning, innovation, and research. The students are encouraged to participate in extracurricular &amp; co-curricular activities along with regular academic activities to groom their holistic personalities. The skill set of students is enhanced through regular Hackathons, Extension Lectures, workshops, Industrial Visits, Alumni Interactions, and professional body activities. The department brings out the magazine ‘Stride’ annually to showcase the innate talents of the students. The College attracts hundreds of companies every year to provide jobs to our students. Most of the eligible students get placed in reputed companies. The quality of our students is reflected in their placement track record (both on Campus &amp; off Campus) and the applications developed by them. Learning is a continuous process and does not end at the end of three years. The department believes that innovative teaching-learning methods, coupled with problem-solving using modern tools &amp; self-study help the students to enhance their skills and enable them to handle them in their personal and professional lives. Vision To emerge as a premier knowledge center for imparting education in Computer applications. Mission M1: To empower students with knowledge, skills and attitude to develop competency in computer applications through a well-defined curriculum. M2: To engage in research and development leading to publications/start-ups. M3: To enhance active collaboration with Industry.</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-03-14T06:31:41.523Z</v>
+        <v>2026-03-19T18:34:59.373Z</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://bmsce.ac.in/home/About-R-and-D</v>
+        <v>https://bmsce.ac.in/home/Management-Studies-and-Research-Centre-About</v>
       </c>
       <c r="B16" t="str">
         <v>html</v>
       </c>
       <c r="C16" t="str">
-        <v>About R &amp; DHomeResearch Dr. Chandasree Das Head, R &amp; D RESEARCH &amp; DEVELOPMENT CENTRE R&amp;D Center involves in identifying new research areas, developing projects leading to publications in National/International Journals and conferences. Established an R&amp;D center at the Institution level to promote Research &amp; Innovation among the faculty &amp; students. The center helps in developing co-operative and complimentary research among various Departments under BMSCE to explore advanced technologies. The Centre acts as the liaison between the University (VTU and Mangalore University) and the research centers at BMSCE. The Centre also guides and facilitates in writing of project proposals, and scientific papers leading to publication as well as in identifying the research outcomes of research for filing patents. Since academic autonomy, the Institution has provided with an excellent opportunity to create, revise, redesign or introduce innovations in the curriculum. Threading this path, the Institution foregrounded the concept of research amongst the students from the first year of their program. The Centralized labs and design centers titled propel labs were established for nurturing research from the first year of engineering. These labs are broad based and not confined to a single area/discipline. Student groups (multidisciplinary) work on various engineering projects in these labs - concept to designing the prototype. The Propel labs are open for students of all disciplines with no terms or conditions attached. Each Lab is headed by a faculty and supported by competent technical staffs who volunteer to act as mentors for the students and ensure that students conduct the research. Creative thinking skills of the students and mentoring by faculty guides result in the development creating systematic processes and products. These research labs help the students to build prototypes which enable them to participate in competitions both in India &amp; Abroad. IRINS Portal link: https://bmsce.irins.org/ Sl. No Research Center (Year of estb.) No. of Guides Ph.D Registered Ph.D Awarded M.Sc Awarded 1 Civil Engineering (2002) 24 64 33 14 2 Mechanical Engineering (2002) 34 34 34 2 3 Electrical and Electronics Engineering (2002) 15 27 13 0 4 Electronics and Communication Engineering (2002) 24 69 22 1 5 Industrial Engineering and Management (2002) 3 8 3 2 6 Chemical Engineering (2004) 5 4 4 1 7 Mathematics (2004) 11 18 5 0 8 MBA (2004) 8 25 19 0 9 Biotechnology (2009) 6 4 5 2 10 Computer Science and Engineering (2010) 13 34 20 0 11 Information Science and Engineering (2011) 9 22 6 0 12 Physics (2011) 6 7 4 0 13 Chemistry (2011) 8 10 7 0 14 Electronics &amp; Telecommunication Engineering (2013) 6 9 1 0 TOTAL 172 335 176 22 ResearchAbout R &amp; DR &amp; D CommitteeStaffApplication DownloadsResearch CentersInnovative LabsFunded Research ProjectsMoU's With Industries &amp; Research CenterList of Ph.D AwardedList of M.Sc AwardedPh.D Enrollment in Reseach CentresB S Narayan Ph.D FellowshipB S Narayan Centre for Nano-Materials &amp; DisplaysJournal PublicationsPatents FiledGalleryIRINS PortalContact Us</v>
+        <v>About Dr.Minu Zachariah Professor and Head - Department of Management Studies and Research Centre About Department The Department of Management Studies &amp; Research Centre is accredited by NBA (National Board of Accreditation). It was started in the year 1992 with an objective of imparting quality Management Education. With an initial intake of 60, the Department increased its intake to 120 in the year 2011 and to 180 in the year 2024. It was approved as a Research Centre in the year 2004 by VTU, Belgaum. The Department has been striving to offer quality Management Education through a team of qualified and experienced faculty members. It also offers various value added programmes such as guest lectures, seminars, workshops, case based learning, course assignments, meet the CEO series, industrial visits etc., to prepare the students to face the challenges in the corporate world. The program focuses on holistic development of students in addition to instilling excellent managerial skills and leadership qualities, which are essential to succeed in a globalized economy. The students also get an experience in organizing a Management Event through ‘QUEST’ which is an inter-collegiate event organized by the department. The International Conference organized by the department gives the students an opportunity to do research &amp; publish papers. The Department has an exclusive placement cell to handle training needs of the students, project and final placements. Vision Develop leaders through quality Management Education, Research and Entrepreneurship contributing to the society. Mission 1. To enhance the knowledge and capabilities to meet global challenges through suitable curriculum. 2. To be concerned and connected with the societal issues. 3. To foster collaborative contributions through training. 4. To inculcate sense of professional ethics, commitment and integrity.</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-03-14T06:31:42.464Z</v>
+        <v>2026-03-19T18:35:00.043Z</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://bmsce.ac.in/home/About-Placements</v>
+        <v>https://bmsce.ac.in/home/Mathematics-Department-About</v>
       </c>
       <c r="B17" t="str">
         <v>html</v>
       </c>
       <c r="C17" t="str">
-        <v>About PlacementsHomePlacements Dr. J. Sharana Basavaraj Professor Dean, Training and Placement Years of experience: 28 Phone: +91-80-22423789, +91-80-26603936 Email: placement@bmsce.ac.in Dr. K.R.Sudhindra Professor Associate Placement Officer Years of experience: 18 Phone: +91-80-22423789, +91-80-26603936 Email: placement@bmsce.ac.in Dr. Nandhini Vineeth Professor Associate Placement Officer Years of experience: 17 Phone: +91-80-22423789, +91-80-26603936 Email: placement@bmsce.ac.in B.M.S College of Engineering has authored and set many examples of yeomen student centric initiatives. One such initiative is the Department of Training and Placement. The Institution ﬁrmly believes that placements are the major benchmark to the performance of the institute. The placement cell is the nodal center and an integral part of the institution. Started during 1995 it has scaled great heights and touched about 18500+ cumulative offers since its inception. The centre has very active linkages and collaborations with industry. The centre helps students in pursuing their career interests and also assists the employers in achieving their hiring goals. The vital roles of the Centre is to groom and shape the students and make them industry ready by imparting necessary skills and training. More than 350 reputed National and Multinational companies visit our institution for campus recruitment annually. The department facilitates training programs on soft-skills and technical talks from industry experts. Online mock assessments on quantitative aptitude and competitive coding are conducted for the benefits of students. The centre offers state-of-the-art physical, communication and computing infrastructure for its effective functioning. Our highly skilled and dedicated staff will deliver precisely planned services to the student community and companies. Our highly skilled and dedicated staff will deliver precisely planned services to the student community and companies. Vision To emerge as a most preferred destination for all corporates to hire globally competent and ethically strong engineering talent. Mission To nurture fresh talent to be industry ready by conducting purposeful and value added teaching and training. To identify the right career option for the students in tandem with their skills, personal values and interest. To strive hard to enhance the employability of students and meet the aspirations of the students and corporate community. To facilitate students to acquire contemporary and futuristic skills. Process The placement ofﬁce shall establish network and build relations with potential recruiters. Invitation will be sent to potential recruiters to visit the Institute. The placement team communicates the dates for campus visit for each recruiter by considering factors like student preference, job proﬁle etc. Companies are encouraged to give pre-placement talks before the commencement of recruitment process. The companies conduct different rounds of selection process (aptitude test, group discussion, technical interviews and HR interviews) and inform the names of selected students to the placement department. The same shall be communicated to the concerned students and take acceptance from students. The placement ofﬁce conducts general follow-up, joining formalities and other administrative activities. Message from Advisor In the emerging and fast changing world, there an obvious need to produce graduates high level of adaptability, and who are innovate enough to face the diverse challenges. B.M.S.C.E has been promoting quality engineering education over the past seven decades to meet the develpment needs of the country. The institution seeks to provide best possibile opportunities to its students and make them ready to enter the industry portals. Rigorous sylabus and practival industry exposure has instilled confidence in our students to face real-time problems. The Training &amp; Placement Centre strongly believes that each student is a valuable resource and focuses in maximising their career prospects by providing comprehensive career solutions. I thank all the stake holders for their sustained support to the institution and look forward for stronger and deeper relationship. My best wishes to the student community. Dr.H S Jagadeesh Advisor Message from Dean,Training and Placement Dear Recruiter, BMSCE has a rich tradition of producing professionally competent graduates by providing value-based and quality education. The Institution ensures that they are adaptable to ever changing demands and requirements of the world. Seven decades and counting, BMSCE graduates go through an updated, balanced but rigorous program. The teaching methodology has high focus on self-learning and practice. The outcome-based curriculum design and teaching method adopted by the Institution focuses on learning outcomes where the emphasis is on what a student is able to learn and do after the learning activity. The Institution has been embarking the syllabus by bench-marking with the syllabus of reputed institutions like NIITs, etc. BMSCE also provides its students a wide range of training programmes aimed at enhancing their employability skills, as well as providing them with many curricular and extra-curricular events to ignite their minds. We are confident that our graduates would be able to adapt to various challenging situations and fulfil the organisational objectives. I am sure that our students will turn out to be assets to your organisation. With great honour and pride, I take this opportunity to extend a warm invitation to the recruiters and hope that we will enjoy a mutually beneficial relationship. Dr.J. Sharana Basavaraja Dean, Training and Placement Message from Associate Placement Officers, Training and Placement BMSCE has a strong rooted belief in quality education and responsibility in making every student industry ready. The Training &amp; Placement Centre equips its students with skills that will help them contribute almost immediately to the organizations that they join. The centre regularly interacts with the industries to increase the employment opportunities of the students and also increase their awareness on realtime working environment. We highly appreciate the confidence reposed in us and the invalueable support extended by our recruiters over the years. You are our biggest strength and we seek your continued patronage at all times. We are confident that recruiters looking for talented pool of people will be greeted with young, bright and aspiring minds. Dr. K.R.Sudhindra, Dr. Nandhini Vineeth Associate Placement Officers PlacementsAbout PlacementsPlacement TrainingPlacement AchievementsStaffPlacement StatisticsPlacement ActivitiesRecruiting CompaniesGalleryContact Us</v>
+        <v>About Dr Rangaswamy Associate Professor and Head - Department of Mathematics About Department The Department of Mathematics was established in the year 1946. The Department has faculty strength of 32 members (3 Professors, 2 Associate Professor and 27 Assistant Professors). Twenty five of them have doctoral degree and seven are pursuing their Ph.D. program. The department offers courses for both UG and PG Programs. The department is recognized as one of its research centers by the VTU during 2004. Apart from regular teaching, the faculties are involved in research and many faculties are recognized as research supervisors at VTU. The department is running externally funded projects from STARS/IISc, Ministry of Education, Bangalore and VGST. Eight research scholars are awarded Ph.D. degree and currently Fifteen persons are perusing part time Ph.D. program. The thrust areas of research of the department include Fluid Mechanics, Mathematical modelling, Integral transforms, Number theory, Graph theory, Functional Analysis and Differential Geometry . Faculties have published many research papers in reputed peer-reviewed journals as well as presented their work in several national and international conferences. Based on the needs of various disciplines, the department is imparting the updated curriculum from time to time. With the available expertise, in addition to offering the core courses during the first four semesters of BE programs, is offering 4 electives at the Institutional level during the third and fourth year of BE program. Vision Be one of the leading centers for teaching &amp; research in Mathematics Mission Encourage analytical, independent, rational thinking and enhance problem solving skills of the students</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-03-14T06:31:43.411Z</v>
+        <v>2026-03-19T18:35:00.687Z</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://bmsce.ac.in/home/About-Library</v>
+        <v>https://bmsce.ac.in/home/Physics-Department-About</v>
       </c>
       <c r="B18" t="str">
         <v>html</v>
       </c>
       <c r="C18" t="str">
-        <v>About LibraryHomeFacilitiesLibrary Libraries are established for the systematic collection, organization, preservation and dissemination of knowledge and information. It is very important for man to preserve and maintain the valuable knowledge and information contained in the books and documents because we want to preserve our knowledge and wisdom for the coming generations. By preserving the documents in a library this knowledge can be made available to others so that they can benefit from it. Libraries play a vital role in the development of any society by enhancing the cause of education and academic research. They cater to the information needs of thousands of peoples. Location The library is aesthetically located in a central place of the college and is very prominently housed in a big and spacious building with a floor area of 4200 Sq. mts (45200 Sq.ft). Mission The mission of BMSCE Library is to seek, create, communicate and preserve knowledge and understanding and carryout the mission in a unified community known as College. The library, in support of the educational and research mission of the college, is the local repository and the principal gateway to current information and the scholarly record. As such, it is simultaneously collection and connection for the current and future students and faculty of the college. Vision It is an information hub of academic community and a center of unbridled intellectual inquiry. A place where the past converges with the present and the road to the future is littered with every imaginable tried ideas and tested theory. Objective To develop a collection of documents (both in print and in electronic form) and keep them up to date in accordance with growing needs of users of today and tomorrow. To support academic programmes of the parent institution by providing necessary reading materials. To provide individual and group guidance to readers in making maximum use of Library resources. To encourage students to develop skills for self-education, which can sharpen their intellect and can contribute for their personality development. To support teaching staff in their teaching and research activity. To conduct user education programmes to train students and staff in making effective use Library resources. E-Library Facilities The Digital library provides On-line access to 27 e-resources on Science and Technology for studies and research, and has access to 12499 e-journals &amp; 51662 e- books on various branches of Science, Technology, Engineering &amp;, Management. Library also subscribes 84 National and International printed journals. Provide access to all streams of Question Papers through Digital Software–TechFocuz via Intranet. Subscribed to NPTEL lectures are streamed using Internet View Central Libray LibraryAbout LibraryAutomated ServicesIssue of BooksPrinted JournalsE-JournalsE-ResourcesLibrary EventsSwayam NPTEL - LCLibrary ServicesWorking HoursLibrary StaffRule Governing LoansStatisticsGalleryContactFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About Dr. B. L. Suresha Associate Professor and Head - Department of Physics About Department The Physics Department at BMS College of Engineering was established in 1946. The vision of the department is to be a dynamic, inclusive and competitive center of excellence in teaching, learning and research in Physics to ensure that the technical needs of engineering students are addressed. The Department has well qualified, experienced and highly motivated faculties. The faculties of the Department teach Applied Physics course for I year B E students. Department is offering open elective and institutional elective courses to higher semester students. Department faculties are involved in research and consultancy activities. They have received funding for conducting research from various external funding agencies such as DST, VGST, BARC etc. The department is a recognized research center under VTU since 2011 and under Mangalore University since 2018. Vision To be a dynamic, inclusive and competitive center of excellence in teaching, learning and research in Physics to ensure that the technical needs of students are addressed. Mission To provide quality basic education and training in Physics.</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-03-14T06:31:44.359Z</v>
+        <v>2026-03-19T18:35:01.322Z</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://bmsce.ac.in/home/Innovative-Labs</v>
+        <v>https://bmsce.ac.in/home/Chemistry-Department-About</v>
       </c>
       <c r="B19" t="str">
         <v>html</v>
       </c>
       <c r="C19" t="str">
-        <v>Innovative LabsHomeResearch PROPEL LAB – I (ROBOTICS AND EMBEDED SYSTEM LAB) Mr. Harish V Mekali hvm.ece@bmsce.ac.in Coordinator Mr. Girish K gk.mca@bmsce.ac.in Coordinator The lab provides a platform for students having interest in the field of Robotics and Embedded Systems. Major projects in the lab are related to the Machine Learning in Robotics space and Internet of Thing(IoT) in Embedded Systems. Through these projects students get to experience the depth of technologies. Students in here learn how to program a micro-controller, design a robot using many equipment’s which are at the disposal of propel lab. The students pass on the knowledge gained by working in the lab to their juniors by conducting workshops and competitions. Lab also facilitates academic and funded projects. Lab is supported by many industries and organizations like, ARM Ltd, Mediatek Labs, Nuetech Solar Systems Pvt. Ltd., ALS, and IIT – Bombay. At present we have 3 patents pending, 1 copyright, 7 international and 6 national publications. We have also received more than 10 awards from prestigious organizations like TCS, ARM, TI, IITB, and ONGC. We have youtube channel: Experiments@BMSCE. PROPEL LAB – II (3 D PRINTING) Arpitha KV Coordinator Background: In June 2014, our state-of-the-art 3D Printing Lab was inaugurated. The event was graced by esteemed figures including Dr. B. S. Ragini Narayan, Donor Trustee of BMSET, Dr. U. Chandrashekar, Former Additional Director at GTRE Bangalore, and Sri M. Krishnaswamy, Retired Project Director of ISRO, along with numerous dignitaries. Since its inception, the lab has supported over 400 projects, showcasing its versatility across various automotive, architecture, aerospace, and electrical &amp; electronics industries. During the COVID-19 pandemic, the lab leveraged IEEE grants to initiate six innovative projects to combat the virus, further exemplifying our commitment to technological advancement and societal contribution. As a cutting-edge technology known as Additive Manufacturing, 3D printing allows users to create and manufacture designs in three dimensions with minimal or no post-processing, revolutionizing traditional manufacturing practices. With only three decades of development, this technology holds immense potential for research and innovation, and there is a growing demand for trained engineers, operators, and designers in this field. The lab currently features a diverse array of 3D printers, including the Creality Ender3 V3 SE, Makerbot Replicator Z18, Adventure FlashForge 3, Wol3D I Maker, and X-Smart. These state-of-the-art machines enable students and researchers to explore a wide range of applications and push the boundaries of creativity in their projects. Facility: PROPEL LAB – III (AEROSPACE LAB) Sri.Ram Rohit V Coordinator Sri K. Satyanarayana Reddy Technical Staff The facility of Aerospace lab was inaugurated in the year 2012 by Dr.Roddam Narasimha and Wing Commander D P Sabarwal. Since, Aero BMSCE is participating in various National and International Aero Design competitions. Our Aim: To Create Awareness about the Exciting Fields of Aviation and aerospace. To encourage UG Students to take up R&amp;D, Innovation and Entrepreneurship. To provide the opportunity for students to use their learning to solve complex engineering challenges, through projects and competitions. What we do at Aero BMSCE: Aero BMSCE is a student team working on complex engineering challenges, such as designing aircrafts to perform according to required parameters such as reducing empty weight and maximizing weight of payload carried. We work on innovative projects to promote interdisciplinary research. We have completed many projects such as Project Kalam, Quadcopter Project, etc. We also participate in National and International Aero Design Competitions, which have different problems to be solved. Facility: Laser Machine (Cutting &amp; Engraving) 3Axis. CNC Milling Machine. Fat Shark Attitude SD Goggles with MIG v5 Head Tracking. Grupuner MZ-24 12 Channel Transmitter. Turnigy HD Wi-Fi Camera. Dremel 4000 machine. Stanley 53 Set tool box. Turnigy Thrust Measuring Stand. Two Sky surfer trainer planes. Apple Work station (Design, Analysis, and Report etc.). Bosch GLM 80 Laser Rangefinder. Air compressor for laser machine. Water chillier for laser machine. Oxygen cylinder for laser machine. Achievements of the Team Secured in the first prize(One lakh) overall (micro) in SAE India competition March 2020, Anna University, Chennai. Participated in Technoxian Quadcopter Challenge 22nd to 25th September 2019, New Delhi. Participated in SAE Indian Southern Section 2019, Anna University, Chennai. Overall 3rd rank, 2nd place in a design report, in SAE India Southern Section 2018, Anna University, Chennai. Secured 23rd rank in SAE Aero Design East 2018 held in Lake Land, Florida, USA. Best innovation in the micro class of Manovegam Aero Championship 2017 in SAE India held at SIT Tumkur. 17th place out of 30 teams in Boeing 2017 held at IIT Madras. Secured 14th rank in SAE Aero Design East 2016 held in California, USA. 2nd place in Boeing competition out of 174 teams across India. Secured 13th rank in SAE Aero Design West 2016 held in California, USA. Secured 14th rank in SAE Aero Design West 2015 held at Los Angeles, USA. Secured 15th rank in SAE Aero Design West 2014 held in Texas, USA. Secured 18th rank in SAE Aero Design West 2013 held at Los Angeles, USA. Best presentation at IITM Shaastra 2013. Secured 23rd rank in SAE Aero Design East 2012 held at Atlanta, USA. 1st place at NIT Trichy 2012. 1st place at NIT Warangal 2012. 1st place at IIT KGP Kshitij 2012 Laws of Motion. 3rd place at IITM Shaastra 2011 Wright Design. 1st place at IITM Shaastra 2011 Top Gun. PROPEL LAB - IV (SAE BULLZ RACING) Dr. Rathanraj K J Sri. RAJESH. P Bullz Racing founded in the year 2010, is the Automotive engineering division of BMS College of Engineering, Bangalore. We are an all-student collegiate club of SAEINDIA, strategic alliance partner of the Society of Automotive Engineers, or SAE International. We primarily intend to take the experience of engineering beyond four walls and into the real world. We are a team of young, hungry and eager students from various disciplines of engineering. Over the years, we have participated in various National Level engineering competitions and have carved a niche for ourselves. This is where ardour shall strive as we do what we’re best at: Innovation and Its Application. 2011: First Car – Best Design Award Baja SAE - Korea 2017: First Go-Kart: Top 20 out of 150 teamsat NKRC 2017 2015: First Electric Car – 7th Place Overall Mahindra Baja SAE 2015 2017: 3rd Place Overall Mahindra Baja SAE 2015 PROPEL LAB - V (BSNCSIS) Dr. Anil Chandra Sri. Sreenivas Murthy Dr. Rathan Raj K J ResearchAbout R &amp; DR &amp; D CommitteeStaffApplication DownloadsResearch CentersInnovative LabsFunded Research ProjectsMoU's With Industries &amp; Research CenterList of Ph.D AwardedList of M.Sc AwardedPh.D Enrollment in Reseach CentresB S Narayan Ph.D FellowshipB S Narayan Centre for Nano-Materials &amp; DisplaysJournal PublicationsPatents FiledGalleryIRINS PortalContact Us</v>
+        <v>About Dr. K. L. Nagashree Assistant Professor and Head - Department of Chemistry About Department The chemistry department is one of the oldest departments of B.M.S. College of Engineering and was established in the year 1946. The department offers Applied Chemistry courses for I/II sem B. E. and Materials Chemistry and Applications course for III sem B. E. students in Chemical Engineering. In addition to regular core courses, department is also offering eight Institutional elective courses for VII &amp; VIII semester B. E. students. The department has well qualified, experienced and motivated faculty members. The department is a recognized research center by Visvesvaraya Technological University (VTU) since 2011 and Mangalore University since 2017. Apart from regular teaching, the faculty are involved in research and consultancy activities. The department has successfully completed several externally funded projects from DST-SERB and VGST with more than one crore research grant money. Faculty members have been publishing many research papers in reputed peer-reviewed journals as well as presented their work in several national and international conferences. One of the faculty has written a book for UG students. Two of the faculty members are Co-Principal investigator for DST-FIST grant. Vision Preparing professionals who provide leadership and exemplary educational and related services to improve the lives of individuals in the changing and complex global society. Mission To prepare outstanding educators, scholars and researchers and to advance the profession of education through research on science and art of teaching and learning.</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-03-14T06:31:45.298Z</v>
+        <v>2026-03-19T18:35:01.951Z</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://bmsce.ac.in/home/rankings</v>
+        <v>https://bmsce.ac.in/home/Aerospace-Engineering-About</v>
       </c>
       <c r="B20" t="str">
         <v>html</v>
       </c>
       <c r="C20" t="str">
-        <v>Recent Rankings and Accreditations StatusHomeRankings Rankings and Accreditations Status BMSCE has recently achieved the prestigious ISO 14001:2015 certification for its Environmental Management System through qualified external ISO 14001 auditors. . The UGC, New Delhi extended the autonomous status of the Institution for a period of 10 years from the session 2022-23 to 2031-32 : with a CGPA of 3.83 on a scale of four which is highest in the Country. The re-accreditation status is valid from 28.03.2019 to 28.03.2024. The College has the distinction of being awarded best performance rating in all three Phases of TEQIP The institution is a Beneficiary of Global Initiative Academic Network (GIAN). BMSCE is the only Partner institution in the country of the Melton Foundation, USA which promotes cross cultural learning for the selected students along with peers from five other countries. The College is accredited by National Assessment and Accreditation Council (NAAC) with the highest grade of A++ in the Second Cycle and a CGPA of 3.83 on a scale of four. Currently all the Undergraduate Programmes and post-Graduate Programmes hold the status of Accreditation from National Board of Accreditation (NBA), New Delhi in tier I Format. AICTE has recognized the college under AICTE Doctoral Fellowship Scheme (ADF) since 2018-19. BMSCE is listed as a lead innovator for the year 2020 and 2021 by Clarivate Analytics (Web of Science) based on the Derwent World Patent Index. In the ARIIA (ATAL Rankings) 2021, the college is ranked in band-Excellent. BMSCE has the distinction of being one of the 100 higher education institutions in the Country awarded 5G use Case Laboratory by Government of India. Accreditation Status of UG Programs SNo Program Level Accreditation Status From Validity 1 Civil Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 2 Mechanical Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2028 3 Electrical and Electronics Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 4 Industrial Engineering &amp; Management Under Graduate ACCREDITED 01/07/2022 30/06/2025 5 Computer Science and Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 6 Electronics and Telecommunication Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 7 Information Science &amp; Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 8 Electronics and Instrumentation Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 9 Medical Electronics Under Graduate ACCREDITED 01/07/2022 30/06/2025 10 Chemical Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2028 11 Biotechnology Under Graduate ACCREDITED 01/07/2022 30/06/2028 12 Electronics &amp; Communication Engineering Under Graduate ACCREDITED 01/07/2023 30/06/2026 NBA Accreditation Status of PG Programs SNo Program Level Accreditation Status From Validity 1 Machine Design Post Graduate ACCREDITED 01/07/2018 30/06/2024 2 Masters in Computer Applications Post Graduate ACCREDITED 01/07/2019 30/06/2024 3 Masters of Business Administration Post Graduate ACCREDITED 01/07/2022 30/06/2025 4 VLSI &amp; Embedded Systems Post Graduate ACCREDITED 01/07/2022 30/06/2025 5 Construction Technology Post Graduate ACCREDITED 01/07/2023 30/06/2026 6 Computer Science and Engineering Post Graduate ACCREDITED 01/07/2023 30/06/2026 7 Power Electronics Post Graduate ACCREDITED 01/07/2023 30/06/2026 8 Transportation Engineering and Management Post Graduate ACCREDITED 01/07/2023 30/06/2026 9 Computer Networking &amp; Engineering Post Graduate ACCREDITED 01/07/2023 30/06/2026 10 Digital Communications Post Graduate ACCREDITED 01/01/2024 30/06/2027 11 Electronics Post Graduate ACCREDITED 01/01/2024 30/06/2027</v>
+        <v>About Dr. K.Veerabhadrappa Professor &amp; HOD About Department The Department of Aerospace Engineering is one of the youngest engineering disciplines of the B.M.S. College of Engineering autonomous under Visvesvaraya Technological University, established in the year 2018. The department has fostered excellence in undergraduate education while advancing research that pushes the boundaries of aeronautical and astronautical engineering. It focuses on teaching and research in aerodynamics, propulsion &amp; combustion, flight mechanics and dynamics, aircraft materials &amp; structures, avionics &amp; navigation systems and space mechanics for driving the powerful insights and innovations needed to take on today's most complex engineering challenges. Having an undergraduate intake strength of 60, the Department has successfully passed out students from the academic year 2022. Department Profile Department of Aerospace Engineering has currently total of 10 faculties with most of the faculty having their doctoral studies done in Indian Institutes of Technologies and IISc. The faculty research competency is spread across the various domains of Aerospace Engineering: Aerodynamics, Combustion, Aerospace Materials and Structures and others. Visiting faculties have a very rich experience from the Defense and Aerospace industry, offering specialized course on Aircraft Maintenance. This is helping the student community to further their studies blended with research in their higher semesters. Therefore many of the students have published their research work in reputed conferences and journals. On the placement front, students have been placed in many industries like Airbus, Collins Aerospace, TATA Advanced Systems, TCS, TCE, Axiscades, Belcan, SG Aerospace and many other companies. Our students have equally excelled in post-graduation studies by continuing their Masters and Ph.D studies in IITs, US Universities like Georgia Tech, Sothern California, Purdue, Arizona and others along with European universities like ISAE-SUPAero, TUM and others. Department has the proud distinction of making students achieve their dreams in Defense forces with graduates completing their training in Indian Airforce as pilots and maintenance engineers. Aerospace students routinely participate and win many national Aircraft and Drone design, building and flying competitions. Vision To impart quality education and conduct research in the field of aerospace engineering to meet the global challenges. Mission M1: Impart aerospace technical education through effective fundamentals. M2: Create state-of-the-art laboratories, infrastructure facilities and skilled manpower for promoting research and higher education. M3: Strengthen industry-institute relationship to provide internships and encourage entrepreneur skills to produce engineers with ethics and responsibility.</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-03-14T06:31:46.218Z</v>
+        <v>2026-03-19T18:35:02.590Z</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://bmsce.ac.in/home/About-BMSET-Hostels</v>
+        <v>https://bmsce.ac.in/home/Machine-Learning-AI-and-ML-About</v>
       </c>
       <c r="B21" t="str">
         <v>html</v>
       </c>
       <c r="C21" t="str">
-        <v>About BMSET HostelsHomeFacilitiesHostel The B.M.S. Educational Trust (BMSET) is a prestigious institution which founded and manages the top class colleges viz., B.M.S. College of Engineering (BMSCE) , BMS Institute of Technology &amp; Management, BMS College of Law, BMS College for women and others institutions. B.M.S. Educational Trust Hostels are part of BMSET and BMSET Hostels in the campus of B.M.S. College of Engineering (BMSCE) provide accommodation to the students wishing to reside in the hostels. BMSET Hostels gives a distinct advantage of befriending with students from across the globe and expose them different religions, languages and customs of countries. Additionally, living as a community in the hostel will lead to all-round development of personality of a hostelite and will definitely go a long way in fostering world-class citizens. Hostels are independent units in respects to its internal administration under the overall supervision of council of wardens and the hostel management. The hostels are located in the southern side and adjacent to the college campus and have a separate hostel office and mess within the hostel premises. The mess has a centralized modern kitchen and a separate dining hall for boys and girls. General menus for each month is are decided by the hostelite representatives selected by the hostels. Special menus are introduced and served on all important festivals. THE BMSETH HOSTELS: B.M.S College of Engineering has an extensive campus spread in nearly 15 acres of land. The area consists of several buildings - old and modern, with well laid roads, play grounds and lawns. Apart from this, the hostel complex on the southern side of the college campus consists various hostel blocks. The BMSET Hostel is a place to grow and evolve one’s personality. Academics indeed is one of the area of primary concern of our management as we are among the pioneers of education in our Country. One of the salient features of the Hostel is its care for students. HOSTEL UNIT-I : MAIN HOSTEL: Indian Main Hostel for male students was built in the year of 1977 with a plinth area of 39,000 sq. ft. comprising of a ground plus two floors with a small basement to accommodate 150 pre-final and final year students in single rooms. The facilities available include water heaters with a capacity of 3000 liters per day, TV lounge, Volley Ball Court, Indoor games like Carom Board, Table Tennis and a Multi Gym. Washing machine are provided to the students for their convenience GIRLS HOSTEL BLOCK UNIT-II: This block was constructed between 1980-1984 with a plinth area of 42,586 sq. feet to accommodate Female students. The hostel has Ground plus 5 floors consisting of 125 fully furnished rooms. All rooms are provided on twin sharing basis. The basement consists of warden’s office, Visitors lounge, reading room, kitchen and a dining hall, solar water heaters of 6,000 liters capacity, two lifts to carry 8 passengers each are provided. There are TV lounges and reading rooms in alternate floors and the lounge in the top floor accommodates indoor games like Table Tennis etc. Managed by International co-operation division Hostel Unit-III: BOYS HOSTEL- This unit constructed in 2003 to accommodate 288 boys has a plinth area of 5,611.29sq meters (60,377.48 sq. ft.) comprising of basement, ground and five upper floors. All rooms are on twin sharing basis. Basement is meant for vehicle parking. Each floor consists of three wings and in each wing, there are 8 rooms totalling to 24 rooms per floor. Each student is provided with a wardrobe, study table, chair, cot and overhead book storing cabinet. solar heaters of 7500 litres capacity are installed in terrace. Two lifts to carry 9 Passengers each with 7 Stops and fire-fighting services are installed. Other facilities include reading rooms, two TV lounges, visitors lounge, Indoor games like Carom, Table Tennis. Hostel Unit-IV: GIRLS HOSTEL- This hostel building was constructed in 2003 exclusively for accommodating 117girl students with a plinth area of 5402 sq. meters (5,8125 sq. ft.) comprising of basement, ground and three upper floors. Three Students are accommodated in each room. Warden’s office, visitors lounge, reading room, dining hall, TV lounge, indoor games are Provided in the basement and parking for two wheelers is provided on the eastern side adjacent to the compound wall. There are 9 rooms in each floor and 10 rooms in each of the upper floors, solar water heater of 5,000 liters capacity, two lifts to carry 5 passengers each with 5 stops are provided. Washing machines are provided in all wings. Main Hostel (Phase-1) (GIRLS HOSTEL): This newly constructed hostel is also exclusively for girl students. This new hostel building with a plinth area of 539 sq meters (5,799.64 sq. ft.) comprising of basement, ground and three upper floors was completed in the year 2012 to accommodate 76 girls. All rooms are twin sharing with attached toilet and bathrooms with internet facility. Basement is meant for vehicle parking. Each floor consists of three wings (east, middle and west). There are 10 rooms in each floor, out of which nine rooms are twin sharing and one room is single occupancy. Each student is provided with a wardrobe, study table, chair, cot and book storing cabinet. The building is equipped with solar water heating System of 3,000 LPD capacity. The facilities include reading room, 24/7 Wi-fi-Internet accessibility, TV, Gymnasium, Washing machine, power back-up, RO drinking water system, indoor sports facilities and parking space for student vehicles. (Two wheelers only) The hostels are strictly under CC TV surveillance. Main Hostel Dining Block: Two separate dining halls are available for boys &amp; girls, which accommodates 180 boys &amp; 60 girls at a time. This has both vegetarian and non-vegetarian centralized modern kitchens. Stores for provisions, vegetables and other commodities are placed in the basement. A branch of the Allahabad Bank and internet centre are located on the western side of the dining block. The board room of the hostel committee, office of the Indian hostels, Secretary and Warden’s chambers and the residence of the assistant warden are located in the first floor of the dining block. Multi-Purpose Hall: A multipurpose hall, a part of the hostel complex, with the dimensions of 100’ x 43’ was constructed in the year 1985. This is used for conducting the meetings, seminars, functions organized by the management, cultural programs, farewell functions, get-togethers, food arrangements for examiners etc. This hall is equipped with a stage and can accommodate about 200 peoples, attached with a green room, required furniture and audio systems. During UTSAV this hall is exclusively used for conducting auditions and musical events. Annexure-I (Outside Campus-Rented Buildings) New Boys Hostel-I (about 300 Mtrs. from Main Hostel) Address: BMSET Hostel annexure-1 (I) (Mathrushree Comforts) # 48, New #710/2, 2nd Block, BSK 1st Stage, Ashoknagar, Bengaluru-560050 Accommodation Available:34 17 Rooms(Twin Sharing) Annexure-II (Outside Campus-Rented Building) New Boys Hostel-II (about 300 Mtrs. from Main Hostel) Address: BMSET Hostel annexure-11 (II) (Muniyamman Nilaya) # 898/25, 2nd Block, BSK 1st Stage, Ashoknagar, Bengaluru-560050 Accommodation Available:48 24 Rooms(Twin Sharing) Annexure-III (Outside Campus-Rented Building) New Hostel (Adjacent to Mess Block)) Address: BMSET Hostel annexure-111 (III) (Chinnapa Krupa) # 9/3, 2nd Cross, N.R. Colony, Basavanagudi, Bengaluru-560019 Accommodation Available:44 22 Rooms(Twin Sharing) Annexure-IV (Outside Campus-Rented Building) - Boys hostel ( about 1000 mts from Main hostel) Address: #73, vidhyapeetha road, Balaji Nagar, BSK 3rd Stage, Bengaluru-560085. Accommodation Available:50 Annexure-V (Outside Campus-Rented Building) - Boys hostel ( about 400 mts from Main hostel) Address: #73, vidhyapeetha road, 6th Cross, Ashoknagar, BSK 3rd Stage, Bengaluru-560085. Accommodation Available: 60 HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About Dr. M Dakshayini Professor and Head - Department of Machine Learning About Department The Department of Machine Learning at B.M.S. College of Engineering, established in 2020, is a rapidly growing discipline focused on advancing education and research in Artificial Intelligence and Machine Learning. With an undergraduate intake of 360, the department emphasizes cutting-edge areas such as Deep Learning, Data Mining, Big Data, Natural Language Processing, and Generative AI. The faculty, a blend of experienced and innovative educators, excels in making complex concepts accessible and engaging, enriched by industry experience and interdisciplinary collaborations. The department is dedicated to shaping skilled professionals ready to tackle today's technological challenges. Department Profile ABOUT B.S. NARAYAN CENTER OF EXCELLENCE IN AI &amp; ML B. S. Narayan Center of Excellence (CoE) in Artificial Intelligence &amp; Machine Learning manages research and development activities related to Al at the Department of Machine Learning, BMSCE. It fosters dynamic industry-academic synergy for AI adoption, impactful projects with industry and government, facilitating the NVIDIA DGX A100 server, the world's first purpose-built system for Deep Learning and accelerated analytics, delivering performance of 56 instances in parallel without any deterioration of performance and computations. Vision To achieve excellent standards of quality education in the field of Artificial Intelligence and Machine Learning. Mission To nurture the students with strong fundamentals for a successful career in the field of Artificial Intelligence and Machine Learning. To motivate the students for post- graduation and research. To create impact in the society with continuous research and innovations.</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-03-14T06:31:47.140Z</v>
+        <v>2026-03-19T18:35:03.288Z</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://bmsce.ac.in/home/Hostel-Activities</v>
+        <v>https://bmsce.ac.in/home/Computer-Science-and-Engineering-DS-About</v>
       </c>
       <c r="B22" t="str">
         <v>html</v>
       </c>
       <c r="C22" t="str">
-        <v>ActivitiesHomeFacilitiesHostel Hostel Activities Hostel celebrates almost all festivals celebrated across the country such as New Year, Independence Day, Holi, Diwali, Lakshmi, Saraswathi and Ganesha festivals etc. The annual hostel magazine is being released on the occasion of the hostel day. As a culmination of yearlong co-curricular and extra-curricular activities, pleasantries and prizes were distributed to the winners in recognition of their achievements on the hostel day. Every year hostel day showcases not only organizational abilities, but also active participation of all the hostelites in recreational, cultural, literary and social activities of the hostelites, who hail from various parts of the globe. Fresher’s Day The Hostel is a platform for the students to develop all their talents. Fresher’s Day is organized with variety of entertainment programmes. It is indeed a spring board for many to begin well. This is followed by various programmes under the able guidance of cultural team as well as wardens &amp; secretary. Cultural team The Hostel cultural team organizes a fantastic cultural programmes bringing joy to both the participants and the audience. The students potentialities and capabilities is brought to lime light. Team spirit, feeling of oneness, sharing of resources, learning the art of organizing &amp; building of leadership qualities are the fruits of such a show. Food Fiesta The Hostel management encourages and permits the hostelites to conduct the Food Fiesta during every Hostel month. We give opportunities for the students from 1st year to final year to prepare their own new menu representing each state food with the help of the wardens assisted by dedicated mess workers. Here again the energetic &amp; enthusiastic hostelites conduct the food fiesta deserves praises &amp; prizes. Nutrition Forum The Mess facilities of the hostel deserve a special note of appreciation. The BMSET Hostel Mess provides very healthy, hygienic &amp; nutritious food to all the students with the team comprising of Wardens &amp; dedicated mess workers. In fact every semester the hostel organizes seminars by Nutrition experts to create awareness among all about the nutrition values of the food that is served in the Hostel Mess. Sports Forum Sports plays a very vital role in keeping everyone fit and energetic and it is something very essential and part of life to young ones. The BMSET Hostel is proud of our sports team that on various occasions brought together the hostel student community through several sports event. Relevant Sports kits is been supplied to the hostelites to participate in various sports activities. The hostels have Gym Trainer &amp; Yoga Trainer to guide &amp; train the hostelites systematically. Health Forum The Health Forum of the hostel takes initiative to build &amp; bringing awareness among all the students with regard to their health. Under the BMS Hospital Trust regular medical check-up, health care facilities are being offered at concessional rates to all the hostelites and staff . Services of Specialized doctors can be availed in the said hospital. Hostel Day (Farouche) In view of the hostel day – Farouche , every year the hostel management encourage the students to organize many competitions under the leader ship of sports &amp; cultural team such as various indoor &amp; outdoor game events , singing, debate, essay writing/ poem, poster making, drawing &amp; painting, rangoli competitions paving way for the students to come out with best in them. It is a true platform for the development of several hidden talents. HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About Dr. Shambhavi B R Professor &amp; HoD About Department Data science has witnessed rapid expansion and is projected to sustain its upward trajectory in the job market. According to US News and World Report 2022, Data Scientist is ranked among the top technology jobs. The Department of Computer Science and Engineering (Data Science) was established in 2022 with an aim to prepare Generation Z professionals for a career in Data Science. The department has an intake of 60 for UG program. As an autonomous institution, the department has flexibility in designing the curriculum. The curriculum is a blend of core computer science fundamental courses with specialization in data science. Students will gain expertise in machine learning, statistical knowledge, mathematical reasoning, data visualization skills and optimization principles to appropriately formulate and analyse data. AI tools and technologies to build and evaluate data intensive systems are taught to the students through experiential learning. The department’s primary focus is to foster holistic development of students to make them exceptional engineers with societal awareness and social responsibility. Vision To be recognized as Centre for Quality Education in Computer Science and Engineering with emphasis on Data Science Mission * Enable quality Computer Science education through continually evolving curriculum and pedagogical techniques. * Conduct research collaboratively with established research labs and industries contributing to the futuristic field of Data Science. * Nurture ethical and skilled professionals by promoting multi-disciplinary thinking in solving problems of the data-driven world.</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-03-14T06:31:48.074Z</v>
+        <v>2026-03-19T18:35:03.910Z</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://bmsce.ac.in/home/Hostel-Charges</v>
+        <v>https://bmsce.ac.in/home/Computer-Science-and-Engineering-IoT-and-CS-About</v>
       </c>
       <c r="B23" t="str">
         <v>html</v>
       </c>
       <c r="C23" t="str">
-        <v>ChargesHomeFacilitiesHostel Mess Regulations &amp; Mess Charges The mess arrangement of the hostel is compulsory for all the inmates without any exception i.e., no student is allowed to stay in the hostel without being a member of mess. When the hostels have excess demand for accommodation and is unable to provide accommodation to all the applicants, the students who find accommodation nearby may be permitted to have the mess facility by collecting full charges for that academic year with an undertaking from such students that they shall join the hostels as and when the hostels provide them accommodation. However, this number shall not exceed 25 at any time. Such students have to submit a separate request form in the format provided by paying the prescribed fee and submit the same to the office. Students should sign the mess joining register kept in the mess at the time of joining the mess. Service in the mess shall be between scheduled hours only &amp; closed after lunch on every Saturday for maintenance. The Mess timings are as follows and the students should strictly adhere to these timings. Working Hours Breakfast 7.00 am to 9.00 am Lunch 12.45 pm to 2.45 pm Snacks 4.45 pm to 5.45 pm Dinner 7.00 pm to 9.00 pm The Self system of disposable will be followed in all messes. No food will be reserved for the late comers. The Non vegetarian food will be served (Chicken only) as an extra item on specified days of the week. The Management of the Mess may be entrusted to student prefects (six members committee – three from north &amp; three from south of which two shall be girls) who change every month, but the financial control will rest with the Management. In case of no student or students come forward to be prefects, the Warden with the assistance of Mess Supervisor will run the mess. Submission of the menu and approval shall be made on or before the last day of every month. The approved menu will be displayed on the notice board. The prefect ship will be valid from 5th to 4th of next month. In case of no prefects the hostel management will run the mess. A boarder can change the Mess only once in a semester from vegetarian to non-vegetarian or vice-versa. Mess charges collected are per annum and non-refundable. Neither the prefects nor any other students have a right to stop food or any other mess facility to any of the bonafide students of the mess. If any such act is found, such prefect/hostelite shall be expelled from the hostel and mess by the Warden with immediate effect. No student/prefect has any right to appoint or dispense with service of any staff member of the mess. Food will not be supplied to hostel rooms except to sick students, with the permission of the Warden and only sick diet (i.e. milk and bread) will be supplied. Used utensils shall be return to the mess immediately by the hostelite. Except Mess prefects, other hostelites are forbidden to enter the kitchen. They should treat all the the Mess workers with courtesy. Manhandling of any staff or using abusive language against them will end in the expulsion of the student from the hostel immediately after due enquiry. The boarders should produce identity cards whenever the mess supervisor/security feels to identify them before taking food. The menu of the mess should be prepared by the prefects in consultation of the Warden. The menu so specified by the mess prefects will be duly approved by the Secretary, to have an effective control over the cost. The Mess prefects will act as representatives for the whole hostel and report to the warden about the quality of food &amp; on the general cleanliness in and around the mess. The Mess prefects shall also bring to the notice about the quality of service given by the mess staff. Entertaining Guests into the mess can be done only by the hostelites. The host should accompany the guest and obtain the guest coupon at the dining hall with the mess supervisor. The guest rates shall be according to the rates fixed by the hostel management from time to time. No boarder other than prefects should interfere in the Mess affair. If he /she has any grievance or suggestion, he/she should report to the Warden The sole aim of the Management is to provide all the facilities to the inmates, both in the hostel and the mess and creation of an environment conducive for study and peaceful stay. The Management reserves the right to add, alter or delete, any rules from time to time. Hostelites who are found violating the rules and regulations of the Hostel and Mess are liable to be expelled from the Hostel. During vacation if the strength of the boarder falls below 100 the management reserves the right to stop the mess services temporarily. The Mess will remain closed for half a day (after lunch) on Saturdays. Students who absent themselves on the date of reopening of the college after any semester vacation will be deemed to have joined the mess wherein they dined during the previous semester and will be charged accordingly. HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About Dr. Prasad G R Professor and HoD About Department Advances in Cyber Security and IoT have opened a whole new realm of opportunities in many areas of our connected digital society. We the Department of Computer Science and Engineering (IoT and Cybersecurity including Blockchain) at BMSCE offer quality undergraduate program in an autonomous environment integrated with engineering practices, research and continuing professional education. The Department was started in the year 2022 with a sanctioned intake of 60 students and aims to create a vibrant learning ecosystem where every student is professionally groomed to full-fill the needs of new era of Cyber Security, IoT and Blockchain Technology. The Department aims to: • Provide strong fundamentals through learner centric approach. • Instill technical, interpersonal, interdisciplinary skills and logical thinking for holistic development of the students. • Enable students to handle various aspects of cybersecurity issues in real time scenarios. • Serve the student community by creating best career opportunities by arranging in-house progressive training, projects and internships with corporate organizations thus providing students with a comprehensive industry orientation helpful in polishing their skills. • Enhance employability of students by empowering them with technical competencies, domain skills, leadership skills, techno-managerial qualities, and communicative abilities to make them industry ready. Vision To be a model center for education and training in the frontier areas of computing in IoT, Cybersecurity and Blockchain for solving societal problems. Mission • Strengthen learning environment that facilitates quality education in the field of IoT, Cybersecurity and Blockchain. • To foster professional ethics and values with concern for environment and society to provide sustainable solutions. • Imbibe passion for research, entrepreneurship, higher studies or professional growth through life-long learning.</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-03-14T06:31:49.019Z</v>
+        <v>2026-03-19T18:35:04.538Z</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://bmsce.ac.in/home/Code-of-Conduct-for-Hostelites</v>
+        <v>https://bmsce.ac.in/home/Artificial-Intelligence-and-Data-Science-About</v>
       </c>
       <c r="B24" t="str">
         <v>html</v>
       </c>
       <c r="C24" t="str">
-        <v>Code of Conduct for HostelitesHomeFacilitiesHostel CLOSURE OF MAIN GATE OF HOSTELS: It is mandatory for all the hostelites to possess the identification card duly signed and issued by the Hostel authorities. It is directed to produce on request by Security. The Main gates of the Boys hostels will be closed by 9.30 P.M. and the Main gates of the Girls hostel will be closed by 8.30 P. M. The gates will be reopened only at 5-30 A.M. On saturdays the Main gates of the Boys hostels will be closed by 10.30 P.M. and the gates of the Girls hostel will be closed by 9 .30 P. M. The gates will be reopened only at 5-30 A.M. Any hostelite coming late after the closure of the gates in the night, shall call the respective Wardens for permission to entry into the hostels. If permission is granted they shall surrender the Hostel ID to the security &amp; record the reason for late coming in the late night register. Repeated late comings will be brought to the notice of the parents &amp; further course of disciplinary action will be initiated. The ID cards surrendered to the security shall be collected from their respective Wardens the next day. The time between 9.30 P.M.to 6.00 A.M. ( Boys ) 8 .30 P.M to 6 .00 A. M ( Girls ) is exclusively meant for study and sleep. No indoor games, radio or tapes , Computer speakers etc., at high volume or any other kind of disturbances by the hostelites causing inconvenience to other hostelites or outsiders is strictly prohibited. Also during these hours, hostelites shall avoid visiting other hostelites. If a student goes out of the Hostel for more than 24 hours or on leave etc. he/she must inform &amp; take prior written permission from their respective Wardens &amp;the same shall be entered in the register maintained for the purpose. The hostelites must compulsorily sign in the attendance register brought to their room, by the security, after closure of main gates. VISITORS ENTRY : No hostelite shall permit any outsider in the room, The visitors or guests are permitted only during day time upto the visitors lounge inside the hostel (only to meet such hostelite) with the permission of their respective wardens. The visit of boy students to the girls Hostel and vice versa is prohibited. Visitors are not permitted in the common areas of the hostels like Gym, TV lounge, indoor games area, Bathroom, Toilet etc., Any visitor found inside the hostels after 6.00 P.M. shall be sent out by the security and the hostelite permitting such unauthorized guest will be penalised. The parents/guardian or any family member of a hostelite may be permitted by the Warden/secretary in the rooms of the hostelite, upto one hour when request is made in advance by the concerned hostelite. Security shall make a note of such entries in the register provided for the said purpose. T.V. ROOM TIMINGS : The T.V. Lounge/ T.T. Room will be locked at 11.00 P.M. except when permitted by the wardens on special occasions. Except hostelites no outsiders are allowed inside the TV room. Any hostelites found responsible for bringing any outsiders inside the hostels, suitable action will be initiated immediately. The same will be informed to their parents. Code of conduct. All hostelites should ensure that the common areas in the hostel complex or common areas around the floor of the hostel always remain vacant and not obstructed or hindered in any manner. No commercial or any other activity shall be permitted in the hostels in the covered or open areas of the premises. It is prohibited to throw garbage, trash or any other things outside the hostel through the windows/balconies. All such waste materials shall be dropped separately in the dustbins kept at the corners of all the wings of the hostels. The housekeeping staff engaged by the hostel collects garbage every day and dispose the same. Playing of Football, Cricket and such other games which may cause damage to glass panels and properties, damage to vehicles and which may cause injury to any person is strictly prohibited in common or covered areas inside the premises. The hostelites of one block should not enter into the premises of other hostel block without prior permission of the Warden/Secretary. In case of students residing in International Hostel, boys entering the ground and First Floor are prohibited. Likewise the girls entering the second, third and fourth floor is prohibited. Hostelites are required to avoid singing aloud, shouting and making any type of noise likely to distract the attention of those who may be at their books or the neighbors or visitors. Protection of the hostel property is also the responsibility of the inmates. The hostelites are responsible to safeguard the materials of gymnasium, news papers and periodicals, sports goods, Water purifiers, coolers, telephones, computer equipment, T.V. or any other property of the hostel. The Hostelits are not permitted to convene meetings to attempt signature campaigns of any sort in the hostel. Every room is provided with internet connectivity, unauthorized access to internet will lead to seizure of their computer/laptops. Hostelites should strictly observe the normal rules of morality, conduct and behavior in their daily life and should not indulge in any activity unbecoming of students of this hostel. Violation of the rules &amp; regulations will be informed to their parents, Secretary, respective H.O.D.s &amp; the Principal. USE OF LIFTS: Maximum of 8 persons are permitted to use each lift at a time. Lifts are only for carrying personnel with small luggage. Carrying weights more than the permissible limit is not permitted. Damaging the switches &amp; other accessories pertaining to lifts are prohibited. ACTIVITIES BANNED / FORBIDDEN IN THE HOSTELS: Indulging in ragging or interference of any other kind is strictly prohibited. Any violation of this rule entails expulsion from the Hostel and action will be taken as per law. When a student is expelled from the hostels, such students shall not be entitled for any refunds from the hostel/mess. Hostelites are not permitted to celebrate birthday parties or any festivals inside the hostel buildings. They are barred from handling, tampering, fiddling with any equipment, scribbling on walls or displaying obscene &amp; vulgar pictures or paintings, bursting of crackers are forbidden and are liable for disciplinary action. Smoking, consumption of alcoholic beverages or intoxicated drugs, playing cards or any kind of gambling, keeping of any dangerous drugs or weapons, performing experiments in the hostels, shouting or causing any kind of disturbances inside or outside the hostel premises are strictly prohibited. Similarly no pets are allowed to be kept in the hostel premises. The Security is authorized to check the bags of any student at any time for prohibited materials, in case of a doubt. Students shall not enter the Hostel premises in intoxicated state and should not possess such materials. Depending on the case, the Management reserves the right to take direct disciplinary action, mounting to even expulsion to short notice from the hostel. PARKING INSIDE THE HOSTELS: Parking of four wheelers is banned in the hostel. Only two Wheelers are permitted to be parked in the parking area only. Visitors or outsiders vehicles are not allowed inside the hostels. The hostelites shall inform the Warden about the purchase of a vehicle (two wheelers only) &amp; affixing the hostel stickers on their two wheelers. The stickers will be issued by the hostel supervisor on production of a Xerox copy of their R.C. Book. Hostelites should park the vehicles in the parking slots of their respective blocks. The common areas either open or covered shall remain clear, unhindered and unoccupied. Hostel authorities will not take any responsibility for the damage or loss of any Motor Vehicles or parts of Motor vehicles. Hostelites should ensure slow movement of vehicles to avoid any accident in the hostel premises. Use of appliances The use of electrical appliances such as immersion heaters, electric stove / heaters / electric irons are forbidden in any of the rooms allotted the residence. Private cooking in the Hostels / students rooms is strictly forbidden. Such appliances, if found will be confiscated and a fine will be imposed. The use of Audio systems which may cause inconvenience to other occupants are not allowed. The use of personal TV, VCR and VCD/DVD is prohibited. The students should not hire objectionable CDs from outside. When the students go out of their rooms they should switch off all the Fans, lights, PC etc., and keep it locked (at all times).Violation will attract suitable penalty and punishment by the authorities. Collective Responsibilities General damages to the Hostel property will be the collective responsibility of all the Hostelites and they will be required to make good of such damage, if the students who caused the damage could not be identified. Hostelites should not indulge in practices / activities, which may endanger their own personal safety as well as others. Hostelites are required to obey all traffic rules inside the Hostel campus. Hostelites are duty bound to report to the concern wardens, in case they notice any unwanted incidents or undesirable activity going on in the hostel or on the campus. Hostelites are required to park their two wheelers in the space provided for them in an orderly manner by putting the main stand only. Hostelites should not arrange any functions or meetings within the hostel or outside or within the campus without specific permission of concern authorities. Hostelites should not arrange/ participate for any picnic, excursions, trekking and parties outside. Hostelites are required to be conscious of the environment in which they live by keeping it clean, healthy and presentable. Hostelites should not throw litter indiscriminately and should not use non-bio-degradable items, such as plastics materials. The Hostelites are responsible for the safe keeping of their personal belongings. They are advised to keep under lock (preferably a branded one) all valuable items such as laptop, mobile phones, etc. and lock the room even when they move out for a small interval of time. HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About Dr. Indiramma M Professor &amp; HoD About Department Artificial Intelligence and Data Science Globalization, fast paced growth of data and technological advancement has created a lot of career opportunities in the field of Artificial Intelligence &amp; Data Science. AI &amp; DS being an interdisciplinary course is used in almost every sector of technical industry, academics and research. The Department of Artificial Intelligence &amp; Data Science at BMS College of Engineering was established in the year 2022 with an intake of 60. The department aims to provide quality teaching and learning in the field of Artificial Intelligence &amp; Data Science domain to create the best platform for creative learning and thinking. The department endeavours a good collaboration with industries which are working in AI domain. The Department aims at: • Providing holistic development of the students to meet industry and societal needs. • Promoting self-learning in students by exploring beyond the syllabus content for better learning. • Promoting research culture and ethical values among students for better opportunities. • Facilitating Students learning groups in the Area of Data Science, Machine Learning, Deep Learning, Gaming etc. • Encouraging students to participate in Hackathons, co curricular and extra-curricular activities Vision Develop globally competent professionals in the field of Artificial Intelligence &amp; Data Science for the betterment of self and society Mission • State of the art curriculum design and infrastructure facilities to impart quality • Promote high quality research through industry academia collaborations • Inculcate professional ethics and promote sustainable solutions for society</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-03-14T06:31:49.970Z</v>
+        <v>2026-03-19T18:35:05.159Z</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://bmsce.ac.in/home/Hostel-Fee-Structure</v>
+        <v>https://bmsce.ac.in/home/Computer-Science-and-Business-Systems-About</v>
       </c>
       <c r="B25" t="str">
         <v>html</v>
       </c>
       <c r="C25" t="str">
-        <v>Fee StructureHomeFacilitiesHostel For Hostel Fee Structure contact:- BMSET Hostel office: 080-26679928 HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About Dr. R. Ashok Kumar Professor &amp; Head - Computer Science and Business Systems About Department Department of Computer Science and Business Systems offers a 4 year under graduation program specifically tuned for the current IT industry needs and for the future demands. The program is curated with essentials of core computer science and emerging technologies with desirable principles of management science to build a strong foundation for business engineers. There is a continuous improvement in the curriculum on the emerging technologies under the expertise mentors from the IT industries. The curriculum is designed by the eminent academicians along with professional experts from Tata Consultancy Services (TCS). More Details: https://www.tcs.com/careers/india/computer-science-business-system-program Vision Holistically develop world class business engineers for IT industry Mission Provide strong foundation in computer science principles to adapt for a rapidly changing technologies. Enable deep understanding of global business processes for translating technical solutions into tangible business value. Carry out research work in innovation, ideation, and disruptive technologies to capitalize on future developments in technology and business.</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-03-14T06:31:50.898Z</v>
+        <v>2026-03-19T18:35:05.787Z</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://bmsce.ac.in/home/Hostel-Admission</v>
+        <v>https://bmsce.ac.in/home/Under-Graduation</v>
       </c>
       <c r="B26" t="str">
         <v>html</v>
       </c>
       <c r="C26" t="str">
-        <v>Hostel AdmissionHomeFacilitiesHostel Accommodation The B.M.S.E.T. Hostels is managed by the Hostel Committee Constituted by the B.M.S. Educational Trust. It provides accommodation to only bonafide students of BMSCE wishing to reside in the Hostels. The object being that the Management believes in moulding of healthy, sound, &amp; high morale of each individual. Each Hostel is an independent unit in respect to its internal administration under the overall supervision of the Council of Wardens and the Hostel Management. The Hostel is administrated by a Secretary appointed by the B.M.S. Educational Trust and he is assisted by Joint Secretary and Wardens in all matters relating to Hostels. The office staffs take great effort in making the admission flow smooth. BMS Educational trust hostels is indeed a ‘’mini global village’’ with students hailing from different states in the National Hostels &amp; different nations in the International Hostels with different classes, cultures, and religions. The Hostel is meant for the students of B.M.S. College of Engineering, B.M.S. College for Women and B.M. S. College of Law. The hostelite is an occupant of the Hostel, authorized by the hostel authorities of B.M.S.E.T. Hostels. The Committee reserves the right of admission to any Hostels. Statutorily, hostel accommodation is available to BE Students for a maximum length of stay for four years, BE Architecture for 5 years, Law students for 3 /5 years , ME, M.B.A., students for 2 years &amp; M.C.A. students for a maximum length of stay for three years. Hostel accommodation is also available for Ph.D. Scholars. Only Foreign students are permitted to get accommodation in IH. All the foreign/PIO students should possess valid VISA/ Residential permit. Only such students are permitted accommodation in IH. The moment their VISA/ Residential permit expires automatically they have to vacate their rooms and can rejoin with valid VISA/ Residential permit. Admission Applications for admission shall be made in the prescribed form, which can be procured from the Hostel Office on production of a copy of fee receipt paid in the college &amp; on payment of prescribed Application fee (not refundable). The duly filled Application approved by the Principal that He/She is a bonofide student of the college, shall be submitted to Hostel Office. The Admission shall be made strictly on merit basis not on first cum first serve basis. Accordingly the allocation of seats is done on the following guidelines. Sl No. Category under which admitted to College % of Hostel seats allotted 1 Management ( Freshers ) 40% 2 CET ( Freshers ) 25% 3 Comed-K( Freshers ) 25% 4 Others (GOI, UG/ PG students in the Wait list ) 10% Any change of address/phone number of the hostelites/ parents/local guardian at any point of time, has to be intimated to the hostel office in writing, at once. On approval of admission by the Secretary of the hostels, the parents shall be informed by the office to pay the prescribed deposit within the date mentioned through two crossed Demand Drafts (NO cash Transactions). One DD drawn in favour of BMSET Hostel &amp; another in favour of BMSET Hostel Mess. If the prescribed fees are not paid within the due date, it will be presumed that the student does not require the hostel, and then the seat will be allotted to the next waiting candidate. Once the prescribed fee is been paid within the due date, then the student becomes an occupant of the Hostel. Rooms are allotted to each student by the Secretary of the Hostels, the same shall be informed to the Wardens of respective blocks and occupy the rooms. Three passport size and 4 stamp size photographs shall be submitted to the hostel office at the time of admission. During admission to the Hostels every student shall make a declaration in the presence of the Wardens, in the declaration form provided along with the application. Allotment of Rooms The allotment of rooms to the freshers will be made purely on lottery system. Rooms are allotted to each student by the Secretary of the Hostels, the same shall be informed to the Wardens of respective blocks and occupy the rooms. At the time of occupying the room, the student shall check all the accessories provided to him/her and make a declaration in the check list provided by the Hostel Supervisor. The hostelite who is in receipt of the accessories in good condition will be liable for damages if any, during his/her stay. Rooms once allotted to the students for an academic year will not be changed except on special situations with the permission of the Secretary. The parent/guardian of the student shall enter into an Hostel agreement paper with a clear understanding that the hostelite should vacate the room after 11 months or after the completion of the annual examination and also be a responsible for the payment of all the dues. Rooms are allotted to each student on his/her personal responsibility. Students should see the upkeep of his/her room. In case of damage or loss of the Hostel property the cost will be recovered from the students responsible for such damage or loss, as decided by the Warden. The students are entitled for accommodation in the hostel as long as they are full time registered students. Accommodation will not be provided to any students whose registration is cancelled. Any student who is removed from the Rolls of the college will automatically cease to be a member of the hostel. Vacating the Hostels To vacate the hostels after the completion of the course, the hostelite has to submit the requisite form (vacating form) in the format provided and submit the same to the office. At the time of receiving the refund of security deposits (after deducting damage charges, if any) ,the hostelite must surrender their room keys and ID card to the office failing which he/she has to pay the prescribed amount and obtain the receipt. The security deposit is refunded to the students who leave the hostel. This deposit is subjected to deduction for any loss of equipment provided to him/her it is lost or not accounted by them at the end of each academic year. If any hostelite is not eligible to go to next higher semester he/she shall vacate the hostel immediately for one academic year. He /She may readmitted to the hostel after he/she obtains the eligibility provided the security deposit paid by such hostelite should be retained in the hostels. If any hostelite indulged in malpractice during the tests/examination such hostelite will be expelled from the hostels by forfeiting the Security Deposit &amp; Service charges paid by the hostelite. Any student who is removed from the rolls of the college will automatically cease to be a member of the Hostel. Occupation and Continuance Each admission will be valid for a period of one academic year only. The hostelite willing to continue his/her stay in the hostel for the succeeding year shall submit his/her requisition to the Warden in prescribed format available in the hostel/ICD office by paying the prescribed fee, duly forwarded by the HOD, before leaving for vacation at the end of even semester; (result sheet attested by the HOD shall be attached). The hostelite should vacate the room after his annual examination within ten (10) days after the examination and hand over the charge of the room to the Hostel Office. In case he/she does not vacate the room within ten (10) days a penalty of Rs.100/- per day will be levied for the next ten (10) days after which the warden has the power to take charge of the room without any notice and shift the articles at the risk of the concerned student. If it is decided to expel a hostelite, the Warden shall have the full right to enter into the room and if there be a necessity, break open the lock and take charge of the room without any notice and shift the articles of the student at the risk of the student. The Management may make rules and regulations from time to time and the hostelites are bound to obey the rules. The overall possession of every room, even if allotted to a student shall always be deemed to vest with the Warden and he shall be entitled to open and enter any room if in his opinion it is necessary to do so. The hostelites shall only use a lock with six/seven lever key and submit one key of the said lock to the office to enable the Warden to take charge of the room whenever it is found necessary/emergency. The hostelites should take due care to ensure the safety of the property in their individual rooms. The Hostel Authorities do not accept any responsibility for losses of their personal belongings etc. However, any loss of hostel assets should be reported to the Warden who would render all possible assistance for recovery of lost property. If a hostelite notices the requirement of any maintenance such as Civil/Electrical/Carpentry/Plumbing etc., he/she shall enter in the complaint book and bring the same to the notice of the Warden in the prescribed format which can be obtained from the hostel supervisor. During vacations, the hostelites shall surrender their rooms to the Warden or his/her representative to perform the regular maintenance works. At any cost they should not hand over the room keys to any outsiders or non-hostelites. Continuation of students stay in IH depends on payment of Institutional Cost by IH students and are advised to maintain the official receipt issued towards the Institutional Cost/Accommodation/Mess charges and have to produce the same on demand. HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>Under Graduation Notice:- Admissions for Management Quota seats are Opened for First Year B.E Courses for 2026-27 at B.M.S. College of Engineering. Four Years Bachelor of Engineering (B.E) Programs in: CIVIL ENGINEERING MECHANICAL ENGINEERING ELECTRICAL &amp; ELECTRONICS ENGINEERING ELECTRONICS &amp; COMMUNICATION ENGINEERING INDUSTRIAL ENGINEERING &amp; MANAGEMENT COMPUTER SCIENCE AND ENGINEERING BIO TECHNOLOGY CHEMICAL ENGINEERING ARTIFICIAL INTELLIGENCE AND MACHINE LEARNING COMPUTER SCIENCE AND ENGINEERING (DATA SCIENCE) COMPUTER SCIENCE AND ENGINEERING (INTERNET OF THINGS AND CYBER SECURITY INCLUDING BLOCK CHAIN TECHNOLOGY) ARTIFICIAL INTELLIGENCE (AI) AND DATA SCIENCE COMPUTER SCIENCE AND BUSINESS SYSTEMS Academic Eligibility for Four Years under Graduate Programs (B.E.): 1. Through KEA/COMED-K FOR GENERAL MERIT CANDIDATES: A candidate who has Passed in 2nd PUC / 12 Std / Equivalent Examination with English as one of the Language and obtained a Minimum of 45% of Marks in aggregate in Physics and Mathematics as compulsory subjects along with Chemistry / Bio Technology / Biology / Computer Science / Electronics as optional subjects in the qualifying examination is eligible to pursue in under graduate programs (BE). FOR SC/ST &amp; OBC (Cat-I, 2A, 2B, 3A 3B) CATEGORY CANDIDATES: A candidate who has Passed in 2nd PUC / 12 Std / Equivalent Examination with English as one of the Language and obtained a Minimum of 40% of Marks in aggregate in Physics and Mathematics as compulsory subjects along with Chemistry / Bio Technology / Biology / Computer Science / Electronics as optional subjects in the qualifying examination is eligible to pursue in under graduate pogroms (BE). The marks obtained by the candidate in Biotechnology/Biology/Computer Science / Electronics in the qualifying examination will be considered in the place of Chemistry in case the marks obtained in Chemistry is less for the required aggregate percentage for the pursue of determination of eligibility. Entrance Examination: KEA / COMED-K For Management Admissions: Students have to take any one of the Entrance Examination 2. Through Lateral Entry Scheme Three Years Bachelor of Engineering (B.E. – Lateral Entry Scheme) Programs: A candidate who has passed Qualifying Examination i.e. any diploma examination or equivalent examination and obtained an aggregate minimum of 45 % ( for General Merit Candidates) of marks taken together in all the subjects of the final year (i.e.,fifth and six semesters) diploma examination (Q E) is eligible for admission to B E-Courses and 40% of marks in Q. E. in case of SC, ST and Backward Classes of Karnataka Candidates. NOTE: The aggregate percentage of marks of the course of the qualifying examination shall be calculated as follows: Aggregate Percentage of Marks = Sum of the marks scored by the candidate in all the subjects of the final year (5th &amp; 6th semester) examinations X 100 Sum of the maximum marks of all the subjects of the final years (5th &amp; 6th semester) examinations 3. Through Management Quota APPROVED MANAGEMENT FEE STRUCTURE FOR 2026-27 S.No Name of the Branch Fee for 2026-27 (Rs. in Lakh per annum) 1 Civil Engineering 6.0 2 Electrical &amp; Electronics Engg. 6.0 3 Industrial Engineering &amp; Mgmt 6.0 4 Electronics &amp; Communication Engg. 9.0 5 Mechanical Engineering 6.0 6 Computer Science and Engineering 15.0 7 Chemical Engineering 4.0 8 Bio-Technology 7.0 9 Artificial Intelligence and Machine Learning 12.5 10 Artificial Intelligence and Data Science 12.0 11 Computer Science and Engineering (Data Science) 12.0 12 Computer Science and Engineering (Internet of Things &amp; Cyber Security including Blockchain Technology) 12.0 13 Computer Science &amp; Business Systems 10.0 Note: Eligibility for BE under Management Quota: Physics &amp; Mathematics (compulsory) Optional Subjects: Highest Marks obtained in any of the subjects- Chemistry/ Biology/Bio-Tech./Computer Science/Electronics are considered for Engineering Courses. (compulsory) Entrance Exams conducted by CET/COMED-K/JEE Paper-I are must for Engineering Courses for admissions under Management Seat. The student must qualify in the Entrance Exam. HOSTEL FEES IS EXTRA (NOT INCLUDED IN THE ABOVE MENTIONED FEES STRUCTURE) BMS EDUCATIONAL TRUST DOES NOT ENCOURAGE ADMISSIONS THROUGH AGENTS OR SUPPORT AGENTS FOR THE ADMISSIONS IN THE COLLEGE. For Management Admission related information: Please visit: Director (Admissions), International Division, Ground Floor, Platinum Jubilee Block of BMSCE Campus, Bull Temple Road, Basavanagudi, Bengaluru – 560 019 Counselling will be held from Monday to Friday from 10:00 AM - 4:00 PM. Please note that BMS Educational Trust Admission Office remains closed on Sundays, 2nd &amp; 4th Saturdays and on Government Holidays. E-Mail ID: contact@bmsetadmission.org Management Admission Contact No.:080-26611636 Payment Mode for Management Admission: Demand Draft favouring BMS Educational Trust payable at Bengaluru and to be brought from the PARENT’S ACCOUNT ONLY.</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-03-14T06:31:51.846Z</v>
+        <v>2026-03-19T18:35:06.456Z</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://bmsce.ac.in/home/Hostel-Committee-Members</v>
+        <v>https://bmsce.ac.in/home/Post-Graduation</v>
       </c>
       <c r="B27" t="str">
         <v>html</v>
       </c>
       <c r="C27" t="str">
-        <v>Hostel Committee MembersHomeFacilitiesHostel Honourable BMSET Hostel Committee Members Dr Dayananda Pai Life Trustee &amp; Honorary Chairman, BMSCE BMSET Hostels, Bengaluru. Dr.B.S Ragini Narayan Donor Trustee &amp; Member Secretary, Member, BMSET Hostels, Bengaluru. Sri. Aviram Sharma Trustee, BMSET &amp; Chairman BMSCL, Member, BMSET Hostels, Bengaluru. Sri. Ravi Venkatesan Trustee BMSET &amp; Member, BMSET Hostels, Bengaluru. Dr. Bheemsha Arya Principal, BMSCE &amp; Working Chairman, BMSET Hostels Dr. L. Ravikumar Vice Principal - Academic, BMSET, Member, BMSET Hostels. Dr. Seshachalam. D Vice Principal - Administration, BMSET, Member, BMSET Hostels. Sri. Prakash D Rao Senior Manager(Finance-1), BMSET, Member, BMSET Hostels. Sri Sanjeeva B S Director ( Finance ), BMSET, Member, BMSET Hostels. Dr. H.S. Jagadish Director-ICD, Member, BMSET Hostels Sri. P. Khaleel Director-Projects, BMSET, Member, BMSET Hostels Prof. Rahul R. Secretary, National Hostels, BMSET Hostels. Dr.Boddapati Venkatesh Secretary, International Hostels, BMSET Hostels. HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>Post Graduation Notice: Admissions are Opened for Management Quota seats for First Year PG Courses (M.Tech, MBA &amp; MCA) for 2026-27 at B. M. S. College of Engineering. Two Years Full-Time PG programs in: DEPARTMENT OF COMPUTER APPLICATIONS DEPARTMENT OF MANAGEMENT STUDIES AND RESEARCH CENTRE M.Tech- COMPUTER NETWORKING M.Tech- TRANSPORTATION ENGINEERING AND MANAGEMENT M.Tech- VLSI DESIGN &amp; EMBEDDED SYSTEMS CONSTRUCTION TECHNOLOGY ENVIRONMENTAL ENGINEERING MACHINE DESIGN POWER ELECTRONICS ELECTRONICS DIGITAL COMMUNICATION COMPUTER SCIENCE AND ENGINEERING Academic Eligibility for Full Time Two Years Post Graduate Programs (M.Tech): A candidate with valid GATE score or PGCET of Karnataka A candidate who has passed qualifying examination (i.e., BE/B. Tech Degree) in the relevant discipline and obtained an aggregate minimum of 50% of marks (for General Merir Candidates) taken together in all the subjects of all the years / semesters of the Degree Examination is eligible for admission to ME / M. Tech programs. ( 45% of marks in qualifying examination in case of SC, ST and Cat-I candidates. (Reservation is applicable only for Karnataka Candidate) NOTE: The aggregate percentage of marks of the course of the qualifying examination shall be calculated as follows: Aggregate Percentage of Marks = Sum of the marks scored by the candidate in all the subjects of all the examinations / semesters X 100 Sum of all the maximum marks of all the subjects of all the years / semesters GATE Scholarship: For receiving GATE Scholarship, a candidate must have a valid GATE Score Card. Candidate with valid GATE score, opting seats under Sponsored Quota, are not entitled for GATE stipend SC/ST/OBC candidates with valid GATE Score claiming any other scholarship from Government of Karnatake / India are not entitled for GATE Scholarship. Candidates with valid GATE score opting for seat under Part-Time ME / M. Tech Program are not entitled for GATE stipend. Two Years Master of Business Administration (MBA) Degree for the academic year 2026-27: A candidate who has passed Qualifying Examination i.e., any Recognised Bachelor’s Degree of minimum of 3 years duration examination or equivalent examination and obtained an aggregate minimum of 50 % of (for General Merit Candidates) marks taken together in all the subjects including language in all the years of the Degree Examination is eligible for admission to full time MBA course. (45% of marks in Q. E. in case of SC, ST and Category – I of Karnataka Candidates) (Reservation is applicable only for Karnataka Candidates) [Entrance Examination: KMT / CMAT / MAT / PGCET – ANYONE IS MANDATORY] NOTE: ROUNDING OFF AGGREGATE PERCENT IS NOT PERMITTED. Two Years Master of Computer Application (MCA) Degree from the academic year 2026-27: A candidate who have passed Qualifying Examination i.e, any Recognised under graduate examination or equivalent examination with Mathematics or Statistics or Computer Science or Computer Application or Computer Programming or Business Mathematics or Business Statistics as one of the optional subjects and obtained an aggregate minimum of 50% [for General Merit Candidate] of marks taken together in all the subjects in all the years of the Degree Examination is eligible for admission to MCA courses. ( 45% of marks in Q. E. in case of SC, ST and Category – I of Karnataka Candidates. [Entrance Examination: KMT or PGCET – ANYONE IS MANDATORY] NOTE: ROUNDING OFF AGGREGATE PERCENT IS NOT PERMITTED. APPROVED MANAGEMENT FEE STRUCTURE FOR 2026-27 S.No Name of the Branch Fee for 2026-27 (Rs. in Lakh per annum) 1. MBA 4.0 2. MCA 3.5 3. M. Tech - Data Science (New Course) 3.0 4. M. Tech – Transportation &amp; Engg. 1.5 5. M.Tech - VLSI &amp; Embedded Systems 4.0 For Management Admission related information: Please visit: Director (Admissions), International Division, Ground Floor, Platinum Jubilee Block of BMSCE Campus, Bull Temple Road, Basavanagudi, Bengaluru – 560 019 Counselling will be held from Monday to Friday from 10:00 AM - 4:00 PM. Please note that BMS Educational Trust Admission Office remains closed on Sundays, 2nd &amp; 4th Saturdays and on Government Holidays. E-Mail ID: contact@bmsetadmission.org Management Admission Contact No.:080-26611636 Payment Mode for Management Admission: Demand Draft favouring BMS Educational Trust payable at Bengaluru and to be brought from the PARENT’S ACCOUNT ONLY.</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-03-14T06:31:52.766Z</v>
+        <v>2026-03-19T18:35:07.081Z</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>https://bmsce.ac.in/home/Hostel-Management</v>
+        <v>https://bmsce.ac.in/home/International-Admissions</v>
       </c>
       <c r="B28" t="str">
         <v>html</v>
       </c>
       <c r="C28" t="str">
-        <v>Hostel ManagementHomeFacilitiesHostel FACILITIES ARE PROVIDED IN THE HOSTELS IS FOR OUR DEAR STUDENTS TO EXCEL NOT ONLY ACADEMICALLY BUT ALSO IN EVERY AREA OF LIFE. Rights of Hostel Management Hostel Warden has every right to ask the hostelite to vacate the room, if he firmly convinced that the Hostelite’s behavior/conduct is against the hostel rules or against the moral tone of the hostel or if there is a violation of any of the rules of discipline mentioned above. Any breach of these rules will invite an enquiry that will be conducted by the Hostel Management. If the student is found guilty, then the Hostel Management will take disciplinary action that deems fit. Depending upon the case, the Management reserves the right to take disciplinary action, amounting to even expulsion at short notice from the Hostel. The Hostel Management reserves the right to change any rules from time to time keeping the students informed through circulars displayed on the notice boards The hostelites are required to treat the hostel employees, security, house-keeping and staff of the office and mess, with due consideration and courtesy and render assistance to them, in the discharge of their duties. They can lodge a written complaint to the Warden/Secretary about any of their grievance with reference to any of the employees. HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>International Admissions Students who hold Overseas Citizen of India (OCI) status or foreign passports are eligible to submit applications to the International Division. Scholarships are available to students who were born in the UK, US, or Australia that hold foreign passports. Scroll down to download the application. Dr. B. S. Ragini Narayan Chairperson ICD, Donor Trustee &amp; Member Secretary BMS Educational Trust. Dr. H.S. Jagadeesh. M.Tech, Ph.D. Professor &amp; Director ICD (BMS COLLEGE OF ENGINEERING CAMPUS) BMS Educational Trust. This division was established in 1979 to initiate innovative ventures at national and international levels. The purpose is to establish a good relationship and linkages with outside agencies and foreign universities for exchange programmers that would contribute towards the advancement of science and technology. The excellence of BMSCE in the field has been amply acknowledged by many agencies around the world. In recognition, these agencies have been funding special programmers for more than two decades for training international students from various countries. Governments of Malawi, Tanzania, Botswana, Nepal, Sri Lanka, Malaysia, Rwanda, and others have been regularly sponsoring their students studying at BMS institutions. An International Hostel with all modern amenities is provided to the students. More than 1000 international students have graduated from portals of BMSCE since the inception of ICD. Established in 1946, BMS College of Engineering has been rated now as one of the best 25 Engineering Institutions in India and second best in Karnataka. Considering the reputation of the Institution, AICTE: the mandatory authorities governing the Engineering Colleges throughout India, have approved the admission of Foreign Nationals, PIOs and children of Indian Workers in Gulf Countries under 15% Supernumerary Quota. In the view of above, all foreign Nationals, Persons of Indian Origin who have passed/appeared for 10+2/’A‘ level examination can apply for the Engineering courses and with a minimum basic degree for MBA &amp; MCA course. Likewise, children whose parents are working in Gulf countries (minimum period of employment is stipulated as two years) can also apply. Hostel accommodation in the College campus is available on twin sharing basis. WHO CAN APPLY NRIs - Children of Indian Parents who are working in Gulf Countries are eligbile for admission under Gulf quota Foreign Nationals - Citizens of all countries other than India PIO - Persons who are citizens of other countries (except Pakistan and Bangladesh) who at any time held an Indian Passport, or who or either of his parents or any of hsi grandparents was a citizen of India by virtue of the provisions of the Constitution of India HOW TO APPLY Gulf/PIO/FN Category - BMSCE Campus : Download Application Form Gulf/PIO/FN Category - BMSIT Campus : Download Application Form Nepal nationals - BMSCE Campus : Download Application Form Nepal nationals - BMSIT Campus : Download Application Form Student Registration link "Study in India" - Click here to Login Download Application and Scanned copy of duly filled Application should be sent to nriadmissions@bmsce.ac.in and bmsicd@gmail.com Course Details: B.E/MBA/MCA Kindly Visit: B.M.S. College of Engineering Website: https://www.bmsce.ac.in/ BMS Institute of Technology Website: https://bmsit.ac.in/ FOR GENERAL DEGREE ADMISSIONS: BA / B.Com / B.SC/ BCA/ BBM BMS College for Women Website www.bmscw.edu.in</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-03-14T06:31:53.711Z</v>
+        <v>2026-03-19T18:35:07.704Z</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>https://bmsce.ac.in/home/List-of-Hostels</v>
+        <v>https://bmsce.ac.in/home/BMS-Hospital</v>
       </c>
       <c r="B29" t="str">
         <v>html</v>
       </c>
       <c r="C29" t="str">
-        <v>List of HostelsHomeFacilitiesHostel Sl. No Hostel Unit Type of Rooms Single/Double/Triple Total seats available in each hostel Accommodation meant for 1 Main Hostel Unit-I 150 Single rooms 150 Pre-final and final year 2 International Hostel Unit-II 125 rooms (Twin Sharing) 250 Girls 3 Boys Hostel Unit-III 144 rooms (Twin Sharing) 288 I year and II year boys 4 Girls Hostel Unit-IV 41 rooms (Triple Sharing) 123 Girls - Pre-final and final year 5 New Boys Hostel Annexure I 17 Rooms (Twin Sharing) 34 I year 6 New Boys Hostel Anexure II 24 Rooms (Twin Sharing) 48 I year 7 New Girls Hostel 22 Rooms (Twin Sharing) 44 I year 8 Main Hostel Phase I Girls Hostel 36 Rooms (Twin Sharing) 72 I &amp; II year HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>BMS Hospital B.M.S Campus Health Care Centre Dr. Megha BMS Campus Health Care Centre BMS College of Engineering Bull Temple Road,Bangalore-19 B.M.S Hospital Opp. BMS Engineering College, Bull Temple Road, Bangalore – 560019, Karnataka Phone: 91(80) 26613888/26613993 Mobile: +91 9900013234 Website: http://bmshospital.com/ Six decades ago a man with a mission to educate people first private Engineering College. The man was none other than the founding father of BMS educational institution Sri B.M Sreenivasaiah. His son, Mr. B.S Narayan, pursued his father’s dream to help the needy and laid the foundation stone for B.S Narayan memorial hospital in the year 1991. Before his efforts could gain momentum his soul left us with the responsibility to carry forward his legacy and give the best affordable medical facility. Our life trustee Mrs. Ragini Narayan, kindled by the benevolent and noble thoughts of her husband, has turned B.S Narayan Memorial Day Care center into a state of the art multidimensional hospital, where anyone can seek cure and are under the guidance of experienced doctors without worrying about the cost. Facilities and Specialities Facilities Available Specialities Available OPD Consultations General Medicine Emergency General Surgery Operation Theatre with fully Equipped Recovery Room Obstetrician and Gynecology Trauma and Casualty Pediatrics Inpatient Services Orthopedic and Physiotherapy Radiology (Digital X-Ray, Ultrasound, Doppler) Cardiology 2D Echo + Colour Doppler, TMT(Stress ECG) Diabetology Laboratory Gastroenterology Pulmonary Function Test Oncology Physiotherapy ENT Ambulance Services Pulmonology Pharmacy Urology Yoga Nephrology Dentistry Ophthalmology Cosmetology Neurology Thermal Mammography</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-03-14T06:31:54.638Z</v>
+        <v>2026-03-19T18:35:08.355Z</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>https://bmsce.ac.in/home/Hostel-Secretary</v>
+        <v>https://bmsce.ac.in/home/About-Library</v>
       </c>
       <c r="B30" t="str">
         <v>html</v>
       </c>
       <c r="C30" t="str">
-        <v>Hostel SecretaryHomeFacilitiesHostel List of Hostel Secretaries Prof. Rahul R Designation: Assistant Professor Department: Mathematics Department Role: Secretary, National Hostel(NH), BMSET HOSTELS Contact: 8755144124 Email: rahul.maths@bmsce.ac.in Dr.Boddapati Venkatesh Designation: Associate Professor Department: Electrical and Electronics Engineering Role: Secretary, International Hostels(IH), BMSET Hostels. Contact: 8951606016 Email: venkateshb.eee@bmsce.ac.in HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About Library Libraries are established for the systematic collection, organization, preservation and dissemination of knowledge and information. It is very important for man to preserve and maintain the valuable knowledge and information contained in the books and documents because we want to preserve our knowledge and wisdom for the coming generations. By preserving the documents in a library this knowledge can be made available to others so that they can benefit from it. Libraries play a vital role in the development of any society by enhancing the cause of education and academic research. They cater to the information needs of thousands of peoples. Location The library is aesthetically located in a central place of the college and is very prominently housed in a big and spacious building with a floor area of 4200 Sq. mts (45200 Sq.ft). Mission The mission of BMSCE Library is to seek, create, communicate and preserve knowledge and understanding and carryout the mission in a unified community known as College. The library, in support of the educational and research mission of the college, is the local repository and the principal gateway to current information and the scholarly record. As such, it is simultaneously collection and connection for the current and future students and faculty of the college. Vision It is an information hub of academic community and a center of unbridled intellectual inquiry. A place where the past converges with the present and the road to the future is littered with every imaginable tried ideas and tested theory. Objective To develop a collection of documents (both in print and in electronic form) and keep them up to date in accordance with growing needs of users of today and tomorrow. To support academic programmes of the parent institution by providing necessary reading materials. To provide individual and group guidance to readers in making maximum use of Library resources. To encourage students to develop skills for self-education, which can sharpen their intellect and can contribute for their personality development. To support teaching staff in their teaching and research activity. To conduct user education programmes to train students and staff in making effective use Library resources. E-Library Facilities The Digital library provides On-line access to 27 e-resources on Science and Technology for studies and research, and has access to 12499 e-journals &amp; 51662 e- books on various branches of Science, Technology, Engineering &amp;, Management. Library also subscribes 84 National and International printed journals. Provide access to all streams of Question Papers through Digital Software–TechFocuz via Intranet. Subscribed to NPTEL lectures are streamed using Internet View Central Libray</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-03-14T06:31:55.561Z</v>
+        <v>2026-03-19T18:35:09.026Z</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>https://bmsce.ac.in/home/Hostel-Members-and-Wardens</v>
+        <v>https://bmsce.ac.in/home/About-BMSET-Hostels</v>
       </c>
       <c r="B31" t="str">
         <v>html</v>
       </c>
       <c r="C31" t="str">
-        <v>Members &amp; WardensHomeFacilitiesHostel List of National Hostel Members and Wardens Sri. Rahul R Designation: Assistant Professor Department: Mathematics Department Role: Secretary-National Hostel(NH), BMSET HOSTELS Contact: 8755144124 Email: rahul.maths@bmsce.ac.in Dr. Srinidhi M Designation: Assistant Professor Department: Chemistry Department Role: Joint Secretary-National Hostel(NH), BMSET HOSTELS Contact: 9986273000 Email: srinidhir.chem@bmsce.ac.in Mrs. Archana K Designation: Assistant Professor Department: Telecommunication Department Role: Joint Secretary-National Hostel(NH), BMSET HOSTELS Contact: 9980911130 Email: archana.tce@bmsce.ac.in Mr. John Moses Role: Administrative Officer, BMSET HOSTELS Dr.Latha H N Designation: Assistant Professor Department: Electronics and Communication Department Role: WARDEN-National Hostel(NH), BMSET HOSTELS Contact: 8296390933 Email: lathahn.ece@bmsce.ac.in Dr. Ambika K Designation: Associate Professor Department: Telecommunication Department Role: WARDEN-National Hostel(NH), BMSET HOSTELS Contact: 9845339902 Email: ambikak.tce@bmsce.ac.in Dr. Bandaru Mallikarjuna Designation: Assistant Professor Department: Mathematics Department Role: WARDEN FOR MESS-National Hostel(NH), BMSET HOSTELS Contact: 8971319832 Email: mallikarjunab.maths@bmsce.ac.in Mr. Harish V Mekali Designation:Assistant Professor Department: Electronics and Communication Department Role: WARDEN-National Hostel(NH), BMSET HOSTELS Contact: 9538765141 Email: hvm.ece@bmsce.ac.in Dr. Chetan Raj D Designation:Assistant Professor Department: Electricals and Electronics Department Role: WARDEN-National Hostel(NH), BMSET HOSTELS Contact: 9738128573 Email: chethanrd.eee@bmsce.ac.in Dr.Shekar M Designation:Assistant Professor Department: Mathematics Department Role: WARDEN-National Hostel(NH), BMSET HOSTELS Contact: 9916223260 Email: shekarm.maths@bmsce.ac.in Dr.Sreenivasamurthy A Designation:Assistant Professor Department: Civil Engineering Department Role: WARDEN-National Hostel(NH), BMSET HOSTELS Contact: 9886885848 Email: asm.civ@bmsce.ac.in List of International Hostel Members and Wardens Dr.Boddapati Venkatesh Designation: Associate Professor Department: Electricals and Electronics Department Role: Secretary, International Hostels(IH), BMSET Hostels. Contact: 89516 06016 Email: secretary.hostel@bmsce.ac.in Dr. Hadagali Ashoka Designation: Associate Professor Department: Bio Technology Department Role: Joint Secretary, International Hostels(IH), BMSET Hostels. Contact: 9902433100 Email: hadagaliashoka.bt@bmsce.ac.in Dr. Madhusudhan K. N Designation:Associate Professor Department: Electronics and Communication Engineering Department Role: Warden-BOYS, International Hostels(IH), BMSET Hostels. Contact: 9845409693 Email: wardenboys.ih@bmsce.ac.in Dr. Shyamala G Designation:Professor Department: Computer Science and Engineering Department Role: Warden-GIRLS, International Hostels(IH), BMSET Hostels. Contact: 8296598004 Email: wardengirls.ih@bmsce.ac.in HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About BMSET Hostels The B.M.S. Educational Trust (BMSET) is a prestigious institution which founded and manages the top class colleges viz., B.M.S. College of Engineering (BMSCE) , BMS Institute of Technology &amp; Management, BMS College of Law, BMS College for women and others institutions. B.M.S. Educational Trust Hostels are part of BMSET and BMSET Hostels in the campus of B.M.S. College of Engineering (BMSCE) provide accommodation to the students wishing to reside in the hostels. BMSET Hostels gives a distinct advantage of befriending with students from across the globe and expose them different religions, languages and customs of countries. Additionally, living as a community in the hostel will lead to all-round development of personality of a hostelite and will definitely go a long way in fostering world-class citizens. Hostels are independent units in respects to its internal administration under the overall supervision of council of wardens and the hostel management. The hostels are located in the southern side and adjacent to the college campus and have a separate hostel office and mess within the hostel premises. The mess has a centralized modern kitchen and a separate dining hall for boys and girls. General menus for each month is are decided by the hostelite representatives selected by the hostels. Special menus are introduced and served on all important festivals. THE BMSETH HOSTELS: B.M.S College of Engineering has an extensive campus spread in nearly 15 acres of land. The area consists of several buildings - old and modern, with well laid roads, play grounds and lawns. Apart from this, the hostel complex on the southern side of the college campus consists various hostel blocks. The BMSET Hostel is a place to grow and evolve one’s personality. Academics indeed is one of the area of primary concern of our management as we are among the pioneers of education in our Country. One of the salient features of the Hostel is its care for students. HOSTEL UNIT-I : MAIN HOSTEL: Indian Main Hostel for male students was built in the year of 1977 with a plinth area of 39,000 sq. ft. comprising of a ground plus two floors with a small basement to accommodate 150 pre-final and final year students in single rooms. The facilities available include water heaters with a capacity of 3000 liters per day, TV lounge, Volley Ball Court, Indoor games like Carom Board, Table Tennis and a Multi Gym. Washing machine are provided to the students for their convenience GIRLS HOSTEL BLOCK UNIT-II: This block was constructed between 1980-1984 with a plinth area of 42,586 sq. feet to accommodate Female students. The hostel has Ground plus 5 floors consisting of 125 fully furnished rooms. All rooms are provided on twin sharing basis. The basement consists of warden’s office, Visitors lounge, reading room, kitchen and a dining hall, solar water heaters of 6,000 liters capacity, two lifts to carry 8 passengers each are provided. There are TV lounges and reading rooms in alternate floors and the lounge in the top floor accommodates indoor games like Table Tennis etc. Managed by International co-operation division Hostel Unit-III: BOYS HOSTEL- This unit constructed in 2003 to accommodate 288 boys has a plinth area of 5,611.29sq meters (60,377.48 sq. ft.) comprising of basement, ground and five upper floors. All rooms are on twin sharing basis. Basement is meant for vehicle parking. Each floor consists of three wings and in each wing, there are 8 rooms totalling to 24 rooms per floor. Each student is provided with a wardrobe, study table, chair, cot and overhead book storing cabinet. solar heaters of 7500 litres capacity are installed in terrace. Two lifts to carry 9 Passengers each with 7 Stops and fire-fighting services are installed. Other facilities include reading rooms, two TV lounges, visitors lounge, Indoor games like Carom, Table Tennis. Hostel Unit-IV: GIRLS HOSTEL- This hostel building was constructed in 2003 exclusively for accommodating 117girl students with a plinth area of 5402 sq. meters (5,8125 sq. ft.) comprising of basement, ground and three upper floors. Three Students are accommodated in each room. Warden’s office, visitors lounge, reading room, dining hall, TV lounge, indoor games are Provided in the basement and parking for two wheelers is provided on the eastern side adjacent to the compound wall. There are 9 rooms in each floor and 10 rooms in each of the upper floors, solar water heater of 5,000 liters capacity, two lifts to carry 5 passengers each with 5 stops are provided. Washing machines are provided in all wings. Main Hostel (Phase-1) (GIRLS HOSTEL): This newly constructed hostel is also exclusively for girl students. This new hostel building with a plinth area of 539 sq meters (5,799.64 sq. ft.) comprising of basement, ground and three upper floors was completed in the year 2012 to accommodate 76 girls. All rooms are twin sharing with attached toilet and bathrooms with internet facility. Basement is meant for vehicle parking. Each floor consists of three wings (east, middle and west). There are 10 rooms in each floor, out of which nine rooms are twin sharing and one room is single occupancy. Each student is provided with a wardrobe, study table, chair, cot and book storing cabinet. The building is equipped with solar water heating System of 3,000 LPD capacity. The facilities include reading room, 24/7 Wi-fi-Internet accessibility, TV, Gymnasium, Washing machine, power back-up, RO drinking water system, indoor sports facilities and parking space for student vehicles. (Two wheelers only) The hostels are strictly under CC TV surveillance. Main Hostel Dining Block: Two separate dining halls are available for boys &amp; girls, which accommodates 180 boys &amp; 60 girls at a time. This has both vegetarian and non-vegetarian centralized modern kitchens. Stores for provisions, vegetables and other commodities are placed in the basement. A branch of the Allahabad Bank and internet centre are located on the western side of the dining block. The board room of the hostel committee, office of the Indian hostels, Secretary and Warden’s chambers and the residence of the assistant warden are located in the first floor of the dining block. Multi-Purpose Hall: A multipurpose hall, a part of the hostel complex, with the dimensions of 100’ x 43’ was constructed in the year 1985. This is used for conducting the meetings, seminars, functions organized by the management, cultural programs, farewell functions, get-togethers, food arrangements for examiners etc. This hall is equipped with a stage and can accommodate about 200 peoples, attached with a green room, required furniture and audio systems. During UTSAV this hall is exclusively used for conducting auditions and musical events. Annexure-I (Outside Campus-Rented Buildings) New Boys Hostel-I (about 300 Mtrs. from Main Hostel) Address: BMSET Hostel annexure-1 (I) (Mathrushree Comforts) # 48, New #710/2, 2nd Block, BSK 1st Stage, Ashoknagar, Bengaluru-560050 Accommodation Available:34 17 Rooms(Twin Sharing) Annexure-II (Outside Campus-Rented Building) New Boys Hostel-II (about 300 Mtrs. from Main Hostel) Address: BMSET Hostel annexure-11 (II) (Muniyamman Nilaya) # 898/25, 2nd Block, BSK 1st Stage, Ashoknagar, Bengaluru-560050 Accommodation Available:48 24 Rooms(Twin Sharing) Annexure-III (Outside Campus-Rented Building) New Hostel (Adjacent to Mess Block)) Address: BMSET Hostel annexure-111 (III) (Chinnapa Krupa) # 9/3, 2nd Cross, N.R. Colony, Basavanagudi, Bengaluru-560019 Accommodation Available:44 22 Rooms(Twin Sharing) Annexure-IV (Outside Campus-Rented Building) - Boys hostel ( about 1000 mts from Main hostel) Address: #73, vidhyapeetha road, Balaji Nagar, BSK 3rd Stage, Bengaluru-560085. Accommodation Available:50 Annexure-V (Outside Campus-Rented Building) - Boys hostel ( about 400 mts from Main hostel) Address: #73, vidhyapeetha road, 6th Cross, Ashoknagar, BSK 3rd Stage, Bengaluru-560085. Accommodation Available: 60</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-03-14T06:31:56.517Z</v>
+        <v>2026-03-19T18:35:09.675Z</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>https://bmsce.ac.in/home/Hostel-Prevention-and-Prohibition-of-Ragging</v>
+        <v>https://bmsce.ac.in/home/About-Data-Center</v>
       </c>
       <c r="B32" t="str">
         <v>html</v>
       </c>
       <c r="C32" t="str">
-        <v>Prevention and Prohibition of RaggingHomeFacilitiesHostel PREVENTION AND PROHIBITION OF RAGGING IN THE B.M.S.EDUCATIONAL TRUST HOSTELS Objective: Ragging of students admitted to B M S Educational Trust Hostel is totally prohibited and banned both in the Campus and Hostels (including IH). Any violation of this by the Students/Hostelites will be viewed very seriously and punished as per the regulations prevailing in the State and the Central Government. The Punishment will be severe / harsh which can be to the extent of rusticating from the Institution and / or removed from the Hostel without any notice by forfeiting all kinds of refundable deposits. The B M S Educational Trust Hostel has constituted an Anti-ragging committee, comprising of dedicated cadre of wardens headed by the secretary. It shall monitor the anti-ragging activities in the hostels, consider the recommendations of the anti-ragging squad and take appropriate decisions, including spelling out suitable punishments to those found guilty. It shall also monitor and oversee the performance of the anti-ragging squad in prevention of ragging in the hostels. Other measures for prevention of ragging: The wardens will pay regular visits, periodic meetings/counseling and orientations for students (for freshers separately as well as jointly with the seniors). The professional counselors will be called for psychological counseling during the first three months of the new academic year. The security personnel posted in the hostels especially at vulnerable places and will be under the direct control of the wardens and assessed by them. If necessary intense policing shall be escorted to at such points at odd hours during early months of academic sessions. Anonymous random surveys will be conducted by the wardens or design its own methodologies of conducting such surveys. Freshers welcome parties will be organized in the hostels by senior students and the hostel management together soon after the admissions, preferably with in first two weeks of the beginning of the academic session, thus helping them to shed their inferiority complex, if any, remove their inhibitions. A student seeking admissions to the hostels will have to submit an affidavit during the time of allotment of their room that he/she is also aware of the law in this regard and agrees to abide by the punishment meted out if he/she is found guilty of ragging and/or abetting ragging as in ANNEXURE-II of the application. The parents shall also have to submit an affidavit during the allotment of the room that their son/daughter/ward will not indulge in any act of ragging, if they found guilty of any aspects of ragging, they may be punished as per the AICTE/UGC/VTU/ Supreme Court regulations as in ANNEXURE-III of the application. Action to be taken against students indulging and abetting ragging: Depending upon the nature and gravity of the offense as established by the anti-ragging committee of the hostels, the possible punishments for those found guilty of ragging at the Hostel level shall be any one of or combinations of the following: First the matter will be brought to the notice of the secretary of the hostels by the wardens (anti-ragging committee). Then the matter shall be informed to the parents/guardian immediately by the wardens and shall ask them to come to the hostels within 48 hours. The matter shall also be informed to the Principal, concerned HOD’s and their Proctor. The matter shall also be informed to the placement officer debarring from appearing in any tests/examination or withdrawing from any placement opportunities. Till the parents/guardian arrival, he/she will be suspended from the mess and will be provided separate accommodation with minimum facilities. The anti-ragging committee of the hostels may recommend for further punishments as follows: Suspension from the mess. Expulsion from hostels (forfeiting any kind of refunds or deposits). Recommend to the college cancellation of admission, suspending from attending classes. Withholding/Withdrawing scholarships/ fellowship and other benefits. Debarring from representing the institution in any regional, national, International meet, tournament, youth festival etc. Rusticating from the institution for a period ranging from 1 to 4 semesters. Fine ranging from Rs.25,000/- to Rs.50,000/-. For Further details, refer the Information brochure with Rules and Regulation of the Hostel. HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About Data Center Dr.Gowrishankar Chief Coordinator chiefcoordinator@bmsce.ac.in Data Centre &amp; Campus Wide Networking The Data Centre monitors the Campus Wide Networking (CWN) facility of the institution for ubiquitous network connectivity throughout the campus. At present CWN is having three redundant high end carrier class core switches and two hundred access switches. The Connectivity between the core switch to the access switch is though multimode fiber optic backbone. The existing bandwidth of the intranet is 10 GBPS. Currently the CWN is supplemented with 4.7 GBPS of redundant internet link to cater to the internet requirement of the campus. The college has hosted a private cloud on virtualized environment of flex servers with fiber SAN storage to meet the computing requirement of the campus. Campus intranet has paved way to provide seamless access to e-journals, online lecture streaming and application software. The Data Centre also hosts e-mail and webservers of the institution. Additionally, the CWN is supplemented with mobility aware wireless connectivity of wireless network enabled electronic gadgets of students and staff. APNIC, of which BMSCE is a proud member, has allotted three blocks of static IP addresses and ASNs. This facilitated the institution a global presence in the internet domain. In India BMSCE is the first educational institution to obtain APNIC membership and static IP addresses. Features Monitors Campus-wide networking facility Ubiquitous network connectivity through Wi-Fi 2 Nos Flex Servers with 24 TB storage 4 Rack Mount Servers Enable offline access to NPTEL lectures Enables online access to International Journals Dedicated 4.7 Gbps Mbps leased line 24/7 Internet facility to the college / hostels Official email Service &amp; Messaging Total number of computers on network-4100 Number of Printers-400 Number of Copiers-25 Total number of Core Switches 3 Nos Total number of Non-POE Switches 250 Nos Total number of POE Switches 25 Nos Total number of Wifi Access Points 350 Nos Total number of Firewall 1 No Licensed System Software’s- 8 Licensed Application Software’s- 95 Escan Antivirus Software - 5000 users Qualified technical support staff</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-03-14T06:31:57.447Z</v>
+        <v>2026-03-19T18:35:10.307Z</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>https://bmsce.ac.in/home/Hostel-Gallery</v>
+        <v>https://bmsce.ac.in/home/About-Sports</v>
       </c>
       <c r="B33" t="str">
         <v>html</v>
       </c>
       <c r="C33" t="str">
-        <v>GalleryHomeFacilitiesHostel HostelAbout BMSET HostelsActivitiesChargesCode of Conduct for HostelitesFee StructureHostel AdmissionHostel Committee MembersHostel ManagementList of HostelsHostel SecretaryMembers &amp; WardensPrevention and Prohibition of RaggingGalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About Sports B.M.S College of Engineering has made name for itself in several sports - indoor &amp; outdoor like Archery, Badminton, Basketball, Chess, Cricket, Football, Handball, Hockey, Judo, Kabaddi, Kho-Kho, Netball, Powerlifting, Swimming, Tennis, Table Tennis, Throwball, Volleyball, Softball, Yoga, Wrestling and Weight Lifting. The institution supports and encourages the students to involve in these sports. We are ranked at the top by VTU for securing highest points in Sports &amp; cultural Competitions/tournaments. We are grateful to the management for providing Indoor &amp; outdoor stadiums and well equipped gym facilities with International standards. The Majestic Indoor Stadium we see today at B.M.S.C.E is the result of the Physical Education Director's vision and hard work and also the encouragement by BMS Management. In the year 2000 he prepared the project for the construction of the Indoor Stadium. This was approved by the MHRD and the matching grant was received and the project got completed in 2004. The Department offers proper scientific and technical training to its teams by trained and experienced professionals. Providing opportunities to promote sports programmes and bringing about qualitative improvement in the performance of sports persons is the goal of the department. The Department organized South Zone Inter University Table Tennis Competition (Men &amp; Women) in the year 2006. State Level Memorial Tournament “BMSCE KREEDOTSAV” is being conducted every year. It was started in the year 1996 &amp; we have been the Overall Champions for many years. National Level Inter Collegiate Techno - Cultural Festival “UTSAV” is conducted on a yearly basis with the support of the Management and it has been ranked first in Karnataka in the top ten cultural festival listed by Deccan Herald. The Principal and management are very supportive of the Athletes &amp; Artists who take part in sports and cultural activities. Cash incentives of Rs.3,000/-, Rs.2,000/- &amp; Rs.1,000/- respectively is awarded from the institution to the Winners, Runners &amp; Second Runners-Up in VTU Inter-Collegiate competitions. The Students are very active, interested and dedicated and make use all the facilities provided by the management through the Department of Physical Education and Sports Science. We have left no stones unturned in bringing laurels to the college. Director, Physical Education of B.M.S.C.E was nominated as Coach for Indian Aquatic Team (M&amp;W). The AIU Aquatic team participated in 30th World Summer Universiade 2019 at Napoli, ITALY held from 3rd to 14th July 2019. Director, Physical Education of B.M.S.C.E was nominated as Coach for BCCI South Zone Cricket (M) and the team participated in the Vizzy Trophy Cricket Tournament held at Gwalior from 17th March 2019. Director, Physical Education of B.M.S.C.E was nominated as Manager of VTU Cultural team and it participated in 3rd SAUFEST, held at Katmandu University, Katmandu, Nepal from 7th to 11th February 2008. INTRODUCTION: Department of Physical Education &amp; Sports Science serve as a vital and integral part of the student life in campus. The mission of the department is to provide a broad spectrum of sports, recreation and leisure activities for students, staff and faculty, as well as the members of the local community. The primary direction is to provide services and programs that stimulate growth, development and retention of students in a contemporary and safe environment that develops fitness and wellness, social interaction and leadership opportunities. VISION: To engage in relentless pursuit of excellence in promotion and development of Physical Education, sporting and extra-curricular activities through an innovative approach in teaching, coaching, research and outreach activities and to evolve a holistic approach to the all-round betterment of human resources through a harmonious blend of body, mind and spirit. MISSION: To design and introduce innovative, integrated, inter-disciplinary curriculum in physical education, sports, games and allied areas. To recognize and encourage budding athletes/students with potential and further encourage them by coaching/training. To develop and provide modern amenities in par with the Global standards in the field of sporting. To produce dedicated and passionate sports persons, who will always display high morale and sportsmanship at all times.</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-03-14T06:31:58.404Z</v>
+        <v>2026-03-19T18:35:10.944Z</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>https://bmsce.ac.in/home/BMS-Hospital</v>
+        <v>https://bmsce.ac.in/home/About-Placements</v>
       </c>
       <c r="B34" t="str">
         <v>html</v>
       </c>
       <c r="C34" t="str">
-        <v>BMS HospitalHomeFacilities B.M.S Campus Health Care Centre Dr. Megha BMS Campus Health Care Centre BMS College of Engineering Bull Temple Road,Bangalore-19 B.M.S Hospital Opp. BMS Engineering College, Bull Temple Road, Bangalore – 560019, Karnataka Phone: 91(80) 26613888/26613993 Mobile: +91 9900013234 Website: http://bmshospital.com/ Six decades ago a man with a mission to educate people first private Engineering College. The man was none other than the founding father of BMS educational institution Sri B.M Sreenivasaiah. His son, Mr. B.S Narayan, pursued his father’s dream to help the needy and laid the foundation stone for B.S Narayan memorial hospital in the year 1991. Before his efforts could gain momentum his soul left us with the responsibility to carry forward his legacy and give the best affordable medical facility. Our life trustee Mrs. Ragini Narayan, kindled by the benevolent and noble thoughts of her husband, has turned B.S Narayan Memorial Day Care center into a state of the art multidimensional hospital, where anyone can seek cure and are under the guidance of experienced doctors without worrying about the cost. Facilities and Specialities Facilities Available Specialities Available OPD Consultations General Medicine Emergency General Surgery Operation Theatre with fully Equipped Recovery Room Obstetrician and Gynecology Trauma and Casualty Pediatrics Inpatient Services Orthopedic and Physiotherapy Radiology (Digital X-Ray, Ultrasound, Doppler) Cardiology 2D Echo + Colour Doppler, TMT(Stress ECG) Diabetology Laboratory Gastroenterology Pulmonary Function Test Oncology Physiotherapy ENT Ambulance Services Pulmonology Pharmacy Urology Yoga Nephrology Dentistry Ophthalmology Cosmetology Neurology Thermal Mammography FacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>About Placements Dr. J. Sharana Basavaraj Professor Dean, Training and Placement Years of experience: 28 Phone: +91-80-22423789, +91-80-26603936 Email: placement@bmsce.ac.in Dr. K.R.Sudhindra Professor Associate Placement Officer Years of experience: 18 Phone: +91-80-22423789, +91-80-26603936 Email: placement@bmsce.ac.in Dr. Nandhini Vineeth Professor Associate Placement Officer Years of experience: 17 Phone: +91-80-22423789, +91-80-26603936 Email: placement@bmsce.ac.in B.M.S College of Engineering has authored and set many examples of yeomen student centric initiatives. One such initiative is the Department of Training and Placement. The Institution ﬁrmly believes that placements are the major benchmark to the performance of the institute. The placement cell is the nodal center and an integral part of the institution. Started during 1995 it has scaled great heights and touched about 18500+ cumulative offers since its inception. The centre has very active linkages and collaborations with industry. The centre helps students in pursuing their career interests and also assists the employers in achieving their hiring goals. The vital roles of the Centre is to groom and shape the students and make them industry ready by imparting necessary skills and training. More than 350 reputed National and Multinational companies visit our institution for campus recruitment annually. The department facilitates training programs on soft-skills and technical talks from industry experts. Online mock assessments on quantitative aptitude and competitive coding are conducted for the benefits of students. The centre offers state-of-the-art physical, communication and computing infrastructure for its effective functioning. Our highly skilled and dedicated staff will deliver precisely planned services to the student community and companies. Our highly skilled and dedicated staff will deliver precisely planned services to the student community and companies. Vision To emerge as a most preferred destination for all corporates to hire globally competent and ethically strong engineering talent. Mission To nurture fresh talent to be industry ready by conducting purposeful and value added teaching and training. To identify the right career option for the students in tandem with their skills, personal values and interest. To strive hard to enhance the employability of students and meet the aspirations of the students and corporate community. To facilitate students to acquire contemporary and futuristic skills. Process The placement ofﬁce shall establish network and build relations with potential recruiters. Invitation will be sent to potential recruiters to visit the Institute. The placement team communicates the dates for campus visit for each recruiter by considering factors like student preference, job proﬁle etc. Companies are encouraged to give pre-placement talks before the commencement of recruitment process. The companies conduct different rounds of selection process (aptitude test, group discussion, technical interviews and HR interviews) and inform the names of selected students to the placement department. The same shall be communicated to the concerned students and take acceptance from students. The placement ofﬁce conducts general follow-up, joining formalities and other administrative activities. Message from Advisor In the emerging and fast changing world, there an obvious need to produce graduates high level of adaptability, and who are innovate enough to face the diverse challenges. B.M.S.C.E has been promoting quality engineering education over the past seven decades to meet the develpment needs of the country. The institution seeks to provide best possibile opportunities to its students and make them ready to enter the industry portals. Rigorous sylabus and practival industry exposure has instilled confidence in our students to face real-time problems. The Training &amp; Placement Centre strongly believes that each student is a valuable resource and focuses in maximising their career prospects by providing comprehensive career solutions. I thank all the stake holders for their sustained support to the institution and look forward for stronger and deeper relationship. My best wishes to the student community. Dr.H S Jagadeesh Advisor Message from Dean,Training and Placement Dear Recruiter, BMSCE has a rich tradition of producing professionally competent graduates by providing value-based and quality education. The Institution ensures that they are adaptable to ever changing demands and requirements of the world. Seven decades and counting, BMSCE graduates go through an updated, balanced but rigorous program. The teaching methodology has high focus on self-learning and practice. The outcome-based curriculum design and teaching method adopted by the Institution focuses on learning outcomes where the emphasis is on what a student is able to learn and do after the learning activity. The Institution has been embarking the syllabus by bench-marking with the syllabus of reputed institutions like NIITs, etc. BMSCE also provides its students a wide range of training programmes aimed at enhancing their employability skills, as well as providing them with many curricular and extra-curricular events to ignite their minds. We are confident that our graduates would be able to adapt to various challenging situations and fulfil the organisational objectives. I am sure that our students will turn out to be assets to your organisation. With great honour and pride, I take this opportunity to extend a warm invitation to the recruiters and hope that we will enjoy a mutually beneficial relationship. Dr.J. Sharana Basavaraja Dean, Training and Placement Message from Associate Placement Officers, Training and Placement BMSCE has a strong rooted belief in quality education and responsibility in making every student industry ready. The Training &amp; Placement Centre equips its students with skills that will help them contribute almost immediately to the organizations that they join. The centre regularly interacts with the industries to increase the employment opportunities of the students and also increase their awareness on realtime working environment. We highly appreciate the confidence reposed in us and the invalueable support extended by our recruiters over the years. You are our biggest strength and we seek your continued patronage at all times. We are confident that recruiters looking for talented pool of people will be greeted with young, bright and aspiring minds. Dr. K.R.Sudhindra, Dr. Nandhini Vineeth Associate Placement Officers</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-03-14T06:31:59.332Z</v>
+        <v>2026-03-19T18:35:11.583Z</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>https://bmsce.ac.in/home/About-Data-Center</v>
+        <v>https://bmsce.ac.in/home/Placement-Recruiting-Companies</v>
       </c>
       <c r="B35" t="str">
         <v>html</v>
       </c>
       <c r="C35" t="str">
-        <v>About Data CenterHomeFacilitiesData Center Dr.Gowrishankar Chief Coordinator chiefcoordinator@bmsce.ac.in Data Centre &amp; Campus Wide Networking The Data Centre monitors the Campus Wide Networking (CWN) facility of the institution for ubiquitous network connectivity throughout the campus. At present CWN is having three redundant high end carrier class core switches and two hundred access switches. The Connectivity between the core switch to the access switch is though multimode fiber optic backbone. The existing bandwidth of the intranet is 10 GBPS. Currently the CWN is supplemented with 4.7 GBPS of redundant internet link to cater to the internet requirement of the campus. The college has hosted a private cloud on virtualized environment of flex servers with fiber SAN storage to meet the computing requirement of the campus. Campus intranet has paved way to provide seamless access to e-journals, online lecture streaming and application software. The Data Centre also hosts e-mail and webservers of the institution. Additionally, the CWN is supplemented with mobility aware wireless connectivity of wireless network enabled electronic gadgets of students and staff. APNIC, of which BMSCE is a proud member, has allotted three blocks of static IP addresses and ASNs. This facilitated the institution a global presence in the internet domain. In India BMSCE is the first educational institution to obtain APNIC membership and static IP addresses. Features Monitors Campus-wide networking facility Ubiquitous network connectivity through Wi-Fi 2 Nos Flex Servers with 24 TB storage 4 Rack Mount Servers Enable offline access to NPTEL lectures Enables online access to International Journals Dedicated 4.7 Gbps Mbps leased line 24/7 Internet facility to the college / hostels Official email Service &amp; Messaging Total number of computers on network-4100 Number of Printers-400 Number of Copiers-25 Total number of Core Switches 3 Nos Total number of Non-POE Switches 250 Nos Total number of POE Switches 25 Nos Total number of Wifi Access Points 350 Nos Total number of Firewall 1 No Licensed System Software’s- 8 Licensed Application Software’s- 95 Escan Antivirus Software - 5000 users Qualified technical support staff Data CenterAbout Data CenterCoordinator &amp; StaffData Center GalleryFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>Recruiting Companies COMPANIES VISITED FOR – 2024 ABB (HITHACHI) E2OPEN MOTORALA ACCENTURE EDGEVERVE MRESULT ACCOLITE EDUREKA MRT ACCURENT IDC ELI LILLY NATIONAL INSTRUMENTS ACE DESIGNERS LIMITED ELLUCIAN NCR ADECCO NETAPP ADOBE EMBITAL NETAPP CODE HUB AIRASIA ENARKA NETCRACKER AIRTEL ENDURANCE NETRADYNE AKAMAI ENVESTNET YODLEE NETSKOPE AKZONOBEL ENZEN NEXTUPLE INDIA PVT.LTD ALIEN BRAINS ERICSSON NO BROKER ALSTOM ESI NOESYS ALTIMETRIK EUROFINS NOKIA AMADEUS EY GDS NOVARTIS AMAGI EY INDIA NOVELSYNTH AMAZON FAURECIA NOVOZYMES AMAZON (NON TECHNICAL) FINASTRA NTT DATA AMAZON (TECHNICAL) FINFLUX NUMOCITY AMBERROOT SYSTEMS FLY GOLDFINCH NUTANIX AMD FYNDHREE NUTANIX (2ND TIME) AMDOCS GE APPLIANCE NXP SEMICONDUCTORS AMITI SOFTWARE GE HEALTH CARE OLCADEMY ANALOG GOLDMANSACH ORACLE ANSYS SOFTWARE PVT.LTD HANSA PAYTM APISERO HERMAN MILLER PEACOCK SOLAR APOLLO HEVO DATA PENSANDO SYSTEMS APPLIED MATERIALS HFCL PERFAWARA APTIV PEAK SOFTWARE PHILIPS ARCADIS HIKAL PLANETSPARK ARRIS (COMMSCOPE) HOMELANE PRIMENUMBER TECHNOLOGIES ARYAKA HONEYWELL PROTEGRITY ASTRA ZENECA HP (PHYSICALLY CHALLENGED) PROTONN ATHENA HEALTH HPE PUBLICIIS SAPIENT ATHER ENERGY HUL Q2 SOFTWARE AVANTI HUMAN FRACTAL QUALCOMM AVIN SYSTEM HUNGER BOX QUANTIPHI AXELOR TECHNOLOGIES HYPERVERGE QUICK RIDE BARTLEBY IBM QUPO INDIA BLUEYONDER IGNITARIUM RACANNA ENERGY BLUEYONDER (YANTRIKS) INDEGENE RELEVANCE LAB BOSCH INFINEON RESIDEO BRIGOSHA TECHNOLOGIES INFOBLOX RIBBON COMMUNICATION BRILLIO INFOGAIN RINEX CADENCE INFOSYS RISHAB INSTRUMENTS CADENCE DESIGN SYSTEMS INFOSYS (HACKWITHINFY) ROBERT BOSCH CANFIN HOMES INFYNIX ROCKWELL CAPGEMINI INMOVDU TECH RYSTAD ENERGY CARGILL INTEL SABRE CORPORATION CAROUSELL INTELIPAAT SAHAJ SOFTWARE CATERPILLAR INTELLICAR TELIMATICS SALES FORCE CELEBFIE INTERNSHALA SANDVINE CERMATI INTUGINE(FLIPER) SCHNEIDER ELECTTRIC CGI INTUIT SCIERA CISCO IP EXCEL SECON CISMA JUMBOTAIL SEDIGN SOLUTION CLARIVATE KALEYRA SHELL CLOUDERA KAS SERVICES SIEMENS TECHNOLOGY CLUMIO KHATIB ALAMI SIGNALCHIP INNOVATIONS PVT.LTD CODEWALLA KICKDRUM SIXT R&amp;D COHESITY KPMG SKILLLABOURS COLLINS AEROSPACE L&amp;T CONSTRUCTION TALENT SERVE COMMSCOPE LAM RESEARCH TALERANG COMMVAULT LEGATO TCS (CODEVITA) CONGA LIFERAY TCS (DIGITAL) CROPIN LINDE TE CONECTIVITY CSG LOGMEIN TELAVERAGE CYIENT LOHIA TELSTRA CYPRESS SEMICONDUCTORS LTTS TEXTRON DANSKE IT LTTS THE MATH COMPANY DATA CHAI MAGNITUDE TITAN DEEVIA MAST GLOBAL TOYOTA KIRLOSKAR DELHIVERY MAVENIR SYSTEM TREDENCE ANALYTICS DELL TECHNOLOGIES (LIVE PROJECT) MCKINLEY AND RICE UNISYS DELOITTE (INDIA) MCKINSEY DIGITAL LAB VALUE BOUND DELOITTE (US) MEDRIX HEATH CARE VERZEO DELPHI (BORGWARNER) MERCEDES BENZ VOLVO DELTA ELECTRONICS MICROCHIP WILEY DXC TECHNOLOGIES MINDSET XIAOMI DEVTOOLS MINDTREE ZEBRA TECHNOLOGIES DIGITAL HORIZON MOLEX INDIA BUSINESS SEERVICES PVT.LTD ZINNOV (BAZAAR VOICE) DINERO MONEYVIEW ZS ASSOCIATES DXC TECHNOLOGIES MOSAIQUE ZYCUS</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-03-14T06:32:00.278Z</v>
+        <v>2026-03-19T18:35:12.209Z</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>https://bmsce.ac.in/home/About-Sports</v>
+        <v>https://bmsce.ac.in/assets/img/Slider/Admission_document_and_process_flow.pdf</v>
       </c>
       <c r="B36" t="str">
-        <v>html</v>
+        <v>pdf</v>
       </c>
       <c r="C36" t="str">
-        <v>About SportsHomeFacilitiesSports B.M.S College of Engineering has made name for itself in several sports - indoor &amp; outdoor like Archery, Badminton, Basketball, Chess, Cricket, Football, Handball, Hockey, Judo, Kabaddi, Kho-Kho, Netball, Powerlifting, Swimming, Tennis, Table Tennis, Throwball, Volleyball, Softball, Yoga, Wrestling and Weight Lifting. The institution supports and encourages the students to involve in these sports. We are ranked at the top by VTU for securing highest points in Sports &amp; cultural Competitions/tournaments. We are grateful to the management for providing Indoor &amp; outdoor stadiums and well equipped gym facilities with International standards. The Majestic Indoor Stadium we see today at B.M.S.C.E is the result of the Physical Education Director's vision and hard work and also the encouragement by BMS Management. In the year 2000 he prepared the project for the construction of the Indoor Stadium. This was approved by the MHRD and the matching grant was received and the project got completed in 2004. The Department offers proper scientific and technical training to its teams by trained and experienced professionals. Providing opportunities to promote sports programmes and bringing about qualitative improvement in the performance of sports persons is the goal of the department. The Department organized South Zone Inter University Table Tennis Competition (Men &amp; Women) in the year 2006. State Level Memorial Tournament “BMSCE KREEDOTSAV” is being conducted every year. It was started in the year 1996 &amp; we have been the Overall Champions for many years. National Level Inter Collegiate Techno - Cultural Festival “UTSAV” is conducted on a yearly basis with the support of the Management and it has been ranked first in Karnataka in the top ten cultural festival listed by Deccan Herald. The Principal and management are very supportive of the Athletes &amp; Artists who take part in sports and cultural activities. Cash incentives of Rs.3,000/-, Rs.2,000/- &amp; Rs.1,000/- respectively is awarded from the institution to the Winners, Runners &amp; Second Runners-Up in VTU Inter-Collegiate competitions. The Students are very active, interested and dedicated and make use all the facilities provided by the management through the Department of Physical Education and Sports Science. We have left no stones unturned in bringing laurels to the college. Director, Physical Education of B.M.S.C.E was nominated as Coach for Indian Aquatic Team (M&amp;W). The AIU Aquatic team participated in 30th World Summer Universiade 2019 at Napoli, ITALY held from 3rd to 14th July 2019. Director, Physical Education of B.M.S.C.E was nominated as Coach for BCCI South Zone Cricket (M) and the team participated in the Vizzy Trophy Cricket Tournament held at Gwalior from 17th March 2019. Director, Physical Education of B.M.S.C.E was nominated as Manager of VTU Cultural team and it participated in 3rd SAUFEST, held at Katmandu University, Katmandu, Nepal from 7th to 11th February 2008. INTRODUCTION: Department of Physical Education &amp; Sports Science serve as a vital and integral part of the student life in campus. The mission of the department is to provide a broad spectrum of sports, recreation and leisure activities for students, staff and faculty, as well as the members of the local community. The primary direction is to provide services and programs that stimulate growth, development and retention of students in a contemporary and safe environment that develops fitness and wellness, social interaction and leadership opportunities. VISION: To engage in relentless pursuit of excellence in promotion and development of Physical Education, sporting and extra-curricular activities through an innovative approach in teaching, coaching, research and outreach activities and to evolve a holistic approach to the all-round betterment of human resources through a harmonious blend of body, mind and spirit. MISSION: To design and introduce innovative, integrated, inter-disciplinary curriculum in physical education, sports, games and allied areas. To recognize and encourage budding athletes/students with potential and further encourage them by coaching/training. To develop and provide modern amenities in par with the Global standards in the field of sporting. To produce dedicated and passionate sports persons, who will always display high morale and sportsmanship at all times. SportsAbout SportsFaculty and CoachesUpcoming EventsFacilitiesEvents OrganisedAchievementsLegends of BMSCEBMSCE FITNESS CHALLENGEKREEDOTSAV 2022-23KREEDOTSAV 2021KREEDOTSAV 2019KREEDOTSAV 2018PULSEFitness and Yoga TrainingGallerySports CalendarContact UsFacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>Admission Process Flow Procedure www.bmsce.ac.in For any query: 080-26614357 College E-mail ID Creation College official mail ID along with Password provided, keep it safely for future process. Photography Live photo is taken for ID card purpose KEA Admission card download Document Verification Process Candidate should take allotment copy from respected KEA portal for verification process Online Admission form process Candidate should fill required details in college portal and pay the college miscellaneous fee through online. Candidate should submit required documents in college along with a set of self attested copy. (Soft &amp; Hard Copy) admissionsupport@bmsce.ac.in Start Exit B.M.S. COLLEGE OF ENGINEERING (An Autonomous Institute, Affiliated to VTU, Belagavi) Step 1 Step 2 Step 3 Step 4 Step 5 ENGINEERING ADMISSIONS 2025-2026 B.M.S. COLLEGE OF ENGINEERING, BENGALURU (AUTONOMUS INSTITUTION UNDER VTU) C h e c k l i s t o f t h e O r i g i n a l D o c u m e n t s t o b e submitted by the Candidates selected through CET / at the time of verification of documents in the college DCET KEA Verifica_x0000_on Slip TH II PUC/12 STD. / Diploma (For DCET) Marks Cards A.Study Cer_x0000_ficate from previous College/ Ins_x0000_tute (Total 07 Years) B.Students allo_x0000_ed under RURAL / Kannada Medium QUOTA are required to submit 10 years cer_x0000_ficates Caste Cer_x0000_ficate in case of Reserved Category [ i.e., SC, ST &amp; OBC] and students admi_x0000_ed under SNQ Quota are required to submi_x0000_ed Income Cer_x0000_ficate compulsorily Transfer Cer_x0000_ficate Migra_x0000_on Cer_x0000_ficate shall be submi_x0000_ed by Non-Karnataka students and students who have passed their qualifying examina_x0000_on other than PU Board. Students allo_x0000_ed under SPECIAL CATEGORY QUOTA (i.e. NCC, Sports, PH, Defence candidates etc.,) are required to submit the relevant original cer_x0000_ficates &amp; students admi_x0000_ed under Hyderabad Karnataka Quota (371J), are required to submit the relevant original cer_x0000_ficates. [ Annexure - “A'' – Eligibility Cer_x0000_ficate &amp; Annexure - “B'' – Residience Cer_x0000_ficate] Recent Photos – 02 Nos. (Passport Size) Copy of AADHAAR CARD and any other documents if required CANDIDATES HAVE TO SUBMIT ORIGINALS OF ALL THE ABOVE DOCUMENTS FOR VERIFICATION ALONG WITH OF SELF TWO SETS ATTESTED XEROX COPIES. . STUDENTS ARE INFORMED TO KEEP SUFFICIENT COPIES OF NOTE : THE ABOVE DOCUMENTS WITH THEM AS THE ORIGINAL WILL BE SENT TO VTU FOR APPROVAL OF THEIR ADMISSION. Q ORIGINAL MARKS CARDS WILL BE RETURNED TO STUDENTS ONLY AFTER APPROVAL OBTAINED / U S N RECEIVED FROM V T U, BELAGAVI. COLOUR XEROX NOT ALLOWED INSIDE THE VERIFICATION CENTER ENGINEERING ADMISSIONS 2025-2026 B.M.S. COLLEGE OF ENGINEERING, BENGALURU (AUTONOMUS INSTITUTION UNDER VTU) Check list of the Original Documents to be submitted by the Candidates selected through at the time of verification of Management &amp; Comed-K documents in the college Seat Allotment Letter issued by Comed-K / Original Fee reciept issued by Management (04 Copies) . Please ensure that the candidate name and parent name should be printed as per SSLC / 10th STD. marks cards TH II PUC/12 STD. Marks Cards TH SSLC / 10 STD. Marks Cards [ for proof of Date of Birth] Transfer Cer_x0000_ficate Migration Certificate shall be submitted by Non-Karnataka students and students who have passed their qualifying examination other than PU Board. Students allotted through Comed-K under Hyderabad Karnataka Quota, are required to submit the relevant original certificates. [ Annexure - “A'' – Eligibility Certificate &amp; Annexure - “B'' – Residience Certificate] Rank Card of any one of the Competitive Examination i.e, CET/Comed-K / JEE of Current Year (i.e., 2025-26 ) in respect of Management Quota only Recent Photos – 02 Nos. (Passport Size) Copy of AADHAAR CARD and any other documents if required CANDIDATES HAVE TO SUBMIT ORIGINALS OF ALL THE ABOVE DOCUMENTS FOR VERIFICATION ALONG WITH OF TWO SETS SELF ATTESTED XEROX COPIES. STUDENTS ARE INFORMED TO KEEP SUFFICIENT COPIES NOTE : OF THE ABOVE DOCUMENTS WITH THEM AS THE ORIGINAL WILL BE SENT TO VTU FOR APPROVAL OF THEIR ADMISSION. a ORIGINAL MARKS CARDS WILL BE RETURNED TO STUDENTS ONLY AFTER APPROVAL OBTAINED / U S N RECEIVED FROM V T U, BELAGAVI COLOUR XEROX NOT ALLOWED INSIDE THE VERIFICATION CENTER B.M.S. COLLEGE OF ENGINEERING, BENGALURU (AUTONOMUS INSTITUTION UNDER VTU) ENGINEERING ADMISSIONS 2025-2026 GENERAL INSTRUCTIONS TO CANDIDATES Venue : CCP Lab – FOURTH FLOOR, PG BLOCK Step Step by Step Process Venue On-line entry of application Remittance of Fees On-Line / Indian Bank, BMSCE Campus 1. 2. 3. 4. 5. 6. 7. 8. 9. 10. 1. 2. 3. 4. 5. 6. 7. 8. 9. 10. 1. 2. 4. TH SSLC / 10 STD. Marks Cards [ for proof of Date of Birth] A. Study Cer_x0000_ficate from previous College/ Ins_x0000_tute B. Caste Cer_x0000_ficate in respect of students having score less than 45% in qualifying examina_x0000_on i.e.,II PUC/12TH Std Lunch Time: 01.00 PM to 02.00 PM 3. AT VERIFICATION CENTER [4th Floor] CCP LAB [4th Floor] CCP LAB [ 4th floor PG, BLOCK] Students are required to Submit all the original documents and Scan file along with name. The scan file should be in JPEG format only (200 DPI resolution) &amp; size should be less than 2MB and need to be submitted in the form of soft copy compulsorily. (Mobile scanned copy not allowed) Documents Verification &amp; submit Original Documents along with three sets of self-attested copies in respect of Comed-K &amp; Management Students and Two Sets of self-attested copies in respect of KEA Students (Colour xerox not allowed). WORKING HOURS Monday to Friday : 09.30 AM to 04.30 PM Saturdays : 09.30 AM to 01.30 PM College is remain closed on all Sundays and on Government Holidays. Process is supervised by : Prof. K Girish – Faculty of M C A People to be contacted: 1. Dr. Srinidhi Raghavan M ., (Assistant Professor, Dept. of Chemistry) In-charge of Document related issues. 2. Dr. H S Gururaja - (Faculty of CSBS) In-charge of Software related issues. Overall In-Charge of Admission Process Dr. Bheemsha Arya - Principal</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-03-14T06:32:01.209Z</v>
+        <v>2026-03-19T18:35:13.041Z</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>https://bmsce.ac.in/home/Counselling-Center</v>
+        <v>https://bmsce.ac.in/assets/img/Slider/yuva%20nidhi%20doc.pdf</v>
       </c>
       <c r="B37" t="str">
-        <v>html</v>
+        <v>pdf</v>
       </c>
       <c r="C37" t="str">
-        <v>Counselling CenterHomeFacilities Sneha Harish PSYCHOLOGIST B.A MSc Clinical psychology snehah@bmsce.ac.in The counseling center at BMSCE was started in April 2016. Sneha Harish is in charge of the center right from inception. The center was started with the vision of fostering holistic development of students by addressing their social, emotional and psychological needs apart from their regular academics. The center provides professional, confidential, effective and accessible counseling in a friendly &amp; non-threatening setting and acts as a resource for faculty &amp; parents in managing behavioral &amp; psychological issues pertaining to students. Issues addressed are maladjustment, absenteeism, low self-esteem, lack of study skills, Relationship problems, addictions, and parental issues of students. On an average 40-50 students are approaching the center with their concerns. Nearly 150 to 180 sessions are held every year. The center is open from 10 AM to 4 PM, Monday to Friday and on Saturday from 10 AM to 1 PM, in PG Block 4th floor, B.M.S College of Engineering. FacilitiesBMS HospitalLibraryHostelData CenterSportsCounselling Center</v>
+        <v>Documents required for Yuva Nidhi Scheme Karnataka ➢ Aadhaar card ➢ Residence/domicile certificate ➢ Income certificate ➢ Educational qualification documents ➢ Bank account details How can you apply for Yuva Nidhi Scheme Karnataka Here are the steps to apply for the Yuva Nidhi Scheme in Karnataka: ➢ Visit the official website of the scheme seva sindhu ➢ Click on the “Yuva Nidhi Yojana” link. ➢ Click on the “Apply Online” button. ➢ Fill out your yuva nidhi application form and upload the required documents. ➢ Click on the “Submit” button. You will receive an acknowledgement number.</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-03-14T06:32:02.151Z</v>
+        <v>2026-03-19T18:35:13.629Z</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>https://bmsce.ac.in/Glimpse</v>
+      </c>
+      <c r="B38" t="str">
+        <v>html</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Go to Website</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38" t="str">
+        <v>2026-03-19T18:35:14.211Z</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>https://bmsce.ac.in/home/news/0/dst-fist-sponsored-one-week-faculty-development-program-on-micro-and-nano-characterization-for-advanced-materials-research-1</v>
+      </c>
+      <c r="B39" t="str">
+        <v>html</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Home 09 Mar DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” Date: 09/03/2026 to 13/03/2026 Organized by Department of Electrical and Electronics Engineering in Association with Department of Physics and Department of Chemistry Click here to View Broucher Back to Home</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39" t="str">
+        <v>2026-03-19T18:35:14.824Z</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>https://bmsce.ac.in/home/news/0/illuminating-the-future-a-comprehensive-workshop-on-indian-standards-codes-and-regulations-in-lighting-1</v>
+      </c>
+      <c r="B40" t="str">
+        <v>html</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Home 16 Feb Illuminating the Future: A Comprehensive Workshop on Indian Standards, Codes and Regulations in Lighting The Bureau of Indian Standards (BIS), the National Standards Body of India under the Ministry of Consumer Affairs, Food &amp; Public Distribution, is organizing a National Program on Indian Standards, Codes and Regulations in Lighting (Bengaluru Edition) in collaboration with the Electric Lamp and Component Manufacturers Association (ELCOMA) and B.M.S. College of Engineering, Bengaluru and BMSCE IEEE PES and sensors council. Venue: B.M.S. College of Engineering. Bull Temple Road, Basavanagudi, Bengaluru, Karnataka 560019 The registration link for Bangalore session is : https://www.elcomaindia.com/?page_id=4746 Click here to View Broucher Click here to View Agenda Back to Home</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40" t="str">
+        <v>2026-03-19T18:35:15.444Z</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>https://bmsce.ac.in/home/news/0/sri-s-nijalingappa-scholarship-2025-26</v>
+      </c>
+      <c r="B41" t="str">
+        <v>html</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Home 05 Feb Sri S Nijalingappa Scholarship 2025-26 Sri S Nijalingappa Scholarship 2025-26 CLICK HERE TO VIEW MORE DETAILS Back to Home</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41" t="str">
+        <v>2026-03-19T18:35:16.038Z</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>https://bmsce.ac.in/home/news/0/networking-embedded-and-wireless-systemsnews-2025-national-conference-organised-by-the-department-of-electronics-and-communication-engineering-bms-college-of-engineering-bengaluru-on-14th-and-15th-november-2025</v>
+      </c>
+      <c r="B42" t="str">
+        <v>html</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Home 14 Nov NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru on 14th and 15th November 2025 NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru, on 14th and 15th November 2025 CLICK HERE TO VIEW WORKSHOP DETAILS CLICK HERE TO VIEW BROCHURE Back to Home</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42" t="str">
+        <v>2026-03-19T18:35:16.665Z</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>https://bmsce.ac.in/home/news/0/phase-shift-2025-meridian-on-19th-and-20th-september-1</v>
+      </c>
+      <c r="B43" t="str">
+        <v>html</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Home 19 Sep Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 Click here to view the Phase Shift 2025 brochure Back to Home</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43" t="str">
+        <v>2026-03-19T18:35:17.289Z</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>https://bmsce.ac.in/home/AllNews</v>
+      </c>
+      <c r="B44" t="str">
+        <v>html</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Home # Date News / Event Actions 1.09-03-2026DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” Read more2.16-02-2026Illuminating the Future: A Comprehensive Workshop on Indian Standards, Codes and Regulations in Lighting Read more3.05-02-2026Sri S Nijalingappa Scholarship 2025-26 Read more4.14-11-2025NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru on 14th and 15th November 2025 Read more5.19-09-2025Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 Read more6.08-09-2025Induction and Inauguration for the 2025 Batch of Students Event is on September 8th 2025 Read more7.05-04-2025Graduation Day - IIAwarding Degree Certifcates to the Autonomous Batch UG &amp; PG Graduates of 2024 on Saturday, 05th April 2025 at 4.30 PM Read more8.21-03-2025Reg-Blood Donation Drive Read more9.05-03-2025IP awareness talk on 12th March 2025 Read more10.01-02-2025Grand challenge impact Lab (GCIL) with university of Washington : Sessions Read more11.16-01-2025UDYAMOTSAV 2025 - On Thursday 16th January 2025 at 9 AM in Auditorium I, PJ Block, BMSCE Read more12.17-12-202411th Annual Alumni Day -2024 on Saturday, 21st December, 2024. Read more13.17-09-2024B.M.S. College of Engineering and B.M.S. College of Architecture Cordially invites you to "Inauguration Function of First Year B.E., &amp; B.Arch for the Academic year 2024-25 on Friday 20th September 2024. Read more14.30-07-2024Department of Civil Engineering is organising a One Week Hands-On Faculty Development Programme on “BIM Application in Civil Engineering and Construction” 29-7-2024 to 2-8-2024 Read more15.16-07-2024The Department of Computer Applications, in collaboration with the Indian Society for Technical Education (ISTE), is organizing a One Week Faculty Development Program (FDP) on DevOps. The FDP will be held in Online mode from 29th July 2024 to 03rd August 2024. Read more16.21-04-2024IEEE INTERNATIONAL CONFERENCE ON EMERGING TECHNOLOGIES IN COMPUTER SCIENCE FOR INTERDISCIPLINARY APPLICATIONS (ICETCS 2024), 22nd -23rd April 2024 Read more17.19-03-2024State-Level Wheel Chair Cricket Tournament Date: March 23, 2024. Read more18.01-02-2024First IEEE International Conference on Communications and Computer Science-2024 (InCCCS-2024) 22nd – 24th May, 2024 Read more19.12-01-2024Department of Mechanical Engineering is organising a FDP on "Latest Trends in Additive Manufacturing" from 29 January to 2 February, 2024. Read more20.27-12-2023ATAL sponsored FDP is organized from Dept. of EEE, BMSCE during 29th Jan 2024 to 3rd Feb 2024. Read more21.20-12-2023Department of Electronics and Instrumentation Engineering, conducting A one day Tech Summit “ TechSolstice ” on 21 December 2023 (Thursday) at BMSCE, Auditorium 1, Platinum Jubilee Academic Block Read more22.15-12-202310th Annual Alumni Day 2023. Read more23.15-11-2023Department of EEE in association with EEEA, invited talk on “Internship Opportunities at IISc” on 17 November 2023 (Friday),3pm at Auditorium 2. Read more24.26-10-2023" Award of 100 5G use case Labs to to selected academic institutions was held by Hon'ble Prime Minister Shri. Narendra Modiji on 27th October 2023 as part of Indian Mobile Congress, 2023 Read more25.06-06-2023Department of Electronics and Instrumentation Engineering, presents a one day workshop on ADFT-2023,'' Antenna design, Fabrication and testing workshop", on 16th June 2023 (Friday) at Auditorium 1,PJAB , BMSCE. Read more26.06-05-2023Faculty development programme on "Current Trends in Material Physics for Engineering Applications" by the Department of Physics from 15-05-2023 to 19-05-2023. Read more27.27-04-2023Department of EEE is organising an FDP in blended mode on "Modelling and Design of Power Converters-Hands-On '' from 15th May to 19th May 2023. Read more28.20-04-2023Department of Computer Science and Engineering &amp; Department of Medical Electronics organizing one week FDP/SDP on “Bio-Medical Signal Acquisition and Analysis " 24th April 2023 to 28th April 2023 Read more29.28-03-2023Department of Electronics and Instrumentation Engineering Organizing “IACT 2023” (ISA Bangalore Automation and Control Technology day) on 31st March (Friday) and 1 April, (Saturday) 2023 Read more30.12-01-2023Department of Computer Applications organizes Two Weeks Value Added Program on “Augment Reality” in Blended mode Date: 18th January 2023 to 31th January, 2023 Read more31.11-01-2023The NSS UNIT in collaboration with NCC UNIT, Civil Defence Corps and Leo Satva of BMSCE is organizing a Blood Donation Camp in association with Jayadeva Hospital, Kidwai Memorial Institute of Oncology and BMST Rotary on 12/01/2023. Read more32.01-12-2022Annual Alumni day -2022 and Alumni Sports Day- 2022 Read more33.01-12-2022International Conference on Data, Decision and Systems (ICDDS) 2022 - 2nd and 3rd of December, 2022. Read more34.12-11-2022Inauguration of First Year Induction Program on 13.11.2022 @ 11 AM Read more35.08-11-2022Department of Computer Science and Engineering and BMSCE IEEE SB in association with is conducting a value added course on "Problem Solving and Working with HackerRank Platform" from 11th to 15th November 2022 Read more36.12-10-2022IEEE Power and Energy Society Bangalore Chapter in collaboration with BMSCE IEEE PES and Sensors Council presents Young Researchers' Meet 2022* on 4th and 5th November 2022 Read more37.22-08-2022IEEE IC SCT in collaboration with BMSCE IEEE SB presents, ICHACK'22 - A Student Run Hackathon! This is your opportunity to show-off your technical skills at National Level - 3rd &amp; 4th September 2022 Read more38.22-08-2022IEEE India Council in collaboration with BMSCE IEEE SB and BMSCE IEEE CS presents to you "SCYTALE - Lost In The Abyss Of Time", an 18-hour online cryptic hunt on 27 August, 2022 @ 9 PM Read more39.09-08-2022To upload selfie with flag on website www.harghartiranga.com and use official hashtag#harghartiranga for social media promotions Read more40.24-07-2022Technical fest BMSCE- SRISHTI July 25-27, 2022 Read more41.15-07-2022National Level Seminar on “Digital Transformations under NEP 2020” on 15-07-2022 Read more42.22-07-2022BMSCE Alumni Network is pleased to invite the batch of 2021, 2020 and 2019 students for their Graduation Day. on 22nd and 23rd July 2022 Read more43.08-07-2022“Sensing and Related Technologies for the Grand Challenges of the 21st Century: Climate, Energy, Water, Food, Health and Mega-Cities” is scheduled from 11th July to 22nd July 2022, Read more44.02-07-2022One day National conference on "Additive Manufacturing in Aerospace, Defence (AMAD-2022) &amp; Other Engineering Sectors (In Online Mode)" Co-hosted by the Department of Mechanical Engineering,BMSCE on 2nd July(Saturday) at 9.15 A.M. Read more45.16-06-2022Department of Electronics &amp; Communication Engineering in Association with IETE is organizing Fifth National Conference on Networking, Embedded and Wireless Systems-NEWS-2022 which will be held during October 12th -14th, 2022. Read more46.16-06-2022 BMSCE IEEE Computer Society in collaboration with the IEEE Computer Society Bangalore - an intercollegiate hackathon - GirlGeeksHack 2022 on the 18th and 19th of June, 2022. Read more47.04-06-2022Department of EEE is organizing a Two weeks online Value Added Course on VLSI, Verilog and Image Processing - 6th June 2022 to 18th June 2022 Read more48.09-05-2022The Department of Computer Applications, BMSCE is organizing a Two-week Online Value Added Course on "Python for Data Science" from 16th to 27th May, 2022 Read more49.02-05-2022Department of ISE, Student's Club, BMSCE in association with IEEE student's Chapter and BMSCEAN is organizing a 30 hrs hand-on value added course on "Kubernetes for Beginners" from 4th May, 2022 in blended Mode Read more50.16-04-2022Two Week Value Added Course on "Python Programming" from 18th to 29th April, 2022 Read more51.26-03-2022Department of EEE (EEE Association) and BMSCE IEEE PES and Sensors Council present ENERGY SWARAJ YATRA Talk by Prof. Chetan Singh Solanki on 28th March 2022 from 2:00 PM Read more52.24-03-2022Interactive contents development enabling the better presentation of fluid mechanics and hydraulic engineering concept in engineering education Read more53.21-03-2022Two weeks Value Added Program on Introduction to Python and LaTeX Programming 28th March, 2022 to 8th April, 2022 Read more54.19-03-2022Two week Value Added course on Modelling, Simulation, Robotics &amp; Automation - March 21st to 1st April 2022 Read more55.12-03-2022Department of Information Science and Engineering is organizing VGST Sponsored Five Day Faculty Development Program on “Machine Learning and Deep Learning with Python” from 14th to 18th March 2022. Read more56.18-02-2022GIAN course "Modeling and Simulation of Turbulence" in collaboration with the Department of Mechanical Engineering during March 25-29th,2022 Read more57.20-01-2022Department of Civil Engineering is organizing an AICTE Training and Learning (ATAL) Academy sponsored Online Faculty Development Program (FDP) on "Carbon Balance and Environmental Sustainability",CBES-2022 during 7th-11th February 2022. Read more58.29-11-2021UG/PG Online Admission Registration for the AY 2021-22 (CET/COMED-K/MGT/GOI/PMSS/PIO/ DCET/PGCET) Read more59.25-11-2021BMSCE PHASE SHIFT 2021 - November 26-27,2021 Read more60.13-11-2021Two-Days WORKSHOP ON IMPLEMENTATION OF NEP 2020 15.11.2021 and 16.11.2021 Read more61.06-11-2021International Conference on Power, Control and Sustainable Energy Systems 28th – 30th JULY 2022. Read more62.24-09-2021Virtual Education Series - Industry 4.0 Real Life Implementation Case Studies 25th September 2021 Saturday - 11:30 am to 01.30 pm Read more63.20-09-2021One week online FDP program on " Recent Advances in CFD &amp; Its Applications" from 27th to 01st October 2021 Read more64.09-09-2021Analog Signal Processing Concepts using Python - 15th to 30th September 2021. Read more65.02-09-20212 Week online Internship on Simulation Tools for Engineering Applications - 6th - 18th September 2021 Read more66.02-09-2021Virtual Series of Lectures on 'Digital Transformation' in Industries for students. Read more67.24-08-2021AICTE Invites all students and faculty to observe 30th August to 4th September as YuWaah Echoes – by Young Warrior filled with knowledge sessions, talks, presentations, competitions and challenges. Read more68.23-08-2021Two week online Internship on MULTISIM between 23-08-2021 and 04-09-2021. Read more69.21-08-2021Python Bootcamp. A 36 Hour Learn-A-Thon starts at 11:00 am on the 28th of August 2021. Read more70.28-06-2021Hands-on Workshop on " Up &amp; Running in AWS" Saturdays ( 03/07/2021, 10/07/2021, 17/07/2021 and 24/07/2021) from 2:00 PM to 4:30 PM.) Read more71.27-05-2021Online 24-hour Hackathon - "Ode to Code" on 5th June 2021 (Saturday) organized by CSE, BMSCE in association with Riskcovry Read more72.19-02-2021International Conference on Operations Management, Systems &amp; Business Analytics (COMSB) on 26th March 2021 Read more73.10-02-2021Talk by Padma Sri Dr. Sudha Murty, Chairperson of Infosys Foundation a Prolific Writer and Social Worker to address the 75th batch of Engineering students on 12.02.2021 at 11.00 AM. Read more74.09-02-2021One week online STTP on " REO-AMST-2021”, “Renewable Energy options in developing countries with Advanced Materials and Scientific Tools " from 8th to 13th March , 2021. Read more75.05-02-2021One Week Faculty Development Program (FDP) on Functional Materials for Engineering Applications -15-02-2021 to 19-02-2021 Read more76.22-01-2021VETOMAC - XVI 16th International Conference on Vibration Engineering and Technology of Machinery on 16–18 December 2021. Read more77.21-01-2021Level One C Programming Bootcamp, is being conducted by the department of CSE and ECE, for the first-year UG students on the 23rd and 24th of January 2021.” Read more78.13-01-2021JustVend: Smart App based vending machine developed by BMS students. Read more79.07-01-2021Department of Mathematics and Humanities is organizing a Two-Days Webinar on Skill-set and Stress Management on 11th &amp; 12th, January 2021 from 5.00 to 6.30 PM Read more80.02-01-2021Blockchain &amp; Decentralized Application Development (Hands-on)" from 27th January to 2nd February 2021 Read more81.29-12-2020Inauguration of Techbarath Hackthon 2021 0n 30-12-2020 @ 3 PM Read more82.02-12-2020UG/PG Online Admission Registration for the AY 2020-21 (CET/COMED-K/MGT/GOI/PMSS/PIO/DCET/PGCET) Read more83.21-11-2020Two day online Workshop for faculties on Virtual Lab - 23.11.2020 and 24.11.2020 Read more84.01-10-2020Implementation Plan on NEP 2020 on MyGov portal seeking suggestions/feedbacks-Date Extended 31.10.2020 Read more85.09-09-2020FDP on AICTE- ATAL on Waste Technologies - Wealth From Waste from 23 to 27th November 2020 Read more86.01-09-2020One week Online Value-added Course on "Emerging Technologies: Industry Perspectives" from 4th to 10th September 2020 Read more87.02-09-2020Webinar on Cross Platform Mobile App Development Webinar - 08/09/2020 @ 11.30 am Read more88.29-08-2020AICTE Training And Learning (ATAL) Academy Online Faculty Development Programme (FDP) On “Prospects and Challenges in 3D Printing: A Design Perspective” -01/09/2020 to 05/09/2020 Read more89.22-08-2020IEEE-SSIT-ES Joint Chapter Bangalore Section is Organizing an Online Lecture on “Sociological, Psychological Issues and Possible Remedies During COVID-19” on 29/08/2020 at 11AM Read more90.06-08-2020Value-added Course on "Challenges and Opportunities in the Semiconductor Industry" from 10th to 14th August 2020 Read more91.05-08-2020Guest Lecture on National Education Policy 2020 - from the perspective of Higher Education - 05/08/2020 @ 2.30 pm Read more92.01-10-2020Admissions for MBA Programme for the Academic Year 2020-21 - Reg Read more93.29-07-2020One week Faculty Development Programme on Python Programming - 24th to 29th August, 2020 Read more94.25-07-2020IEEE Online Hands-on Workshop on “Simulation tools for Power converters and applications”. - 27th to 31st July 2020 Read more95.16-07-2020FDP on "IoT and Data Analytics: an End to End perspective" from 27th July to 1st Aug 2020 Read more96.13-07-2020One week online FDP on "MATLAB for Mechanical Engineers" from 20th to 24th of July 2020 Read more97.01-09-2020Admissions to B.E. Degree Program in Artificial Intelligence and Machine Learning Read more98.02-07-2020Protocol Club is organizing Protocol Day 2020 from 4th July 2020 to 5th July 2020. Read more99.01-07-2020WEBINAR on "Civil Services As a Career Option", Wednesday , 1st July 2020 at 5:30 PM - 7:00 PM Read more100.02-07-2020Two-Week Online FDP on "Applied Data Science" from 6th to 17th July 2020 Read more101.30-06-2020"Recent Advances in Heat Transfer and Its Applications" - 13th to 17th July 2020. Read more102.29-06-2020ONE WEEK Online FDP On "Climate change and Carbon Issues" from " 6th July to 10th July 2020" Read more103.25-06-2020One Week Online FDP on "GREEN ENERGY" from JUNE 29th to JULY 4th, 2020. Read more104.20-06-2020Enhancement of curriculum through CDIO on 24th and 25th June 2020 Read more105.12-06-2020One - Week Online FDP on Structural Health Monitoring and its Implications -- 15th -19th June 2020 Read more106.10-06-2020BMSCE Hackathon: Beat the Pandemic (June 5 to 7, 2020) Read more107.26-05-2020BMSCE Hackathon:Building effective solution to win battle against COVID19 - 5th to 7th June,2020. Read more108.26-05-2020Webinar on “Three Amigos: Mouse clicks, Humans and Threats” on 28 May 2020 from 4.30 to 6.00 PM Read more109.07-05-2020Duration of MCA Program as per AICTE Approval Hand Book 2020-21 Read more110.12-05-2020Young Professional Program to infuse fresh and young talent in its incubator at IIT Kanpur Read more111.11-05-2020PUBLIC NOTICE on REDRESSAL OF GRIEVANCES RELATED TO COVID-19 Read more112.08-05-2020Urgent Circular- Live QnA session of VCs and Principals/Directors of TEQIP Institutions with Guruji Sri Sri Ravishankar Tommorow- May 9th,2020 11:30 AM-reg Read more113.06-05-2020edX Remote Access Program at BMSCE Read more114.24-04-2020Coursera at B.M.S. College of Engineering - Free registration and Certification Read more115.06-03-2020International Women's Week 2020 - Activities from 6th March to 10th March 2020. Read more116.17-02-2020National Science Day events from 17th Feb. 2020 to 28th Feb. 2020 Read more117.12-02-2020B.M.S College of Engineering in association with Mitsubishi Electric India is organizing a mega event, the 5th Edition of Mitsubishi Electric Cup 2020, a National Level Competition for Factory Automation on 14th and 15th February 2020 (Friday and Saturday). Read more118.25-01-2020Schedule of Induction Program for First B.E.Students 2019-2020, Phase-II - 27/01/2020 to 01/02/2020. Read more119.09-01-2020"Machine Learning and Deep Learning with Python" - 20/01/2020 to 24/01/2020 Read more120.01-01-2020Recent trends in Deep learning and its applications - 21/01/2020 to 25/01/2020 Read more121.21-12-2019IEEE International Conference on Mainstream Block Chain Implementation (ICOMBI) Read more122.14-10-2019BMSCE - Dassault Systems La Fondation Academic Partnership Read more123.23-08-2019Two day’s National Symposium Read more124.04-08-2019Inaugural function of commencement of First Year B.E. &amp; B.Arch - 2019-20 Read more125.22-07-2019One week FDP on 'Contact and Non-Contact Measurements' Read more</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44" t="str">
+        <v>2026-03-19T18:35:17.922Z</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20Application%20BMSCE%2005092025.pdf</v>
+      </c>
+      <c r="B45" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C45" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8. Nationality 9.Religon 10. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 11. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 12. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 13. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 14. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 15. Patents (please attach a separate sheet) Filed Published Granted 16. Consultancy (please attach a separate sheet) Awarded On-going 17. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 18. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 19. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 20. Special Award / Achievements or any other information : (please attach a separate sheet) 21. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 22. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 23. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 24. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 25. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 26. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 27. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45" t="str">
+        <v>2026-03-19T18:35:18.566Z</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20Application%20BMSCE_05092025.pdf</v>
+      </c>
+      <c r="B46" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C46" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8. Nationality 9.Religon 10. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 11. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 12. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 13. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 14. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 15. Patents (please attach a separate sheet) Filed Published Granted 16. Consultancy (please attach a separate sheet) Awarded On-going 17. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 18. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 19. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 20. Special Award / Achievements or any other information : (please attach a separate sheet) 21. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 22. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 23. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 24. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 25. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 26. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 27. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46" t="str">
+        <v>2026-03-19T18:35:19.200Z</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Newspaper%20Advertisement%20December%202025.pdf</v>
+      </c>
+      <c r="B47" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C47" t="str">
+        <v>B.M.S. EDUCATIONAL TRUST, BENGALURU B.M.S, COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU Notification No: BMS 08 EST (U) 2025 BENGALURU - 560 019 MCA Program Applications are invited from candidates with high academic achievements, research craving mind with constructive attitude for the post of Assistant Professor under Management Cadre: o Artificial Intelligence &amp;Machine Learning Lat B.M.Sreenivasaiah Founder, BMSET " Mechanical Enginering "Electronics &amp; Communication Enginering " Computer Science&amp;Qualification &amp; Experience: Engineering (CSE) As per AICTE Norms (Preference willbe given to the candidates with Ph.D. degree from premier institutions with quality publications) Salary: As per AICTE 7th Pay Scale Late BSNarayan Donor Truste, BMISET Date: 24.12.2025 Requirement for the position Qualification &amp;Experience: Candidates with Ph.D. degree from premier institutions with quality publications Salary: As per AICTE 7th Pay Scale For further details, please visit www.bmsce.ac.in Duly filled in applications along with required enclosures should reach the Principal on or before 10h January 2026. sd/- Principal, BMSCE</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47" t="str">
+        <v>2026-03-19T18:35:19.777Z</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20Application%20BMSCE%2005092025%20(1).pdf</v>
+      </c>
+      <c r="B48" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C48" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8. Nationality 9.Religon 10. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 11. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 12. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 13. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 14. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 15. Patents (please attach a separate sheet) Filed Published Granted 16. Consultancy (please attach a separate sheet) Awarded On-going 17. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 18. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 19. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 20. Special Award / Achievements or any other information : (please attach a separate sheet) 21. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 22. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 23. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 24. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 25. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 26. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 27. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48" t="str">
+        <v>2026-03-19T18:35:20.396Z</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>https://bmsce.ac.in/home/B-S-Narayan-PhD-Fellowship</v>
+      </c>
+      <c r="B49" t="str">
+        <v>html</v>
+      </c>
+      <c r="C49" t="str">
+        <v>B S Narayan Ph.D Fellowship B.S Narayan Doctoral Fellowship 2025-2026 No Details Action 1. Terms and Conditions for BSN Fellowship &amp; Application form for BSN Fellowship Download 2. BSN Ph.D Fellowship Brochure Download</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49" t="str">
+        <v>2026-03-19T18:35:21.021Z</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20Application%20BMSCE%200509202.pdf</v>
+      </c>
+      <c r="B50" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C50" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8. Nationality 9.Religon 10. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 11. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 12. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 13. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 14. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 15. Patents (please attach a separate sheet) Filed Published Granted 16. Consultancy (please attach a separate sheet) Awarded On-going 17. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 18. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 19. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 20. Special Award / Achievements or any other information : (please attach a separate sheet) 21. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 22. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 23. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 24. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 25. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 26. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 27. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50" t="str">
+        <v>2026-03-19T18:35:21.653Z</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>https://bmsce.ac.in/website_notifications/General%20Conditio%20MATH.pdf</v>
+      </c>
+      <c r="B51" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C51" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING &amp; Staff) The application can be downloaded from the website. The duly filled in applications along with required enclosures should reach the Principal on or before 15.10.2025 . ASSISTANT PROFESSOR 1. Mathematics &amp; Humanities M.A. in English with Minimum first class. Preference will be given to the candidates with Ph.D. qualification. NOTE: Preference shall be given to candidates with Ph.D. Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms • The details of the publications / patents/ funded projects need to be mentioned in the application. • Experience: As per AICTE norms. • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules as per the norms of the College. • Management reserves the rights of processing (accept/reject) the application. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration.</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51" t="str">
+        <v>2026-03-19T18:35:22.250Z</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>https://bmsce.ac.in/home/Notifications</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Notifications # Details Files 1.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25/03/2026. Teaching Application General Condition 2.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), 2. Department of Machine Learning (AI &amp; ML), 3. MCA 4. Department of Mechanical Engineering 5. Department of Electronics &amp; Communication Engineering Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10th January 2026. Please refer to the advertisement for more details. Teaching Application General Condition3.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/12/2025. Teaching Application General Condition4.B.S. Narayan Doctoral Fellowship 2025-26. Last date for receipt of filled-in application form is 31st December 2025 Link5.Admissions are Open for Management Quota seats for First Year PG Courses (M.Tech, MBA &amp; MCA) for 2025-26 at B. M. S. College of Engineering. Kindly contact the undersigned on or before 13th November 2025. Sd/- Principal 6.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10/11/2025. Teaching Application General Condition7.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Mathematics. Note: PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/10/2025 Teaching Application General Condition8.Application for Change Of Branch(COB) Circular for the Academic Year 2025-26 Download 9.Circular for payment of Tuition and Miscellaneous Fee for 2nd Semester (MTech, MCA and MBA) for AY-2025-26 Download 10.Circular for Fee Structure for 2nd Year B.E admitted through CET, COMEDK and Management Quota for AY-2025-26 Download 11.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25/09/2025. Teaching Application General Condition12.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. 2. Department of Physics Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 08.09.2025 Teaching Application General Condition13.Notification for Faculty Recruitment under Management Cadre for the post of ADJUNCT FACULTY AND PROFESSOR OF PRACTICE in ALL DEPARTMENTS. Note: Preference shall be given to candidates with Degree from premier institutions in addition to the qualification and experience as per AICTE norms. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25.08.2025 Teaching Application General Condition14.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. 2. Department of Mathematics Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25.08.2025 Teaching Application General Condition15.Fee Structure for 3rd Year and 4th Year B.E students for the Academic Year 2025-26. Download 16.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 09.08.2025 Teaching Application General Condition17.1. Fees in respect of 1st year BE CET/COMEDK/MGMT/GOI Quota admission for the year 2025-26 2. Fees in respect of 2nd year BE (Diploma) DCET Quota admission for the year 2025-26 1st year BE CET/COMEDK/MGMT/GOI 2nd year BE (Diploma)18.Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 22.07.2025 Teaching Application General Condition19.PM-Vidyalaxmi Scheme The Government of India has approved PM-Vidyalaxmi scheme to provide financial support to meritorious students so that financial constraints do not prevent any youth of India from pursuing quality higher education. A special loan product has been introduced to enable for collateral free, guarantor free education loans to meritorious students who get admission in the top 860 quality higher educational institutions of the nation; made accessible through a simple, transparent, student-friendly and entirely digital application process. Furthermore, for students with up to Rs. 8 lakhs annual family income, the scheme will also provide for 3% interest subvention on loans up to Rs 10 lakh. The list of 860 quality higher education institutions is at: https://dashboard.aishe.gov.in Please visit the PM-Vidyalaxm portal for the detailed guidelines of the Scheme Students can apply online for education loan and interest subvention under PM-Vidyalaxmi and CSIS Scheme at https://pmvidyalaxmi.co.in Link20.1. Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. 2. Placement Officer in Department of Training &amp; Placement with TWO years MBA preferably specialization in HR. At least 10 years prior experience in placement related activities in leading Institutes/Organizations. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS for Teaching positions. The duly filled-in applications along with the required enclosures should reach the Principal on or before 05.07.2025 Teaching Application Non Teaching Notification Advertisement General Condition 21.Applications are invited for the post of Project Associate under the Dassault Systemes Foundation Grant for the project "3-D Modelling based Simulation of Rain induced Urban Flooding and creation of methodology for mitigation Measures". Principal investigator of the project is Dr. Reshmi Devi T.V, Associate Professor, Dept. Civil Engineering, B.M.S. College of Engineering, Bengaluru. The project team includes Prof. Alok Pandey and Dr. Geetha Kuntoji (Dept. Civil Engineering, BMSCE) and Dr. Dr. ShivashankarR. Srivatsa (Dept. Mechanicl Engineering, BMSCE). Eligible candidates fulfilling the criteria, may apply through the following Google form - https://forms.gle/a532di5bHYq8J5Mu9 Notification22.Applications are invited from eligible candidates for the post of a Senior Research Fellow (SRF) on contract basis for the Prasanna Technologies Pvt. Ltd. (PTPL) funded project entitled: “Predicting residual life of structures using artificial intelligence enabled thermography”, under Dr. Anil Chandra A. R., and Dr. Sangamesh C. Godi, , Department of Mechanical Engineering, B.M.S. College of Engineering, Bengaluru. Eligible candidates fulfilling the criteria, may apply with their resume and relevant documents by sending the same through e-mail to the address anilchandraar.mech@bmsce.ac.in or by posting to the address mentioned below. Last date for submitting the documents is 12 th April 2025, 5PM IST. For further details please refer the notification. Download 23.DATE EXTENDED till 30/04/2025 Applications are invited for JRP position(1 post ) under DRDO grant sanctioned by DRDO titled "Investigations on Ge-Sn Alloys Suitable for photodetector in SWIR range". Desiring candidates are requested to submit their CV to PI via email: chandasreedas.eee@bmsce.ac.in with the subject line "Application for DRDO Grant JRF Advertisement No: BMSCE/EEE/DRDO/JRF/1/2025" on or before 30/04/2025 Notification24.Notification for Faculty and Staff Recruitment under Management Cadre for the Post of 1. Assistant Professor in Department of Management Studies and Research Centre 2. System Analyst Note: 1. For Faculty:7th PAY SCALE AS PER MANAGEMENT NORMS. 2. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10.04.2025. Notification Teaching Application Non-Teaching Application25.APPLICATIONS ARE INVITED FOR B.S. NARAYAN DOCTORAL FELLOWSHIP PH.D. ADMISSION (FULL TIME) FOR THE ACADEMIC YEAR 2025-26. The last date to submit the application is extended to 20th March 2025. Ph.D. Notification Application 26.Admission to Ph.D. Programme (Full-Time/Part-Time) under Visvesvaraya Ph.D. Scheme - Last date for the submission of online Application form 15/02/2025 Download 27.In view of Government Order No. ಸಿಆಸುಇ 40 ಹೆಚ್ ಹೆಚ್ ಎಲ್ 2024, dated 26.12.2024, 27th December 2024 (Friday) is declared as holiday to mourn the sad demise of Sri. Manmohan Singh, Former Prime Minister of India. Download 28.Notification for Faculty Recruitment under Management Cadre for the Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Block Chain Technology), Computer Science &amp; Business Systems, Statistics, MCA (Ph.D. Preferable). Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled in applications along with the required enclosures should reach the Principal on or before 31.12.2024. General Conditions Application Form (Teaching) 29.In view of Government Order No.DPAR/35/HHL/2024 dated 10.12.2024, 11th December 2024 (Wednesday) is declared as holiday to mourn the sad demise of Sri. S.M. Krishna, Former Chief Minister of Karnataka. Download 30.In accordance with the communication received from Basavanagudi Traffic Police Station and the direction from the higher authorities, the college remains closed on 25th November 2024(Monday) owing to the issues regarding mobility of people and vehicles in view of Kadalekai Parishe.31.NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE (Department of MBA-Placement Officer) Last Date: 14-12-2024. Application Form (Non-Teaching Application form) Notification32.First year Miscellaneous Fees of M.Tech, MBA and MCA for the academic year 2024-25. Download 33.Due to Annual Kadalekai Parishe, the entry and exit of all the staff and students’ vehicles on 22nd, 25th, and 26th November 2024 will be through the Hostel Gate only. Download 34.Notification for Faculty Recruitment under Management Cadre for the Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Block Chain Technology), Computer Science &amp; Business Systems, Statistics, MCA (Ph.D. Preferable). Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled in applications along with the required enclosures should reach the Principal on or before 30.11.2024. General Conditions Application Form (Teaching) 35.NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE (Diploma in Mechanical/Civil/Aero/Tool &amp; Die making) Last Date: 28-11-2024. Application Form (Non-Teaching Application form) Notification36.Change of Branch Students List 2024-25 Download 37.Change of branch 2024 -25 (Date of Counselling: 19th October 2024 @ 9:30 AM Download 38.Change of Branch (CoB) for the Academic year 2024-2025. The last date to apply in the VTU portal is 22-09-2024 Download 39.Fees in respect of 1 year BE CET Quota admission for the year 2024-25 Download 40.Admission to Ph.D. Programme (Full-Time/Part-Time) under Visvesvaraya Ph.D. Scheme - Last date to apply is 15-08-2024 Download 41.Fees in respect of 1 year BE GOI Quota and Management Quota admission for the year 2024-25 Download 42.Check list of the Original Documents to be submitted by the Candidates selected through Various Quota at the time of verification of documents in the college. Download 43.Notification for Faculty Recruitment under Management Cadre for the Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Block Chain Technology), Computer Science &amp; Business Systems, Statistics, Mathematics, Chemistry and Physics. Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Assistant/Associate Professor Position for Computer Science Cluster Departments. The duly filled in applications along with the required enclosures should reach the Principal on or before 03.08.2024. General Conditions Application Form (Teaching) 44.Fee in respect of II year BE CET DIPLOMA Lateral entry quota admission for the year 2024-25 Download 45.Fee in respect of 1st year COMEDK quota admission for the year 2024-25. Download 46.TECHNOLOGY DEMONSTRATION OF INTERSHAFT SQUEEZE FILM DAMPER (ISSFD) FOR TWO SPOOL GAS TURBINE APPLICATION. A write up on the Project details and requirement for the JRF recruitment(PDF) JRF Application Format (Word File 47.Notification for Faculty Recruitment under Management Cadre for For the Departments of Computer Science &amp; Engineering (CSE), Machine Learning (Artificial Intelligence &amp; Machine Learning), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Block Chain Technology), Computer Science &amp; Business Systems, MBA, Statistics Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled in applications along with required enclosures should reach the Principal on or before 29.06.2024. General Conditions Application Form (Teaching) Application Form (Placement officer) Notification 48.The students belonging to the SC category admitted to UG/PG 2023–24 are hereby informed to submit their scholarship applications online at the State Scholarship Portal (SSP), https://ssp.postmatric.karnataka.gov.in immediately and without fail. Note: Last date for SC category students is April 30, 202449.NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE(e-Governance). Last Date: 19-02-2024. Click here to Apply Online50.Notification for Faculty Recruitment under Management Cadre for Computer Science &amp; Engineering, Information Science &amp; Engineering, Machine Learning( AI &amp; ML), CSE (Data Science), CSE (IOT and Cyber Security &amp; blockchain technology), Artificial Intelligence (AI), and Data Science, Computer Science &amp; Business Systems. The last date to apply online is June 10th, 2024. Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Click here to Apply Online 51.VTU Notification (Submission of online Exam application forms for UG Silver Jubilee Special Examination to be held during December 2023/January 2024) dated 17.01.2024 Download 52.First Year Miscellaneous Fees for M.Tech, MBA and MCA for the academic year 2023-24 Download 53.Applications are invited from eligible and interested candidates for the post of Junior Research Fellow (JRF) or Project Associate on a consolidated basis to work on the Scheme for Transformational and Advanced Research in Sciences (STARS) funded project by IISC, Bangalore. Download 54.Notification for Faculty Recruitment under Management Cadre for Computer Science &amp; Engineering, Information Science &amp; Engineering, Machine Learning( AI &amp; ML), CSE (Data Science), CSE (IOT and Cyber Security &amp; blockchain technology), Artificial Intelligence (AI), and Data Science, Computer Science &amp; Business Systems. Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Click here to Apply Online 55.Applications are invited from eligible and interested candidates for the post of Junior Research Fellow (JRF) on a consolidated basis to work on the Scheme for Transformational and Advanced Research in Sciences (STARS) funded project by IISC, Bangalore. Download 56.Notification for Faculty Recruitment under Management Cadre for Computer Science Engineering, Information Science Engg, &amp; Machine Learning( AI &amp; ML), CSE (Data Science),CSE (IOT and Cyber Security &amp; blockchain technology), Artificial Intelligence (AI), and Data Science and Placement Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Notification Click here to Apply Online Application Form (Teaching) Download 57.Fees in respect of II year BE CET Diploma Lateral entry quota admission for the year 2023-24 Download 58.Change of Branch (CoB) for the Academic year 2023 - 2024. The last date to apply in the VTU portal is 22-11-2022 Download 59.Call for Research Assistant / Field Investigator ICSSR Funded Short-Term Empirical Research Project Download 60.Applications are invited for the position of Junior Research Fellow (JRF) Senior Research Fellow (SRF) and Research Assistant (RA), in a research and development project (under CHIPS TO START-UP PROGRAMME (C2S) CATEGORY – I PROPOSALS) for the duration of 2 years (2023-2025) Download 61.Call for recruitment of Field Officer and Resaerch Assistant as per ICSSR for Short-term Empirical Research Project Download 62.Call for Application : Research Study (National Commission for Women) on : “Women in Decision Making Roles in Corporate” Download 63.Dear Students, The First year classes will commence from October 11, 2023. Principal, BMSCE.64.Fees in respect of 1 year, II year lateral entry BE CET, Comed-K, and Management Quota admission for the year 2023-24 Download 65.Fees in respect of 1st year BE CET, Comed-K, and Management Quota admission for the year 2023-24 Download 66.Advertisement for the post of Faculty Positions for various departments in B.M.S.C.E. The duly filled application along with required enclosures should reach the Principal on or before 02-08-2023. Advertisement General Conditions Teaching Application67.Students of non-NEP branch (6th &amp; 8th Semesters) are informed that supplementary semester (fast track) is commencing tentatively from 25th July 2023. The students can enroll the failed courses at the respective departments . The last date for enrollment is 22nd July 2023.68.CHECK LIST FOR FIRST YEAR BE ADMISSION FOR STUDENTS REPORTING TROUGH VARIOUS QUOTA FOR THE ACADEMIC YEAR 2023-24 in BMSCE. Download 69.Special examinations for UG and PG Students who have completed their course and have only backlogs - VTU circular attached for your reference. you may contact the COE office {OR} Dean Academics Office. Download 70.Pubic Holiday Declared on Wednesday, 10th May 2023 due to Karnataka Legislative Assembly Elections. Download 71.Notification for Faculty Recruitment under Management Cadre for Computer Science Engineering, Information Science Engg, &amp; Machine Learning( AI &amp; ML), CSE (Data Science),CSE (IOT and Cyber Security &amp; blockchain technology), Artificial Intelligence (AI), and Data Science. Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Click here to Apply Online 72.First year Miscellaneous Fees of M.Tech, MBA, and MCA for the academic year 2022-23. Download 73.Fees in respect of II year BE CET Diploma Fresh admission Students for the Year 2022-23. Download 74.Notification for Faculty Recruitment under Management Cadre for Computer Science Engineering, Information Science Engg, Machine Learning( AI &amp; ML), Aerospace Engineering &amp; Department of Mathematics. The last date is 27-01-2023. Application Form (Teaching) Notification 75.NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE. Last Date: 16-01-2023. Application Form (Non-Teaching Application form) Notification76.Scholarship Circulars - Submissions of online Applications for the AY 2022-23. Scholarship Circular-1 Scholarship Circular-2 Scholarship Circular-3 Scholarship Circular-477.NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE(R &amp; D, Electronics * Instrumentation Engg, Aerospace Engg. Last Date: 16-01-2023. Application Form (Non-Teaching Application form) Notification78.The Dean (Academic) of BMSCE, Dr. Seshachalam D, will be addressing the first year students of the batch of 2022-2023 regarding the online Course Registration and choice of courses for 1st semester, tomorrow (Friday 09.12.2022 ) at 11.00 AM. The address will be online. Please find the link for the online session attached herewith: https://ieeemeetings.webex.com/ieeemeetings/j.php?MTID=m3d98a0aec81dc4e96559500f3bcac9e2 The Mock Online registration will be conducted tomorrow (Friday 09.12.2022) at 2.00 PM. Link to the portal: https://firstyear.bmsce.ttcindia.co/ If a first year student has not yet registered on the student portal, please register using the aforementioned link. The actual online Course Registration will be conducted on 10.12.2022 (Saturday) at 9.30 AM, instead of 12.12.2022 (Monday). User Manual Download Link79.Change of Branch (CoB) for the Academic year 2022 - 2023. The last date to apply in the VTU portal is 30-11-2022. Change of Branch Notification Download 80.Advertisement for Research Assistant for the project “Development of a Polymer Nanocomposite based Rapid Malaria Sensing Device” sponsored by the SCIENCE &amp; ENGINEERING RESEARCH BOARD (SERB) - Last Date is 7th Nov.2022 Download 81.Notification for Faculty Recruitment under Management Cadre for Computer Science Engineering, Information Science Engg &amp; Department of Mathematics. Application Form (Teaching) Notification 82.Fees in respect of 1 Year B.E. CET, Comed-K and Management Quota admission for the year 2022-23 - Circular Download 83.Housekeeping Tender Notification - Last Date 31st October 2022 Tender Notification Covering Letter Quotation HK Services84.Notification for Faculty Recruitment under Management Cadre for Computer Science Engineering, Information Science Engg &amp; Department of Mathematics. Notification Application Form (Teaching) Download 85.Advertisement for the post of Teaching and Non-Teaching Positions for various departments in B.M.S.C.E. The dully filled application along with required enclosures should reach the Principal on or before 11-05-2022. Notification General Conditions (Teaching &amp; Non-Teaching) Application Form (Teaching) Application Form (Non-Teaching) Application Form (Librarian)86.As per the latest directions from the GOK &amp; VTU, the classes are to be conducted in Offline mode. For further details, students are informed to contact their concerned HOD. Further, as per the Government Order, in view of weekend curfew, the college remains closed on 8th January 2022 (Saturday). However, online classes would be conducted on 8th Jan. 2022. The CIE &amp; SEE scheduled will be conducted in Offline mode only at the college. 87.Melton Foundation is opening fellowship applications Download 88.Inauguration of First Year B.E.(2021-2022) classes to be held on 19th December 2021 at 11 AM. Download 89.Results of Supervisors Allotment and Document Verification - The last date is 20-12-2021 Download 90.Commencement of First Year B.E. (2021-2022) Program - Monday 13th December 2021. Download 91.Change of Branch for the academic year 2021-22 as per the merit list -Counselling dated 17.11.2021 @ 10 AM. Download 92.Change of Branch (CoB) for the Academic year 2021 - 2022. Change of Branch-VTU Circular College Circular VTU Revised Circular93.AICTE Swanath Scholarship Scheme (Both Degree and Diploma Level) Download 94.Advertisement for the post of Assistant Professor for Civil Engineering Department in B.M.S.C.E. The duly filled application along with required enclosures should reach the Principal on or before 04-10-2021. - CLOSED Advertisement Teaching Application95.Advertisement for JRF (Junior Research Fellow) position under SERB POWER Grant sanctioned by DST-SERB. The last date to submit their Curriculum Vitae to the Principal Investigator email is 15-09-2021 - CLOSED Download 96.Advertisement for the post of Faculty Positions for various departments in B.M.S.C.E. The duly filled application along with required enclosures should reach the Principal on or before 06-09-2021. - CLOSED Advertisement General Conditions Teaching Application97.Applications are invited from eligible candidates for the post of Junior Research Fellow (JRF) - Last date for submitting the application is 25 July 2021, 5 PM IST. - CLOSED Download Link98.Advertisement for the post of Technical Assistant in the Department of Electrical &amp; Electronics Engineering, B.M.S.C.E. The duly filled in application with all relevant documents should reach the Principal on or before 15.05.2021 through post or through e-mail to "establishmentsection@bmsce.ac.in". - CLOSED Advertisement Application 99.II Semester B.E. classes Time Table with effect from 28th April 2021 Download 100.Constitution of Task Team for implementation of COVID-precaution-SOPs - Circular Download 101.B.E.,5th Semester, 7th Semester, MCA 3rd and 5th Semester, MBA 3rd Semester Results - January 2021 Link102.Revised III Semester B.E. Consolidated Theory Semester End Main Examination - Time Table March 2021 Examinations Download 103.submission of online applications at the State Scholarship Portal (SSP) by eligible students 2020-21. Download 104.Commencement of First semester B.E. (2020-2021) offline classes from 22.02.2021. Download 105.SEE for III Semester B.E., are scheduled from 12.03.2021. Download 106.SEE Timetable for the Odd Semester B.E., B.Arch, MBA, MCA and M.Tech &amp; Even Semester Improvement Examinations - January/February 2021 starting from 27.01.2021. Download 107.No change in the examination schedule as per the VTU Circular - Text Highlighted FYI. Download 108.SEE for VII Semester B.E., B. ARCH, III &amp; V Semester MCA, III Semester MBA and MTech Jan/Feb 2021 are rescheduled from 27.01.2021. Download 109.Attention to 5th Semester BE Students - SEE Circular Download 110.Grade Improvement Examinations for the II Semester - Circular Download 111. First Semester B.E.(2020-2021) Time Table with effect from 28.12.2020. Physics Cycle (2020) Chemistry Cycle (2020)112.II Semester Grade Improvement Examinations - Circular Download 113.SCHEDULE OF INDUCTION PROGRAM FOR FIRST YEAR B.E. STUDENTS 2020-2021 Phase -I. Circular114.Advertisement for the post of Teaching and Non-Teaching for various departments in B.M.S.C.E. The duly filled application along with required enclosures should reach the Principal on or before 20-12-2020. Advertisement General Conditions Teaching Application115.VTU Circular related to offline examinations for both UG and PG Courses -Reg Download 116.Final List of Students who have been allotted change of branch for the academic year 2020-21 Download 117.Online Examination Circular for UG/PG Students for Supplementary Semester End Exams, Re-registered, Grade Improvement Students Download 118.B.E. /M.Tech /M.C.A /M.B.A Programmes Results Announced - July/August 2020 Link119. CONDUCTION OF FINAL YEAR EXAMINATION AU</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52" t="str">
+        <v>2026-03-19T18:35:23.085Z</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>https://bmsce.ac.in/home/Notifications</v>
+      </c>
+      <c r="C53" t="str">
+        <v>GUST 2020 (ADDITIONAL INSTRUCTIONS TO STUDENTS) Download 120.Online Examination Time Table August - 2020 Download 121.Examination Circular - Reg Download 122.UPDATED CIRCULAR-CONDUCTION OF FINAL YEAR EXAMINATION AUGUST 2020 Download 123.SUPPLEMENTARY SEMESTER 2019-20 (AUG-SEPT 2020) UG &amp; PG PROGRAMMES - Calendar &amp; Guidelines (Fast Track Semester UG, MBA &amp; MCA) Download 124. Examination and Announcements Important Information- 2020 Download 125.APPLY NOW!(Students/Faculty) for SEED FUNDING UP TO 15 LACS to MSME approved Business incubator at B.M.S. COLLEGE OF ENGINEERING (Institute's HI/BI Number: HIBIKI 000342) Deadline: 20th Feb 2020. MSME-HI_BI Brochure Innovate Indiea (Teaching &amp; Non-Teaching) 126.Advertisement for the post of Teaching and Non-Teaching Positions for various departments in B.M.S.C.E. The dully filled application along with required enclosures should reach the Principal on or before 07-02-2020. Notification General Conditions (Teaching &amp; Non-Teaching) Application Form (Teaching) Application Form (Non-Teaching)127.KSCST invites project proposals from the final year BE, M Tech. MSc, and MBA students for sponsorship under the 43rd series of SPP: 2019-20 Download 128.Advertisement for Positions at BMSET Hostel Download 129.Advertisement for JRF (Junior Research Fellow) position under ASEAN-India Collaborative Project sanctioned by DST-SERB. Download 130.Admissions are open for Management Quota seats for First Year PG Courses (MCA, MBA) for 2019-20 at B.M.S. College of Engineering. Link131.CHANGE OF BRANCH FOR III SEMESTER FOR THE ACADEMIC YEAR 2019-20. Download 132.Schedule of Activities for Odd Semester B.E. Programs 2019-20 Download 133.First Semester B. E classes (2019-2020) Time Table. Link134.First Year B.E Syllabus Book (2019-2020) Download 135.Results and Notifications - COE Link</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="str">
+        <v>2026-03-19T18:35:23.085Z</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>https://bmsce.ac.in/home/COE-Notifications</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Notifications # Details Files 1.Time Table for IV Semester Makeup Examination MBA- Mar-2026. Download 2.Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. III Semester End Examinations conducted during Jan/Feb-26. Download 3.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. I, III Semesters and Reappear Semester UG Semester End Examinations conducted during Jan/Feb-26. Download 4.Notification for Answer Scripts of I &amp; III Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure as per the attached schedule. Download 5.Circular for makeup registration for I and III Semester March -2026 Download 6.Addtional Time Table for III Semester Makeup Examination - Mar-2026. Download 7.Time Table for I Semester MBA (Re-Appear) theory Semester End Examination March- 2026. Download 8.Time Table for I Semester M.Tech (Re-Appear) theory Semester End Examination March- 2026. Download 9.Time Table for III Semester Makeup Examination - Mar-2026. Download 10.Time Table for I Semester Makeup Examination - Mar-2026. Download 11.Time Table for MBA I Semester (Reappear) theory Semester End Examination March- 2026. Download 12.Time Table for M.Tech I Semester theory Semester End Examination March- 2026. Download 13.Time Table for MCA I Semester theory Semester End Examination March- 2026. Download 14.Time Table for MBA I Semester theory Semester End Examination March- 2026. Download 15.Additional/Revised Time Table for V Semester B.E. theory Semester End Examinations-Jan/Feb-2026. Download 16.Additional/Revised Time Table for IV Semester B.E. theory Semester End Examinations-Jan/Feb-2026. Download 17.Revised Time Table for I Semester B.E. theory Semester End Examinations-Jan/Feb-2026 Download 18.Additional/Revised Time Table for III Semester B.E. theory Semester End Examinations-Jan/Feb-2026. Download 19.Time Table for VII Semester B.E. makeup theory Semester End Examinations-Jan/Feb-2026 Download 20.Time Table for V Semester B.E. makeup theory Semester End Examinations-Jan/Feb-2026 Download 21.Time Table for Revised VI Semester B.E. theory Semester End Examinations-Jan/Feb-2026 Download 22.Time Table for PG M.Tech Re-Appear II Semester theory Semester End Examination JAN/FEB-2026. Download 23.Additional Time Table for MBA III Semester theory Semester End Examination JAN/FEB- 2026. Download 24.Time Table for VIII Semester B.E. theory Re-Appear Semester End Examinations- Jan/Feb -2026 Download 25.Time Table for VI Semester B.E. theory Re-Appear Semester End Examinations- Jan/Feb -2026 Download 26.Additional Time Table for III Semester B.E theory Semester End Examination Jan/Feb- 2026. Download 27.Revised Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (for 2024, 2023, 2022 &amp; 2021 batch Reappear -Reregisteration) Download 28.attached Time Table for PG II Semester Re-appear M.Tech Theory Semester End Examination Jan- 2026. Download 29.attached Time Table for PG Revised III Semester M.Tech Theory Semester End Examination Jan- 2026. Download 30.Time Table for III Semester MCA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 31.Time Table for III Semester MBA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 32.Time Table for II Semester MBA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 33.Time Table for II Semester MCA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 34.Revised Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. V, VII and Reappear Semester Dec-2025/Jan-2026 Semester End Examination. Download 35.NOTIFICATION:Answer Scripts of V &amp; VII Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure on 28-01-2026 &amp; 29-01-2026. Download 36.Time Table for PG III Semester M.Tech Theory Semester End Examination Jan- 2026. Download 37.Additional /Revised Time Table for IV Semester B.E. theory Semester End Examinations-Jan-2026. Download 38.Additional /Revised Time Table for III Semester B.E. theory Semester End Examinations-Jan-2026. Download 39.Time Table for IV Semester B.E. theory Semester End Examinations-Jan-2026 (All batch Reappear &amp; Re registeration).. Download 40.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. V, VII and Reappear Semester Dec-2025/Jan-2026 Semester End Examination. Download 41.Time Table for III Semester B.E. theory Semester End Examinations-Jan-2026 (All batch Regular, Reappear &amp; Re registeration) Download 42.Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (Non-NEP batch Reappear -Re registeration) Download 43.Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (for 2021 batch Reappear -Re registeration) Download 44.Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (for 2024, 2023 &amp; 2022 batch Reappear -Reregisteration) Download 45.Time Table for Semester B.E. theory Semester End Examinations-Jan-2026 (for 2025 batch only) Download 46.Time Table for MCA III Semester theory Semester End Examination JAN- 2026. Download 47.Time Table for MBA III Semester theory Semester End Examination JAN- 2026. Download 48.Notifications for submission of application for ensuring Reappear Examination PG -ODD-2026 Download 49.Additional Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 50.additional Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 51.Additional Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 52.Additional Time Table for VIII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 53.additional Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 54.additional Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 55.Additional Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 56.Revised Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.( For 2022,2021 and Non-NEP Batches) Download 57.Revised Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2022,2021 Batches) Download 58.Revised Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2023 ,2022,2021 and Non-NEP Batches) Download 59.Time Table for VIII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.( For 2023, 2022,2021 Batches) Download 60.Notifications for submission of application for ensuing Reappear Examination Dec-2025 to Jan-2026 (NEP Batches). (21 TO 23 BATCH).. Download 61.Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.( For 2022,2021 and Non-NEP Batches) Download 62.Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2022,2021 Batches) Download 63.Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2023 ,2022,2021 and Non-NEP Batches) Download 64.Notifications for submission of application for ensuing Reappear Examination Dec-2025 to Jan-2026 (NEP Batches)(24 BATCH) .. Download 65.Circular for Fees and Regulations for Photocopy and Challenge Valuation of Re-Appear for I to II semester of P.G. Oct 2025 Examination. Download 66.Circular for Fees and Regulations for Photocopy and Challenge Valuation of Supplementary/Re-Appear for I to IV semester of P.G. Sep/Oct 2025 Examination. Download 67.Circular for Fees and Regulations for Photocopy and Challenge Valuation of Supplementary III to VIII semester of U.G. Sep/Oct 2025 Examination. Download 68.Time Table for PG M.Tech II Semester(2024 batch) theory Re-Appear Examinations Oct- 2025. Download 69.Time Table for PG M.Tech I Semester(2024 batch) theory Re-Appear Examinations Oct- 2025. Download 70.Time Table for PG MBA II Semester theory Re-Appear Examinations Oct- 2025. Download 71.Time Table for PG MBA I Semester theory Re-Appear Examinations Oct- 2025. Download 72.Time Table for PG MCA II Semester theory Re-Appear Examinations Oct- 2025. Download 73.Time Table for PG MCA I Semester theory Re-Appear Examinations Oct- 2025. Download 74.Circular for Fees and Regulations for Challenge Valuation of Summer semester/Supplementary semester of U.G. Sep 2025 Examination. Download 75.Time Table for PG M.Tech I Semester theory Supplementary Examination Sep- 2025 Download 76.Notifications for Reappear Examination Application for PG Sep-2025. Download 77.Time table for Supplementary Examination -Sep- 2025 (MCA). Download 78.Time tables for Supplementary Examination -Sep- 2025 (MBA). Download 79.Revised/additional Time Table for V Semester theory Supplementary /Reappear Examination Sep- 2025 Download 80.Additional Time Table for PG I-II Semester MBA reappear Examination Sep-2025. Download 81.Additional Time Table for PG M.Tech SEE Reappear Examination Sep-2025. Download 82.Additional Time Table for V Semester B.E theory Supplementary Examination Aug/Sep- 2025. Download 83.Additional Time Table for III Semester B.E theory Supplementary Examination Aug/Sep- 2025. Download 84.Revised Time Table for I/II Semester B.E theory Summer Semester Examination Sep- 2025.(Regular 2024 batch and 2022 batch*only). *Ref : VTU notification 12-09-2025 Download 85.Submission of reappear examination application for summer semester examination (2022 batch only-who are not eligible to move to VII Semester due to vertical progression) Download 86.Time Table for PG theory Reappear Examination Sep- 2025 III and IV Semester MBA theory Reappear Examinations. Download 87.Time Table for PG theory Reappear Examination Sep- 2025 I and II Semester MBA theory Reappear Examinations. Download 88.Time Table for PG theory Reappear Examination Sep- 2025 I,II and III Semester MCA theory Reappear Examination. Download 89.Time Table for PG theory Reappear Examination Sep- 2025 I,II,III and IV Semester M.Tech theory Reappear Examination. Download 90.Time Table for I/II Semester theory Summer Semester Examination Sep- 2025 (2024 batch only). Download 91.Time Table for VI Semester theory Supplementary /Makeup Examination Aug- Sep- 2025 (All batches). Download 92.Time Table for V Semester theory Supplementary Examination Aug-Sep- 2025 (All batches). Download 93.additional Time Table for VII Semester theory Supplementary /Reappear Examination Sep- 2025 Download 94.Additional Time Table for III Semester theory Supplementary /Reappear Examination Sep- 2025 Download 95.Additional Time Table for VII Semester B.E theory Supplementary Examination Aug/Sep- 2025 Download 96.Additional Time Table for VIII Semester B.E theory Supplementary Examination Aug/Sep- 2025 Download 97.Notifications for Summer Semester Examination Sep-2025.(2024 Batch) Download 98.Additional Time Table for I Semester theory Supplementary /Reappear Examination Sep- 2025 Download 99.Time Table for VIII Semester theory Supplementary Examination Aug-Sep- 2025. Download 100.Time Table for VII Semester theory Supplementary Examination Aug-Sep- 2025. Download 101.Time Table for IV Semester theory Supplementary /Makeup Examination Aug- Sep- 2025. Download 102.Time Table for III Semester theory Supplementary Examination Aug-Sep- 2025. Download 103.Revised I/II Semester Supplementary Time Table -Aug-2025. Download 104.Notifications for extension of reappear examination PG -MBA/MCA/M.Tech . Download 105.Time Table for I/II Semester B.E theory Makeup Examination Aug- 2025( 2024 batch). Download 106.Time Table for I/II Semester B.E theory Supplementary Examination Aug- 2025 (2022 &amp; 2023 batches). Download 107.Time Table for I/II Semester B.E theory Supplementary Examination Aug- 2025 (2021 batch). Download 108.Time Table for I/II Semester B.E theory Supplementary Examination Aug- 2025 (2016/2017/2018/2018/2020 batches). Download 109.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. II Semester July/Aug-2025 Semester End Examination. Download 110.Notifications for Supplementary Examination Aug-2025.(2023 and 2024 lateral entry Re-Appear) Download 111.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. IV, VI Semester July/Aug-2025 Semester End Examination. Download 112.Time Table for PG II theory Semester End Examination JULY/AUG- 2025 (Re-Registered). Download 113.Notifications for Supplementary Examination Aug-2025.(non-NEP batch) Download 114.Notifications for Supplementary Examination Aug-2025.(2021 and 2022 lateral entry) Download 115.Time Table for PG theory (M TECH)Semester End Examination JULY/AUG- 2025. Download 116.Time Table for PG theory (MCA)Semester End Examination JULY/AUG- 2025. Download 117.Time Table for PG theory (MBA)Semester End Examination JULY/AUG- 2025. Download 118.Time Table for VIII Semester B.E theory Semester End Examination JULY- 2025( Makeup Examination). Download 119.Time Table for Additional I/II Semester B.E theory Semester End Examination JULY- 2025 (2022 BATCH ONLY). Download 120.Time Table for IV Semester M Tech theory Semester End Examination July- 2025. Download 121.Revised Time Table for I/II Semester B.E theory Semester End Examination JULY- 2025.(Regular 2024 batch, 2023,2022 batch reappear &amp; Re-registration). Download 122.Revised Time Table for IV Semester MBA theory Semester End Examination JULY- 2025. Download 123.I/II SEMESTER Time Table for 2022,2023,2024 batch (Re reg and Re Appear) Download 124.I/II SEMESTER Time Table for 2021 batch (Re reg and Re Appear) Download 125.Notifications for reappear examination for UG (2024 Batch)-2025. Download 126.I/II SEMESTER Time Table for 2016 to 2020 batch (Re reg and Re Appear) Download 127.Additional Time Table for VI Semester B.E theory Semester End Examination May/June- 2025. Download 128.Notifications for reappear examination for UG-2025. Download 129.Additional Time Table for IV &amp; VI Semester B.E theory Semester End Examination May/June- 2025. Download 130.Revised Time Table -June-2025 Download 131.Revised Time Table -June-2025. (AEROSPACE ENGINEERING) Download 132.Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. MBA, MCA, M.Tech I Semester May-2025 Semester End Examination. Download 133.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. VIII Semester JUNE-2025 Semester End Examination. Download 134.Revised Time Table -June-2025 (4TH,5TH,6TH AND 7TH SEMESTER) Download 135.Revised Time Table for VII Semester B.E. Theory Semester End Main Examination - June-2025 ( Re-Appear- 2021) Download 136.Revised Time Table for VI Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2022 batch, Re-Appear- 2021 batch &amp; NON NEP REREGISTRATION) Download 137.Revised Time Table for V Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear- 2022, 2021 batch) Download 138.Revised Time Table for IV Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2023 batch, Re-Appear- 2022, 2021 batch) Download 139.Revised Time Table for III Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear-2023, 2022, 2021 batch) Download 140.Time Table for VII Semester B.E. Theory Semester End Main Examination - June-2025 ( Re-Appear- 2021) Download 141.Time Table for VI Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2022 batch, Re-Appear- 2021 batch &amp; NON NEP RE-REGISTRATION) Download 142.Time Table for V Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear- 2022, 2021 batch) Download 143.Time Table for IV Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2023 batch, Re-Appear- 2022, 2021 batch) Download 144.Time Table for III Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear-2023, 2022, 2021 batch) Download 145.Reschedule of Time Table for VIII Semester Semester End Examination May- 2025. Download 146.Notifications for reappear examination for UG-2025. Download 147.notification regarding Graduation day fee -2025. Download 148.Revised Time Table for VIII Semester B.E. theory Semester End Examination MAY- 2025. Download 149. Notification regarding the submission of applications for Annual Convocation-2024-2025. Download 150.Time Table for VIII Semester B.E. theory Semester End Examination MAY- 2025. Download 151.RE APPEAR Time Table for I Semester MCA, MBA, M.Tech theory Semester End Examination April- 2025. Download 152.Notification Answer Scripts disclosure of III Semester MBA/MCA/M.TECH Students SEE Examination April-2025 Download 153.1st semester Makeup Examinations Time table - APR-2025 Download 154.Circular for Fees and Regulations for Reappear Examination of I Semester P.G (MBA/MCA/M.TECH) Apr -2025. Download 155.Circular for Fees and Regulations for Makeup Examination of I Semester U.G Semester End Makeup Examinations Apr -2025. Download 156.Circular for Fees and Regulations for Photocopy/Revaluation/Challenge Valuation of I Semester U.G Semester End Examinations Feb/Mar -2025. Download 157.Time Table for P.G I Semester M Tech Semester End Examination Apr-2025 Download 158.Time Table for P.G I Semester MCA Semester End Examination Apr-2025 Download 159.Time Table for P.G I Semester MBA Semester End Examination Apr-2025 Download 160.Revised Time Table for VII Semester Makeup Examination - Mar/Apr-2025 Download 161.Revised Time Table for V Semester Makeup Examination - Mar/Apr-2025 Download 162. Revised Time Table for III Semester Makeup Examination - Mar/Apr-2025 Download 163.III SEM MBA REAPPEAR TIME TABLE -MAR-2025 Download 164.Time Table for III Semester Makeup Examinations Mar-2025 Download 165.Circular for Makeup Examination -mar-2025 Download 166.Time Table for V Semester Makeup Examinations -Mar-2025 Download 167.Time Table for III Semester MBA theory Semester End Examination March- 2025.. Download 168.Time Table for III Semester MCA theory Semester End Examination March- 2025. Download 169.Fee and Regulations for RV,CV,Photocopyfor III,V,VII Semester -jan-feb-2025 Download 170.Revised and additional Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025 (2022 reappear). Download 171.Notifications for PG -MBA/MCA. Download 172.Time Table for III Semester M.Tech theory Semester End Examination JAN/FEB- 2025. Download 173.Revised and additional Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan/Feb- 2025 (2021 &amp; 2022 batch only) Download 174.Revised and additional Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025 (2021 reappear). Download 175.Revised and additional Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025 (2022 reappear). Download 176.Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025.(2021 batch re-registration/ reappear) Download 177.Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025.(2016,2017,2018,2019,2020 batch re-registration) Download 178.Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025.(Regular 2024 batch, 2023,2022 batch reappear) Download 179.Revised and additional Time Table for MBA Semester End MAKEUP Examination-OCT-2024 Download 180.Revised and additional Time Table for VI Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 batch &amp; non nep equivalent) Download 181.Revised and additional Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 &amp; 2022 batch only) Download 182.Revised and additional Time Table for III Semester B.E theory Semester End Examination Jan- 2025 (2023 batch regular, reappear 2021, 2022 batch and non NEP batch re-registration) Download 183.Revised and additional Time Table for V Semester B.E theory Semester End Examination Jan- 2025 ( 2022 batch regular, reappear 2021 &amp; non NEP rereg) Download 184.Revised and additional Time Table for VII Semester B.E theory Semester End Examination Jan- 2025 (2021 regular &amp; Non-NEP). Download 185.Circular for Fees and Regulations for Photocopy / Challenge Valuation of PG Supplementary Dec - 2024. Download 186.Revised Time Table for IV, IV and VIII Semester B.E theory Semester End Examination Jan- 2025 ( All Non-Nep batch only) Download 187.Revised Time Table for VI Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 batch &amp; non nep equivalent) Download 188.Revised Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 &amp; 2022 batch only) Download 189.Revised Time Table for III Semester B.E theory Semester End Examination Jan- 2025 (2023 batch regular, reappear 2021, 2022 batch and non nep batch re-registration) Download 190.Revised Time Table for V Semester B.E theory Semester End Examination Jan- 2025 ( 2022 batch regular, reappear 2021 &amp; non nep rereg) Download 191.Revised Time Table for VII Semester B.E theory Semester End Examination Jan- 2025 (2021 regular &amp; Non-Nep). Download 192.Time Table for IV, IV and VIII Semester B.E theory Semester End Examination Jan- 2025 ( All Non-Nep batch only) Download 193.Time Table for VI Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 batch &amp; non nep equivalent) Download 194.Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 &amp; 2022 batch only) Download 195.Time Table for III Semester B.E theory Semester End Examination Jan- 2025 (2023 batch regular, reappear 2021, 2022 batch and non nep batch re-registration) Download 196.Time Table for V Semester B.E theory Semester End Examination Jan- 2025 ( 2022 batch regular, reappear 2021 &amp; non NEP rereg) Download 197.Time Table for VII Semester B.E theory Semester End Examination Jan- 2025 (2021 regular &amp; Non-Nep). Download 198.Circular for extended date of reappearing for the Ensuing Examination UG- (2021,2022,2023 Batch). Download 199.Rescheduling of M.Tech/MBA/MCA Examination reg. Download 200.Notifications for Reappearing for the Ensuing Examination UG- (2021,2022,2023 Batch). Download 201.Reschedule of Time Table for M.Tech Supplementary Examination December- 2024. Download 202.Revised Time Table for Supplementary Examination December- 2024 I,III Semester MCA: Supplementary Examination Dec-2024. Download 203.Revised Time Table for Supplementary Examination December- 2024 I,II,III and VI Semester MBA: Supplementary Examination Dec-2024. Download 204.Time Table for Supplementary Examination December- 2024 III &amp; VI Semester MCA : Supplementary Examination Dec-2024 Download 205.Revised Time Table for Supplementary Examination December- 2024 II and IV Semester M.Tech: Supplementary Examination Dec-2024. Download 206.Time Table for Supplementary Examination December- 2024 II &amp; IV Semester M.Tech: Supplementary Examination Dec-2024 Download 207.Time Table for Supplementary Examination December- 2024 I Semester M.Tech: Supplementary Examination Dec-2024 Download 208.Time Table for Supplementary Examination December- 2024 III &amp; VI Semester MBA : Supplementary Examination Dec-2024 Download 209.Time Table for Supplementary Examination December- 2024 II Semester MBA: Supplementary Examination Dec-2024 Download 210.Time Table for Supplementary Examination December- 2024 I Semester MBA: Supplementary Examination Dec-2024 Download 211.Time Table for Supplementary Examination December- 2024 III &amp; VI Semester MCA : Supplementary Examination Dec-2024 Download 212.Time Table for Supplementary Examination December- 2024 II Semester MCA: Supplementary Examination Dec-2024 Download 213.Time Table for Supplementary Examination December- 2024 I Semester MCA: Supplementary Examination Dec-2024 Download 214.Circular for Fees and Regulations for Photocopy / Challenge Valuation of II semester (PG) Exam Oct - 2024. Download 215.Notifications for Reappearing for the Ensuing Examination PG- MBA/MCA/M.Tech. Download 216.Circular for Fees and Regulations for Challenge Valuation of III to VIII semester of Evening Batch Supplementary Reappear Exam Oct - 2024. Download 217.Time Table for IV Semester M.Tech theory Reappear Examination Nov- 2024. Download 218.Circular for Fees and Regulations for Challenge Valuation of supplementary semester of U.G. 2024 Examination. Download 219.Additional Time Table for III Semester MCA theory Reappear Examination Oct- 2024. Download 220.Additional Time Table for I Semester M.Tech theory Reappear Examination Oct- 2024. Download 221.Circular for Fees and Regulations for Challenge Valuation of I and II semester of U.G. Oct -2024 Semester End Examination. Download 222.Time Table for I &amp; IV Semester M.Tech theory Reappear Examination Oct- 2024. Download 223.Time Table for III Semester Supplementary Examination Oct- 2024 (2022 batch). Download 224.Time Table for IV Semester Supplementary /Re-Appear/ Makeup Examination Oct- 2024 (2022 batch). Download 225.Time Table for III &amp; IV Semester MBA Re-Appear Examination Oct- 2024. Download 226.Time Table for I &amp; II Semester MCA Re-Appear Examination Oct- 2024. Download 227.Time Table for I Semester MBA Re-Appear Examination Oct- 2024. Download 228.Time Table for III &amp; IV Semester MCA Re-Appear Examination Oct- 2024. Download 229.Time Table for Re-Scheduling of I &amp; II Semester Supplementary-2022 batch. Download 230.Time Table for Re-Scheduling of II Semester M.Tech Examination Sep- 2024. Download 231.Additional Time Table for VII Semester theory Supplementary /Reappear Examination Sep- 2024.(Evening Batch) Download 232.Revised Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of IV semester of U.G. Sep -2024 Semester End Examination. Download 233.Time Table for II Semester MCA theory Semester End Examination (Regular &amp; Reappear) Download 234.Time Table for II Semester MBA theory Semester End Examination (Regular &amp; Reappear) Download 235.Time Table for II Semester M.Tech theory Semester End Examination (Regular &amp; Reappear) Download 236.Circular for Fees and Regulations for Challenge Valuation of I &amp; II semester (2023 Batch Supplementary reappear exam Sep -2024) Semester End Examination. Download 237.Notifications for Reappearing and Makeup for the Ensuing Examination UG-2022 batch. Download 238.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of IV semester of U.G. Sep -2024 Semester End Examination. Download 239.Time Table for Revised VI Semester theory Supplementary/Re-Appear/MAKEUP Examination Sep- 2024.(2021 BATCH) Download 240.Time Table for VII Semester theory Supplementary /Reappear Examination Sep- 2024.(Evening Batch) Download 241.Time Table for I &amp; II Semester theory Supplementary Examination Sep- 2024.(2022 BATCH) Download 242.Time Table for revised IV Semester B.E. Supplementary Examination Sep- 2024 (2021 batch). Download 243.Time Table for VI Semester theory Supplementary/ reappear/ Makeup Semester End Examination Sep- 2024.(2021 BATCH ) Download 244.Time Table for VII &amp; VIII Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 245.Time Table for VI Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 246.Time Table for V Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 247.Time Table for IV Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 248.Time Table for III Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 249.additional Time Table for V Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 250.Additional Time Table for III Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 251.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of Re-registered Exams (Evening Batch) of U.G. Aug/Sep -2024 Semester End Examination. Download 252.PG Notifications for Reappearing for the Ensuing Examination (PG). Download 253.Time Table for V Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 254.Time Table for IV Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 255.Time Table for III Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 256.Time Table for I &amp; II Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 257.Notifications and formats for Reappearing for the Ensuing Examination-2021 batch( UG). Download 258.Time Table for Reappear and Makeup Examinations - Sep-2024 (for 2023 Batch). Download 259.Time Table for I Semester MBA Makeup theory Examination Sep- 2024. Download 260.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of I &amp; II Semester (2023 batch &amp; 2022 batch reappear) of U.G. July/Aug -2024 Semester End Examination. Download 261.Notifications and formats for Reappearing for the Ensuing Examination( UG). Download 262.Time Table for additional /revised V Semester B.E. Supplementary/Reappear and III Semester Reappear (NEP) theory Examination Aug- 2024. Download 263.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. &amp; P.G. June/July -2024 Semester End Examination. Download 264.Time Table for III Semester theory Semester End Examination Aug- 2024.(2022 &amp; 2021 BATCH REAPPEAR) Download 265.Time Table for Additional /revised III Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non- Nep batch. Download 266.Time Table for Additional /revised VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non- Nep batch. Download 267.Time Table for I/II Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 268.Time Table for additional /revised VI Semester B.E. Supple</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54" t="str">
+        <v>2026-03-19T18:35:24.194Z</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>https://bmsce.ac.in/home/COE-Notifications</v>
+      </c>
+      <c r="C55" t="str">
+        <v>mentary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non- NEP batch. Download 269.Time Table for V Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 270.Time Table for IV Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 271.Time Table for III Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 272.Rescheduling of Examination Aug-2024 for M.Tech IV Semester Civil stream. Download 273.Time Table for Additional /revised VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-NEP batch. Download 274.Time Table for Additional /revised VI Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-NEPbatch. Download 275.Additional/revised Time Table for VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 276.Additional/revised Time Table for VIII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 277.additional/revised Time Table for VI Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 278.Time Table for IV Semester B.E. theory Semester End Main Examination-Aug-2024 (2022 Batch Regular &amp; 2021 Batch Reappear) Download 279.Time Table for VI Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 batch (Non-Nep). Download 280.Time Table for VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 batch (Non-Nep). Download 281.Time Table for Revised IV Semester M.Tech Semester End Main Examination-Aug-2024 Download 282.Time Table for VIII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 batch. Download 283.Time Table for IV Semester PG (MBA) theory Semester End Examination Aug- 2024. Download 284.Time Table for IV Semester PG (M.Tech) theory Semester End Examination Aug- 2024. Download 285.Revised Time Table for I &amp; II Semester theory Semester End Examination July- 2024. Download 286.Circular regarding disclosure of answer Scripts of I Semester PG Students who have obtained 'F' Grade in the SEE Examination Download 287.Revised 2 Time Table for I-II Semester 2021 batch (Re-Appear &amp; Re-Registration) and I/II old scheme re-registration (non-nep) theory Semester End Examination Aug- 2024. Download 288.Time Table for V Semester (Re-Appear) theory Semester End Examination July- 2024. Download 289.Time Table for III, IV and VI Semester theory Semester End Examination (Evening) July- 2024. Download 290.Supplementary Exam Non NEP Batch notification. Download 291.Time Table for VIII Semester theory Semester End Examination July- 2024. Download 292.Reappearing for the Ensuing Examination( UG) 2021 BATCH Download 293.Reappearing for the Ensuing Examination( UG) 2022 BATCH Download 294.Reappearing for the Ensuing Examination( UG) 2023 BATCH Download 295.additional (makeup) and re registration Time Table for VI Semester B.E. theory Semester End Examination June- 2024. Download 296.Additional (makeup) and re registration Time Table for VIII B.E. theory Semester End Examination June- 2024. Download 297.Revised Time Table for VI Semester B.E. theory Semester End Examination June- 2024. Download 298.Time Table for VI Semester B.E. theory Semester End Examination June- 2024. Download 299.Tme Table for III Semester B.E theory Semester End Makeup Examination June- 2024. Download 300.Tme Table for VIII Semester B.E. theory Semester End Makeup Examination June- 2024. Download 301.Tme Table for VII Semester B.E theory Semester End makeup Examination (Second Phase) June- 2024. Download 302.Tme Table for III Semester MBA theory Semester End Makeup Examination June- 2024. Download 303.Revised Disclosure of Answer Scripts of III Semester PG Students who have obtained 'F' Grade in the SEE Examination. Download 304.Revised Time Table for I M.Tech theory Semester End Examination May- 2024. Download 305.Revised Time Table for II Semester MCA theory Semester End Examination May- 2024. Download 306.Revised Time Table for I Semester MBA theory Semester End Examination May- 2024. Download 307.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation for U.G and P G April- May -2024 Semester End Examination. Download 308.Disclosure of Answer Scripts of III Semester PG Students who have obtained 'F' Grade in the SEE Examination. Download 309.Revised Disclosure of Answer Scripts of III Semester UG Students who have obtained 'F' Grade in the SEE Examination. Download 310.Time Table for II Semester (Re appear) PG theory Semester End Examination (MCA) May- 2024. Download 311.Time Table for II Semester (Re appear) PG theory Semester End Examination (MBA) May- 2024. Download 312.Revised Time Table for I and II Semester PG theory Semester End Examination (MCA) May- 2024. Download 313.Revised Time Table for I Semester PG theory Semester End Examination (MBA) May- 2024. Download 314.Time Table for V Semester Re-Registered theory Semester End Examination May- 2024. Download 315.Time Table for I Semester PG theory Semester End Examination (M TECH) May- 2024. Download 316.Time Table for I Semester PG theory Semester End Examination (MCA) May- 2024. Download 317.Time Table for I Semester PG theory Semester End Examination (MBA) May- 2024. Download 318.Notification for Reappearing for the Ensuing Examination (PG -I &amp; II Semester). Download 319.Time Table for VIII Semester theory Semester End Examination May- 2024. Download 320.Makeup Examination Timetable for the 5th semester May-2024 . Download 321.3rd Semester Re registered Time table. Download 322.Makeup Examination Timetable for the 1st semester May-2024 . Download 323.Circular for the Semester End Makeup Examination for I, V Semester B.E April 2024. Download 324.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of I and V Semester U.G. March-April -2024 Semester End Examination. Download 325.Time Table for VII Semester B.E. theory Semester End Examination April- 2024. Download 326.III Semester M.Tech theory Semester End Examination April- 2024(Re-Appear). Download 327.III Semester M.Tech theory Semester End Examination April- 2024. Download 328. Revised VII Semester B.E. theory Semester End Makeup Examination April- 2024. Download 329. III Semester MCA theory Semester End Examination April- 2024 (Re-Appear). Download 330.III &amp; IV Semester MBA theory Semester End Examination April- 2024 (Re-Appear). Download 331.Revised IV Semester ( 2021 batch Re-Appear) B.E. theory Semester End Examination April- 2024. Download 332.Revised III Semester ( 2022 batch regular, 2021 batch Re-Appear and Re-Registration non-NEP batch) B.E. theory Semester End Examination April- 2024. Download 333.Time Table for VII Semester B.E. theory Semester End Makeup Examination April- 2024. Download 334.IV Semester ( 2021 batch Re-Appear) B.E. theory Semester End Examination April- 2024. Download 335.Time Table for III Semester ( 2022 batch regular, 2021 batch Re-Appear and Re-Registration non-NEP batch) Download 336.Time Table for III Semester MCA theory Semester End Examination March- 2024. Download 337.Time Table for III Semester MBA theory Semester End Examination March- 2024 Download 338.Notification for Reappearing for the Ensuing Examination (PG -III &amp; IV Semester) Download 339.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of VII Semester U.G Semester End Examination Jan-2024. Download 340.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of I/II/III and IV Semester (2021 batch) U.G. Supplementary Examination Dec-2023. Download 341.Revised Time Table for the I Semester (2022 batch &amp; 2023 batch) B.E. Theory Semester End Examination Feb/March- 2024. Download 342.Time Table I/II Semester Re-appear (2021 Batch), and the Re-Registered non-NEP batch B.E. Theory Semester End Examination Feb/March- 2024. Download 343.Notification for Reappearing for the Ensuing Examination (UG 2021 batch -III &amp; IV Semester). Download 344.Additional timetable for the V Semester Examination Feb/March-2024 Download 345.Circular Regarding rescheduling of V Semester B.E. Theory Semester End Examination Feb- 2024. Download 346.Time Table for V Semester B.E. Theory Semester End Examination Feb- 2024. Download 347.Notification for Reappearing for the Ensuing Examination (UG 2021 &amp; 2022 batch). Download 348.Circular for Fees and Regulations for Photocopy/Challenge Valuation of Supplementary Semester Examination for MBA/MCA/M.Tech Dec-2023. Download 349.Revised time table for VII Semester B.E. (CIVIL ENGINEERING) Theory Semester End Examination Jan- 2024. Download 350.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of I/II Semester 2022 batch B.E Semester End Examination Dec-2023. Download 351.Revised Time table for VII Semester B.E. Theory Semester End Examination Jan- 2024. Download 352.Additional Time table for VII Semester B.E. (Biotechnology)Theory Semester End Examination Jan- 2024. Download 353.Revised M.Tech timetable for Supplementary Examination Dec-2023. Download 354.Revised MCA timetable for Supplementary Examination Dec-2023 . Download 355.Revised MBA timetable for Supplementary Examination Dec-2023 . Download 356.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of IV Semester B.E Sep/Oct-2023 Semester End Examination and II semester PG Semester End Examination MBA/MCA/M.Tech Oct/Nov-2023. Download 357.Circular for Answer Scripts disclosure of M.Tech II Semester PG Students who have obtained 'F' Grade in the SEE Examination . Download 358.Circular for Answer Scripts disclosure of IV Semester UG Students who have obtained 'F' Grade in the SEE Examination . Download 359.Timetable for the B.E. (Evening College) Supplementary Examination Jan 2024 Download 360.Revised Timetable for the 5TH and 6TH SEMESTER B.E. (Evening College) Supplementary Examination Jan 2024. Download 361.Circular for Reappearing Examination December-2023 for 2021 batch Download 362.Time Table for I/II Semester (2022 scheme) B.E. Supplementary Examination Dec- 2023. Download 363.Revised notification for reappearing for ensuing examinations. Download 364.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of II Semester B.E Sep/Oct-2023 Semester End Examination. Download 365.Answer Scripts of II Semesters UG Students who have obtained 'F' Grade in the SEE Examination are open for disclosure from 27.11.2023 to 29.11.2023. Venue: P.G Block -IV Floor.-Room No.EE 4003 Download 366.Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of MBA IV Semester B.E Sep/Oct-2023 Semester End Examination. Download 367.Timetable for (Re-Registered) IV Semester B.E. Theory Semester End Examination Oct- 2023. Download 368.Timetable for (Re-Registered) III Semester MBA Theory Semester End Examination Oct- 2023. Download 369.Timetable for (Re-Registered) II Semester B.E. Theory Semester End Examination Oct- 2023. Download 370.Timetable for VI Semester B.E. Theory Semester End Examination Nov- 2023. Download 371.Revised Timetable for (Re-Registered) IV Semester B.E. Theory Semester End Examination Oct- 2023. Download 372.Time Table for the Rescheduling of the Examination for III Semester B.E. Theory Semester End Examination (Re-appear) Oct- 2023. Download 373.Time table for II Semester M TECH theory Semester End Examination Oct- 2023. Download 374.Time table for II Semester MCA theory Semester End Examination Oct- 2023. Download 375.Time table for II Semester MBA theory Semester End Examination Oct- 2023. Download 376.Circular Regarding Reschedule of Examination on 26th and 29th of September,14th and 19th of October . Download 377.Circular Regarding Reschedule of Examination on 26th of September. Download 378.ADDITIONAL (4)SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 379.Time Table for I/II Semester B.E Reappear (2021 Scheme) theory Semester End Examination Sep- 2023. Download 380.Time Table for III Semester B.E Reappear (2021 Scheme) theory Semester End Examination Sep- 2023. Download 381.Time Table for II Semester B.E and I Semester Reappear (2022 Scheme) theory Semester End Examination Sep- 2023. Download 382.ADDITIONAL (3)SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 383.ADDITIONAL (2)SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 384.Time Table for IV Semester UG (BE) theory SEMESTER END EXAMINATION SEP/OCT-2023. Download 385.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER /MAKEUP EXAMINATION FOR 5TH AND 6TH SEMESTER SEP 2023 Download 386.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of VI Semester B.E July-2023 Semester End Examination. Download 387.ADDITIONAL SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 388.Answer Scripts of VI Semesters UG Students who have obtained 'F' Grade in the SEE Examination are open for disclosure -CIRCULAR Download 389.Notification for Reappearing for the Ensuing Examination. Download 390.Circular Regarding disclosure of Answer Scripts of VI Semester B.E Students who have obtained 'F' Grade in the SEE Examination July-2023 Download 391.Time Table for IV SEM Semester M.Tech theory SEE Aug-2023 Download 392.Time Table for Revised III Semester B.E theory Makeup Examination Aug-2023 Download 393.Time Table for Revised I Semester B.E theory Makeup Examination Aug-2023 Download 394.Circular for registration fees for SEE Makeup Exam B.E I, II &amp; VIII Semester &amp; I Semester MBA August 2023. Download 395.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of VIII Semester B.E July-2023 Semester End Examination. Download 396.Time Table for IV Semester MBA theory SEE Sep-2023 Download 397.CIRCULAR FOR VIII SEM - MAKE-UP CHALLENGE VALUATION Download 398.III SEMESTER BE (RE-REGISTRATION) Time Table- AUG-2023 Download 399.VIII SEMESTER BE MAKEUP Time Table- AUG-2023 Download 400.I SEM M TECH MAKEUP Time Table- AUG-2023 Download 401.I SEM MBA MAKEUP Time Table- AUG-2023 Download 402.CIRCULAR:The Answer Scripts of VIII Semesters UG Students who have obtained 'F' Grade in the SEE Examination July-2023 are open for disclosure Download 403.CIRCULAR:The Answer Scripts of I Semesters UG Students who have obtained 'F' Grade in the SEE Examination May/June-2023 are open for disclosure Download 404.CIRCULAR:The Answer Scripts of I Semesters PG Students who have obtained 'F' Grade in the SEE Examination May/June-2023 are open for disclosure Download 405.CIRCULAR:The Answer Scripts of III Semesters UG Students who have obtained 'F' Grade in the SEE Examination May/June-2023 are open for disclosure Download 406.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of I Sem and III Semester B.E May -2023 &amp; PG I Sem June-2023 Semester End Examination. Download 407.Time Table for III Semester Semester End Examination - May - 2023.. Download 408.Circular Regarding disclosure of Answer Scripts of V,VII Semester B.E Students who have obtained 'F' Grade in the SEE Examination March-2023 Download 409.Time Table for I and II Semester Semester End Examination (UG-Re appear and re-registration)- May - 2023.. Download 410.Time Table for I Semester Semester End Examination - May- 2023. Download 411.Circular for Fees and Regulations for RT/Photocopy/CV for 5th and 7th semester SEE Semester U.G Feb/March -2023. Download 412.Circular Reg-Rescheduling of Examination-MCA &amp; MBA Mar/April-2023. Download 413.III Semester MCA Time Table for Semester End Examination - March- 2023. Download 414.III Semester MBA Time Table for Semester End Examination - March- 2023. Download 415.Time Table for III and IV Semester Supplementary Examination - March- 2023. Download 416.M TECH Time Table for III Semester SEE - March-2023. Download 417.REVISED Time Table for VII Semester Semester End Examination - Feb/March- 2023. Download 418.REVISED Time Table for V Semester Semester End Examination - Feb/March- 2023. Download 419.Circular Regarding disclosure of Answer Scripts of IV Semester B.E Students who have obtained 'F' Grade in the SEE Examination Jan-2023 . Download 420.Circular Regarding Rescheduling of exam for SEE Examination Jan-2023 . Download 421.Revised Time Table for IV Semester B.E. Theory SEE Examination January- 2023. Download 422.Circular for Fees and Regulations for Challenge Valuation of Supplementary and SEE Semester U.G/P.G December Examinations-2022. Download 423.Circular Regarding Reappear of ensuing Examination . Download 424.M TECH Time Table for I,II and III Semester Supplementary Examination - Dec- 2022. Download 425.Time Table for IV Semester Supplementary/Makeup Examination - Dec- 2022.(ADDITIONAL) Download 426.MBA Time Table for II Semester Supplementary Examination - Dec- 2022. Download 427.MCA Time Table for I and II Semester Supplementary Examination - Dec- 2022. Download 428.Time Table for IV Semester Supplementary/Makeup Examination - Dec- 2022. Download 429.Time Table for III Semester Supplementary/Makeup Examination - Dec- 2022. Download 430.Revised Time Table for B.E. II Semester SEE Makeup Examination November- 2022. Download 431.Circular regarding disclosure of answer Scripts of II Semester M.Tech Students who have appeared in the SEE Examination Oct/Nov-2022 on 26.11.2022. Download 432.Revised IV Semester B.E Students who have obtained 'F' Grade in the SEE Examination Oct-2022 are open for disclosure from 22.11.2022 to 24.11.2022. Download 433.Revised II Semester B.E Students who have obtained 'F' Grade in the SEE Examination Oct-2022 are open for disclosure from 22.11.2022 to 24.11.2022. Download 434.Circular for Fees and Regulations for Re-totaling/Photocopy/Revaluation/Challenge Valuation of II Semester &amp; IV Semester U.G SEE October-2022. Download 435.Circular regarding Semester End Makeup Exam II &amp; IV Semester B.E. Nov/Dec-2022 Download 436.Time Table for I and II Semester Supplementary Examination - Dec- 2022. Download 437.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of M.B.A. &amp; M.C.A. II Semester SEE Examinations -Oct-2022. Download 438.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of M.Tech I Semester SEE Examinations (21-22 ACY). Download 439.Circular Regarding Disclosure of answer scripts for 2nd Semester MBA &amp; MCA OCT 2022 SEE. Download 440.Circular for Fees and Regulations for Re-totaling/Photocopy/Revaluation/Challenge Valuation of VIII, VII, V Semester U.G Supplementary Examinations Sep/Oct-2022. Download 441.II Semester M.Tech Theory SEE Examination October/November- 2022 Download 442.8TH SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE OCT 2022.. Download 443.REVISED Time Table for II Semester MCA. SEE Examination - Oct- 2022. Download 444.Time Table for II Semester MBA SEE Examination - Oct- 2022. Download 445.Revised Time Table for IV Semester B.E. Theory SEE Examination October- 2022. Download 446.MBA Supplementary III and IV Semester Examination Time Table - Sep/Oct- 2022. Download 447.2ND SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) OCT 2022.. Download 448.Circular Regarding Disclosure of answer scripts for 6th semester BE (ALL BRANCHES) AUG 2022 SEE. Download 449.SUPPLEMENTARY EXAMINATION TIME TABLE FOR 2ND,3RD,5TH,7TH SEMESTER B ARCH SEP 2022.. Download 450.SUPPLEMENTARY EXAMINATION TIME TABLE FOR 3RD AND 5TH SEMESTER MCA SEP 2022.. Download 451.REVISED MBA MAKEUP EXAMINATION TIME TABLE FOR 1ST SEMESTER MBA SEP 2022.. Download 452.Notification regd: Reappear for ensuing examination Download 453.SUPPLEMENTARY EXAMINATION TIME TABLE FOR 6TH SEMESTER BE (ALL BRANCHES) SEP 2022.. Download 454.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 5TH SEMESTER BE (ALL BRANCHES) SEP 2022.. Download 455.REGISTRATION FEE FOR MBA MAKEUP EXAMINATION (1ST SEMESTER) SEP 2022.. Download 456.MBA MAKEUP EXAMINATION TIME TABLE FOR 1ST SEMESTER MBA SEP 2022.. Download 457.SEMESTER END EXAMINATION TIME TABLE FOR 3RD SEM BE SEP 2022.. Download 458.REVISED SEMESTER END EXAMINATION TIME TABLE FOR 3RD SEM BE SEP 2022.. Download 459.Time Table for II Semester MCA. SEE Examination - Oct- 2022. Download 460.Circular Regarding Disclosure of answer scripts for M TECH 1ST semester JUNE 2022 SEE. Download 461.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR MBA,MCA FOR 1ST SEM --SEE JUNE/JULY 2022 Download 462.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 8TH SEMESTER BE (ALL BRANCHES) AUGUST 2022.. Download 463.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 7TH SEMESTER BE (ALL BRANCHES) AUGUST 2022.. Download 464.Circular Regarding Disclosure of answer scripts for 1st semester MBA,MCA JUNE/JULY 2022 SEE. Download 465.SEMESTER END EXAMINATION TIME TABLE FOR 4TH MBA AUGUST 2022.. Download 466.SEMESTER END EXAMINATION TIME TABLE FOR 4TH B ARCH AUGUST 2022.. Download 467.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 8TH SEM --SEE JULY 2022 Download 468.6TH SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) AUGUST 2022.. REVISED Download 469.8TH SEMESTER MAKEUP EXAM TIME TABLE FOR BE (ALL BRANCHES) AUGUST 2022. Download 470.Circular Regarding Disclosure of Answer scripts for B.E VIII semester-July 2022 Download 471.Circular Regarding Disclosure of answer scripts for 1st semester M TECH(ALL BRANCHES) JUNE 2022 SEE. Download 472.Circular -FEE STRUCTURE SEMESTER END MAKEUP EXAMINATION FOR 1ST AND 3RD SEMESTER BE (all branches) --MAY/JUNE 2022 Download 473.SEMESTER END MAKEUP EXAMINATION TIME TABLE FOR 3RD SEMESTER BE (ALL BRANCHES) JULY 2022 Download 474.SEMESTER END MAKEUP EXAMINATION TIME TABLE FOR 1ST SEMESTER BE (ALL BRANCHES) JULY 2022 Download 475.SEMESTER END EXAMINATION TIME TABLE FOR 4TH SEMESTER M TECH AND 6TH SEMESTER MCA JULY 2022.. Download 476.8TH SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) JULY 2022.. Download 477.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 1ST SEM --SEE MAY 2022 Download 478.Circular Regarding DISCLOSURE OF ANSWER SCRIPTS FOR 1ST SEMESTER BE (all branches) SEE MAY 2022 Download 479.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 3rd SEM --SEE MAY 2022 Download 480.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 5TH AND 7TH SEM --SEE FEB/MARCH 2022 Download 481.Circular Regarding Disclosure of answer scripts for 5TH semester BE FEB/MARCH 2022 SEE. Download 482.Circular REGARDING REGISTRATION FOR SEMESTER END MAKEUP EXAMINATION FOR BE (all branches)5TH AND 7TH SEMESTER,PG (MBA 3RD SEM,MCA 3RD AND 5TH SEMESTER) --FEB/MARCH 2022 Download 483.Circular Regarding Disclosure of answer scripts for MBA 3RD SEM ,MCA 3RD AND 5TH semester FEB/MARCH 2022 SEE. Download 484.Circular Regarding Disclosure of answer scripts for 7th semester BE FEB/MARCH 2022 SEE. Download 485.Notification regarding Registration for grade improvement exam with registration form.(BOTH UG AND PG) Download 486.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 3RD AND 5TH SEMESTER MCA SEP 2022.. Download 487.REVISED 2ND SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) (OLD SCHEME) SEP/OCT 2022.. Download 488.SEE Time Table for MCA 1st semester - June- 2023. Download 489.SEE Time Table for MBA 1st semester - June- 2023. Download 490.SEE Time Table for M TECH 1st semester (ALL BRANCH)0- June- 2023. Download 491.ADDITIONAL Time Table for VI Semester Semester End Examination - July- 2023. Download 492.ADDITIONAL Time Table for VIII Semester Semester End Examination - July- 2023. Download 493.Revised Time Table for VI Semester Semester End Examination - July- 2023. Download 494.Revised Time Table for VIII Semester Semester End Examination - July- 2023. Download 495.Time Table for 5th Semester Semester End Examination - July- 2023. Download 496.Circular Regd RESCHEDULED of Time Table for III Semester (due to overlapping) Semester End Examination - May - 2023.. Download 497.Circular Regarding disclosure of Answer Scripts of III Semester MBA,MCA Students who have obtained 'F' Grade in the SEE Examination March-2023 Download 498.Circular for Fees and Regulations for RT/Photocopy/CV for MBA,MCA SEE P.G Feb/March -2023. Download 499.Circular for Fees and Regulations for RT/Photocopy/CV for 3rd and 4th supplementary semester SEE Semester U.G Feb/March -2023. Download 500.Time Table for 5th Semester makeup Examination - May- 2023. Download 501.Time Table for 7th Semester makeup Examination - May- 2023. Download 502.Time Table for MBA 3rd semester makeup Examination - May- 2023. Download 503.Circular regarding 23rd annual Convocation Download 504.Circular regarding registration for 5th,7th semester UG &amp; 3rd semester MBA SEE Makeup Exam-2023 Download</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55" t="str">
+        <v>2026-03-19T18:35:24.194Z</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>https://bmsce.ac.in/home/The-Visionaries</v>
+      </c>
+      <c r="B56" t="str">
+        <v>html</v>
+      </c>
+      <c r="C56" t="str">
+        <v>The Visionaries Late Sri. B.M.Sreenivasaiah Founder B.M.S. Educational Trust In the history of Karnataka, the name of Late Businayana Mukundadas Sreenivasaiah (BMS) occupies a prominent place in the field of Philanthropy. The Maharaja of Mysore honored him with the title of Raja Karya Prasaktha in 1946. He started the B.M.S. College of Engineering in the same year. He had forseen the urgent need for high quality technical education in India, even before independence. The ideals for which Sri. B. M. Sreenivasaiah stood, continued to inspire the inheritors of his legacy. Late Sri. B. S. Narayan Donor Trustee B.M.S. Educational Trust After the demise of "Sri. B.M.Sreenivasaiah", his dynamic and enterprising son Sri. B. S. Narayan, took over the reigns of the college. The institution grew from strength-to-strength under his able guidance. He was also instrumental in initiating international collaborative programmes such as training foreign students under International Co-operation Division (ICD) and cross cultural programs with Melton Foundation.</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56" t="str">
+        <v>2026-03-19T18:35:24.808Z</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>https://bmsce.ac.in/assets/files/Dr_Bheemsha_Arya_Principal.pdf</v>
+      </c>
+      <c r="B57" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C57" t="str">
+        <v>1 Dr. Bheemsha Arya Principal B.M.S. College of Engineering, Bull Temple Road, Basavanagudi, Bengaluru - 560 019, India Tel: +91-26622131-135 (O) Extn: 8004 Mobile : +91-9448410228 E-mail: arya.mech@bmsce.ac.in PROFILE LEADERSHIP QUALITIES ➢ Male, Indian, Born on May 3 rd , 1967 ➢ Received B.E degree in Industrial and Production Engineering from Bangalore University, Bangalore ➢ Further studied in Mechanical Engineering and received M.E degree (Manufacturing Science and Engineering) from U.V.C.E. Bangalore ➢ Ph.D. from Visvesvaraya Technological University, Belagavi Karnataka, India. ➢ Founder President, BMSCE Aided faculty forum ® ➢ President, All Karnataka Aided Engineering College SC/ST Employees Welfare Association ® ➢ Secretary, All Karnataka Aided and Government Engineering Colleges Professors Association ® ➢ Mentor / Advisor to many Social, Non-Political and Non-Government Organizations. ➢ Financially supporting to many poor and needy students for their education and social needs. ➢ Create a transformative vision, guide employees in making it a reality, and enable them to overcome barriers ➢ Inspire all colleagues towards the achievement of the goals of the institute and leading them from the forefront. ➢ To encourage, guide, and direct faculty, staff, and other stake holders to work together in achieving the set goals. ➢ Ability to Planning, Organizing, Leading, Directing, Coordinating and Controlling various activities in the college. 2 ➢ Take initiatives to build the team spirit among the employees. ➢ Ability to effective liaison between employees and management. ➢ Set high standards of discipline. ➢ Sincere, committed and dedicated in work pattern. RESEARCH INTERESTS AND EXPERTISE ➢ Established and Developed a Thermoacoustic Refrigeration system. ➢ Heat Transfer enhancement, experimentation on Thermoacoustics, heat exchangers, pressure sensors. ➢ Composite Materials. ➢ Published many research articles in various reputed International and national journals SUBJECT &amp; FIELD OF SPECIALIZATI- ON ➢ Mechanical Engineering ➢ Manufacturing Technology ➢ Production Engineering ➢ Industrial Engineering ➢ Thermal Sciences and Composite Materials EDUCATIONA- TIONAL QUALIFICATI- ON PROFESSIONAL EXPERIENCES (I) Research Experience: Worked on the research project entitled : “Design, Development and Performance Evaluation of Thermoacoustics cooling systems”, All India Council for Technical Education (AICTE) funded project of Rs. 9.7 Lakhs at R&amp;D Centre, B.M.S. College of Engineering, Bengaluru, India as a Principal investigator from March 2008 to February 2014. Qualification Branch/Stream University/Board Year Ph.D. Thermoacoustics cooling systems VTU, Belagavi, Karnataka India. 2014 M.E. Manufacturing Science and Engineering Bangalore University, Karnataka, India 2001 B.E. Industrial Production and Engineering Bangalore University, Karnataka, India 1994 3 (II) Teaching Experience : Working as a Principal and Professor in the Department of Mechanical Engineering. Worked as Vice-Principal (Academics &amp; Administration) at B.M.S. College of Engineering, Autonomous Institution, Affiliated to Visvesvaraya Technological University, Belagavi, Karnataka India, since April 2003 to Till date. (III) Industry Experience: Worked as Manager in M/s Malu Group of Industries Bangalore, for a period of 09 years from June 1994 to March 2003. (IV) Academic &amp; Administrative Activities : ➢ Actively involved in the advances in teaching learning methodology, outcome based education (OBE) in engineering curriculum. ➢ Expert in OBE and Accreditation process. ➢ Implementation of OBE &amp; Accreditation in the college and Programmes by NAAC &amp; NBA. ➢ Effective Implementation of NEP-2020 and progress. ➢ Provide conceptual knowledge to students and make them visualize the things. ➢ Identify the weak points of students and motivate them to achieve. ➢ Organize the industrial visit for students. ➢ Develop the curricular and extracurricular activities for students. ➢ Provide Educational Social and economic support to poor students. ➢ Conducting lectures and preparing the course material for students. ➢ Researching on different subjects like Thermal sciences and Manufacturing Technology. ➢ Collaborate with colleagues at Faculty Forum / Association as President to address their grievances / issues. ➢ Serving Faculty Forum / Association as President to deal with welfare of the employees. ➢ Acting as adviser to students as Proctor. ➢ Acting as adviser / mentor to many Social, Non-political and Participating in Department / campus and community events. ➢ Motivating the faculty to write and submit the research proposals to external funding agencies like DRDO, SERB, DST, VGST, AICTE etc. ➢ Motivating the faculty to publish research papers in good quality journals 4 / publications. ➢ Initiated the modernization of classroom cum laboratories. ➢ Providing guidance to the students for developing their career as well as making them familiar with different career opportunities. ➢ Advising the students for making them efficient in their work. ➢ Preparing effective course material and utilizing it for the progress of students. ➢ Encouraging the students for preparing for higher studies and competitive examinations like UPSC, KPSC and others. ➢ Applying creativity and technical expertise to produce a high- caliber projects for the students. ➢ Guiding and monitoring the research scholars for completing their projects / research work with good publications and patents. ➢ Actively involved in organizing the National and International Conferences on Engineering and Technology. ➢ Responsible for getting 6 years NBA Accreditation to PG program M.Tech in Machine Design as HOD. ➢ Measures taken to upgrade and establish new laboratories to create State of Art Laboratories such as EME Lab, MMM Lab, Flow Lab, H.A.P Lab, H.M.T Lab, Mechatronics Lab, Design Lab, Machine Shop &amp; CNC Lab etc. as HOD during 2017 to 2019. ➢ Upgraded and calibrated all the equipment’s, machinery’s by using in - house experts in the department. ➢ Effectively carried out managerial and administrative duties as Machine shop superintendent during the period from May 2005 to 2011 and 2014 to 2017. ➢ Planning, evaluating and revise curricula, course content, and course materials and methods of Instruction as Member / Chairman BOS and BOE ➢ Initiated felicitation program for staff and faculty members who rendered 25 years of service in BMS Institutions. ➢ As Principal at BMS Evening College of Engineering steps taken to improve the admissions and maintained the discipline in functioning the college. 5 ➢ Under the able guidance and leadership responsible to get accredited by NAAC with highest grade of “A++” (3rd c ycle) in 2024. BMSCE is proud to be first and only Engineering College in Karnataka accredited with highest Grade in three consecutive cycles of NAAC Accreditation. ➢ A Framework for the Effective Implementation of 21 Strategies for the Holistic Development of Institutional Growth. (V) Courses Taught : 1) Elements of Mechanical Engineering 2) Basics of Thermodynamics 3) Elements of Engineering Drawing 4) Manufacturing Processes 5) Foundry Technology 6) Machine Drawing 7) Industrial Engineering and Management 8) Organizational Behaviors 9) Management and Entrepreneurship 10) Constitution of India and Professional Ethics (VI) Laboratory Taught : 1) Energy Conversion Engineering Lab 2) Foundry and Forging Lab 3) Manufacturing Process Lab 4) Basic Work Shop Practices Lab, etc. (VII) Membership of Professional Bodies: ➢ Lifetime Member Fellow (FIE) of The Institute of Engineers (India) ➢ Lifetime Member of Indian Society for Heat and Mass Transfer (ISHMT) ➢ Lifetime Member of Indian Society for Technical Education (ISTE) ➢ Lifetime Member of Indian Society for Fluid Mechanics and Fluid Power (FMFP) (VIII) Career Summary: ✓ A progressive and multitalented Professor with extensive practical knowledge having 30 year of experience in Industry and Institution. ✓ Excellent knowledge of Mechanical Engineering / Technology and the innovative methodologies. 6 ✓ Proficient in managing the opportunities for students. ✓ Expert in offering up-to-date technological information. ✓ Highly proficient in both subject matter and application. ✓ Exceptional subject knowledge combined with a strong ability to impart practical knowledge. (IX) Personality Traits: ✓ Excellent Presentation, motivational and leadership skills. ✓ Strong analytical, logical and mathematical skills. ✓ Ability to handle the students, Staff and Faculty members and resolve their issues and problems immediately. ✓ Ability to provide quality knowledge and guidance. ✓ Ability to take everybody into confidence and work together. (X) KEY RESPONSIBILITIES WITHIN THE COLLEGE: Sl No. Responsibility Period 1 Workshop Superintendent May 2004 to 2011 and 2014 to 2017 2. Head of the Department May 2017 to May 2019 3. Principal B.M.S Evening College of Engineering April 2019 to Aug 2020 4. Vice Principal (Academics) 31.01.2022 to 30.10.2022 5. Vice Principal (Administration) 31.10.2022 to 31.06.2024 6. Principal 29.06.2024 to Till Date 7 (XI) KEY RESPONSIBILITIES OUTSIDE THE COLLEGE: Sl No. Organization Responsibility Period 1. Visvesvaraya Technological University (VTU) Member, Executive Council From 03.12.2025 2. Dr. Ambedkar Institute of Technology, Bengaluru – 560 056 Member, BOG From 27.06.2025 3. Visvesvaraya Technological University (VTU) Member, Academic Senate From 25.06.2025 4. UVCE, Bangalore University (BU) Member, Academic Expert From 19.04.2025 5. All India Council for Technical Education (AICTE) Member, Standing Committee for Granting Autonomous Status 02.04.2025 6. Visvesvaraya Technological University (VTU) Member, Governing Council From 22.03.2025 7. Visvesvaraya Technological University (VTU) Member, Steering Committee From 22.03.2025 8. Harsha Institute of Technology, Varadhanayakana Halli, Bengaluru – 560 074 VTU Nominee Scrutiny Committee 25.01.2025 9. Don Bosco Institute of Technology, Kumbalagodu, Bengaluru – 560 074 VTU Nominee Academic Council From 02.01.2025 10. R.N.S. Institute of Technology, Channasandra, Bengaluru – 560 098 VTU Nominee Academic Council From 02.07.2024 11. Dr. Ambedkar Institute of Technology, Bengaluru – 560 056 VTU Nominee for faculty selection committee From 13.05.2024 12. Visvesvaraya Technological University (VTU) Member Petition Enquiry From 2024 13. Defense Research and Development Organization (DRDO) Departmental Promotional Committee Member From 2021 14. Visvesvaraya Technological University (VTU) LIC Member From 2020 15. Gandhi Krishi Vigyana Kendra (GKVK) Bangalore CAS Promotion Committee Member 2019-2020 16. Social / Non-Political and Non- Governmental Organizations (NGO) Mentor/ Advisor From Student Days 8 (X) Ph.D. SCHOLARS: Sl.No Student Name USN Registration Year Current Status 1 Shivakumara N V 1BM17PMA01 Feb-2017 Awarded in April 2021 2 Maharudra 1BM18PME07 Sept-2017 Awarded in Dec 2023 3 Pampapathi Gaddi 1BM18PME02 Oct-2017 In Progress 4 Sandesh N U 1BM19PVC06 Apr-2019 In Progress 5 Ramesh Mallappa 1BM21PME04 Feb-2023 In Progress 6 Parmeshkumar 1BM22PME05 Feb-2024 In Progress 7 Mallappa Komar 1BM22PME04 Feb-2024 In Progress (XI) RESEARCH GRANTS: Sl.No. Funding Agency Amount Period 1*. AICTE 9.70 Lakhs 2008 – 2014 * Established Thermoacoustic Laboratory in the Mechanical Engineering Department and produced 03 Ph.D’s along with many UG / PG Projects (Annexure-I). (XII) PATENTS: Sl.No. Title Application Number Cash award Period 1*. A heating Element for a Cooking apparatus using DC Power supply 201841014926 Rs. 5.00 Lakhs from Ministry of ONGC, GOI 2019 * (Annexure-II). (XIII) BEST PAPER AWARDS: Sl.No. Paper title Publisher Best paper award Period 1*. Effect of trapezoidal shapes on the thermal buckling behaviour of perforated composite plates. American Journal of Materials Science, 2021 11(1), pp. 10-19, 10.5923/j.materials.20211 101.02 37 th Indian Engineering Congress held in Chennai 16 th December 2022 * (Annexure-III). 9 (XIV) WORKSHOPS / FDPs ATTENDED: Title From To Duration AICTE sponsored Staff Development Program on ‘Emerging Trends in Energy Sources’ at Ghousia College of Engineering, Ramanagara. 13/06/2011 24/06/2011 Two weeks AICTE sponsored Industry Institute Partnership Cell Activity Faculty Development Program on ‘Lab VIEW and its Applications in Engineering at B.M.S College of Engineering, Bengaluru. 11/07/2011 16/07/2011 One week VTU-VGST Faculty Development Program on ‘Alternate Fuels for IC Engines at P.D.A College of Engineering, Gulbarga. 12/03/2012 16/03/2012 One week DST sponsored National Institute for Micro, Small &amp; Medium Enterprises Faculty Development Program in Entrepreneurship Development at B.M.S College of Engineering, Bengaluru. 19/03/2012 30/03/2012 Two weeks TEQIP-II sponsored Faculty Development Program on ‘Biostatics and Bio-modeling using Software Tools’ at B.M.S College of Engineering, Bengaluru. 22/07/2013 26/07/2013 One week TEQIP-II sponsored Workshop on ‘MEMS and Nano Technology’ at B.M.S College of Engineering, Bengaluru. 19/08/2013 24/08/2013 One week TEQIP-II sponsored Workshop on ‘Japanese Management Techniques’ at B.M.S College of Engineering, Bengaluru. 26/08/2013 30/08/2013 One week TEQIP-II sponsored Faculty Development Program on ‘Intelligent Machines &amp; Systems’ at B.M.S College of Engineering, Bengaluru. 20/01/2014 24/01/2014 One week TEQIP-II sponsored Faculty Development Program on ‘Developments in Hydraulic and Pneumatic Controls at B.M.S College of Engineering, Bengaluru. 27/01/2014 31/01/2014 One week 10 TEQIP-II sponsored Workshop on ‘Gas Turbine Technology and Current Challenges’ at B.M.S College of Engineering, Bengaluru. 21/03/2014 23/04/2014 Three days TEQIP-II sponsored Faculty Development Program on ‘Theoretical, Computational and Applied Mechanics’ at B.M.S College of Engineering, Bengaluru. 16/06/2014 20/06/2014 One week TEQIP-II sponsored Workshop on ‘Modelling Using Microsoft Office Excel at B.M.S College of Engineering, Bengaluru. 21/07/2014 25/07/2014 One week (XVII) RESEARCH PUBLICATIONS: (i) INTERNATIONAL JOURNALS: 1. Venkatesh T lamani, Sudarshan B, Ramesh m Chalkapuri, Bheemsha Arya , Banjara Kotresh, “Investigation of combustion, performance and emission studies of HCCI engine operated with carbon free fuels, Engineering Research Express , Vol. 7, Issue 2 (2025), p. 025540. http://doi.org/10.1088/2631-8695/adcff7 . 2. Maharudra, Rajanna T, Bheemsha Arya , “Effect of trapezoidal shapes and non- uniform edge loads on buckling behaviour of plates with cutouts ”, Proceedings of Institutional of Mechanical Engineers, Part C: Journal of Mechanical Engineering Science , Vol. 236, Issue 7 (2022), pp. 3512-3529. https://doi.org/10.1177/09544062211022258 . 3. Shivakumara N V, Bheemsha Arya , “Performance analysis of thermoacoustic refrigerator of 10W cooling power made up of poly-vinyl-chloride for different parallel plate stacks by using helium as a working f luid”, Journal of Thermal Science , Vol. 30, Issue 6 (2021), pp. 2037-2055. https://doi.org/10.1007/s11630-021-1390-y. 4. Venkatesh T. Lamani, Adithya U. Baliga M, Ajay Kumar Yadav, Kumar G. N, Rudra Naik, Bheemsha Arya , “Optimum injection timings for bioethanol -diesel blends and its effect on tail pipe emission in common rail diesel e ngine”, In AIP Conference Proceedings, Vol. 2316, Issue 1 (2021), pp. 030031, AIP Publishing LLC. https://doi.org/10.1063/5.0036569. 5. Maharudra, Rajanna T, Bheemsha Arya , “Influence of trapezoidal shapes and linearly 11 varying edge load s on the buckling characteristics of plates with cutouts”, Journal of The Institution of Engineers (India): Series C . Vol. 102, Issue 5, (2021), pp. 1231- 1249. 6. Maharudra, Rajanna T, Bheemsha Arya , “Thermal buckling b ehaviours of laminated composite trapezoidal panel under thermally induced l oads”, American Journal of Materials Science , Vol. 11, Issue 1 (2021) pp. 10-19. https://doi:10.5923/j.materials.20211101.02. 7. Maharudra, Rajanna T, Bheemsha Arya , “Effect of trapezoidal shapes on the thermal buckling be haviour of perforated composite plates”, Advances in Materials Science , Vol. 21, No. 1 (67), (2021), pp. 10-26. https://doi: 10.2478/adms-2021-0002. 8. Maharudra., Rajanna T, Bheemsha Arya , “Influence of trapezoidal shapes and cutout sizes on the buckling behaviour of composite laminates under thermally induced loads”, Latin American Journal of Solids &amp; Structures , Vol. 18, Issue 3 (2021), pp.1- 13. https://doi.org/10.1590/1679-78256331. 9. Maharudra, Bheemsha Arya , Rajanna T, “Buckling behaviour of composite la minates of trapezoidal panel with cutout subjected to non-uniform in- plane edge loads”, Materials Today: Proceedings , Vol. 45, (2021), pp. 21-26. https://doi.org/10.1016/j.matpr.2020.09.224. 10. Maharudra, Bheemsha Arya , Rajanna T, “Effect of trapezoidal shap ed laminated composite plate with and without cutout on vibration characteristics”, Materials Today: Proceedings , Vol. 45, (2021), pp.34-40. https://doi.org/10.1016/j.matpr.2020.09.228. 11. Maharudra, Bheemsha Arya , Rajanna T, “Effect of ply -orientation and boundary conditions on the vibrational characteristics of laminated composite panels using HODST”, Materials Today: Proceedings , Vol. 20, (2020), pp. 134-139. https://doi.org/10.1016/j.matpr.2019.10.062. 12. Shivakumara N V, Bheemsha Arya , “Effect of parallel pl ate stack spacing on the performance of thermoacoustic refrigerator in terms of temperature difference using air as a working fluid”, In Journal Physics: Conference Series , Vol. 1473, Issue 1, p. 01205. IOP publishing, 2020. 13. Shivakumara N V, Bheemsha Arya , “Experimental performance evaluation of thermoacoustic refrigerator made up of poly-vinyl-chloride for different parallel plate stacks using air as a working medium”, Materials Today: Proceedings , Vol. 22 (2020), pp. 2160-2171. 12 14. Shivakumara N V, Bheemsha Arya , “Performance evaluation of 10 W cooling power thermoacoustic refrigerator with spiral stacks using air and helium as working fluids” Engineering Research Express , Vol. 2, Issue 1 (2020), p. 015032. 15. Shivakumara N V, Bheemsha Arya , “Influence of p arallel plate stack spacing on the temperature difference of Thermoacoustic refrigerator by using helium as a working m edium”, International Journal of Recent Technology and Engineering (IJRTE) , Vol. 8, Issue 4 (2019), pp. 2704-2712. 16. Shivakumara N V, Bheemsha Arya , “Effect of Spacing in a parallel plate stack on the performance of thermoacoustic refrigerator made up of PVC for an operating pressure of 8 made up of PVC for an operating pressure of 8”, Journal of Emerging Technologies and Innovative Research , Vol. 6, Issue 1 (2019), pp. 1063-1069. 17. Shivakumara NV, Kapil Chhetri, Mayur P Kodikal, Myron Chris Menezes, Bheemsha Arya “Thermoacoustic refrigerator: A Review on design, fabrication and Performance” Journal of Emerging Technologies and Innovative Research , Vol. 5, Issue 7 (2018), pp. 848-854. 18. Bheemsha Arya , B Ramesh Nayak, N.V Shivakumara “Effect of Dynamic Pressure on the Performance of Thermoacoustic Refrigerator with Aluminium (Al) Resonator” IMMT 2017 – In IOP Conference Series: Materials Science and Engineering , Vol. 346, Issue 1, p. 012034. IOP publishing, 2018. http://doi:10.1088/1757- 899X/346/1/012034. 19. B Ramesh Nayak, G Pundarika, Bheemsha Arya , “Influence of stack geometry on the performance of thermoacoustic refrigerator”, Sadhaana , Vol. 4, Issue 2 (2017), pp. 223-230. 20. Bheemsha , Ramesh Nayak, Pundarika, “Performance evaluation of thermoacoustic refrigerator using air as working medium”, SSRG International Journal of Thermal Engineering (SSRG-IJTE) , Vo. 1, Issue 3 (2015), pp. 16-21. https://doi.org/10.14445/23950250/IJTE-V1I3P101. 21. Bheemsha , Harsha D N, Arvind Rao, “Study of sustainable utility of bio mass energy technologies for rural infrastructure and village power – Opportunities by developing bio village model”, International Journal Research in Engineering and Technology , Vol. 3, Issue 1 (2014) pp.1 -7. 22. Bheemsha , Ramesh Nayak, Pundarika G, “Design of the resonator tube and buffer volume for thermos- acoustic refrigerator” International Journal of Advanced Scientific &amp; Technical Research , Vol. 2, Issue 1 (2011), pp. 276-288. 23. Bheemsha , Ramesh Nayak &amp; Pundarika.G, “Design of a parallel plate stack for a 13 thermoacoustic refrigerator” International Journal of Advanced Scientific &amp; Technical Research , Vol. 2, Issue 1 (2011), pp. 1-20. 24. Bheemsha , Ramesh Nayak, Pundarika G, “Design and optimization of a thermoacoustic r efrigerator”, International Journal of Emerging Trends in Engineering and Development , Vol. 2, Issue 1 (2011), pp. 47-65. * (Annexure-IV). (XVIII) BOOK CHAPTER PUBLISHED: 1. Venkatesh Lamani, Ravi L, Bheemsha Arya , Rudra Naik, Rohan C, Srikanth P, Rajashekar Gowda M.D, R.S. Verma, “STATE OF ART TECHNOLOGIES IN AGRICULTURE AND RECOMMENDATION TO IMPROVE FARMER‟S ECONOMY THROUGH SOLAR TREE CONCEPT” Recent Research in Agriculture for doubling of far mer‟s Income, Book Chapter edited by Shampi Jain and Neeraj Verma 2023. *(Annexure-V) (XIX) NATIONAL AND INTERNATIONAL CONFERENCE: 1. Venkatesh Lamani, Ravi L, Bheemsha Arya , Rudra Naik, R S Verma, Rohan C, Srikanth P, Rajashekharegowda M D, “ State of art technologies in agriculture and recommendation to improve farmer’ s economy through solar tree concept ”, National Conference on Biotechnology and Sustainable Agriculture in Doubling of Farmer’s Income by 2022, Department of Agriculture Science, AKS University Sherganj, Panna Road, Satna – 485001 Madhya Pradesh, India. 2. Venkatesh T Lamani, Ravi L, L. Ravikumar, Rudra Naik, Bheemsha Arya , “CFD analysis of N- butanol - diesel blends and low temperature combustion in CRDI e ngine” has been accepted for presentation in the Proceedings of the 3 rd National Aerospace Propulsion Conference (NAPC 2020) , jointly organized by B.M.S. College of Engineering, Bengaluru &amp; Gas Turbine Research Establishment, DRDO, Bengaluru under the auspices of National Committee on Air Breathing Engines on a digital platform during 17th – 19th , December, 2020. 3. Maharudra, Rajanna T, Bheemsha Arya , “Buckling behaviour of composite laminates of trapezoidal panels with cutout subjected to non-uniform in-plane loads ”, ICAMMME-2020 held at Reva University Bengaluru during 10-11 th July- 2020 4. Maharudra, Rajanna T, Bheemsha Arya , “ Effect of trapezoidal shaped laminated composite plate with and without cutout on vibration characteristics ”, ICAMMME- 2020 held at Reva University Bengaluru during 10-11 th July-2020. 5. Venkatesh T Lamani, Rudra Naik, Bheemsha Arya , Ravi L,Abhishek J, Abhishek 14 Krishnan, Angshuman Bhattacharya, Nikhil Setty, “Fire Simulation of Car Park to Optimise Fire Ventilation System” has been accepted for presentation in the Proceedings of the 25thNational and 3rd International ISHMT-ASTFE Heat and Mass Transfer Conference (IHMTC-2019), 28 th -31 st December 2019, IIT Roorkee, Roorkee, India. 6. Venkatesh T Lamani, Rudra Naik, Bheemsha Arya , Ravi L, L Lokesh Kumar, Ashish SV, B.S Raviteja , Arun A, “Nanop articles use for the effective hyperthermia of liver tumor ” has been accepted for presentation in the Proceedings of the 25 th National and 3 rd International ISHMT-ASTFE Heat and Mass Transfer Conference (IHMTC-2019) , 28 th - 31 st December 2019, IIT Roorkee, Roorkee, India. 7. Shivakumara N V, Bheemsha Arya, “Effect of parallel plate stack spacing on the performance of thermoacoustic refrigerator in terms of temperature difference using air as a working medium” ICTES 2019 held at BNMIT, Bengaluru during 23-24 December 2019. 8. Venkatesh T Lamani, Adithya U Baliga M, Ajay Kumar Yadav, Kumar G N, Rudra Naik, Bheemsha Arya , “Optimum injection timings for bioethanol -diesel blends and its effect on tail pipe Emission in common rail diesel engine ”, International Conference on Advance Trends in Mechanical &amp; Aerospace Engineering (Theme: Research Innovation in Mechanical and Aerospace Technologies) from 7 th – 9 th November 2019 organized by Dayananda Sagar University, School of Engineering Hosur Main Road, Kudlu Gate, Bengaluru. 9. Maharudra, Rajanna T, Bheemsha , “Effect of ply -orientation and boundary conditions on dynamic behaviour of laminated composite panels”, 35th National conference on Trends and Developments in Automotive Industries , held at The IEI(India), Hosur local center during 4 th - 5 th Sept 2019. 10. Maharudra, Rajanna T, Bheemsha Arya , “Effect of ply -orientation and boundary conditions on the vibrational characteristics of laminated composite panels using HODST”, ICRRETMME-2019 held at Reva University Bengaluru during 12-13th July-2019. 11. Shivakumara N V, Bheemsha Arya , Effect of spacing in a parallel plate stack on the performance of Thermoacoustic Refrigerator made up of PVC for an operating pressure of 8 bar using air as a working medium. NCIMIMP-2019 held at Dr.AIT, Bengaluru during June 7 - 8 of 2019. 12. Maharudra, Rajanna T, Bheemsha Arya , “Finite element formulation for static and dynamic analysis of laminated composite plates using HOSDT”, National Conference on Recent Trends in Science, Engineering and Management held at Dr. AIT Bengaluru during 6 th -7 th June 2019. 13. Shivakumara N V, Bheemsha Arya , “Experimental performance evaluation of 15 thermoacoustic refrigerator made up of poly-vinyl-chloride for different parallel plate stacks using air as a working medium ” ICMMM-2019 held at VIT Vellore during 29 th – 31 st March 2019. 14. Venkatesh T Lamani, L.Ravi, Bheemsha Arya , “ CFD Study of blood flow in carotid artery ” in the Proceedings of the 7 th International &amp; 45 th National Conference on Fluid Mechanics &amp; Fluid Power (FMFP) organized by Indian Institute of Technology-Bombay, Mumbai from 10 th -12 th December 2018. 15. Bheemsha , Pundarika G, Ramesh Nayak B, Rudra Naik, “Production of biodiesel from Jatropha for Diesel engines” National Seminar on Advances in Automobile Engineering , Pune 23&amp;24 May 2009. 16. Bheemsha , Suresh S M, Rudra Naik, Pundarika G “Design of Resonator for thermoacoustic refrigerator” National conference On emerging technologies in Mechanical engineering . Krishna institute of Engineering and Technology Ghaziabad New Delhi, 27&amp;28 June 2008. 17. Bheemsha , Pundarika G, Rudra Naik, Suresh S M &amp; Pundarika G, “Thermodynamics Anaysis of Gas Turbine Cogeneration System”, International Conference on Recent Development in Mechanical Engineering , 23-25 Janauary 2008 SUSCET Mohali, Chandighar. 18. Bheemsha , Pundarika.G, Rudra Naik, Suresh S.M &amp; Pundarika.G. „Design Of Heat Exchanger For Thermoacoustic Refrigerator‟ International Conference on Recent Development in Mechanical Engineering, 23-25 Janauary 2008 SUSCET Mohali, Chandighar. 19. Bheemsha , Ramesh Nayak, RudraNaik, Pundarika G , “Production of jatropha o il and performance characteristics of a twin cylinder diesel engine using jatropha-diesel b lend” International Conference on I.C. Engines and Combustion , Dec 6-9 2007. JNTUH, Hyderabad. 20. Bheemsha , Rudra Naik, Ramesh Nayak, Pundarika G, “Air -conditioning of cars using waste heat driven a bsorption system”, National Conference on Futuristic trends in Mechanical Engineering , 13-14 September, 2007 at SUS College of Engineering &amp; Technology, Mohali-Chandigarh. 21. Bheemsha, Rudra Naik, Ramesh Nayak, Pundarika G, “Structural analysis of c hip substrate assembly”, National Conference on Futuristic trends in Mechanical Engineering , 13-14 September, 2007 at SUS College of Engineering &amp; Technology, Mohali-Chandigarh. 22. Bheemsha , Sheshadri T S, Rudra Naik, Pundarika G, “Experimental Study of Supersonic Impinging Jet on Flat Plate” National Symposium on Acoustics” National Physical Laboratory. 15-17 November 2006. Jamia Millia Islamia Central University, New Delhi. 16 23. Bheemsha , Suresh S M, Rudra Naik, Pundarika G, “Numerical Study on Supersonic Jet Noise” National conference on Advances in Mechanical Engineering, 21-22 January 2006. Jamia Millia Islamia Central University, New Delhi. 24. Bheemsha, Suresh S M, Rudra Naik, Pundarika G, “ Design of stack for thermoacoustic r efrigerator” National conference on recent advances in Mechanical Engineering, 1-3 rd December 2005, P. A. College of Engineering, Mangalore. 25. Bheemsha , Hithesh Shah, RudraNaik, Pundarika G , “Design an d Theoretical construction of thermoacoustic r efrigeration” Inte rnational conference on Theoretical Applied Computational and Experimental mechanics . Dec 28-30 2004. IIT, Kharagpur. 26. Bheemsha , Pavankumar S S, Thyagaraj S K, C K Chandrababu, G Pundarika, “ Experimental investigations on the performance characteristics of a jatropha blend as a diesel engine fuel ”, First national conference on Energy and Fuel Issues of Future , November 5-6, 2004. I hereby declare that above information provided is true and correct to the best of my knowledge. Dr. BHEEMSHA ARYA Place: Bengaluru Date: 08, Dec 2025</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57" t="str">
+        <v>2026-03-19T18:35:25.860Z</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>https://bmsce.ac.in/home/About-BMSCE</v>
+      </c>
+      <c r="B58" t="str">
+        <v>html</v>
+      </c>
+      <c r="C58" t="str">
+        <v>About BMSCE Vision Promoting Prosperity of mankind by augmenting human resource capital through quality Technical Education &amp; Training. Mission Accomplish Excellence in the field of Technical Education through Education, Research and Service needs of Society. B.M.S. College of Engineering (BMSCE) Bengaluru has the unique distinction of being the first private engineering college established in the country. Started in the year 1946, the institution owes its existence to the vision of its beloved founders, Late Sri. B. M. Sreenivasaiah and his illustrious son Late Sri. B. S. Narayan. Over the past 77 years of its illustrious existence, BMSCE has produced more than 40,000 graduates who have enriched the world through their immense contributions as engineers or leaders for mankind. The Institution is approved by All India Council of Technical Education (AICTE) and permanently affiliated to Visvesvaraya Technological University (VTU), Belagavi. The college is aided by Government of Karnataka. BMSCE is approved as QIP Centre in Engineering &amp; Technology by AICTE. The College became autonomous, UGC approved, in 2008 and has been effectively practicing Outcomes-based Education. The College has the distinction of being awarded best performance rating in all three Phases of TEQIP. The institution is also a Beneficiary of Global Initiative Academic Network (GIAN). BMSCE is the only Partner institution in the country of the Melton Foundation, USA which promotes cross cultural learning for the selected students along with peers from five other countries. The College is accredited by National Assessment and Accreditation Council (NAAC) with the highest grade of A++ in the Second Cycle and a CGPA of 3.83 on a scale of four. Currently all the Undergraduate Programmes and post-Graduate Programmes hold the status of Accreditation from National Board of Accreditation (NBA), New Delhi in tier I Format. AICTE has recognized the college under AICTE Doctoral Fellowship Scheme (ADF) since 2018-19. BMSCE is listed as a lead innovator for the year 2020 and 2021 by Clarivate Analytics (Web of Science) based on the Derwent World Patent Index. In the ARIIA (ATAL Rankings) 2021, the college is ranked in band-Excellent. BMSCE is one of the 100 colleges in the country awarded 5G use case laboratory. The College currently offers 17 Undergraduate &amp; 15 Postgraduate courses both in conventional and emerging areas. More than 344 research scholars are pursuing their Ph.D Degree in the 14 research centres of the college. 244 PhDs and 22 M.Sc. (by research) have been produced so far through these research centres. BMSCE has recently achieved the prestigious ISO 14001:2015 certification for its Environmental Management System through qualified external ISO 14001 auditors. The Institution has MOUs with various organizations across the globe. It has developed many Centres of Excellence, cutting edge laboratories and incubation centres in collaboration with industries with an aim to enrich the learning experiences of the graduating students and to comply with the programme outcomes. The learning experiences and quality educational practices created at the institute supplemented with academic ambience, state of the art infrastructure, pedagogy, academic innovations, research, incubation, training opportunities and entrepreneurship provided to diverse student population is enabling the institute to produce graduates who are industry ready. BMSCE is one of the most preferred higher educational destination for the students all across the country and also attracts students from various countries. The institution has played significant role in developing human resource capital to meet the requirement of society in India and abroad. The College has one of the largest student populations amongst engineering colleges in the state of Karnataka. The academic performance of the students has been exceptional. The Institution has an excellent Training and Placement Cell. More than 350 reputed companies visit the campus every year. The College results and placement bear testimony to the high standard of education provided by the institution. The academic processes are developed with due weightage to provide skills through project-based learning model. Curriculum design &amp; development, Pedagogy and Assessment are given highest priority. The institution has consciously put efforts in encouraging innovation and has adopted best practices/processes in Teaching Learning Processes. In order to enhance the learnability of the students and to make them industry ready by bringing down the gap, technology tools, self-learning, social learning, MOOCs, internships/industry training are introduced as a part of the curriculum. The faculties are well qualified, experienced and highly dedicated. Many of whom have the distinction of being NBA, NAAC Evaluators, Members of BOS, BOE, LIC, AICTE, governing bodies of VTU etc. Faculty members have received numerous awards for their teaching, research, and public service also for their contribution in finding suitable solutions to environmental challenges. The institution has adopted best practices and key principles of good governance in all its administrative procedures. The Institution has received many Distinctions/Awards in recognition of its contribution in the field of Technical Education. The college is being ranked consistently among the top engineering colleges in the country by various media sources.</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58" t="str">
+        <v>2026-03-19T18:35:26.475Z</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>https://bmsce.ac.in/home/About-R-and-D</v>
+      </c>
+      <c r="B59" t="str">
+        <v>html</v>
+      </c>
+      <c r="C59" t="str">
+        <v>About R &amp; D Dr. Chandasree Das Head, R &amp; D RESEARCH &amp; DEVELOPMENT CENTRE R&amp;D Center involves in identifying new research areas, developing projects leading to publications in National/International Journals and conferences. Established an R&amp;D center at the Institution level to promote Research &amp; Innovation among the faculty &amp; students. The center helps in developing co-operative and complimentary research among various Departments under BMSCE to explore advanced technologies. The Centre acts as the liaison between the University (VTU and Mangalore University) and the research centers at BMSCE. The Centre also guides and facilitates in writing of project proposals, and scientific papers leading to publication as well as in identifying the research outcomes of research for filing patents. Since academic autonomy, the Institution has provided with an excellent opportunity to create, revise, redesign or introduce innovations in the curriculum. Threading this path, the Institution foregrounded the concept of research amongst the students from the first year of their program. The Centralized labs and design centers titled propel labs were established for nurturing research from the first year of engineering. These labs are broad based and not confined to a single area/discipline. Student groups (multidisciplinary) work on various engineering projects in these labs - concept to designing the prototype. The Propel labs are open for students of all disciplines with no terms or conditions attached. Each Lab is headed by a faculty and supported by competent technical staffs who volunteer to act as mentors for the students and ensure that students conduct the research. Creative thinking skills of the students and mentoring by faculty guides result in the development creating systematic processes and products. These research labs help the students to build prototypes which enable them to participate in competitions both in India &amp; Abroad. IRINS Portal link: https://bmsce.irins.org/ Sl. No Research Center (Year of estb.) No. of Guides Ph.D Registered Ph.D Awarded M.Sc Awarded 1 Civil Engineering (2002) 24 64 33 14 2 Mechanical Engineering (2002) 34 34 34 2 3 Electrical and Electronics Engineering (2002) 15 27 13 0 4 Electronics and Communication Engineering (2002) 24 69 22 1 5 Industrial Engineering and Management (2002) 3 8 3 2 6 Chemical Engineering (2004) 5 4 4 1 7 Mathematics (2004) 11 18 5 0 8 MBA (2004) 8 25 19 0 9 Biotechnology (2009) 6 4 5 2 10 Computer Science and Engineering (2010) 13 34 20 0 11 Information Science and Engineering (2011) 9 22 6 0 12 Physics (2011) 6 7 4 0 13 Chemistry (2011) 8 10 7 0 14 Electronics &amp; Telecommunication Engineering (2013) 6 9 1 0 TOTAL 172 335 176 22</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59" t="str">
+        <v>2026-03-19T18:35:27.088Z</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>https://bmsce.ac.in/home/Innovative-Labs</v>
+      </c>
+      <c r="B60" t="str">
+        <v>html</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Innovative Labs PROPEL LAB – I (ROBOTICS AND EMBEDED SYSTEM LAB) Mr. Harish V Mekali hvm.ece@bmsce.ac.in Coordinator Mr. Girish K gk.mca@bmsce.ac.in Coordinator The lab provides a platform for students having interest in the field of Robotics and Embedded Systems. Major projects in the lab are related to the Machine Learning in Robotics space and Internet of Thing(IoT) in Embedded Systems. Through these projects students get to experience the depth of technologies. Students in here learn how to program a micro-controller, design a robot using many equipment’s which are at the disposal of propel lab. The students pass on the knowledge gained by working in the lab to their juniors by conducting workshops and competitions. Lab also facilitates academic and funded projects. Lab is supported by many industries and organizations like, ARM Ltd, Mediatek Labs, Nuetech Solar Systems Pvt. Ltd., ALS, and IIT – Bombay. At present we have 3 patents pending, 1 copyright, 7 international and 6 national publications. We have also received more than 10 awards from prestigious organizations like TCS, ARM, TI, IITB, and ONGC. We have youtube channel: Experiments@BMSCE. PROPEL LAB – II (3 D PRINTING) Arpitha KV Coordinator Background: In June 2014, our state-of-the-art 3D Printing Lab was inaugurated. The event was graced by esteemed figures including Dr. B. S. Ragini Narayan, Donor Trustee of BMSET, Dr. U. Chandrashekar, Former Additional Director at GTRE Bangalore, and Sri M. Krishnaswamy, Retired Project Director of ISRO, along with numerous dignitaries. Since its inception, the lab has supported over 400 projects, showcasing its versatility across various automotive, architecture, aerospace, and electrical &amp; electronics industries. During the COVID-19 pandemic, the lab leveraged IEEE grants to initiate six innovative projects to combat the virus, further exemplifying our commitment to technological advancement and societal contribution. As a cutting-edge technology known as Additive Manufacturing, 3D printing allows users to create and manufacture designs in three dimensions with minimal or no post-processing, revolutionizing traditional manufacturing practices. With only three decades of development, this technology holds immense potential for research and innovation, and there is a growing demand for trained engineers, operators, and designers in this field. The lab currently features a diverse array of 3D printers, including the Creality Ender3 V3 SE, Makerbot Replicator Z18, Adventure FlashForge 3, Wol3D I Maker, and X-Smart. These state-of-the-art machines enable students and researchers to explore a wide range of applications and push the boundaries of creativity in their projects. Facility: PROPEL LAB – III (AEROSPACE LAB) Sri.Ram Rohit V Coordinator Sri K. Satyanarayana Reddy Technical Staff The facility of Aerospace lab was inaugurated in the year 2012 by Dr.Roddam Narasimha and Wing Commander D P Sabarwal. Since, Aero BMSCE is participating in various National and International Aero Design competitions. Our Aim: To Create Awareness about the Exciting Fields of Aviation and aerospace. To encourage UG Students to take up R&amp;D, Innovation and Entrepreneurship. To provide the opportunity for students to use their learning to solve complex engineering challenges, through projects and competitions. What we do at Aero BMSCE: Aero BMSCE is a student team working on complex engineering challenges, such as designing aircrafts to perform according to required parameters such as reducing empty weight and maximizing weight of payload carried. We work on innovative projects to promote interdisciplinary research. We have completed many projects such as Project Kalam, Quadcopter Project, etc. We also participate in National and International Aero Design Competitions, which have different problems to be solved. Facility: Laser Machine (Cutting &amp; Engraving) 3Axis. CNC Milling Machine. Fat Shark Attitude SD Goggles with MIG v5 Head Tracking. Grupuner MZ-24 12 Channel Transmitter. Turnigy HD Wi-Fi Camera. Dremel 4000 machine. Stanley 53 Set tool box. Turnigy Thrust Measuring Stand. Two Sky surfer trainer planes. Apple Work station (Design, Analysis, and Report etc.). Bosch GLM 80 Laser Rangefinder. Air compressor for laser machine. Water chillier for laser machine. Oxygen cylinder for laser machine. Achievements of the Team Secured in the first prize(One lakh) overall (micro) in SAE India competition March 2020, Anna University, Chennai. Participated in Technoxian Quadcopter Challenge 22nd to 25th September 2019, New Delhi. Participated in SAE Indian Southern Section 2019, Anna University, Chennai. Overall 3rd rank, 2nd place in a design report, in SAE India Southern Section 2018, Anna University, Chennai. Secured 23rd rank in SAE Aero Design East 2018 held in Lake Land, Florida, USA. Best innovation in the micro class of Manovegam Aero Championship 2017 in SAE India held at SIT Tumkur. 17th place out of 30 teams in Boeing 2017 held at IIT Madras. Secured 14th rank in SAE Aero Design East 2016 held in California, USA. 2nd place in Boeing competition out of 174 teams across India. Secured 13th rank in SAE Aero Design West 2016 held in California, USA. Secured 14th rank in SAE Aero Design West 2015 held at Los Angeles, USA. Secured 15th rank in SAE Aero Design West 2014 held in Texas, USA. Secured 18th rank in SAE Aero Design West 2013 held at Los Angeles, USA. Best presentation at IITM Shaastra 2013. Secured 23rd rank in SAE Aero Design East 2012 held at Atlanta, USA. 1st place at NIT Trichy 2012. 1st place at NIT Warangal 2012. 1st place at IIT KGP Kshitij 2012 Laws of Motion. 3rd place at IITM Shaastra 2011 Wright Design. 1st place at IITM Shaastra 2011 Top Gun. PROPEL LAB - IV (SAE BULLZ RACING) Dr. Rathanraj K J Sri. RAJESH. P Bullz Racing founded in the year 2010, is the Automotive engineering division of BMS College of Engineering, Bangalore. We are an all-student collegiate club of SAEINDIA, strategic alliance partner of the Society of Automotive Engineers, or SAE International. We primarily intend to take the experience of engineering beyond four walls and into the real world. We are a team of young, hungry and eager students from various disciplines of engineering. Over the years, we have participated in various National Level engineering competitions and have carved a niche for ourselves. This is where ardour shall strive as we do what we’re best at: Innovation and Its Application. 2011: First Car – Best Design Award Baja SAE - Korea 2017: First Go-Kart: Top 20 out of 150 teamsat NKRC 2017 2015: First Electric Car – 7th Place Overall Mahindra Baja SAE 2015 2017: 3rd Place Overall Mahindra Baja SAE 2015 PROPEL LAB - V (BSNCSIS) Dr. Anil Chandra Sri. Sreenivas Murthy Dr. Rathan Raj K J</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60" t="str">
+        <v>2026-03-19T18:35:27.709Z</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>https://bmsce.ac.in/home/rankings</v>
+      </c>
+      <c r="B61" t="str">
+        <v>html</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Recent Rankings and Accreditations Status Rankings and Accreditations Status BMSCE has recently achieved the prestigious ISO 14001:2015 certification for its Environmental Management System through qualified external ISO 14001 auditors. . The UGC, New Delhi extended the autonomous status of the Institution for a period of 10 years from the session 2022-23 to 2031-32 : with a CGPA of 3.83 on a scale of four which is highest in the Country. The re-accreditation status is valid from 28.03.2019 to 28.03.2024. The College has the distinction of being awarded best performance rating in all three Phases of TEQIP The institution is a Beneficiary of Global Initiative Academic Network (GIAN). BMSCE is the only Partner institution in the country of the Melton Foundation, USA which promotes cross cultural learning for the selected students along with peers from five other countries. The College is accredited by National Assessment and Accreditation Council (NAAC) with the highest grade of A++ in the Second Cycle and a CGPA of 3.83 on a scale of four. Currently all the Undergraduate Programmes and post-Graduate Programmes hold the status of Accreditation from National Board of Accreditation (NBA), New Delhi in tier I Format. AICTE has recognized the college under AICTE Doctoral Fellowship Scheme (ADF) since 2018-19. BMSCE is listed as a lead innovator for the year 2020 and 2021 by Clarivate Analytics (Web of Science) based on the Derwent World Patent Index. In the ARIIA (ATAL Rankings) 2021, the college is ranked in band-Excellent. BMSCE has the distinction of being one of the 100 higher education institutions in the Country awarded 5G use Case Laboratory by Government of India. Accreditation Status of UG Programs SNo Program Level Accreditation Status From Validity 1 Civil Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 2 Mechanical Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2028 3 Electrical and Electronics Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 4 Industrial Engineering &amp; Management Under Graduate ACCREDITED 01/07/2022 30/06/2025 5 Computer Science and Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 6 Electronics and Telecommunication Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 7 Information Science &amp; Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 8 Electronics and Instrumentation Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2025 9 Medical Electronics Under Graduate ACCREDITED 01/07/2022 30/06/2025 10 Chemical Engineering Under Graduate ACCREDITED 01/07/2022 30/06/2028 11 Biotechnology Under Graduate ACCREDITED 01/07/2022 30/06/2028 12 Electronics &amp; Communication Engineering Under Graduate ACCREDITED 01/07/2023 30/06/2026 NBA Accreditation Status of PG Programs SNo Program Level Accreditation Status From Validity 1 Machine Design Post Graduate ACCREDITED 01/07/2018 30/06/2024 2 Masters in Computer Applications Post Graduate ACCREDITED 01/07/2019 30/06/2024 3 Masters of Business Administration Post Graduate ACCREDITED 01/07/2022 30/06/2025 4 VLSI &amp; Embedded Systems Post Graduate ACCREDITED 01/07/2022 30/06/2025 5 Construction Technology Post Graduate ACCREDITED 01/07/2023 30/06/2026 6 Computer Science and Engineering Post Graduate ACCREDITED 01/07/2023 30/06/2026 7 Power Electronics Post Graduate ACCREDITED 01/07/2023 30/06/2026 8 Transportation Engineering and Management Post Graduate ACCREDITED 01/07/2023 30/06/2026 9 Computer Networking &amp; Engineering Post Graduate ACCREDITED 01/07/2023 30/06/2026 10 Digital Communications Post Graduate ACCREDITED 01/01/2024 30/06/2027 11 Electronics Post Graduate ACCREDITED 01/01/2024 30/06/2027</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61" t="str">
+        <v>2026-03-19T18:35:28.325Z</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>https://www.bmsce.ac.in</v>
+      </c>
+      <c r="B62" t="str">
+        <v>html</v>
+      </c>
+      <c r="C62" t="str">
+        <v>View Document Seva Sindu Link Documents Required Know More ! News &amp; Events 09 Mar DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” read more 16 Feb Illuminating the Future: A Comprehensive Workshop on Indian Standards, Codes and Regulations in Lighting read more 05 Feb Sri S Nijalingappa Scholarship 2025-26 read more 14 Nov NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru on 14th and 15th November 2025 read more 19 Sep Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 read more View All Notifications COE Notifications Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25/03/2026. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), 2. Department of Machine Learning (AI &amp; ML), 3. MCA 4. Department of Mechanical Engineering 5. Department of Electronics &amp; Communication Engineering Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10th January 2026. Please refer to the advertisement for more details. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/12/2025. Teaching Application General Condition B.S. Narayan Doctoral Fellowship 2025-26. Last date for receipt of filled-in application form is 31st December 2025 link Admissions are Open for Management Quota seats for First Year PG Courses (M.Tech, MBA &amp; MCA) for 2025-26 at B. M. S. College of Engineering. Kindly contact the undersigned on or before 13th November 2025. Sd/- Principal Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10/11/2025. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Mathematics. Note: PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/10/2025 Teaching Application General Condition Application for Change Of Branch(COB) Circular for the Academic Year 2025-26 Download Circular for payment of Tuition and Miscellaneous Fee for 2nd Semester (MTech, MCA and MBA) for AY-2025-26 Download Circular for Fee Structure for 2nd Year B.E admitted through CET, COMEDK and Management Quota for AY-2025-26 Download View All Time Table for IV Semester Makeup Examination MBA- Mar-2026. read more Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. III Semester End Examinations conducted during Jan/Feb-26. read more Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. I, III Semesters and Reappear Semester UG Semester End Examinations conducted during Jan/Feb-26. read more Notification for Answer Scripts of I &amp; III Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure as per the attached schedule. read more Circular for makeup registration for I and III Semester March -2026 read more Addtional Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester MBA (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for I Semester M.Tech (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester Makeup Examination - Mar-2026. read more View All Late Sri. B.M.Sreenivasaiah Founder B.M.S. Educational Trust Late Sri. B.S.Narayan Donor Trustee B.M.S. Educational Trust The Visionaries B.M.S. College of Engineering (BMSCE) was Founded in the year 1946 by Late Sri. B. M. Sreenivasaiah a great visionary and philanthropist and nurtured by his illustrious son Late Sri. B. S. Narayan. BMSCE is the first private sector initiative in engineering education in India. BMSCE has completed 70+ years of dedicated service in the field of Engineering Education. Started with only 03 undergraduate courses, BMSCE today offers 13 Undergraduate &amp; 16 Postgraduate courses both in conventional and emerging areas. Know More Dr. Bheemsha Arya Principal, B.M.S.C.E A nation’s real and sustainable growth is possible with technological advancement as well as development of its human resource and the role of engineers is immensely pertinent. With globalization, engineers should be able to perform in a larger environment and are expected to face challenges &amp; find solutions in any given situation. The key to meet the demand for such quality engineers remains in providing holistic engineering education. Over the last 75 years, B.M.S.C.E has been offering best engineering programmes and is benchmarked with the leading educational institutions in the Country. Ever since its inception, B.M.S.C.E has focused on augmenting human resource by producing world-class engineers. Today, BMS Alumni occupy coveted positions in reputed organizations both in India and abroad. They have acted as the ambassadors of change. Magnanimous and committed College management has been regularly augmenting the academic/para-academic facilities at the college to suite the present day requirements. A cozy and well maintained campus provides good academic ambience. Well qualified &amp; experienced faculty and committed staff of the college are eager to provide effective education to students. In addition to gaining academic knowledge and skills, opportunities are many for the students to groom and develop further. View Profile B.M.S. College of Engineering BMSCE Alumni can be found all over the world. BMSCE takes proud in educating students since 1946 in various fields of Engineering and continues to provide world class education in the coming years with more emphasis on research and development. Values View More Research View More Placements View More Library View More Innovative Labs View More Accreditations and Rankings B.M.S. College of Engineering is determined to impart quality education to students and provide industry ready engineers for the country. To make this possible the college participates in several audits internally and externally for quality assurance with quality assurance committees and university committees from AICTE, VTU, NBA and NAAC. Know More Rankings / Surveys A++ in NAAC Third Cycle 83rd NIRF-2022 Ranking 8th among top 140 Eng8ineering in The Times Engineering Institute 2019 Survey 1st among top 50 Institutes on Placements in The Times Engineering Institute 2019</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62" t="str">
+        <v>2026-03-19T18:35:29.091Z</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>http://www.bmsce.ac.in</v>
+      </c>
+      <c r="B63" t="str">
+        <v>html</v>
+      </c>
+      <c r="C63" t="str">
+        <v>View Document Seva Sindu Link Documents Required Know More ! News &amp; Events 09 Mar DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” read more 16 Feb Illuminating the Future: A Comprehensive Workshop on Indian Standards, Codes and Regulations in Lighting read more 05 Feb Sri S Nijalingappa Scholarship 2025-26 read more 14 Nov NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru on 14th and 15th November 2025 read more 19 Sep Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 read more View All Notifications COE Notifications Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 25/03/2026. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in 1. Departments of Computer Science &amp; Engineering (CSE), 2. Department of Machine Learning (AI &amp; ML), 3. MCA 4. Department of Mechanical Engineering 5. Department of Electronics &amp; Communication Engineering Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10th January 2026. Please refer to the advertisement for more details. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/12/2025. Teaching Application General Condition B.S. Narayan Doctoral Fellowship 2025-26. Last date for receipt of filled-in application form is 31st December 2025 link Admissions are Open for Management Quota seats for First Year PG Courses (M.Tech, MBA &amp; MCA) for 2025-26 at B. M. S. College of Engineering. Kindly contact the undersigned on or before 13th November 2025. Sd/- Principal Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Computer Science &amp; Engineering (CSE), Machine Learning (AI &amp; ML), Artificial Intelligence &amp; Data Science (AI &amp; DS), Computer Science &amp; Engineering (Data Science), Computer Science &amp; Engineering (IoT &amp; Cyber Security including Blockchain Technology), Computer Science &amp; Business Systems. Note: 7th PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 10/11/2025. Teaching Application General Condition Notification for Faculty Recruitment under Management Cadre for the post of Assistant Professor in Departments of Mathematics. Note: PAY SCALE AS PER MANAGEMENT NORMS. The duly filled-in applications along with the required enclosures should reach the Principal on or before 15/10/2025 Teaching Application General Condition Application for Change Of Branch(COB) Circular for the Academic Year 2025-26 Download Circular for payment of Tuition and Miscellaneous Fee for 2nd Semester (MTech, MCA and MBA) for AY-2025-26 Download Circular for Fee Structure for 2nd Year B.E admitted through CET, COMEDK and Management Quota for AY-2025-26 Download View All Time Table for IV Semester Makeup Examination MBA- Mar-2026. read more Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. III Semester End Examinations conducted during Jan/Feb-26. read more Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. I, III Semesters and Reappear Semester UG Semester End Examinations conducted during Jan/Feb-26. read more Notification for Answer Scripts of I &amp; III Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure as per the attached schedule. read more Circular for makeup registration for I and III Semester March -2026 read more Addtional Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester MBA (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for I Semester M.Tech (Re-Appear) theory Semester End Examination March- 2026. read more Time Table for III Semester Makeup Examination - Mar-2026. read more Time Table for I Semester Makeup Examination - Mar-2026. read more View All Late Sri. B.M.Sreenivasaiah Founder B.M.S. Educational Trust Late Sri. B.S.Narayan Donor Trustee B.M.S. Educational Trust The Visionaries B.M.S. College of Engineering (BMSCE) was Founded in the year 1946 by Late Sri. B. M. Sreenivasaiah a great visionary and philanthropist and nurtured by his illustrious son Late Sri. B. S. Narayan. BMSCE is the first private sector initiative in engineering education in India. BMSCE has completed 70+ years of dedicated service in the field of Engineering Education. Started with only 03 undergraduate courses, BMSCE today offers 13 Undergraduate &amp; 16 Postgraduate courses both in conventional and emerging areas. Know More Dr. Bheemsha Arya Principal, B.M.S.C.E A nation’s real and sustainable growth is possible with technological advancement as well as development of its human resource and the role of engineers is immensely pertinent. With globalization, engineers should be able to perform in a larger environment and are expected to face challenges &amp; find solutions in any given situation. The key to meet the demand for such quality engineers remains in providing holistic engineering education. Over the last 75 years, B.M.S.C.E has been offering best engineering programmes and is benchmarked with the leading educational institutions in the Country. Ever since its inception, B.M.S.C.E has focused on augmenting human resource by producing world-class engineers. Today, BMS Alumni occupy coveted positions in reputed organizations both in India and abroad. They have acted as the ambassadors of change. Magnanimous and committed College management has been regularly augmenting the academic/para-academic facilities at the college to suite the present day requirements. A cozy and well maintained campus provides good academic ambience. Well qualified &amp; experienced faculty and committed staff of the college are eager to provide effective education to students. In addition to gaining academic knowledge and skills, opportunities are many for the students to groom and develop further. View Profile B.M.S. College of Engineering BMSCE Alumni can be found all over the world. BMSCE takes proud in educating students since 1946 in various fields of Engineering and continues to provide world class education in the coming years with more emphasis on research and development. Values View More Research View More Placements View More Library View More Innovative Labs View More Accreditations and Rankings B.M.S. College of Engineering is determined to impart quality education to students and provide industry ready engineers for the country. To make this possible the college participates in several audits internally and externally for quality assurance with quality assurance committees and university committees from AICTE, VTU, NBA and NAAC. Know More Rankings / Surveys A++ in NAAC Third Cycle 83rd NIRF-2022 Ranking 8th among top 140 Eng8ineering in The Times Engineering Institute 2019 Survey 1st among top 50 Institutes on Placements in The Times Engineering Institute 2019</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63" t="str">
+        <v>2026-03-19T18:35:29.871Z</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>https://www.bmsce.ac.in/assets/files/NewsEvents/DST%20FIST%20FDP.pdf</v>
+      </c>
+      <c r="B64" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C64" t="str">
+        <v>B. M. S. College of Engineering (An Autonomous Institution Affiliated to VTU) DST - FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” Date: 09/03/2026 to 13/03/2026 Organized by Department of Electrical and Electronics Engineering in Association with Department of Physics and Department of Chemistry APPLICATION FORM Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” DATE: 09/03/2026 to 13/03/2026 1. Name: 2. Educational qualification: 3. Designation: 4. Institution: 5. Address for communication:…………………………… ………………………………………………………..……… ……………………………………………………................. 6. Mobile: 7. Email: 8. Accommodation Required: Yes/No (Accommodation will be provided on a chargeable basis and is on a first - come, first - served basis) Please register online using the following link or QR code Registration Link: https ://forms.gle/La8xb7wqWYyk6xwk8 Chief Patrons Dr. B S Ragini Narayan Donor Trustee - B.M.S.E.T Dr. P Dayananda Pai Chairman, BMSCE, Life Trustee - B.M.S.E.T Sri. Aviram Sharma Trustee - B.M.S.E.T Dr. Tirumalachari Ramasami Trustee - B.M.S.E.T Smt. N. Manjushree, I.A.S Trustee - B.M.S.E.T Patrons Dr. Bheemsha Arya Principal, BMSCE Dr. L. Ravikumar Vice - Principal (Academic), BMSCE Dr. Seshachalam D Vice - Principal (Admin), BMSCE Conveners Dr . Chandasree Das, Department of EEE Dr . Latha Kumari, Department of Physics Dr . Nagashree K . L, Department of Chemistry Dr . Srinidhi Raghavan, Department of Chemistry Co - ordinators : Dr. Venkata Madhava Ram Tatabhatla , Department of EEE Email: madhavaram.eee@bmsce.ac.in, +91 - 7893222486 Dr. H. S. Sumantha , Department of Physics Phone: +91 - 7353815841 Dr. Sagar K. S., Department of Chemistry Phone: +91 - 9740605944 https://forms.gle/La8xb7wqWYyk6xwk8 B . M . S . College of Engineering (BMSCE) was founded by a great visionary and philanthropist Late Sri . B . M . Sreenivasaiah (B . M . S) in the year 1946 . The College became an autonomous institution under Visvesvaraya Technological University (VTU) in the year 2008 - 09 . B . M . S . C . E offers 17 UG, 15 PG &amp; 14 Research programs . BMSCE is accredited with A++ Grade by NAAC and by National Board of Accreditation (NBA), New Delhi, under Tier - I NBA Accreditation Washington accord . The institution is consistently ranked among India's top engineering colleges, and Technical Education Quality Improvement Programme (TEQIP) Institute since 2006 . The Government of India is making significant strategic investments in emerging and transformative technologies through national initiatives such as the Semiconductor Mission, Quantum Mission, Artificial Intelligence (AI) development, and Next - Generation Computing . In this context, micro and nano characterization techniques play a vital role in enabling cutting - edge research in nanotechnology, advanced materials, energy systems, electronics, and quantum devices . Recognising this importance, premier funding agencies such as DST, ANRF, and AICTE are actively encouraging capacity - building programs, workshops, and faculty development initiatives in this domain . This Faculty Development Program (FDP) is a blend of theory, practical exposure, and industry interaction and aims to equip faculty members and researchers with the necessary skills to contribute effectively to advanced materials research, align with national technology missions, and enhance the quality of research publications, funded projects, and interdisciplinary collaborations . About the Institution About FDP On 09/03/2026 10:00 AM – 11:30 AM: Registration &amp; Inauguration 11:30 AM - 11:45 AM: Tea break 11:45 AM – 1:15 PM: Session 1:15 PM – 2:15 PM: Lunch 2:15 PM – 4:15 PM: Hands - on Training From 10/03/2026 to 13/03/2026 10: 00 AM – 11:30 AM: Session 11:30 AM - 11:45 AM: Tea break 11:45 AM - 1.15 PM: Session 1:15 PM – 2:15 PM: Lunch 2:15 PM – 4:15 PM: Hands - on Training Industrial visit will be arranged on 12 th March, 2026 Schedule of the FDP Resource persons The resource persons are eminent Academicians/Researchers/Professionals with in - depth knowledge of research in multidisciplinary areas . The program will provide comprehensive exposure to : • Fundamental principles of material characterization . • Selection and application of appropriate techniques for specific research problems . • Industry - relevant characterization practices and standards • Practical insights into modern micro and nano characterization techniques relevant to advanced materials research . The FDP includes extensive hands - on laboratory sessions, enabling participants to gain practical experience with widely used characterization tools such as Stylus Profiler, Particle Size Analyzer, X - Ray Diffraction (XRD), Scanning Electron Microscope (SEM) and Electrochemical Workstation FDP Objectives Who can attend ? The FDP on Micro and Nano Characterization for Advanced Materials Research is open to faculty members from engineering and science disciplines, research scholars (Ph . D . /M . S . ), postdoctoral researchers, scientists, and industry professionals working in materials, nanotechnology, electronics, energy, physics, or chemistry . Registration Link How to Apply? Interested participants should register by filling out the Registration Link (Google Form) on or before 22 nd February 2026 . A nominal registration fee of ₹ 500 is to be paid during the registration process to confirm participation .</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" t="str">
+        <v>2026-03-19T18:35:30.507Z</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>https://www.bmsce.ac.in/assets/files/NewsEvents/Flyer-ELCOMA_National%20Program%20on%20Indian%20Standards,%20Codes%20and%20Regulations%20in%20Lighting_Brochure-final%20(1).pdf</v>
+      </c>
+      <c r="B65" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Illuminating the Future: A Comprehensive Workshop on Indian Standards on Lighting and Regulations - Date: 8th January 2026, Netaji Subhas University of Technology (NSUT) (Room No. 8A-206) Azad Hind Fauj Marg, Sector - 3, Dwarka, New Delhi – 110078 - Date: 30th January 2026, Veermata Jijabai Technological Institute (V.J.T.I.) 2VC4+VCQ, H R Mahajani Rd, Matunga East, Mumbai, Maharashtra 400019 - Date: 27th March 2026, Sri Sai Ram Engineering College Sai Leo Nagar, West Tambaram, Chennai – 600 044, Tamil Nadu, India. - 16th February 2026 BMS College of Engineering, Bull Temple Rd, Basavanagudi, Bengaluru, Karnataka 560004 - 09th March 2026 Jadavpur University , 188, Raja Subodh Chandra Mallick Rd, Jadavpur, Kolkata, West Bengal 700032 Sponsors:</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65" t="str">
+        <v>2026-03-19T18:35:31.536Z</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>https://www.bmsce.ac.in/assets/files/NewsEvents/Draft%20agenda-%20BIS%20ELCOMA%20Joint%20session-%2016th%20Feb%202026%20at%20Bangalore.pdf</v>
+      </c>
+      <c r="B66" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Draft Agenda- Bangalore Program on 16 th February 2026 at Auditorium 1, Ground Floor, Platinum Jubilee Academic Block, B.M.S. College of Engineering, Bull Temple Road, Basavanagudi, Bengaluru, Karnataka 560019 Illuminating the Future: A Comprehensive Workshop on “National Program on Indian Standards, Codes and Regulations in Lighting’’ 9.00 – 10.00 REGISTRATION &amp; TEA 10:00 – 10:30 AM INAUGURAL SESSION Welcome Address Head-BMS Collage Purpose and Context Shri Asit Kuma Maharana, HETD, BIS Keynote Address TBD-Wipro Inaugural Address TBD Vote of Thanks Shri Amal Sengupta, ELCOMA 10:30 AM – 1:30 PM National Lighting Code of India, SP 72: 2025 And Regulatory Landscape 10:30 AM – 11:15 AM Understanding the National Lighting Code (NLC) - Ms. Neha Agarwal, BIS  Evolution and Purpose of NLC  Structure and key chapters 11:15 AM -11.20 AM Q&amp;A 11:20 AM – 12:05 PM Foundation of NLC indoor lighting application chapters - Ms. Sudeshna Mukhopadhyay, Havells  IS 3646 Indoor Lighting application standard 12:05 PM – 12:10 PM Q&amp;A 12:10 AM – 12:55 PM Foundation of NLC outdoor lighting application chapters- Mr. Nitish Poonia, Signify IS 1944 Outdoor Lighting application standard 12:55 PM – 01:00 PM Q&amp;A 1:00 PM- 2:00 PM Regulatory Landscape  Understanding the BIS Compulsory Registration Scheme (CRS) for lighting products: scope, process, and compliance- BIS Registration Team  BEE Star Labeling Scheme for lighting products- Mr. Nitish Poonia, Signify  Overview of relevant environmental regulations (RoHS, E-waste)- Mr. Nitish Poonia, Signify  Impact of these regulations on product design, manufacturing, and market.- Mr. Nitish Poonia, Signify 2:00 PM- 2:05 PM Q&amp;A 2:05 PM – 2:40 PM NETWORKING LUNCH 2:40 PM- 3:25 PM LED Lamp – Safety &amp; Performance LED Module - Mr. Santosh Agnihotri, Orien t  Detailed review of safety and performance standards.  Constructional Requirements.  Key changes and updates in the latest revisions.  Implication for manufacturers and quality assurance 3:25 PM- 3:30 PM Q&amp;A 3:30 PM- 4:20 PM Driver Standards- Mr. Soumo Ghosal, Havells  Deep dive into safety and performance standards for luminaires and drivers  Key changes and updates in the latest revisions.  Implications for manufacturers and quality assurance. 3:30 PM- 4:20 PM Q&amp;A 4:20 PM – 5:25 PM LED Luminaire Standards - Mr. Pankaj Mittal, Havells  Deep dive into safety and performance standards for luminaires  Key changes and updates in the latest revisions.  Implications for manufacturers and quality assurance. 5:25 PM- 5: 30 PM Q&amp;A 5:30 PM- 5:35 PM CLOSING REMARKS &amp; VOTE OF THANKS</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66" t="str">
+        <v>2026-03-19T18:35:32.146Z</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>https://www.bmsce.ac.in/assets/files/NewsEvents/brochure_%20News%20June%202025%20v13.pdf</v>
+      </c>
+      <c r="B67" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C67" t="str">
+        <v>About B.M.S. College of Engineering The B.M.S. College of Engineering (BMSCE) was founded by a great visionary and philanthropist Late Sri. B. M. Sreenivasaiah (BMS) in the year 1946. After demise of the founder, Sri. B. S. Narayan the illustrious son of the Founder took over the reins of the College. Under his able leadership, the college grew from strength to strength. BMSCE is the first engineering college established in the country (pre independent India) by a private enterprise. The col- lege is an aided institution (by Government of Kar- nataka) and affiliated to Visvesvaraya Technological University (VTU). BMSCE offers 13 UG, 12 PG &amp; 15 Research programmes. BMSCE is proud to be the First and only Engineering Institute in Karnataka ac- credited with the Highest Grade in three consecutive cycles of NAAC accreditation. The College became an autonomous insti- tution under VTU in the year 2008-09. In the year 2011, BMSCE was recognized as a QIP Centre in En- gineering &amp; Technology by All India Council for Technical Education (AICTE). BMSCE is the only part- ner institution from India along with the other uni- versities located in Chile, China, Germany and USA for the Melton Foundation, USA. . The college has a strong alumni base. About the Department of ECE The Department of Electronics and Communication Engineering (ECE) of BMSCE was established in 1971 with an initial intake of 60 students to the Under Graduate (UG) program and is enhanced to an in- take of 420 students currently. The department of- fers three PG programs: Electronics (since 1986), Digital Communication Engineering (since 1996) and VLSI Design &amp; Embedded Systems (since 2014). The department is also a recognized Research Centre (RC) by VTU from 2002 and is a recognized Quality Improvement Program (QIP) center by the AICTE from 2011. Department is accredited by NBA (Washington accord) for 3 years under TIER-1 (cycle -2) from 2023-2026. Important Dates Submission Guidelines Visit website https://bmsce.ac.in/news2025/ for submission guidelines. Registration Details • Certificates will be issued for registered participants only Category Offline Mode (In - Person) Online Mode (Virtual) Student -UG/PG/ Research Scholars ₹ 900 ₹ 750 Faculty/Industry Persons ₹ 1000 ₹ 750 About NEWS 2025 The sixth edition of NEWS 2025 invites papers/ Project on diverse topics, including the next gener- ation of wireless communication like 5G/6G, smart embedded systems, and cutting-edge applications in healthcare, industrial automation, and smart grids. Discussions will cover everything from secure blockchain networks and advanced VLSI design to novel quantum technologies and practical testbed deployments. This conference offers a vital plat- form for sharing groundbreaking ideas and foster- ing collaborations in these rapidly evolving fields. Call for papers/prototypes • Sustainable Models and Systems for Next- Generation Wireless Communication and RF Engi- neering • Vehicle-to-Everything (V2X) Communication • Modeling, Simulation of Communication Net- works • Intelligent Embedded Systems and Edge AI • Biomedical Signal Processing and Smart Healthcare Devices • Digital Signal Processing &amp; Image Processing • Cyber-Physical Systems, Industrial Automation • Smart Grids, Power Electronics, Renewable Energy • Advanced Instrumentation, Measurement, Control Systems • Quantum Technologies • VLSI Design, Flexible Electronics, Emerging Mate- rials for a Sustainable Future • Network Security, Blockchain Technologies • Photonics, Optoelectronics, Optical Networking • Testbeds, Prototypes, Experimental Deployments • Other allied areas towards Sustainable Eco system Paper/Project Submission Opens 5 Aug. 2025 Last Date for Paper Submission 8 Nov. 2025 Acceptance Notification 10 Nov. 2025 Registrations for Authors / 11-12 Nov. 2025 Camera-Ready Paper (Revised Submissions) 12 Nov. 2025 Final Presentation Schedule 13 Nov. 2025 Conference events-Hackathon, Workshops 13-16 Nov. 2025 B. M. S. College of Engineering , (Autonomous College under VTU) Bengaluru - 19 Advisory Board Dr. Sai Siva Gorthi, General Secretary, ISoI Dr. Mukartihal. G.B., Joint Secretary, ISoI Dr. Srinivas Talabattula , Professor, IISc. Dr. Vishal Kumar , Professor, IIT Roorkee Dr. Yogesh Vijay Hote , Professor, IIT Roorkee Dr. S. Venkatesh , Professor, IIT Kanpur Dr. Vivek Natarajan , Assoc. Professor, IIT Bombay Dr. Shiban Koul , Adjunct Professor, IIT Delhi Dr. Vijay Prakash A. M. , Professor, ECE, BIT Mr. H. D. Ananda , Former Director, SPROC Mr. Chandrashekhar B. U., Senior Architect, Synopsys Inc. Mr. Somashekhar , Co - Founder &amp; Technical Director, SM Electronic Technologies Pvt. Ltd. Dr. Jayesh Barve , Principal - Digital, Controls &amp; Optimization, GE Vernova Dr. Ramesh G. , GC Member, IETE Registration Committee Mrs. Sowmya Sunkara , Asst. Prof., ECE, BMSCE Mrs. Pooja A. P ., Asst. Prof., ECE, BMSCE Dr. Shivkumar M., Asst. Prof., ECE, BMSCE Mrs. Geeta , Asst. Prof., ECE , BMSCE Hospitality Coordinator Prof. Harish V. Mekali , Asst. Prof., ECE, BMSCE Mrs. K. Poornima Kamath , Asst. Prof., ECE, BMSCE Website cordinator Mr. Suprith Kumar K. S., Asst. Prof., ECE, BMSCE Mr. Syed Akram, Asst. Prof., CSE, BMSCE Mr. Darshan , Student, ECE 6 th National Conference on Networking Embedded and Wireless Systems (NEWS 2025) Driving Sustainable Innovation Hybrid mode (14-15 November 2025) Organized by Department of Electronics &amp; Communication Engineering Shri Chief Patrons Dr. B. S. Ragini Narayan, Donor Trustee Dr. Dayanand Pai, Chairman, BMSCE Patrons Dr. Bheemsha Arya, Principal, BMSCE Advisors Dr. L. Ravikumar, Vice - Principal(Aca), BMSCE Dr. Seshachalam D, Vice - Principal(Admin), BMSCE Conference Chair Dr. K. P. Lakshmi, Prof. &amp; Head, ECE, BMSCE Conveners Dr. Santosh R. Desai, Professor, ECE, BMSCE (M: 8618242724, santoshdesai.intn@bmsce.ac.in) Dr. Surendra H.H., Assoc. Prof., ECE, BMSCE (M: 9449859023, surendrahh.ece@bmsce.ac.in) Technical Program Committee Dr. Karthikeya G. S. , Asst. Prof., ECE, BMSCE Dr. Archana H. R. , Asst. Prof., ECE, BMSCE Publication and Marketing Committee Dr. Lalitha S., Assoc. Prof., ECE, BMSCE Dr. Madhusudhan K. N., Assoc. Prof., ECE, BMSCE Mrs. Priyadarshini Jainapur , Asst. Prof., BMSCE Finance Committee Prof. Radha R. C ., Asst. Prof., ECE, BMSCE Prof. Eesha D ., Asst. Prof., ECE, BMSCE Prof. Ashwini , Asst. Prof., ECE, BMSCE</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67" t="str">
+        <v>2026-03-19T18:35:32.918Z</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>https://bmsce.ac.in/home/news/1/dst-fist-sponsored-one-week-faculty-development-program-on-micro-and-nano-characterization-for-advanced-materials-research-1</v>
+      </c>
+      <c r="B68" t="str">
+        <v>html</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Home 09 Mar DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” DST-FIST Sponsored One Week Faculty Development Program on “Micro and Nano Characterization for Advanced Materials Research” Date: 09/03/2026 to 13/03/2026 Organized by Department of Electrical and Electronics Engineering in Association with Department of Physics and Department of Chemistry Click here to View Broucher Back to All News</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" t="str">
+        <v>2026-03-19T18:35:33.903Z</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>https://bmsce.ac.in/home/news/1/illuminating-the-future-a-comprehensive-workshop-on-indian-standards-codes-and-regulations-in-lighting-1</v>
+      </c>
+      <c r="B69" t="str">
+        <v>html</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Home 16 Feb Illuminating the Future: A Comprehensive Workshop on Indian Standards, Codes and Regulations in Lighting The Bureau of Indian Standards (BIS), the National Standards Body of India under the Ministry of Consumer Affairs, Food &amp; Public Distribution, is organizing a National Program on Indian Standards, Codes and Regulations in Lighting (Bengaluru Edition) in collaboration with the Electric Lamp and Component Manufacturers Association (ELCOMA) and B.M.S. College of Engineering, Bengaluru and BMSCE IEEE PES and sensors council. Venue: B.M.S. College of Engineering. Bull Temple Road, Basavanagudi, Bengaluru, Karnataka 560019 The registration link for Bangalore session is : https://www.elcomaindia.com/?page_id=4746 Click here to View Broucher Click here to View Agenda Back to All News</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69" t="str">
+        <v>2026-03-19T18:35:34.517Z</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>https://bmsce.ac.in/home/news/1/sri-s-nijalingappa-scholarship-2025-26</v>
+      </c>
+      <c r="B70" t="str">
+        <v>html</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Home 05 Feb Sri S Nijalingappa Scholarship 2025-26 Sri S Nijalingappa Scholarship 2025-26 CLICK HERE TO VIEW MORE DETAILS Back to All News</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70" t="str">
+        <v>2026-03-19T18:35:35.115Z</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>https://bmsce.ac.in/home/news/1/networking-embedded-and-wireless-systemsnews-2025-national-conference-organised-by-the-department-of-electronics-and-communication-engineering-bms-college-of-engineering-bengaluru-on-14th-and-15th-november-2025</v>
+      </c>
+      <c r="B71" t="str">
+        <v>html</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Home 14 Nov NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru on 14th and 15th November 2025 NETWORKING EMBEDDED AND WIRELESS SYSTEMS(NEWS) 2025 NATIONAL CONFERENCE organised by the Department of Electronics and Communication Engineering, B.M.S. College of Engineering, Bengaluru, on 14th and 15th November 2025 CLICK HERE TO VIEW WORKSHOP DETAILS CLICK HERE TO VIEW BROCHURE Back to All News</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2026-03-19T18:35:35.740Z</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>https://bmsce.ac.in/home/news/1/phase-shift-2025-meridian-on-19th-and-20th-september-1</v>
+      </c>
+      <c r="B72" t="str">
+        <v>html</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Home 19 Sep Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 Phase Shift 2025 MERIDIAN on 19th and 20th September 2025 Click here to view the Phase Shift 2025 brochure Back to All News</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2026-03-19T18:35:36.361Z</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>https://bmsce.ac.in/home/news/1/induction-and-inauguration-for-the-2025-batch-of-students-event-is-on-september-8th-2025</v>
+      </c>
+      <c r="B73" t="str">
+        <v>html</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Home 08 Sep Induction and Inauguration for the 2025 Batch of Students Event is on September 8th 2025 Induction and Inauguration for the 2025 Batch of Students Event: September 8th, 2025. Click here to view the Induction Program Schedule Click here for Inauguration Invitation Details Back to All News</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73" t="str">
+        <v>2026-03-19T18:35:36.974Z</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>https://bmsce.ac.in/home/news/1/graduation-day-iiawarding-degree-certifcates-to-the-autonomous-batch-ug-pg-graduates-of-2024-on-saturday-05th-april-2025-at-430-pm</v>
+      </c>
+      <c r="B74" t="str">
+        <v>html</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Home 05 Apr Graduation Day - IIAwarding Degree Certifcates to the Autonomous Batch UG &amp; PG Graduates of 2024 on Saturday, 05th April 2025 at 4.30 PM Toppers List for UG &amp; PG Graduates of 2024 Click here to view Graduation Day Invitation for 5th April 2025 Click here to view General Instructions for Graduation Day 5th April 2025 Click here to view Back to All News</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74" t="str">
+        <v>2026-03-19T18:35:37.617Z</v>
+      </c>
+      <c r="F74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>https://bmsce.ac.in/home/news/1/reg-blood-donation-drive-1</v>
+      </c>
+      <c r="B75" t="str">
+        <v>html</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Home 21 Mar Reg-Blood Donation Drive Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75" t="str">
+        <v>2026-03-19T18:35:38.231Z</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>https://bmsce.ac.in/home/news/1/ip-awareness-talk-on-12th-march-2025</v>
+      </c>
+      <c r="B76" t="str">
+        <v>html</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Home 05 Mar IP awareness talk on 12th March 2025 Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76" t="str">
+        <v>2026-03-19T18:35:38.851Z</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>https://bmsce.ac.in/home/news/1/grand-challenge-impact-lab-gcil-with-university-of-washington-sessions</v>
+      </c>
+      <c r="B77" t="str">
+        <v>html</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Home 01 Feb Grand challenge impact Lab (GCIL) with university of Washington : Sessions "Department of Civil Engineering and Department of Chemical Engg are conducting 12 weeks GCIL sessions ( Grand challenge impact Lab ) for students of UOW( University of Washington) and Students of BMSCE from 3 rd January 2025. Students from UOW visit BMSCE to takepart in GCIL to address challenges in Bangalore through design thinking, interactive sessions, project work, field visit and presentations. Link: www.gcil.uw.edu/ " Back to All News</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77" t="str">
+        <v>2026-03-19T18:35:39.486Z</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>https://bmsce.ac.in/home/news/1/udyamotsav-2025-on-thursday-16th-january-2025-at-9-am-in-auditorium-i-pj-block-bmsce</v>
+      </c>
+      <c r="B78" t="str">
+        <v>html</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Home 16 Jan UDYAMOTSAV 2025 - On Thursday 16th January 2025 at 9 AM in Auditorium I, PJ Block, BMSCE Click here to view the brochure Back to All News</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78" t="str">
+        <v>2026-03-19T18:35:40.089Z</v>
+      </c>
+      <c r="F78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>https://bmsce.ac.in/home/news/1/11th-annual-alumni-day-2024-on-saturday-21st-december-2024</v>
+      </c>
+      <c r="B79" t="str">
+        <v>html</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Home 17 Dec 11th Annual Alumni Day -2024 on Saturday, 21st December, 2024. 11th Annual Alumni Day -2024 on Saturday, 21st December, 2024. Click here to view the invitation. Back to All News</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79" t="str">
+        <v>2026-03-19T18:35:40.731Z</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>https://bmsce.ac.in/home/news/1/bms-college-of-engineering-and-bms-college-of-architecture-cordially-invites-you-to-inauguration-function-of-first-year-be-barch-for-the-academic-year-2024-25-on-friday-20th-september-2024</v>
+      </c>
+      <c r="B80" t="str">
+        <v>html</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Home 17 Sep B.M.S. College of Engineering and B.M.S. College of Architecture Cordially invites you to "Inauguration Function of First Year B.E., &amp; B.Arch for the Academic year 2024-25 on Friday 20th September 2024. B.M.S. College of Engineering and B.M.S. College of Architecture Cordially invites you to "Inauguration Function of First Year B.E., &amp; B.Arch for the Academic year 2024-25 on Friday 20th September 2024. Click here to view the Invitation Please Note: 1. Students need to report to the Registration Desk [Registration Time: 9.30 AM] on arrival. 2. The inauguration function will be followed by Lunch. 3. Commencement of Induction Programme: 23-09-2024 to 02.10.2024. 4. One family member is allowed to accompany the student (due to space constraints) Back to All News</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80" t="str">
+        <v>2026-03-19T18:35:41.351Z</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-civil-engineering-is-organising-a-one-week-hands-on-faculty-development-programme-on-bim-application-in-civil-engineering-and-construction-29-7-2024-to-2-8-2024</v>
+      </c>
+      <c r="B81" t="str">
+        <v>html</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Home 30 Jul Department of Civil Engineering is organising a One Week Hands-On Faculty Development Programme on “BIM Application in Civil Engineering and Construction” 29-7-2024 to 2-8-2024 Department of Civil Engineering is organising a One Week Hands-On Faculty Development Programme on “BIM Application in Civil Engineering and Construction” 29-7-2024 to 2-8-2024 Click here to view the brochure Back to All News</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81" t="str">
+        <v>2026-03-19T18:35:41.970Z</v>
+      </c>
+      <c r="F81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>https://bmsce.ac.in/home/news/1/the-department-of-computer-applications-in-collaboration-with-the-indian-society-for-technical-education-iste-is-organizing-a-one-week-faculty-development-program-fdp-ondevops-thefdpwill-be-held-inonlinemode-from-29th-july-2024-to-03rd-august-2024</v>
+      </c>
+      <c r="B82" t="str">
+        <v>html</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Home 16 Jul The Department of Computer Applications, in collaboration with the Indian Society for Technical Education (ISTE), is organizing a One Week Faculty Development Program (FDP) on DevOps. The FDP will be held in Online mode from 29th July 2024 to 03rd August 2024. The Department of Computer Applications, in collaboration with the Indian Society for Technical Education (ISTE), is organizing a One Week Faculty Development Program (FDP) on DevOps. The FDP will be held in Online mode from 29th July 2024 to 03rd August 2024. The FDP aims to provide valuable insights and practical knowledge on DevOps, enhancing the skills and expertise of our faculty members. We believe this program will be highly beneficial for their professional development. Registration fee: ISTE Members - ₹500/- Non-ISTE Members - ₹750/- Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82" t="str">
+        <v>2026-03-19T18:35:42.587Z</v>
+      </c>
+      <c r="F82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>https://bmsce.ac.in/home/news/1/ieee-international-conference-on-emerging-technologies-in-computer-science-for-interdisciplinary-applications-icetcs-2024-22nd-23rd-april-2024</v>
+      </c>
+      <c r="B83" t="str">
+        <v>html</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Home 21 Apr IEEE INTERNATIONAL CONFERENCE ON EMERGING TECHNOLOGIES IN COMPUTER SCIENCE FOR INTERDISCIPLINARY APPLICATIONS (ICETCS 2024), 22nd -23rd April 2024 IEEE INTERNATIONAL CONFERENCE ON EMERGING TECHNOLOGIES IN COMPUTER SCIENCE FOR INTERDISCIPLINARY APPLICATIONS (ICETCS 2024), 22nd -23rd April 2024. Click here to view the brochure. Click here to view the invitation Back to All News</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83" t="str">
+        <v>2026-03-19T18:35:43.199Z</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>https://bmsce.ac.in/home/news/1/state-level-wheel-chair-cricket-tournament-date-march-23-2024</v>
+      </c>
+      <c r="B84" t="str">
+        <v>html</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Home 19 Mar State-Level Wheel Chair Cricket Tournament Date: March 23, 2024. State-Level Wheel Chair Cricket Tournament Date: March 23, 2024. Click here to View the Brochure Back to All News</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84" t="str">
+        <v>2026-03-19T18:35:43.806Z</v>
+      </c>
+      <c r="F84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>https://bmsce.ac.in/home/news/1/first-ieee-international-conference-on-communications-and-computer-science-2024-incccs-2024-22nd-24th-may-1</v>
+      </c>
+      <c r="B85" t="str">
+        <v>html</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Home 01 Feb First IEEE International Conference on Communications and Computer Science-2024 (InCCCS-2024) 22nd – 24th May, 2024 First IEEE International Conference on Communications and Computer Science-2024 (InCCCS-2024) : 22nd – 24th May, 2024 Click here to view the details Back to All News</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85" t="str">
+        <v>2026-03-19T18:35:44.426Z</v>
+      </c>
+      <c r="F85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-mechanical-engineering-is-organising-a-fdp-on-latest-trends-in-additive-manufacturing-from-29-january-to-2-february-2024</v>
+      </c>
+      <c r="B86" t="str">
+        <v>html</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Home 12 Jan Department of Mechanical Engineering is organising a FDP on "Latest Trends in Additive Manufacturing" from 29 January to 2 February, 2024. Department of Mechanical Engineering is organising a FDP on "Latest Trends in Additive Manufacturing" from 29 January to 2 February, 2024 with the support from NCAM, GoI. Click here to download the Application Form Back to All News</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86" t="str">
+        <v>2026-03-19T18:35:45.080Z</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>https://bmsce.ac.in/home/news/1/atal-sponsored-fdp-is-organized-from-dept-of-eee-bmsce-during-29th-jan-2024-to-3rd-feb-2024</v>
+      </c>
+      <c r="B87" t="str">
+        <v>html</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Home 27 Dec ATAL sponsored FDP is organized from Dept. of EEE, BMSCE during 29th Jan 2024 to 3rd Feb 2024. ATAL sponsored FDP is organized from Dept. of EEE, BMSCE during 29th Jan 2024 to 3rd Feb 2024. Click here to view ATAL FDP Brochure Back to All News</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87" t="str">
+        <v>2026-03-19T18:35:45.700Z</v>
+      </c>
+      <c r="F87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-electronics-and-instrumentation-engineering-conducting-a-one-day-tech-summit-techsolstice-on-21-december-2023-thursday-at-bmsce-auditorium-1-platinum-jubilee-academic-block</v>
+      </c>
+      <c r="B88" t="str">
+        <v>html</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Home 20 Dec Department of Electronics and Instrumentation Engineering, conducting A one day Tech Summit “ TechSolstice ” on 21 December 2023 (Thursday) at BMSCE, Auditorium 1, Platinum Jubilee Academic Block Department of Electronics and Instrumentation Engineering, conducting A one day Tech Summit “ TechSolstice ” on 21 December 2023 (Thursday) at BMSCE, Auditorium 1, Platinum Jubilee Academic Block. The resource person is Professor Mel Siegel, Professor Emeritus from Carnegie Mellon University (CMU), USA. He will deliver a keynote address titled "The Coming Revolution in Inertial Navigation". Click here to view the brochure Back to All News</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88" t="str">
+        <v>2026-03-19T18:35:46.328Z</v>
+      </c>
+      <c r="F88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>https://bmsce.ac.in/home/news/1/10th-annual-alumni-day-2023</v>
+      </c>
+      <c r="B89" t="str">
+        <v>html</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Home 15 Dec 10th Annual Alumni Day 2023. Click here to view the invitation Back to All News</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89" t="str">
+        <v>2026-03-19T18:35:46.930Z</v>
+      </c>
+      <c r="F89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-eee-in-association-with-eeea-invited-talk-on-internship-opportunities-at-iisc-on-17-november-2023-friday3pm-at-auditorium-2</v>
+      </c>
+      <c r="B90" t="str">
+        <v>html</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Home 15 Nov Department of EEE in association with EEEA, invited talk on “Internship Opportunities at IISc” on 17 November 2023 (Friday),3pm at Auditorium 2. Department of EEE in association with EEEA, invited talk on “Internship Opportunities at IISc” on 17 November 2023 (Friday),3pm at Auditorium 2. - Click here to View the Brochure Back to All News</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90" t="str">
+        <v>2026-03-19T18:35:47.559Z</v>
+      </c>
+      <c r="F90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>https://bmsce.ac.in/home/news/1/award-of-1005gusecaselabs-toto-selected-academic-institutions-was-held-by-honble-prime-minister-shri-narendra-modiji-on-27th-october-2023-as-part-of-indian-mobile-congress-2023</v>
+      </c>
+      <c r="B91" t="str">
+        <v>html</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Home 26 Oct " Award of 100 5G use case Labs to to selected academic institutions was held by Hon'ble Prime Minister Shri. Narendra Modiji on 27th October 2023 as part of Indian Mobile Congress, 2023 Click here to view the Document Back to All News</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91" t="str">
+        <v>2026-03-19T18:35:48.183Z</v>
+      </c>
+      <c r="F91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-electronics-and-instrumentation-engineering-presents-a-one-day-workshop-on-adft-2023-antenna-design-fabrication-and-testing-workshop-on-16th-june-2023-friday-at-auditorium-1pjab-bmsce</v>
+      </c>
+      <c r="B92" t="str">
+        <v>html</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Home 06 Jun Department of Electronics and Instrumentation Engineering, presents a one day workshop on ADFT-2023,'' Antenna design, Fabrication and testing workshop", on 16th June 2023 (Friday) at Auditorium 1,PJAB , BMSCE. The Department of Electronics and Instrumentation Engineering, BMS College Of Engineering in association with Entuple technology pvt limited, presents a one day workshop on ADFT-2023,'' Antenna design, Fabrication and testing workshop", on 16th June 2023(Friday) at Auditorium 1,PJAB, BMSCE. Click here to View the Brochure. Back to All News</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92" t="str">
+        <v>2026-03-19T18:35:48.820Z</v>
+      </c>
+      <c r="F92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>https://bmsce.ac.in/home/news/1/faculty-development-programme-on-current-trends-in-material-physics-for-engineering-applications-by-the-department-of-physics-from-15-05-2023-to-19-05-2023</v>
+      </c>
+      <c r="B93" t="str">
+        <v>html</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Home 06 May Faculty development programme on "Current Trends in Material Physics for Engineering Applications" by the Department of Physics from 15-05-2023 to 19-05-2023. Faculty development programme on "Current Trends in Material Physics for Engineering Applications" by the Department of Physics from 15-05-2023 to 19-05-2023. Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93" t="str">
+        <v>2026-03-19T18:35:49.429Z</v>
+      </c>
+      <c r="F93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-eee-is-organising-an-fdp-in-blended-mode-on-modelling-and-design-of-power-converters-hands-on-from-15th-may-to-19th-may-2023</v>
+      </c>
+      <c r="B94" t="str">
+        <v>html</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Home 27 Apr Department of EEE is organising an FDP in blended mode on "Modelling and Design of Power Converters-Hands-On '' from 15th May to 19th May 2023. The Department of EEE is organising an FDP in blended mode on "Modelling and Design of Power Converters-Hands-On '' from 15th May to 19th May 2023. Click here to View the Brochure Back to All News</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94" t="str">
+        <v>2026-03-19T18:35:50.037Z</v>
+      </c>
+      <c r="F94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-computer-science-and-engineering-department-of-medical-electronics-organizing-one-week-fdpsdp-on-bio-medical-signal-acquisition-and-analysis-24th-april-2023-to-28th-april-2023</v>
+      </c>
+      <c r="B95" t="str">
+        <v>html</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Home 20 Apr Department of Computer Science and Engineering &amp; Department of Medical Electronics organizing one week FDP/SDP on “Bio-Medical Signal Acquisition and Analysis " 24th April 2023 to 28th April 2023 Department of Computer Science and Engineering &amp; Department of Medical Electronics organizing one week FDP/SDP on “Bio-Medical Signal Acquisition and Analysis" from 24th April 2023 to 28th April 2023. Click here to view the brochure Back to All News</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95" t="str">
+        <v>2026-03-19T18:35:50.667Z</v>
+      </c>
+      <c r="F95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-electronics-and-instrumentation-engineering-organizing-iact-2023-isa-bangalore-automation-and-control-technology-day-on-31st-march-friday-and-1-april-saturday-2023</v>
+      </c>
+      <c r="B96" t="str">
+        <v>html</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Home 28 Mar Department of Electronics and Instrumentation Engineering Organizing “IACT 2023” (ISA Bangalore Automation and Control Technology day) on 31st March (Friday) and 1 April, (Saturday) 2023 Department of Electronics and Instrumentation Engineering conducting an event “IACT 2023” (ISA Bangalore Automation and Control Technology day) on 31st March (Friday) and 1 April, (Saturday) 2023 at B.M.S.C.E. Click here to View the Brochure. “IACT 2023” (ISA Bangalore Automation and Control Technology day), hosted by the Department of Electronics and Instrumentation Engg, B.M.S. College of Engineering (B.M.S.C.E.), Bengaluru in association with the International Society for Automation Bangalore Section (ISAB). The theme of the event is “Digital transformation through contemporary technologies” and is scheduled on 31 March (Friday) and 1 April, (Saturday) 2023 at B.M.S.C.E. This Intercollegiate Technology festival lasting two days is the seventh edition and is aimed to bring in participants from various ISAB Student sections across different states together. During this technology festival, participating students showcase their talents and skills through projects, paper presentations, technical competitions, hackathon, ideathon, solving complex Engineering problems and several others. Subject domain experts drawn from nearly three hundred Industry professionals of ISA Bangalore together with Academia have agreed to help adjudicate during the two-day event. The event will witness a footfall of over 200 participants from various engineering colleges from Karnataka, Tamil Nadu, and Kerala. In addition, the event will comprise of keynote speeches, technical sessions and workshops on the latest advancements and trends in the field of automation, control and allied areas. Any queries contact : Dr. Veena N Hegde Faculty Advisor - 9886081532 | Mr. Kumar D - 9743114046 Mihir P ISA SS BMSCE President- 8296689145 | Bhavye Bhasin - 9148722891 Date: 31st March 2023 to 1st April 2023 Back to All News</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96" t="str">
+        <v>2026-03-19T18:35:51.281Z</v>
+      </c>
+      <c r="F96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-computer-applications-organizes-two-weeks-value-added-program-on-augment-reality-in-blended-mode-date-18th-january-2023-to-31th-january-1</v>
+      </c>
+      <c r="B97" t="str">
+        <v>html</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Home 12 Jan Department of Computer Applications organizes Two Weeks Value Added Program on “Augment Reality” in Blended mode Date: 18th January 2023 to 31th January, 2023 Department Of Computer Applications organizes Two Weeks Value Added Program on “Augment Reality” in Blended mode Date: 18th January 2023 to 31th January, 2023 (30 hours Direct contact and self-study) Course Overview ● Introduction to Computer Graphics using OpenGL ● Transformations &amp; Camera Calibration ● Introduction to AR ● Unity Installation, Creating Environment using 3D models ● Creating simple Animations using Unity, Keyboard &amp; Mouse events using unity ● Pose Estimation and Tracking, Vuforia installation ● Creating simple AR applications using Vuforia ● Introduction to AI &amp; its applications in AR ● ARKit – to create interactive augmented reality experiences. Click here to view the Brochure Click here to view the Schedule Course Outcomes Students will be able to  Write OpenGL programs to build and transform 2D models.  Work with AR development tools like unity, vuforia, ARKit  Develop AR applications using AR Tools Open to UG &amp; PG students Pursuing Engineering, Computer Applications or Management from all Colleges (including BMSCE) Deadline for Registration: 17th January 2023 Registration fee: Rs.700/- Mode of Payment Account name: HoD MCA Account Number: 20274186038 Bank Name: Indian Bank IFSC: IDIB000B607 One can also pay directly in the Indian Bank in BMSCE campus. CASH payments are not accepted Register: https://forms.gle/xz8oF5LJ9MbUryTJ9 Back to All News</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97" t="str">
+        <v>2026-03-19T18:35:51.897Z</v>
+      </c>
+      <c r="F97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>https://bmsce.ac.in/home/news/1/thenss-unitin-collaboration-withncc-unitcivil-defence-corps-and-leo-satvaof-bmsce-is-organizing-ablood-donation-campin-association-withjayadeva-hospital-kidwai-memorial-institute-of-oncologyandbmst-rotaryon12012023</v>
+      </c>
+      <c r="B98" t="str">
+        <v>html</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Home 11 Jan The NSS UNIT in collaboration with NCC UNIT, Civil Defence Corps and Leo Satva of BMSCE is organizing a Blood Donation Camp in association with Jayadeva Hospital, Kidwai Memorial Institute of Oncology and BMST Rotary on 12/01/2023. Greetings from the NSS UNIT OF BMSCE "The gift of blood is a gift to someone's life". The NSS UNIT in collaboration with NCC UNIT, Civil Defence Corps and Leo Satva of BMSCE is organizing a Blood Donation Camp in association with Jayadeva Hospital, Kidwai Memorial Institute of Oncology and BMST Rotary on 12/01/2023. Time: 9:00 AM to 4:00 PM. Location: Indoor Stadium, BMS college of Engineering. It's open for all. You can register for the same by filling out the form below: https://forms.gle/ujvUwrYMJVmaRPFm6 (No registrations required for staff.) For further queries, please contact: Moulya J: 9036199618 Likitha V: 77607 08216 Back to All News</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98" t="str">
+        <v>2026-03-19T18:35:52.500Z</v>
+      </c>
+      <c r="F98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>https://bmsce.ac.in/home/news/1/annual-alumni-day-2022-and-alumni-sports-day-2022</v>
+      </c>
+      <c r="B99" t="str">
+        <v>html</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Home 01 Dec Annual Alumni day -2022 and Alumni Sports Day- 2022 Annual Alumni day -2022 and Alumni Sports Day- 2022 Click here to view the Annual Alumni Day Click here to view the Alumni Sports Day Back to All News</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99" t="str">
+        <v>2026-03-19T18:35:53.122Z</v>
+      </c>
+      <c r="F99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>https://bmsce.ac.in/home/news/1/international-conference-on-data-decision-and-systems-icdds-2022-2nd-and-3rd-of-december-2022</v>
+      </c>
+      <c r="B100" t="str">
+        <v>html</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Home 01 Dec International Conference on Data, Decision and Systems (ICDDS) 2022 - 2nd and 3rd of December, 2022. We are happy to inform you that BMSCE IEEE Computer Society in collaboration with the IEEE Computer Society Bangalore Chapter is hosting The International Conference on Data, Decision and Systems (ICDDS), a flagship conference of IEEE Computer Society Bangalore Chapter on the 2nd and 3rd of December, 2022. The conference is sponsored by various companies namely Continental, Boeing, Dozee, and Bosch. We would be happy to witness active participation from all the students hence, we request you to kindly grant us permission to upload the details of the event on the official website of B.M.S. College of Engineering. Details(text): Greetings from IEEE Computer Society Bangalore Chapter! We are honoured to conduct the International Conference on Data Decisions and Systems 2022 hosted in B.M.S College of Engineering. ICDDS'22 is an annual conference which aims to bring together great minds from across the world. It will feature experts of various domains helping in extending the horizons of young minds. Date : 2nd and 3rd of December. Venue : Auditorium 1 and Auditorium 2, B.M.S. College of Engineering Click here to view the Poster Click here to view the program schedule Registration Here: https://forms.gle/wWrpC2oHQyRBJ9Ey9 For further queries, feel free to contact PG Supriya: 78992 47219 Kalp: 70606 80819 Back to All News</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100" t="str">
+        <v>2026-03-19T18:35:53.733Z</v>
+      </c>
+      <c r="F100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>https://bmsce.ac.in/home/news/1/inauguration-of-first-year-induction-program-on-13112022-11-am</v>
+      </c>
+      <c r="B101" t="str">
+        <v>html</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Home 12 Nov Inauguration of First Year Induction Program on 13.11.2022 @ 11 AM Inauguration of First Year Induction Program on 13.11.2022 @ 11 AM. Click here to View the Invitation. Back to All News</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101" t="str">
+        <v>2026-03-19T18:35:54.341Z</v>
+      </c>
+      <c r="F101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-computer-science-and-engineeringandbmsce-ieee-sbin-association-with-is-conducting-avalueaddedcourseonproblem-solving-and-working-with-hackerrank-platform-from-11th-to-15th-november-2022</v>
+      </c>
+      <c r="B102" t="str">
+        <v>html</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Home 08 Nov Department of Computer Science and Engineering and BMSCE IEEE SB in association with is conducting a value added course on "Problem Solving and Working with HackerRank Platform" from 11th to 15th November 2022 Greetings from the CSE Department and BMSCE IEEE SB! The Department of Computer Science and Engineering and BMSCE IEEE SB in association with &lt;/CodeIO&gt; is conducting a value added course on "Problem Solving and Working with HackerRank Platform". Date: 11th to 15th November, 2022 Venue: Blended mode (for PG students only) Click here to download the Schedule Click here to download the Brochure Back to All News</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102" t="str">
+        <v>2026-03-19T18:35:54.944Z</v>
+      </c>
+      <c r="F102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>https://bmsce.ac.in/home/news/1/ieee-power-and-energy-society-bangalore-chapter-in-collaboration-with-bmsce-ieee-pesand-sensors-council-presents-young-researchers-meet-2022-on-4th-and-5th-november-2022</v>
+      </c>
+      <c r="B103" t="str">
+        <v>html</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Home 12 Oct IEEE Power and Energy Society Bangalore Chapter in collaboration with BMSCE IEEE PES and Sensors Council presents Young Researchers' Meet 2022* on 4th and 5th November 2022 IEEE Power and Energy Society Bangalore Chapter in collaboration with BMSCE IEEE PES and Sensors Council presents Young Researchers' Meet 2022. Click here to download the event brochure YRM is the flagship event of the IEEE Power and Energy Society Bangalore Chapter, which offers a platform for bringing together young promising graduate students and researchers, throughout the nation. We, BMSCE IEEE PES and Sensors Council are glad to be hosting Young Researchers’ Meet 2022 on the premises of our institution, BMS College of Engineering, Bangalore. YRM' 22 will be a two-day event and will feature a broad range of events such as panel discussions, workshops, seminars, and focused sessions mentored by highly skilled and experienced professionals. Lunch and Refreshments will be provided on both days. Date: 4th and 5th November 2022 Registration is open to all. Registration fees: For IEEE Members: ₹200 For Non- IEEE members: ₹500 For registration and additional details please visit https://bit.ly/YRM_22_website For further queries, contact: Shamitha: 8296893018 Aneesh: 6362350744 Back to All News</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103" t="str">
+        <v>2026-03-19T18:35:55.557Z</v>
+      </c>
+      <c r="F103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>https://bmsce.ac.in/home/news/1/ieee-ic-sct-in-collaboration-with-bmsce-ieee-sb-presents-ichack22-a-student-run-hackathon-this-is-your-opportunity-to-show-off-your-technical-skills-at-national-level-3rd-4th-september-2022</v>
+      </c>
+      <c r="B104" t="str">
+        <v>html</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Home 22 Aug IEEE IC SCT in collaboration with BMSCE IEEE SB presents, ICHACK'22 - A Student Run Hackathon! This is your opportunity to show-off your technical skills at National Level - 3rd &amp; 4th September 2022 "Hackathons are where your crazy idea becomes reality” Click here to view the Brochure IEEE IC SCT in collaboration with BMSCE IEEE SB presents, ICHACK'22 - A Student Run Hackathon! This is your opportunity to show-off your technical skills at National Level! Date: 3rd and 4th September, 2022 Venue: BMS College of Engineering, Bengaluru. Prize Pool: ₹1,00,000 Registration Fees: - IEEE Members: ₹200 - Non- IEEE Members: ₹300 Take part in the national level hackathon and get various benefits! From fun activities to snacks and goodies, we've got it covered! For more details, check out our website: bit.ly/ic-hack22 For further queries, contact: Mohit: 81471 97203 Niharika: 83105 83476 Back to All News</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104" t="str">
+        <v>2026-03-19T18:35:56.185Z</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>https://bmsce.ac.in/home/news/1/ieee-india-council-in-collaboration-with-bmsce-ieee-sb-and-bmsce-ieee-cs-presents-to-you-scytale-lost-in-the-abyss-of-time-an-18-hour-online-cryptic-hunt-on-27-august-2022-9-pm-1</v>
+      </c>
+      <c r="B105" t="str">
+        <v>html</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Home 22 Aug IEEE India Council in collaboration with BMSCE IEEE SB and BMSCE IEEE CS presents to you "SCYTALE - Lost In The Abyss Of Time", an 18-hour online cryptic hunt on 27 August, 2022 @ 9 PM Click here to view the Brochure "It is by venturing into the abyss that we challenge our wits and unlock hidden treasures of our minds." IEEE India Council in collaboration with BMSCE IEEE SB and BMSCE IEEE CS presents to you "SCYTALE - Lost In The Abyss Of Time", an 18-hour online cryptic hunt. Challenge your minds in various rounds ranging from logical thinking to deciphering codes. Get a chance to win prizes worth 15K! Date: 27 August, 2022 Time: 9 PM Participate in Teams of two or less. Registration fee per member: IEEE members: ₹50 Non-IEEE members: ₹80 Payments to be made at: pradyunnaik713@okaxis/8792251103 Hurry up! Register now for this thrilling virtual adventure. https://rb.gy/0hl2ci For any further queries, contact: Ankita: 6366088662 Pradyun: 8792251103 Back to All News</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105" t="str">
+        <v>2026-03-19T18:35:56.797Z</v>
+      </c>
+      <c r="F105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>https://bmsce.ac.in/home/news/1/to-upload-selfie-with-flag-on-website-wwwharghartirangacom-and-use-official-hashtagharghartiranga-for-social-media-promotions-1</v>
+      </c>
+      <c r="B106" t="str">
+        <v>html</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Home 09 Aug To upload selfie with flag on website www.harghartiranga.com and use official hashtag#harghartiranga for social media promotions Instructions to upload selfie with flag on website www.harghartiranga.com and use official hashtag#harghartiranga for social media promotions. Click here to download the Circular Back to All News</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106" t="str">
+        <v>2026-03-19T18:35:57.447Z</v>
+      </c>
+      <c r="F106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>https://bmsce.ac.in/home/news/1/technical-fest-bmsce-srishti-july-25-27-1</v>
+      </c>
+      <c r="B107" t="str">
+        <v>html</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Home 24 Jul Technical fest BMSCE- SRISHTI July 25-27, 2022 The technical fest, “SRISHTI” organised by Yuvaka sangha would be hosted by the college during July 25th – 27st, 2022. In this regard, there will be 39 different events involving the participation of 1500 students from 104 engineering colleges. The main attraction of the event would be a project exhibition cum competition in which, 285 projects from different colleges would be exhibited. Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107" t="str">
+        <v>2026-03-19T18:35:58.107Z</v>
+      </c>
+      <c r="F107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>https://bmsce.ac.in/home/news/1/national-level-seminar-ondigital-transformations-under-nep-2020-on-15-07-2022</v>
+      </c>
+      <c r="B108" t="str">
+        <v>html</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Home 15 Jul National Level Seminar on “Digital Transformations under NEP 2020” on 15-07-2022 The IQAC, BMSCE in association with NAAC is organising a National Level Seminar on “Digital Transformations under NEP 2020” on 15.07.2022 in online mode. The seminar addresses the effective use of technology in the perspective of NEP 2020. The last date to register for the seminar is 13-07-2022. The brochure attached for your reference. Registration Link: https://tinyurl.com/bdfxj69j Click here to view Brochure Back to All News</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108" t="str">
+        <v>2026-03-19T18:35:58.742Z</v>
+      </c>
+      <c r="F108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>https://bmsce.ac.in/home/news/1/bmsce-alumni-network-is-pleased-to-invite-the-batch-of-2021-2020-and-2019-students-for-their-graduation-day-on-22nd-and-23rd-july-1</v>
+      </c>
+      <c r="B109" t="str">
+        <v>html</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Home 22 Jul BMSCE Alumni Network is pleased to invite the batch of 2021, 2020 and 2019 students for their Graduation Day. on 22nd and 23rd July 2022 Dear Alumni students of 2021,2020 and 2019 batches BMSCE Alumni Network is pleased to invite the batch of 2021, 2020 and 2019 students for their Graduation Day. The ceremony will be held on 22nd July 2022(Friday) for the batch of 2021 and on 23rd July 2022 (Saturday) for the batches of 2019 and 2020 at the Indoor Stadium, BMSCE. Registrations are completely online and mandatory to attend the Graduation Day ceremony. * No spot registrations are entertained RSVP here: https://lu.ma/bmsgrad Latdate for RSVP is : 17th July 2022 Details: Program starts at 10am at Indoor stadium, BMSCE, you are requested to be seated in the seat alloted[numbered] to you on or before 9:30am. Latecomers will not be allowed inside the stadium after 9:30 to maintain the discipline One parent per graduate is allowed but they will be seated in auditoriums and they will have live streaming in the audi. They can also watch the streaming from their homes, if they are unable to attend. You will receive individual mails from your Department too Please keep checking your emails and BMSCE Website for updates Please find attached the Graduation Day Invitations If you have any questions, feel free to reach out to bmscealumni@bmsce.ac.in. Click here to View Invitation 22nd 2022 Click here to View Invitation 23rd 2022 Click here to View General Instructions for Graduation Day 2022 Back to All News</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109" t="str">
+        <v>2026-03-19T18:35:59.373Z</v>
+      </c>
+      <c r="F109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>https://bmsce.ac.in/home/news/1/sensing-and-related-technologies-for-the-grand-challenges-of-the-21st-century-climate-energy-water-food-health-and-mega-cities-is-scheduled-from-11th-july-to-22nd-july-2022</v>
+      </c>
+      <c r="B110" t="str">
+        <v>html</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Home 08 Jul “Sensing and Related Technologies for the Grand Challenges of the 21st Century: Climate, Energy, Water, Food, Health and Mega-Cities” is scheduled from 11th July to 22nd July 2022, GIAN PROGRAMME AT BMSCE: A GIAN course on “Sensing and Related Technologies for the Grand Challenges of the 21st Century: Climate, Energy, Water, Food, Health and Mega-Cities” is scheduled from 11 th July to 22 nd July 2022, in online mode. The international faculty for the course is Mel Siegel, Professor Emeritus, CMU, USA and local faculty in charge are Dr.Veena N.Hegde, Professor, Department of Electronics and Instrumentation Engg. and Prof. Preethi. K. Mane, Associate Professor, Department of Electronics and Instrumentation Engineering. Click here to View the Brochure Back to All News</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110" t="str">
+        <v>2026-03-19T18:35:59.995Z</v>
+      </c>
+      <c r="F110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-day-national-conference-on-additive-manufacturing-in-aerospace-defence-amad-2022-other-engineering-sectors-in-online-mode-co-hosted-by-the-department-of-mechanical-engineeringbmsce-on-2nd-julysaturday-at-915-am</v>
+      </c>
+      <c r="B111" t="str">
+        <v>html</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Home 02 Jul One day National conference on "Additive Manufacturing in Aerospace, Defence (AMAD-2022) &amp; Other Engineering Sectors (In Online Mode)" Co-hosted by the Department of Mechanical Engineering,BMSCE on 2nd July(Saturday) at 9.15 A.M. One day National conference on "Additive Manufacturing in Aerospace, Defence (AMAD-2022) &amp; Other Engineering Sectors (In Online Mode)" Co-hosted by the Department of Mechanical Engineering,BMSCE on 2nd July(Saturday) at 9.15 A.M. Venue: Mechanical Engineering Seminar Hall (M.E.S.H), 2nd Floor, Department of Mechanical Engineering Click here to View NDRF-Inauguration Click here to View Program Schedule Click here to View Brochure - National Conference Back to All News</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111" t="str">
+        <v>2026-03-19T18:36:00.607Z</v>
+      </c>
+      <c r="F111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-electronics-communication-engineering-in-association-with-iete-is-organizing-fifth-national-conference-on-networking-embedded-and-wireless-systems-news-2022-which-will-be-held-duringoctober-12th-14th2022</v>
+      </c>
+      <c r="B112" t="str">
+        <v>html</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Home 16 Jun Department of Electronics &amp; Communication Engineering in Association with IETE is organizing Fifth National Conference on Networking, Embedded and Wireless Systems-NEWS-2022 which will be held during October 12th -14th, 2022. Department of Electronics &amp; Communication Engineering in Association with IETE is organising Fifth National Conference on Networking, Embedded and Wireless Systems-NEWS-2022 which will be held during Oct 12th -14th 2022 at BMS College of Engineering, Bengaluru, India . Click here to view the Brochure Conveners: Dr. Archana H.R., M: +91-9538844314 Dr. Surendra H.H., M: +91-9449859023 Back to All News</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112" t="str">
+        <v>2026-03-19T18:36:01.209Z</v>
+      </c>
+      <c r="F112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>https://bmsce.ac.in/home/news/1/bmsce-ieee-computer-society-in-collaboration-with-the-ieee-computer-society-bangalore-an-intercollegiate-hackathon-girlgeekshack-2022-on-the-18th-and-19th-of-june-2022</v>
+      </c>
+      <c r="B113" t="str">
+        <v>html</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Home 16 Jun BMSCE IEEE Computer Society in collaboration with the IEEE Computer Society Bangalore - an intercollegiate hackathon - GirlGeeksHack 2022 on the 18th and 19th of June, 2022. We are happy to inform you that BMSCE IEEE Computer Society in collaboration with the IEEE Computer Society Bangalore Chapter is hosting one of their most prestigious events, an intercollegiate hackathon - GirlGeeksHack 2022 on the 18th and 19th of June, 2022. The event is being conducted in association with the Department of ISE, BMSCE and is sponsored by HUSHL. The registration link is as follows: https://in.explara.com/e/girl-geeks-hack Click here to View the Brochure Dr. Sandeep Varma N Chapter Advisor BMSCE IEEE Computer Society Back to All News</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113" t="str">
+        <v>2026-03-19T18:36:01.826Z</v>
+      </c>
+      <c r="F113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-eee-is-organizing-a-two-weeks-online-value-added-course-on-vlsi-verilog-and-image-processing-6th-june-2022-to-18th-june-2022</v>
+      </c>
+      <c r="B114" t="str">
+        <v>html</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Home 04 Jun Department of EEE is organizing a Two weeks online Value Added Course on VLSI, Verilog and Image Processing - 6th June 2022 to 18th June 2022 Department of EEE is organising a two weeks Value Added Course on "VLSI, Verilog and Image Processing", from 6th June 2022 to 18th June 2022 from 5pm to 8pm. Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114" t="str">
+        <v>2026-03-19T18:36:02.449Z</v>
+      </c>
+      <c r="F114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>https://bmsce.ac.in/home/news/1/the-department-of-computer-applications-bmsce-is-organizing-a-two-week-online-value-added-course-on-python-for-data-science-from-16th-to-27th-may-1</v>
+      </c>
+      <c r="B115" t="str">
+        <v>html</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Home 09 May The Department of Computer Applications, BMSCE is organizing a Two-week Online Value Added Course on "Python for Data Science" from 16th to 27th May, 2022 The Department of Computer Applications, BMSCE is organizing a Two-week Online Value Added Course on "Python for Data Science" from 16th to 27th May, 2022. Registration Link: https://forms.gle/broiwRafZKQiEZND7 Click here to view the brochure Click here to view the schedule Registration Fee: -Registration fee: Rs. 250 -Open to all UG and PG students of all colleges Deadline for Registration: 15th May 2022 Payments to be made at: Account name: HoD MCA Account Number: 20274186038 Bank Name: Indian Bank IFSC: IDIB000B607 Payments can also be made directly at the Indian Bank in BMSCE campus. Herewith, please find the attachments of the brochure and schedule. Once the user fills the form, he/she will automatically get an email to join whatsapp group. For payment, users need to do payment manually, and need to put the transaction id and the time stamp in the form. If any queries, contact: Student Coordinator: Bhagyashri, Department of Computer Applications, BMSCE, Bangalore.bhagyashri.mca21 @bmsce.ac.in. Faculty coordinators: Prof. R.V. Raghavendra Rao and Dr. Ch. Ram Mohan Reddy, Dept. of Computer Applications, BMSCE. Back to All News</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115" t="str">
+        <v>2026-03-19T18:36:03.053Z</v>
+      </c>
+      <c r="F115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-ise-students-club-bmsce-in-association-with-ieee-students-chapter-and-bmscean-is-organizing-a-30-hrs-hand-on-value-added-course-on-kubernetes-for-beginners-from-4th-may-2022-in-blended-mode</v>
+      </c>
+      <c r="B116" t="str">
+        <v>html</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Home 02 May Department of ISE, Student's Club, BMSCE in association with IEEE student's Chapter and BMSCEAN is organizing a 30 hrs hand-on value added course on "Kubernetes for Beginners" from 4th May, 2022 in blended Mode Click here to view the brochure All the interested[both UG and PG] students can register for this course using the following link Registration Link: https://bmsce.typeform.com/ciiedevelopers Registration Fee: ₹300 Mode of Payment Account name: HOD, ISE, Account Number: 20274184983 Indian Bank IFSC: IDIB000B607 (Note First FOUR characters are alphabets) One can also pay directly in the Indian Bank in BMSCE campus. CASH payments are NOT accepted Deadline for Registration: 3rd May 2022 Once the user fills out the form, he/she will automatically get an email to join a WhatsApp group. For payment, users need to do payment manually and need to put the transaction id and the time stamp in the form. Back to All News</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116" t="str">
+        <v>2026-03-19T18:36:03.673Z</v>
+      </c>
+      <c r="F116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>https://bmsce.ac.in/home/news/1/two-week-value-added-course-on-python-programming-from-18th-to-29th-april-2022</v>
+      </c>
+      <c r="B117" t="str">
+        <v>html</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Home 16 Apr Two Week Value Added Course on "Python Programming" from 18th to 29th April, 2022 The department of CSE, BMSCE in association with BMSCE CSE Protocol and BMSCE IEEE Student Branch, is organizing a two-week online value added course on "Python Programming" from 18th to 29th April, 2022. Registration Link: https://forms.gle/c7f6f77VNLfRyYpy7 Click here to view the Brochure Click here to view the Poster Click here to view the Schedule Registration Fee: -For IEEE members: Rs/- 280 -For Non-IEEE members: Rs/- 400 Open to all UG and PG students of all colleges Deadline for Registration: 17th April 2022 Payments to be made at: Account name: HOD, Computer Science and Engineering Account Number: 20274184972 Indian Bank IFSC: IDIB000B607 Payments can also be made directly at the Indian Bank in BMSCE campus. The brochure and schedule are available: https://bit.ly/3E8wHUH Herewith, please find the attachments of the poster, brochure and schedule. If any queries, contact: Ranjini: 99028 88866 Sameecha: 99003 28495 Akansha: 78932 73366 Faculty coordinators: Prof.Saritha A N and Dr. Nandhini Vineeth, Dept. of CSE, BMSCE. Back to All News</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117" t="str">
+        <v>2026-03-19T18:36:04.300Z</v>
+      </c>
+      <c r="F117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-eee-eee-association-andbmsce-ieee-pes-and-sensors-council-present-energy-swaraj-yatra-talk-by-prof-chetan-singh-solanki-on-28th-march-2022-from-200-pm</v>
+      </c>
+      <c r="B118" t="str">
+        <v>html</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Home 26 Mar Department of EEE (EEE Association) and BMSCE IEEE PES and Sensors Council present ENERGY SWARAJ YATRA Talk by Prof. Chetan Singh Solanki on 28th March 2022 from 2:00 PM Click here to view the Poster The Department of EEE (EEE Association) and BMSCE IEEE PES and Sensors Council cordially invite you to attend the interactive session with the Solar man of India/Solar Gandhi, Prof. Chetan Singh Solanki, Founder of Energy Swaraj Foundation, and Professor, IIT Bombay. He is constantly keeping enormous efforts to make the nation sustainable and as a part this he is on Energy Swaraj Yatra where he will be covering the entire nation for the next 10 years in a solar powered bus to convey the message of the importance of solar energy and to combine synergies of climate change mitigation efforts. I cordially invite you to witness the journey of Solar Gandhi along with his own solar bus on 28th March 2022 from 2:00 PM onwards at Auditorium 1, BMSCE. Register using the link below: https://forms.gle/SSmktEXaJomdwQHo7 Registration is open on a first come first serve basis ! For further details, contact: Amogh: 9632932765 Shamitha: 8296893018 Back to All News</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118" t="str">
+        <v>2026-03-19T18:36:04.907Z</v>
+      </c>
+      <c r="F118">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>https://bmsce.ac.in/home/news/1/interactive-contents-development-enabling-the-better-presentation-of-fluid-mechanics-and-hydraulic-engineering-concept-in-engineering-education</v>
+      </c>
+      <c r="B119" t="str">
+        <v>html</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Home 24 Mar Interactive contents development enabling the better presentation of fluid mechanics and hydraulic engineering concept in engineering education Project title: Interactive contents development enabling the better presentation of fluid mechanics and hydraulic engineering concept in engineering education Sanctioned year: 2021 (December) (MoU for one year) Funding Agency: La Fondation Dassault Systems Project cost: Rs. 13.75 L Grant received from the external agency: Rs. 11.15 L Status: Ongoing Research Team: Prof. Alok Pandey, Dr. Reshmi Devi T.V, Dr. Geetha Kuntoji, Dr. Suresh Ramaswwamy Reddy (Civil Engineering) Click here to View the document Back to All News</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119" t="str">
+        <v>2026-03-19T18:36:05.516Z</v>
+      </c>
+      <c r="F119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>https://bmsce.ac.in/home/news/1/two-weeks-value-added-program-on-introduction-to-python-and-latex-programming-28th-march-2022-to-8th-april-2022</v>
+      </c>
+      <c r="B120" t="str">
+        <v>html</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Home 21 Mar Two weeks Value Added Program on Introduction to Python and LaTeX Programming 28th March, 2022 to 8th April, 2022 Two weeks Value Added Program on Introduction to Python and LaTeX Programming 28th March, 2022 to 8th April, 2022. Deadline for Registration: 26th March, 2022 Register: https://forms.gle/ybbSGUkTn5mh9uNf6 Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120" t="str">
+        <v>2026-03-19T18:36:06.586Z</v>
+      </c>
+      <c r="F120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>https://bmsce.ac.in/home/news/1/two-week-value-added-course-on-modelling-simulation-robotics-automation-march-21st-to-1st-april-2022</v>
+      </c>
+      <c r="B121" t="str">
+        <v>html</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Home 19 Mar Two week Value Added course on Modelling, Simulation, Robotics &amp; Automation - March 21st to 1st April 2022 Two week Value Added course on Modelling, Simulation, Robotics &amp; Automation - March 21st to 1st April 2022 Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121" t="str">
+        <v>2026-03-19T18:36:07.239Z</v>
+      </c>
+      <c r="F121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-information-science-and-engineering-is-organizing-vgst-sponsored-five-day-faculty-development-program-on-machine-learning-and-deep-learning-with-python-from14thto-18thmarch-2022</v>
+      </c>
+      <c r="B122" t="str">
+        <v>html</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Home 12 Mar Department of Information Science and Engineering is organizing VGST Sponsored Five Day Faculty Development Program on “Machine Learning and Deep Learning with Python” from 14th to 18th March 2022. The Department of Information Science and Engineering, BMS College of Engineering, Bengaluru is organizing VGST Sponsored Five Day Faculty Development Program on “Machine Learning and Deep Learning with Python” from 14th to 18th March 2022. Click here to download the brochure Back to All News</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122" t="str">
+        <v>2026-03-19T18:36:07.851Z</v>
+      </c>
+      <c r="F122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>https://bmsce.ac.in/home/news/1/gian-course-modeling-and-simulation-of-turbulence-in-collaboration-with-the-department-of-mechanical-engineering-during-march-25-29th2022</v>
+      </c>
+      <c r="B123" t="str">
+        <v>html</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Home 18 Feb GIAN course "Modeling and Simulation of Turbulence" in collaboration with the Department of Mechanical Engineering during March 25-29th,2022 GIAN course "Modeling and Simulation of Turbulence" in collaboration with the Department of Mechanical Engineering during March 25-29th,2022. To View the Details of the Brochure - Click Here Back to All News</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123" t="str">
+        <v>2026-03-19T18:36:08.487Z</v>
+      </c>
+      <c r="F123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-civil-engineering-is-organizing-an-aicte-training-and-learning-atal-academy-sponsored-online-faculty-development-program-fdp-on-carbon-balance-and-environmental-sustainabilitycbes-2022-during-7th-11th-february-2022</v>
+      </c>
+      <c r="B124" t="str">
+        <v>html</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Home 20 Jan Department of Civil Engineering is organizing an AICTE Training and Learning (ATAL) Academy sponsored Online Faculty Development Program (FDP) on "Carbon Balance and Environmental Sustainability",CBES-2022 during 7th-11th February 2022. The Department of Civil Engineering, BMS College of Engineering is organizing an AICTE Training and Learning (ATAL) Academy sponsored Online Faculty Development Program (FDP) on " Carbon Balance and Environmental Sustainability", CBES-2022 during 7th-11th February 2022. Click here to view the Poster of the FDP. Click here to view the Brochure of the FDP. Click here to view the Schedule of the FDP. Registration Process for the same is as follows: Registration Fee: Nil Participants: Faculty members, Research scholars, PG Scholars, Government, Industry (bureaucrats /Technicians /Participants from Industry, etc.), and staff from host institutions Procedure: Step 1. Login using link https://atalacademy.aicte-india.org/login Step 2. Select workshops-&gt;select Karnataka state, February month, Thrust area-&gt;Engineering, select mode-&gt;Online, BMS College of Engineering, and register. Details can be found in the brochure attached Upload the details of the FDP on our BMSCE college Website. Back to All News</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124" t="str">
+        <v>2026-03-19T18:36:09.090Z</v>
+      </c>
+      <c r="F124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>https://bmsce.ac.in/home/news/1/ugpg-online-admission-registration-for-the-ay-2021-22-cetcomed-kmgtgoipmsspio-dcetpgcet</v>
+      </c>
+      <c r="B125" t="str">
+        <v>html</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Home 29 Nov UG/PG Online Admission Registration for the AY 2021-22 (CET/COMED-K/MGT/GOI/PMSS/PIO/ DCET/PGCET) UG/PG Online Admission Registration for the AY 2021-22 - Click Here (CET/COMED-K/MGT/GOI/PMSS/PIO/DCET/PGCET) Back to All News</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125" t="str">
+        <v>2026-03-19T18:36:09.701Z</v>
+      </c>
+      <c r="F125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>https://bmsce.ac.in/home/news/1/bmsce-phase-shift-2021-november-26-272021</v>
+      </c>
+      <c r="B126" t="str">
+        <v>html</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Home 25 Nov BMSCE PHASE SHIFT 2021 - November 26-27,2021 Greetings from Team BMSCE Phase Shift, We are honoured and pleased to invite you for the 7th edition of Phase Shift, the annual technical fest of B.M.S. College of Engineering. We hope that you will find time to participate in the events during Phase Shift 2021 amidst your multifarious duties. Your gracious presence and active participation at Phase Shift 2021, would not only enrich but also enhance the experience of the participants from both academia and industry. Phase Shift is the National Annual Technical Symposium of B.M.S. College of Engineering, Bangalore. Since its conception, the fest has grown in heaps and bounds. With the motto of rising in the spirit of innovation, the symposium has successfully been contributing to the creation of a platform for students to showcase their talents. The seventh edition of Phase Shift will be held on the 26th and 27th November, 2021 in blended mode marking the Diamond Jubilee of our prestigious institution with the theme being Digital Disruption. By embracing technology, Phase Shift organizes a plethora of events in collaboration with industries that provide a neat paradigm to encourage technological advances. With the participation of many industry experts and professionals, Phase Shift will create a congenial atmosphere for constructive ideas and a process that knits learning and fun. For more details about the events held during Phase Shift 2021, please visit our website : https://phaseshift.bmsce.in Back to All News</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126" t="str">
+        <v>2026-03-19T18:36:10.318Z</v>
+      </c>
+      <c r="F126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>https://bmsce.ac.in/home/news/1/two-days-workshop-on-implementation-of-nep-2020-15112021-and-16112021</v>
+      </c>
+      <c r="B127" t="str">
+        <v>html</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Home 13 Nov Two-Days WORKSHOP ON IMPLEMENTATION OF NEP 2020 15.11.2021 and 16.11.2021 VENUE: Auditoruim 1- B. S Narayan Platinum Jubilee Block Click here to view the BROCHURE and SCHEDULE Day &amp; Date Time Programme MONDAY 15.11.2021 10:00 am -10:30 am Inauguration of the Workshop 10:30 am -11:00 am Coffee Break 11:00 am to 12 Noon Governance Practices of NEP 2020 by Dr Karisiddappa-Hon’ble Vice Chancellor-VTU 12 Noon to 1:00 pm Overview of Outcomes Based Eduction (OBE) by Dr R V Ranganath, Professor, Civil Engg.B.M.S.C.E 1:00 pm to 2:00 pm Lunch Break 2:00 pm to 3:30 pm Models for Implementation of NEP 2020-Domain Specific** 3:30 pm to 4:00 pm High Tea TUESDAY 16.11.2021 10:30 am to 11:30 am Preparations of Institute Development Programme (IDP) by Dr L Ravikumar, Professor, Mechanical Engg. B.M.S.C.E 11:30 am to 12 Noon Coffee Break 12 Noon to 1:00 pm Ability Enhancement Course 1:00 pm to 2:00 pm Lunch Break 2:00 pm to 3:30 pm Panel Discussion 3:30 pm to 4:00 pm High Tea ** BOS Chairpersons for VTU- Deliberations with reference to First Year B.E. syllabus (2021- 2022) Dr. Khaji Fakruddin-Engineering Physics, Engineering Chemistry and Engineering Mathematics Dr. M K Venkatesha- Basic Electronics Dr. H Sudharshan Reddy/Dr V Keshvamurthy- Basic Electrical Engineering Dr. K B Prakash-Elements of Civil Engineering and Mechanics Dr. Katti Vadiraj-Elements of Mechanical Engineering Dr. K S Shreedhara-Computer Programming Dr. Thimmesh-Communicative English Dr. H S Dayanand-Professional Writing Skills in English Google Form Link for Registration https://forms.gle/2eUZ8uhHQXoLqmd89 Back to All News</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127" t="str">
+        <v>2026-03-19T18:36:10.929Z</v>
+      </c>
+      <c r="F127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>https://bmsce.ac.in/home/news/1/international-conference-on-power-control-and-sustainable-energy-systems-28th-30th-july-2022</v>
+      </c>
+      <c r="B128" t="str">
+        <v>html</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Home 06 Nov International Conference on Power, Control and Sustainable Energy Systems 28th – 30th JULY 2022. International Conference on Power, Control and Sustainable Energy Systems (28th– 30th JULY 2022) B.M.S. College of Engineering, Bengaluru www.icpcses2022.org. We are pleased to inform you that the International Conference on Power, Control and Sustainable Energy Systems (ICPCSES-2022) is being organized by the Department of Electrical and Electronics Engineering, B.M.S. College of Engineering, Bengaluru, Karnataka, India during 28th– 30th JULY 2022. All accepted, registered and presented papers in the conference will be published in the River Publication (Scopus indexed). We invite you to submit your manuscript and participate in this international conference and make this event a huge success. Please circulate this email among faculties, scientists, researchers and students and encourage maximum participation in ICPCSES-2022. IMPORTANT DATES Last date for paper submission 31st March 2022 Notification of acceptance 31st May 2022 Submission of camera ready paper 15th June 2022 Early Bird registration 30th June 2022 Last date for Author registration 10th July 2022 Conference dates 28th -30th July 2022 Click here to view the brochure For further details, please visit the conference web link: www.icpcses2022.org. Link for the paper submission is attached for the reference: https://cmt3.research.microsoft.com/ICPCSES2022 Thanks and Regards, Conference Chair (ICPCSES-2022) Back to All News</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128" t="str">
+        <v>2026-03-19T18:36:11.546Z</v>
+      </c>
+      <c r="F128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>https://bmsce.ac.in/home/news/1/virtual-education-series-industry-40-real-life-implementation-case-studies-25th-september-2021-saturday-1130-am-to-0130-pm</v>
+      </c>
+      <c r="B129" t="str">
+        <v>html</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Home 24 Sep Virtual Education Series - Industry 4.0 Real Life Implementation Case Studies 25th September 2021 Saturday - 11:30 am to 01.30 pm Virtual Education Series - Industry 4.0 Real Life Implementation Case Studies 25th September 2021 Saturday - 11:30 am to 01.30 pm To View the Brochure - Click Here Back to All News</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129" t="str">
+        <v>2026-03-19T18:36:12.184Z</v>
+      </c>
+      <c r="F129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-week-online-fdp-program-on-recent-advances-in-cfd-its-applications-from-27th-to-01st-october-2021</v>
+      </c>
+      <c r="B130" t="str">
+        <v>html</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Home 20 Sep One week online FDP program on " Recent Advances in CFD &amp; Its Applications" from 27th to 01st October 2021 The Department of Mechanical Engineering in association with the ISTE-BMSCE chapter is organizing a One-week faculty development program on "Recent Advances in CFD and Its Applications" from 27th September to 01st October 2021. To View, the Brochure - Click Here Back to All News</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130" t="str">
+        <v>2026-03-19T18:36:12.881Z</v>
+      </c>
+      <c r="F130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>https://bmsce.ac.in/home/news/1/analog-signal-processing-concepts-using-python-15th-to-30th-september-2021</v>
+      </c>
+      <c r="B131" t="str">
+        <v>html</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Home 09 Sep Analog Signal Processing Concepts using Python - 15th to 30th September 2021. Analog Signal Processing Concepts using Python - 15th to 30th September 2021. To view the Brochure - Click here Back to All News</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131" t="str">
+        <v>2026-03-19T18:36:13.492Z</v>
+      </c>
+      <c r="F131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>https://bmsce.ac.in/home/news/1/2-week-online-internship-on-simulation-tools-for-engineering-applications-6th-18th-september-1</v>
+      </c>
+      <c r="B132" t="str">
+        <v>html</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Home 02 Sep 2 Week online Internship on Simulation Tools for Engineering Applications - 6th - 18th September 2021 2 Week online Internship on Simulation Tools for Engineering Applications - 6th - 18th September 2021 To view the brochure - Click Here Back to All News</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132" t="str">
+        <v>2026-03-19T18:36:14.133Z</v>
+      </c>
+      <c r="F132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>https://bmsce.ac.in/home/news/1/virtual-series-of-lectures-on-digital-transformation-in-industries-for-students</v>
+      </c>
+      <c r="B133" t="str">
+        <v>html</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Home 02 Sep Virtual Series of Lectures on 'Digital Transformation' in Industries for students. To view the Brouchre - Click Here The professional body with which Electronics and Instrumentation Engg, BMSCE is a part of, International Society of Automation (ISA) Bangalore in association with BMSCE and other student sections of ISA Bangalore, has come out with a Virtual Series of Lectures on 'Digital Transformation' in Industries. Students from different disciplines can participate in this series which will be conducted on Saturdays, get certificates from ISA Bangalore and also get to meet various industry experts through this virtual series. Back to All News</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133" t="str">
+        <v>2026-03-19T18:36:14.755Z</v>
+      </c>
+      <c r="F133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>https://bmsce.ac.in/home/news/1/aicte-invites-all-students-and-faculty-to-observe-30th-august-to-4th-september-as-yuwaah-echoes-by-young-warrior-filled-with-knowledge-sessions-talks-presentations-competitions-and-challenges</v>
+      </c>
+      <c r="B134" t="str">
+        <v>html</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Home 24 Aug AICTE Invites all students and faculty to observe 30th August to 4th September as YuWaah Echoes – by Young Warrior filled with knowledge sessions, talks, presentations, competitions and challenges. Greetings from AICTE, UNICEF and YuWaah ..!! Brochure - Click Here This is in continuation with AICTE’s communication on Young Warrior Movement on 1st June 2021, and its subsequent launch for AICTE affiliated institutions on 12 July, 2021. AICTE has partnered with UNICEF- YuWaah and 1350+ other collation partners and launched the Young Warrior movement for AICTE affiliated institutions on 12th August, 2021. The Young Warrior movement enables young people to take action against COVID-19 and cumulatively impact the lives of millions of people within their families and communities. Since May 2021, more than 6.6 million actions have been taken by young people under the Young Warrior movement. To involve students of AICTE affiliated institutions in a meaningful and engaging way, for actions against COVID 19, AICTE invites all institutions to observe 30th September 2021 to 4th Sep 2021 as YuWaah Echoes – by Young Warrior filled with knowledge sessions, talks, presentations, competitions and challenges. This is as an opportunity by individual institutions to engage students to take part in a unique learning and experiential journey around COVID 19, by expressing, innovating, learning, changemaking and building resilience. Students who complete one or more of the below mentioned activities will earn a certificate from UNICEF. All the winners of the above challenges will be recognized by UNICEF on a national platform. Students start by taking a pledge to ensure that they will observe and amplify COVID-appropriate behaviours. After the pledge, they will have an opportunity to engage in the following: • Solve-A-thon: An innovation challenge for the Youth on COVID 19 • Artists Unite: Hybrid space for youth to self-expression through art • COVID Academy: Attend knowledge building sessions around COVID 19 • Quiz Masters: A multilevel quiz on COVID 19 The registration link for all students and faculty is available through the QR code below (or follow - https://www.yuwaah.org/yuwaah-echoes). There is no limit of participation per institution and students can participate in one or more activities of their interest. AICTE encourage all institutions to promote and inform about YuWaah Echoes – by Young Warrior to all students along with banners and social media posts over website and social pages, indicative creative is attached below. Statutory information: Students and Faculty are strictly advised to follow COVID appropriate behavior at all times while engaging with any activity or task under this initiative. All activities, including pledging, will be performed at the safety of your homes. Best regards, Manoj Singh, Assistant Director (eGovernance), All India Council for Technical Education, Nelson Mandela Marg, Vasant Kunj, New Delhi-110070 Ph 011-29581330 Back to All News</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134" t="str">
+        <v>2026-03-19T18:36:15.386Z</v>
+      </c>
+      <c r="F134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>https://bmsce.ac.in/home/news/1/two-week-online-internship-on-multisim-between-23-08-2021-and-04-09-2021</v>
+      </c>
+      <c r="B135" t="str">
+        <v>html</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Home 23 Aug Two week online Internship on MULTISIM between 23-08-2021 and 04-09-2021. Two week online Internship on MULTISIM between 23-08-2021 and 04-09-2021. Brochure -Click here to view Back to All News</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135" t="str">
+        <v>2026-03-19T18:36:15.995Z</v>
+      </c>
+      <c r="F135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>https://bmsce.ac.in/home/news/1/python-bootcamp-a-36-hour-learn-a-thon-starts-at-1100-am-on-the-28th-of-august-2021</v>
+      </c>
+      <c r="B136" t="str">
+        <v>html</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Home 21 Aug Python Bootcamp. A 36 Hour Learn-A-Thon starts at 11:00 am on the 28th of August 2021. Title: Python Bootcamp. A 36 Hour Learn-A-Thon starts at 11:00 am on the 28th of August 2021. POSTER:- CLICK HERE Content: ISCB (IUCEE Student Chapter of BMSCE) and BS Narayan Centre for Advanced Learning and Software Development brings to you “Python Bootcamp”, open to all the students of BMSCE, on the 28th and 29th August, 2021 (Saturday and Sunday). This bootcamp is aimed to enable students to understand, grasp and discover the concepts involved in the basics of Python Programming and inculcate in them a streak for computational thinking. This bootcamp will employ a Problem Based Learning approach with the help of hands-on activities. The bootcamp is designed for absolute beginners in Python. The Bootcamp will be self-paced, meaning students can join in and do the activities as per their convenience and comfort, in the allotted 36 hours of time. Student volunteers would be present at all times to enable the learning of participants during the course of this Bootcamp. Starting at 11 AM, 28th August, 2021, the bootcamp will conclude at 11 PM, 29th August, 2021, covering a time-span of 36 hours. Registration fees for the same will be ₹100/- per participant. Hurry up and register through the link given below: https://events.iucee-bmsce.live/python-bootcamp Want to know more about ISCB? Visit our website! https://iucee-bmsce.live/aboutus Back to All News</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="E136" t="str">
+        <v>2026-03-19T18:36:16.609Z</v>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>https://bmsce.ac.in/home/news/1/hands-on-workshop-on-up-running-in-aws-saturdays-03072021-10072021-17072021-and-24072021-from-200-pm-to-430-pm</v>
+      </c>
+      <c r="B137" t="str">
+        <v>html</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Home 28 Jun Hands-on Workshop on " Up &amp; Running in AWS" Saturdays ( 03/07/2021, 10/07/2021, 17/07/2021 and 24/07/2021) from 2:00 PM to 4:30 PM.) Greetings from B S Narayan Centre For Advanced Learning and Software Development. (Brochure - Click here) B S Narayan Centre For Advanced Learning and Software Development in collaboration with Dept. of Computer Applications, BMSCE organizing a workshop on "Up and Running in AWS". The workshop will be conducted only on Saturdays ( 03/07/2021, 10/07/2021, 17/07/2021 and 24/07/2021) from 2:00 PM to 4:30 PM.) Cloud Computing - AWS ( Amazon Web Services ) skills are in high demand for all industries. As per a recent survey, 81% of all enterprises are using the cloud for various operations. The workshop will be useful for the UG/PG students of Computer Science Engineering(CSE), Information Science Engineering(ISE), Electronics and Communication Engineering (ECE) Telecommunication Engineering(TCE) and Master of Computer Applications(MCA). Participants will get digital certificates who have cleared the test/assignment. Registration Link: https://forms.gle/bBUYBN2CdSPUTDFcA WhatsApp Group Link: https://chat.whatsapp.com/CJxOBJaxMA65w8P95fLcUy Registration fee : Rs 100/-( Per 8 hours ) Regards B.S Narayan Centre for Advanced Learning and Software Development BMS College of Engineering Bull Temple Road, Bengaluru e-mail : bsncentre@bmsce.ac.in Mob : 8618970874 Back to All News</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137" t="str">
+        <v>2026-03-19T18:36:17.236Z</v>
+      </c>
+      <c r="F137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>https://bmsce.ac.in/home/news/1/online-24-hour-hackathon-ode-to-codeon5th-june-2021-saturday-organized-by-cse-bmsce-in-association-with-riskcovry</v>
+      </c>
+      <c r="B138" t="str">
+        <v>html</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Home 27 May Online 24-hour Hackathon - "Ode to Code" on 5th June 2021 (Saturday) organized by CSE, BMSCE in association with Riskcovry The Department of CSE, B.M.S. College of Engineering in association with Riskcovry is organizing a 24-hour virtual (Online) Hackathon - "Ode to Code" on 5th June 2021 (Saturday). To view the brochure Click Here The problem statement will be provided by Riskcovry. Exciting prizes as well as Internship opportunities for winners. Team size: 2-4 members Attached below is the Poster for the Hackathon and you can also find the details of the Hackthona at the Dare2Compete website link mentioned below for registration. Please circulate among your friends too. Hurry up and register soon! Register at D2C: https://dare2compete.com/o/ode-to-code-riskcovry-167230?utm_campaign=site-emails&amp;utm_medium=site-emails&amp;utm_source=ode-to-code-goes-live-on-dare2compete The rules of the event are as follows: Team size: 2-4 Members. Third and fourth-year B.E./B.Tech. or M.Tech students are eligible to take part in the competition. One participant cannot be a part of more than one team. The problem statement will be shared at the beginning of the competition. Teams will then submit their solution based on which the finalists would be selected. The finalists will then present their solution in front of the panel. There would be small quizzes and games during the competition, the winners of which will get exciting prizes. If a team or a team member is found guilty of fraudulent conduct, the team will be disqualified from the competition. The decision of the judging panel and organizing body of the event will be final and binding in all matters. Back to All News</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138" t="str">
+        <v>2026-03-19T18:36:17.856Z</v>
+      </c>
+      <c r="F138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>https://bmsce.ac.in/home/news/1/international-conference-on-operations-management-systems-business-analytics-comsb-on-26th-march-2021</v>
+      </c>
+      <c r="B139" t="str">
+        <v>html</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Home 19 Feb International Conference on Operations Management, Systems &amp; Business Analytics (COMSB) on 26th March 2021 We are happy to inform you that the Department of Industrial Engineering &amp; Management, B.M.S. College of Engineering, Bengaluru in association with Rajagiri Business School &amp; Rajagiri College of Social Sciences, (Autonomous), Kochi, Kerala along with IISE, IIT Kharagpur Students Chapter, Kharagpur, India are organizing online international conference on “Operations Management, Systems and Business Analytics” on 26th March 2021. Click here to view the brochure. The interested participants also submit scientific abstracts on https://easychair.org/cfp/OMSBA2021. The last date for abstract submission is on 10th March 2021. Dr. B. Ramesh Nayak Associate Professor and Head Department of Industrial Engineering and Management Back to All News</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139" t="str">
+        <v>2026-03-19T18:36:18.512Z</v>
+      </c>
+      <c r="F139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>https://bmsce.ac.in/home/news/1/talk-by-padma-sri-dr-sudha-murty-chairperson-of-infosys-foundation-a-prolific-writer-and-social-worker-to-address-the-75th-batch-of-engineering-students-on-12022021-at-1100-am-1</v>
+      </c>
+      <c r="B140" t="str">
+        <v>html</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Home 10 Feb Talk by Padma Sri Dr. Sudha Murty, Chairperson of Infosys Foundation a Prolific Writer and Social Worker to address the 75th batch of Engineering students on 12.02.2021 at 11.00 AM. Talk by Padma Sri Dr. Sudha Murty, Chairperson of Infosys Foundation a Prolific Writer and Social Worker to address the 75th batch of Engineering students on 12.02.2021 at 11.00 AM. Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140" t="str">
+        <v>2026-03-19T18:36:19.114Z</v>
+      </c>
+      <c r="F140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-week-online-sttp-on-reo-amst-2021-renewable-energy-options-in-developing-countries-with-advanced-materials-and-scientific-tools-from-8th-to-13th-march-1</v>
+      </c>
+      <c r="B141" t="str">
+        <v>html</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Home 09 Feb One week online STTP on " REO-AMST-2021”, “Renewable Energy options in developing countries with Advanced Materials and Scientific Tools " from 8th to 13th March , 2021. The Department of Civil Engineering, BMSCE, is conducting a one week online STTP on " REO-AMST-2021”, “Renewable Energy options in developing countries with Advanced Materials and Scientific Tools " from 8th to 13th March , 2021. Click here to view the Brochure Click here to view the Program Schedule Back to All News</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141" t="str">
+        <v>2026-03-19T18:36:19.735Z</v>
+      </c>
+      <c r="F141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-week-faculty-development-program-fdp-on-functional-materials-for-engineering-applications-15-02-2021-to-19-02-1</v>
+      </c>
+      <c r="B142" t="str">
+        <v>html</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Home 05 Feb One Week Faculty Development Program (FDP) on Functional Materials for Engineering Applications -15-02-2021 to 19-02-2021 The Department of Chemistry and Physics, B.M.S. College of Engineering is organizing, One Week Faculty Development Program (FDP) on Functional Materials for Engineering Applications, from 15-2-2021 to 19-2-2021. sponsored by the centre of excellence in Advanced Materials Research. (TEQIP-1.2.1) The registration link is as follows. https://docs.google.com/forms/d/e/1FAIpQLSfd6YkywCFMrtFQLlxpR9ZnsMUzt03_U6GDXTr39lKfrsrXBg/viewform?usp=sf_link Click here to view the brochure. Back to All News</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142" t="str">
+        <v>2026-03-19T18:36:20.373Z</v>
+      </c>
+      <c r="F142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>https://bmsce.ac.in/home/news/1/vetomac-xvi-16th-international-conference-on-vibration-engineering-and-technology-of-machinery-on-1618-december-2021</v>
+      </c>
+      <c r="B143" t="str">
+        <v>html</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Home 22 Jan VETOMAC - XVI 16th International Conference on Vibration Engineering and Technology of Machinery on 16–18 December 2021. About the conference: The first International Conference on Vibration Engineering and Technology of Machinery (VETOMAC) was organized at IISc Bangalore, India, in the year 2000 with the intention of encouraging scientific and technical cooperation and exchange across the globe. The 16th VETOMAC will be held at B. M. S College of Engineering, Bengaluru, India, during 16th to 18th December 2021. This conference is the sixteenth in the series of annual symposia that started in Bengaluru, India (2000), and were subsequently held in Mumbai, India (2002), Kanpur, India (2004), Hyderabad, India (2007), Wuhan, China (2009), New Delhi, India (2010), Hong Kong (2011), Vaddeswaram, India (2012), Nanjing, China (2013), United Kingdom (2014), Taiwan (2015), Polland (2016), Queensland, Australia (2017), Lisbon, Portugal (2018), and Curitiba, Brazil (2019). This conference has emerged as a popular international forum to promote vital exchange of knowledge, ideas and information on the state of the art developments and applied technologies of concurrent machinery dynamics related problems in mechanical, automotive and aerospace domains. The conference includes invited keynote lectures by distinguished experts from across the globe. There will be plenary and keynote sessions and a large number of parallel technical sessions spread over the conference period. It will bring together researchers and practitioners from academia, research institutions and industry to exchange experiences, disseminate information, and explore new opportunities in this domain. The organizers believe that the 16th Vibration Engineering and Technology of Machinery (VETOMAC-2021) will stimulate researchers while furthering cooperation among investigators in the field of machinery dynamics. To View the Brochure - Click Here For more details, visit https://vetomac.com/ E-Mail: vetomac2021@bmsce.ac.in Website: https://vetomac.com/ Abstract Submission: https://ocs.springer.com/misc/home/VETOMAC2021 Back to All News</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143" t="str">
+        <v>2026-03-19T18:36:21.003Z</v>
+      </c>
+      <c r="F143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>https://bmsce.ac.in/home/news/1/level-one-c-programming-bootcamp-is-being-conducted-by-the-department-of-cse-and-ece-for-the-first-year-ug-students-on-the-23rd-and-24th-of-january-1</v>
+      </c>
+      <c r="B144" t="str">
+        <v>html</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Home 21 Jan Level One C Programming Bootcamp, is being conducted by the department of CSE and ECE, for the first-year UG students on the 23rd and 24th of January 2021.” This Bootcamp is aimed at enabling students to understand, grasp and discover the concepts involved in the basics of C Programming and inculcate in them a streak for computational thinking. It would be an interactive, self-paced and activity based Bootcamp which would focus on self-enabled learning and would provide a headstart to your programming journey. This Bootcamp is designed in such a way that it can accommodate both absolute beginners and experienced coders. The Bootcamp will begin at 3:00 pm on 23rd January 2021 (Saturday) and will continue up to 9:00 pm on the 24th of January 2021 (Sunday). The Bootcamp will be self-paced, meaning students can join in and do the activities as per their convenience and comfort, in the allotted 30 hours of time. Student volunteers would be present at all times to enable the learning of participants during the course of this Bootcamp. The registrations are limited and are based on a first-come-first-serve plus evaluation basis. The registration link is attached herewith: https://forms.gle/oqpUwxvFNzBHB9aRA Click here to view the Brochure Students are encouraged to participate in this Bootcamp and make the most out of it. Back to All News</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144" t="str">
+        <v>2026-03-19T18:36:21.651Z</v>
+      </c>
+      <c r="F144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>https://bmsce.ac.in/home/news/1/justvend-smart-app-based-vending-machine-developed-by-bms-students</v>
+      </c>
+      <c r="B145" t="str">
+        <v>html</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Home 13 Jan JustVend: Smart App based vending machine developed by BMS students. Click here to watch the video. JustVend is a touchless, cashless and IoT enabled smart vending machine. The vending machine is operated by a mobile application called JustVend App. The whole product is a combination of hardware (involving logical circuits, IoT enabled systems, mechanical concepts of machine design) and software(involving application development for android &amp; IOS devices) developed by ShivamVaish, currently 5th semester Computer Science bearing USN 1BM18CS152 and Nikhil DS, currently 5th semester, Information Science bearing USN 1BM18IS144. Machine learning is implemented to predict the inventory depending on the demand. Thestartup aims at solving the problems faced by students during the break time. Usually it takes 15-20 minutes for the students to get a quick snack from canteen but from theJustVend vending machine it takes 15-20 seconds. The user can order from anywhere within the campus and collect the order from the nearest vending machine. The user can also pre-order/reserve the item in the vending machine for a certain period of time. The startup has implemented digital payments in the application making the payment options simple and easy. The whole process is seamless and all these features help the user to save a lot of time. It is made cashless, touchless and there’s almost zero human intervention involved and completely automated. So everybody can use the vending machine amidst the pandemic also. The startup is supporting AatmaNirbhar Bharat and Vocal for local in making a self-reliant India. Back to All News</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145" t="str">
+        <v>2026-03-19T18:36:22.266Z</v>
+      </c>
+      <c r="F145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>https://bmsce.ac.in/home/news/1/department-of-mathematics-and-humanities-is-organizing-a-two-days-webinar-on-skill-set-and-stress-management-on-11th-12th-january-2021-from-500-to-630-pm-1</v>
+      </c>
+      <c r="B146" t="str">
+        <v>html</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Home 07 Jan Department of Mathematics and Humanities is organizing a Two-Days Webinar on Skill-set and Stress Management on 11th &amp; 12th, January 2021 from 5.00 to 6.30 PM Department of Mathematics and Humanities is organizing a Two-Days Webinar on Skill-set and Stress Management on 11th &amp; 12th, January 2021 from 5.00 to 6.30 PM. Click here to download the brochure Back to All News</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146" t="str">
+        <v>2026-03-19T18:36:22.866Z</v>
+      </c>
+      <c r="F146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>https://bmsce.ac.in/home/news/1/blockchain-decentralized-application-development-hands-on-from-27th-january-to-2nd-february-2021</v>
+      </c>
+      <c r="B147" t="str">
+        <v>html</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Home 02 Jan Blockchain &amp; Decentralized Application Development (Hands-on)" from 27th January to 2nd February 2021 The department of CSE and ISE, BMSCE is organizing a one-week online FDP on "Blockchain &amp; Decentralized Application Development (Hands-on)" from 27th January to 2nd February 2021". Herewith I am attaching the brochure of the FDP. Registration Link: https://forms.gle/QzJb1agh9Ufotqy28 Brochure Download - Click here Registration Fees: Rs. 100/- Faculty coordinators for this on-line FDP are Prof.Saritha A. N, Dept of CSE, BMSCE and Prof. Sreelatha R, Dept of ISE, BMSCE. We have taken permission from the Principal, to organize this FDP. Back to All News</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147" t="str">
+        <v>2026-03-19T18:36:23.488Z</v>
+      </c>
+      <c r="F147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>https://bmsce.ac.in/home/news/1/inauguration-of-techbarath-hackthon-2021-0n-30-12-2020-3-pm</v>
+      </c>
+      <c r="B148" t="str">
+        <v>html</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Home 29 Dec Inauguration of Techbarath Hackthon 2021 0n 30-12-2020 @ 3 PM B.S. Narayan Centre For Advanced Learning and Software Development, BMSCE in association with TechBharat inviting you for TechBarath National Hackathon inauguration 30/12/2020 at 3.00PM Please register for inauguration using the following link https://hackathon.techbharat.org.in/ Back to All News</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148" t="str">
+        <v>2026-03-19T18:36:24.115Z</v>
+      </c>
+      <c r="F148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>https://bmsce.ac.in/home/news/1/ugpg-online-admission-registration-for-the-ay-2020-21-cetcomed-kmgtgoipmsspiodcetpgcet</v>
+      </c>
+      <c r="B149" t="str">
+        <v>html</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Home 02 Dec UG/PG Online Admission Registration for the AY 2020-21 (CET/COMED-K/MGT/GOI/PMSS/PIO/DCET/PGCET) UG/PG Online Admission Registration for the AY 2020-21 - Click Here (CET/COMED-K/MGT/GOI/PMSS/PIO/DCET/PGCET) Back to All News</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149" t="str">
+        <v>2026-03-19T18:36:24.739Z</v>
+      </c>
+      <c r="F149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>https://bmsce.ac.in/home/news/1/two-day-online-workshop-for-faculties-on-virtual-lab-23112020-and-24112020</v>
+      </c>
+      <c r="B150" t="str">
+        <v>html</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Home 21 Nov Two day online Workshop for faculties on Virtual Lab - 23.11.2020 and 24.11.2020 Two day online Workshop for faculties on Virtual Lab - 23.11.2020 and 24.11.2020. Click here for more details Back to All News</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150" t="str">
+        <v>2026-03-19T18:36:25.352Z</v>
+      </c>
+      <c r="F150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>https://bmsce.ac.in/home/news/1/implementation-plan-on-nep-2020-on-mygov-portal-seeking-suggestionsfeedbacks-date-extended-31102020</v>
+      </c>
+      <c r="B151" t="str">
+        <v>html</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Home 01 Oct Implementation Plan on NEP 2020 on MyGov portal seeking suggestions/feedbacks-Date Extended 31.10.2020 After announcement of NEP 2020 a detailed consultation process with various stakeholders is underway to finalise the Implementation Plan. As a part of the consultation process, an outline of the Implementation Plan covering the Actionable Points and associated activities as envisioned in the NEP 2020 has been prepared and the same has been shared with various stakeholders including States / UTs for seeking suggestions/feedbacks on the implementation of NEP 2020. In this regard, it has been decided by the Department of Higher Education, Ministry of Education, GoI to use the MyGov platform for inviting suggestions/feedbacks from the stakeholders on the outline of Implementation Plan on NEP 2020. Discussion on an outline of the Implementation Plan on NEP, 2020 is live on MyGov Portal at the link: https://innovateindia.mygov.in/nep2020-citizen/ The last date to submit feedback currently till 18.10.2020, is proposed to be extended till 31.10.2020. It is requested that the institution may be give wide publicity amongst the faculty members and other stakeholders encouraging to give their suggestions/feedbacks on MyGov portal. Back to All News</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151" t="str">
+        <v>2026-03-19T18:36:26.034Z</v>
+      </c>
+      <c r="F151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>https://bmsce.ac.in/home/news/1/fdp-on-aicte-atal-on-waste-technologies-wealth-from-waste-from-23-to-27th-november-1</v>
+      </c>
+      <c r="B152" t="str">
+        <v>html</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Home 09 Sep FDP on AICTE- ATAL on Waste Technologies - Wealth From Waste from 23 to 27th November 2020 FDP on AICTE- ATAL on Waste Technologies - Wealth From Waste from 23 to 27th November 2020. To View the Brochure - Click Here Back to All News</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="E152" t="str">
+        <v>2026-03-19T18:36:26.656Z</v>
+      </c>
+      <c r="F152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-week-online-value-added-course-on-emerging-technologies-industry-perspectives-from-4th-to-10th-september-2020</v>
+      </c>
+      <c r="B153" t="str">
+        <v>html</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Home 01 Sep One week Online Value-added Course on "Emerging Technologies: Industry Perspectives" from 4th to 10th September 2020 We are conducting a one-week online Value-added course on "Emerging Technologies: Industry Perspectives" from 4th to 10th September 2020. Registration Link is here: https://forms.gle/DMww5iVMFkFcCEeh6 To View the Brochure - Click Here *Registration Fee: UG/PG students/Full-time Research scholars: Rs. 100/- Faculty: Rs. 150/- Industry Personnel: Rs. 200/- Account No: 20274180376 Account Name: HOD-ECE Bank Name: Indian Bank (Allahabad Bank) B.M.S.C.E Campus, Hanumanthnagar, Bengaluru 560019. IFSC Code: ALLA0212011 E-certificate will be provided to the participants who attend the programme. Coordinators: Dr. Rajanikanth K N, Email: rajanikanthnkashi.ece@bmsce.ac.in, M: 9880424584. Prof. Madhusudhan K. N, Email: madhusudhankn.ece@bmsce.ac.in, M: 9845409693. Back to All News</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153" t="str">
+        <v>2026-03-19T18:36:27.301Z</v>
+      </c>
+      <c r="F153">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>https://bmsce.ac.in/home/news/1/webinar-on-cross-platform-mobile-app-development-webinar-08092020-1130-am</v>
+      </c>
+      <c r="B154" t="str">
+        <v>html</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Home 02 Sep Webinar on Cross Platform Mobile App Development Webinar - 08/09/2020 @ 11.30 am Webinar on Cross Platform Mobile App Development Webinar - 08/09/2020 @ 11.30 am HIGHLIGHTS - DEMAND OF FLUTTERIN THEMARKET - E-CERTIFICATEWILL BEPROVIDED - FREEREGISTRATION REGISTRATION LINK : https://forms.gle/QB6mwCbb99H8wAFd8 To view the brochure : Click Here Back to All News</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154" t="str">
+        <v>2026-03-19T18:36:27.942Z</v>
+      </c>
+      <c r="F154">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>https://bmsce.ac.in/home/news/1/aictetrainingandlearning-atal-academyonline-faculty-development-programme-fdponprospects-and-challenges-in-3d-printing-a-design-perspective-01092020-to-05092020</v>
+      </c>
+      <c r="B155" t="str">
+        <v>html</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Home 29 Aug AICTE Training And Learning (ATAL) Academy Online Faculty Development Programme (FDP) On “Prospects and Challenges in 3D Printing: A Design Perspective” -01/09/2020 to 05/09/2020 AICTE Training And Learning (ATAL) Academy Online Faculty Development Programme (FDP) On “Prospects and Challenges in 3D Printing: A Design Perspective” to be held from 01st September 2020 to 05th September 2020. To view the brochure - Click Here To Register - Click Here Back to All News</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="E155" t="str">
+        <v>2026-03-19T18:36:28.558Z</v>
+      </c>
+      <c r="F155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>https://bmsce.ac.in/home/news/1/ieee-ssit-es-joint-chapter-bangalore-section-is-organizing-an-online-lecture-on-sociological-psychological-issues-and-possible-remedies-during-covid-19-on-29082020-at-11am</v>
+      </c>
+      <c r="B156" t="str">
+        <v>html</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Home 22 Aug IEEE-SSIT-ES Joint Chapter Bangalore Section is Organizing an Online Lecture on “Sociological, Psychological Issues and Possible Remedies During COVID-19” on 29/08/2020 at 11AM Greetings from BMS College of Engineering &amp; IEEE-SSIT-ES Joint Chapter, Bangalore Section!!! I am happy to inform that Department of Electrical &amp; Electronics Engineering, BMS College of Engineering in association with Bangalore Institute of Technology (BIT) &amp; IEEE-SSIT-ES Joint Chapter Bangalore Section is Organizing an Online Lecture on “Sociological, Psychological Issues and Possible Remedies During COVID-19” on 29th August 2020 at 11 AM. We will be sharing the online link for the lecture on 28th August 2020. Click here to view the Poster Back to All News</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="E156" t="str">
+        <v>2026-03-19T18:36:29.164Z</v>
+      </c>
+      <c r="F156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>https://bmsce.ac.in/home/news/1/value-added-course-on-challenges-and-opportunities-in-the-semiconductor-industry-from-10th-to-14th-august-2020</v>
+      </c>
+      <c r="B157" t="str">
+        <v>html</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Home 06 Aug Value-added Course on "Challenges and Opportunities in the Semiconductor Industry" from 10th to 14th August 2020 The Department of Electronics and Communication Engineering in association with the Institution of Electronics and Telecommunication Engineers (IETE, Bangalore Centre) is organizing a one-week online Value-added Course on "Challenges and Opportunities in the Semiconductor Industry" from 10th to 14th August 2020. Registration link is here: https://forms.gle/qwcD3DhmpgjWZajm7 To View the Brochure: Click Here Registration Fee: UG students: Rs. 100/- PG students/Full-time Research Scholars: Rs. 150/- Faculty: Rs. 200/- payable to the following bank account: Account No: 20274180376 Account Name: HOD-ECE Bank Name: Indian Bank (Allahabad Bank) B.M.S.C.E Campus, Hanumanthnagar, Bengaluru 560019. IFSC Code: ALLA0212011 E-certificate will be provided to the participants who attend the course. Coordinators: Dr. Rajath Vasudevamurthy, Email: rajathv.ece@bmsce.ac.in, M: 7259520557. Dr. M. Anantha Sunil, Email: sunil.ece@bmsce.ac.in, M: 9480773444. Back to All News</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157" t="str">
+        <v>2026-03-19T18:36:30.002Z</v>
+      </c>
+      <c r="F157">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>https://bmsce.ac.in/home/news/1/guest-lecture-on-national-education-policy-2020-from-the-perspective-of-higher-education-05082020-230-pm</v>
+      </c>
+      <c r="B158" t="str">
+        <v>html</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Home 05 Aug Guest Lecture on National Education Policy 2020 - from the perspective of Higher Education - 05/08/2020 @ 2.30 pm The Office of Dean Academics is organizing an online lecture on "National Education Policy 2020 - from the perspective of Higher Education" on 05.08.2020 at 2.30 PM delivered by Dr. Leena Chandran Wadia. Dr. Leena Chandran Wadia. Senior Fellow, Observer Research Foundation Mumbai, Senior Consultant, Committee on National Education Policy, Govt. of India Dr. Leena Chandran Wadia is a Senior Fellow at the Observer Research Foundation (ORF), Mumbai, member of the drafting committee of the policy of India’s Draft National Education Policy 2019. It is proud to mention that Dr. Leena Wadia is also one of the members of our Academic Council. The link for registering for the Guest Lecture is provided below: Link: https://forms.gle/cjyHu8verPQCRiNMA Click Here for the Guest Lecture Details Back to All News</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158" t="str">
+        <v>2026-03-19T18:36:30.636Z</v>
+      </c>
+      <c r="F158">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>https://bmsce.ac.in/home/news/1/admissions-for-mba-programme-for-the-academic-year-2020-21-reg</v>
+      </c>
+      <c r="B159" t="str">
+        <v>html</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Home 01 Oct Admissions for MBA Programme for the Academic Year 2020-21 - Reg Details related to Admissions for MBA Programme for the Academic Year 2020-21. The Approved Management Fee Structure for the academic year 2020-21 is Rs. 2,50,000/- Per year. MBA Admission information - Click here MBA Admission application form - Click here Back to All News</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159" t="str">
+        <v>2026-03-19T18:36:31.253Z</v>
+      </c>
+      <c r="F159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-week-faculty-development-programme-on-python-programming-24th-to-29th-august-2020</v>
+      </c>
+      <c r="B160" t="str">
+        <v>html</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Home 29 Jul One week Faculty Development Programme on Python Programming - 24th to 29th August, 2020 "Online One week Faculty Development Programme on Python Programming" to be conducted from 24th to 29th August 2020 in association with spoken tutorials, IIT Bombay. Click here to view the brochure Back to All News</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160" t="str">
+        <v>2026-03-19T18:36:31.861Z</v>
+      </c>
+      <c r="F160">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>https://bmsce.ac.in/home/news/1/ieee-online-hands-on-workshop-on-simulation-tools-for-power-converters-and-applications-27th-to-31st-july-2020</v>
+      </c>
+      <c r="B161" t="str">
+        <v>html</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Home 25 Jul IEEE Online Hands-on Workshop on “Simulation tools for Power converters and applications”. - 27th to 31st July 2020 Dept. of Electrical &amp; Electronics Engg, BMSCE in association with IEEE PELS, IES, SSITBangalore Chapters is organizing Online Hands-on Workshop On “Simulation tools for Power converters and applications” from 27th to 31th July 2020. Registration Link: https://docs.google.com/forms/d/e/1FAIpQLSfUfsseR1CuuXw0bV2S_rBmTlFbCDDi4vABP5MRoHshHDXB6w/viewform Click here to view the Brochure Click here to view the Flyer Date: - 27th to 31st July-2020 Time: 10.0 a.m-12.00 p.m &amp; 2p.m. -4.00 p.m The areas of discussion are: 1) Introduction to LTspice:- Magnetic power Converter 2) Introduction to Scilab:-EMTP Coding 3) Simulation of buck Converter and its Compensation techniques:- Tina software 4) - Analytical Modelling of Power Electronic Converter and Drivers Using MATLAB 5) Closed loop control of power converter with different Controller using MATLAB Registration Fee: IEEE MEMBERS-Rs 300 NON IEEE MEMBERS-Rs 500 In case of any query feel free to contact the coordinators, Dr.Prema V :9986041498 Ms.Soniya Agrawal :8792817419 Back to All News</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161" t="str">
+        <v>2026-03-19T18:36:32.481Z</v>
+      </c>
+      <c r="F161">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>https://bmsce.ac.in/home/news/1/fdp-on-iot-and-data-analytics-an-end-to-end-perspective-from-27th-july-to-1st-aug-1</v>
+      </c>
+      <c r="B162" t="str">
+        <v>html</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Home 16 Jul FDP on "IoT and Data Analytics: an End to End perspective" from 27th July to 1st Aug 2020 Department of CSE and ECE, BMSCE is organizing a one-week online FDP on "IoT and Data Analytics: an End to End perspective" from 27th July to 1st Aug 2020. Registration Link: https://forms.gle/Rrepv5MbHvAXX8fNA Registration Fees: Nil To View the Brouchure - Click Here Faculty coordinators for this FDP are Prof.Saritha A N, CSE, BMSCE and Prof. Sanjana T, ECE, BMSCE. Back to All News</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162" t="str">
+        <v>2026-03-19T18:36:33.102Z</v>
+      </c>
+      <c r="F162">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-week-online-fdp-on-matlab-for-mechanical-engineers-from-20th-to-24th-of-july-2020</v>
+      </c>
+      <c r="B163" t="str">
+        <v>html</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Home 13 Jul One week online FDP on "MATLAB for Mechanical Engineers" from 20th to 24th of July 2020 Department of Mechanical Engineering in association with ISTE-BMSCE chapter is conducting a one-week online FDP on "MATLAB for Mechanical Engineers" from 20th to 24th of July 2020. To View, the Brochure - Click Here Back to All News</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163" t="str">
+        <v>2026-03-19T18:36:33.718Z</v>
+      </c>
+      <c r="F163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>https://bmsce.ac.in/home/news/1/admissions-to-be-degree-program-in-artificial-intelligence-and-machine-learning</v>
+      </c>
+      <c r="B164" t="str">
+        <v>html</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Home 01 Sep Admissions to B.E. Degree Program in Artificial Intelligence and Machine Learning Pleased to inform that from the ensuing academic year i.e. 2020-21, AICTE has accorded approval to start undergraduate (B.E.) program in Artificial Intelligence and Machine Learning with an intake of 60 along with PIO quota Click here for the Draft Scheme on Artificial Intelligence and Machine Learning. Click here to know the Fee Details. Back to All News</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164" t="str">
+        <v>2026-03-19T18:36:34.338Z</v>
+      </c>
+      <c r="F164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>https://bmsce.ac.in/home/news/1/protocol-club-is-organizing-protocol-day-2020-from-4th-july-2020-to-5th-july-1</v>
+      </c>
+      <c r="B165" t="str">
+        <v>html</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Home 02 Jul Protocol Club is organizing Protocol Day 2020 from 4th July 2020 to 5th July 2020. Event Name: Protocol Day 2020 Date of the Event: 4-7-2020 to 5-7-2020 Short description of the Event: Department of Computer Science and Engineering in association with Protocol Club is organizing Protocol Day 2020 from 4th July 2020 to 5th July 2020. Registration Link: https://forms.gle/BsuYLW8jD895ttCU9 Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165" t="str">
+        <v>2026-03-19T18:36:34.953Z</v>
+      </c>
+      <c r="F165">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>https://bmsce.ac.in/home/news/1/webinar-oncivil-services-as-a-careeroptionwednesday-1st-july-2020-at-530-pm-700-pm</v>
+      </c>
+      <c r="B166" t="str">
+        <v>html</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Home 01 Jul WEBINAR on "Civil Services As a Career Option", Wednesday , 1st July 2020 at 5:30 PM - 7:00 PM We from COMPETITIVE EXAMINATIONS &amp; HIGHER STUDIES CELL, B. M. S. COLLEGE OF ENGINEERING in association with SHANKAR IAS ACADEMY - Bengaluru, Conducted a WEBINAR on "Civil Services as a Career Option", Wednesday , 1st July 2020 at 5:30 PM - 7:00 PM By Dr. C. Sylendra Babu, DGP, Prisons &amp; Railway Police Force , Tamil Nadu. Click here to View the Brochure Back to All News</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="E166" t="str">
+        <v>2026-03-19T18:36:35.577Z</v>
+      </c>
+      <c r="F166">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>https://bmsce.ac.in/home/news/1/two-week-onlinefdpon-applied-data-science-from-6th-to-17th-july-1</v>
+      </c>
+      <c r="B167" t="str">
+        <v>html</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Home 02 Jul Two-Week Online FDP on "Applied Data Science" from 6th to 17th July 2020 The Department of Electronics and Communication Engineering in association with the Institution of Electronics and Telecommunication Engineers (IETE, Bangalore Centre) is organizing a two-week online FDP on "Applied Data Science" from 6th to 17th July 2020. Registration link is here: https://forms.gle/YFk8ETnvRe6qNxfQ9 To View the Brochure - Click Here *Registration Fee: Rs. 500/- payable to the following bank account: Account No: 20274180376 Account Name: HOD-ECE Bank Name: Indian Bank (Allahabad Bank) B.M.S.C.E Campus, Hanumanthnagar, Bengaluru 560019. IFSC Code: ALLA0212011 E-certificate will be provided to the participants who attend the programme. Coordinators: Dr. M. Anantha Sunil, Email: sunil.ece@bmsce.ac.in, M: 9480773444. Dr. Rajath Vasudevamurthy, Email: rajathv.ece@bmsce.ac.in, M: 7259520557. Back to All News</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167" t="str">
+        <v>2026-03-19T18:36:36.205Z</v>
+      </c>
+      <c r="F167">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>https://bmsce.ac.in/home/news/1/recent-advances-in-heat-transfer-and-its-applications-13thto-17thjuly-2020</v>
+      </c>
+      <c r="B168" t="str">
+        <v>html</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Home 30 Jun "Recent Advances in Heat Transfer and Its Applications" - 13th to 17th July 2020. The Department of Mechanical Engineering in association with ISTE-BMSCE chapter is organizing a One-week faculty development program on "Recent Advances in Heat Transfer and Its Applications" from 13th to 17th July 2020. For Brochure - Click Here Back to All News</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168" t="str">
+        <v>2026-03-19T18:36:36.864Z</v>
+      </c>
+      <c r="F168">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-week-online-fdp-on-climate-change-and-carbon-issues-from-6th-july-to-10th-july-2020</v>
+      </c>
+      <c r="B169" t="str">
+        <v>html</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Home 29 Jun ONE WEEK Online FDP On "Climate change and Carbon Issues" from " 6th July to 10th July 2020" We are very happy to inform you that, Department of Civil Engineering is organizing " ONE WEEK Online FDP" On "Climate change and Carbon Issues" from " 6th July to 10th July 2020" In association with ISTE, IWWA &amp;IGBC For Brochure - Click Here You are requested to use the following link for registration https://forms.gle/16WdSVxybo8tBRVm8 Registration Fee: ISTE/IWWA/ IGBCMembers/ Research scholars Rs.300/- Others Rs.400/ Payable to the following bank account A/C NAME:- HOD CIVIL ENGG BANK :-ALLAHABAD BANK,Hanumanth Nagar, Bangalore A/C NO. 20274181427 BRANCH:- BMSCE campus IFSC: - ALLA0212011 E-Certificate will be issued to all the participants Hard Copy of the Certificate will be sent on request. Mode of Conduction: Go To meeting Co-ordinators: Dr. K Asha, email:asha.civ@bmsce.ac.in, M:9916374887 Prof.T.Deepa, email:deepat.civ@bmsce.ac.in, M: 9108856789 Prof.Nandita Pal, email:nanditap.civ@bmsce.ac.in, M: 7760915245 Prof.Arjun.K, email: arjunk.civ@bmsce.ac.in,M:8722700123 Back to All News</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169" t="str">
+        <v>2026-03-19T18:36:37.532Z</v>
+      </c>
+      <c r="F169">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-week-online-fdp-on-green-energy-from-june-29th-to-july-4th-2020</v>
+      </c>
+      <c r="B170" t="str">
+        <v>html</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Home 25 Jun One Week Online FDP on "GREEN ENERGY" from JUNE 29th to JULY 4th, 2020. Department of Civil Engineering, BMSCE, is conducting a One Week Online FDP on "GREEN ENERGY" from JUNE 29th to JULY 4th, 2020. WGE-2020 Youtube Link - Click Here WGE-2020 Registration Link - Click Here WGE-2020 Invitation - Click Here WGE-2020 Brochure - Click Here Back to All News</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170" t="str">
+        <v>2026-03-19T18:36:38.161Z</v>
+      </c>
+      <c r="F170">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>https://bmsce.ac.in/home/news/1/enhancement-of-curriculum-through-cdio-on-24th-and-25th-june-1</v>
+      </c>
+      <c r="B171" t="str">
+        <v>html</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Home 20 Jun Enhancement of curriculum through CDIO on 24th and 25th June 2020 Two days webinar on "Enhancement of curriculum through CDIO". on 24th and 25th June 2020. Registration Link: https://docs.google.com/forms/d/e/1FAIpQLSdG8YAz0RVRz15QEbTss80B9ZHjVJPej51r-j35TOSDipucgg/viewform?usp=sf_link Click here for Brochure Back to All News</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171" t="str">
+        <v>2026-03-19T18:36:38.781Z</v>
+      </c>
+      <c r="F171">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-week-online-fdp-on-structural-health-monitoring-and-its-implications-15th-19th-june-2020</v>
+      </c>
+      <c r="B172" t="str">
+        <v>html</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Home 12 Jun One - Week Online FDP on Structural Health Monitoring and its Implications -- 15th -19th June 2020 We are very happy to inform you that, *Department of Civil Engineering is organizing *One Week Online FDP on “structural health monitoring and its implications "* from *15th June to 19th June 2020.*in association with ISTE You are requested to use the following link for registration. FDP Brochure -- Click Here One Week FDP Program Details -- Click Here *Registration link:* https://docs.google.com/forms/d/e/1FAIpQLSdNTM_cJEOXKt0jEDjZWyyw66atzUnZ-nSlrYfRSm0E9m5r0A/viewform?usp=sf_link *Registration Fee: Rs. 500 /for Non ISTE &amp; Rs 400 for ISTE members E-Certificate will be issued to all the participants who will attend all the sessions completely. *Account Detail* A/C NAME:- HOD CIVIL ENGG BANK :-ALLAHABAD BANK,Hanumanth Nagar, Bangalore A/C NO. 20274181427 BRANCH:- BMSCE campus IFSC :- ALLA0212011 *Registration Deadline:* 14 June 2020, 8:00PM. After registration, Please join WhatsApp group of this e-FDP for further information. *Link to join WhatsApp Group:-* https://chat.whatsapp.com/DJjov3PMs9y88Sx2HTE6Mv *Mode of Conduction:- Online via Cisco WebEx* Prof. P Prasanna kumar Head, Department of civil Engineering BMSCE, Bangalore *Co-ordinator:* Dr.T Rajanna -- 9900445005 Prof. Vinay M L Gowda --9972971007 Dr. Manjunath R -- 8197203686 Prof. Sandesh N U -- 8951123424 Back to All News</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="E172" t="str">
+        <v>2026-03-19T18:36:39.405Z</v>
+      </c>
+      <c r="F172">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>https://bmsce.ac.in/home/news/1/bmsce-hackathon-beat-the-pandemic-june-5-to-7-1</v>
+      </c>
+      <c r="B173" t="str">
+        <v>html</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Home 10 Jun BMSCE Hackathon: Beat the Pandemic (June 5 to 7, 2020) During this Pandemic times, B.M.S. College of Engineering had organized 3 days online hackathon from 5 to 7, June 2020 to combat COVID19. Students from all the departments and programs participated in this hackathon. There were 48 teams formed who had submitted various ideas and the top ten teams qualified for the grand finale after vigorous evaluation. Each team had a faculty mentor who helped the student teams to conceptualize the ideas virtually. On the last day, the top ten teams presented to the esteemed jury members and 5 prizes were announced. These teams will be supported by the college to realize their ideas into reality. The following link gives a glimpse of the 3 days COVID19 Hackathon held last weekend. Click here to view the details of the Hackathon Click here to View Hackathon Winners Back to All News</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173" t="str">
+        <v>2026-03-19T18:36:40.027Z</v>
+      </c>
+      <c r="F173">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>https://bmsce.ac.in/home/news/1/bmsce-hackathonbuilding-effective-solution-to-win-battle-against-covid19-5th-to-7th-june2020</v>
+      </c>
+      <c r="B174" t="str">
+        <v>html</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Home 26 May BMSCE Hackathon:Building effective solution to win battle against COVID19 - 5th to 7th June,2020. Click here for more Details Back to All News</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="E174" t="str">
+        <v>2026-03-19T18:36:40.653Z</v>
+      </c>
+      <c r="F174">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>https://bmsce.ac.in/home/news/1/webinar-on-three-amigos-mouse-clicks-humans-and-threats-on-28-may-2020-from-430-to-600-pm-1</v>
+      </c>
+      <c r="B175" t="str">
+        <v>html</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Home 26 May Webinar on “Three Amigos: Mouse clicks, Humans and Threats” on 28 May 2020 from 4.30 to 6.00 PM Greetings !!! IEEE Young Professionals Bangalore Section with MCA Department, BMSCE is organizing Student Transition &amp; Elevation Partnership Program (STEP) webinar on “Three Amigos: Mouse clicks, Humans and Threats” on 28 May 2020 from 4.30 to 6.00 PM Click here to download the Brochure. Free Registrations @ https://bit.ly/YPSTEP Speaker: Sneha Shekar, Security Threat Researcher, Cisco Abstract: Securing yourself in today’s digital world is becoming so much more important now. A single mouse click could lead to salary debit or to your banking credentials being stolen. Cyber-attacks are constantly evolving and the only cure to be secure is you! This webinar deals with the threat landscape today, different kinds of cyber-attacks, current trends in cybersecurity, and what we as individuals can do to secure ourselves in this digital world. Speaker profile : Sneha Shekar is part of the Umbrella Research India team. She is a Cisco Security Ninja Black belt. She is one of the few women security researchers from Asia and one of the youngest too. Sneha comes with a strong python background and is actively involved in building prototypes that aid in decoding malware and threat hunting. She was instrumental in building a machine learning classifier for hunting threats in the wild. Sneha works actively on decoding malware and was instrumental in solving the very complex malware called .scr malware. Sneha has delivered talks in SecCon Village and also faculty development program in New horizon College, Bangalore. She has conducted workshops at universities like BITS Pilani, RVCE and KL University, Vijayawada. contact - sivaram.mca@bmsce.ac.in or ashwini.am@ieee.org Back to All News</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175" t="str">
+        <v>2026-03-19T18:36:41.317Z</v>
+      </c>
+      <c r="F175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>https://bmsce.ac.in/home/news/1/duration-of-mca-program-as-per-aicte-approval-hand-book-2020-21</v>
+      </c>
+      <c r="B176" t="str">
+        <v>html</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Home 07 May Duration of MCA Program as per AICTE Approval Hand Book 2020-21 Duration of MCA Program as per AICTE Approval Hand Book 2020-21 - Click Here Back to All News</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176" t="str">
+        <v>2026-03-19T18:36:41.932Z</v>
+      </c>
+      <c r="F176">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>https://bmsce.ac.in/home/news/1/young-professional-program-to-infuse-fresh-and-young-talent-in-itsincubator-at-iit-kanpur-1</v>
+      </c>
+      <c r="B177" t="str">
+        <v>html</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Home 12 May Young Professional Program to infuse fresh and young talent in its incubator at IIT Kanpur IIT Kanpur recently launched Young Professional Program to infuse fresh and young talent in its incubator at IIT Kanpur. The opportunity involves one-year-long training before incumbents are inducted as Assistant Managers within the setup to lead different incubation processes. The incumbents are paid stipend during the traineeship and offered a handsome salary after successful completion of the training when they're inducted as employees in the setup The following link is for further details about the program and the application. ( http://www.siicincubator.com/ypp) Click here Back to All News</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177" t="str">
+        <v>2026-03-19T18:36:42.568Z</v>
+      </c>
+      <c r="F177">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>https://bmsce.ac.in/home/news/1/public-notice-on-redressal-of-grievances-related-to-covid-19</v>
+      </c>
+      <c r="B178" t="str">
+        <v>html</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Home 11 May PUBLIC NOTICE on REDRESSAL OF GRIEVANCES RELATED TO COVID-19 PUBLIC NOTICE on REDRESSAL OF GRIEVANCES RELATED TO COVID-19 - Click Here Back to All News</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178" t="str">
+        <v>2026-03-19T18:36:43.164Z</v>
+      </c>
+      <c r="F178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>https://bmsce.ac.in/home/news/1/urgent-circular-live-qna-session-of-vcs-and-principalsdirectors-of-teqip-institutions-with-guruji-sri-sri-ravishankar-tommorow-may-9th2020-1130-am-reg</v>
+      </c>
+      <c r="B179" t="str">
+        <v>html</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Home 08 May Urgent Circular- Live QnA session of VCs and Principals/Directors of TEQIP Institutions with Guruji Sri Sri Ravishankar Tommorow- May 9th,2020 11:30 AM-reg Greetings from NPIU! In order to prepare the students to avoid any kind of stress or panic related to their studies, health and related issues and enable smooth transition into the post-lockdown adjustments, NPIU is hosting a live QnA session for VCs and Principal /Directors of TEQIP Institutions with Guruji Sri Sri Ravi Shankar. 2. The session is being hosted Tomorrow- May 9th ,2020 (Saturday) at 11.30 am. The entire live session will be broadcast live exclusively for all the students of all TEQIP Institutes on the following link – https://youtu.be/4QXl9Tkd46Y Students/Faculty can post their questions in live chat box for addressal by Guruji. Kindly circulate the message on priority to your faculty and students in this regard through Mail/WhatsApp/Google-Classroom. Faculty members may forward the message to Class Representatives for onward transmission to Student WhatsApp groups. We look forward to seeing you at the live session. Back to All News</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179" t="str">
+        <v>2026-03-19T18:36:43.771Z</v>
+      </c>
+      <c r="F179">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>https://bmsce.ac.in/home/news/1/edx-remote-access-program-at-bmsce</v>
+      </c>
+      <c r="B180" t="str">
+        <v>html</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Home 06 May edX Remote Access Program at BMSCE We are happy to launch the edX remote access program at BMSCE. This program is to provide free edX course access for students and faculties of BMSCE. edX (MOOC platform) was started by MIT and Harvard University in 2012. The catalog in the link below gives various courses that we can sign up for free and get certification offered by top universities including Harvard University, Massachusetts Institute of Technology (MIT), and many others. Click here to check the edX higher ed Access Catalog The following are the steps Register for edX account using BMSCE email ID Fill this form https://forms.gle/ZFxpWnhhYdcmVkR67 Wait for one day Receive 16 digit coupon-code from edX - BMSCE Enroll for a course you like from the list of the available courses Click on Pursue a valid certificate Enter 16-digit coupon-code received in step 4 &amp; apply and place an order for free Happy learning and receive a certificate after completion. Please note: The last date to complete the courses in edX is 30 June 2020. Click here to check the screenshots in STEP by STEP process For more details click the link below to know about both Coursera and edX at BMSCE https://tinyurl.com/bmsce-coursera-edx Back to All News</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180" t="str">
+        <v>2026-03-19T18:36:44.420Z</v>
+      </c>
+      <c r="F180">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>https://bmsce.ac.in/home/news/1/coursera-at-bms-college-of-engineering-free-registration-and-certification-1</v>
+      </c>
+      <c r="B181" t="str">
+        <v>html</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Home 24 Apr Coursera at B.M.S. College of Engineering - Free registration and Certification At B.M.S. College of Engineering, we are committed to making the educational experience relevant for our students’ careers, ensuring that each of you is equipped with job-ready skills when you graduate. With this goal in mind, we are excited to announce a new partnership with Coursera - the leading online learning platform in the world. Let us flatten the pandemic curve and not the learning experience curve. As a first step, please fill this form and we will send you the invitation link from BMSCE Coursera in one day https://tinyurl.com/bmsce-coursera Please note the following You can complete the course by the end of September 2020. Free certificate for all students/faculties who complete the course successfully. Take any course you want and any number of courses you want This is only for BMSCE faculties and students Coursera offers more than 3,800 cutting-edge courses (https://www.coursera.org/browse), all taught by top instructors from over 200 leading universities and companies like Yale, University of Michigan, Google, and IBM. Our new partnership gives you access to these high-quality courses, allowing you to learn online on Coursera in addition to our on-campus curricula. We’ve worked closely with Coursera to identify courses that give you job-relevant technology, business, and interpersonal “soft” skills that companies are hiring for today. Once you sign up on Coursera, you will be able to: Learn in-demand technology and business skills that prepare you for today’s job opportunities Enjoy interactive learning experiences and be a part of Coursera’s global learning community Balance your on-campus coursework by studying at your own pace with Coursera’s bite-sized sessions, self-paced learning model, and convenient mobile experience Earn job-relevant certifications that can help boost your resume Sign up with these simple steps to get started Look out for the invitation email in your inbox including spam Click the included link to go to the program's home page Complete the signup process and join the program Select and enroll in a course Specific courses will already be recommended for you, but if you need further courses not on the list, please fill the form https://tinyurl.com/request-new-coursera-bmsce, who will be happy to provide additional recommendations/courses. We have limited Licenses to offer, the registrations will be on first-come-first-serve basis. Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="E181" t="str">
+        <v>2026-03-19T18:36:45.030Z</v>
+      </c>
+      <c r="F181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>https://bmsce.ac.in/home/news/1/international-womens-week-2020-activities-from-6th-march-to-10th-march-1</v>
+      </c>
+      <c r="B182" t="str">
+        <v>html</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Home 06 Mar International Women's Week 2020 - Activities from 6th March to 10th March 2020. BMSCE Women Cell is Organising a week long activities for Women Empowerment. The activities start on 6th March 2020 to 10th March 2020. Click here to view the Brochure Back to All News</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="E182" t="str">
+        <v>2026-03-19T18:36:45.658Z</v>
+      </c>
+      <c r="F182">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>https://bmsce.ac.in/home/news/1/national-science-day-events-from-17th-feb-2020-to-28th-feb-1</v>
+      </c>
+      <c r="B183" t="str">
+        <v>html</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Home 17 Feb National Science Day events from 17th Feb. 2020 to 28th Feb. 2020 National Science Day events from 17th Feb. 2020 to 28th Feb. 2020 - Click Here for the Google link Form Click Here for the Brochure Back to All News</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183" t="str">
+        <v>2026-03-19T18:36:46.335Z</v>
+      </c>
+      <c r="F183">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>https://bmsce.ac.in/home/news/1/bms-college-of-engineering-in-association-with-mitsubishi-electric-india-is-organizing-a-mega-event-the-5th-edition-of-mitsubishi-electric-cup-2020-a-national-level-competition-for-factory-automation-on-14th-and-15th-february-2020-friday-and-saturday-1</v>
+      </c>
+      <c r="B184" t="str">
+        <v>html</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Home 12 Feb B.M.S College of Engineering in association with Mitsubishi Electric India is organizing a mega event, the 5th Edition of Mitsubishi Electric Cup 2020, a National Level Competition for Factory Automation on 14th and 15th February 2020 (Friday and Saturday). Invitation of Inaugural function of ME Cup - Click Here Invitation of Prize distribution Ceremony of ME Cup - Click Here Event Details - Click Here Back to All News</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184" t="str">
+        <v>2026-03-19T18:36:46.943Z</v>
+      </c>
+      <c r="F184">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>https://bmsce.ac.in/home/news/1/schedule-of-induction-program-for-first-bestudents-2019-2020-phase-ii-27012020-to-01022020</v>
+      </c>
+      <c r="B185" t="str">
+        <v>html</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Home 25 Jan Schedule of Induction Program for First B.E.Students 2019-2020, Phase-II - 27/01/2020 to 01/02/2020. Click here download the Event Schedule Back to All News</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="E185" t="str">
+        <v>2026-03-19T18:36:47.568Z</v>
+      </c>
+      <c r="F185">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>https://bmsce.ac.in/home/news/1/machine-learning-and-deep-learning-with-python-20012020-to-1</v>
+      </c>
+      <c r="B186" t="str">
+        <v>html</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Home 09 Jan "Machine Learning and Deep Learning with Python" - 20/01/2020 to 24/01/2020 Click Here for the brochure. Back to All News</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186" t="str">
+        <v>2026-03-19T18:36:48.170Z</v>
+      </c>
+      <c r="F186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>https://bmsce.ac.in/home/news/1/recent-trends-in-deep-learning-and-its-applications-21012020-to-25012020</v>
+      </c>
+      <c r="B187" t="str">
+        <v>html</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Home 01 Jan Recent trends in Deep learning and its applications - 21/01/2020 to 25/01/2020 The Department of ECE &amp; CSE are jointly organizing One Week Faculty Development Program on "Recent trends in deep learning and its applications" from 21st to 25th January 2020. The registration link is: https://forms.gle/wQ7fpiS9RHvgnWfU9 Click Here for the brochure. Back to All News</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187" t="str">
+        <v>2026-03-19T18:36:48.777Z</v>
+      </c>
+      <c r="F187">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>https://bmsce.ac.in/home/news/1/ieee-international-conference-on-mainstream-block-chain-implementation-icombi-1</v>
+      </c>
+      <c r="B188" t="str">
+        <v>html</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Home 21 Dec IEEE International Conference on Mainstream Block Chain Implementation (ICOMBI) IEEE International Conference on Mainstream Block Chain Implementation (ICOMBI)-February 21-22, 2020, Bengaluru, India Click here to download flyer Back to All News</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="E188" t="str">
+        <v>2026-03-19T18:36:49.403Z</v>
+      </c>
+      <c r="F188">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>https://bmsce.ac.in/home/news/1/bmsce-dassault-systems-la-fondation-academic-partnership-1</v>
+      </c>
+      <c r="B189" t="str">
+        <v>html</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Home 14 Oct BMSCE - Dassault Systems La Fondation Academic Partnership BMSCE-DASSAULT SYSTEMES LA FONDATION ACADEMIC PARTNERSHIP Click here to download Back to All News</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="E189" t="str">
+        <v>2026-03-19T18:36:50.025Z</v>
+      </c>
+      <c r="F189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>https://bmsce.ac.in/home/news/1/two-days-national-symposium-1</v>
+      </c>
+      <c r="B190" t="str">
+        <v>html</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Home 23 Aug Two day’s National Symposium Two day’s National Symposium On Recent development in Infectious Diseases (REDIND-2019) 23-24 August 2019. Click here to download the brochure Click here to download the abstract Back to All News</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190" t="str">
+        <v>2026-03-19T18:36:50.644Z</v>
+      </c>
+      <c r="F190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>https://bmsce.ac.in/home/news/1/inaugural-function-of-commencement-of-first-year-be-barch-2019-1</v>
+      </c>
+      <c r="B191" t="str">
+        <v>html</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Home 04 Aug Inaugural function of commencement of First Year B.E. &amp; B.Arch - 2019-20 The Inaugural function of commencement of First Year B.E. &amp; B.Arch - 2019-20 will be on 04.08.2019 at 11.00 AM in the college sports complex (Indoor Stadium). Click here to view the invitation Back to All News</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="E191" t="str">
+        <v>2026-03-19T18:36:51.251Z</v>
+      </c>
+      <c r="F191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>https://bmsce.ac.in/home/news/1/one-week-fdp-on-contact-and-non-contact-measurements</v>
+      </c>
+      <c r="B192" t="str">
+        <v>html</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Home 22 Jul One week FDP on 'Contact and Non-Contact Measurements' One week FDP on "Contact and Non-Contact Measurements" from 22nd July 2019 to 27th July 2019. This FDP is conducted under the banner of ISTE BMSCE Chapter in association with the Department of Mechanical Engineering, BMSCE. Click here to download the brochure Back to All News</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192" t="str">
+        <v>2026-03-19T18:36:51.851Z</v>
+      </c>
+      <c r="F192">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>https://bmsce.ac.in/assets/img/Research/TOC%20BSN%20FELLOWSHIP%20APPLICATION.pdf</v>
+      </c>
+      <c r="B193" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C193" t="str">
+        <v>B. M. S. College of Engineering, Bengaluru Research and Development Centre Application for B.S. Narayan Fellowship for full-time Ph.D. Research Scholars NAME: _________________________________________ USN: _______________________________________ Research Centre : ________________________________ University: VTU / Mangalore University Year of Admission: ___________________________________________ Research Supervisor: _________________________________________ Research Supervisor Designation/Department: ________________________ Proposed Research Domain/Title : _________________________________ __________________________________________ Email:________________________________________________ Contact Number:__________________________________ Address for communication:_______________________________________ Passport Photo ______________________________________________________________ ______________________________________________________________ Research Progress, for existing scholars: ____________________________ ______________________________________________________________ Recommendation of Research Supervisor: ____________________________ ______________________________________________________________ I hereby certify that above particulars are correct. Signature with date Signature of Research Supervisor Signature of Head of the Research Centre B. M. S. College of Engineering, Bengaluru Research and Development Centre B.S. Narayan Fellowship for full-time Ph.D. Research Scholars To nurture research and development activities among research scholars and to attract Full-time Ph.D. scholars, B.M.S. College of Engineering has constituted the B.S. Narayan Fellowship for full-time Ph.D. research scholars. BMSCE has 13 research centres recognised by Visvesvaraya Technological University and/or Mangalore University. The research scholars who are admitted to the Ph.D. Programs through these recognised research centers are entitled to the fellowship. The Terms and conditions for award of the fellowship are listed below 1. Eligibility: The research scholar should have obtained admission by qualifying VTU-ETR in the same academic year. Note: The research scholars receiving the fellowship from any government or private agencies in India and abroad (ex: AICTE QIP / AICTE Doctoral fellowship (ADF), Project fellowship, Industry fellowship, etc) are not eligible for BSN Fellowship. In case any scholar receives the fellowship in between from any other funding agencies/sources, the BSN Fellowship will be discontinued. 2. Fellowship: The research scholars pursuing full-time Ph.D. at BMSCE are entitled to a monthly stipend of Rs.25,000/- (Rupees Twenty Five Thousand Only). 3. Duration of fellowship: The fellowship will be extended for a period of 3 years. 4. Start of fellowship: The date of the start of the fellowship will be mentioned in the confirmation letter issued by the R&amp;D Centre after confirmation of the admission by the University. 5. Workload: The candidate will be expected to carry out a minimum 6 hours per week of Teaching workload including laboratory, tutorials, CIE Invigilations, etc as assigned by the Head of the Department in consultation with the research supervisor. 6. Progress review: The progress of the BSN fellow will be reviewed biannually. The progress has to be satisfactory to continue receiving the fellowship. 7. Coursework and Comprehensive Viva: The research scholar is expected to complete the coursework within the first 2 semesters and appear for comprehensive viva within the second year of research. 8. Publications: He/She shall publish at least one quality journal article (Web of Science/Scopus indexed) before the comprehensive viva. However, the candidate must submit at least three journal articles (Web of Science/Scopus indexed) as a first author by the end of the third year of research. 9. Deputation for workshop/training/research activities: The full-time research scholars will not be allowed to take up any assignments outside of BMSCE. However, the scholars can be deputed to other premier institutes or companies for training/workshops/research activities, etc based on research requirements and recommendations from the R &amp; D committee and supervisor. Financial support will not be provided by the Institution for any such activities. 10. Casual Leaves: He/She is entitled to a total of 30 days of Casual Leaves in a calendar year with the prior permission of the Supervisor and Head of the research center, subject to the condition that such leave will not be longer than 5 days at a time. This leave cannot be carried over to the next calendar year. The leave will be calculated proportionately in accordance with the date of joining and leaving. 11. Attendance: The candidate will have to register his attendance in the register/biometric twice a day. The working hours will be the same as the college working hours. The Research centre shall maintain a record of leave every month and cumulative leave details are to be entered in the attendance register. Loss of pay if any must be clearly indicated in the attendance report submitted to the R&amp;D centre. 12. Monthly report: The candidate should submit the attendance statement of the month and the monthly report of research and academic activities on or before the 5th of every subsequent month to receive the fellowship. The same has to be attested and recommended by the supervisor and the head of the research centre. 13. Undertaking: The candidate selected for the award of B S Narayan Fellowship should give undertaking, wherein he/she agrees to complete the Doctoral studies in the same research centre. If the candidate discontinues the course, he/she will have to repay the stipend with interest as per the institute norms. 14. All the research fellows must abide by the rules and regulations of the Universities and policies of the B.M.S. College of Engineering. Sd/- Date: 01.02.2025 PRINCIPAL</v>
+      </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="E193" t="str">
+        <v>2026-03-19T18:36:52.507Z</v>
+      </c>
+      <c r="F193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>https://bmsce.ac.in/assets/img/Research/B%20S%20Narayan%20Doctoral%20Fellowship%202025-26.pdf</v>
+      </c>
+      <c r="B194" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C194" t="str">
+        <v>B.M.S. College of Engineering,Bull Temple Road , Bengaluru -560019 (Autonomous Institute Under VTU) B.S. Narayan Doctoral Fellowship 2025-26 APPLICATIONS ARE INVITED FOR PH.D ADMISSION (FULL TIME) FOR THE ACADEMIC YEAR 2025-26 Accredited by NAAC with A++ grade [ 3rd cycle] Name Of The Department Civil Engineering Mechanical Engineering Management Studies Chemical Engineering Physics Chemistry Mathematics Biotechnology Master of Computer Applications Computer Science and Engineering Industrial Engineering and Management Electronics and Communications Engineering Electrical and Electronics Engineering Eligibility: Candidates with valid VTU-ETR score for two Years are eligible. Registered Students of Mangalore University can apply for the BSN Fellowship. For more details, please visit www.bmsce.ac.in BSN Fellowship 25-26 Application Process: Duly filled and signed application form should be sent to the following address on or before the deadline. The Principal, BMSCE, Bull Temple Road, Bangalore - 560019. Fellowship Details Last date for receipt of filled-in application form is 31st December 2025 For more details, visit: BMSCE Official Website Tel: 080 26622130/Extn:6099 | Email: hod.rnd@bmsce.ac.in Founder, BMSET Late Shri B M Sreenivasaiah Donor Trustee, BMSET Late Shri B.S.Narayan ESTD. 1946 B.M.S. College of Engineering (BMSCE) Bengaluru has the unique distinction of being one of the first private engineering colleges established in the country. Started in the year 1946, the institution owes its existence to the vision of its beloved founders, Late Sri. B. M. Sreenivasaiah and his illustrious son, Late Sri. B. S. Narayan. The College currently offers 13 Undergraduate &amp; 12 Postgraduate courses in both conventional and emerging areas. More than 350 research scholars are pursuing Ph.D. in various research centers of the college. In the last few years, 293 Ph.Ds and 23 M.Sc. (by research) have been produced so far through the research centers. Applications are invited for the Ph.D. Program (Full Time) in the following departments for the academic year 2025-26. are A Fellowship amount of Rs 35,000/- per month is provided for a period of two years from the date of registration. Upon successful completion of the comprehensive viva, or after successful completion of two years of research (whichever is later), the fellowship may be enhanced to Rs 40,000/- per month. The decision of the committee regarding the selection of Candidates for the BSN Fellowship in the PhD program shall be final. Fellowship upto ₹ 40k per month</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194" t="str">
+        <v>2026-03-19T18:36:55.327Z</v>
+      </c>
+      <c r="F194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20Application%20BMSCE%2025092025.pdf</v>
+      </c>
+      <c r="B195" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C195" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8. Nationality 9.Religon 10. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 11. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 12. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 13. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 14. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 15. Patents (please attach a separate sheet) Filed Published Granted 16. Consultancy (please attach a separate sheet) Awarded On-going 17. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 18. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 19. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 20. Special Award / Achievements or any other information : (please attach a separate sheet) 21. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 22. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 23. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 24. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 25. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 26. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 27. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195" t="str">
+        <v>2026-03-19T18:36:55.931Z</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20Application_25.pdf</v>
+      </c>
+      <c r="B196" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C196" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 13. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 16. Patents (please attach a separate sheet) Filed Published Granted 17. Consultancy (please attach a separate sheet) Awarded On-going 18. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 19. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 20. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 21. Special Award / Achievements or any other information : (please attach a separate sheet) 22. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 23. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 24. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 25. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 26. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 27. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 28. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196" t="str">
+        <v>2026-03-19T18:36:56.573Z</v>
+      </c>
+      <c r="F196">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>https://bmsce.ac.in/website_notifications/GTC.pdf</v>
+      </c>
+      <c r="B197" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C197" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING &amp; Staff) The application can be downloaded from the website. The duly filled in applications along with required enclosures should reach the Principal on or before 08.09.2025 . ASSISTANT PROFESSOR 1 CSE/AIML/AIDS/CSDS/ CSE(IOT)/ CSBS (CSE Cluster) The minimum qualification required is as per AICTE 7th Pay Norms. Preference will be given to the candidates with Ph.D qualification. 2 Department of Physics NOTE: Preference shall be given to candidates with Ph.D Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms  The details of the publications / patents/ funded projects need to be mentioned in the application.  Experience: As per AICTE norms.  Candidates should appear for the interview, if called, at their own cost with all the original documents.  The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules as per the norms of the College.  Management reserves the rights of processing (accept/reject) the application.  Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration.</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197" t="str">
+        <v>2026-03-19T18:36:57.142Z</v>
+      </c>
+      <c r="F197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching_ADJUNT.pdf</v>
+      </c>
+      <c r="B198" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C198" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION (ADJUNCT FACULTY/PROFESSOR OF PRACTICE) Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8. Nationality 9.Religon 10. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 11. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 12. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 13. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 14. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 15. Patents (please attach a separate sheet) Filed Published Granted 16. Consultancy (please attach a separate sheet) Awarded On-going 17. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 18. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 19. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 20. Special Award / Achievements or any other information : (please attach a separate sheet) 21. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 22. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 23. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 24. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 25. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 26. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 27. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198" t="str">
+        <v>2026-03-19T18:36:57.748Z</v>
+      </c>
+      <c r="F198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>https://bmsce.ac.in/website_notifications/GC_ADJUNT.pdf</v>
+      </c>
+      <c r="B199" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C199" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU NOTIFICATION OF FACULTY RECRUITMENT (ADJUNCT FACULTY AND PROFESSOR OF PRACTICE) MANAGEMENT ADVERTISEMENT GENERAL CONDITIONS (TEACHING) The application can be downloaded from the website. The duly filled in applications along with required enclosures should reach the Principal on or before 25.08.2025. ADJUNCT FACULTY AND PROFESSOR OF PRACTICE (POP) ALL DEPARTMENTS QUALIFICATIONS AND EXPERIENCE: An Adjunct Faculty/ Resource person / Professor of Practice / Industry Expert shall be a Faculty retired from Technical Institution or a person of eminence, with or without a Post Graduate or Ph.D. qualifications having 10 to 15 years of experience from Industry/ Organization. There shall be no upper age limit for Adjunct Faculty/ Resource Person as long as he/ she add value to the Education and academic activities of the Institution NOTE: Preference shall be given to candidates with Degree from premier institutions in addition to the qualification and experience as per AICTE norms. • Experience: As per AICTE norms. • Candidates should appear for the interview, if called, at their own cost with all the original documents. • Management reserves the rights of processing (accept/reject) the application. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration.</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199" t="str">
+        <v>2026-03-19T18:36:58.307Z</v>
+      </c>
+      <c r="F199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20Application%20BMSCE_New.pdf</v>
+      </c>
+      <c r="B200" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C200" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8. Nationality 9.Religon 10. Languages known Language Read Speak Write 11. Highest Educational Qualification Details of Educational Qualification Please Affix recent Passport (35 x 35 mm) Photograph Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 12. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 13. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 14. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 15. Patents (please attach a separate sheet) Filed Published Granted 16. Consultancy (please attach a separate sheet) Awarded On-going 17. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 18. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 19. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 20. Special Award / Achievements or any other information : (please attach a separate sheet) 21. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 22. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 23. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 24. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 25. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 26. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 27. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200" t="str">
+        <v>2026-03-19T18:36:58.939Z</v>
+      </c>
+      <c r="F200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20-%20General%20Conditions-August.pdf</v>
+      </c>
+      <c r="B201" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C201" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING) The application can be downloaded from the website. The duly filled in applications along with required enclosures should reach the Principal on or before 25.08.2025 ASSISTANT PROFESSOR CSE/AIML/AIDS/ CSDS/ CSE(IOT)/ CSBS (CSE Cluster) The minimum qualification required is as per AICTE 7th Pay Norms. Preference will be given to the candidates with Ph.D qualification, candidates who have registered for Ph.D can also apply. Department of Mathematics The minimum qualification required is as per AICTE 7th Pay Norms. Preference will be given to the candidates with Ph.D qualification. NOTE: Preference shall be given to candidates with Ph.D Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms.. • The details of the publications / patents/ funded projects need to be mentioned in the application. • Experience: As per AICTE norms. • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules as per the norms of the College. • Management reserves the rights of processing (accept/reject) the application. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration.</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="E201" t="str">
+        <v>2026-03-19T18:36:59.491Z</v>
+      </c>
+      <c r="F201">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20Applicatio.pdf</v>
+      </c>
+      <c r="B202" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C202" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 13. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 16. Patents (please attach a separate sheet) Filed Published Granted 17. Consultancy (please attach a separate sheet) Awarded On-going 18. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 19. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 20. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 21. Special Award / Achievements or any other information : (please attach a separate sheet) 22. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 23. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 24. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 25. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 26. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 27. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 28. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="E202" t="str">
+        <v>2026-03-19T18:37:00.153Z</v>
+      </c>
+      <c r="F202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20GC.pdf</v>
+      </c>
+      <c r="B203" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C203" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING) The application can be downloaded from the website. The duly filled in applications along with required enclosures should reach the Principal on or before 09.08.2025 ASSISTANT PROFESSOR CSE/AIML/AIDS/ CSDS/ CSE(IOT)/ CSBS (CSE Cluster) The minimum qualification required is as per AICTE 7th Pay Norms. Preference will be given to the candidates with Ph.D qualification, candidates who have registered for Ph.D can also apply. NOTE: Preference shall be given to candidates with Ph.D Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms.. • The details of the publications / patents/ funded projects need to be mentioned in the application. • Experience: As per AICTE norms. • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules as per the norms of the College. • Management reserves the rights of processing (accept/reject) the application. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration.</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203" t="str">
+        <v>2026-03-19T18:37:00.944Z</v>
+      </c>
+      <c r="F203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teachingg_Application%20(03.04.2025).pdf</v>
+      </c>
+      <c r="B204" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C204" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 13. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 16. Patents (please attach a separate sheet) Filed Published Granted 17. Consultancy (please attach a separate sheet) Awarded On-going 18. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 19. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 20. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 21. Special Award / Achievements or any other information : (please attach a separate sheet) 22. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 23. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 24. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 25. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 26. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 27. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 28. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204" t="str">
+        <v>2026-03-19T18:37:01.686Z</v>
+      </c>
+      <c r="F204">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20-%20Generalll%20Conditions.pdf</v>
+      </c>
+      <c r="B205" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C205" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING) The application can be downloaded from the website. The duly filled in applications along with required enclosures should reach the Principal on or before 22.07.2025 ASSISTANT PROFESSOR CSE/AIML/AIDS/ CSDS/ CSE(IOT)/ CSBS (CSE Cluster) The minimum qualification required is as per AICTE 7th Pay Norms. Preference will be given to the candidates with Ph.D qualification, candidates who have registered for Ph.D can also apply. NOTE: Preference shall be given to candidates with Ph.D Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms..  The details of the publications / patents/ funded projects need to be mentioned in the application.  Experience: As per AICTE norms.  Candidates should appear for the interview, if called, at their own cost with all the original documents.  The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules as per the norms of the College.  Management reserves the rights of processing (accept/reject) the application.  Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration.</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="E205" t="str">
+        <v>2026-03-19T18:37:02.270Z</v>
+      </c>
+      <c r="F205">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teachng%20Application%20BMSCE.pdf</v>
+      </c>
+      <c r="B206" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C206" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 13. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 16. Patents (please attach a separate sheet) Filed Published Granted 17. Consultancy (please attach a separate sheet) Awarded On-going 18. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 19. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 20. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 21. Special Award / Achievements or any other information : (please attach a separate sheet) 22. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 23. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 24. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 25. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 26. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 27. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 28. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206" t="str">
+        <v>2026-03-19T18:37:02.894Z</v>
+      </c>
+      <c r="F206">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>https://bmsce.ac.in/website_notifications/NonTeaching%20Application%20form-%20BMSCE.pdf</v>
+      </c>
+      <c r="B207" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C207" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA Non-Teaching Application No.___________________________________________ For the Post of:____________________________________________ Department:______________________________________________ Reference:________________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupati on 3. Address for Correspondence 4. Contact Number &amp; E-mail address Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Examination passed(if any) Please affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Examination passed SSLC onwards (for group D posts give the highest exam passed) Name of the Institution/University Year of Passing Percentage of Marks Class Awarded 13. Total No. of Year Experience Name of the Institution/Organization Designation Date of Job Details Entry Leaving Declaration I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate Check – List of documents to be attached with the application Title of the document No’s Please tick Attached Not Attached SSLC Marks Card or age proof document Caste Certificate Qualification Certificate Experience Certificate Technical Certificate Copy of Aadhar Card Copy of PAN Card Details of Fee Paid DD No. Date Amount Bank &amp; Branch Name The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207" t="str">
+        <v>2026-03-19T18:37:03.475Z</v>
+      </c>
+      <c r="F207">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Advertisemnt%20BMSCE.pdf</v>
+      </c>
+      <c r="B208" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C208" t="str">
+        <v>B.M.S. EDUCATIONAL TRUST, BENGALURU B.M.S. COLLEGE OF ENGINEERING Bull Temple Road, BENGALURU - 560 019 Autonomous Institute, Afiliated to VTU BMSCE invites applications from candidates with high academic achievements, research craving mind with constructive attitude for the following positions under Management Cadre: 4tORE Program Late B.M.Sreenivasaiah Founder, BMSET ASSISTANT PROFESSOR Requirement for the position » Computer Science &amp; Engineering (CSE) Qualification &amp; Experience: » Machine Learning (Artificial Intelligence|As per AICTE Norms (Preference &amp;Machine Learning) willbe given to the candidates » Artificial Intelligence &amp; Data Science (AI &amp; DS) with Ph.D. degree from premier » Computer Science &amp; Engineering|institutions with good publications). (Data Science) |Salary:As per AICTE 7th Pay Scale Computer Science &amp; Engineering (loT &amp; Cyber Security including Block Chain Technology) Computer Science &amp;Business Systems Late B.S.Narayan Donor Truste, BMSET Faculty with 10+ years of experience are eligible for salary protection. ASSISTANT PROFESSOR FOR MBA PROGRAM Specialisation in Business Analytics &amp;Marketing PLACEMENT OFFICER Two years MBA Preferably Specialisation in HR. Atleast 10 years prior experience in Placement related activities in Leading Institutes / Organisations For further details, please visit www.bmsce.ac.in. Duly filled in applications along with required enclosures should reach the Principal on or before 5th July 2025 Sd/- Principal, BMSCE</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208" t="str">
+        <v>2026-03-19T18:37:04.112Z</v>
+      </c>
+      <c r="F208">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>https://bmsce.ac.in/website_notifications/General%20Condit.pdf</v>
+      </c>
+      <c r="B209" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C209" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING &amp; Staff) The application can be downloaded from the website. The duly filled in applications along with required enclosures should reach the Principal on or before 05.07.2025 . ASSISTANT PROFESSOR 1 CSE/AIML/AIDS/CSDS/ CSE(IOT)/ CSBS (CSE Cluster) The minimum qualification required is as per AICTE 7th Pay Norms. Preference will be given to the candidates with Ph.D qualification. 2 MBA The minimum qualification required is Ph.D. Candidates who have completed Ph.D. Preference will be given to the candidates with Ph.D from premier institutions. PLACEMENT OFFICER 3 PLACEMENT OFFICE Two years MBA preferably specialization in HR. At least 10 years prior experience in placement related activities in leading Institutes/Organizations. NOTE: Preference shall be given to candidates with Ph.D Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms for Sl.no 1 &amp; 2. • The details of the publications / patents/ funded projects need to be mentioned in the application. • Experience: As per AICTE norms. • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules as per the norms of the College. • Management reserves the rights of processing (accept/reject) the application. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration.</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209" t="str">
+        <v>2026-03-19T18:37:04.726Z</v>
+      </c>
+      <c r="F209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>https://bmsce.ac.in/website_notifications/advertisement%20for%20project%20associate-new1.pdf</v>
+      </c>
+      <c r="B210" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C210" t="str">
+        <v>B.M.S. College of Engineering Department of Civil Engineering 11 April 2025 Ref: BMSCE/CV/DSF Contract ID 2025-293 Advertisement for Project Associate position (1 post) under the Dassault Systemes Foundation Grant Applications are invited for the post of Project Associate under the Dassault Systemes Foundation Grant for the project "3-D Modelling based Simulation of Rain induced Urban Flooding and creation of methodology for mitigation Measures". Principal investigator of the project is Dr. Reshmi Devi T.V, Associate Professor, Dept. Civil Engineering, B.M.S. College of Engineering, Bengaluru. The project team includes Prof. Alok Pandey and Dr. Geetha Kuntoji (Dept. Civil Engineering, BMSCE) and Dr. Shivashankar R. Srivatsa (Dept. Mechanical Engineering, BMSCE). Name of the post Project Associate Number of posts One Essential qualification Masters/ Integrated Masters in Hydraulic Engineering, Hydro-informatics, Water Resources Engineering OR B.E or B.Tech in Civil or Mechanical Engineering from a recognized University AND 2 years' experience in Research and Development in Industrial and Academic Institutions or Science and Technology Organizations and Scientific activities and services Age limit (yrs) 35 Desirable qualification Experience in GIS, CFD software, and/or hydrological modelling (HEC-RAS and HEC-HMS) Monthly Emoluments (a) 35,000/- + HRA for those candidates who have qualified GATE, CSIR-UGC or NET (b) 28,000/- + HRA for others who do not fall under (a) above Nature of appointment Purely on temporary basis Duration of the employment The joining date will be immediately after the selection. The initial appointment will be for six months which is extendable up to 18 months subject to performance of the candidate Last date for application 17 th April 2025 Eligible candidates fulfilling the criteria, may apply through the following Google form https://forms.gle/a532di5bHYq8J5Mu9 Instructions: • The position is purely temporary for 6 months and is extendable up to 18 months if the performance is satisfactory • Only shortlisted candidates will be called for the interview. Mere fulfillment of qualification/ experience requirements does not entitle a candidate to be called for interview. • No TA/DA or accommodation will be provided to attend the interview • At the time of interview, candidates should produce original certificates as proof for the details furnished in the application, failing which they will not be allowed to appear for the interview.</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="E210" t="str">
+        <v>2026-03-19T18:37:05.349Z</v>
+      </c>
+      <c r="F210">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Notification-advt-SRF-Msprasanna.pdf</v>
+      </c>
+      <c r="B211" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Name of the post B. M. S. College of Engineering, Bengaluru Ref: BMSCEME/ PTPL Contract ID: U72900KA2008 PTCO48512 Number of posts Applications are invited from eligible candidates for the post of a Senior Research Fellow (SRF)on contract basis for the Prasanna Technologies Pvt. Ltd. (PTPL) funded project entitled: Predicting residual life of structures using artificial intelligence enabled thermography", under Dr. Anil Chandra A. R., and Dr. Sangamesh C. Godi, Department of Mechanical Engineering, B.M.S. College of Engineering, Bengaluru. Essential qualification Desirable qualification Maximum Age limit Department of Mechanical Engineering. Monthly salary structure Duration of employment Notification: Call for SRF Address for posting: Senior research fellow (SRF) One M.Tech. in Mechanical Engineering Sciences. Must have completed course work in Fracture Mechanics, Machine Learning, Design of Experiments Preference will be given to those who have exposure to digital image correlation and experimental fracture mechanics 32 years Rs. 36,000/ The joining date will be on 1 May 2025. Theinitial appointment will be for next ten months. Eligible candidates fulfilling the criteria, may apply with their resume and relevant to e-mail the address the by sending documents anilchandraar.mech@bmsce,ac.in or by posting to the address mentioned below. Last date for submitting the documents is 12th April 2025, SPM IST. sth April 2025 same For any further queries or clarification contact anilchandraar.mech@bmsce.ac.in / sangameshcg.mech@bmsce.ac.in Dr. AnilChandra A. R., Assistant Professor, Department of Mechanical Engineering Bull Temple Road, Bengaluru-560019 through</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="E211" t="str">
+        <v>2026-03-19T18:37:05.919Z</v>
+      </c>
+      <c r="F211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Notification%20(Website)-26.03.2025.pdf</v>
+      </c>
+      <c r="B212" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C212" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE-19 Autonomous Institute, Affiliated to VTU No. BMS 08 EST (U) 2025 Date: 25.03.2025 NOTIFICATION FOR FACULTY / STAFF RECRUITMENT UNDER MANAGEMENT CADRE Applications are invited for the following Posts under Management cadre Sl.N o. Designation Qualification required 1 Assistant Professor, Department of MBA → The minimum qualification required is Ph.D. Candidates who have completed Ph.D. viva voce may also apply. → P reference will be given to the candidates with Ph.D from premier institutions. → Age limit: below 35 years. 2 System Analysist → B.E.in Computer Science &amp; Engineering / Allied branches → Total of 3 -5 years of experience in managing LINUX SERVERS → Preferably with LINUX OS Certification having knowledge of DOCKERS, Kubernates &amp; Shell Scripting preferably with UNUX OS Certification → Preference will be given to candidate s having experience in handling NVIDIA Servers. → Age limit: below 35 years. The application can be downloaded from the website. The duly filled in application with all relevant documents should reach the Principal on or before 10.04.2025 Candidates should appear for the interview, if called, at their own cost with all the Original documents Management reserves the rights of processing (accept/reject) the application Notwithstanding the above conditions, if any relevant orders issued and which are in force will be made applicable for consideration Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="E212" t="str">
+        <v>2026-03-19T18:37:06.576Z</v>
+      </c>
+      <c r="F212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20Application%20(12.02.2025).pdf</v>
+      </c>
+      <c r="B213" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C213" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 13. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 16. Patents (please attach a separate sheet) Filed Published Granted 17. Consultancy (please attach a separate sheet) Awarded On-going 18. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 19. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 20. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 21. Special Award / Achievements or any other information : (please attach a separate sheet) 22. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 23. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 24. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 25. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 26. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 27. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 28. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213" t="str">
+        <v>2026-03-19T18:37:07.235Z</v>
+      </c>
+      <c r="F213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Non-Teaching%20Application%20form-%2015-11-2024.pdf</v>
+      </c>
+      <c r="B214" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C214" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA Non-Teaching Application No.___________________________________________ For the Post of:____________________________________________ Department:______________________________________________ Reference:________________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupati on 3. Address for Correspondence 4. Contact Number &amp; E-mail address Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Examination passed(if any) Please affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Examination passed SSLC onwards (for group D posts give the highest exam passed) Name of the Institution/University Year of Passing Percentage of Marks Class Awarded 13. Total No. of Year Experience Name of the Institution/Organization Designation Date of Job Details Entry Leaving Declaration I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate Check – List of documents to be attached with the application Title of the document No’s Please tick Attached Not Attached SSLC Marks Card or age proof document Caste Certificate Qualification Certificate Experience Certificate Technical Certificate Copy of Aadhar Card Copy of PAN Card Details of Fee Paid DD No. Date Amount Bank &amp; Branch Name The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214" t="str">
+        <v>2026-03-19T18:37:07.801Z</v>
+      </c>
+      <c r="F214">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>https://www.bmsce.ac.in/assets/files/Research/BSNnotification.pdf</v>
+      </c>
+      <c r="B215" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C215" t="str">
+        <v>B.M.S. College of Engineering, Bengaluru ESTD. 1 9 4 6 B.S. Narayan Doctoral Fellowship 2025-26 APPLICATIONS ARE INVITED FOR PH.D ADMISSION (FULL TIME) FOR THE ACADEMIC YEAR 2025-26 B.M.S. College of Engineering (BMSCE) Bengaluru has the unique distinction of being the first private engineering college established in the country. Started in the year 1946, the institution owes its existence to the vision of its beloved founders, Late Sri. B. M. Sreenivasaiah and his illustrious son, Late Sri. B. S. Narayan. The College currently offers 14 Undergraduate &amp; 12 Postgraduate courses in both conventional and emerging areas. More than 350 research scholars are pursuing Ph.D. in various research centers. In the last few years, 126 Ph.Ds and 23 M.Sc. (by research) have been produced so far through the research centers. Applications are invited for the Ph.D. Program (Full Time) in the following departments: S. No Name of the Department 1 2 3 4 5 6 7 8 9 10 11 12 13 Civil Engineering Mechanical Engineering Electrical and Electronics Engineering Electronics and Communications Engineering Industrial Engineering and Management Computer Science and Engineering Master of Computer Applications Management Studies Chemical Engineering Physics Chemistry Mathematics Biotechnology Eligibility: Candidates with valid VTU-ETR scores for two years are eligible. For more details, please visit: https://bmsce.ac.in/home/Application-Downloads Application Process: The application must be filled online and signed. A printout of the completed application, along with relevant documents, should be sent to the following address on or before the deadline: The Principal, BMSCE, Bull Temple Road, Bangalore - 560019. Opening date of application form 12th February 2025 Last date for receipt of filled-in application form 05th March 2025 Additional Information • Incomplete applications are liable to be rejected, and further correspondence will not be entertained under any circumstances. • Interview Process: The date of the interview will be communicated to shortlisted candidates. • Travel Allowance: No TA/DA will be provided for attending the interview. Fellowship Details A fellowship amount of Rs. 25,000/- per month is provided for a period of three years from the date of registration, based on the recommendation of the Committee. The decision of the Committee is final for the BSN Fellowship in the Ph.D. Program. For more details, visit: BMSCE Official Website Tel: 080 26622130 | Email: hod.rnd@bmsce.ac.in Founder, BMSET Late B M Sreenivasaiah Donor Trustee, BMSET Late Sri B.S.Narayan Accredited by NAAC with A++ grade [ 3rd cycle]</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="E215" t="str">
+        <v>2026-03-19T18:37:09.401Z</v>
+      </c>
+      <c r="F215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>https://bmsce.ac.in/home/Application-Downloads</v>
+      </c>
+      <c r="B216" t="str">
+        <v>html</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Application Downloads # Details File 1 PhD BMSCE application Download 2 Faculty Research Promotion Scheme Application T &amp; C 3 BMSCE Journal Incentive Claim Form PDF Download 4 Peformance based Incentive Scheme for Research Reimbursement Claim PDF Download 5 Application Form - Conferences PDF Download 6 Terms and Conditions for BSN Fellowship &amp; Application form for BSN Fellowship PDF Download</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216" t="str">
+        <v>2026-03-19T18:37:10.029Z</v>
+      </c>
+      <c r="F216">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>https://bmsce.ac.in/website_notifications/BMSCE_DIC_PhD_Advertisement_2025.pdf</v>
+      </c>
+      <c r="B217" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C217" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING ( Estd 1946, Autonomous Institute under VTU ) Bull Temple Road, Bangalore - 560 019, Karnataka, India ________________________________________________________________ No. BMSCE/Ph.D. Admission/2024-25/Feb Session Date: 03.02.2025 Admission to Ph.D. Programme (Full-Time/Part-Time) under Visvesvaraya Ph.D. Scheme Digital India Corporation, Ministry of Electronics and Information Technology, Govt. of India Implementation Order No: PhD-PT02/2024-01/51 &amp; PhD-02/2024-02/72 Applications are invited from eligible and interested research candidates for the Ph.D programme (Full-Time/Part-Time) under “Visvesvaraya PhD Scheme for Electronics &amp; IT- Phase-II”, by Digital India Corporation (DIC), MeitY, Govt. of India. B.M.S. College of Engineering will be the research centre and the degree will be awarded by Visvesvaraya Technological University, Belgaum, Karnataka. Details of the Scheme: https://www.myscheme.gov.in/schemes/vpseit VTU Ph.D Regulations: jnanashodha.vtu.ac.in/Regulations/PhD2023Regulation.pdf Vacancy Table Full-Time Ph.D. 02 Part-Time Ph.D. 01 The summary of the scheme is as below Eligibility: ● The candidates shall possess a master’s degree in engineering/ technology or equivalent degree by the University, with a minimum CGPA of 6.75 out of 10 or 60% aggregate marks at the Master’s degree. ● GATE candidates will be given preference. ● For the part-time registration, the candidate should be working in an organization (Academic institution or industry). Financial Assistance: Full time Candidates: ● Stipend/Fellowship (Full-time Ph.D.) @ Rs. 38,750/- per month for fi rst and second years @ Rs. 43,750/- per month for Third, Fourth and Fifth Year ● Reimbursement of Rent (RoR): 24% (As per the prevailing norms &amp; approval from DIC) ● Research Contingency Grant: Rs.1,20,000/Year ● Support for attending International Conference : Support up to 1.5 Lakhs from third year onwards ● Visit to labs abroad : From third year of PhD based on approval from DIC Part time Candidates ● A one-time incentive of ₹ 3,00,000/- would be provided on successful completion of the Ph.D. Important Dates Online application registration process start date 04/02/2025 Last date for the submission of online Application form 15/02/2025 Web noti fi cation of the short-listed candidates for written test and/or Interview 20/02/2025 Dates of interview (for short-listed candidates) 25/02/2025 Announcement of Results 25/02/2025 Application Procedure: ● Interested and eligible candidates shall submit an online application using the form https://forms.gle/5HwSW5wNCFm2uxzD7 along with the following o Application Form: https://tinyurl.com/phd-dic-application o Enclosures to be submitted along with the application ▪ Date of Birth (DOB) Certi fi cate or High School (Class 10th) Certi fi cate with DOB ▪ SC/ST/OBC(NCL) Certi fi cate, if applicable ▪ Certi fi cate of Physical Disability, if applicable ▪ A valid GATE/CSIR/UGC score card, if applicable ▪ Copies of mark/grade sheets of qualifying degree or higher ▪ No Objection Certi fi cate from employer (only for part-time). Full-time students currently working must produce an NOC or Relieving Certi fi cate from the employer at the time of admission. ▪ Details of two referees (Name, Designation, A ffi liation, Email ID) Selection Procedure: Based on norms of the University and DIC, MeitY, GOI Department Tentative Broad Research Areas: (Under Visvesvaraya Fellowship) for Full-Time and Part-Time Research Areas ECE &amp; allied Electronics System Design &amp; Manufacturing (ESDM) and IT/IT Enabled Services (IT/ITES) For any queries, the applicants can contact Dr. Abhishek Appaji, Nodal O ffi cer (Visvesvaraya PhD Scheme for Electronics and IT), B.M.S. College of Engineering, Bengaluru E mail to: abhishek.ml@bmsce.ac.in / Mobile: 9844923632</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217" t="str">
+        <v>2026-03-19T18:37:10.620Z</v>
+      </c>
+      <c r="F217">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>https://bmsce.ac.in/website_notifications/General%20Conditions%20for%20Faculty%20Recruitment.pdf</v>
+      </c>
+      <c r="B218" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C218" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU NOTIFICATION DATED: 06.09.2024 IN TIMES OF INDIA NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING) The application can be downloaded from the website. The duly filled in applications along with required enclosures should reach the Principal on or before 21 st Sept. 2024. ASSISTANT PROFESSOR CSE/AIML/AIDS/CSDS/ CSE(IOT)/ CSBS • The minimum qualification required is as per AICTE Norms. Preference will be given to the candidates with Ph.D qualification, candidates who have registered for Ph.D can also apply. Master of Computer Applications (MCA)/B.E.1 st year Computer Science (Cluster Departments) • The minimum qualification required is as per AICTE Norms. In addition MCA with Ph.D. (preferable). Preference will be given to the candidates with Ph.D qualification, candidates who have registered for Ph.D can also apply. STATISTICS • The minimum qualification required is B.Sc (Statistics) and M.Sc (Statistics) or B.Stat and M.Stat with Ph.D degree in concerned/allied disciplines. The candidates who have completed Ph.D Viva Voce may also apply. Separate applications are to be submitted in the event of candidates applying for more than one faculty position. NOTE : Preference shall be given to candidates with Ph.D. Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms. • The details of the publications / patents/ funded projects need to be mentioned in the application. • Experience: As per AICTE norms. • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules • Management reserves the rights of processing (accept/reject) the application. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration.</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218" t="str">
+        <v>2026-03-19T18:37:11.228Z</v>
+      </c>
+      <c r="F218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Placement%20Officer%20(Website%20Notification%20-%2016.11.2024).pdf</v>
+      </c>
+      <c r="B219" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C219" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE-19 Autonomous Institute, Affiliated to VTU No. BMS 08 EST (U) 2024 Date: 16.11.2024 NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE Applications are invited for appointment of technical staff in the following department under Management cadre on consolidated pay . Sl. No. Department Designation No. Posts Qualification required 1 MBA PLACEMENT OFFICER 1 Eligibility Criteria : • Master’s Degree (Full Time) from a reputed university, MBA preferable. • Minimum 5 years of industry experience with 2 years in a leadership role, preferably in Placement or related roles like marketing/recruitment etc., • Should be a dynamic person with excellent communication skills, PR, liaison and good in relationship building • Ability to develop sound, credible and reciprocal relations with industry • Ability to work with MBA department and should have a track record of good placements The application can be downloaded from the college website. The duly filled in application with all relevant documents should reach the Principal on or before 14.12.2024. The age limit is as per the Karnataka Civil Service (General Recruitment) Rules. Candidates should appear for the interview, if called, at their own cost with all the Original documents Management reserves the rights of processing (accept/reject) the application Notwithstanding the above conditions, if any relevant orders issued and which are in force will be made applicable for consideration Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219" t="str">
+        <v>2026-03-19T18:37:11.869Z</v>
+      </c>
+      <c r="F219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Website%20Notification%20-%2014.11.2024.pdf</v>
+      </c>
+      <c r="B220" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C220" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE-19 Autonomous Institute, Affiliated to VTU No. BMS 08 EST (U) 2024 Date: 14.11.2024 NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE Applications are invited for appointment of technical staff in the following department under Management cadre on consolidated pay . Sl.N o. Department Designation No. Posts Qualification required 1 R &amp; D Technical Assistant 1 Essential: Diploma in Mechanical/Civil/Aero/Tool &amp; Die making Desirable: • Must be a holder of Diploma or higher degree (First Class) in Mechanical/Civil/ tool &amp; Die making with experience in material testing, exposure to using testing standards • Proficient with CAD tools such as AutoCAD/CATIA etc.,) The application can be downloaded from the college website. The duly filled in application with all relevant documents should reach the Principal on or before 28.11.2024. The age limit is as per the Karnataka Civil Service (General Recruitment) Rules. Candidates should appear for the interview, if called, at their own cost with all the Original documents Management reserves the rights of processing (accept/reject) the application Notwithstanding the above conditions, if any relevant orders issued and which are in force will be made applicable for consideration Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220" t="str">
+        <v>2026-03-19T18:37:12.616Z</v>
+      </c>
+      <c r="F220">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>https://bmsce.ac.in/website_notifications/BMSCE_DIC_PhD_Advertisement_2024.pdf</v>
+      </c>
+      <c r="B221" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Page 1 of 2 B.M.S. COLLEGE OF ENGINEERING ( Estd 1946, Autonomous Institute under VTU ) Bull Temple Road, Bangalore - 560 019, Karnataka, India. No. BMSCE/Ph.D. Admission /2024-25/July Session Date: 23.07.2024 Admission to Ph.D. Programme (Full-Time/Part-Time) under Visvesvaraya Ph.D. Scheme Digital India Corporation, Ministry of Electronics and Information Technology, Govt. of India Implementation Order No: PhD-PT02/2024-01/51 &amp; PhD-02/2024-02/72 Applications are invited from eligible and interested research candidates for the Ph.D programme (Full-Time/Part- Time) under “Visvesvaraya PhD Scheme for Electronics &amp; IT- Phase- II”, by Digital India Corporation (DIC), MeitY, Govt. of India. B.M.S. College of Engineering will be the research centre and the degree will be awarded by Visvesvaraya Technological University, Belgaum, Karnataka. Details of the Scheme: https://www.myscheme.gov.in/schemes/vpseit VTU Ph.D Regulations: jnanashodha.vtu.ac.in/Regulations/PhD2023Regulation.pdf Vacancy Table Full-Time Ph.D. 02 Part-Time Ph.D. 01 The details of the scheme can be found at the end of this advertisement. The summary of the same is as below Eligibility: • The candidates shall possess a master’s degree in engineering/ technology or equivalent degree by the University, with a minimum CGPA of 6.75 out of 10 or 60% aggregate marks at the Master’s degree. • GATE candidates will be given preference. • For the part-time registration, the candidate should be working in an organization (Academic institution or industry). Financial Assistance: Full time Candidates: • Stipend/Fellowship (Full-time Ph.D.) @ Rs. 38,750/- per month for first and second years @ Rs. 43,750/- per month for Third, Fourth and Fifth Year • Reimbursement of Rent (RoR): 24% (As per the prevailing norms &amp; approval from DIC) • Research Contingency Grant: Rs.1,20,000/Year • Support for attending International Conference : Support up to 1.5 Lakhs from third year onwards • Visit to labs abroad : From third year of PhD based on approval from DIC Page 2 of 2 Part time Candidates • A one- time incentive of ₹ 3,00,000/- would be provided on successful completion of the Ph.D. Important Dates Online application registration process start date 29/07/2024 Last date for the submission of online Application form 15/08/2024 Web notification of the short-listed candidates for written test and/or Interview 16/08/2024 Dates of interview (for short-listed candidates) 24/08/2024 Announcement of Results 25/08/2024 Application Procedure: • Interested and eligible candidates shall submit an online application using the form https://tinyurl.com/phd-bmsce-application-dic along with the following o Application Form: https://tinyurl.com/phd-dic-application o Enclosures to be submitted along with the application ▪ Date of Birth (DOB) Certificate or High School (Class 10th) Certificate with DOB ▪ SC/ST/OBC(NCL) Certificate, if applicable ▪ Certificate of Physical Disability, if applicable ▪ A valid GATE/CSIR/UGC score card, if applicable ▪ Copies of mark/grade sheets of qualifying degree or higher ▪ No Objection Certificate from employer (only for part-time). Full-time students currently working must produce NOC or Relieving Certificate from the employer at the time of admission. ▪ Details of two referees (Name, Designation, Affiliation, Email ID) Selection Procedure: Based on norms of the University and DIC, MeitY, GOI Tentative Broad Research Areas: (Under Visvesvaraya Fellowship) Department Full-Time and Part-Time ECE &amp; allied VLSI (ASIC, FPGA, Chip design, etc), Embedded Systems, Communications, Digital Signal Processing, Digital Image Processing, Instrumentation, Antennas, Power Electronics, Photonics, Photovoltaics, optical fibre communication and other related areas of Electronics and Communication Engineering For any queries, the applicants can contact Dr. Abhishek Appaji, Head R&amp;D and Nodal Officer (Visvesvaraya PhD Scheme for Electronics and IT), B.M.S. College of Engineering, Bengaluru email to: hod.rnd@bmsce.ac.in / Mobile: 9844923632</v>
+      </c>
+      <c r="D221">
+        <v>0</v>
+      </c>
+      <c r="E221" t="str">
+        <v>2026-03-19T18:37:13.839Z</v>
+      </c>
+      <c r="F221">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Check_List.pdf</v>
+      </c>
+      <c r="B222" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C222" t="str">
+        <v>ENGINEERING ADMISSIONS 2024-2025 B.M.S. COLLEGE OF ENGINEERING, BENGALURU (AUTONOMUS INSTITUTION UNDER VTU) Check list of the Original Documents to be submitted by the Candidates selected through CET at the time of verification of documents in the college Admission Order issued by KEA ( 04 copies) TH II PUC/12 STD. Marks Cards A.Study Cer_x0000_ficate from previous College/ Ins_x0000_tute (Total 07 Years) B.Students allo_x0000_ed under RURAL QUOTA are required to submit 10 years rural cer_x0000_ficates Caste Cer_x0000_ficate in case of Reserved Category [ i.e., SC, ST &amp; OBC] and students admi_x0000_ed under SNQ Quota are required to submi_x0000_ed Income Cer_x0000_ficate compulsorily Transfer Cer_x0000_ficate Migra_x0000_on Cer_x0000_ficate shall be submi_x0000_ed by Non-Karnataka students and students who have passed their qualifying examina_x0000_on other than PU Board. Students allo_x0000_ed under SPECIAL CATEGORY QUOTA (i.e., Rural, Kannada Medium, NCC, Sports, PH, Defence candidates etc.,) are required to submit the relevant original cer_x0000_ficates &amp; students admi_x0000_ed under Hyderabad Karnataka Quota, are required to submit the relevant original cer_x0000_ficates. [ Annexure - “A'' – Eligibility Cer_x0000_ficate &amp; Annexure - “B'' – Residience Cer_x0000_ficate] Recent Photos – 02 Nos. (Passport Size) Copy of AADHAAR CARD and any other documents if required CANDIDATES HAVE TO SUBMIT ORIGINALS OF ALL THE ABOVE DOCUMENTS FOR VERIFICATION ALONG WITH TWO SETS OF SELF ATTESTED COPIES . NOTE : STUDENTS ARE INFORMED TO KEEP SUFFICIENT COPIES OF THE ABOVE DOCUMENTS WITH THEM AS THE ORIGINAL WILL BE SENT TO VTU FOR APPROVAL OF THEIR ADMISSION. ORIGINAL MARKS CARDS WILL BE RETURNED TO STUDENTS ONLY AFTER APPROVAL OBTAINED / U S N RECEIVED FROM V T U, BELAGAVI. ENGINEERING ADMISSIONS 2024-2025 B.M.S. COLLEGE OF ENGINEERING, BENGALURU (AUTONOMUS INSTITUTION UNDER VTU) Check list of the Original Documents to be submitted by the Candidates selected through Mgt. &amp; Comed-K at the time of verification of documents in the college Seat Allotment Letter issued by Comed-K / Endorsement issued by Management (04 Copies) with fee receipt. Please ensure that the candidate name and parent name should be printed as per SSLC / 10th STD. marks cards TH II PUC/12 STD. Marks Cards TH SSLC / 10 STD. Marks Cards [ for proof of Date of Birth] Transfer Cer_x0000_ficate Migration Certificate shall be submitted by Non-Karnataka students and students who have passed their qualifying examination other than PU Board. Students allotted through Comed-K under Hyderabad Karnataka Quota, are required to submit the relevant original certificates. [ Annexure - “A'' – Eligibility Certificate &amp; Annexure - “B'' – Residience Certificate] Rank Card of any one of the Competitive Examination i.e, CET/Comed-K / JEE of Current Year (i.e., 2023-24 ) in respect of Management Quota only Recent Photos – 02 Nos. (Passport Size) Copy of AADHAAR CARD and any other documents if required CANDIDATES HAVE TO SUBMIT ORIGINALS OF ALL THE ABOVE DOCUMENTS FOR VERIFICATION ALONG WITH TWO SETS OF SELF ATTESTED COPIES NOTE : STUDENTS ARE INFORMED TO KEEP SUFFICIENT COPIES OF THE ABOVE DOCUMENTS WITH THEM AS THE ORIGINAL WILL BE SENT TO VTU FOR APPROVAL OF THEIR ADMISSION. ORIGINAL MARKS CARDS WILL BE RETURNED TO STUDENTS ONLY AFTER APPROVAL OBTAINED / U S N RECEIVED FROM V T U, BELAGAVI B.M.S. COLLEGE OF ENGINEERING, BENGALURU (AUTONOMUS INSTITUTION UNDER VTU) ENGINEERING ADMISSIONS 2024-2025 GENERAL INSTRUCTIONS TO CANDIDATES Venue : PLATINUM ACADEMIC JUBILEE BUILDING – GROUND FLOOR Step Step by Step Process Venue On-line entry of application Remittance of Fees Library - NPTEL LAB [First Floor] On-Line / Indian Bank, BMSCE Campus 1. 2. 3. 4. 5. 6. 7. 8. 9. 10. 1. 2. 3. 4. 5. 6. 7. 8. 9. 10. 1. 2. 4. Documents Verification &amp; submit Original Documents along with three sets of self-attested copies in respect of Comed-K &amp; Management Students and Two Sets of self-attested copies in respect of KEA Students [ Ground Floor] Dining Hall Behind Auditorium 1 &amp; 2 Overall In-Charge of Admission Process Dr. Bheemsha - Principal Process is supervised by : Prof. K Girish – Faculty of M C A People to be contacted: 1. Dr. Srinidhi Raghavan M., (Assistant Professor, Dept. of Chemistry) In-charge of Document related issues. 2. Prof. H S Gururaja - (Faculty of ISE) In-charge of Software related issues. WORKING HOURS Monday to Friday : 09.30 AM to 04.30 PM nd th College is remain closed on all Sundays, 2 &amp; 4 Saturdays and on Government Holidays. TH SSLC / 10 STD. Marks Cards [ for proof of Date of Birth] A. Study Cer_x0000_ficate from previous College/ Ins_x0000_tute B. Caste Cer_x0000_ficate in respect of students having score less than 45% in qualifying examina_x0000_on i.e.,II PUC/12TH Std Lunch Time: 01.00 PM to 02.00 PM Students are required to scan all the original documents along with name of file in JPEG format only &amp; size should be less than 200 DPI resolution and need to be submitted in the form of soft copy compulsorily in a pen drive. 3. Library - NPTEL LAB [First Floor]</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222" t="str">
+        <v>2026-03-19T18:37:14.594Z</v>
+      </c>
+      <c r="F222">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>https://bmsce.ac.in/website_notifications/General%20Conditions%20for%20recruitment.pdf</v>
+      </c>
+      <c r="B223" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C223" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU NOTIFICATION OF FACULTY RECRUITMENT General Conditions (TEACHING) The application can be downloaded from the website. The duly filled in applications along with required enclosures should reach the Principal as per the last date given on the BMSCE college website. CSE/AIML/AIDS/CSDS/ CSE(IOT)/CSBS Assistant Professor: The minimum qualification required is as per AICTE Norms, preference will be given to the candidates with Ph.D qualification, candidates who have registered for Ph.D can also apply. Associate Professor: • Ph.D degree in the relevant field and First Class or equivalent at either Bachelor’s or Master’s level in the relevant branch. And At least total of 6 research publications in SCI / Scopus journals approvaed list of journals. And Minimum of 8 years of experience in teaching/research/industry out of which at least 2 years shall be Post Ph.D. experience. STATISTICS Assistant Professor: The minimum qualification required is B.Sc (Statistics) and M.Sc (Statistics) or B.Stat and M.Stat with Ph.D degree in concerned/allied disciplines. The candidates who have completed Ph.D Viva Voce may also apply. MATHEMATICS/PHYSICS/CHEMISTRY Assistant Professor: The minimum qualification required is as per AICTE Norms, preference will be given to the candidates with Ph.D qualification, candidates who have registered for Ph.D can also apply. NOTE : Preference shall be given to candidates with Ph.D. Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms. • The details of the publications / patents/ funded projects need to be mentioned in the application. • Experience: As per AICTE norms. • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules • Management reserves the rights of processing (accept/reject) the application. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration.</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223" t="str">
+        <v>2026-03-19T18:37:15.180Z</v>
+      </c>
+      <c r="F223">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>https://www.bmsce.ac.in/assets/files/NewsEvents/Mech_JRF_BMSCE.pdf</v>
+      </c>
+      <c r="B224" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Department of Mechanical Engineering B.M.S. College of Engineering PB No.1908, Bull Temple Road Bengaluru – 560 019 Ph: +91-80-26622130-35, Extn. 119,8016 Fax: +91-80-2661 4357 URL: www.bmsce.ac.in Email: hod.mech@bmsce.ac.in Autonomous Institute, affiliated to VTU Accredited by NBA &amp; NAAC A Aeronautics R&amp;D Board (AR&amp;DB) DRDO, Ministry of Defence Room No. 411, DRDO HQ Annexe Metcalfe House, Civil Lines Delhi – 110 054 Ph: 011-2390 2743 Fax: 011-2390 2794 Email: ardb.hqr@gov.in Ref. No. BMS/ARDB-4522/2024/01 Date: 01-07-2024 Advertisement for Junior Research Fellow (JRF) Applications are invited for the position of Junior Research Fellow (JRF) in a research and development project ( Under grants-in-aid scheme of Aeronautics R&amp;D Board ) for a duration of 3 years (2024-2027) with the following details: Project Title: TECHNOLOGY DEMONSTRATION OF INTERSHAFT SQUEEZE FILM DAMPER (ISSFD) FOR TWO SPOOL GAS TURBINE APPLICATION Candidates with experience or knowledge in the following domains can apply: 1. Knowledge of subjects viz. Strength of Materials, Design of M/c elements, Mechanical Vibrations and Rotor Dynamics 2. Basic knowledge on Solid Modelling &amp; Analytical software 3. Basic knowledge on Data acquisition &amp; Signal processing is preferable. Job description: The research staff is required: 1. To be part of Design &amp; development of Two-spool Test setup and will be working at B.M.S. College of Engineering Campus, Bengaluru-19. 2. To work on the project assigned and will be reporting to principal and co-principal investigators. 3. To carry out testing and field studies and preparation of reports. 4. To be part of research team in completion of project leading to Product development. 5. To be part of research team in taking care of publication, patenting and technical documentation of the project. Job position: Name of the position No. of vacancies Minimum Qualification Junior Research Fellow (JRF) 01 Degree in B.E. BE – Mechanical Engineering/Aerospace Engineering &amp; M.Tech / M.E in Machine Design/Maintenance Engineering/ Aerospace Engineering Terms and Conditions for JRF are as follows: Age Limit : Not more than 35 years. Salary: As per DRDO norms (Rs. 37,000 pm +HRA for first Two years and SRF @ Rs.42,000+HRA for Third year) Essential Qualifications: M.Tech./M.E. in Machine Design/Maintenance Engineering/Aerospace Engineering/Any other relevant stream with a minimum of 60% aggregate score (6.5/10 CGPA). Proof of M. Tech/ M.E certificate has to be provided during the interview. Duration: Maximum of 03 years or up to the termination of the project, subject to annual performance review. The candidate is encouraged to apply for Ph.D. at BMSCE. How to apply: Interested candidates must apply by filling out the attached application form along with the following documents. (1) Cover letter (2) Bio-data with passport-sized photograph (3) Scanned copies of educational certificates and mark sheets (class-X onwards) and (4) Scanned copies of Proof of research experience &amp; special achievements and publications (if any). The soft copies of the application form and required documents (pdf format) must be emailedto shivaprasad.mech@bmsce.ac.in by 10 th July 2024 .Only shortlisted candidates will be intimated by email and called for an interview. The position is available immediately. The appointment will be on a purely temporary basis co-terminus with the project.</v>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224" t="str">
+        <v>2026-03-19T18:37:16.063Z</v>
+      </c>
+      <c r="F224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>https://bmsce.ac.in/website_notifications/General%20Conditions%20for%20recruitment%20(21.06.2024).pdf</v>
+      </c>
+      <c r="B225" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C225" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING Autonomous Institute, Affiliated to VTU NOTIFICATION DATED: _21.06.2024 IN TIMES OF INDIA NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING) The application can be downloaded from the website. The duly filled in applications along with required enclosures should reach the Principal on or before 29.06.2024. CSE/AIML/AIDS/CSDS/ CSE(IOT)/CSBS Assistant Professor: • The minimum qualification required is as per AICTE Norms, preference will be given to the candidates with Ph.D qualification, candidates who have registered for Ph.D can also apply. Associate Professor: • Ph.D degree in the relevant field and First Class or equivalent at either Bachelor’s or Master’s level in the relevant branch. And At least total of 6 research publications in SCI / Scopus journals approvaed list of journals. And Minimum of 8 years of experience in teaching/research/industry out of which at least 2 years shall be Post Ph.D. experience. MBA Assistant Professor: • The minimum qualification required is as per AICTE Norms, preference will be given to the candidates with Ph.D qualification, candidates who have registered for Ph.D can also apply. Associate Professor: • Ph.D degree in the relevant field and First Class or equivalent at either Bachelor’s or Master’s level in the relevant branch. And At least total of 6 research publications in ABDC/Scopus indexed/UGC/Pear reviewed unpaid journals. Post Ph.D publication and guiding Ph.D students is highly desirable. And Minimum of 8 years of experience in teaching/research/industry out of which at least 2 years shall be Post Ph.D. experience. STATISTICS Assistant Professor: • The minimum qualification required is B.Sc (Statistics) and M.Sc (Statistics) or B.Stat and M.Stat with Ph.D degree in concerned/allied disciplines. The candidates who have completed Ph.D Viva Voce may also apply. NOTE : Preference shall be given to candidates with Ph.D Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms. • The details of the publications / patents/ funded projects need to be mentioned in the application. • Experience: As per AICTE norms. • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules • Management reserves the rights of processing (accept/reject) the application. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration. PLACEMENT OFFICER Qualification &amp; Eligibility Criteria for Placement Officer: • Master's Degree (full-time) from a reputed university, MBA Preferable. • Minimum 5-10 years of industry experience with 2 years in a leadership role, preferably in related roles. • Excellent Communication Skills, PR, liaison and relationship building. • Ability to develop sound, credible and reciprocal relations with industry. • Ability to work with UG and students who are from various social and economic backgrounds. • . Note : • Mere fulfillment of the minimum qualification will not vest any right on a candidate for being called for a written test/skill test/interview, etc. • The Institute reserves the right to hold a written test / skill test / interview as the case may be to select candidates for these positions. • The Institute reserves the right of rejecting any or all the applications without assigning any reasons thereof and also to re-advertise the posts if no suitable candidates are found. Decision of the Institute will be final and binding in this regard. • The Institute reserves the right to relax any of the qualifications and/or experience in exceptional cases of meritorious candidates. Higher initial basic pay may be given to exceptionally qualified and deserving candidate(s). The Institute reserves the right not to fill any/some posts herein advertised, cancel the advertisement in whole or in part without assigning any reason and its decision in this regard shall be final. Canvassing in any form/bringing in any influence political or otherwise will be treated as a disqualification for the post. “Interim Enquiry will not be entertained.” • The Institute reserves its right to place a reasonable limit on the total number of candidates to be called for an interview. • In case of any inadvertent mistake in the process of selection which may be detected at any stage even after the issue of appointment letter, the Institute reserves the right to modify/withdraw/cancel any communication made to the candidate. • No correspondence whatsoever will be entertained from candidates regarding conduct and result of test/interview and reasons for not being called for interview. PRINCIPAL</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225" t="str">
+        <v>2026-03-19T18:37:16.793Z</v>
+      </c>
+      <c r="F225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>https://www.bmsce.ac.in/website_notifications/Placement%20Officer%20Application%20(21.06.2024).pdf</v>
+      </c>
+      <c r="B226" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C226" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR PLACEMENT OFFICER Application No. For the Post of: Department: Reference: (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of Application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 13. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 16. Patents (please attach a separate sheet) Filed Published Granted 17. Consultancy (please attach a separate sheet) Awarded On-going 18. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 19. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 20. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 21. Special Award / Achievements or any other information : (please attach a separate sheet) 22. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 23. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 24. Leadership (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 25. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 26. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 27. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 28. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226" t="str">
+        <v>2026-03-19T18:37:17.439Z</v>
+      </c>
+      <c r="F226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>https://www.bmsce.ac.in/website_notifications/Advertisement%20(21.06.2024).pdf</v>
+      </c>
+      <c r="B227" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C227" t="str">
+        <v>B.M.S. EDUCATIONAL TRUST, BENGALURU B.M.S. COLLEGE OF ENGINEERING BENGALURU – 560 019 Autonomous Institute, Affiliated to VTU Notification No: BMS 08 EST (U) 2024 Date: 21.06.2024 BMSCE invites applications from candidates with high academic achievements, research craving mind with constructive attitude for the following positions under Management Cadre: ASSOCIATE PROFESSOR For the Departments of • Machine Learning (Artificial Intelligence &amp; Machine Learning) • MBA ASSISTANT PROFESSOR For the Departments of • Computer Science &amp; Engineering (CSE) • Machine Learning (Artificial Intelligence &amp; Machine Learning) • Artificial Intelligence &amp; Data Science (AI &amp; DS) • Computer Science &amp; Engineering (Data Science) • Computer Science &amp; Engineering (IoT &amp; Cyber Security including Block Chain Technology) • Computer Science &amp; Business Systems. • MBA • Statistics PLACEMENT OFFICER Associate Professor &amp; Assistant Professor : Ph.D. degree preferred from premier institutions with good publications in addition to the qualification and experince as per AICTE norms. For Qualification, Experience, application format and other conditions, please visit www.bmsce.ac.in . The duly filled in applications along with required enclosures should reach the Principal on or before 29.06.2024. PRINCIPAL, BMSCE</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227" t="str">
+        <v>2026-03-19T18:37:18.053Z</v>
+      </c>
+      <c r="F227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>https://bmsce.ac.in/recruitment</v>
+      </c>
+      <c r="B228" t="str">
+        <v>html</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Note:- 7th PAY SCALE AS PER MANAGEMENT NORMS. Instructions : Applications are invited for the Management Faculty positions at the level of Assistant Professors for the following Departments. Departments Qualification Experience 1)Department of Computer Science &amp; Engineering. 2) Information Science Engineering. 3) Artificial Intelligence &amp; Machine Learning. 4) CSE (Data Science). 5) CSE (IOT and Cyber Security &amp; blockchain technology). 6) Artificial Intelligence and Data Science. 7) Computer Science and Business Systems. Candidates with PhD in the relevant domain are preferred. Desirable BMSCE Recruitment Portal Use registered Email-id to Login into the portal Email ID Password Login Forgot Password? If you don't have an Account, Click here to Register</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228" t="str">
+        <v>2026-03-19T18:37:18.615Z</v>
+      </c>
+      <c r="F228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>https://bmsce.ac.in/website_notifications/JRF-Recruitment-Notfication_STARS-IISC-project-Jan-2024.pdf</v>
+      </c>
+      <c r="B229" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C229" t="str">
+        <v>B.M.S. College of Engineering, Bengaluru Department of Mathematics Notification: Call for the position of JRF (OR) PROJECT ASSOCIATE Ref: BMSCE/MATH/STARS2-IISC/2023/0820 08 th Jan 2024 Applications are invited from eligible and interested candidates for the post of Junior Research Fellow (JRF) or Project Associate on a consolidated basis to work on the Scheme for Transformational and Advanced Research in Sciences (STARS) funded project by IISC, Bangalore. Name of the post Junior Research Fellow (JRF) (OR) Project Associate Title of the Project DEEP NEURAL NETWORK PATH TO MULTIPHYSICS MODELING OF HEAT TRANSFER IN POROUS MEDIA Principal Investigator Dr. Bandaru Mallikarjuna, Assistant Professor, Dept. of Mathematics, B.M.S. College of Engineering, Bengaluru Co-PIs Prof. B.V.Rathish Kumar, Professor in Mathematics &amp; Statistics, IIT Kanpur, Kanpur. Dr. Sandeep Varma N, Associate Professor, Dept. of Machine Learning, B.M.S. College of Engineering, Bengaluru Number of posts One Duration of employment The joining date will be immediately after selection. The initial appointment will be for one year, which is extendable up to 2 years, subject to the candidate’s performance . S.No. Manpower Position Essential Qualification Upper Age Limit (Years) Monthly Emoluments (Rs.) 1 JRF M.Sc. in Mathematics or equivalent from a recognized University/Institution with CSIR-UGC NET / GATE. (OR) 30 Rs 31,000/- + HRA p.m. for the first two years and Rs 35,000/- p.m +HRA for the third year 2 PROJECT ASSOCIATE – I M.Sc. in Mathematics or equivalent from a recognized University/Institution without CSIR-UGC NET / GATE. 30 Rs 25,000/- + HRA p.m. for the first two years and Rs 28,000/- p.m +HRA for the third year 3 PROJECT ASSOCIATE – II M.Sc. in Mathematics or equivalent from a recognized University/Institution without CSIR-UGC NET / GATE and two years ’ experience in Research and Development in Industrial and Academic Institutions or Science and Technology organizations 30 Rs 28,000/- + HRA p.m. Note: There is a provision for the selected candidate to enroll in the Ph.D. program at the department, as per the host institution's affiliated university norms. B.M.S. College of Engineering, Bengaluru Department of Mathematics Expectations: ● Work on developing a Neural Network Framework to solve Differential Equations ● Work along with industry research and development team ● Possible presentation and attending conferences/workshops ● Possible publications in refereed journals ● Experience the research culture in modern computation labs ● Collaborate with Undergraduate and postgraduate students for experimentation ● Interact with academicians and researchers for the research work General Conditions: 1) Eligible candidates fulfilling the criteria may apply with their resume and relevant documents without fail. Otherwise, the applications will not be considered by filling out the Google form below: https://docs.google.com/forms/d/e/1FAIpQLSf_V1Su8bPg4ySFMUdlrhhU4ez0PBiLF5- lawiMUTFIQh85aQ/viewform?usp=pp_url 2) The last date for receiving applications is 20th Jan 2024, 5 PM IST. 3) The applicant will be responsible for the authenticity of the information, other documents and photographs submitted. 4) The Institute reserves the right to accept applications at any time and consider candidates of exceptional credentials without applications. Qualification and experience may be relaxed at any point in time for extraordinary candidates. 5) Possessing the prescribed qualification does not ensure that the candidate will be called for an interview. The Candidates will be shortlisted based on merit and need of the project. 6) Shortlisted candidates will be emailed about the interview after the deadline. So, the candidate must provide a valid email ID. 7) Shortlisted candidates must present themselves for the interview on the interview date with an updated CV and original and attested photocopies of mark sheets/certificates supporting their academic qualifications. 8) No TA/DA will be paid for attending the written test/interview. 9) Candidates who are already employed should produce a relieving certificate from their employers if selected. 10) This appointment will be purely contractual. Initially, an appointment will be for one year. It will be extendable for two more years based on the performance of the c andidate and the recommendation of the selection/review committee. Address for Correspondence: Dr. B. Mallikarjuna, (Principal Investigator), Assistant Professor in the Department of Mathematics, B.M.S. College of Engineering, Bull Temple Road, Bengaluru-560019, India. Mobile: +91-8971319832, Email: mallikarjunab.maths@bmsce.ac.in B.M.S. College of Engineering, Bengaluru Department of Mathematics Application for the Position of Junior Research Fellow 1. Post Applied for: JRF / PROJECT ASSOCIATE 2. Name of the Candidate: 3. Father’s Name: 4. Mother’s Name: 5. (a) Date of Birth: (DD/MM/YYYY) (b) Sex (Male/Female/Other): (c) Marital Status: Married/Single (d) Category: SC/ST/OBC/PWD/ General 6. Previous Research Experience: (use additional sheet if required) 7. Publication(s), if any: (use additional sheet if required) 8. GATE/ UGC-NET details: Qualified (Yes/No): 9. Score: Rank: Specialization: Year: 10. Academic Qualification: (Starting from Standard 10 or equivalent Examination) Name of Exam Passed Name of the School/College/Institute/ University Year of Passing Discipline/ Specialization Percentage of Marks/ CGPA B.M.S. College of Engineering, Bengaluru Department of Medical Electronics Engineering 11. a) Address for Communication: (BLOCK LETTERS): (b) Contact No (Mob): (c) E-mail ID: 12. Contact Details of two referees: Referee I Referee II Name: Designation: Organization: Office Address: Office Phone Number: Email ID: 13. Experience if any (in years and use additional sheet if required) I do hereby declare that the information furnished in this application is true to the best of my knowledge and belief. If selected, I promise to abide by the rules and regulations of the Institute. Date: Place: Signatur e Note - An extra A4 sheet may be attached if any information is required.</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229" t="str">
+        <v>2026-03-19T18:37:19.334Z</v>
+      </c>
+      <c r="F229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>https://bmsce.ac.in/website_notifications/JRF-Recruitment-Notfication_STARS-IISC-project-Dec-2023.pdf</v>
+      </c>
+      <c r="B230" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C230" t="str">
+        <v>B.M.S. College of Engineering, Bengaluru Department of Mathematics Notification: Call for the position of JRF Ref: BMSCE/MATH/STARS2-IISC/2023/0820 06 th Dec 2023 Applications are invited from eligible and interested candidates for the post of Junior Research Fellow (JRF) on a consolidated basis to work on the Scheme for Transformational and Advanced Research in Sciences (STARS) funded project by IISC, Bangalore. Name of the post Junior Research Fellow (JRF) Title of the Project DEEP NEURAL NETWORK PATH TO MULTIPHYSICS MODELING OF HEAT TRANSFER IN POROUS MEDIA Principal Investigator Dr. Bandaru Mallikarjuna, Assistant Professor, Dept. of Mathematics, B.M.S. College of Engineering, Bengaluru Co-PIs Prof. B.V.Rathish Kumar, Professor in Mathematics &amp; Statistics, IIT Kanpur, Kanpur. Dr. Sandeep Varma N, Associate Professor, Dept. of Machine Learning, B.M.S. College of Engineering, Bengaluru Number of posts One Essential qualification M.Sc. in Mathematics or equivalent recognized University/Institution with CSIR-UGC NET / GATE Desirable qualification Differential Equations, Fluid Mechanics, Neural Networks, Python programming. Upper Age limit Maximum 28 years Relaxation SC/ST/OBC/Women/PWD/EWS applicants will get relaxation as per the GOI norms. Consolidated salary Rs 31,000/- + HRA p.m. for the first two years and Rs 35,000/- p.m +HRA for the third year Duration of employment The joining date will be immediately after selection. The initial appointment will be for one year, which is extendable up to 2 years, subject to the candidate’s performance . Note: There is a provision for the selected candidate to enroll in the Ph.D. program at the department, as per the host institution's affiliated university norms. B.M.S. College of Engineering, Bengaluru Department of Mathematics Expectations: ● Work on developing a Neural Network Framework to solve Differential Equations ● Work along with industry research and development team ● Possible presentation and attending conferences/workshops ● Possible publications in refereed journals ● Experience the research culture in modern computation labs ● Collaborate with Undergraduate and postgraduate students for experimentation ● Interact with academicians and researchers for the research work General Conditions: 1) Eligible candidates fulfilling the criteria may apply with their resume and relevant documents without fail. Otherwise, the applications will not be considered by filling out the Google form below: https://docs.google.com/forms/d/e/1FAIpQLSf_V1Su8bPg4ySFMUdlrhhU4ez0PBiLF5- lawiMUTFIQh85aQ/viewform?usp=pp_url 2) The last date for receiving applications is 20th Dec 2023, 5 PM IST. 3) The applicant will be responsible for the authenticity of the information, other documents and photographs submitted. 4) The Institute reserves the right to accept applications at any time and consider candidates of exceptional credentials without applications. Qualification and experience may be relaxed at any point in time for extraordinary candidates. 5) Possessing the prescribed qualification does not ensure that the candidate would be called for an interview. The Candidates will be shortlisted based on merit and need of the project. 6) Shortlisted candidates will be emailed about the interview after the deadline. So, the candidate must provide a valid email ID. 7) Shortlisted candidates must present themselves for the interview on the interview date with an updated CV and original and attested photocopies of mark sheets/certificates supporting their academic qualifications. 8) No TA/DA will be paid for attending the written test/interview. 9) Candidates who are already employed should produce a relieving certificate from their employers if selected. 10) This appointment will be purely contractual. Initially, an appointment will be for one year. It will be extendable for two more years based on the performance of the c andidate and the recommendation of the selection/review committee. Address for Correspondence: Dr. B. Mallikarjuna, (Principal Investigator), Assistant Professor in the Department of Mathematics, B.M.S. College of Engineering, Bull Temple Road, Bengaluru-560019, India. Mobile: +91-8971319832, Email: mallikarjunab.maths@bmsce.ac.in B.M.S. College of Engineering, Bengaluru Department of Mathematics Application for the Position of Junior Research Fellow 1. Post Applied for: JRF 2. Name of the Candidate: 3. Father’s Name: 4. Mother’s Name: 5. (a) Date of Birth: (DD/MM/YYYY) (b) Sex (Male/Female/Other): (c) Marital Status: Married/Single (d) Category: SC/ST/OBC/PWD/ General 6. Previous Research Experience: (use additional sheet if required) 7. Publication(s), if any: (use additional sheet if required) 8. GATE/ UGC-NET details: Qualified (Yes/No): 9. Score: Rank: Specialization: Year: 10. Academic Qualification: (Starting from Standard 10 or equivalent Examination) Name of Exam Passed Name of the School/College/Institute/ University Year of Passing Discipline/ Specialization Percentage of Marks/ CGPA B.M.S. College of Engineering, Bengaluru Department of Medical Electronics Engineering 11. a) Address for Communication: (BLOCK LETTERS): (b) Contact No (Mob): (c) E-mail ID: 12. Contact Details of two referees: Referee I Referee II Name: Designation: Organization: Office Address: Office Phone Number: Email ID: 13. Experience if any (in years and use additional sheet if required) I do hereby declare that the information furnished in this application is true to the best of my knowledge and belief. If selected, I promise to abide by the rules and regulations of the Institute. Date: Place: Signatur e Note - An extra A4 sheet may be attached if any information is required.</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230" t="str">
+        <v>2026-03-19T18:37:19.950Z</v>
+      </c>
+      <c r="F230">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Advertisement%20(21.06.2024).pdf</v>
+      </c>
+      <c r="B231" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C231" t="str">
+        <v>B.M.S. EDUCATIONAL TRUST, BENGALURU B.M.S. COLLEGE OF ENGINEERING BENGALURU – 560 019 Autonomous Institute, Affiliated to VTU Notification No: BMS 08 EST (U) 2024 Date: 21.06.2024 BMSCE invites applications from candidates with high academic achievements, research craving mind with constructive attitude for the following positions under Management Cadre: ASSOCIATE PROFESSOR For the Departments of • Machine Learning (Artificial Intelligence &amp; Machine Learning) • MBA ASSISTANT PROFESSOR For the Departments of • Computer Science &amp; Engineering (CSE) • Machine Learning (Artificial Intelligence &amp; Machine Learning) • Artificial Intelligence &amp; Data Science (AI &amp; DS) • Computer Science &amp; Engineering (Data Science) • Computer Science &amp; Engineering (IoT &amp; Cyber Security including Block Chain Technology) • Computer Science &amp; Business Systems. • MBA • Statistics PLACEMENT OFFICER Associate Professor &amp; Assistant Professor : Ph.D. degree preferred from premier institutions with good publications in addition to the qualification and experince as per AICTE norms. For Qualification, Experience, application format and other conditions, please visit www.bmsce.ac.in . The duly filled in applications along with required enclosures should reach the Principal on or before 29.06.2024. PRINCIPAL, BMSCE</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231" t="str">
+        <v>2026-03-19T18:37:20.533Z</v>
+      </c>
+      <c r="F231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Teaching%20Application%20-%2027.04.2022.pdf</v>
+      </c>
+      <c r="B232" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C232" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No.___________________________________________ For the Post of: ____________________________________________ Department: ______________________________________________ Reference: ________________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2 . Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on 11-05-2022 (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 13. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 16. Patents (please attach a separate sheet) Filed Published Granted 17. Consultancy (please attach a separate sheet) Awarded On-going 18. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 19. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 20. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 21. Special Award / Achievements or any other information : (please attach a separate sheet) 22. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 23. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 24. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 25. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 26. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 27. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 28. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters Details of Fee Paid DD No. Date Amount Bank &amp; Branch Name</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232" t="str">
+        <v>2026-03-19T18:37:21.157Z</v>
+      </c>
+      <c r="F232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>https://bmsce.ac.in/website_notifications/ICSSR_Call_for_Research_Assistant_Field_Investigator.pdf</v>
+      </c>
+      <c r="B233" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C233" t="str">
+        <v>BMS Phone : +91-80-2662 2130-135, Extn.133 Fax : +91-80-2661 4357 Email : hod.mba@bmsce.ac.in URL : www.bmsce.in ESTD:1946 COLLEGE OF ENGINEERING Autonomous Instiution|Affiliated to VTU|Approved by AICTE|Accredited by NBA Department of Management Studies and Research Centre 15 th October 2023 Ref. No: BMSCE/MBA/ICSSR/SEP2023 Call for Research Assistant / Field Investigator ICSSR Funded Short-Term Empirical Research Project Eligible and interested candidates are invited for an interview for the post of Research Assistant/Field Investigator purely on tenure basis at Department of Management Studies &amp; Research Centre, BMS College of Engineering, Bangalore. The post is created under the Research Project, sanctioned by the Indian Council of Social Science Research (ICSSR), New Delhi under the scheme of ICSSR Special Call for Short Term Empirical Research (Vide Sanction Order F.No. 18/CIS-2023-1776/DDAY/SCD dated 29/09/2023). The details of the position for the above Project, with Consolidated Salary &amp; Eligibility Conditions are given below: Project Title Impact Assessment of Deendayal Antyodaya Yojana with Respect to Support to Urban Street Vendors (SUSV) Scheme in Bengaluru Urban Duration Maximum 03 months Name of Post Research Assistant/Field Investigator Number of Post 01/02 Essential Qualifications A Postgraduate degree with at least 55% marks or its equivalent grade in any Social Science discipline from a recognized university. Desirable Qualifications UGC NET, Proficiency in using Ms. Excel and statistical software such as SPSS, Excellent data analysis and report writing skills Other Essential Requirement Research assistant shall be reporting to department full time during the tenure. Field Investigator is expected to travel in Urban Bangalore for data collection. Experience (Preferable for Research Asst.) Three years’ experience as Researcher/ Research Assistant/ Field Investigator in an academic institute/ research organization of repute Emoluments Rs. 32,000/ p.m.- for Research Assistant &amp; Rs. 28,000/-p.m. for Field Investigator (As per ICSSR guidelines) How to Apply Interested candidates are requested to fill the Google form ( https://forms.gle/a6A6iEfkyRfgEDJX8 ) on or before 18 November, 2023, 5:00 PM. General Terms and Conditions The post is purely temporary. The appointment may be terminated any time before the expiry of the stipulated period if the work is deemed to be unsatisfactory. All original certificates should be produced for verification at the time of interview. No TA/DA will be paid for attending the interview or joining the position. Date of interview will be intimated to the shortlisted candidates by email. For any further query, the candidate may contact at smithavshenoy.mba@bmsce.ac.in Phone: 9480091278. Dr. Smitha V Shenoy Project Director Assistant Professor, Department of Management Studies &amp; Research Centre P.B. NO. 1908, Bull Temple Road, Bangalore - 560 019, Karnataka, INDIA</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233" t="str">
+        <v>2026-03-19T18:37:21.949Z</v>
+      </c>
+      <c r="F233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>https://bmsce.ac.in/website_notifications/C2S_Adv_JRF_SRF_RA-final_BMSCE.pdf</v>
+      </c>
+      <c r="B234" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Ref. No. CRG/2023/001 10-10-2023 Advertisement for Junior Research Fellow (JRF), Senior Research Fellow (SRF) and Research Assistant (RA) Applications are invited for the position of Junior Research Fellow (JRF) Senior Research Fellow (SRF) and Research Assistant (RA) , in a research and development project (under CHIPS TO START-UP PROGRAMME (C2S) CATEGORY – I PROPOSALS) for the duration of 2 years (2023-2025) with the following details: Title of the project: “ DESIGN AND DEVELOPMENT OF GROUND PENETRATING RADAR WITH ON-FIELD RECONFIGURATION CAPABILITY APPLICABLE TO SUSTAINABLE INDUSTRIAL AND AGRICULTURAL PURPOSES ” Candidates with experience or knowledge in the following domains can apply: 1. PCB design 2. Analog &amp; mixed signal design 3. RF CMOS 4. Antenna design 5. CMOS layout design and schematic capture 6. FPGA design 7. Microcontrollers and embedded systems Familiarity with programming languages: 1. HDL 2. MATLAB 3. Embedded C 4. C/C++ 5. Python Job description: 1. System level design of GPR system 2. Design and development of image processing software for ground penetrating radar 3. System in Package of GPR system 4. RF front end design (LNA, Mixers, Power Amplifiers, Buffers) of GPR and Antenna Design 5. ASIC design of base band system 6. FPGA development and prototyping Academic Partners MSME partner End User Implementation Agency 7. Analog design and mixed signal design (data converters) Research staff will be working from Cambridge Institute of Technology campus and visiting collaborating Institute as per the need basis . Fresher’s (with UG/PG/PhD) qualification can apply for the above positions. The core team will be able to train the team members and then deployed on the project. Software familiarity – SYNOPSYS, CANDENCE, Mentor Graphics (Siemens), Ansys, MATLAB, PCB Design Job positions: Name of the Position No. of positions/ vacancies Qualification Junior Research Fellow (JRF) 4 BE – ECE M.Tech – ECE, VLSI or any other equivalent discipline Senior Research Fellow (SRF) 1 M.Tech – ECE, VLSI or any other equivalent discipline PhD - ECE Research Assistant (RA) 2 M.Tech – ECE, VLSI or any other equivalent discipline – 5 years experience PhD - ECE Terms and Conditions for JRF, SRF &amp; RA are as follows Age Limit: - Not more than 28 Years for JRF, 35 years for SRF and RA. Age relaxation as per DST, GOI norms Salary: - As per DST norms + HRA Qualification: Essential Qualifications: - M.Tech./M.E. in Electronics &amp;Communication Engineering with a minimum of 60% aggregate score (6.5/10 CGPA) for JRF &amp; RA, Ph. D degree from reputed University for SRF. Candidate must have qualified GATE examination (old gate score is also considered). Proof of M.Tech/ M.E/ Ph. D certificate has to be provided during the interview. Duration: 01 year or up to the termination of the project, subject to annual performance review. The candidate is encouraged to apply for PhD at Cambridge Institute of Technology or BMSCE or Reva University, Bangalore or SNS college of Technology, Coimbatore, Tamil Nadu. Roles and Responsibilities : The candidate is required work on the project assigned and will be reporting to respective principal investigators of respective colleges. Project progress will be monitored and the candidate needs to participate in all review meetings. All the team members will be responsible for successful completion of project. Product development, testing and field studies need to be carried out. Report preparation, publication, patenting and technical documentation will be part of the project. How to apply: Interested candidates must apply by filling out the attached application form along with the following documents (1) Cover letter (2) Bio-data with passport-sized photograph, (3) Scanned copies of educational certificates and mark sheets (class-X onwards) (4) GATE qualified certificate and (5) Scanned copies of Proof for research experience, special achievements and publications, if any. The soft copies of the application form and required documents (pdf format) must be emailed to girish.ece@cambridge.edu.in by 17 th October 2023 . The email address for correspondence is given above. Only shortlisted candidates will be intimated by email and called for an interview. The position is available immediately. The appointment will be on a purely temporary basis co-terminus with the project. APPLICATION FOR THE POST OF JUNIOR RESEARCH FELLOW / SENIOR RESEARCH FELLOW (SRF) / RESEARCH ASSISTANT For Office Use: Paste your recent Passport size photo Serial Number: Eligible for Written exam/Interview: Yes / No Verified the Certificates: 1. Name: 2. Father’s Name: 3(a). Date of Birth: (DD/MM/YYYY) 3(b). Nationality: 4. Contact information: (i) Address for communication: (ii) Mobile No: (iii) Email ID: 5. Educational Qualifications* Class Subject/ Stream Board/ University Name of Institute Marks/ CGPA Year of Passing X XII B.E/B.Tech. M.E/M.Tech. Ph. D Competitive Exam Qualified Marks / Rank Year CSIR-UGC NET Yes / No GATE Yes / No *Attach self-attested copies of all certificates. 6. Work Experience, if any (in years) ………………………… Organization Designation Duration Responsibilities 7. Number of Publications: (Attach a separate list of publications with full details) National International 8. Workshop/Training programs attended*: Sl. No. Details *Attach separate sheet (if required) 9. Other Achievements*: Sl. No. Details *Attach separate sheet (if required) Declaration : All the above particulars provided by me are true to the best of my knowledge and I understand that, if found incorrect, I may be disallowed to appear in the interview/test. Date: Place: Signature of the Candidate Note: Attach the list of enclosures along with the application.</v>
+      </c>
+      <c r="D234">
+        <v>0</v>
+      </c>
+      <c r="E234" t="str">
+        <v>2026-03-19T18:37:22.573Z</v>
+      </c>
+      <c r="F234">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Ad_for_ICSSR.pdf</v>
+      </c>
+      <c r="B235" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Advertisement to be given for recruitment of Field Officer and Resaerch Assistant as per ICSSR for Short-term Empirical Research Project Field officer: Looking for a Field Officer in the Department of Biotechnology, BMS College of Engineering under Short-term Empirical Research Project ( 3 months ) entitled “A Study of Social Awareness and Education About Eco- friendly Menstruation Hygiene Practices in Rural Karnataka”, Funded by ICSSR, GOI. Interested and eligible Candidates may send their resume to email savithri.bt@bmsce.ac.in Qualification: Postgraduate in Engineering or any Social Science areas ( Economics, Arts, Geography, History, Law, Linguistics, Politics, Psychology and Sociology ) Minimum 60% or 6.0 CGPA Research Assistant: Looking for Research Assistant in the Department of Biotechnology, BMS College of Engineering under Short-term Empirical Research Project (5 months ) entitled “A Study of Social Awareness and Education About Eco-friendly Menstruation Hygiene Practices in Rural Karnataka”, Funded by ICSSR, GOI. Interested and eligible Candidates may send their resume to email savithri.bt@bmsce.ac.in Qualification: graduate or post graduate in engineering or any social science areas. Minimum 70% or 7.5 CGPA</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235" t="str">
+        <v>2026-03-19T18:37:23.130Z</v>
+      </c>
+      <c r="F235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>https://bmsce.ac.in/website_notifications/application_for_RA_filed_inv.pdf</v>
+      </c>
+      <c r="B236" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C236" t="str">
+        <v>B . M . S COL L EGE OF ENG I NEER I NG, B A NGALOR E - 19 (A u t o nom o u s Inst i tute, A f f i liat e d t o V T U ) Department of Management Studies &amp; Research C entre Ref . No: BMS/MBA/NCW/2023 - 2024/GC01 06/10/2023 Call for Application : Research Study ( N ational C ommission for W omen ) on : “Women in Decision Making Roles in C orporate” Eligible and interested candidates are invited to apply for the post of Research Assistant/Fi eld Investigator purely on tenure basis at Department of Management S tudies &amp; R esearch C entre, B.M.S C ollege of Engineering, Bull Temple Road, Bangalore - 560019. The post is created under the Research Project, sanctioned by National Commission for Women , New Delhi (Vide Ack . No: NCW/1202112310321/RS/2023 - 2024/4663 dated 17/08/2023 ). Project Title GLASS CEILING: AN INVISIBLE BARRIER IMPACTING CAREER GROWTH AND ENGAEGMENT OF WOMEN IN CORPORATE SECTOR Duration Maximum 11 months For Research Assistant and 8 months for Field Investigator/s Name of Post Research Assistant/Field Investigator Number of Post 01/02 Essential Qualifications Research Assistant : Postgraduate degree with at least 55% marks in any Social Science discipline from a recognize d university. Field Investigator : Graduate with at least 55% marks in any Social Science discipline from a recognized university. Desirable Qualifications for Research assistant 1. Proficiency in using statistical software such as SPSS or R. 2. Data analysis and report writing skills. Essential Requirement for Filed Investigator Willingness to travel in Karnataka State for data collection. Fluency in English language is essential, Local language desirable Experience ( for Research Assistant) ( for Filed investigator ) Experience as Researcher/ Field Investigator in an academic institute/ R esearch organization of repute would be added advantage Marketing and data collection experience would be added advantage Emoluments Rs. 24 ,000 p.m for Research Assistant (including TA) Rs. 300 per sample collected (As per NCW guidelines) plus TA of Rs 400 per day for Field Investigator How to Apply Interested candidates are requested to fill the Google form https://forms.gle/nhqufCGxmJ4DjjyU9 General Terms and Conditions 1. The post is only for the mentioned duration. The appointment may be terminated before the expiry of the stipulated period if the work is found to be unsatisfactory. 2. The selected candidates need to give an undertaking to complete the assigned work on time. 3. All original certificates should be produced for verification at the time of interview. 4. The shortlisted candidates would appear for an interview, the same would be intimated by email. 5. For any further query, contact at : bns.mba@bmsce.ac.in , shubhamuralidhar.mba@bmsce.ac.in , rsushma.mba@bmsce.ac.in Mobile : 9886264753, 9620023789, 9845942067</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236" t="str">
+        <v>2026-03-19T18:37:23.714Z</v>
+      </c>
+      <c r="F236">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>http://bmsce.ac.in/website_notifications/General%20conditions%20-19.07.2023.pdf</v>
+      </c>
+      <c r="B237" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C237" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE 560 019 Autonomous Institute, Affiliated to VTU NOTIFICATION DATED:1 9.07.2023 IN TIMES OF INDIA NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING)  The application can be downloaded from the website. The duly filled in application along with DD for Rs.1000/- drawn in favour of The Principal, BMSCE, payable at Bangalore and other relevant documents should reach the Principal on or before 02.08.2023.  Separate applications are to be submitted in the event of candidates applying for more than one faculty position with separate DD for each position.  Qualification: Minimum qualification for all faculty positions is PhD Degree preferably from premier Institutions with good publications. NOTE : Preference shall be given to candidates with Ph.D Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms.  The details of the publications / patents/ funded projects need to be mentioned in the application.  Experience: As per AICTE norms.  Candidates should appear for the interview, if called, at their own cost with all the original documents.  The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules.  Management reserves the rights of processing (accept/reject) the application.  Application fee once paid is non-refundable and non-transferable.  Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration. Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237" t="str">
+        <v>2026-03-19T18:37:24.600Z</v>
+      </c>
+      <c r="F237">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>http://bmsce.ac.in/website_notifications/Teaching%20Application-19.07.2023.pdf</v>
+      </c>
+      <c r="B238" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C238" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No.___________________________________________ For the Post of: ____________________________________________ Department: ______________________________________________ Reference: ________________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2 . Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on 11-05-2022 (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 13. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 16. Patents (please attach a separate sheet) Filed Published Granted 17. Consultancy (please attach a separate sheet) Awarded On-going 18. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 19. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 20. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 21. Special Award / Achievements or any other information : (please attach a separate sheet) 22. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 23. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 24. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 25. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 26. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 27. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 28. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters Details of Fee Paid DD No. Date Amount Bank &amp; Branch Name</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238" t="str">
+        <v>2026-03-19T18:37:25.286Z</v>
+      </c>
+      <c r="F238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Updated_Management_Final_GK-CHECK_LIST_FOR_ADM__2023-24.pdf</v>
+      </c>
+      <c r="B239" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C239" t="str">
+        <v>CHECK LIST FOR FIRST YEAR BE ADMISSION FOR STUDENTS REPORTING THROUGH K E A QUOTA FOR THE ACADEMIC YEAR 2023-24 CHECK LIST FOR FIRST YEAR BE ADMISSION FOR STUDENTS REPORTING TROUGH COMED-K AND MANAGEMENT QUOTA FOR THE ACADEMIC YEAR 2023-24 B. M. S. COLLEGE OF ENGINEERING, BENGALURU . (AUTONOMUS INSTITUTION UNDER VTU) ENGINEERING ADMISSIONS – 2023 - 24 Check list of the Original Documents to be submitted by the Candidates selected through CET at the time of verification of documents in the college. B. M. S. COLLEGE OF ENGINEERING, BENGALURU. (AUTONOMUS INSTITUTION UNDER VTU) ENGINEERING ADMISSIONS - 2023 - 24 Check list of the Original Documents to be submitted by the Candidates selected through Mgt. &amp; Comed-K at the time of verification of documents in the college. 1 Admission Order issued by KEA ( 04 Copies) 1 For Comed-K Students: Seat Allotment Letter issued by Comed-K along with Fee receipt (04 Copies) For Management Seats: Provisional seat allotment letter issued by Management along with fee receipt. (04 Copies) Please ensure that the candidate name and parent name should be printed as per SSLC / 10 th marks card. 2 SSLC / 10 TH Marks Card [ for proof of Date of Birth] 2 SSLC / 10 TH Marks Card [ for proof of Date of Birth] 3 II PUC / 12 TH Marks Card. 3 II PUC / 12 TH Marks Card. 4 Study Certificate from previous College/Institute (Total 07 Years) 4 Study Certificate from previous College/Institute &amp; Caste Certificate in respect of students having score less that 45% in qualifying examination 5 Caste Certificate in case of Reserved Category [ i.e., SC, ST &amp; OBC ] and students admitted under S N Q Quota are required to submitted Income Certificate compulsorily. 5 Transfer Certificate 6 Transfer Certificate 6 Migration Certificate shall be submitted by Non-Karnataka students and students who have passed their qualifying examination other than PU Board. 7 Migration Certificate shall be submitted by Non-Karnataka students and students who have passed their qualifying examination other than PU Board. 7 Students allotted through Comed-K under Hyderabad Karnataka Quota, are required to submit the relevant original certificates. [ Annexure - “A’’ – Eligibility Certificate &amp; Annexure - “B’’ – Residience Certificate. 8 Students allotted under SPECIAL CATEGORY QUOTA (i.e., Rural, Kannada Medium, NCC, Sports, PH, Defence candidates etc.,) are required to submit the relevant original certificates &amp; students admitted under Hyderabad Karnataka Quota, are required to submit the relevant original certificates. [ Annexure - “A’’ – Eligibility Certificate &amp; Annexure - “B’’ – Residience Certificate. 8 Rank Card of any one of the Competitive Examination i.e, CET / Comed-K / JEE of Current Year (i.e., 2023-24 ) in respect of Management Quota only. 9 Recent Photos – 02 Nos. (Passport Size) 9 Recent Photos – 02 Nos. (Passport Size) 10 Copy of AADHAAR CARD and any other documents if required. 10 Copy of AADHAAR CARD and any other documents if required. 11 Students are required to scan all the above original documents along with Passport Size Photo and Signature individually in JPEG format only &amp; size should be less than 2MB [ with 200 DPI resolution] and need to be submitted in the form of soft copy compulsorily in a pen drive. 11 Students are required to scan all the above original documents along with Passport Size Photo and Signature individually in JPEG format only &amp; size should be less than 2MB [ with 200 DPI resolution] and need to be submitted in the form of soft copy compulsorily in a pen drive. CANDIDATES HAVE TO SUBMIT ORIGINALS OF ALL THE ABOVE DOCUMENTS FOR VERIFICATION ALONG WITH TWO SETS OF SELF ATTESTED COPIES. NOTE : Students are informed to keep sufficient copies of the above Documents with them as the Original will be sent to VTU for approval of their admission. Original marks cards will be returned to students only after approval obtained / USN received from VTU, belagavi. CANDIDATES HAVE TO SUBMIT ORIGINALS OF ALL THE ABOVE DOCUMENTS FOR VERIFICATION ALONG WITH THREE SETS OF SELF ATTESTED COPIES. NOTE : Students are informed to keep sufficient copies of the above Documents with them as the Original will be sent to VTU for approval of their admission. Original marks cards will be returned to students only after approval obtained / USN received from VTU, belagavi. B. M. S. COLLEGE OF ENGINEERING, BENGALURU . (AUTONOMUS INSTITUTION UNDER VTU) ENGINEERING ADMISSIONS 2023-24 GENERAL INSTRUCTIONS TO CANDIDATES Venue : PLATINUM ACADEMIC JUBILEE BUILDING – GROUND FLOOR Step Step by Step Process Venue 1 On-line entry of application Main Library - NPTEL LAB [ First Floor] 2. Remittance of Fees On-Line / Indian Bank, BMSCE Campus 3. Documents Verification &amp; submit Original Documents along with three sets of self-attested copies in respect of Comed-K &amp; Management Students and Two Sets of self- attested copies in respect of KEA Students Dining Hall Behind Auditorium 1 &amp; 2 [ Ground Floor] Overall In-Charge of Admission Process Dr. Muralidhar S - Principal Process is supervised by: 1. Prof. Girish K – Faculty of MCA. 2. Prof. Gururaja H S – Faculty of ISE. WORKING HOURS Monday to Friday : 09.30 AM to 04.30 PM Saturday : 09.30 AM to 01.00 PM College is remain closed on all Sundays and Government Holidays. Lunch Time: 01.00 PM to 02.00 PM</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239" t="str">
+        <v>2026-03-19T18:37:25.940Z</v>
+      </c>
+      <c r="F239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Non-Teaching%20Application%20form-%2015-12-2022.pdf</v>
+      </c>
+      <c r="B240" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C240" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA Non-Teaching Application No.___________________________________________ For the Post of:____________________________________________ Department:______________________________________________ Reference:________________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupati on 3. Address for Correspondence 4. Contact Number &amp; E-mail address Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Examination passed(if any) Please affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Examination passed SSLC onwards (for group D posts give the highest exam passed) Name of the Institution/University Year of Passing Percentage of Marks Class Awarded 13. Total No. of Year Experience Name of the Institution/Organization Designation Date of Job Details Entry Leaving Declaration I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate Check – List of documents to be attached with the application Title of the document No’s Please tick Attached Not Attached SSLC Marks Card or age proof document Caste Certificate Qualification Certificate Experience Certificate Technical Certificate Copy of Aadhar Card Copy of PAN Card Details of Fee Paid DD No. Date Amount Bank &amp; Branch Name The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240" t="str">
+        <v>2026-03-19T18:37:26.812Z</v>
+      </c>
+      <c r="F240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Website%20Notification%20-%2015.12.2022.pdf</v>
+      </c>
+      <c r="B241" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C241" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE-19 Autonomous Institute, Affiliated to VTU No. BMS 08 EST (U) 2022 Date: 08.12.2022 NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE Applications are invited for appointment of technical staff in the following department under Management cadre on consolidated pay. Sl.N o. Department Designatio n No. Posts Qualification required 1 Information Science &amp; Engg. Instructor 3 Nos 1. Must be a holder of First Class diploma in the respective branch of Engineering/Technology granted by an institution recognized by the Government or equivalent qualification to Diploma granted by the Board of Technical Examinations. 2. Must have an experience of not less than three years in the field from an institution recognized by the State Government. 2 Basic Chemistry Lab Technician 1 No. Must be a holder of First Class B.Sc. /M.Sc. by an institution recognized by the Government or equivalent qualification. (Preference will be given to B.Sc./M.Sc. in Analytical Chemistry) 3 Civil Engineering Asst. Instructor 2 Nos. Must be a holder of B.E./Diploma in Civil Engineering 4 Biotechnology Technical Asst. 1 No. Must be a holder of First Class B.Sc. Bio- Chemistry/ Microbiology/ Biotechnology) OR M.Sc.(Bio-Chemistry/Microbiology/Bio technology) OR B.E. in Biotechnology by an institution recognized by the Government or equivalent qualification. 5 Electronics &amp; Communication Engg. Instructor 1 No. Must be a holder of First Class diploma in the respective branch of Engineering/ Technology granted by an institution recognized by the Government or equivalent qualification to Diploma granted by the Board of Technical Examinations. Must have an experience of not less than three years in the field from an institution recognized by the State Government 6 Machine Learning (AI &amp; ML) Programmer 1 No. 1. B.E. in CSE/ISE/AIML with three years of experience OR Asst. Instructor 1 No. 2. Must be a holder of First Class Diploma in CSE/ISE/AIML with ten years of experience in Industry/Institution recognized by the Government. 1. Must be a holder of diploma in the respective branch of Engineering/Technology granted by an institution recognized by the Government or equivalent qualification to Diploma granted by the Board of Technical Examinations. The application can be downloaded from the website and Demand Draft of Rs.500/- towards the application fee shall be drawn in favour of the Principal, BMSCE payable at Bangalore. The duly filled in application with all relevant documents along with DD should reach the Principal at the earliest. The age limit is as per the Karnataka Civil Service (General Recruitment) Rules. Candidates should appear for the interview, if called, at their own cost with all the Original documents Management reserves the rights of processing (accept/reject) the application Application fee once paid is non-refundable and non-transferable Notwithstanding the above conditions, if any relevant orders issued and which are in force will be made applicable for consideration Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241" t="str">
+        <v>2026-03-19T18:37:27.368Z</v>
+      </c>
+      <c r="F241">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Website%20Notification%20-%2004.01.2023.pdf</v>
+      </c>
+      <c r="B242" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C242" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE-19 Autonomous Institute, Affiliated to VTU No. BMS 08 EST (U) 2023 Date: 04.01.2023 NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE Applications are invited for appointment of technical staff in the following department under Management cadre on consolidated pay . Sl.N o. Department Designation No. Posts Qualification required 1 Electronics &amp; Instrumentation Engg. Technical Assistant 2 Must be a Diploma holder in Instrumentation and allied branches 2 Aerospace Engg. Technical Asst. 3 Must be a holder of ITI/Diploma from Aerospace background 3 R &amp; D Technical Assistant 1 Must be a holder of Diploma in Mechanical/Civil/Aero/tool &amp; Die making. (1. Preference will be given to First Class holders with experience in material testing, exposure to using testing standards (2. Proficient with CAD tools such as AutoCAD/CATIA etc.,) The application can be downloaded from the website and Demand Draft of Rs.500/- towards the application fee shall be drawn in favour of the Principal, BMSCE payable at Bangalore. The duly filled in application with all relevant documents along with DD should reach the Principal on or before 15.01.2023. The age limit is as per the Karnataka Civil Service (General Recruitment) Rules. Candidates should appear for the interview, if called, at their own cost with all the Original documents Management reserves the rights of processing (accept/reject) the application Application fee once paid is non-refundable and non-transferable Notwithstanding the above conditions, if any relevant orders issued and which are in force will be made applicable for consideration Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D242">
+        <v>0</v>
+      </c>
+      <c r="E242" t="str">
+        <v>2026-03-19T18:37:28.145Z</v>
+      </c>
+      <c r="F242">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>https://bmsce.ac.in/website_notifications/User%20Manual%20for%20the%20Course%20Registration%20Portal.pdf</v>
+      </c>
+      <c r="B243" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C243" t="str">
+        <v>User Manual This user manual will explain the procedure for using the Course Registration Portal for first-year students. This document also highlights the guidelines which are to be followed while registering for the courses. Registration for the courses will be of two types: 1. Compulsory Courses. 2. Choice-Based Courses. Compulsory Courses: These courses are mandatory to register for and no choice will be given to the students. During the registration of such courses, the course name and code directly appear and the student is to click on the “Register” button for successful registration. Choice-Based Courses: For such courses, the students have to select one course from a list of subjects. During the registration of such courses when you click on the “Select” button, the dropdown menu will appear with the list of subjects, out of which the students is to select one subject by clicking on the “Select” button. After selecting one of the subjects, the student must click on the “Register” button for successful registration. Step-by-Step instructions for Course Registration Prerequisites: 1. Laptop or Desktop. 2. The latest version of one of these web browsers: Google Chrome / Mozilla Firefox / Brave / Safari, is recommended. 3. Stable internet connection. Instructions: Step 1: Head over to a web browser and open the first-year student portal. Link: https://firstyear.bmsce.ttcindia.co/ A window as displayed below should appear on your web browser. Login with the credentials you have used during your registration for the student portal. If you have not yet registered on the student portal. You can click on the “Sign Up” button, in the top right corner of the window. Step 2: On the top of the portal click on the “Course Registration” button. Step 3: The “Student Course Registration” window will appear as shown below. Click on the “Register” button to register for the course. Please note that the selection of the courses is sequential . This means one cannot proceed to the next course without registering for the previous course, which you can notice in the picture given below. Once you click the “Register” button, the button turns green in colour, indicating successful registration. Step 4: For choice-based subjects, click on the “Select” button. A drop down menu will open as shown in the figure below. Select one of the courses and click on the “Select” button. The button will turn green indicating successful selection. After this click on the “Register” button for successful registration. A dropdown of list of subjects available for registration Note: Once you click on the “Register” button, the course will be registered and cannot be changed for choice-based subjects. Step 5: After all 8 courses have been registered you will see a “Course registration completed” pop-up. Click on the “Finish” button to complete the registration process.</v>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+      <c r="E243" t="str">
+        <v>2026-03-19T18:37:28.754Z</v>
+      </c>
+      <c r="F243">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>https://bmsce.ac.in/website_notifications/User_Manual_for_the_Course_Registration_Portal.pdf</v>
+      </c>
+      <c r="B244" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C244" t="str">
+        <v>User Manual This user manual will explain the procedure for using the Course Registration Portal for first-year students. This document also highlights the guidelines which are to be followed while registering for the courses. Registration for the courses will be of two types: 1. Compulsory Courses. 2. Choice-Based Courses. Compulsory Courses: These courses are mandatory to register for and no choice will be given to the students. During the registration of such courses, the course name and code directly appear and the student is to click on the “Register” button for successful registration. Choice-Based Courses: For such courses, the students have to select one course from a list of subjects. During the registration of such courses when you click on the “Select” button, the dropdown menu will appear with the list of subjects, out of which the students is to select one subject by clicking on the “Select” button. After selecting one of the subjects, the student must click on the “Register” button for successful registration. Step-by-Step instructions for Course Registration Prerequisites: 1. Laptop or Desktop. 2. The latest version of one of these web browsers: Google Chrome / Mozilla Firefox / Brave / Safari, is recommended. 3. Stable internet connection. Instructions: Step 1: Head over to a web browser and open the first-year student portal. Link: https://firstyear.bmsce.ttcindia.co/ A window as displayed below should appear on your web browser. Login with the credentials you have used during your registration for the student portal. If you have not yet registered on the student portal. You can click on the “Sign Up” button, in the top right corner of the window. Step 2: On the top of the portal click on the “Course Registration” button. Step 3: The “Student Course Registration” window will appear as shown below. Click on the “Register” button to register for the course. Please note that the selection of the courses is sequential . This means one cannot proceed to the next course without registering for the previous course, which you can notice in the picture given below. Once you click the “Register” button, the button turns green in colour, indicating successful registration. Step 4: For choice-based subjects, click on the “Select” button. A drop down menu will open as shown in the figure below. Select one of the courses and click on the “Select” button. The button will turn green indicating successful selection. After this click on the “Register” button for successful registration. A dropdown of list of subjects available for registration Note: Once you click on the “Register” button, the course will be registered and cannot be changed for choice-based subjects. Step 5: After all 8 courses have been registered you will see a “Course registration completed” pop-up. Click on the “Finish” button to complete the registration process.</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244" t="str">
+        <v>2026-03-19T18:37:29.334Z</v>
+      </c>
+      <c r="F244">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Advertisement_No.pdf</v>
+      </c>
+      <c r="B245" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C245" t="str">
+        <v>B.M.S COLLEGE OF ENGINEERING, BANGALORE-560019 Autonomous Institution affiliated to VTU, Belagavi Advertisement No. DST-SERB/JRF/1/2022 Advertisement for Research Assistant for the project “Development of a Polymer Nano composite based Rapid Malaria Sensing Device” sponsored by SCIENCE &amp; ENGINEERING RESEARCH BOARD (SERB), with File No:SPG/2021/002668. Principal Investigator : Dr. Suma M S , Professor, Department of Medical Electronics Engineering, BMSCE, Bangalore-19. Essential Qualifications: M.E/MSc. /PhD in the area of Material Science /Electronics/Sensors Salary: Rs.25000/-(Rupees Twenty Five Thousand only) per month (Consolidated). Nature of Appointment: Contract based, extendable based on performance. Desirable candidates are requested to attend the walk-in interview on 7 th Nov.2022 Time: 10.30 a.m Venue: Dept.of Medical Electronics Engg.Platinum Jubilee Block, 6thFloor, B.M.S.C.E</v>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+      <c r="E245" t="str">
+        <v>2026-03-19T18:37:29.955Z</v>
+      </c>
+      <c r="F245">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Website%20Notification%20-%2010.10.2022.pdf</v>
+      </c>
+      <c r="B246" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C246" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE-19 Autonomous Institute, Affiliated to VTU No. BMS 08 EST (U) 2022 Date: 08.10.2022 NOTIFICATION FOR FACULTY RECRUITMENT UNDER MANAGEMENT CADRE Applications are invited for the Management Faculty positions at the level of Assistant Professors in the department of Computer Science Engineering, Information Science Engineering and Mathematics. Department Qualification Experience Computer Science Engg. and Information Science Engg. Note: Candidates with PhD are preferred. B.E./B.Tech and M.E./M.Tech in relevant branch with First Class or equivalent either in B.E.,/ B.Tech or M.E., M.Tech Desirable Mathematics Note: Ph.D Degree from premier institutions is mandatory in addition to the qualification and experience as per AICTE norms (candidates who have submitted thesis or completed their defense are also eligible). Must have First Class M.Sc degree (for Science) or must have secured not less than 60 percent of marks or an equivalent CGPA at the Master’s Degree level in the relevant subject from an Indian University. Must have passed the National Eligibility Test [NET] for Lecturers conducted by the UGC., CSIR or SLET conducted by the State Government or any authority accredited by the UGC. Provided that the candidates who have possessed PhD/ M. Phill qualification are exempted from passing NET/SLET. Desirable The application can be downloaded from the website and Demand Draft of Rs.1000/- towards the application fee shall be drawn in favour of the Principal, BMSCE payable at Bangalore. The duly filled in application with all relevant documents along with DD should reach the Principal at the earliest . The age limit is as per the Karnataka Civil Service (General Recruitment) Rules Candidates should appear for the interview, if called, at their own cost with all the original documents Management reserves the rights of processing (accept/reject) the application Application fee once paid is non-refundable and non-transferable Notwithstanding the above conditions, if any relevant orders issued and which are in force will be made applicable for consideration The details of the journal paper publications need to be mentioned in the application. Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D246">
+        <v>0</v>
+      </c>
+      <c r="E246" t="str">
+        <v>2026-03-19T18:37:30.520Z</v>
+      </c>
+      <c r="F246">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Website_Notification_-_08_10_2022.pdf</v>
+      </c>
+      <c r="B247" t="str">
+        <v>html</v>
+      </c>
+      <c r="C247" t="str">
+        <v>404 Not Found. The requested page url was not found in BMSCE Website. GO BACK TO HOME PAGE</v>
+      </c>
+      <c r="D247">
+        <v>0</v>
+      </c>
+      <c r="E247" t="str">
+        <v>2026-03-19T18:37:31.260Z</v>
+      </c>
+      <c r="F247">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>https://bmsce.ac.in/website_notifications/General%20conditions%20-27.04.2022.pdf</v>
+      </c>
+      <c r="B248" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C248" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE 560 019 Autonomous Institute, Affiliated to VTU NOTIFICATION DATED: 27.04.2022 IN TIMES OF INDIA NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING) • The application can be downloaded from the website. The duly filled in application along with DD for Rs.1000/- drawn in favour of The Principal, BMSCE, payable at Bangalore and other relevant documents should reach the Principal on or before 11.05.2022. • Separate applications are to be submitted in the event of candidates applying for more than one faculty position with separate DD for each position. • Qualification: Minimum qualification for all faculty positions is PhD Degree preferably from premier Institutions with good publications. Librarian : Qualifying in the national level test conducted for the purpose by the UGC or any other agency approved by the UGC. Master’s degree in Library Science / Information Science/Documentation or an equivalent professional degree with at least 55% of the marks or its equivalent CGPA and consistently good academic record, computerization of library. NOTE : Preference shall be given to candidates with Ph.D Degree from premier institutions with good publications in addition to the qualification and experience as per AICTE norms. • The details of the publications / patents/ funded projects need to be mentioned in the application. • Experience: As per AICTE norms. • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules. • Management reserves the rights of processing (accept/reject) the application. • Application fee once paid is non-refundable and non-transferable. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration. Sd/- PRINCIPAL B.M.S. COLLEGE OF ENGINEERING, BANGALORE 560 019 Autonomous Institute, Affiliated to VTU NOTIFICATION DATED: 27.04.2022 IN TIMES OF INDIA NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (NON-TEACHING) • The application can be downloaded from the website. The duly filled in application along with DD for Rs.500/- drawn in favour of The Principal, BMSCE, payable at Bangalore and other relevant documents should reach the Principal on or before 11.05.2022. • Qualification: Basic degree with good communication skills and experience in liaisoning activities with Alumni &amp; Management. • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules. • Management reserves the rights of processing (accept/reject) the application. • Application fee once paid is non-refundable and non-transferable. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration. Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D248">
+        <v>0</v>
+      </c>
+      <c r="E248" t="str">
+        <v>2026-03-19T18:37:31.960Z</v>
+      </c>
+      <c r="F248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Non-Teaching%20Application%20-%2027-04-2022.pdf</v>
+      </c>
+      <c r="B249" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C249" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA Non-Teaching Application No.___________________________________________ For the Post of:____________________________________________ Department:______________________________________________ Reference:________________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupati on 3. Address for Correspondence 4. Contact Number &amp; E-mail address Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Examination passed(if any) Please affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Examination passed SSLC onwards (for group D posts give the highest exam passed) Name of the Institution/University Year of Passing Percentage of Marks Class Awarded 13. Total No. of Year Experience Name of the Institution/Organization Designation Date of Job Details Entry Leaving Declaration I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate Check – List of documents to be attached with the application Title of the document No’s Please tick Attached Not Attached SSLC Marks Card or age proof document Caste Certificate Qualification Certificate Experience Certificate Technical Certificate Copy of Aadhar Card Copy of PAN Card Details of Fee Paid DD No. Date Amount Bank &amp; Branch Name The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+      <c r="E249" t="str">
+        <v>2026-03-19T18:37:32.547Z</v>
+      </c>
+      <c r="F249">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Librarian%20Application%20-%2027-04-2022.pdf</v>
+      </c>
+      <c r="B250" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C250" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR LIBRARIAN POSITION Application No.___________________________________________ For the Post of: ____________________________________________ Department: ______________________________________________ Reference: ________________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on 11-05-2022 (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) M.Lib Sc. M.Phil. UNDER GRADUATION (UG) Dip in Lib Sc. B.Lib Sc. Other 13. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 16. Patents (please attach a separate sheet) Filed Published Granted 17. Consultancy (please attach a separate sheet) Awarded On-going 18. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 19. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 20. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 21. Special Award / Achievements or any other information : (please attach a separate sheet) 22. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 23. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 24. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 25. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 26. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 27. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 28. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters Details of Fee Paid DD No. Date Amount Bank &amp; Branch Name</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250" t="str">
+        <v>2026-03-19T18:37:33.146Z</v>
+      </c>
+      <c r="F250">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>https://bmsce.ac.in/website_notifications/2021_Recruitment_Flyer_(1).pdf</v>
+      </c>
+      <c r="B251" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Applications are open! facebook.com/meltonfoundation @MFglobalcitizen @meltonfoundation linkedin.com/company/melton-foundation www.meltonfoundation.org The Melton Fellowship invests in young people from across the world who exhibit leadership in their local spheres. We bring these young people together to explore the global repercussions of local problems first hand and to equip them with skills and tools to drive change together , with their global peers and in their local communities. Calling all UN SDG advocates and young social impact leaders! Visit meltonfoundation.org or scan the QR code for more information! The Melton Foundation is leading proponent of global citizenship practice worldwide. Since 1991, our fellowship has empowered young change agents to become global problem solvers. By working together across boundaries of place and identity, we leverage cultural diversity and cross-sector collaboration to forge social change and innovation. The tech entrepreneur Bill Melton and peace activist Patricia Smith founded the Melton Foundation in 1991 to create a network of emerging leaders capable of positive global impact. Since then, the network has grown to over 550 Melton Fellows and a myriad of partner organizations across the globe! Global Citizenship is both attitude and action . To us, it is a combination of: Awareness about relevant global topics such as the United Nations Sustainable Development Goals (SDGs) and about how our actions have effects in our own communities and around the globe. Taking responsibility for the world’s problems, and because of this responsibility, Acting to forge solutions to these problems in both local and global contexts. Our Fellowship enables young people from across the world who exhibit leadership in their local spheres fellows ... to draw connections between the challenges faced in their communities and around the world, ... and provides them with the tools to take action to solve them together with others. Our Global Citizenship Model www.meltonfoundation.org What is the Melton Foundation? Melton Fellows complete a 1.5 year Global Citizenship Program followed by lifelong opportunities in our supported network as “Senior Fellows”. Our community is home to almost 600 Fellows ranging in age from 18 to 50+! Throughout our experiential learning program, Melton Fellows acquire skills in areas such as design thinking , intercultural communication, teamwork, project management, ethical leadership , community engagement, systems thinking and strategic communications. Throughout the fellowship, Melton Fellows develop strong bonds and truly enjoy working together. Thus, our model capitalizes on the power of trusting relationships as a catalyst for social change and develops role models for a generation of global citizens – empowered individuals working across boundaries of place and identity to help solve the challenges of today’s interconnected world. Our Program Fellows develop into responsible and accountable global problem solvers through hands-on experience and collaborative actions rooted in trust and mutual respect. After graduation from the program, Fellows form part of a supported network where they continue to build and contribute their capacity to think and act as global citizens in their growing spheres of influence in diverse world regions. www.meltonfoundation.org Young people with the motivation to become a local multiplier of positive social impact and join a global network of other emerging and established impact leaders who believe in Global Citizenship as a vital bridge toward better social and environmental relationships. Becoming a global citizen is a serious commitment – and fellows are expected to be active and engaged throughout the program. If selected into the fellowship, our commitment to you is to constantly support and challenge you on your path towards global citizenship. Who can apply? Bangalore, India Greater Accra, Ghana New Orleans, United States Jena, Germany Temuco, Chile Hangzhou, China To be eligible for the cohort of 202 2 , you must be a university student who is 18-25 years old as of the application deadline, and who will foreseeably live within the city limits of any of our partner universities for the next 1.5 years: www.meltonfoundation.org Applications are open! Visit meltonfoundation.org for more information or scan the QR code for more information!</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251" t="str">
+        <v>2026-03-19T18:37:33.989Z</v>
+      </c>
+      <c r="F251">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>https://bmsce.ac.in/website_notifications/First_Year_B_E__Inauguration_Invitation.pdf</v>
+      </c>
+      <c r="B252" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C252" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU Autonomous Institute, Affiliated to VTU You are cordially invited to the Inauguration First Year B.E. (2021-2022) Classes On Sunday, 19 th December 2021 at 11:00 am in the Indoor Stadium Chief Guest Prof. N. C. Shivaprakash Retd. Professor, Department of Instrumentation, IISc., Bengaluru Presided by Dr. B. S. Ragini Narayan Donor Trustee and Chairperson, BMSET &amp; BMSCE Guests of Honour Dr. P. Dayananda Pai Life Trustee, BMSET Sri. Aviram Sharma Trustee, BMSET Sri. Ravi Venkatesam Trustee, BMSET Principal, Faculty, Staff &amp; Students PROGRAMME SCHEDULE 11:00 am Invocation 11:05 am Lighting the Lamp 11:10 am Welcome Address by Dr S. Jayanthi, Dean FYB 11:15 am Brief Introduction about Principal 11:20 am Address by Principal Dr S. Muralidhara 11:30 am Brief Introduction about Dr. B.S. Ragini Narayan 11:35 am Presidential Address by Dr B. S. Ragini Narayan Donor Trustee and Chairperson BMSET&amp; BMSCE 11:40 am Brief introduction about Chief Guest 11:45 am Inaugural Address by Chief Guest Prof. N. C. Shivaprakash 12:05 pm Introduction of Sri Aviram Sharma 12:10 pm Address by Trustee Sri Aviram Sharma 12:20 pm Brief introduction about other Trustees 12:25 pm Feedback from Alumni students 12:30 pm Feedback from Parents 12:35 pm Vote of Thanks by Dr Krishnappa Olekar 12:40 pm National Anthem Programme followed by Lunch</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252" t="str">
+        <v>2026-03-19T18:37:34.696Z</v>
+      </c>
+      <c r="F252">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>http://bmsce.ac.in/website_notifications/Advertisement%20-27.09.2021.pdf</v>
+      </c>
+      <c r="B253" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C253" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE-19 Autonomous Institute, Affiliated to VTU No. BMS 08 EST (U) 2021 Date: 27.09.2021 NOTIFICATION FOR FACULTY RECRUITMENT UNDER MANAGEMENT CADRE IN DEPARTMENT OF CIVIL ENGINEERING Applications are invited for the Management Faculty positions at the level of Assistant Professors in the department of Civil Engineerng Qualification Experience M.E./M.Tech in relevant branch with First Class and Ph.D (Specialization in Structural, Environmental and Geo-Technical Engineering) Desirable Ph.D Degree from premier institutions is mandatory in addition to the qualification and experience as per AICTE norms (candidates who have submitted thesis or completed their defense are also eligible). The application can be downloaded from the website and Demand Draft of Rs.500/- towards the application fee shall be drawn in favour of the Principal, BMSCE payable at Bangalore. The duly filled in application with all relevant documents along with DD should reach the Principal on or before 04.10.2021. The age limit is as per the Karnataka Civil Service (General Recruitment) Rules Candidates should appear for the interview, if called, at their own cost with all the original documents Management reserves the rights of processing (accept/reject) the application Application fee once paid is non-refundable and non-transferable Notwithstanding the above conditions, if any relevant orders issued and which are in force will be made applicable for consideration The details of the journal paper publications need to be mentioned in the application. Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D253">
+        <v>0</v>
+      </c>
+      <c r="E253" t="str">
+        <v>2026-03-19T18:37:37.823Z</v>
+      </c>
+      <c r="F253">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>http://bmsce.ac.in/website_notifications/Teaching%20Application%20-%20%2025.08.2021.pdf</v>
+      </c>
+      <c r="B254" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C254" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA APPLICATION FOR FACULTY POSITION Application No.___________________________________________ For the Post of: ____________________________________________ Department: ______________________________________________ Reference: ________________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2 . Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; Email ID Mobile No : Email ID : 5. Date of Birth 6. Age as on 06-09-2021 (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRADUATION (PG) ME / M Tech M. Sc.(Engg) M.Phil/M.Sc. UNDER GRADUATION (UG) BE/B.Tech Other 13. Total No. of years of Research Experience Details ( Use separate sheets, if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Research grants (please attach a separate sheet) Awarded (Numbers &amp; In Rs.) On-going (Numbers &amp; In Rs.) 16. Patents (please attach a separate sheet) Filed Published Granted 17. Consultancy (please attach a separate sheet) Awarded On-going 18. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Months 19. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Months 20. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 21. Special Award / Achievements or any other information : (please attach a separate sheet) 22. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 23. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 24. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 25. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 26. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 27. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 28. List of documents to be attached with the application Title of the document Number of documents Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelors Degree Certificate Bachelors Degree Marks cards Masters Degree Certificate Masters Degree Marks cards Ph.D. Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore Title of the document Number of documents Please tick Attached Attached Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters Details of Fee Paid DD No. Date Amount Bank &amp; Branch Name</v>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+      <c r="E254" t="str">
+        <v>2026-03-19T18:37:38.495Z</v>
+      </c>
+      <c r="F254">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Advertisement_SERB_SPG.pdf</v>
+      </c>
+      <c r="B255" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C255" t="str">
+        <v>BMS COLLEGE OF ENGINEERING, BANGALORE (An autonomous institute under VTU) Advertisement No: BMSCE/EEE/DST-SERB/JRF/1/2021 Date: 25/08/2021 Advertisement for JRF (Junior Research Fellow) position under SERB POWER Grant sanctioned by DST-SERB Applications are invited for JRF (Junior Research Fellow) position (1 post) under the SERB POWER Grant sanctioned by DST-SERB titled “Investigations on electronic and optoelectronic properties of transition metal doped chalcogenide materials suitable for phase change memory (PCM) applicat ions” (File No. SPG/2021/000359) Principal Investigator Dr. Chandasree Das, Associate Professor, Micro Devices Lab, Department of Electrical and Electronics Engineering, BMS College of Engineering, Bengaluru-19 Essential Qualifications M.Tech. in Electrical and Electronics, Electronics and Communication, Electronics and Instrumentation, Electronics and Telecommunication, Medical Electronics or allied branches. Desirable (not must) Valid GATE score card is required to apply for this scholarship Salary Fellowship- Rs. 31000/- PM (Applicable to candidates with valid GATE Score card) Nature of Appointment Purely on temporary basis Duration of Employment The joining date will be immediately after selection. The initial appointment will be for six months which is extendable up to 2 years subject to performance of the candidate. Last Date for Application 15/09/2021 Desiring candidates are requested to submit their Curriculum Vitae to Principal Investigator by email: chandasreedas.eee@bmsce.ac.in with subject line “Application for DST -SERB Power Grant JRF Advertisement No.: BMSCE/EEE/DST-SERB/JRF/1/2021 ” Instructions:  The position is purely temporary for 6 months and likely to be continued if the performance is satisfactory  Mere fulfilment of qualifications/experience requirements does not entitle a candidate to be called for interview. Only shortlisted candidate will be called for an interview and no TA/DA will be paid to attend the interview.  Canvassing in any form will be a disqualification and no interim correspondence will be entertained.  Candidates should produce original testimonials/certificates, as a proof of the details furnished in their application, at the time of test/interview for verification, failing which they will not be allowed to appear for test/interview.  It is necessary to work until one year and if candidate leaves in the middle of the project he/she may have to return the salary drawn from the project money and proper non-disclosure agreement need to be signed by the candidate relevant to this condition.</v>
+      </c>
+      <c r="D255">
+        <v>0</v>
+      </c>
+      <c r="E255" t="str">
+        <v>2026-03-19T18:37:39.056Z</v>
+      </c>
+      <c r="F255">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>http://bmsce.ac.in/website_notifications/General%20conditions%20-%2025.08.2021.pdf</v>
+      </c>
+      <c r="B256" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C256" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE 560 019 Autonomous Institute, Affiliated to VTU NOTIFICATION DATED: 25.08.2021 IN TIMES OF INDIA NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING)  The application can be downloaded from the website. The duly filled in application along with DD for Rs.500/- drawn in favour of The Principal, BMSCE, payable at Bangalore and other relevant documents should reach the Principal on or before 06.09.2021.  Separate applications are to be submitted in the event of candidates applying for more than one faculty position with separate DD for each position.  Qualification: Minimum qualification for all faculty positions is PhD Degree preferably from premier Institutions with good publications.  The details of the publications / patents/ funded projects need to be mentioned in the application.  Experience: As per AICTE norms.  Candidates should appear for the interview, if called, at their own cost with all the original documents.  The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules.  Management reserves the rights of processing (accept/reject) the application.  Application fee once paid is non-refundable and non-transferable.  Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration. Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256" t="str">
+        <v>2026-03-19T18:37:39.648Z</v>
+      </c>
+      <c r="F256">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>https://bmsce.ac.in/website_notifications/BMSCE_DST_CSRI_NOTIFICATION_Jul_2021.pdf</v>
+      </c>
+      <c r="B257" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C257" t="str">
+        <v>B.M.S. College of Engineering, Bengaluru Department of Medical Electronics Engineering Notification: Call for JRF Ref: BMSCE/ML/DST-CSRI/2021-22/002 12 th July 2021 Applications are invited from eligible candidates for the post of a Junior Research Fellow (JRF) on contract basis for the DST-CSRI funded project entitled “Are retinal vascular abnormalities endophenotype in schizophrenia: An examination in first degree relatives”, under Dr. H N Suma, Professor &amp; Dr. Abhishek Appaji, Assistant Professor, Dept. of Medical Electronics Engineering, B.M.S. College of Engineering, Bengaluru. Name of the post Junior research fellow (JRF) Number of post One Essential qualification M. Tech in Biomedical Signal Processing and Instrumentation or allied Desirable qualification Hands on experience on acquisition and analysis of retinal images will be required Maximum Age limit 35 years Monthly salary structure Rs 31000 + 24% HRA Duration of employment The joining date will be immediately after selection. The initial appointment will be for six months which is extendable up to 1.5 years subject to performance of the candidate Eligible candidates fulfilling the criteria, may apply with their resume and relevant documents without fail, otherwise the applications will not be considered. Please fill the form in the link https://forms.gle/XoZVsKw8TEQ83RSM8. Last date for submitting the application is 25 July 2021, 5PM IST. For any further queries or clarification contact hns.ml@bmsce.ac.in / abhishek.ml@bmsce.ac.in.</v>
+      </c>
+      <c r="D257">
+        <v>0</v>
+      </c>
+      <c r="E257" t="str">
+        <v>2026-03-19T18:37:40.202Z</v>
+      </c>
+      <c r="F257">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>https://bmsce.ac.in/notifications/Website%20Advt%20for%20Tech%20staff%20-%20EE.pdf</v>
+      </c>
+      <c r="B258" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C258" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE-19 Autonomous Institute, Affiliated to VTU No. BMS 08 EST (U) 2021 Date: 27.04.2021 NOTIFICATION FOR TECHNICAL STAFF RECRUITMENT UNDER MANAGEMENT CADRE Applications are invited for appointment of technical staff in the department of Electrical &amp; Electronics Engineering under Management cadre Departments Qualification Experience Electrical &amp; Electronics Engg Diploma in respective branch of Engineering Desirable The application can be downloaded from the college website. The duly filled in application with all relevant documents should reach the Principal on or before 15.05.2021 through post or through mail establishmentsection@bmsce.ac.in . The age limit is as per the Karnataka Civil Service (General Recruitment) Rules Candidates should appear for the interview, if called, at their own cost with all the original documents Management reserves the rights of processing (accept/reject) the application Notwithstanding the above conditions, if any relevant orders issued and which are in force will be made applicable for consideration The details of the publication need to be mentioned in the application. Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D258">
+        <v>0</v>
+      </c>
+      <c r="E258" t="str">
+        <v>2026-03-19T18:37:40.826Z</v>
+      </c>
+      <c r="F258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>https://bmsce.ac.in/notifications/Non-Teaching.pdf</v>
+      </c>
+      <c r="B259" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C259" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU / Approved by AICTE / Accredited by NBA Non-Teaching Application No.___________________________________________ For the Post of:____________________________________________ Department:______________________________________________ Reference:________________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupa tion 3. Address for Correspondence 4. Contact Number &amp; E-mail address Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Examination passed(if any) Please affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Examination passed SSLC onwards (for group D posts give the highest exam passed) Name of the Institution/University Year of Passing Percentage of Marks Class Awarded 13. Total No. of Year Experience Name of the Institution/Organization Designation Date of Job Details Entry Leaving Declaration I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate Check – List of documents to be attached with the application Title of the document No’s Please tick Attached Not Attached SSLC Marks Card or age proof document Caste Certificate Qualification Certificate Experience Certificate Technical Certificate Copy of Aadhar Card Copy of PAN Card The Applicants are required to submit the filled in application form in duplicate to the following address. To, The Principal BMS College of Engineering PO Box No. 1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D259">
+        <v>0</v>
+      </c>
+      <c r="E259" t="str">
+        <v>2026-03-19T18:37:41.408Z</v>
+      </c>
+      <c r="F259">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>https://bmsce.ac.in/website_notifications/VTU-clarification_to_extension.pdf</v>
+      </c>
+      <c r="B260" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Visvesvaraya Technological University Belagavi - 590 018, Karnataka State, INDIA Dr. B. E. Rangaswamy Ph.D. Phone : (0831) 2498131 Registrar (Evaluation) Fax : (0831) 2498184 Ref. No.VTU/BGM/Reg(E)/PS/2020-2021/ //4 S Date J 2 0 JAN 2 · ~ . D2J NOTIFICATION Sub: Clarifications to Extension for Su bmission of online Application Forms for All Semesters B.Arch. / B .E . / B .Tech. /B.Plan./MBA /MCA /M.Tech. /M.Arch. Examinat ion s to be h eld during Jan /Feb/ March 202 1 by t h e ELIGIBLE s tuden ts. Ref. 1. No.VTU/ BG M/ Reg(E)/PS/20 20-20 21/1118, dated 05.01.2021 2. No.VTU / BGM / Reg(E)/PS/2020-202 1 I 1133, dated 13.01.2021 3. No.VTU/ BG M/ Reg(E)/PS/2020-202 1/ 1 148, dated 19.01.2021 With reference to the above, th e last date for the submission of examination applications forms was extended up to 21st January 2021 without penalty and from 22nd January 202 1 to 3 0 th January 2 0 2 1 with a penalty of Rs.SOO j- vide ref. (3) above. The extension is only for the students who have not filled the examination application form due critical problems and also for the students who are facing issues in filing exam application form . Please Note: THERE IS NO CHANGE IN THE THEORY /PRACTICAL EXAMINATION DATES OF UG AND PG PROGRAMS and the examin ations will be conducted as per the already circulated schedule. The Princip als of constitue n t and affiliated engineering colleges are requested to bring the contents of this circular to the notice of all the con cern ed. Sd/- REGISTRAR (EVALUATION) To, The Principals of Constituent and Affiliated Engineering colleges Copy FWC's t o : 1. Hon'ble Vice-Chancellor through the Sec. to VC, VTU Belagavi, for kind information . 2. Th e Registrar, VTU Belagavi, for information. 3. The Finance Officer, VTU Belagavi, for information. 4. The Incharge Regional Directors of VTU Regional Offices, for information &amp; needful. ~ a.--yA--1'-) g._ (:Z 0 · ..2-o \' \'l..o ~ REGISTRAR (EVALUATION</v>
+      </c>
+      <c r="D260">
+        <v>0</v>
+      </c>
+      <c r="E260" t="str">
+        <v>2026-03-19T18:37:46.138Z</v>
+      </c>
+      <c r="F260">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>http://bmsce.ac.in/website_notifications/Circular%20with%20Schedule%20Induction%20Program.pdf</v>
+      </c>
+      <c r="B261" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Date Time Activity-Resource Person 7:00 am - 8:00 am Physical Activity- Body stretching exercises- How to stretch to improve flexibility &amp; Mobility Routine- Aerobics-Mr. Saravanan R 9:30 am -10:00 am Innauguration of Induction Programme and First Year B.E. classes 10:00 am-10:45 am Scope and Challenges in Engineering Education - Dr. B.V. Ravishankar, Principal. 10:45 am - 11:00 am COFFEE BREAK 11:00 am -11:45 am Discipline - The way to success, Dr. S.Muralidara, Vice-Principal. 11:45am -12:30 pm First Year Academics-Dr. S.Jayanthi, Dean First Year 12:30pm -1:00 pm B.M.S.C.E. Library- Ms. Nagarathna B A 1:00 pm - 2:00 pm Lunch Break 2:00 pm - 3:00 pm Ensuring good academic performance- Dr. Samita Maitra, Dean Academic. 3:00 pm - 4:00 pm Sports for health &amp; Fitness- Dr. Shivaram Reddy , Director -Sports. 7:00 am - 8:00 am Pranayama and Meditation techniques during COVID-19 9:30 am -10:00 am Students Fora and Support Systems-Dr. H. S. Guruprasad, Dean Student affairs. 10:00 am-10:45 am Placement oppourtunities and career development-Dr. S. Pradeepa, Placement officer. 10:45 am - 11:00 am COFFEE BREAK 11:00 am -11:45 am Rules &amp; Regulations of Examination-Dr. T. S. Pranesha, Controller of Examination. 11:45 am-12.45 pm Campus Tour &amp; Expedition to local areas. 12:45 pm- 1:00 pm Freshers Talents-Singing (Solo/Group/instrumental) 1:00 pm - 2:00 pm Lunch Break 2:00 pm - 3:00 pm Mental Health awareness by Mr. N. Jayanth 3:00 pm - 4:00 pm Universal Human Values - Mr. Sanjay Sehgal- CEO and Chairman MSYS Technologies 7:00 am - 8:00 am Pranayama and Meditation techniques during COVID-19 9:30Am-10:45 am Skill development-1-Creative Thinking anf Goal setting. 10:45 am - 11:00 am COFFEE BREAK 11:00 am-11:30 am Anti Ragging- Police. 11:30 am-12:15 pm Armed Forces - 12:15pm-12:30 pm Freshers Talents- Monacting/Dumb Charades/Stand up Comedy. 12:30pm-1:00 pm Startups at B.M.S.C.E 1:00 pm - 2:00 pm Lunch Break 2:00 pm - 3:00 pm Group A: Pentagram/ Group B:Quiz 3:00 pm - 4:00 pm Group B: Pentagram/ Group A:Quiz B.M.S. COLLEGE OF ENGINEERING, BANGALORE - 560 019 SCHEDULE OF INDUCTION PROGRAM FOR FIRST YEAR B.E. STUDENTS 2020-2021 Phase -I Theme: Students Empowerment through Professional Accomplishment 21.12.2020 MONDAY 22.12.2020 TUESDAY 23.12.2020 WEDNESDA Y Date Time Activity-Resource Person B.M.S. COLLEGE OF ENGINEERING, BANGALORE - 560 019 SCHEDULE OF INDUCTION PROGRAM FOR FIRST YEAR B.E. STUDENTS 2020-2021 Phase -I Theme: Students Empowerment through Professional Accomplishment 21.12.2020 MONDAY 7:00 am - 8:00 am Physical Activity-Physical Fitness Capsule 9:00 am -10:00 am Awareness to COVID-19 and Safety percautions. Dr. Girish Chandra, Prof &amp; Head, Forensic Dept, M.S.Ramaiah Medical College. 10:00 am - 10:15 am B.M.S. Hospital 10:15 am - 10:30 am COFFEE BREAK 10:30 am-11:30 am Universal Human Values - Mr. M. K. Anand - Entrepreneur 11.30 am-12:00 Noon Incubation cell at B.M.S.C.E- Dr. Suma H N 12:00 Noon -1:00 pm Lectures- Eminent resource person 1:00 pm - 2:00 pm Lunch Break 2:00 pm -4:30 pm Utsav/Phase Shift/Club Activities. 25.12.2020 FRIDAY HOLIDAY-CHRISTMAS 7:00 am - 8:00 am Yoga 9:30 am-10:00 am NSS Acivities 10:00 am-10:45 am Robotics/Propel labs 10:45 am-11:00 am COFFEE BREAK 11:00 am -1:00 pm Department level induction programme. 1:00 pm - 2:00 pm Lunch Break 2:00 pm -4:30 pm IEEE-treasure hunt 26.12.2020 SATURDAY 24.12.2020 THURSDAY</v>
+      </c>
+      <c r="D261">
+        <v>0</v>
+      </c>
+      <c r="E261" t="str">
+        <v>2026-03-19T18:37:47.187Z</v>
+      </c>
+      <c r="F261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>http://bmsce.ac.in/website_notifications/General%20Conditions.pdf</v>
+      </c>
+      <c r="B262" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C262" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE 560 019 Autonomous Institute, Affiliated to VTU NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (TEACHING) • The application can be downloaded from the website. The duly filled in application along with DD for Rs.500/- drawn in favour of The Principal, BMSCE, payable at Bangalore and other relevant documents should reach the Principal on or before 07.02.2020. • Separate applications are to be submitted in the event of candidates applying for more than one faculty position with separate DD for each position. • Qualification: Minimum qualification for all faculty positions is PhD Degree preferably from premier Institutions with good publications. • Experience: As per AICTE norms • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules. • Management reserves the rights of processing (accept/reject) the application. • Application fee once paid is non-refundable and non-transferable. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration. • The details of the publications need to be mentioned in the application. Sd/- PRINCIPAL B.M.S. COLLEGE OF ENGINEERING, BANGALORE 560 019 Autonomous Institute, Affiliated to VTU NOTIFICATION OF FACULTY RECRUITMENT MANAGEMENT ADVERTISEMENT General Conditions (NON-TEACHING) • The application can be downloaded from the website. The duly filled in application along with DD for Rs.250/- drawn in favour of The Principal, BMSCE, payable at Bangalore and other relevant documents should reach the Principal on or before 07.02.2020. • Separate applications are to be submitted in the event of candidates applying for more than one position with separate DD for each position. • Qualification: Position Qualification Experience Receptionist Degree or Master ’ s Degree with basic computer knowledge and very good communication skill in Kannada, English &amp; Hindi. Should be able to handle EPABX, e-mail &amp; M S Office Library Assistant Bachelor ’ s or Master ’ s Degree in Library Science Preference will be given to experience candidates. Assistant Instructor Bachelor ’ s Degree in Science • Candidates should appear for the interview, if called, at their own cost with all the original documents. • The age limit is as per the Karnataka Civil Service (General Recruitment) Rules and subsequent orders in force and is relaxable to the extent as provided in the said Rules. • Management reserves the rights of processing (accept/reject) the application. • Application fee once paid is non-refundable and non-transferable. • Notwithstanding the above conditions if any relevant orders issued and which are in force will be made applicable for consideration. Sd/- PRINCIPAL</v>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+      <c r="E262" t="str">
+        <v>2026-03-19T18:37:47.958Z</v>
+      </c>
+      <c r="F262">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>http://bmsce.ac.in/website_notifications/Teaching%20Application%20Form.pdf</v>
+      </c>
+      <c r="B263" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C263" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE-19 Autonomous College under VTU / Approved by AICTE / Accredited by NBA Bull Temple Road, Bangalore-560019 APPLICATION FOR FACULTY POSITION Application No. ____________________________________________ For the Post of ____________________________________________ Department _____________________________________________ Reference _____________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; email address Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Please Affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Degree Course Specialization Name of the Institution Year of Passing Percentage of Marks Class Awarded PhD POST GRAD UATION (PG) ME / M Tech M.Sc.(Engg) M.Phil/M.Sc. UNDER GRA DUATION (UG) BE/B.Tech Other 13. Total No. of years of Research Experience Details ( Use separate if required) Name of the University / Institution Area of Research Period From To Total 14. Total No. of Publications ( National &amp; International Journals, Conferences and Books with ISBN Number if any) For details of Publications (Please attach separate sheet giving details of journal/ impact factors and citations from Google scholar, Scopus and web of science) Title of the Paper National / International Year and Month of Publication Conference / Journal 15. Teaching Experience ( Total No. of years) Details of Teaching Experience Name of the University / Institution Designation Period From To Total Years Month 16. Industrial Experience ( Total No. of years) Details of Industrial Experience Name of the Organization Position Held Period From To Total Years Years 17. Affiliations to Professional Organizations Name of the Professional Body Grade of Membership Number of Membership Year of Selection 18. Special Award / Achievements or any other information : 19. Consultancy: (Please attach a separate sheet giving details of innovative consultancy projects executed in the last 5 years) 20. Sponsored/Collaborative Research Projects: (Please attach a separate sheet giving details of the projects executed in the last 5 years ) 21. Social Engineering: (Please attach a separate sheet giving details of your involvement as solution provider for societal issues in the last 5 years) 22. Leadership (Applicable for Professor, Associate professor and R&amp;D positions) (Please attach a separate sheet indicating your role in providing leadership in any of the Academic /Research activities which were significant in your previous organization in the last 5 years) 23. Statement of Purpose (SOP): (Please attach a separate sheet stating your purpose to join as a faculty member in BMSCE) 24. Details of the References Name Occupation or Position Address for Communication with Contact Number (Please furnish at least 2 testimonials from the reference who are acquainted with the character and work of the applicant. Attach the testimonials / reference letters separately) 25. Declaration : I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate 26. List of documents to be attached with the application Title of the document No’s Please tick Attached Not Attached SSLC Marks Card or age proof document Bachelor’s Degree Certificate Bachelor’s Degree Marks cards Master’s Degree Certificate Master’s Degree Marks cards Ph.D Degree Certificate Other Certificates ( Please Specify) Research Experience Certificate Teaching Experience Certificate Industrial Experience Certificate Research Publications/ Papers Professional Membership Certificate Copy of Aadhar card Copy of PAN card Reference Letters Details of Fee Paid DD No. Date Amount Bank &amp; Branch Name The Applicants are required to submit the filled in application form to the following address: To The Principal B.M.S. College of Engineering Post Box No.1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, BMS College of Engineering, Bangalore</v>
+      </c>
+      <c r="D263">
+        <v>0</v>
+      </c>
+      <c r="E263" t="str">
+        <v>2026-03-19T18:37:48.605Z</v>
+      </c>
+      <c r="F263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Notification.pdf</v>
+      </c>
+      <c r="B264" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C264" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU _________________________________________________________________ No.VP/2020-21 Date:19.09.2020 NOTIFICATION The college would be conducting current Supplementary Semester End examinations Online mode . The online Supplementary Semester End Exams for UG higher semester courses would be conducted tentatively from October 5 th - 16 th , 2020 and for UG first year courses from 28 th October 2020 to 5 th November 2020. The supplementary semester end examinations ONLINE for MBA, MCA and M.Tech students will also start from 5 th October 2020. Re-registered students, during even semester, also have to take the online exams during supplementary semester end examinations. Students who have opted for GRADE IMPROVEMENT have to take the exams during supplementary semester end examinations. Students would be subjected to at least two online mock examinations before the actual exam. The Supplementary Semester End Exam Time Table will be announced shortly on the website. PRINCIPAL</v>
+      </c>
+      <c r="D264">
+        <v>0</v>
+      </c>
+      <c r="E264" t="str">
+        <v>2026-03-19T18:37:49.642Z</v>
+      </c>
+      <c r="F264">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>https://bmsce.ac.in/website_notifications/CONDUCTION_OF_FINAL_YEAR_EXAMINATION_AUGUST_2020-1.pdf</v>
+      </c>
+      <c r="B265" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C265" t="str">
+        <v>CONDUCTION OF FINAL YEAR EXAMINATION AUGUST 2020 (Students of VIII semester BE, IV semester M Tech and IV semester MBA) IMPORTANT ADDITIONAL INSTRUCTIONS TO STUDENTS o The students are advised to login one hour before the commencement of the examination and download the question paper to avoid last minute rush. o Reference materials required during the examination (e. g. probability tables etc.) are uploaded along with the question paper. In case the student wants use the code book (as notified in the question paper) for a particular course, the same is allowed. The student need to show the code book to the laptop/mobile phone camera at the beginning of the examination. o The students need to preserve all answer sheets of each course. After the completion of all the examinations, the students need to post the entire set of answer sheets (of all the courses) to the CoE’s office without fail. The records need to be submitted by the college to VTU whenever required. The students need to write his/her Name and the branch on the envelope. The envelope be posted to: THE CONTROLLER OF EXAMINATIONS BMS COLLEGE OF ENGINEERING BULL TEMPLE ROAD BENGALURU-560019 o A student is allowed to withdraw within 1 hour from the commencement of the online examination, if he/she desires to do so. The information in this regard should be mailed immediately to: office.coe@bmsce.ac.in o The student who has withdrawn from the course as mentioned above is allowed to take up the examination of the withdrawn course as and when it is held in the college. This is not treated as an additional attempt. THE CONTROLLER OF EXAMINATIONS</v>
+      </c>
+      <c r="D265">
+        <v>0</v>
+      </c>
+      <c r="E265" t="str">
+        <v>2026-03-19T18:37:50.223Z</v>
+      </c>
+      <c r="F265">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>https://bmsce.ac.in/website_notifications/UPDATED_CIRCULAR-CONDUCTION_OF_FINAL_YEAR_EXAMINATION_AUGUST_2020.pdf</v>
+      </c>
+      <c r="B266" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Page 1 of 4 CONDUCTION OF FINAL YEAR EXAMINATION AUGUST 2020 ( S tudents of VIII semester BE, IV semester M Tech and IV semester MBA) INFORMATION/INSTRUCTIONS  Examination will be conducted in the proctored online mode.  Students need to arrange for a room/place where there will be no intrusion during the course of the examination.  T he student s need to arrange a laptop with camera and microphone with windows 8 and above OS /an android phone.  The answers can be written or typed.  The mobile phone can be used to scan the answer sheets.  The examination application which will be used needs internet for downloading the question paper and while uploading the answer document after the completion of examination. However, d uring the course of the examination the requirement is optional .  Connectivity disruption will not stop the examination session. The answers entered within the application will be saved real - time on the device. In - case the a pplication closes / device restarts exam will resume from the same point with no data loss. The time lost in restarting the device / app will be added to the session.  An additional time of 30 minutes is given for scanning and uploading the answer sheets .  Email and call center s upport s are available . Very Important Note:  As a special provision due to the pandemic, the examination for BE is with open choice question paper . There will be seven questions and the students Page 2 of 4 need to answer any five. ( The e xisting question paper pattern is followed for M Tech and MBA).  O ur college has taken the decision to adopt online mode of examination and complete the process early in order to facilitate the students for the placements.  With the online examination we are shifting to a new paradigm. Mutual cooperation of college administration and the student community is essential to make this a success. In view of this students are advised t o follow principles and ethical values, not to indulge any non - ethical and unfair practices which may harm their interests.  If a student is not willing to take up the online examination (due to connectivity or any other issues), he/she has the provision t o take the examination offline whenever it is held in the college. In this case, the student carries the CIE earned by him/her during the current semester. Further, this is treated as the first attempt only.  If the student is not taking the online examin ation, he/she has to inform the same on or before the day of examination at the following e - mail id: office.coe@bmsce.ac.in In addition to the general examination regulations ( https://bmsce.ac.in/home/COE-Rules-and-Regulations ), the students need to adopt the following in view of the online examinations Page 3 of 4 REQUIREMENTS FOR ONLINE EXAMINATION (CHECKLIST) 1. Room/place without intrusion. 2. Laptop with camera and microphone with windows 8 or above OS/an android phone. 3. Sufficient number of A4 size white sheets, pen, pencil, eraser, calculator and graph sheets (if required). 4. If the student is using both laptop and the phone, should keep the data cable (to connect phone to the laptop) ready for scanning the written material after the examination. 5. Internet connection. 6. Make sure that the devices are fully charged/connected to power. Do’s 1. The requirements listed above should be kept ready 30 minutes before the start of the examination. 2. The camera and the microphone of the devise used for proctoring should be kept on throughout the examination. 3. The camera should once scan the entire room before the start of the examination. 4. The student should remain seated throughout the examination and ensure he/she is within the view of the camera. The entire event of the examination is recorded. 5. Each answer should start from a fresh page. 6. Each answer needs to be uploaded under the respective question number. Don’ts 1. The students should not use any additional devices. Page 4 of 4 2. The student should not have any books, notes, written material in the place where he/she is writing the examination. 3. The student should not attend phone calls, should not converse with anyone. 4. The student is allowed to keep essential medicine (if any) and the drinking water. However, no eatables are allowed during the examination. Online Technical Support For any technical help contact PEXA email: support.efh@littlemoreinnovation.com OR phone number: 080-47191116 Sd/- Sd/- CONTROLLER OF EXAMINATIONS PRINCIPAL</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266" t="str">
+        <v>2026-03-19T18:37:50.988Z</v>
+      </c>
+      <c r="F266">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Examination_and_Academics-Important_.pdf</v>
+      </c>
+      <c r="B267" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Examination and Academics-Important Announcements EXAMINATIONS As per the directions received from VTU: • The students of II, IV and VI semester BE, II semester M Tech, MBA and MCA, IV semester MCA are passed and are assessed based on the 50% CIE of the current semester and 50% SEE of the previous semester. The final semester examinations of undergraduate (UG) and postgraduate (PG) programmes are scheduled as follows: • Online preparatory classes for final semester of both UG and PG will be held from 01.08.2020. (The attendance is optional). • The final semester UG, PG project evaluation will be done online. The students are suggested to be in contact with department for the detailed schedule. • Online semester end theory examination for final semester UG and PG students: 17.08.2020 onwards. (The detailed time table will be posted in due course. Please see the note below). FAST TRACK SEMESTER The fast track semester classes for the students of final semester who have backlogs will start from 01.08.2020 on online mode. The fast track semester details for lower semester will be announced soon. ACADEMIC CALENDER FOR ODD SEMESTER The classes for odd semesters (UG and PG) will initially be on online mode and the commencement will be notified on the college website. Note: 1. In order to take the online semester end theory examination, all the final semester students of UG and PG need to arrange for a laptop with web camera. 2. The examination registration form for VIII semester BE, IV semester M Tech and IV semester MBA will be made available on the department portals for online submission. Students are suggested to keep visiting the portals for the details. Announcements for B Arch Programme EXAMINATIONS • The students of VIII semester are passed. The theory courses are assessed based on the 50% CIE of the current semester and 50% SEE of the previous semester. The viva-voce of the Architectural Design Project will be conducted online. • The Professional Training viva-voce of the X semester will be conducted online. The students are advised to be in contact with the department for the schedule of online viva-voce. FAST TRACK SEMESTER The fast track semester classes for the students of X semester who have backlogs will start from 01.08.2020 on online mode. The fast track semester details will be announced soon. ACADEMIC CALENDER FOR ODD SEMESTER The classes for IX semester will initially be on online mode and commencement will be notified on the college website. Principal</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267" t="str">
+        <v>2026-03-19T18:37:51.642Z</v>
+      </c>
+      <c r="F267">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>http://bmsce.ac.in/website_notifications/MSME-HI_BI.pdf</v>
+      </c>
+      <c r="B268" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C268" t="str">
+        <v>SEED FUNDING UP TO 15 LACS B.M.S. COLLEGE OF ENGINEERING Bengaluru HIBIKR000342 (Institute's HI/BI Number) Dr. H. N. SUMA (BI (Business Incubator) Incharge) INCUBATION SUPPORT APPLY NOW! Deadline: 20th Feb 2020 #IdeasForNewIndiaChallenge2020 (Students/Faculty/MSMEs) Logistics &amp; Construction Nanotechnology Renewable Energy Healthcare &amp; Life sciences Internet Of Things Robotics Safety Sports Textiles &amp; Apparel Transportation &amp; Storage Telecommunication Waste Management and others... Aerospace &amp; Defence Agriculture AI / Computer Vision Animation Art &amp; Photography Automotive Biotechnology Chemicals Design / Fashion Food &amp; Beverages Green Technology Enterprise Software Broad Sectors For any Queries, please contact Email: hns.ml@bmsce.ac.in</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268" t="str">
+        <v>2026-03-19T18:37:52.335Z</v>
+      </c>
+      <c r="F268">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>http://bmsce.ac.in/website_notifications/Non-Teaching%20Applicatin%20Form.pdf</v>
+      </c>
+      <c r="B269" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C269" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE-19 Autonomous College under VTU / Approved by AICTE / Accredited by NBA Bull Temple Road, Bangalore-560019 Non-Teaching Application No. ___________________________________________ For the Post of ___________________________________________ Department ___________________________________________ Reference ____________________________________________ (Notification Number &amp; Date) 1. Name in Full (In capital Letters only) 2. Father’s Name &amp; Occupation 3. Address for Correspondence 4. Contact Number &amp; E-mail address Mobile No : Email ID : 5. Date of Birth 6. Age as on the last date of submission of application (YY/MM/DD) 7. Place of Birth 8.Religon 9. Caste 10. Reservation Category (Enclose copies of Certificate issued by competent authority) 11. Languages known Language Read Speak Write Examination passed(if any) Please affix recent Passport (35 x 35 mm) Photograph 12. Highest Educational Qualification Details of Educational Qualification Examination Name of the Institution/University Year of Passing Percentage of Marks Class Awarded 13. Total No. of Year Experience Name of the Institution/Organization Designation Date of Job Details Entry Leaving Declaration I hereby declare that the information furnished in this application form is true to the best of my knowledge and behalf. Place: Date: Signature of the candidate Check – List of documents to be attached with the application Title of the document No’s Please tick Attached Not Attached SSLC Marks Card or age proof document Caste Certificate Qualification Certificate Experience Certificate Technical Certificate Copy of Aadhar card Copy of PAN card Details of Fee Paid DD No. Date Amount Bank &amp; Branch Name The Applicants are required to submit the filled in application form to the following address: To The Principal B.M,S, College of Engineering Post Box No.1908 Bull Temple Road Bangalore-560019 Karnataka, India. Phone: 080-26622130 - 35 Issued by the Office of the Principal, B.M.S. College of Engineering, Bangalore</v>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269" t="str">
+        <v>2026-03-19T18:37:53.690Z</v>
+      </c>
+      <c r="F269">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>https://bmsce.ac.in/website_notifications/Hostel_Advertisement-_06-11-2019.pdf</v>
+      </c>
+      <c r="B270" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C270" t="str">
+        <v>B.M.S COLLEGE OF ENGINEERING, BENGALURU- 19 Autonomous Institute, Affiliated to VTU Date: 24-10-2019 Advertisement for Positions at BMSET Hostel BMSET Hostel invites application from eligible candidate for the following positions:- Sl No Position Requirements 1 Cooks Specialising in cooking North Indian/South Indian Dish Interested candidates may submit their resume on or before 11.11.2019 To, The Secretary (National Hostel), BMSET Hostel, Hanumanthanagar, Bangalore-560004 General Conditions: 1. Candidates should attend interview at their own cost. 2. Age limit as per KCSR rules. 3. Management resolves the right to accept/reject application. 4. Proving false information will lead to disqualification.</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270" t="str">
+        <v>2026-03-19T18:37:54.652Z</v>
+      </c>
+      <c r="F270">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>http://bmsce.ac.in/home/Post-Graduation</v>
+      </c>
+      <c r="B271" t="str">
+        <v>html</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Post Graduation Notice: Admissions are Opened for Management Quota seats for First Year PG Courses (M.Tech, MBA &amp; MCA) for 2026-27 at B. M. S. College of Engineering. Two Years Full-Time PG programs in: DEPARTMENT OF COMPUTER APPLICATIONS DEPARTMENT OF MANAGEMENT STUDIES AND RESEARCH CENTRE M.Tech- COMPUTER NETWORKING M.Tech- TRANSPORTATION ENGINEERING AND MANAGEMENT M.Tech- VLSI DESIGN &amp; EMBEDDED SYSTEMS CONSTRUCTION TECHNOLOGY ENVIRONMENTAL ENGINEERING MACHINE DESIGN POWER ELECTRONICS ELECTRONICS DIGITAL COMMUNICATION COMPUTER SCIENCE AND ENGINEERING Academic Eligibility for Full Time Two Years Post Graduate Programs (M.Tech): A candidate with valid GATE score or PGCET of Karnataka A candidate who has passed qualifying examination (i.e., BE/B. Tech Degree) in the relevant discipline and obtained an aggregate minimum of 50% of marks (for General Merir Candidates) taken together in all the subjects of all the years / semesters of the Degree Examination is eligible for admission to ME / M. Tech programs. ( 45% of marks in qualifying examination in case of SC, ST and Cat-I candidates. (Reservation is applicable only for Karnataka Candidate) NOTE: The aggregate percentage of marks of the course of the qualifying examination shall be calculated as follows: Aggregate Percentage of Marks = Sum of the marks scored by the candidate in all the subjects of all the examinations / semesters X 100 Sum of all the maximum marks of all the subjects of all the years / semesters GATE Scholarship: For receiving GATE Scholarship, a candidate must have a valid GATE Score Card. Candidate with valid GATE score, opting seats under Sponsored Quota, are not entitled for GATE stipend SC/ST/OBC candidates with valid GATE Score claiming any other scholarship from Government of Karnatake / India are not entitled for GATE Scholarship. Candidates with valid GATE score opting for seat under Part-Time ME / M. Tech Program are not entitled for GATE stipend. Two Years Master of Business Administration (MBA) Degree for the academic year 2026-27: A candidate who has passed Qualifying Examination i.e., any Recognised Bachelor’s Degree of minimum of 3 years duration examination or equivalent examination and obtained an aggregate minimum of 50 % of (for General Merit Candidates) marks taken together in all the subjects including language in all the years of the Degree Examination is eligible for admission to full time MBA course. (45% of marks in Q. E. in case of SC, ST and Category – I of Karnataka Candidates) (Reservation is applicable only for Karnataka Candidates) [Entrance Examination: KMT / CMAT / MAT / PGCET – ANYONE IS MANDATORY] NOTE: ROUNDING OFF AGGREGATE PERCENT IS NOT PERMITTED. Two Years Master of Computer Application (MCA) Degree from the academic year 2026-27: A candidate who have passed Qualifying Examination i.e, any Recognised under graduate examination or equivalent examination with Mathematics or Statistics or Computer Science or Computer Application or Computer Programming or Business Mathematics or Business Statistics as one of the optional subjects and obtained an aggregate minimum of 50% [for General Merit Candidate] of marks taken together in all the subjects in all the years of the Degree Examination is eligible for admission to MCA courses. ( 45% of marks in Q. E. in case of SC, ST and Category – I of Karnataka Candidates. [Entrance Examination: KMT or PGCET – ANYONE IS MANDATORY] NOTE: ROUNDING OFF AGGREGATE PERCENT IS NOT PERMITTED. APPROVED MANAGEMENT FEE STRUCTURE FOR 2026-27 S.No Name of the Branch Fee for 2026-27 (Rs. in Lakh per annum) 1. MBA 4.0 2. MCA 3.5 3. M. Tech - Data Science (New Course) 3.0 4. M. Tech – Transportation &amp; Engg. 1.5 5. M.Tech - VLSI &amp; Embedded Systems 4.0 For Management Admission related information: Please visit: Director (Admissions), International Division, Ground Floor, Platinum Jubilee Block of BMSCE Campus, Bull Temple Road, Basavanagudi, Bengaluru – 560 019 Counselling will be held from Monday to Friday from 10:00 AM - 4:00 PM. Please note that BMS Educational Trust Admission Office remains closed on Sundays, 2nd &amp; 4th Saturdays and on Government Holidays. E-Mail ID: contact@bmsetadmission.org Management Admission Contact No.:080-26611636 Payment Mode for Management Admission: Demand Draft favouring BMS Educational Trust payable at Bengaluru and to be brought from the PARENT’S ACCOUNT ONLY.</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271" t="str">
+        <v>2026-03-19T18:37:56.461Z</v>
+      </c>
+      <c r="F271">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>http://bmsce.ac.in/home/Computer-Science-and-Engineering-Syllabus</v>
+      </c>
+      <c r="B272" t="str">
+        <v>html</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Syllabus UG Syllabus # Name Download 1UG syllabus 2023-2027 batch Download2UG syllabus 2022-2026 batch Download3UG Syllabus 2023-2027 Download4UG Syllabus 2022-2026 Download5UG Syllabus 2021-25 Download6UG Syllabus 2018-21 Download7UG Syllabus 2014-18 Download8UG Syllabus 2010-14 Download9UG Syllabus 2009-13 DownloadPG Syllabus # Name Download 1PG Syllabus 2024-26 I -II sem Download2PG Syllabus 2024-2026(III &amp; IV Semester) Download3PG Syllabus 2022-24 Download4PG Syllabus 2020-22 Download5PG Syllabus 2018-20 Download6PG Syllabus 2016-18 Download7PG Syllabus 2014-16 Download8PG Syllabus 2012-14 Download9PG Syllabus 2010-12 DownloadTIME TABLE # Name Download 12025-2026 -PHYSICS CYCLE- FIRST SEMESTER CLASS TIME TABLE Download22025-2026 -CHEMISTRY CYCLE- FIRST SEMESTER CLASS TIME TABLE Download32024-2025 -CHEMISTRY CYCLE-II SEM CLASS TIME TABLE Download42024-2025 - PHYSICS CYCLE - II SEM CLASS TIME TABLE Download52024-2025 - PHYSICS CYCLE - I SEM CLASS TIME TABLE Download62024-2025 - CHEMISTRY CYCLE- I SEM CLASS TIME TABLE Download72023-2024 - PHYSICS CYCLE - I SEM CLASS TIME TABLE Download82023-2024 - CHEMISTRY CYCLE- I SEM CLASS TIME TABLE Download92022-2023 - PHYSICS CYCLE - I SEM CLASS TIME TABLE Download102022-2023 - CHEMISTRY CYCLE- I SEM CLASS TIME TABLE Download112021-2022 - PHYSICS CYCLE -II SEM CLASS TIME TABLE Download122021-2022 - CHEMISTRY CYCLE-II SEM CLASS TIME TABLE DownloadFIRST YEAR SYLLABUS # Name Download 6.KANNADA SYLLABUS1Kannada Syllabus 2021-22 Download2Kannada Syllabus 2020-21 Download3Kannada Syllabus 2019-20 Download4Kannada Syllabus 2018-19 Download5Kannada Syllabus 2015-18 Download6Kannada Syllabus 2014-15 Download7Kannada Syllabus 2011-14 Download8Kannada Syllabus 2009-11 Download5.CONSTITUTION OF INDIA &amp; PROFESSIONAL ETHICS1UG Syllabus 2017-18 Download2UG Syllabus 2015-17 Download3UG Syllabus 2014-15 Download4UG Syllabus 2013-14 Download5UG Syllabus 2012-13 Download6UG Syllabus 2011-12 Download7UG Syllabus 2010-11 Download4.ELEMENTS OF MECHANICAL ENGINEERING123ME1ESEME-ELEMENTS OF MECHANICAL ENGINEERING Download3.UNIVERSAL HUMAN VALUES1UG First Year Syllabus 2020-21 Download2.FIRST YEAR SYLLABUS BOOK1First Year B.E Syllabus Book 2023-2024 Download2First Year B.E Syllabus Book 2022-2023 Download3First Year B.E Syllabus Book 2021-2022 Download4First Year B.E Syllabus Book 2020-2021 Download5First Year B.E Syllabus Book 2019-2020 Download1.FIRST YEAR1UG First Year Syllabus 2025-26 Download2UG First Year Syllabus 2023-24 Download3UG First Year Syllabus 2022-23 Download4UG First Year Syllabus 2020-21 Download5UG First Year Syllabus 2019-20 Download6UG First Year Syllabus 2018-19 Download7UG First Year Syllabus 2017-18 Download8UG First Year Syllabus 2016-17 Download9UG First Year Syllabus 2015-16 Download10UG First Year Syllabus 2014-15 Download</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272" t="str">
+        <v>2026-03-19T18:37:57.332Z</v>
+      </c>
+      <c r="F272">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>https://bmsce.ac.in/website_notifications/first_year_b_e__syllabus_2019-2020.pdf</v>
+      </c>
+      <c r="C273" t="str">
+        <v>BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 1 FIRST YEAR SYLLABUS BOOK With effect from the A.Y.2019-2020 CONTENTS S No Particulars Page 01 Scheme of Instructions I Semester B.E 2019-2020 (Physics Cycle) 3 02 Scheme of Instructions I Semester B.E 2019-2020 (Chemistry Cycle) 3 03 Scheme of Instructions II Semester B.E 2019-2020 (Physics Cycle) 4 04 Scheme of Instructions II Semester B.E 2019-2020 (Chemistry Cycle) 4 05 Curriculum for - 5.1 18MA1BSEM1 – Engineering Mathematics – 1 5 5.2 18PY1BSPHY/18PY2BSPHY - Applied Physics 7 5.3 18EC1ESECE/18EC2ESECE - Elements of Electronics Engineering 10 5.4 18ME1ESEME/18ME2ESEME – Elements of Mechanical Engineering 12 5.5 18CS1ESCCP/18CS2ESCCP – ‘C’ Programming 15 5.6 18HS1NCKAN/18HS2NCKAN - Kannada Language 18 5.7 18CY1BSCHY/18CY2BSCHY - Engineering Chemistry 20 5.8 18EE1ESELE/18EE2ESELE - Elements of Electrical Engineering 23 5.9 18CV1ESENM/18CV2ESENM - Engineering Mechanics 26 5.10 18ME1ESEED/18ME2ESEED - Elements of Engineering Drawing 28 5.11 18HS1NCENG/18HS2NCENG - Functional English 30 5.12 18MA2BSEM2 - Engineering Mathematics - 2 33 BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 2 Scheme &amp; Syllabus for UG Programme – I &amp; II Semesters ABBREVATIONS AY Academic Year AAT Alternative Assessment Tools BOE Board of Examiners BOS Board of Studies CBCS Choice Based Credit System CGPA Cumulative Grade Point Averages CIE Continuous Internal Evaluation HS Humanity and Social Science Courses L-T-P-S Lecture-Tutorial- Practical-Self study NFTE Not Fit for Technical Education SEE Semester End Examination SGPA Semester Grade Point Average BS Basic Science ES Engineering Science NC No Credit BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 3 Scheme &amp; Syllabus for UG Programme – I Semester Scheme of Instruction for First Semester B.E. 2019-2020 (PHYSICS CYCLE) S No Course Code Course Title Credits L T P Total 1 1 8 M A 1 B S E M 1 Engineering Mathematics – 1 3 1 0 4 2 1 8 P Y 1 B S P H Y Applied Physics 4 0 1 5 3 1 8 E C 1 E S E C E Elements of Electronics Engineering 3 0 0 3 4 1 8 M E 1 E S E M E Elements of Mechanical Engineering 3 0 1 4 5 1 8 C S 1 E S C C P ‘C’ Programming 3 0 1 4 6 1 8 H S 1 N C K A N Kannada Language* Mandatory Course 0 Total 20 Scheme of Instruction for First Semester B.E. 2019-2020 (CHEMISTRY CYCLE) S No Course Code Course Title Credits L T P Total 1 1 8 M A 1 B S E M 1 Engineering Mathematics – 1 3 1 0 4 2 1 8 C Y 1 B S C H Y Engineering Chemistry 4 0 1 5 3 1 8 E E 1 E S E L E Elements of Electrical Engineering 3 0 1 4 4 1 8 C V 1 E S E N M Engineering Mechanics 3 1 0 4 5 1 8 M E 1 E S E E D Elements of Engineering Drawing 1 0 2 3 6 1 8 H S 1 N C E N G Functional English* Mandatory Course 0 Total 20 L -Lecture (1 credit=1 contact hr.); T -Tutorial (1 credit=2 contact hrs.); P -Practical (1 credit=2 contact hrs.); * CIE only BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 4 Scheme &amp; Syllabus for UG Programme – II Semester Scheme of Instruction for Second Semester B.E. 2019-2020 (CHEMISTRY CYCLE) S No Course Code Course Title Credits L T P Total 1 1 8 M A 2 B S E M 2 Engineering Mathematics – 2 3 1 0 4 2 1 8 C Y 2 B S C H Y Engineering Chemistry 4 0 1 5 3 1 8 E E 2 E S E L E Elements of Electrical Engineering 3 0 1 4 4 1 8 C V 2 E S E N M Engineering Mechanics 3 1 0 4 5 1 8 M E 2 E S E E D Elements of Engineering Drawing 1 0 2 3 6 1 8 H S 2 N C E N G Functional English* Mandatory Course 0 Total 20 Scheme of Instruction for Second Semester B.E. 2019-2020 (PHYSICS CYCLE) S No Course Code Course Title Credits L T P Total 1 1 8 M A 2 B S E M 2 Engineering Mathematics – 2 3 1 0 4 2 1 8 P Y 2 B S P H Y Applied Physics 4 0 1 5 3 1 8 E C 2 E S E C E Elements of Electronics Engineering 3 0 0 3 4 1 8 M E 2 E S E M E Elements of Mechanical Engineering 3 0 1 4 5 1 8 C S 2 E S C C P ‘C’ Programming 3 0 1 4 6 1 8 H S 2 N C K A N Kannada Language* Mandatory Course 0 Total 20 L -Lecture (1 credit=1 contact hr.); T -Tutorial (1 credit=2 contact hrs.); P -Practical (1 credit=2 contact hrs.); * CIE only BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 5 COURSE TITLE ENGINEERING MATHEMATICS-1 COURSE CODE 18MA1BSEM1 CREDITS 04 L – T – P 3 – 1 – 0 CONTACT HOURS 48 Hours Course Objectives: To acquaint the students with principles of mathematics through Calculus and Differential Equations, that serves as an essential tool in several engineering applications. UNIT-I DIFFERENTIAL CALCULUS – 1 Polar curves - Angle between the radius vector and tangent, angle between two curves, length of the perpendicular from pole to the tangent, pedal equation. Curvature and radius of curvature- Cartesian and polar forms (without proof). Taylor’s and Maclaurin’s series expansions for function of one variable (without proof). [9 hours] UNIT-II DIFFERENTIAL CALCULUS – 2 Partial differentiation; Total derivatives-differentiation of composite functions. Jacobians, Taylor’s and Maclaurin’s series expansions for function of two variables. Maxima and minima for a function of two variables. [10 hours] UNIT-III INTEGRAL CALCULUS Multiple integrals: Evaluation of double integrals- change of order of integration and changing into polar co-ordinates, triple integrals. Applications: Area (Polar curves) and volume. Beta and Gamma functions: Definitions, Relation between Beta and Gamma functions and problems. [11 hours] UNIT-IV ORDINARY DIFFERENTIAL EQUATIONS OF FIRST ORDER Bernoulli’s equation. Exact and reducible to exact differential equations. ( ) ( ) ( ) ( ) y x x y M N N M i g x ii h y N M − − = = . Initial value problems. Applications: Orthogonal trajectories and Mixing problems. [9 hours] UNIT-V ORDINARY DIFFERENTIAL EQUATIONS OF HIGHER ORDER Second and higher order linear ordinary differential equations with constant coefficients- Inverse differential operators, Particular Integrals of ( ) ax , sin(ax), cos ax and m e x . Method of variation of parameters; Cauchy’s and Legendre homogeneous equations. [9 hours] BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 6 Text Books 1) Higher Engineering Mathematics, B.S. Grewal, 43 rd edition, 2014, Khanna Publishers. 2) Higher Engineering Mathematics, B.V. Ramana, 7 th reprint, 2009, Tata Mc. Graw Hill. Reference Books 3) Advanced Engineering Mathematics, Erwin Kreyszig, edition 2014, Vol.1 and Vol.2, 2014, Wiley-India. 4) Advanced Engineering Mathematics, Dennis Zill , Warren S Wright , Michael R. Cullen , 4 th edition, 2011, Jones &amp; Bartlett Learning. E-books and Online Resources 5) Advanced Engineering Mathematics, P.V. O’Neil, 7th Indian reprint, 2011, Cengage learn ing India Pvt. Ltd. https://ndl.iitkgp.ac.in/ and https://www.pdfdrive.com/engineering-mathematics-books.html 6) Engineering M a t h e m a t i c , K . A. Stroud , Dexter J. Booth , Industrial Press,2001, https://ndl.iitkgp.ac.in/ and https://www.pdfdrive.com/engineering-mathematics-books.html NPTEL/SWAYAM/MOOCs: 7) http://nptel.ac.in/courses.php/ 8) https://www.class-central.com/subject/math (MOOCS ) Course Outcomes: Course Code CO’s At the end of the course, the student will have the ability to: PO’s mapped Strength of mapping 18MA1BSEM1 CO 1 Understand the concepts of Calculus and differential equations. -- -- CO 2 Apply the concepts of calculus and Differential Equations to Engineering Problems. 1 3 CO 3 Demonstrate an understanding of the multiple integrals using alternate tools. 5 1 * * * * * * BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 7 COURSE TITLE APPLIED PHYSICS COURSE CODE 18PY1BSPHY/ 18PY2BSPHY CREDITS 05 L – T – P 4 – 0 – 1 CONTACT HOURS Theory: 48 Hours. Practical: 24 Hours Course Objectives: To disseminate to the students, the concepts of quantum mechanics, electrical and thermal properties of solids, materials science, lasers, optical fibers, oscillations and facilitate students to apply in their area of specialization. UNIT – I Quantum Mechanics de-Broglie hypothesis. Definition and expression of phase velocity and group velocity. Relation between group velocity and phase velocity, relation between group velocity and particle velocity, relation between group velocity, phase velocity and velocity of light. Derivation of de-Broglie wavelength using group velocity. Matter waves – characteristic properties. Problems. Heisenberg’s uncertainty principle – statement and physical significance. Application of uncertainty principle - Non-existence of electron in the nucleus. Wave function - properties and physical significance. Probability density and normalization of wave function. Setting up of one-dimensional time independent Schrödinger wave equation. Eigen functions and eigenvalues. Applications of Schrodinger’s wave equation: 1. Free particle, 2. Particle in a one-dimensional potential well of infinite height and finite width (Eigen functions, probability density and eigenvalues for the first three states). Problems. [10 hours] UNIT – II Electrical and Thermal Properties of Solids Electric Properties: Review of classical free electron theory, limitations of classical free electron theory. Postulates of quantum free electron theory, Fermi energy, Fermi velocity, Fermi temperature. Expression for Fermi energy. Fermi factor and its dependence on energy and temperature. Electrical conductivity (qualitative expression using effective mass and Fermi velocity). Merits of quantum free electron theory. Density of states (qualitative), Problems. Thermal Properties: Thermal conductivity, expression for thermal conductivity of a conductor using classical free electron theory. Wiedemann – Franz law, calculation of Lorentz number using classical and quantum assumptions. Theory and determination of thermal conductivity using Forbe’s and Lee – Charlton’s methods. Problems. [9 hours] UNIT – III Materials Science Dielectric Materials: Introduction, polarization, expression for polarization, types of polarization, Frequency dependence of polarization. Expression for electronic polarizability. Expression for internal field in liquids and solids (one dimensional), Lorentz field and Clausius – Mossotti relation. Expression for dielectric loss. Problems. BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 8 Physics of Semiconductor: Introduction, Fermi level in intrinsic and extrinsic semiconductors, Expression for concentration of electrons in conduction band. Mention of the expression for hole concentration in valance band, Expression for intrinsic carrier concentration, Conductivity of semiconductors, Hall effect, Expression for Hall coefficient. Problems. [10 hours] UNIT – IV Lasers and Optical Fibers Lasers: Introduction, characteristics of lasers, interaction of radiation with matter, expression for energy density of a system under thermal equilibrium in terms of Einstein’s coefficients, condition for laser action using Einstein’s coefficients, basic requisites of a laser system. Construction and working of He-Ne laser and semiconductor diode laser. Applications of lasers. Holography – recording of hologram and reconstruction of image. Problems. Optical Fibers: Introduction. Principle of propagation in optical fibers. Angle of acceptance, expression for numerical aperture and condition for propagation. Fractional index change. Number of modes – V number, inter-modal dispersion. Classification of optical fibers. Attenuation – causes of attenuation, expression for coefficient of attenuation. Applications of optical fibers. Problems. [10 hours] UNIT – V Theory of Oscillations Theory of free vibrations: Periodic motion, simple harmonic motion, equation of a simple harmonic oscillator, expressions for period and frequency, energy considerations-total energy, conversion of energy from kinetic to potential in SHM, electric to magnetic in an LC circuit. Theory of damped vibrations: Resistive forces, equation of motion-expression for decaying amplitude, cases of damping. Logarithmic decrement, relaxation time and quality factor. Theory of forced vibrations and resonance: Equation of motion-expression for amplitude, mechanical impedance, expression for maximum amplitude. Examples of resonance – ESR and NMR. Problems. [9 hours] LIST OF EXPERIMENTS No. Name of the experiment Skill 1 Wavelength of LEDs Determine 2 Fermi energy of copper Determine 3 Thermal conductivity of a poor conductor by Lee Charlton’s method Determine 4 Thermal conductivity of a metal by Forbe’s method Determine 5 Dielectric constant of a material by charging and discharging of a capacitor Determine BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 9 6 Energy gap of a semiconductor using four probe method Determine 7 Wavelength of semiconductor laser source using diffraction grating Determine 8 Divergence angle of semiconductor laser beam Determine 9 Numerical aperture of an optical fiber Analyse 10 Series and parallel LCR circuits Analyse Text Books: 1. Solid State Physics – Sixth Edition – S. O Pillai – New Age International Publishers. 2. Engineering Physics – V Rajendran – Tata Mcgraw–Hill. Reference Books: 3. Concepts of Modern Physics – Fifth edition- Arthur Beiser – Tata Mcgraw-Hill. 4. Engineering Physics – R K Gaur and S L Gupta – Dhanpat Rai Publications. E-Books/Resources: 5. http://de.physnet.net/PhysNet/education.html 6. http://hyperphysics.phy-astr.gsu.edu/hbase/hframe.html NPTEL/SWAYAM/MOOCs: 7. http://nptel.ac.in/ 8. https://swayam.gov.in/ Course Outcomes: Course Code CO’s At the end of the course, the student will have the ability to: POs Mapped Strength of mapping 18PY1BSPHY/ 18PY2BSPHY CO1 Understand the principles of quantum mechanics, transport phenomena, dielectric and semiconductor material properties of solids, laser and optical fiber and concept of vibrations. -- -- CO2 Apply the principles of quantum mechanics, transport phenomena, dielectric and semiconductor material properties of solids, laser and optical fibre and types of vibrations to obtain desired parameters. PO1 3 CO3 Conduct experiments to obtain the desired parameter of the given material / physical system. PO4 3 * * * * * BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 10 COURSE TITLE ELEMENTS OF ELECTRONICS ENGINEERING COURSE CODE 18EC1ESECE/ 18EC2ESECE CREDITS 03 L – T – P 3 – 0 – 0 CONTACT HOURS 36 Hours UNIT-I Semiconductor Diode &amp; Applications Diode: Working principle Characteristics, Parameters and Specifications, Shockley’s Equation. Half-Wave and Bridge Rectifier: Working principle and parameters Ripple Factor and Efficiency Derivations, Peak Inverse Voltage, Shunt Capacitor Filter, Zener Diode, Zener Diode as a Voltage Regulator, Regulated Power Supply. UNIT-II Transistor &amp; Applications Transistor: Operation, Configurations and Input-Output Characteristics. DC load line and Operating Point, Transistor as a Switch. Transistor as Amplifier: Voltage Divider Bias Circuit, Bias Stabilization, CE Amplifier, Frequency Response. Feedback Principle, Advantages of Negative Feedback. UNIT-III Oscillators and Op-amps Oscillators: Principle of Oscillations, RC Phase Shift Oscillator, Hartley and Colpitts Oscillator, Crystal Oscillator. Operational Amplifiers: Block Diagram of Op-Amp, Ideal Op- Amp v/s Practical Op-Amp, Virtual Ground, Applications: Inverting and Non-Inverting Amplifier, Voltage Follower, Summing Amplifier, Integrator and Differentiator. UNIT-IV Digital Electronics &amp; Circuits Introduction to Number Systems, Boolean Algebra, Boolean laws, Universality of NAND and NOR Gates, Logic Circuits, Sum of Product and Product of-Sum Forms, Simplification of Boolean Expressions using Boolean laws, Simplification of Boolean Expressions: K- Map (Using 2 and 3 variables only). Combinational Logic Circuits: Half Adder, Full Adder. Multiplexer, Decoder, SR and JK flip-flops. UNIT-V C ommunication Systems Analog and Digital Communication: Fundamental Concepts with Block Diagram, Introduction to Cellular Communication, Computer Communication Networks and IOT. Course Objectives : • To provide an understanding of Electronic Devices and Circuits. • To introduce the fundamentals of Digital Electronics. • To assimilate concepts of Electronic Communication Systems and Subsystems. • To reinforce the application based areas of Electronic Systems. BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 11 Text Books: 1. Basic Electronics Devices, Circuits and its Fundamentals, Santiram Kal, PHI.2009 2. Electronic Devices and Circuits, David A Bell, PHI, 5th Edition, 2007 Reference Books: 3. Integrated Electronics, Millman &amp; Halkias, International Student Edition, McGraw Hill Kogakusha Ltd, 2010 4. Electronic Devices and Circuit Theory, Robert L Boylestad and L. Nashelsky,Pearson Education, 9th edition, 2005 E-Books: 5. https://www.elsevier.com/books/basic-electronics/holbrook/978-0-08-006865-7 6. http://www.worldcat.org/title/basic-electronics/oclc/681543319 NPTEL/SWAYAM/ MOOC : 7. http://nptel.ac.in/courses/117103063/ 8. https://swayam.gov.in/course/3595-basic-electronics 9. https://www.mooc-list.com/course/introduction-electronics-coursera Course Outcomes: Course Code CO’s At the end of the course, the student will have the ability to: POs Mapped Strength of mapping 18EC1ICECE/ 18EC2ICECE CO1 Understand the Concepts of Electronic Devices and Circuits and r ealize the Applications of Electronics in Interdisciplinary Engineering Domains. 0 1 CO2 Apply the basic principles of Electronics to solve Analog and Digital circuits. 1 3 CO3 Analyze the characteristics/ performance parameters of Electronic Circuits. 2 3 CO4 Design basic Electronic Circuits for given Specifications. 3 1 CO5 Build cognizance on Electronic Waste and its Management. 6 1 * * * * * * BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 12 COURSE TITLE ELEMENTS OF MECHANICAL ENGINEERING COURSE CODE 18ME1ESEME/ 18ME2ESEME CREDITS 04 L – T – P 3 – 0 – 1 CONTACT HOURS Theory: 36 Hours. Practical: 12 Hours Course Objectives : • To provide a general understanding of energy-machine-application relationship. • To introduce the fundamentals of harnessing energy. • To familiarize the working principles of basic mechanical systems. • To acquaint with basic fabrication processes. UNIT-I Sources of Energy Introduction to sources of energy, conventional and non-conventional sources, solar energy (heliothermal, flat plate, parabolic), Steam formation, properties of steam, specific volume, enthalpy &amp; internal energy, types of steam, Introduction &amp; principle of boilers, types of boilers (No sketching of Boilers),Introduction and classification of steam turbines (Impulse &amp; Reaction),Open and Closed Gas turbines, Working of hydro power plant, Classification of Hydraulic turbines, working principle of Impulse &amp; Reaction turbines ( Pelton, Francis turbine with simple diagram). [9 hours] UNIT-II Refrigeration and Internal Combustion Engines Introduction to refrigeration, properties of an ideal refrigerant, COP, types of refrigerants, working principle of vapour compression and vapour absorption refrigerators, Classification of IC engines, parts of IC engines (simple sketch), working principle of 4-stroke petrol engine, diesel engine, numerical problems on 4 stroke petrol and diesel engines (power and efficiency calculation). [6 hours] UNIT-III Metal joining and Machine Tools Introduction to metal joining process-permanent &amp; temporary joints, nuts and bolts, metric thread profile. Arc welding (explanation with sketch), brazing, soldering. Introduction to Lathe, parts of Lathe, Lathe specifications, type of Lathe operations (turning, taper turning, thread cutting &amp; knurling).Introduction to drilling machine, classification of drilling machines, radial drilling machine, drilling operations (Boring, counter boring, countersinking, reaming, tapping), Introduction to grinding machine, working principle of cylindrical, surface and centreless grinding (line diagram). [9 hours] UNIT-IV Power Transmission Introduction to power transmission, open and crossed belt drives (no derivations), velocity ratio of belt drive, simple numerical problems, Types of gear drives, simple and compound gear trains, numerical problems on gear ratio, velocity ratio calculation, Introduction to Bearing, Classification of Bearings (Ball &amp; Roller) Lubrication – Types &amp;Examples. [6 hours] BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 13 UNIT-V Mechatronics &amp; Additive Manufacturing Introduction, definition of mechatronic systems, measurement and control systems, open and closed loop control systems (simple block diagrams), Examples for Open and Closed Loop systems, Introduction to AM - eight step process of AM (detailing not needed), Materials used in AM, Types of AM processes - FFF process and DLP process, Applications of AM in various industries. [6 hours] LIST OF EXPERIMENTS No. Name of the experiment Skill 1 Drilling, Tapping Fabrication Skills 2 Thread cutting using Dies Fabrication Skills 3 Welding (Lap Joint) Fabrication Skills 4 Sheet metal-Development, joints (Funnel) Fabrication Skills, Apply 5 Soldering Fabrication Skills 6 Demonstration of Additive Manufacturing Demonstrate 7 Demonstration of Lathe operations Demonstrate 8 Lathe- Model on Plain turning Demonstrate 9 Model on step turning Demonstrate Text Books: 1. Elements of Mechanical Engineering, K. R. Gopalakrishna, Subhas Publications, Bangalore- 2008 2. Additive Manufacturing Technologies, Ian Gibson, David Rosen, Brent Stucker, Second Edition, Springer Publication 3. Mechatronics: Electronic Control Systems in Mechanical and Electrical Engineering, 3rd Edition by W. Bolton Reference Books: 3. A Text Book of Elements of Mechanical Engineering – S. Trymbaka Murthy I. K. International Pvt Ltd, 2010 - Mechanical engineering 4. Elements of Mechanical Engineering – Dr. A.S. Ravindra, Best Publicaions, 7 th edition, 2009. 5. Elements of Mechanical Engineering, Vol.1 &amp; 2, Hajra Choudhury, Media Promoters, New Delhi, 2001. BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 14 E-Books: 6. https://www.books-by-isbn.com/81-265/8126553030-Elements-of-Mechanical- Engineering-J-K-Kittur-81-265-5303-0.html 7. Elements of Mechanical Engineering by V. K. MANGLIK https://books.google.co.in/books/about/Elements_of_MECHANICAL_ENGIN EERING.html?id=QlYorohzY_AC NPTEL//MOOC : 8. http://ocw.mit.edu/courses/mechanical 9. www.distance.lehigh.edu/credit/me.html 10. http://www.nptelvideos.com/mechanical/?pn=0 Course Outcomes: Course Code CO’s At the end of the course, the student will have the ability to: POs Mapped Strength of mapping 18ME1ESEME/ 18ME2ESEME CO1 Understand the working principles of various mechanical systems. - - CO2 Identify practical applications of mechanical elements, systems and processes 1 2 CO3 Distinguish the different refrigeration systems, IC engines, fasteners and power transmission systems 1 2 CO4 Compute various performance parameters of IC engines, velocity ratio of belt and gear drives. 1 2 CO 5 Impact of Energy sources on Environment and sustainability 7 1 CO 6 Develop basic fabrication skills through hands on Laboratory Exercises. 4 3 CO7 Apply the knowledge of engineering drawing in the fabrication of sheet metal components 1 1 * * * * * * BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 15 Course Title: C Programming Course Code : 18CS1ESCCP/ 18CS2ESCCP Credits : 04 L:T:P : 3-0-1 Contact Hours :36 Hours/Week : 03 Course Objectives : • To understand basic programming concepts. • To provide knowledge for problem solving through programming. • To provide hands-on experience with the concepts. Note: All the units shall include sample programs. UNIT -I INTRODUCTION TO PROGRAMMING [8 hours] Introduction to computer software, Program Design Tools: Algorithms, Flowcharts, Pseudo codes, Structure of a C program, Writing the first C program, Keywords, Identifiers, Basic Data Types in C, Variables, Constants, Input / Output Statements in C, Operators in C- Arithmetic, Relational, Logical, Conditional, Type conversion and Typecasting. UNIT -II CONDITIONAL AND LOOPING STATEMENTS [7 hours] Conditional branching statements, if, if-else, if-else-if and switch statements, Iterative statements, while, do-while and for loop statements, Nested loops, the break and continue statements. UNIT-III FUNCTIONS AND ARRAYS [7 hours] Functions: Function Declaration/Function Prototype, Function definition, Function call, passing parameters to functions. Arrays: Declaration of arrays, accessing the elements of an array, storing values in arrays, operations on 1-d arrays – Inserting an Element in an array, Deleting an Element from an Array, searching for a Value in an Array, two-dimensional arrays, operations on two- dimensional arrays – Sum, Difference. UNIT-IV STRINGS AND STRUCTURES [7 Hours] Strings: Introduction, Operations on Strings – finding the length of a String, converting characters of a string into upper case, Converting characters of a string into lower case. Structures: Introduction to Structures, Copying and comparing structures, Nested structures. BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 16 UNIT-V POINTERS AND FILE PROCESSING [7 hours] Pointers: Introduction to Pointers, Declaring pointer variables, Passing arguments to function using pointers. File Processing: Introduction to Files, Read Data from Files, Writing data to Files. Text Books: 1. Computer Fundamentals and Programming in C - Reema Thareja: Oxford University Press, Second Edition. (6.1, 8.4, 9.2, 9.3, 9.9, 9.10, 9.11, 9.12, 9.13, 9.14, 9.15.1, 9.15.2, 9.15.4, 9.15.6, 9.16, 10.2, 10.3, 10.4, 10.5, 11.3, 11.4, 11.5, 11.7, 12.2, 12.3, 12.4,12.5.2, 12.5.3,12.5.5,12.7, 12.8, 15.1,15.2,14.2,14.3,14.7,16.1,16.3,16.4) Reference Books: 2. Programming in C – Reema Thareja, Oxford University Press, Second Edition. 3. Programming with C- B S Gottfried: Schaums Outline Series 2003. Online References: VTU e learning, 4. http://videos.vtu.ac.in/video_groups.php?group=COMPUTER%20SCIENCE Concepts of Programming in C Lab 1. Develop a program to find the largest of three numbers. 2. Develop an interactive program to calculate roots of quadratic equation by accepting the coefficients. 3. Develop a program to sum the series: 1/1! + 4/2! + 27/3! +….. using functions. 4. Develop a program to insert a number at a given location in an array. 5. Implement a program to perform a binary search on 1D sorted Array. 6. Develop a program to read a two dimensional array “marks” which stores marks of 5 students in three subjects. Display the highest marks in each subject. 7. Develop a program to concatenate two strings and determine the length of the concatenated string. 8. Develop a program to read and display the information about a student using structures. 9. Implement a program to enter a character and then determine whether it is a vowel or not using pointers. 10. Develop a program to read data from the keyboard, write it to a file called “Input”, again read the same data from the “Input” file and display it on the screen. Mini Projects BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 17 1. Implement a commercial calculator to solve simple computational problems using arithmetic expressions (without using built-in math function). 2. An electricity board charges the following rates for the use of electricity: for the first 200 units 80 paise per unit: for the next 100 units 90 paise per unit: beyond 300 units Rs. 1 per unit. All users are charged a minimum of Rs. 100 as meter charge. If the total amount is more than Rs. 400, then an additional surcharge of 15% of total amount is charged. Develop an application to read the name of the user, number of units consumed and print out the charges. 3. Design and implement an interactive application to calculate Semester Grade Point Average (SGPA) of a student in a Semester End Examination (SEE). Course Outcomes and mapping for the C Programming Course CO1 Ability to describe the basic concepts of C programming CO2 Ability to apply the knowledge of C programming constructs for a given problem CO3 Ability to analyse the given problem to determine the output and correctness of the programs given CO4 Ability to develop C programs to find a solution for the given requirements. CO5 Ability to conduct practical experiments for demonstrating the features of C programming concepts. * * * * * * BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 18 KANNADA KALI 12hours (ONLY FOR NON-KARNATAKA STUDENTS) OBJECTIVES : PÀ£ÀßqÉÃvÀgÀ «zÁåyðUÀ½UÉ ‘ PÀ£ÀßqÀ PÀ° ’ JA§ ¥ÀoÀå¢AzÀ PÀ£ÀßqÀ ¨sÁμÉAiÀÄ£ÀÄß PÀ°¸À¯ÁUÀÄvÀÛzÉ. PART-1 [06 hours] Lesson-1 : Introducing each other-1. Personal Pronouns, Possessive forms, Interrogative forms. Lesson-2 : Absolute Ramayana. Possessive forms of nouns, dubietive question, relative nouns. Lesson-3 : Enquiring about a room for rent, Qualitative and Quantitative adjectives. Lesson-4 : Vegetable market, Numeral, Plurals. PART-2 [06 hours] Lesson-1 : Planning for a picnic, Imperative, Permissive, hortative. Lesson-2 : About Brindavan Garden, Past tense, negation. Lesson-3 : About routine activities of a student, verbal principle, reflexive form, negation. Lesson-4 : About Halebid, Belur, relative, principle, Negation. OUTCOMES : PÀ£ÀßqÉÃvÀgÀ «zÁåyðUÀ¼ÀÄ PÀ£ÀßqÀ ¨sÁμÉAiÀÄ£ÀÄß PÀ°AiÀÄÄªÀÅzÀjAzÀ PÀ£ÁðlPÀzÀ°è NzÀÄªÀ ¸ÀAzÀ¨sÀðzÀ°è PÀ£ÀßrUÀgÉÆA¢UÉ ªÀåªÀºÀj¸À®Ä ¸ÁzsÀåªÁUÀÄvÀzÉ. TEXT BOOKS: Kannada Kali, Prasaranga, Kannada university, Hampi. Reference Books: 1. Kannada Kali – Dr. Lingadevaru Halemane 2. Spoken Kannada – Kannada Sahithya Parishath, Bangalore . * * * * * * Course Code 18HS1NCKAK/ 18HS2NCKAK Course Name KANNADA KALI Credits 0 L – T – P- S 1 -0 -0 -0 B</v>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+      <c r="E273" t="str">
+        <v>2026-03-19T18:37:58.234Z</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>https://bmsce.ac.in/website_notifications/first_year_b_e__syllabus_2019-2020.pdf</v>
+      </c>
+      <c r="C274" t="str">
+        <v>MS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 19 Course Code 18HS1NCKAM / 18HS2NCKAM Course Name KANNADA MANASU Credits 0 L – T – P- S 1 -0 -0 -0 PÀ£ÀßqÀ ªÀÄ£À¸ÀÄ 1 2hours (ONLY FOR KARNATAKA STUDENTS) OBJECTIVES : PÀ£ÁðlPÀzÀ «zÁåyðUÀ½UÉ ‘ PÀ£ÀßqÀ ªÀÄ£À¸ÀÄ ’ JA§ ¥ÀoÀå¢AzÀ PÀ£ÁðlPÀzÀ ¸ÀA¸ÀÌöÈwAiÀÄ£ÀÄß ¥ÀjZÀ¬Ä¸À¯ÁUÀÄvÀÛzÉ. ¨sÁUÀ-1 [06 hours] 1. qÁ.«±ÉéÃ±ÀégÀAiÀÄå-ªÀåQÛ ªÀÄvÀÄÛ LwºÀå (ªÀåQÛ avÀæ) – J.J£ï.ªÀÄÆwðgÁªï 2. ¨Éqï £ÀA§gï K¼ÀÄ (PÀxÉ) – wæªÉÃtÂ 3. ±ÁæªÀt (¥ÀzÀå) – zÀ.gÁ.¨ÉÃAzÉæ 4. £ÀªÀÄä JªÉÄäUÉ ªÀiÁvÀÄ w½AiÀÄÄªÀÅzÉÃ? («£ÉÆÃzÀ) – UÉÆgÀÆgÀÄ gÁªÀÄ¸Áé«Ä CAiÀÄåAUÁgï ¨sÁUÀ-2 [06 hours] 1. PÀ£ÁðlPÀ ¸ÀA¸ÀÌøw MAzÀÄ avÀæ (¥ÀjZÀAiÀÄ ¯ÉÃR£À) – qÁ. gÀºÀªÀÄvï vÀjÃPÉgÉ 2. vÁAwæPÀ AiÀÄÄUÀzÀ°è PÀ£ÀßqÀ ¸Á»vÀåzÀ ¥Àæ¸ÀÄÛvÀvÉ – qÁ. «.dAiÀÄgÁªÀiï 3. UÀÄ§âaÑAiÀÄ UÀÆqÀÄ (CAPÀt §gÀºÀ) – ¦.®APÉÃ±ï 4. J®è ºÀÄqÀÄVAiÀÄgÀ PÀ£À¸ÀÄ (PÀªÀ£À) – ¸À«vÁ £ÁUÀ¨sÀÆμÀt OUTCOMES : PÀ£ÁðlPÀzÀ «zÁåyðUÀ¼ÀÄ ¸ÀA¸ÀÌöÈw CzsÀåAiÀÄ£ÀzÀ ªÀÄÆ®PÀ PÀ£ÁðlPÀ ZÀjvÉæ, ¥Àj¸ÀgÀ, zsÀªÀÄð, DZÁgÀ, «ZÁgÀ ªÀÄÄAvÁzÀ «μÀAiÀÄUÀ¼À£ÀÄß ªÉÄÊUÀÆr¹ PÉÆ¼ÀÄîvÁÛgÉ. ¥ÀoÀå ¥ÀÄ¸ÀÛPÀ: PÀ£ÀßqÀ ªÀÄ£À¸ÀÄ, ¥Àæ¸ÁgÀAUÀ, PÀ£ÀßqÀ «±Àé«zÁå®AiÀÄ, ºÀA¦. ¥ÁgÀªÀiÁ±Àð£À UÀæAxÀUÀ¼ÀÄ: 1. UÁæªÀiÁAiÀÄt - gÁªï§ºÀÄzÀÆÝgï 2. PÁ£ÀÆgÀÄ ºÉUÀÎqÀw – PÀÄªÉA¥ÀÄ 3. £ÀªÀÄä ºÉÆmÉÖAiÀÄ°è zÀQët CªÉÄÃjPÁ - ©.f.J¯ï. ¸Áé«Ä * * * * * * BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 20 COURSE TITLE ENGINEERING CHEMISTRY COURSE CODE 18CY1BSCHY/ 18CY2BSCHY CREDITS 05 L – T – P 4 – 0 – 1 CONTACT HOURS Theory: 48 Hours. Practical: 24 Hours Course Objectives : To impart the knowledge of Chemistry involved in water treatment, electrochemistry, corrosion and its control, conventional energy sources, electrochemical and renewable sources of energy, polymers, nanomaterials and instrumental methods of analysis. UNIT-I Water Treatment Introduction, hardness of water, types, determination of hardness by EDTA method, disadvantages of hard water - boiler scales - formation, disadvantages and prevention, removal of hardness by ion exchange method, Desalination of water - reverse osmosis, forward osmosis and electro dialysis. Dissolved oxygen, BOD and COD - introduction and their significance in waste water treatment, experimental determination of COD of waste water, treatment of waste water - aerobic and anaerobic oxidation, primary, secondary and tertiary treatment methods, numerical problems on hardness &amp; COD. Applications of NTO and Ag NP in waste water treatment. [9 hours] UNIT-II Electrochemistry and Corrosion Electrodes and cells – Introduction, classification of cells-primary, secondary and concentration cells, reference electrodes–calomel electrode and Ag/AgCl electrode, ion- selective electrode - glass electrode, determination of pH using glass electrode, determination of pKa of weak acids, numerical problems on concentration cells and pH determination. Corrosion – Definition of chemical corrosion, electrochemical theory of corrosion, types of corrosion - differential metal, differential aeration (pitting and water line corrosion) and stress corrosion, factors affecting the rate of corrosion, corrosion control: inorganic coatings – anodizing and phosphating, metal coatings - galvanization, tinning and electroplating of chromium, cathodic protection. [10 hours] UNIT-III Energy: Sources, Conversion and Storage Chemical fuels - Introduction, calorific value - definition, gross and net calorific values, determination of calorific value of a solid / liquid fuel using Bomb calorimeter and problems on calorific value, petroleum cracking - fluidized bed catalytic cracking, Octane number, reformation of petrol, synthetic petrol – Fischer-Tropsch’s process, power alcohol, biodiesel and hydrogen as a fuel – advantages, production and storage. Photovoltaic cells – Production of solar grade silicon, physical and chemical properties of silicon relevant to photovoltaics, doping of silicon, construction and working of a PV cell and advantages. Batteries - Basic concepts, classification of batteries – primary and secondary batteries, battery characteristics, modern batteries - construction, working and applications of zinc–air, nickel-metal hydride and Li-ion batteries (one example). Fuel cells - Introduction, construction and working of methanol-oxygen fuel cell with acid electrolyte. [11 hours] BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 21 UNIT-IV Polymer Chemistry Polymers - Introduction, mechanism of coordination polymerization (Ziegler - Natta polymerization), methods of polymerization – bulk, solution, suspension and emulsion polymerization, number average and weight average molecular weight, numerical problems, glass transition temperature, structure and property relationship of polymers. Plastics - Definition of resins and plastics, synthesis, properties and applications of PMMA and UF resin. Elastomers – Synthesis, properties and application of butyl rubber and nitrile rubber. Polymer composites – Composites as structural material, fiber glass, Kevlar, Carbon based composites. Conducting polymers - Introduction, synthesis of polyaniline and mechanism of conduction in it and uses. Biodegradable polymers - Introduction, polyglycolic acid-synthesis, degradation and uses. [9 hours] UNIT-V Nanomaterials and Instrumental methods of analysis Nanomaterials: Introduction, size dependent properties (Surface area, Electrical, Optical, Catalytic and Thermal properties). Synthesis of nanomaterials: Top down and bottom up approaches, Synthesis by solgel, hydrothermal and chemical vapour deposition methods. Nanoscale materials: Carbon nanotubes and graphene – properties and applications. Instrumental methods of analysis: Principle, instrumentation and applications of Colorimetry, Flame Photometry, Potentiometry and Conductometry (mixture of strong acid and a weak acid with a strong base). [9 hours] LIST OF EXPERIMENTS No. Name of the experiment Skill 1 Determination of percentage of copper in brass using standard sodium thiosulphate solution (brass solution to be prepared by weighing brass-making up method). Alloy composition 2 Determination of total hardness of a sample of water using disodium salt of EDTA. Estimation hardness of water 3 Determination of chemical oxygen demand (COD) of the given industrial waste water sample. Estimation of Pollutant level in industrial waste water 4 Determination of pKa of a weak acid using pH meter. Determination of strength of weak acid 5 Potentiometric estimation of FAS using standard K 2 Cr 2 O 7 solution. Application of different electrodes 6 Determination of percentage of iron in the given rust solution (using potassium dichromate) by external indicator method. Corrosion product analysis 7 Determination of calorific value of a solid fuel using Bomb calorimeter. Fuel characteristics 8 Synthesis of polyaniline and its conductivity measurement Synthesis of conducting polyaniline BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 22 9 Estimation of copper by colorimetric method. Absorption spectroscopy 10 Conductometric estimation of HCl + CH 3 COOH using standard sodium hydroxide solution Analysis of acid mixture 11 Estimation of sodium in water by flame photometric method Emission spectroscopy Text Books: 1. A Text book of Engineering Chemistry - by P. C. Jain and Monica Jain, Dhanapatrai Publications, New Delhi, 2011, 16 th Edition, 1404 pages. 2. Engineering Chemistry - by Chandra Shekara B M and Basavaraju B C, Banbayalu (publications), Bengaluru, 2014, 294 pages. Reference Books: 3. Wiley’s Engineering Chemistry (Wiley India), 2 nd Edition, 2013, 1026 pages. 4. Engineering Chemistry: Fundamentals and Applications - by Shikha Agarwal, Cambridge University Press, New Delhi, 2016, 1179 pages. E-Books: 5. Electrochemistry basics by LibreTexts of UCDavis: https://chem.libretexts.org/LibreTexts/University_of_California_Davis/UCD_Chem_002C/U CD_Chem_2C%3A_Larsen/Chapters/Unit_1%3A_Electrochemistry 6. Introduction to Chemistry - Tracy Poulsen; 250 pages; ISBN-13: 9781478298601; ISBN-10: 147829860X. NPTEL/SWAYAM/MOOCs: 7. http://nptel.ac.in/ 8 . https://swayam.gov.in/ Reference Book: (Laboratory) 9. Engineering Chemistry Lab Manual, written by faculty, Dept. of Chemistry, BMSCE, Bangalore. Course Outcomes: Course Code CO’s At the end of the course, the student will have the ability to: POs Mapped Strength of mapping 18CY1BSCHY/ 18CY2BSCHY CO1 Describe the principles of Chemistry involved in water treatment, electrochemistry corrosion and its control, conventional energy sources, electrochemical and renewable sources of energy, polymers, nanomaterials and instrumental methods of analysis. - - CO2 Address the problems based on the learnt chemistry principles. 1 3 CO3 Apply the acquired knowledge to analyze data, conduct experiments and draw meaningful inferences 2 2 * * * * * * BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 23 COURSE TITLE ELEMENTS OF ELECTRICAL ENGINEERING COURSE CODE 18EE1ESELE/ 18EE2ESELE CREDITS 04 L – T – P 3 – 0 – 1 CONTACT Theory: 24 Hours. Practical: 12 Hours Course Objectives: To introduce fundamental concepts and techniques to analyse the behaviour of electrical circuits. To provide the details regarding principle of operation and methods to evaluate the performance of electrical apparatus. To impart an overview about electrical wiring and protection mechanisms for domestic applications UNIT-I D.C.Circuits : Review of Ohm’s Law, analysis of series, parallel and series- parallel circuits excited by independent voltage sources (No numerical problems). Power and energy, Kirchhoff’s laws, branch current method, superposition theorem , illustrative examples. DC motors : Construction and principle of operation, back emf, torque equation, types of dc motors, characteristics of dc motors (shunt and series motors only) and applications, illustrative examples . [7 hours] UNIT-II A.C. Fundamentals :Generation of sinusoidal voltage, frequency of generated voltage, definitions and expressions for average value, root mean square value, form factor and peak factor of sinusoidally varying voltage and current, phasor representation of alternating quantity, illustrative examples. A.C.Circuits : Analysis with phasor diagram of circuits with R, L, C, R-L, R-C, R-L-C for series and parallel configurations. Real power, reactive power, apparent power and power factor, illustrative examples. [7 hours] UNIT-III Three Phase Synchronous Generator : Basic parts, principle of operation, synchronous speed, frequency of generated voltage, emf equation. Concept of winding factor (excluding the derivation of distribution and pitch factors), illustrative examples. Three phase AC Circuits : Three-phase balanced circuits, voltage and current relations in star and delta connections. Measurement of three phase power using two wattmeter method, effect of power factor on wattmeter readings, illustrative examples . [8 hours] UNIT-IV Single Phase Transformers: Construction and principle of operation, emf equation, losses, variation in losses with respect to load, efficiency, condition for maximum efficiency, illustrative examples . [7 hours] BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 24 UNIT-V Three Phase Induction Motors : Concept of rotating magnetic field, construction and working of a three-phase induction motor, slip and its significance, illustrative examples. Domestic Wiring : Service mains, meter board and distribution board. Types of wires and Cables used in domestic wiring, power requirement calculation for domestic applications. Elementary discussion on circuit protective devices, fuse and Miniature Circuit Breaker (MCB’s).Earthing: pipe and plate earthing, engineering practice for domestic earthing . [7 hours] LIST OF EXPERIMENTS No. Name of the Experiment Skill 1 Verification of KCL and KVL for DC circuit. Conduct and analyse 2 Measurement of Power and Power factor in a single phase lighting circuit. Conduct and analyse 3 Measurement of Power and Power factor in a single phase power load circuit. Conduct and analyse 4 Measurement of resistance and inductance of a coil using A-V-W method. Conduct and analyse 5 Verification of voltage and current relationship in a Three phase Star connected load. Conduct and verify 6 Verification of voltage and current relationship in a Three phase Delta connected load. Conduct and verify 7 Measurement of three phase power in star connected load using two wattmeter method. Conduct and analyse 8 Measurement of three phase power in delta connected load using two wattmeter method. Conduct and analyse 9 The speed versus torque characteristic of a DC Shunt motor. Conduct and verify 10 Load test on single phase Transformer Conduct and verify 11 Observation of phase differences between current and voltage Learn 12 Experiment on safety devices and Earthing Learn engineering practices Text Books: 1.“Basic Electrical Engineering”, D.C.Kulshreshta (2009),1 st Edition, Tata-McGraw-Hill. 2. “Basic Electrical Engineering”, N. Narasimhaswamy (2015),1 st Edition, EBPB publishers. Reference Books: 3.“ Electrical and Electronics Technology ” E. Hughes (Revised by J. Hiley, K. Brown and I.M Smith), 9th Edition, Pearson Education, 2005. 4.“Problems in Electrical Engineering” S.S.Parker Smith and N.N Parker Smith. 5.“Electrical Science”, P. M. Chandrashekharaiah, Rajeshwari Publications. BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 25 E-Book: 6. http://nptel.ac.in/courses/108105053/ ONLINE VIDEO LECTURES: 7. http://nptel.ac.in/courses/108108076/ Course Outcomes: Course Code CO’s At the end of the course, the student will have the ability to: POs Mapped Strength of mapping 18EE1ESELE/ 18EE2ESELE CO1 Understand the basic concepts of DC, AC circuits and Electrical Machines. -- -- CO2 Apply the basic knowledge of mathematics, science and electrical engineering to obtain the desired parameters/performance characteristics of Electric circuits and Machines. 1 2 CO3 Analyse the behavior of Electric circuits, transformers and Electrical machines. 2 2 CO4 Conduct a study on safety aspects, wiring and consumption of electrical power in domestic installations. 6 1 CO5 Conduct experiments and study the performance of electrical machines, AC and DC circuits. 4 2 CO6 Norms of engineering practice for domestic earthing. 8 1 * * * * * * BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 26 COURSE TITLE ENGINEERING MECHANICS COURSE CODE 18CV1ESENM/ 18CV2ESENM CREDITS 04 L – T – P 3 – 1 – 0 CONTACT HOURS 48 Hours Course Objectives : Day to day activities of every action follows the fundamental laws of physics. There is a need to know how the laws of physics could be applied to explain these activities. Effects of forces/force systems on an object/engineering structure are to be analyzed under static and dynamic conditions. This course is devised keeping the above objectives in mind. UNIT-1 ENGINEERING MECHANICS – BASIC CONCEPTS AND RESULTANT OF FORCE SYSTEM Concept of force, force Characteristics, internal and external force, force system and types of force systems, Principle of Transmissibility of force, principle of Superposition and physical independence, Idealization of bodies-particle, rigid body, continuum, Moment of a force about a point and about an axis, Couple, characteristics of couple. Resolution and composition of force, Numerical problems on resolution and composition of forces. Resultant and equilibrant of force system, Numerical problems on Resultant and equilibrant of force system, Parallelogram law, Triangle law, and Polygon law of forces, Numerical problems on Parallelogram law, Triangle law, and Polygon law of forces, Varignon’s theorem, problems on resultant of coplanar concurrent and non-concurrent force systems by method of resolution. [12 hours] UNIT-II EQUILIBRIUM OF FORCE SYSTEM : Free body diagram, conditions of equilibrium of concurrent and non-concurrent co planar force system, Lami’s Theorem, problems on particle and rigid body equilibrium; Types of supports in beams; Types of loads. Numerical problems on support reactions in determinate beams and frames. Analysis of plane trusses by method of joints, Numerical problems. [8 hours] UNIT-III FRICTION : Introduction, coefficient of friction, angle of friction, angle of repose; laws of dry (Coulomb) friction, Numerical problems on single and multi-body system on horizontal planes and incline planes, Numerical problems on wedge friction and ladder friction. [8 hours] UNIT-IV CENTROID AND MOMENT OF INERTIA: Centroids and centre of gravity of regular geometrical plane areas including parabola, Derivations on centroid of regular geometrical areas by integration, Numerical problems on centroids of composite areas and built up sections. Second moment (moment of inertia) of an area, moment of inertia of regular geometrical shapes by integration method, polar moment of inertia, radius of gyration, Parallel and Perpendicular axis theorems, Numerical problems on moment of inertia of composite areas and built up sections. [10 hours] BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 27 UNIT-V DYNAMICS: Kinematics - Introduction, types of motion, position vector, velocity and acceleration, Equations of linear motion (no numerical problems), Projectile motion; Numerical problems on projectiles, Kinetics of particles - Introduction , Newton’s Second law of motion, D’Alembert’s principle and its application to problems on system of particles, banking of roads. Work, Power, energy and efficiency, Kinetic energy of particles, Work- Energy Principle and its application to problems on particles and system of particles. Definition of linear momentum, impulse, impulse-momentum equation, Conservation of linear momentum and related problems. [10 hours] Text Books: 1. Mechanics for Engineers, Statics and Dynamics by Ferdinand Beer and E Russell Johnston, 4 th Edition (1972), McGraw Hill Company, New York. 2. Engineering Mechanics by Nelson, 1 st Edition (2009) , McGraw Hill Publishers Reference Books: 3. Engineering Mechanics by Timoshenko and Young; 5 th edition (2017) McGraw Hill Book Company , New Delhi 4. Engineering Mechanics , Statics and Dynamics by Meriam JL Kraige, (1993) Wiley Publishers, New Delhi 5. Applied Mechanics by I B Prasad, Edition 17, Publisher , Khanna Pub., 1996. E-Books/Resources: 6. VTU e-learning center ( Program number 13) 7. NPTEL Lecture Series on Engineering Mechanics, IIT Kanpur 8. MOOCs-http://www.mooc-list.com/course/introduction-engineering-mechanics- coursera Course Outcomes: Course Code COs At the end of the course, the student will be able to POs mapped Strength of mapping 18CV1ESENM/ 18CV2ESENM CO1 Explain basic terminologies, definitions, laws and principles related to statics and dynamics. - - CO2 Apply mathematical and engineering fundamentals for solution of coplanar force system, centroid and second moment of composite and built up areas. PO1 3 CO3 Analyze Engineering problems related to statics, particle Kinematics and Kinetics PO2 3 * * * * * * BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 28 COURSE TITLE ELEMENTS OF ENGINEERING DRAWING COURSE CODE 18ME1ESEED/ 18ME2ESEED CREDITS 03 L – T – P 1 – 0 – 2 CONTACT HOURS 60 Hours Course Objectives : • To understand the concept of projection systems; standards and conventions. • To develop the views of basic geometrical entities - points, lines, planes and solids. • To enhance speed and accuracy in use of drawing instruments and sketching capabilities. • To acquire the skill of expressing two and three dimensional objects as pictorial views. • Exposure to engineering communication. UNIT – 1 A: Introduction : Principles of Engineering Graphics and their significance, usage of Drawing Instruments, BIS Conventions and Dimensioning. [1L + 2P Hrs] B: Orthographic Projections Introduction, Planes of projection, Reference line and conventions employed, Projections of points in all the four quadrants. Projections of straight lines (located in first quadrant and without reference to traces), True and apparent lengths and inclinations to reference planes and application problems. [5L + 10P Hrs] UNIT – II Projections of Plane Surfaces in First Angle Introduction, Projections of plane surfaces: triangle, square, rectangle, rhombus, regular pentagon, regular hexagon and circle in different positions by change of position method. [4L + 06P Hrs] UNIT – III Projections of solids in First Angle Introduction, Projections of regular upright solid: tetrahedron, cube, prism, pyramid, cylinder and cone in different positions by change of position method. [5L + 10P Hrs] UNIT – IV Development of Lateral Surfaces of Solids Concept of section planes(horizontal and vertical traces), Development of lateral surfaces of right regular prisms, pyramids, cylinders and cones resting with base on HP,their frustums and truncations. [4L + 8P Hrs] UNIT – V A: Isometric Projection Introduction, Isometric scale, Isometric projection of simple plane figures, Isometric projection of tetrahedron, hexahedron, right regular prisms, pyramids, cylinders, cones, spheres, cut spheres and combination of solids (maximum of three solids) [ 4L + 8P Hrs] BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 29 B: Use of solid-modelling software for creating cube, right regular prisms, pyramids, cylinders, cones, spheres, and combination of solids (maximum of two solids) and extracting orthographic views, sectional views and Isometric views. Two exercises only. [1L+4P Hrs] Text Books: 1. Engineering Drawings Vols-1 &amp; 2, K. R. Gopalakrishna, Subhas Stores, Bangalore,2005. 2. Engineering Drawing, N.D. Bhat&amp; V.M. Panchal, 45 Edition, Charotar Publishing,Gujarat, 2005. Reference Books: 3. French, Thomas E., Vierck, C. J. and Foster, R. J., Fundamental of Engineering Drawing &amp; Graphics Technology, McGraw Hill Book Company (2005). 4. A Textbook of Engineering Graphics by K. Venugopal &amp; Prabhu Raj, New Age International, 2009. 5. Fundamentals of Engineering Drawing with an Introduction to Interactive Computer Graphics for Design and Production- Luzadder Warren J., Duff John M.,Eastern Economy Edition, 2005- Prentice-Hall of India Pvt. Ltd., New Delhi. Publications of Bureau of Indian Standards 6. IS 10711 – 2001: Technical products documentation – Size &amp; layout of drawing sheets. 7. IS 9609 (Parts 0 &amp; 1) – 2001: Technical products documentation – Lettering. 8. IS 10714 (Part 20) – 2001 &amp; SP 46 – 2003: Lines for technical drawings. 9. IS 11669 – 1986 &amp; SP 46 – 2003: Dimensioning of Technical Drawings. 10. IS 15021 (Parts 1 to 4) – 2001: Technical drawings – Projection Methods. E-Books: 11.Student’s Guide To Learning Solid works Software 12. www.solidworks.com/sw/docs/Student_WB_2011_ENG.pdf NPTEL/SWAYAM/ MOOC : 13.http://www.iitg.ac.in/cet/nptel.html Course Outcomes: * * * * * * Course Code COs At the end of the course, the student will be able to: POs mapped Strength of mapping 18ME1ESEED/ 18ME2ESEED CO1 Draw orthographic projections of basic geometrical entities in various positions and translate the geometric information of engineering objects into engineering drawings. 1 3 CO2 Create sketches and Isometric projections of solids 1 3 CO3 Develop lateral surfaces of solids and appreciate their applications in the industry. 1 3 CO4 Use modern engineering tool (CAD software) necessary for engineering practice. 5 1 BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 30 COURSE TITLE Functional English COURSE CODE 18HS1NCENG/ 18HS2NCENG CREDITS 00 L – T – P 1 – 0 – 1 CONTACT HOURS 24 Hours UNIT -I COMMUNICATION: • Introduction- Role and Importance of English in the Corporate World. • Communication-Importance of technical communication-levels, flow of organizational communication • Effective Presentation strategies: non-verbal communication aspects, Preparing Power Point Presentation • Public Speaking • Listening-Types, traits and importance of listening • Telephone Etiquette • Interviews-types and preparation. • InterpersonalCommunication Skills –Group Discussion Additional Reference: • Communication: Organizational communication, Communication cycle, Barriers • Language as a tool of communication, characteristics of language • Non-verbal communication • Power point presentations • Traits of a good listener, barriers • Interviews: questions frequently asked • Business Meetings/Conferences: Spoken • Effective reading skills [4 hours] UNIT -II Technical Writing / Speaking: Specific Focus • Letter Writing –Job Applications, E-mails and other Official Letters • Writing a résumé • Writing reports and dissertation/thesis-structure and significance • Description of Graphics -kinds, construction, use and application (in scientific texts) and Interpretation Additional Reference: • Paragraph Writing, Expansion of ideas – Précis Writing • Business Letters: Significance, purpose, structure, layout, types and samples • Curriculum Vitae/ résumé/bio-data–different formats Course Objectives: • To impart basic English grammar and essentials of language skills • To train to identify the nuances of phonetics, intonation and enhance pronunciation skills • To enhance with English vocabulary and language proficiency BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 31 • Technical Reports: objectives, characteristics and categories • Manuscript format, prefatory parts and main text • Interpretation of the diagrams and graphs in paragraphs • Structure of a Research dissertation/thesis. [4 hours] UNIT -III Grammar: Basics and Structures • Parts of Speech-in brief • Transformation of Sentences, Active and Passive Voice, Direct and Indirect Speech. • Subject-Verb Agreement Additional Reference: • Nouns, Pronouns, Tenses, Articles and Prepositions. Adjectives, Conjunctions, Adverbs, Interjection • Degrees of comparison • Punctuation • Types of sentences • Simple-compound and complex sentences • Rules governing Active-Passive voice and Direct-Indirect Speech • Singular and plural nouns and verbs. [2 hours] UNIT -IV Vocabulary • Correct pronunciation of important words • Identifying errors in sentences-often mispronounced and misspelt word • Difference between American and British English, • Indianism-Mother tongue influence • Using Idioms and phrases –words commonly misused and confused • Analogy of Comparison • Corporate/conventional idioms. Additional Reference : • IPA script chart to read sounds-vowels and consonants • Spellings chart • Words often mispronounced\ • Homophones and homonyms • American English- evolution, expressions and slangs • How American English has influenced corporate world • Indianized expressions in English • phrasal verbs and proverbs. [2 hours] Language Lab For augmenting LSRW and GV skills (Listening, Speaking, Reading, Writing and Grammar, Vocabulary) through tests, activities, exercises etc., comprehensive web- based learning systems can be referred. (10 levels) [12 hours] BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 32 Text Book : 1. Practice and Perfect- a workbook issued by the Department of Mathematics and Humanities, BMS College of Engineering. 2. Additional Reference Source prepared by the Faculty of English-issued by the Department of Mathematics and Humanities, BMSCE. Reference Books: 3. IELTS Preparation and Practice by Wendy Sahanaya and Terry Hughes, OUP, 2007. 4. Technical Communication; Principles and Practice – Meenakshi Raman and Sangeetha Sharma. 5. English for Presentations by Marion Grussendorf, OUP, 2015 6. Making Sense of English , M.Yadugiri, Viva Publications 7. Advanced English Grammar – Thomson and Martinet, Cambridge University Press. Course Outcomes: * * * * * Course Code COs At the end of the course, the student will be able to: POs mapped Strength of mapping 18HS1NCENG/ 18HS2NCENG CO1 Communicate effectively and creatively in both non-verbal and verbal forms in various multi- disciplinary activities. 10 3 CO2 Upgrade organizational skills/traits, team spirit/working in liaison and thus boost professional etiquette and ethics. 9, 10 3, 2 CO3 Write effective technical reports, dissertation and project documents and make effective oral and written presentations. 9, 10 1, 3 CO4 Enhance employability via training in writing correct and effective Applications/Resumes. 10 3 CO5 Perform well against Domestic and International Industry Standards via group discussions and Power Point Presentations. 9, 10 3, 3 CO6 Strengthen basic grammar components/structures and overcome mistakes/wrong pronunciation and thereby, encourage speaking/writing in flawless English. 10 3 BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 33 COURSE TITLE ENGINEERING MATHEMATICS-2 COURSE CODE 18MA2BSEM2 CREDITS 04 L – T – P 3 – 1 – 0 CONTACT HOURS 48 Hours Course Objectives: To provide students with a solid foundation in mathematical fundamentals such as Laplace Transforms, vectors and orthogonal curvilinear coordinates required for different branches of engineering. UNIT-I LAPLACE TRANSFORMS Definitions, properties, transforms of elementary functions, transforms of derivatives and integrals. Applications: Evaluation of Improper integrals using Laplace transforms, Laplace transform of Periodic functions and Unit step function. [9 hours] UNIT-II INVERSE LAPLACE TRANSFORMS Inverse Laplace Transforms-properties, inverse transforms of standard functions, ( ) ( ) ( ) ( ) 1 1 1 , , . n as F s L L e F s L F s s − − − −               Applications: Solution of differential Equations, LRC series circuits and system of differential Equations. [10 hours] UNIT-III PARTIAL DIFFERENTIAL EQUATIONS Formation of partial differential equations by elimination of arbitrary constants and func</v>
+      </c>
+      <c r="D274">
+        <v>1</v>
+      </c>
+      <c r="E274" t="str">
+        <v>2026-03-19T18:37:58.234Z</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>https://bmsce.ac.in/website_notifications/first_year_b_e__syllabus_2019-2020.pdf</v>
+      </c>
+      <c r="C275" t="str">
+        <v>tions. Solution of non-homogeneous partial differential equations by direct integration. Solution of Lagrange’s linear partial differential equations. Solution of partial differential equations by the method of separation of variables, Derivation of one dimensional heat and wave equations and various possible solutions by the method of separation of variables. [10 hours] UNIT-IV VECTOR CALCULUS Scalar and vector point functions, Gradient, directional derivative, Divergence, Curl, Laplacian of a vector point function, solenoidal, irrotational vectors. Vector identities: divcurl A   , curlgrad φ , div ( ) A φ   , curl ( ) A φ   , div ( ) A B ×     , curlcurl A   and problems on vector identities. Vector integration: Statement and problems on Green’s theorem, Stokes’ theorem and Gauss divergence theorem (without proofs). [10 hours] UNIT-V ORTHOGONAL CURVILINEAR COORDINATES (OCC): Definitions - Orthogonal curvilinear coordinates, scale factors, base vectors, cylindrical and spherical coordinate systems, expressing a given vector in cylindrical and spherical coordinates. Expressions for gradient, divergence, curl and Laplacian in orthogonal curvilinear coordinates. [9 hours] BMS COLLEGE OF ENGINEERING, BENGALURU-19 Autonomous Institute, Affiliated to VTU 34 Text Books 1) Higher Engineering Mathematics, B.S. Grewal, 43 rd edition, 2014, Khanna Publishers. 2) Higher Engineering Mathematics, B.V. Ramana, 7 th reprint, 2009, Tata Mc. Graw Hill. Reference Books 3) Advanced Engineering Mathematics, Erwin Kreyszig, edition 2014, Vol.1 and Vol.2, 2014, Wiley-India. 4) Advanced Engineering Mathematics, Dennis Zill , Warren S Wright , Michael R. Cullen , 4 th edition, 2011, Jones &amp; Bartlett Learning. E- Books and Online Resources 5) Advanced Engineering Mathematics, P.V. O’Neil, 7th Indian reprint, 2011, Cengage learn ing India Pvt. Ltd. https://ndl.iitkgp.ac.in/ and https://www.pdfdrive.com/engineering-mathematics-books.html 6) Engineering Mathematics, K. A. Stroud , Dexter J. Booth , Industrial Press, 2001, https://ndl.iitkgp.ac.in/ and https://www.pdfdrive.com/engineering-mathematics-books.html NPTEL/SWAYAM/MOOCs: 7) http://nptel.ac.in/courses.php/ 8) https://www.class-central.com/subject/math (MOOCS ) Course Outcomes : COURSE CODE CO’s At the end of the course, the student will be able to: PO’s CO-PO Mapping (Strength) 18MA2BSEM2 CO 1 Understand the concepts of transforms, partial differential equations and vector calculus. -- -- CO 2 Apply the concepts of transforms, partial differential equations and calculus to Engineering problems. 1 3 CO 3 Demonstrate an understanding of the Laplace transforms of functions using alternate tools. 5 1 * * * * *</v>
+      </c>
+      <c r="D275">
+        <v>2</v>
+      </c>
+      <c r="E275" t="str">
+        <v>2026-03-19T18:37:58.234Z</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>http://bmsce.ac.in/home/COE-Notifications</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Notifications # Details Files 1.Time Table for IV Semester Makeup Examination MBA- Mar-2026. Download 2.Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. III Semester End Examinations conducted during Jan/Feb-26. Download 3.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. I, III Semesters and Reappear Semester UG Semester End Examinations conducted during Jan/Feb-26. Download 4.Notification for Answer Scripts of I &amp; III Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure as per the attached schedule. Download 5.Circular for makeup registration for I and III Semester March -2026 Download 6.Addtional Time Table for III Semester Makeup Examination - Mar-2026. Download 7.Time Table for I Semester MBA (Re-Appear) theory Semester End Examination March- 2026. Download 8.Time Table for I Semester M.Tech (Re-Appear) theory Semester End Examination March- 2026. Download 9.Time Table for III Semester Makeup Examination - Mar-2026. Download 10.Time Table for I Semester Makeup Examination - Mar-2026. Download 11.Time Table for MBA I Semester (Reappear) theory Semester End Examination March- 2026. Download 12.Time Table for M.Tech I Semester theory Semester End Examination March- 2026. Download 13.Time Table for MCA I Semester theory Semester End Examination March- 2026. Download 14.Time Table for MBA I Semester theory Semester End Examination March- 2026. Download 15.Additional/Revised Time Table for V Semester B.E. theory Semester End Examinations-Jan/Feb-2026. Download 16.Additional/Revised Time Table for IV Semester B.E. theory Semester End Examinations-Jan/Feb-2026. Download 17.Revised Time Table for I Semester B.E. theory Semester End Examinations-Jan/Feb-2026 Download 18.Additional/Revised Time Table for III Semester B.E. theory Semester End Examinations-Jan/Feb-2026. Download 19.Time Table for VII Semester B.E. makeup theory Semester End Examinations-Jan/Feb-2026 Download 20.Time Table for V Semester B.E. makeup theory Semester End Examinations-Jan/Feb-2026 Download 21.Time Table for Revised VI Semester B.E. theory Semester End Examinations-Jan/Feb-2026 Download 22.Time Table for PG M.Tech Re-Appear II Semester theory Semester End Examination JAN/FEB-2026. Download 23.Additional Time Table for MBA III Semester theory Semester End Examination JAN/FEB- 2026. Download 24.Time Table for VIII Semester B.E. theory Re-Appear Semester End Examinations- Jan/Feb -2026 Download 25.Time Table for VI Semester B.E. theory Re-Appear Semester End Examinations- Jan/Feb -2026 Download 26.Additional Time Table for III Semester B.E theory Semester End Examination Jan/Feb- 2026. Download 27.Revised Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (for 2024, 2023, 2022 &amp; 2021 batch Reappear -Reregisteration) Download 28.attached Time Table for PG II Semester Re-appear M.Tech Theory Semester End Examination Jan- 2026. Download 29.attached Time Table for PG Revised III Semester M.Tech Theory Semester End Examination Jan- 2026. Download 30.Time Table for III Semester MCA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 31.Time Table for III Semester MBA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 32.Time Table for II Semester MBA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 33.Time Table for II Semester MCA theory Semester End Examination JAN/FEB- 2026(Re-Appear). Download 34.Revised Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. V, VII and Reappear Semester Dec-2025/Jan-2026 Semester End Examination. Download 35.NOTIFICATION:Answer Scripts of V &amp; VII Semester B.E Students who have obtained 'F' Grade in the SEE Examination are open for disclosure on 28-01-2026 &amp; 29-01-2026. Download 36.Time Table for PG III Semester M.Tech Theory Semester End Examination Jan- 2026. Download 37.Additional /Revised Time Table for IV Semester B.E. theory Semester End Examinations-Jan-2026. Download 38.Additional /Revised Time Table for III Semester B.E. theory Semester End Examinations-Jan-2026. Download 39.Time Table for IV Semester B.E. theory Semester End Examinations-Jan-2026 (All batch Reappear &amp; Re registeration).. Download 40.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. V, VII and Reappear Semester Dec-2025/Jan-2026 Semester End Examination. Download 41.Time Table for III Semester B.E. theory Semester End Examinations-Jan-2026 (All batch Regular, Reappear &amp; Re registeration) Download 42.Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (Non-NEP batch Reappear -Re registeration) Download 43.Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (for 2021 batch Reappear -Re registeration) Download 44.Time Table for I/II Semester B.E. theory Semester End Examinations-Jan-2026 (for 2024, 2023 &amp; 2022 batch Reappear -Reregisteration) Download 45.Time Table for Semester B.E. theory Semester End Examinations-Jan-2026 (for 2025 batch only) Download 46.Time Table for MCA III Semester theory Semester End Examination JAN- 2026. Download 47.Time Table for MBA III Semester theory Semester End Examination JAN- 2026. Download 48.Notifications for submission of application for ensuring Reappear Examination PG -ODD-2026 Download 49.Additional Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 50.additional Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 51.Additional Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 52.Additional Time Table for VIII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 53.additional Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 54.additional Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 55.Additional Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026. Download 56.Revised Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.( For 2022,2021 and Non-NEP Batches) Download 57.Revised Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2022,2021 Batches) Download 58.Revised Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2023 ,2022,2021 and Non-NEP Batches) Download 59.Time Table for VIII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.( For 2023, 2022,2021 Batches) Download 60.Notifications for submission of application for ensuing Reappear Examination Dec-2025 to Jan-2026 (NEP Batches). (21 TO 23 BATCH).. Download 61.Time Table for VII Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.( For 2022,2021 and Non-NEP Batches) Download 62.Time Table for VI Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2022,2021 Batches) Download 63.Time Table for V Semester B.E theory Semester End Examination Dec/Jan- 2025-2026.(For 2023 ,2022,2021 and Non-NEP Batches) Download 64.Notifications for submission of application for ensuing Reappear Examination Dec-2025 to Jan-2026 (NEP Batches)(24 BATCH) .. Download 65.Circular for Fees and Regulations for Photocopy and Challenge Valuation of Re-Appear for I to II semester of P.G. Oct 2025 Examination. Download 66.Circular for Fees and Regulations for Photocopy and Challenge Valuation of Supplementary/Re-Appear for I to IV semester of P.G. Sep/Oct 2025 Examination. Download 67.Circular for Fees and Regulations for Photocopy and Challenge Valuation of Supplementary III to VIII semester of U.G. Sep/Oct 2025 Examination. Download 68.Time Table for PG M.Tech II Semester(2024 batch) theory Re-Appear Examinations Oct- 2025. Download 69.Time Table for PG M.Tech I Semester(2024 batch) theory Re-Appear Examinations Oct- 2025. Download 70.Time Table for PG MBA II Semester theory Re-Appear Examinations Oct- 2025. Download 71.Time Table for PG MBA I Semester theory Re-Appear Examinations Oct- 2025. Download 72.Time Table for PG MCA II Semester theory Re-Appear Examinations Oct- 2025. Download 73.Time Table for PG MCA I Semester theory Re-Appear Examinations Oct- 2025. Download 74.Circular for Fees and Regulations for Challenge Valuation of Summer semester/Supplementary semester of U.G. Sep 2025 Examination. Download 75.Time Table for PG M.Tech I Semester theory Supplementary Examination Sep- 2025 Download 76.Notifications for Reappear Examination Application for PG Sep-2025. Download 77.Time table for Supplementary Examination -Sep- 2025 (MCA). Download 78.Time tables for Supplementary Examination -Sep- 2025 (MBA). Download 79.Revised/additional Time Table for V Semester theory Supplementary /Reappear Examination Sep- 2025 Download 80.Additional Time Table for PG I-II Semester MBA reappear Examination Sep-2025. Download 81.Additional Time Table for PG M.Tech SEE Reappear Examination Sep-2025. Download 82.Additional Time Table for V Semester B.E theory Supplementary Examination Aug/Sep- 2025. Download 83.Additional Time Table for III Semester B.E theory Supplementary Examination Aug/Sep- 2025. Download 84.Revised Time Table for I/II Semester B.E theory Summer Semester Examination Sep- 2025.(Regular 2024 batch and 2022 batch*only). *Ref : VTU notification 12-09-2025 Download 85.Submission of reappear examination application for summer semester examination (2022 batch only-who are not eligible to move to VII Semester due to vertical progression) Download 86.Time Table for PG theory Reappear Examination Sep- 2025 III and IV Semester MBA theory Reappear Examinations. Download 87.Time Table for PG theory Reappear Examination Sep- 2025 I and II Semester MBA theory Reappear Examinations. Download 88.Time Table for PG theory Reappear Examination Sep- 2025 I,II and III Semester MCA theory Reappear Examination. Download 89.Time Table for PG theory Reappear Examination Sep- 2025 I,II,III and IV Semester M.Tech theory Reappear Examination. Download 90.Time Table for I/II Semester theory Summer Semester Examination Sep- 2025 (2024 batch only). Download 91.Time Table for VI Semester theory Supplementary /Makeup Examination Aug- Sep- 2025 (All batches). Download 92.Time Table for V Semester theory Supplementary Examination Aug-Sep- 2025 (All batches). Download 93.additional Time Table for VII Semester theory Supplementary /Reappear Examination Sep- 2025 Download 94.Additional Time Table for III Semester theory Supplementary /Reappear Examination Sep- 2025 Download 95.Additional Time Table for VII Semester B.E theory Supplementary Examination Aug/Sep- 2025 Download 96.Additional Time Table for VIII Semester B.E theory Supplementary Examination Aug/Sep- 2025 Download 97.Notifications for Summer Semester Examination Sep-2025.(2024 Batch) Download 98.Additional Time Table for I Semester theory Supplementary /Reappear Examination Sep- 2025 Download 99.Time Table for VIII Semester theory Supplementary Examination Aug-Sep- 2025. Download 100.Time Table for VII Semester theory Supplementary Examination Aug-Sep- 2025. Download 101.Time Table for IV Semester theory Supplementary /Makeup Examination Aug- Sep- 2025. Download 102.Time Table for III Semester theory Supplementary Examination Aug-Sep- 2025. Download 103.Revised I/II Semester Supplementary Time Table -Aug-2025. Download 104.Notifications for extension of reappear examination PG -MBA/MCA/M.Tech . Download 105.Time Table for I/II Semester B.E theory Makeup Examination Aug- 2025( 2024 batch). Download 106.Time Table for I/II Semester B.E theory Supplementary Examination Aug- 2025 (2022 &amp; 2023 batches). Download 107.Time Table for I/II Semester B.E theory Supplementary Examination Aug- 2025 (2021 batch). Download 108.Time Table for I/II Semester B.E theory Supplementary Examination Aug- 2025 (2016/2017/2018/2018/2020 batches). Download 109.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. II Semester July/Aug-2025 Semester End Examination. Download 110.Notifications for Supplementary Examination Aug-2025.(2023 and 2024 lateral entry Re-Appear) Download 111.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. IV, VI Semester July/Aug-2025 Semester End Examination. Download 112.Time Table for PG II theory Semester End Examination JULY/AUG- 2025 (Re-Registered). Download 113.Notifications for Supplementary Examination Aug-2025.(non-NEP batch) Download 114.Notifications for Supplementary Examination Aug-2025.(2021 and 2022 lateral entry) Download 115.Time Table for PG theory (M TECH)Semester End Examination JULY/AUG- 2025. Download 116.Time Table for PG theory (MCA)Semester End Examination JULY/AUG- 2025. Download 117.Time Table for PG theory (MBA)Semester End Examination JULY/AUG- 2025. Download 118.Time Table for VIII Semester B.E theory Semester End Examination JULY- 2025( Makeup Examination). Download 119.Time Table for Additional I/II Semester B.E theory Semester End Examination JULY- 2025 (2022 BATCH ONLY). Download 120.Time Table for IV Semester M Tech theory Semester End Examination July- 2025. Download 121.Revised Time Table for I/II Semester B.E theory Semester End Examination JULY- 2025.(Regular 2024 batch, 2023,2022 batch reappear &amp; Re-registration). Download 122.Revised Time Table for IV Semester MBA theory Semester End Examination JULY- 2025. Download 123.I/II SEMESTER Time Table for 2022,2023,2024 batch (Re reg and Re Appear) Download 124.I/II SEMESTER Time Table for 2021 batch (Re reg and Re Appear) Download 125.Notifications for reappear examination for UG (2024 Batch)-2025. Download 126.I/II SEMESTER Time Table for 2016 to 2020 batch (Re reg and Re Appear) Download 127.Additional Time Table for VI Semester B.E theory Semester End Examination May/June- 2025. Download 128.Notifications for reappear examination for UG-2025. Download 129.Additional Time Table for IV &amp; VI Semester B.E theory Semester End Examination May/June- 2025. Download 130.Revised Time Table -June-2025 Download 131.Revised Time Table -June-2025. (AEROSPACE ENGINEERING) Download 132.Circular for Fees and Regulations for Photocopy/Challenge Valuation of P.G. MBA, MCA, M.Tech I Semester May-2025 Semester End Examination. Download 133.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. VIII Semester JUNE-2025 Semester End Examination. Download 134.Revised Time Table -June-2025 (4TH,5TH,6TH AND 7TH SEMESTER) Download 135.Revised Time Table for VII Semester B.E. Theory Semester End Main Examination - June-2025 ( Re-Appear- 2021) Download 136.Revised Time Table for VI Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2022 batch, Re-Appear- 2021 batch &amp; NON NEP REREGISTRATION) Download 137.Revised Time Table for V Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear- 2022, 2021 batch) Download 138.Revised Time Table for IV Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2023 batch, Re-Appear- 2022, 2021 batch) Download 139.Revised Time Table for III Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear-2023, 2022, 2021 batch) Download 140.Time Table for VII Semester B.E. Theory Semester End Main Examination - June-2025 ( Re-Appear- 2021) Download 141.Time Table for VI Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2022 batch, Re-Appear- 2021 batch &amp; NON NEP RE-REGISTRATION) Download 142.Time Table for V Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear- 2022, 2021 batch) Download 143.Time Table for IV Semester B.E. Theory Semester End Main Examination - June-2025 (Regular-2023 batch, Re-Appear- 2022, 2021 batch) Download 144.Time Table for III Semester B.E. Theory Semester End Main Examination - June-2025 (Re-Appear-2023, 2022, 2021 batch) Download 145.Reschedule of Time Table for VIII Semester Semester End Examination May- 2025. Download 146.Notifications for reappear examination for UG-2025. Download 147.notification regarding Graduation day fee -2025. Download 148.Revised Time Table for VIII Semester B.E. theory Semester End Examination MAY- 2025. Download 149. Notification regarding the submission of applications for Annual Convocation-2024-2025. Download 150.Time Table for VIII Semester B.E. theory Semester End Examination MAY- 2025. Download 151.RE APPEAR Time Table for I Semester MCA, MBA, M.Tech theory Semester End Examination April- 2025. Download 152.Notification Answer Scripts disclosure of III Semester MBA/MCA/M.TECH Students SEE Examination April-2025 Download 153.1st semester Makeup Examinations Time table - APR-2025 Download 154.Circular for Fees and Regulations for Reappear Examination of I Semester P.G (MBA/MCA/M.TECH) Apr -2025. Download 155.Circular for Fees and Regulations for Makeup Examination of I Semester U.G Semester End Makeup Examinations Apr -2025. Download 156.Circular for Fees and Regulations for Photocopy/Revaluation/Challenge Valuation of I Semester U.G Semester End Examinations Feb/Mar -2025. Download 157.Time Table for P.G I Semester M Tech Semester End Examination Apr-2025 Download 158.Time Table for P.G I Semester MCA Semester End Examination Apr-2025 Download 159.Time Table for P.G I Semester MBA Semester End Examination Apr-2025 Download 160.Revised Time Table for VII Semester Makeup Examination - Mar/Apr-2025 Download 161.Revised Time Table for V Semester Makeup Examination - Mar/Apr-2025 Download 162. Revised Time Table for III Semester Makeup Examination - Mar/Apr-2025 Download 163.III SEM MBA REAPPEAR TIME TABLE -MAR-2025 Download 164.Time Table for III Semester Makeup Examinations Mar-2025 Download 165.Circular for Makeup Examination -mar-2025 Download 166.Time Table for V Semester Makeup Examinations -Mar-2025 Download 167.Time Table for III Semester MBA theory Semester End Examination March- 2025.. Download 168.Time Table for III Semester MCA theory Semester End Examination March- 2025. Download 169.Fee and Regulations for RV,CV,Photocopyfor III,V,VII Semester -jan-feb-2025 Download 170.Revised and additional Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025 (2022 reappear). Download 171.Notifications for PG -MBA/MCA. Download 172.Time Table for III Semester M.Tech theory Semester End Examination JAN/FEB- 2025. Download 173.Revised and additional Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan/Feb- 2025 (2021 &amp; 2022 batch only) Download 174.Revised and additional Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025 (2021 reappear). Download 175.Revised and additional Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025 (2022 reappear). Download 176.Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025.(2021 batch re-registration/ reappear) Download 177.Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025.(2016,2017,2018,2019,2020 batch re-registration) Download 178.Time Table for I/II Semester B.E theory Semester End Examination Feb- 2025.(Regular 2024 batch, 2023,2022 batch reappear) Download 179.Revised and additional Time Table for MBA Semester End MAKEUP Examination-OCT-2024 Download 180.Revised and additional Time Table for VI Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 batch &amp; non nep equivalent) Download 181.Revised and additional Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 &amp; 2022 batch only) Download 182.Revised and additional Time Table for III Semester B.E theory Semester End Examination Jan- 2025 (2023 batch regular, reappear 2021, 2022 batch and non NEP batch re-registration) Download 183.Revised and additional Time Table for V Semester B.E theory Semester End Examination Jan- 2025 ( 2022 batch regular, reappear 2021 &amp; non NEP rereg) Download 184.Revised and additional Time Table for VII Semester B.E theory Semester End Examination Jan- 2025 (2021 regular &amp; Non-NEP). Download 185.Circular for Fees and Regulations for Photocopy / Challenge Valuation of PG Supplementary Dec - 2024. Download 186.Revised Time Table for IV, IV and VIII Semester B.E theory Semester End Examination Jan- 2025 ( All Non-Nep batch only) Download 187.Revised Time Table for VI Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 batch &amp; non nep equivalent) Download 188.Revised Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 &amp; 2022 batch only) Download 189.Revised Time Table for III Semester B.E theory Semester End Examination Jan- 2025 (2023 batch regular, reappear 2021, 2022 batch and non nep batch re-registration) Download 190.Revised Time Table for V Semester B.E theory Semester End Examination Jan- 2025 ( 2022 batch regular, reappear 2021 &amp; non nep rereg) Download 191.Revised Time Table for VII Semester B.E theory Semester End Examination Jan- 2025 (2021 regular &amp; Non-Nep). Download 192.Time Table for IV, IV and VIII Semester B.E theory Semester End Examination Jan- 2025 ( All Non-Nep batch only) Download 193.Time Table for VI Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 batch &amp; non nep equivalent) Download 194.Time Table for IV Semester B.E theory Re-Appear Semester End Examination Jan- 2025 (2021 &amp; 2022 batch only) Download 195.Time Table for III Semester B.E theory Semester End Examination Jan- 2025 (2023 batch regular, reappear 2021, 2022 batch and non nep batch re-registration) Download 196.Time Table for V Semester B.E theory Semester End Examination Jan- 2025 ( 2022 batch regular, reappear 2021 &amp; non NEP rereg) Download 197.Time Table for VII Semester B.E theory Semester End Examination Jan- 2025 (2021 regular &amp; Non-Nep). Download 198.Circular for extended date of reappearing for the Ensuing Examination UG- (2021,2022,2023 Batch). Download 199.Rescheduling of M.Tech/MBA/MCA Examination reg. Download 200.Notifications for Reappearing for the Ensuing Examination UG- (2021,2022,2023 Batch). Download 201.Reschedule of Time Table for M.Tech Supplementary Examination December- 2024. Download 202.Revised Time Table for Supplementary Examination December- 2024 I,III Semester MCA: Supplementary Examination Dec-2024. Download 203.Revised Time Table for Supplementary Examination December- 2024 I,II,III and VI Semester MBA: Supplementary Examination Dec-2024. Download 204.Time Table for Supplementary Examination December- 2024 III &amp; VI Semester MCA : Supplementary Examination Dec-2024 Download 205.Revised Time Table for Supplementary Examination December- 2024 II and IV Semester M.Tech: Supplementary Examination Dec-2024. Download 206.Time Table for Supplementary Examination December- 2024 II &amp; IV Semester M.Tech: Supplementary Examination Dec-2024 Download 207.Time Table for Supplementary Examination December- 2024 I Semester M.Tech: Supplementary Examination Dec-2024 Download 208.Time Table for Supplementary Examination December- 2024 III &amp; VI Semester MBA : Supplementary Examination Dec-2024 Download 209.Time Table for Supplementary Examination December- 2024 II Semester MBA: Supplementary Examination Dec-2024 Download 210.Time Table for Supplementary Examination December- 2024 I Semester MBA: Supplementary Examination Dec-2024 Download 211.Time Table for Supplementary Examination December- 2024 III &amp; VI Semester MCA : Supplementary Examination Dec-2024 Download 212.Time Table for Supplementary Examination December- 2024 II Semester MCA: Supplementary Examination Dec-2024 Download 213.Time Table for Supplementary Examination December- 2024 I Semester MCA: Supplementary Examination Dec-2024 Download 214.Circular for Fees and Regulations for Photocopy / Challenge Valuation of II semester (PG) Exam Oct - 2024. Download 215.Notifications for Reappearing for the Ensuing Examination PG- MBA/MCA/M.Tech. Download 216.Circular for Fees and Regulations for Challenge Valuation of III to VIII semester of Evening Batch Supplementary Reappear Exam Oct - 2024. Download 217.Time Table for IV Semester M.Tech theory Reappear Examination Nov- 2024. Download 218.Circular for Fees and Regulations for Challenge Valuation of supplementary semester of U.G. 2024 Examination. Download 219.Additional Time Table for III Semester MCA theory Reappear Examination Oct- 2024. Download 220.Additional Time Table for I Semester M.Tech theory Reappear Examination Oct- 2024. Download 221.Circular for Fees and Regulations for Challenge Valuation of I and II semester of U.G. Oct -2024 Semester End Examination. Download 222.Time Table for I &amp; IV Semester M.Tech theory Reappear Examination Oct- 2024. Download 223.Time Table for III Semester Supplementary Examination Oct- 2024 (2022 batch). Download 224.Time Table for IV Semester Supplementary /Re-Appear/ Makeup Examination Oct- 2024 (2022 batch). Download 225.Time Table for III &amp; IV Semester MBA Re-Appear Examination Oct- 2024. Download 226.Time Table for I &amp; II Semester MCA Re-Appear Examination Oct- 2024. Download 227.Time Table for I Semester MBA Re-Appear Examination Oct- 2024. Download 228.Time Table for III &amp; IV Semester MCA Re-Appear Examination Oct- 2024. Download 229.Time Table for Re-Scheduling of I &amp; II Semester Supplementary-2022 batch. Download 230.Time Table for Re-Scheduling of II Semester M.Tech Examination Sep- 2024. Download 231.Additional Time Table for VII Semester theory Supplementary /Reappear Examination Sep- 2024.(Evening Batch) Download 232.Revised Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of IV semester of U.G. Sep -2024 Semester End Examination. Download 233.Time Table for II Semester MCA theory Semester End Examination (Regular &amp; Reappear) Download 234.Time Table for II Semester MBA theory Semester End Examination (Regular &amp; Reappear) Download 235.Time Table for II Semester M.Tech theory Semester End Examination (Regular &amp; Reappear) Download 236.Circular for Fees and Regulations for Challenge Valuation of I &amp; II semester (2023 Batch Supplementary reappear exam Sep -2024) Semester End Examination. Download 237.Notifications for Reappearing and Makeup for the Ensuing Examination UG-2022 batch. Download 238.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of IV semester of U.G. Sep -2024 Semester End Examination. Download 239.Time Table for Revised VI Semester theory Supplementary/Re-Appear/MAKEUP Examination Sep- 2024.(2021 BATCH) Download 240.Time Table for VII Semester theory Supplementary /Reappear Examination Sep- 2024.(Evening Batch) Download 241.Time Table for I &amp; II Semester theory Supplementary Examination Sep- 2024.(2022 BATCH) Download 242.Time Table for revised IV Semester B.E. Supplementary Examination Sep- 2024 (2021 batch). Download 243.Time Table for VI Semester theory Supplementary/ reappear/ Makeup Semester End Examination Sep- 2024.(2021 BATCH ) Download 244.Time Table for VII &amp; VIII Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 245.Time Table for VI Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 246.Time Table for V Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 247.Time Table for IV Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 248.Time Table for III Semester theory Supplementary/Re-Appear Examination Sep- 2024.(Evening Batch) Download 249.additional Time Table for V Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 250.Additional Time Table for III Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 251.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of Re-registered Exams (Evening Batch) of U.G. Aug/Sep -2024 Semester End Examination. Download 252.PG Notifications for Reappearing for the Ensuing Examination (PG). Download 253.Time Table for V Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 254.Time Table for IV Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 255.Time Table for III Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 256.Time Table for I &amp; II Semester theory Supplementary Examination Sep- 2024.(2021 BATCH) Download 257.Notifications and formats for Reappearing for the Ensuing Examination-2021 batch( UG). Download 258.Time Table for Reappear and Makeup Examinations - Sep-2024 (for 2023 Batch). Download 259.Time Table for I Semester MBA Makeup theory Examination Sep- 2024. Download 260.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of I &amp; II Semester (2023 batch &amp; 2022 batch reappear) of U.G. July/Aug -2024 Semester End Examination. Download 261.Notifications and formats for Reappearing for the Ensuing Examination( UG). Download 262.Time Table for additional /revised V Semester B.E. Supplementary/Reappear and III Semester Reappear (NEP) theory Examination Aug- 2024. Download 263.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of U.G. &amp; P.G. June/July -2024 Semester End Examination. Download 264.Time Table for III Semester theory Semester End Examination Aug- 2024.(2022 &amp; 2021 BATCH REAPPEAR) Download 265.Time Table for Additional /revised III Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non- Nep batch. Download 266.Time Table for Additional /revised VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non- Nep batch. Download 267.Time Table for I/II Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 268.Time Table for additional /revised VI Semester B.E. Supple</v>
+      </c>
+      <c r="D276">
+        <v>0</v>
+      </c>
+      <c r="E276" t="str">
+        <v>2026-03-19T18:37:58.992Z</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>http://bmsce.ac.in/home/COE-Notifications</v>
+      </c>
+      <c r="C277" t="str">
+        <v>mentary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non- NEP batch. Download 269.Time Table for V Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 270.Time Table for IV Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 271.Time Table for III Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 272.Rescheduling of Examination Aug-2024 for M.Tech IV Semester Civil stream. Download 273.Time Table for Additional /revised VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-NEP batch. Download 274.Time Table for Additional /revised VI Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-NEPbatch. Download 275.Additional/revised Time Table for VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 276.Additional/revised Time Table for VIII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 277.additional/revised Time Table for VI Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 Non-Nep batch. Download 278.Time Table for IV Semester B.E. theory Semester End Main Examination-Aug-2024 (2022 Batch Regular &amp; 2021 Batch Reappear) Download 279.Time Table for VI Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 batch (Non-Nep). Download 280.Time Table for VII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 batch (Non-Nep). Download 281.Time Table for Revised IV Semester M.Tech Semester End Main Examination-Aug-2024 Download 282.Time Table for VIII Semester B.E. Supplementary/Reappear theory Examination Aug- 2024 for 2016/2017/2018/2019/2020 batch. Download 283.Time Table for IV Semester PG (MBA) theory Semester End Examination Aug- 2024. Download 284.Time Table for IV Semester PG (M.Tech) theory Semester End Examination Aug- 2024. Download 285.Revised Time Table for I &amp; II Semester theory Semester End Examination July- 2024. Download 286.Circular regarding disclosure of answer Scripts of I Semester PG Students who have obtained 'F' Grade in the SEE Examination Download 287.Revised 2 Time Table for I-II Semester 2021 batch (Re-Appear &amp; Re-Registration) and I/II old scheme re-registration (non-nep) theory Semester End Examination Aug- 2024. Download 288.Time Table for V Semester (Re-Appear) theory Semester End Examination July- 2024. Download 289.Time Table for III, IV and VI Semester theory Semester End Examination (Evening) July- 2024. Download 290.Supplementary Exam Non NEP Batch notification. Download 291.Time Table for VIII Semester theory Semester End Examination July- 2024. Download 292.Reappearing for the Ensuing Examination( UG) 2021 BATCH Download 293.Reappearing for the Ensuing Examination( UG) 2022 BATCH Download 294.Reappearing for the Ensuing Examination( UG) 2023 BATCH Download 295.additional (makeup) and re registration Time Table for VI Semester B.E. theory Semester End Examination June- 2024. Download 296.Additional (makeup) and re registration Time Table for VIII B.E. theory Semester End Examination June- 2024. Download 297.Revised Time Table for VI Semester B.E. theory Semester End Examination June- 2024. Download 298.Time Table for VI Semester B.E. theory Semester End Examination June- 2024. Download 299.Tme Table for III Semester B.E theory Semester End Makeup Examination June- 2024. Download 300.Tme Table for VIII Semester B.E. theory Semester End Makeup Examination June- 2024. Download 301.Tme Table for VII Semester B.E theory Semester End makeup Examination (Second Phase) June- 2024. Download 302.Tme Table for III Semester MBA theory Semester End Makeup Examination June- 2024. Download 303.Revised Disclosure of Answer Scripts of III Semester PG Students who have obtained 'F' Grade in the SEE Examination. Download 304.Revised Time Table for I M.Tech theory Semester End Examination May- 2024. Download 305.Revised Time Table for II Semester MCA theory Semester End Examination May- 2024. Download 306.Revised Time Table for I Semester MBA theory Semester End Examination May- 2024. Download 307.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation for U.G and P G April- May -2024 Semester End Examination. Download 308.Disclosure of Answer Scripts of III Semester PG Students who have obtained 'F' Grade in the SEE Examination. Download 309.Revised Disclosure of Answer Scripts of III Semester UG Students who have obtained 'F' Grade in the SEE Examination. Download 310.Time Table for II Semester (Re appear) PG theory Semester End Examination (MCA) May- 2024. Download 311.Time Table for II Semester (Re appear) PG theory Semester End Examination (MBA) May- 2024. Download 312.Revised Time Table for I and II Semester PG theory Semester End Examination (MCA) May- 2024. Download 313.Revised Time Table for I Semester PG theory Semester End Examination (MBA) May- 2024. Download 314.Time Table for V Semester Re-Registered theory Semester End Examination May- 2024. Download 315.Time Table for I Semester PG theory Semester End Examination (M TECH) May- 2024. Download 316.Time Table for I Semester PG theory Semester End Examination (MCA) May- 2024. Download 317.Time Table for I Semester PG theory Semester End Examination (MBA) May- 2024. Download 318.Notification for Reappearing for the Ensuing Examination (PG -I &amp; II Semester). Download 319.Time Table for VIII Semester theory Semester End Examination May- 2024. Download 320.Makeup Examination Timetable for the 5th semester May-2024 . Download 321.3rd Semester Re registered Time table. Download 322.Makeup Examination Timetable for the 1st semester May-2024 . Download 323.Circular for the Semester End Makeup Examination for I, V Semester B.E April 2024. Download 324.Circular for Fees and Regulations for Revaluation/Photocopy/Challenge Valuation of I and V Semester U.G. March-April -2024 Semester End Examination. Download 325.Time Table for VII Semester B.E. theory Semester End Examination April- 2024. Download 326.III Semester M.Tech theory Semester End Examination April- 2024(Re-Appear). Download 327.III Semester M.Tech theory Semester End Examination April- 2024. Download 328. Revised VII Semester B.E. theory Semester End Makeup Examination April- 2024. Download 329. III Semester MCA theory Semester End Examination April- 2024 (Re-Appear). Download 330.III &amp; IV Semester MBA theory Semester End Examination April- 2024 (Re-Appear). Download 331.Revised IV Semester ( 2021 batch Re-Appear) B.E. theory Semester End Examination April- 2024. Download 332.Revised III Semester ( 2022 batch regular, 2021 batch Re-Appear and Re-Registration non-NEP batch) B.E. theory Semester End Examination April- 2024. Download 333.Time Table for VII Semester B.E. theory Semester End Makeup Examination April- 2024. Download 334.IV Semester ( 2021 batch Re-Appear) B.E. theory Semester End Examination April- 2024. Download 335.Time Table for III Semester ( 2022 batch regular, 2021 batch Re-Appear and Re-Registration non-NEP batch) Download 336.Time Table for III Semester MCA theory Semester End Examination March- 2024. Download 337.Time Table for III Semester MBA theory Semester End Examination March- 2024 Download 338.Notification for Reappearing for the Ensuing Examination (PG -III &amp; IV Semester) Download 339.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of VII Semester U.G Semester End Examination Jan-2024. Download 340.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of I/II/III and IV Semester (2021 batch) U.G. Supplementary Examination Dec-2023. Download 341.Revised Time Table for the I Semester (2022 batch &amp; 2023 batch) B.E. Theory Semester End Examination Feb/March- 2024. Download 342.Time Table I/II Semester Re-appear (2021 Batch), and the Re-Registered non-NEP batch B.E. Theory Semester End Examination Feb/March- 2024. Download 343.Notification for Reappearing for the Ensuing Examination (UG 2021 batch -III &amp; IV Semester). Download 344.Additional timetable for the V Semester Examination Feb/March-2024 Download 345.Circular Regarding rescheduling of V Semester B.E. Theory Semester End Examination Feb- 2024. Download 346.Time Table for V Semester B.E. Theory Semester End Examination Feb- 2024. Download 347.Notification for Reappearing for the Ensuing Examination (UG 2021 &amp; 2022 batch). Download 348.Circular for Fees and Regulations for Photocopy/Challenge Valuation of Supplementary Semester Examination for MBA/MCA/M.Tech Dec-2023. Download 349.Revised time table for VII Semester B.E. (CIVIL ENGINEERING) Theory Semester End Examination Jan- 2024. Download 350.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of I/II Semester 2022 batch B.E Semester End Examination Dec-2023. Download 351.Revised Time table for VII Semester B.E. Theory Semester End Examination Jan- 2024. Download 352.Additional Time table for VII Semester B.E. (Biotechnology)Theory Semester End Examination Jan- 2024. Download 353.Revised M.Tech timetable for Supplementary Examination Dec-2023. Download 354.Revised MCA timetable for Supplementary Examination Dec-2023 . Download 355.Revised MBA timetable for Supplementary Examination Dec-2023 . Download 356.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of IV Semester B.E Sep/Oct-2023 Semester End Examination and II semester PG Semester End Examination MBA/MCA/M.Tech Oct/Nov-2023. Download 357.Circular for Answer Scripts disclosure of M.Tech II Semester PG Students who have obtained 'F' Grade in the SEE Examination . Download 358.Circular for Answer Scripts disclosure of IV Semester UG Students who have obtained 'F' Grade in the SEE Examination . Download 359.Timetable for the B.E. (Evening College) Supplementary Examination Jan 2024 Download 360.Revised Timetable for the 5TH and 6TH SEMESTER B.E. (Evening College) Supplementary Examination Jan 2024. Download 361.Circular for Reappearing Examination December-2023 for 2021 batch Download 362.Time Table for I/II Semester (2022 scheme) B.E. Supplementary Examination Dec- 2023. Download 363.Revised notification for reappearing for ensuing examinations. Download 364.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of II Semester B.E Sep/Oct-2023 Semester End Examination. Download 365.Answer Scripts of II Semesters UG Students who have obtained 'F' Grade in the SEE Examination are open for disclosure from 27.11.2023 to 29.11.2023. Venue: P.G Block -IV Floor.-Room No.EE 4003 Download 366.Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of MBA IV Semester B.E Sep/Oct-2023 Semester End Examination. Download 367.Timetable for (Re-Registered) IV Semester B.E. Theory Semester End Examination Oct- 2023. Download 368.Timetable for (Re-Registered) III Semester MBA Theory Semester End Examination Oct- 2023. Download 369.Timetable for (Re-Registered) II Semester B.E. Theory Semester End Examination Oct- 2023. Download 370.Timetable for VI Semester B.E. Theory Semester End Examination Nov- 2023. Download 371.Revised Timetable for (Re-Registered) IV Semester B.E. Theory Semester End Examination Oct- 2023. Download 372.Time Table for the Rescheduling of the Examination for III Semester B.E. Theory Semester End Examination (Re-appear) Oct- 2023. Download 373.Time table for II Semester M TECH theory Semester End Examination Oct- 2023. Download 374.Time table for II Semester MCA theory Semester End Examination Oct- 2023. Download 375.Time table for II Semester MBA theory Semester End Examination Oct- 2023. Download 376.Circular Regarding Reschedule of Examination on 26th and 29th of September,14th and 19th of October . Download 377.Circular Regarding Reschedule of Examination on 26th of September. Download 378.ADDITIONAL (4)SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 379.Time Table for I/II Semester B.E Reappear (2021 Scheme) theory Semester End Examination Sep- 2023. Download 380.Time Table for III Semester B.E Reappear (2021 Scheme) theory Semester End Examination Sep- 2023. Download 381.Time Table for II Semester B.E and I Semester Reappear (2022 Scheme) theory Semester End Examination Sep- 2023. Download 382.ADDITIONAL (3)SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 383.ADDITIONAL (2)SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 384.Time Table for IV Semester UG (BE) theory SEMESTER END EXAMINATION SEP/OCT-2023. Download 385.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER /MAKEUP EXAMINATION FOR 5TH AND 6TH SEMESTER SEP 2023 Download 386.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of VI Semester B.E July-2023 Semester End Examination. Download 387.ADDITIONAL SUPPLEMENTARY EXAMINATION TIME TABLE FOR 1ST TO 8TH SEMESTER SEP 2023 Download 388.Answer Scripts of VI Semesters UG Students who have obtained 'F' Grade in the SEE Examination are open for disclosure -CIRCULAR Download 389.Notification for Reappearing for the Ensuing Examination. Download 390.Circular Regarding disclosure of Answer Scripts of VI Semester B.E Students who have obtained 'F' Grade in the SEE Examination July-2023 Download 391.Time Table for IV SEM Semester M.Tech theory SEE Aug-2023 Download 392.Time Table for Revised III Semester B.E theory Makeup Examination Aug-2023 Download 393.Time Table for Revised I Semester B.E theory Makeup Examination Aug-2023 Download 394.Circular for registration fees for SEE Makeup Exam B.E I, II &amp; VIII Semester &amp; I Semester MBA August 2023. Download 395.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of VIII Semester B.E July-2023 Semester End Examination. Download 396.Time Table for IV Semester MBA theory SEE Sep-2023 Download 397.CIRCULAR FOR VIII SEM - MAKE-UP CHALLENGE VALUATION Download 398.III SEMESTER BE (RE-REGISTRATION) Time Table- AUG-2023 Download 399.VIII SEMESTER BE MAKEUP Time Table- AUG-2023 Download 400.I SEM M TECH MAKEUP Time Table- AUG-2023 Download 401.I SEM MBA MAKEUP Time Table- AUG-2023 Download 402.CIRCULAR:The Answer Scripts of VIII Semesters UG Students who have obtained 'F' Grade in the SEE Examination July-2023 are open for disclosure Download 403.CIRCULAR:The Answer Scripts of I Semesters UG Students who have obtained 'F' Grade in the SEE Examination May/June-2023 are open for disclosure Download 404.CIRCULAR:The Answer Scripts of I Semesters PG Students who have obtained 'F' Grade in the SEE Examination May/June-2023 are open for disclosure Download 405.CIRCULAR:The Answer Scripts of III Semesters UG Students who have obtained 'F' Grade in the SEE Examination May/June-2023 are open for disclosure Download 406.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of I Sem and III Semester B.E May -2023 &amp; PG I Sem June-2023 Semester End Examination. Download 407.Time Table for III Semester Semester End Examination - May - 2023.. Download 408.Circular Regarding disclosure of Answer Scripts of V,VII Semester B.E Students who have obtained 'F' Grade in the SEE Examination March-2023 Download 409.Time Table for I and II Semester Semester End Examination (UG-Re appear and re-registration)- May - 2023.. Download 410.Time Table for I Semester Semester End Examination - May- 2023. Download 411.Circular for Fees and Regulations for RT/Photocopy/CV for 5th and 7th semester SEE Semester U.G Feb/March -2023. Download 412.Circular Reg-Rescheduling of Examination-MCA &amp; MBA Mar/April-2023. Download 413.III Semester MCA Time Table for Semester End Examination - March- 2023. Download 414.III Semester MBA Time Table for Semester End Examination - March- 2023. Download 415.Time Table for III and IV Semester Supplementary Examination - March- 2023. Download 416.M TECH Time Table for III Semester SEE - March-2023. Download 417.REVISED Time Table for VII Semester Semester End Examination - Feb/March- 2023. Download 418.REVISED Time Table for V Semester Semester End Examination - Feb/March- 2023. Download 419.Circular Regarding disclosure of Answer Scripts of IV Semester B.E Students who have obtained 'F' Grade in the SEE Examination Jan-2023 . Download 420.Circular Regarding Rescheduling of exam for SEE Examination Jan-2023 . Download 421.Revised Time Table for IV Semester B.E. Theory SEE Examination January- 2023. Download 422.Circular for Fees and Regulations for Challenge Valuation of Supplementary and SEE Semester U.G/P.G December Examinations-2022. Download 423.Circular Regarding Reappear of ensuing Examination . Download 424.M TECH Time Table for I,II and III Semester Supplementary Examination - Dec- 2022. Download 425.Time Table for IV Semester Supplementary/Makeup Examination - Dec- 2022.(ADDITIONAL) Download 426.MBA Time Table for II Semester Supplementary Examination - Dec- 2022. Download 427.MCA Time Table for I and II Semester Supplementary Examination - Dec- 2022. Download 428.Time Table for IV Semester Supplementary/Makeup Examination - Dec- 2022. Download 429.Time Table for III Semester Supplementary/Makeup Examination - Dec- 2022. Download 430.Revised Time Table for B.E. II Semester SEE Makeup Examination November- 2022. Download 431.Circular regarding disclosure of answer Scripts of II Semester M.Tech Students who have appeared in the SEE Examination Oct/Nov-2022 on 26.11.2022. Download 432.Revised IV Semester B.E Students who have obtained 'F' Grade in the SEE Examination Oct-2022 are open for disclosure from 22.11.2022 to 24.11.2022. Download 433.Revised II Semester B.E Students who have obtained 'F' Grade in the SEE Examination Oct-2022 are open for disclosure from 22.11.2022 to 24.11.2022. Download 434.Circular for Fees and Regulations for Re-totaling/Photocopy/Revaluation/Challenge Valuation of II Semester &amp; IV Semester U.G SEE October-2022. Download 435.Circular regarding Semester End Makeup Exam II &amp; IV Semester B.E. Nov/Dec-2022 Download 436.Time Table for I and II Semester Supplementary Examination - Dec- 2022. Download 437.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of M.B.A. &amp; M.C.A. II Semester SEE Examinations -Oct-2022. Download 438.Circular for Fees and Regulations for Re-totaling/Photocopy/Challenge Valuation of M.Tech I Semester SEE Examinations (21-22 ACY). Download 439.Circular Regarding Disclosure of answer scripts for 2nd Semester MBA &amp; MCA OCT 2022 SEE. Download 440.Circular for Fees and Regulations for Re-totaling/Photocopy/Revaluation/Challenge Valuation of VIII, VII, V Semester U.G Supplementary Examinations Sep/Oct-2022. Download 441.II Semester M.Tech Theory SEE Examination October/November- 2022 Download 442.8TH SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE OCT 2022.. Download 443.REVISED Time Table for II Semester MCA. SEE Examination - Oct- 2022. Download 444.Time Table for II Semester MBA SEE Examination - Oct- 2022. Download 445.Revised Time Table for IV Semester B.E. Theory SEE Examination October- 2022. Download 446.MBA Supplementary III and IV Semester Examination Time Table - Sep/Oct- 2022. Download 447.2ND SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) OCT 2022.. Download 448.Circular Regarding Disclosure of answer scripts for 6th semester BE (ALL BRANCHES) AUG 2022 SEE. Download 449.SUPPLEMENTARY EXAMINATION TIME TABLE FOR 2ND,3RD,5TH,7TH SEMESTER B ARCH SEP 2022.. Download 450.SUPPLEMENTARY EXAMINATION TIME TABLE FOR 3RD AND 5TH SEMESTER MCA SEP 2022.. Download 451.REVISED MBA MAKEUP EXAMINATION TIME TABLE FOR 1ST SEMESTER MBA SEP 2022.. Download 452.Notification regd: Reappear for ensuing examination Download 453.SUPPLEMENTARY EXAMINATION TIME TABLE FOR 6TH SEMESTER BE (ALL BRANCHES) SEP 2022.. Download 454.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 5TH SEMESTER BE (ALL BRANCHES) SEP 2022.. Download 455.REGISTRATION FEE FOR MBA MAKEUP EXAMINATION (1ST SEMESTER) SEP 2022.. Download 456.MBA MAKEUP EXAMINATION TIME TABLE FOR 1ST SEMESTER MBA SEP 2022.. Download 457.SEMESTER END EXAMINATION TIME TABLE FOR 3RD SEM BE SEP 2022.. Download 458.REVISED SEMESTER END EXAMINATION TIME TABLE FOR 3RD SEM BE SEP 2022.. Download 459.Time Table for II Semester MCA. SEE Examination - Oct- 2022. Download 460.Circular Regarding Disclosure of answer scripts for M TECH 1ST semester JUNE 2022 SEE. Download 461.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR MBA,MCA FOR 1ST SEM --SEE JUNE/JULY 2022 Download 462.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 8TH SEMESTER BE (ALL BRANCHES) AUGUST 2022.. Download 463.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 7TH SEMESTER BE (ALL BRANCHES) AUGUST 2022.. Download 464.Circular Regarding Disclosure of answer scripts for 1st semester MBA,MCA JUNE/JULY 2022 SEE. Download 465.SEMESTER END EXAMINATION TIME TABLE FOR 4TH MBA AUGUST 2022.. Download 466.SEMESTER END EXAMINATION TIME TABLE FOR 4TH B ARCH AUGUST 2022.. Download 467.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 8TH SEM --SEE JULY 2022 Download 468.6TH SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) AUGUST 2022.. REVISED Download 469.8TH SEMESTER MAKEUP EXAM TIME TABLE FOR BE (ALL BRANCHES) AUGUST 2022. Download 470.Circular Regarding Disclosure of Answer scripts for B.E VIII semester-July 2022 Download 471.Circular Regarding Disclosure of answer scripts for 1st semester M TECH(ALL BRANCHES) JUNE 2022 SEE. Download 472.Circular -FEE STRUCTURE SEMESTER END MAKEUP EXAMINATION FOR 1ST AND 3RD SEMESTER BE (all branches) --MAY/JUNE 2022 Download 473.SEMESTER END MAKEUP EXAMINATION TIME TABLE FOR 3RD SEMESTER BE (ALL BRANCHES) JULY 2022 Download 474.SEMESTER END MAKEUP EXAMINATION TIME TABLE FOR 1ST SEMESTER BE (ALL BRANCHES) JULY 2022 Download 475.SEMESTER END EXAMINATION TIME TABLE FOR 4TH SEMESTER M TECH AND 6TH SEMESTER MCA JULY 2022.. Download 476.8TH SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) JULY 2022.. Download 477.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 1ST SEM --SEE MAY 2022 Download 478.Circular Regarding DISCLOSURE OF ANSWER SCRIPTS FOR 1ST SEMESTER BE (all branches) SEE MAY 2022 Download 479.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 3rd SEM --SEE MAY 2022 Download 480.Circular -FEE AND REGULATION RV,CV,RT,PHOTOCOPY FOR BE (all branches) FOR 5TH AND 7TH SEM --SEE FEB/MARCH 2022 Download 481.Circular Regarding Disclosure of answer scripts for 5TH semester BE FEB/MARCH 2022 SEE. Download 482.Circular REGARDING REGISTRATION FOR SEMESTER END MAKEUP EXAMINATION FOR BE (all branches)5TH AND 7TH SEMESTER,PG (MBA 3RD SEM,MCA 3RD AND 5TH SEMESTER) --FEB/MARCH 2022 Download 483.Circular Regarding Disclosure of answer scripts for MBA 3RD SEM ,MCA 3RD AND 5TH semester FEB/MARCH 2022 SEE. Download 484.Circular Regarding Disclosure of answer scripts for 7th semester BE FEB/MARCH 2022 SEE. Download 485.Notification regarding Registration for grade improvement exam with registration form.(BOTH UG AND PG) Download 486.REVISED SUPPLEMENTARY EXAMINATION TIME TABLE FOR 3RD AND 5TH SEMESTER MCA SEP 2022.. Download 487.REVISED 2ND SEMESTER TIME TABLE FOR SEMESTER END EXAMINATION BE (ALL BRANCHES) (OLD SCHEME) SEP/OCT 2022.. Download 488.SEE Time Table for MCA 1st semester - June- 2023. Download 489.SEE Time Table for MBA 1st semester - June- 2023. Download 490.SEE Time Table for M TECH 1st semester (ALL BRANCH)0- June- 2023. Download 491.ADDITIONAL Time Table for VI Semester Semester End Examination - July- 2023. Download 492.ADDITIONAL Time Table for VIII Semester Semester End Examination - July- 2023. Download 493.Revised Time Table for VI Semester Semester End Examination - July- 2023. Download 494.Revised Time Table for VIII Semester Semester End Examination - July- 2023. Download 495.Time Table for 5th Semester Semester End Examination - July- 2023. Download 496.Circular Regd RESCHEDULED of Time Table for III Semester (due to overlapping) Semester End Examination - May - 2023.. Download 497.Circular Regarding disclosure of Answer Scripts of III Semester MBA,MCA Students who have obtained 'F' Grade in the SEE Examination March-2023 Download 498.Circular for Fees and Regulations for RT/Photocopy/CV for MBA,MCA SEE P.G Feb/March -2023. Download 499.Circular for Fees and Regulations for RT/Photocopy/CV for 3rd and 4th supplementary semester SEE Semester U.G Feb/March -2023. Download 500.Time Table for 5th Semester makeup Examination - May- 2023. Download 501.Time Table for 7th Semester makeup Examination - May- 2023. Download 502.Time Table for MBA 3rd semester makeup Examination - May- 2023. Download 503.Circular regarding 23rd annual Convocation Download 504.Circular regarding registration for 5th,7th semester UG &amp; 3rd semester MBA SEE Makeup Exam-2023 Download</v>
+      </c>
+      <c r="D277">
+        <v>1</v>
+      </c>
+      <c r="E277" t="str">
+        <v>2026-03-19T18:37:58.992Z</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>https://bmsce.ac.in/notifications/Revised_tt_rotated.pdf</v>
+      </c>
+      <c r="B278" t="str">
+        <v>html</v>
+      </c>
+      <c r="C278" t="str">
+        <v>404 Not Found. The requested page url was not found in BMSCE Website. GO BACK TO HOME PAGE</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278" t="str">
+        <v>2026-03-19T18:37:59.905Z</v>
+      </c>
+      <c r="F278">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>https://bmsce.ac.in/notifications/VII_sem_makeup_TT_rotated.pdf</v>
+      </c>
+      <c r="B279" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C279" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BENGALURU-560 019 VIISEMESTER B.E. THEORY SEMESTER END MAKEUP EXAMINATION -FEB-2026 Date &amp; Day 11-02-2026 Wednesday Controller of Examinatio CONTROLLER OF EXAMINATIONS B.M.S. College of Engineering Bengaluru-560 019 MAKEUP EXAMINATION TIME TABLE Computer Science Engineering Course Code 23CSTPCNWP 9.30amn to 12.30 pm Course Title Network Programming DATE : 03.02.2026 Principal Princißal B.M.S. College of Engineering Bengaluru-560 019</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279" t="str">
+        <v>2026-03-19T18:38:00.514Z</v>
+      </c>
+      <c r="F279">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>https://bmsce.ac.in/notifications/V_sem_makeup_TT.pdf</v>
+      </c>
+      <c r="B280" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Date &amp; Day l1-02-2026 Wedncsday Date &amp; Day 11-02-2026 Wednesday 12-02-2026 Thursday Friday 14-02-2026 Saturday Date &amp; Day l1-02-2026 Wednesday Date &amp; Day 13-02-2026 23ISSPCCN1 Monday 11-02-2026 Wednesday Thursday Course Code 23MESPCMEV Friday 14-02-2026 Course Code 09-02-2026 23BSSAEBRM Saturday 23ISSAERML 16-02-2026 Monday 23ISSPCCNS Course Code 23DSSPCDLG 12-02-2026 23BSSPCERP Course Code 13-02-2026 23BSSPCJAP 23BSSPCCON 25CSSPEPSI 23BSSPCSEM B.M.S. COLLEGE OF ENGINEERING, BENGALURU-560 019 V SEMESTER B.E. THEORY SEMESTER END MAKEUP EXAMINATION - FEB - 2026 MAKEUP EXAMINATION TIME TABLE (for X and IGrade Awarded Students only ) Mechanical Engineering Session : 9.30 am to 12.30 pm Course Title Mechanical Vibrations Information Science and Engincering Session :9.30 am to 12.30 pm Rescarch Methodology Computer Networks-1 |Cryptography and Network Security (Autonomous Institute, Afliated to VTU) Deep Leaming Computer Science - Data Science Session:9.30 am to 12.30 pm |Computer Networks Course Title Computer Science and Business Systems Session:9.30 am to 12.30 pm Course Title Business Research Methods Java Programming Enterprise Resource Planning with AI Course Title Controller of Examinations Product, Services and It Service Management CONTROLLER OF EXAMINATIONS B.M.S. College of Engineering BengaluruU-560 019 Software Engineering And Methodologies Course Code l23CHSPCMT2 Course Code 23ECSPCDCT 23ECSPCDSP 23ECSPCFOV 23ECSPEIAD 23ECSPCMTA Course Code |24AM5PCDEL Chemical Engincering DATE: 03.02.2026 Session : 9.30 am to 12.30 pm Course Title Mass Transfer - II Electronics and Communication Engineering Session :9.30 am to 12.30 pm Course Title Digital Communication Theory |Digital Signal Processing Fundamentals of VLSI Advanced Digital Logic Design Microwave Theory and Antenna Al and Machine Learning Session :9.30 am to 12.30 pm Course Title Deep Learning Principal Principal B.M.S. College of Engineering Bengaluru-560 019</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280" t="str">
+        <v>2026-03-19T18:38:01.102Z</v>
+      </c>
+      <c r="F280">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>https://bmsce.ac.in/notifications/Revised_VI_sem_TT.pdf</v>
+      </c>
+      <c r="B281" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C281" t="str">
+        <v>B.M.S.COLLEGE OF ENGINEERING, BENGALURU-560 019 REVISED: VISEMESTER B.E. THEORY SEMESTER END EXAMINATION JAN-FEB-2026 TIME TABLE Due to overlap with other examinations the below course is reschedulded as follows: Civil Engineering- VI Sem. Scheduleded Date &amp; Day 12-02-2026 Thursday Controller of Examinations Re-Scheduleded Date &amp; Day 16-02-2026 Astonemous Institnte, AMlsted to VIU Monday QecONTROLLER OF EXAMINATICA/AR B.M.S. College of Engineering Bengaluru-560 019 Course Code 20CV6PCDSS 09.30 AM TO 12.30 PM Course Title Structural Elements Software Application Lab DATE: 04.02.2026 Principal Principal B.M.S.College of Engineering Bengaluru-560019</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281" t="str">
+        <v>2026-03-19T18:38:01.678Z</v>
+      </c>
+      <c r="F281">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>https://bmsce.ac.in/notifications/Adobe_Scan_Nov_10,_2025.pdf</v>
+      </c>
+      <c r="B282" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Si. BMSCE/COE/2024-25/ Reappear exam-2025 B.M.S. COLLEGE OF ENGINEERING, BANGALORE- 560 019 (Autonomous Institute, Afiliated toVTU) No. Fees and regulations for Photocopy / Challenge Valuation of PG Iand II semester P.G Re-appear Oct-2025. (2024 Admitted batch only) 2 Name of the Items 1 Photocopy of Answer Script CIRCULAR Challenge Valuation of Answer Script* Rs.6,000/- (per course) Last Date With fine of Rs. 1000/- (per application) 16. 11.2025 Rs.850/- (per course) Fees in Rs. 10.11.2025 at BMSCE student's campus portal. issued in the case of irrelevant applications." * 50% fees will be refunded in case of change in grade in Challenge Valuation. Online Application for Photocopy/ Challenge Valuation of answer script will be opened from No Photocopy Challenge Valuation will be entertained after deadline. Date: 10. 11.2025 (https:/campuspay.bmsce.in/) (Scan QR Code for application link) No refunds will be issued under any circum stance Controller of Examinations CONTROLLER OF EXAMINATIONS The application must be submitted through online only and "No refund will be B.M.S. College of Engineering Bengaluru-560 019 Important Dates 10.11.2025 to 13.11.2025 10.1k.2025 to 15.11.2025 Important: Please ensure the hard copy of the receipt is submitted to the concerned departments without fail. Principal Principal B.M.S. College of Engineering Bengaluru-560 019 Page 2 of 2</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282" t="str">
+        <v>2026-03-19T18:38:04.756Z</v>
+      </c>
+      <c r="F282">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>https://bmsce.ac.in/notifications/add-TT_V_SEM-SUPPLE-25_rotated.pdf</v>
+      </c>
+      <c r="B283" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Scheduled Date &amp; Day 23-09-2025 Tuesday Scheduled Date &amp; Day 23-09-2025 Tuesday Scheduled Date &amp; Day 25-09-2025 Thursday 19l9l25 Revised /Additional : V SEMESTER B.E, THEORY SUPPLEMENTARY EXAMINATION- AUGISEP- 2025 B.M.S.College of Engineering Bengaluru-560019 Re-Scheduled Date &amp; Day B.M.S. COLLEGE OF ENGINEERING, BENGALURU-560 019 26-09-2025 Friday Re-Scheduled Date &amp; Day NA Re-Scheduled Date &amp; Day NA TIME TABLE Course Code 23AM5PCIML 22AM5PCIML Course Code 20CS5PCUSP Computer Science and Engineering -V Sem. Machine Learning -V Sem. 9.30 amn to 12.30pm Course Code 221S5PCSEO / 201S5PCSEO Course Title Introduction to Machine Learning Introduction to Machine Learning DATE : 19-09-2025 2.00 pm to 5.00 pm Information Science and Engineering -V Sem. Course Title Unix Shell and System Programming 2.00 pm to 5.00 pm Course Title |Software Engineering &amp; |ObjectOriented Modeling Design Principal Principal B.M.S.College of tnsiage Bengaluru-560 1</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283" t="str">
+        <v>2026-03-19T18:38:05.819Z</v>
+      </c>
+      <c r="F283">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>https://bmsce.ac.in/notifications/Adobe_Scan_Aug_14,_2025_(1).pdf</v>
+      </c>
+      <c r="B284" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C284" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE- 560 019 BMSCE/COE/2024-25/E-RV/CV/ S1. No. 3 (Autonomous Institute, Affiliated to VTU) Fees and regulations for Revaluation/ Re-totaling/ Photocopy /Challenge Valuation of Isemester U.G Semester End Examination and Reappear Examinations Jul/Aug -2025. Name of the Items Photocopy of Answer Script CIRCULAR Revaluation of Answer Script* Challenge Valuation of Answer Scriptt* Rs. 6,000- (per course) Fees in Rs. Last Date With fine of Rs. 1000/- (per application) 20.08.2025 Rs.850/- (per course) Rs.1,000/- (per course) Note only challenge valuation is applicable for the mentioned course: Controller of Pxamina CONTROLLER OF Date: 14.08.2025 B.M.S. College of Engineering Bengaluru-560 019 *Out of 1,000/-, Rs. 500/- will be refunded to the student if the marks improve by more than 15% of the Maximum marks, provided a student pass in the subject. Important Dates ** 50% fees will be refunded in case of change in grade in Challenge Valuation. 14.08.2025 to 16.08.2025 Online Application for re-totaling/revaluation/photocopy/Challenge Valuation of answer script will be opened from 14.08.2025 at BMSCE student's campus portal. The application must be submitted through online only. (https://campuspay.bmsce.in/) (Scan QR Code for application link) 14.08.2025 to 19.08.2025 NoPhotocopy /Revaluation/Challenge Valuation will be entertained after deadline. 14.08.2025 to 19.08.2025 22ME1ESCED: Computer Engineering Drawing Aided Principal Principal B.M.S.College of Engineeriny Bengaluru-560 019 Page 1 of 1</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284" t="str">
+        <v>2026-03-19T18:38:07.747Z</v>
+      </c>
+      <c r="F284">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>https://bmsce.ac.in/notifications/RESCHEDULE.pdf</v>
+      </c>
+      <c r="B285" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Dear Sir/Madam, This is to inform you that the reappear exam scheduled on 27.12.2024 has been postponed in view of Government Order No. DPAR/40/HHL/2024 dated 26.12.2024, declaring a holiday as a mark of respect to the departed soul of our former Prime Minister Dr. Manmohan Singh ji. The revised schedule for the exam(M.Tech/MBA/MCA) is as follows: Scheduled Date Rescheduled Date 27.12.2024 30.12.2024 HODs are hereby requested to bring this to the notice of all the faculty, staff and students. With best wishes... Dr. Ravikumar L. Ph.D. (IIT - KGP). Vice Principal (Academic) Professor, Dept. of Mechanical Engineering BMS College of Engineering Bengaluru - 560 019.</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285" t="str">
+        <v>2026-03-19T18:38:11.554Z</v>
+      </c>
+      <c r="F285">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>https://bmsce.ac.in/notifications/Reappear-UG-2025.pdf</v>
+      </c>
+      <c r="B286" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Ref: BMSCE/COE/S-Exam /24-25/001 B.M.S COLLEGEOF ENGINEERING S1. No. Note: Äutonomous Institute Affiliated to VTU All the Head of the Departments are requested to submit the list of students, those who are wish to re-appear for the Reappear examination starting from JAN-2025 for Failed (F Grade) Courses in Ito VISemester. (UG 2021,2022,2023 Batches only). Eligible Students can apply for the Re-appear Jan-2025 Examination (The students are here by informed to submit the application on or before 31.12.2024 (Without fine) &amp; with fine up to 02.01.2025 (Fine of Rs.250/-per course) &gt; HoD's are requested to Submit final list of students on or before: 04.01.2025. 3. Sub: Reappear Examination for UG - JAN-2025-reg. Program Notification UG- B.E (2021,2022,2023 Batch) (Hard copy) 1. Students can apply any number of courses with F" Grade. Semester Date: 24.12.2024 Ito VI Semester (F-Grade only) 2. Students must apply in the prescribed format of application published herewith. 5. Fee once paid will not be refunded. 4. No further extension will be provided. Fee. Rs.1000/- per course, (With fine Rs. 1250/- per course) Submit the applications to respective Departments on or before last date. Controler of Examinations CONTROLLER OF EXAMINATIONS B.M.S.College of Engineering Bengaluru-560 019 6. No Transitional Grades will be awarded for this Examination (X or IGrade) 7. The student should ensure that they have satisfied Attendance (Minimum 85%) and CIE (Minimum) and other Eligibility Requirements as per regulations. 8. Students awarded NE"Grade are not eligible for the above examination. the Head of the Departments are requested to bring the contents of this circular to the notice of all concerned. Principal, Pincipa! B.M.S. Coliege of Engineering Bengalurü-560 019</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286" t="str">
+        <v>2026-03-19T18:38:12.105Z</v>
+      </c>
+      <c r="F286">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>https://bmsce.ac.in/notifications/III_VI_SEM_MCA_SUPPLE-2024.pdf</v>
+      </c>
+      <c r="B287" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C287" t="str">
+        <v>III &amp; VI SEMESTER Date &amp; Day 16.12.2024 Monday 17.12.2024 B.M.S. COLLEGE OR ENGINEERING, BENGALURU-560 019 Tuesday (Autonomous Institute, Affiliated to VTU) MCA : SUPPLEMENTARY EXAMINATION DECEMBER -2024 Course Code 22MCA3PCMA |22MCA3PESC |22MCA3PCCC 18MCA6HSPR 18.12.2024 22MCA3HSES Wednesday 18MCA3PCNW CONTROLLER OF EXAMINATIONS CONTRCLLER DF EXAMINATIO:S BMS Col!ege of Engineering Bengaluru-500 0139. TIME TABLE Master of Computer Applications 2.00pm to 5.00 pm Mobile Application Development Soft Computing Cloud Computing Cyber Regulation &amp;IPR Entrepreneurship and IPR Computer Networks Course Title DATE: 10.12.2024 SINCIPAL RIMS College of Engineeiy Bengaluru-19</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287" t="str">
+        <v>2026-03-19T18:38:12.843Z</v>
+      </c>
+      <c r="F287">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>https://bmsce.ac.in/notifications/circular_challenge_valuation.pdf</v>
+      </c>
+      <c r="B288" t="str">
+        <v>pdf</v>
+      </c>
+      <c r="C288" t="str">
+        <v>B.M.S. COLLEGE OF ENGINEERING, BANGALORE- 560019 (Äutonomous Institute, Affiliated to VTU BMSCE/COE/SEE/2023-24/ Batches. Fees and regulations for Challenge Valuation of I &amp; VIII Sem of Non NEP Batch Supplementary Reappear Exam AUG/SEP-2024) -2016,2017,2018,2019,2020 S1. No. Name of the Items Challenge Valuation of Answer Script CIRCULAR &gt; The application must be submitted through online only. Fees in Rs. &gt; 50% fees will be refunded in case of change in grade in Challenge Valuation. 6,000/- (per Course) &gt; Online Application for Challenge Valuation of answer script will be opened from 94.11.2024 at Student campus portal and https://reval.bmsce.in. Controller SNov 204 &gt; Last date for submission of application forms for Challenge Valuation is on or before 07.11.2024. (Without fine). &gt; With fine 08.11.2024 to 10.11.2024 (With fine Rs. 200/- Per dav) Date: 16.10.2024 Examinations CONTROLLER OF EXAMINATIONS Last Date 2BS Collcge of Enginaering Bengaluru-560 019. other than the &gt; application received examinations the application will be rejected without any reason, and no refund will be issued. last date of application. 07.11.2024 &gt; Note: Thereafter no Challenge Valuation will be entertained after above-mentioned Principal Principal DMSCoHtege cf Eng.neor, Bangaluru-i9</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288" t="str">
+        <v>2026-03-19T18:38:14.016Z</v>
+      </c>
+      <c r="F288">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>https://bmsce.ac.in/notifications/I_II_SEM_SUPPLE-2022_BATCH_RESCHEDULE.pdf</v>
+      </c>
+      <c r="B289" t="str">
+        <v>html</v>
+      </c>
+      <c r="C289" t="str">
+        <v>404 Not Found. The requested page url was not found in BMSCE Website. GO BACK TO HOME PAGE</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289" t="str">
+        <v>2026-03-19T18:38:15.063Z</v>
+      </c>
+      <c r="F289">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>https://bmsce.ac.in/notifications/Notification-Non-nep_batch.pdf</v>
+      </c>
+      <c r="B290" t="str">
+        <v>html</v>
+      </c>
+      <c r="C290" t="str">
+        <v>404 Not Found. The requested page url was not found in BMSCE Website. GO BACK TO HOME PAGE</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290" t="str">
+        <v>2026-03-19T18:38:17.505Z</v>
+      </c>
+      <c r="F290">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F290"/>
   </ignoredErrors>
 </worksheet>
 </file>